--- a/GBDS AUGUST FILES 2026/INVENTORY COUNT SHEET - AUGUST 2026.xlsx
+++ b/GBDS AUGUST FILES 2026/INVENTORY COUNT SHEET - AUGUST 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS AUGUST FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B53221E-8ED5-45C6-8ACA-A511A93EA64A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28D3A955-1D33-4EDC-81D2-073AF1DB8406}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="5" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
   </bookViews>
   <sheets>
     <sheet name="SAMPLE" sheetId="32" r:id="rId1"/>
@@ -17675,34 +17675,45 @@
       <c r="B7" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="52"/>
+      <c r="C7" s="52">
+        <f>32</f>
+        <v>32</v>
+      </c>
       <c r="D7" s="52"/>
       <c r="E7" s="52"/>
       <c r="F7" s="52"/>
       <c r="G7" s="52"/>
       <c r="H7" s="52"/>
-      <c r="I7" s="52"/>
+      <c r="I7" s="52">
+        <v>3</v>
+      </c>
       <c r="J7" s="53"/>
-      <c r="K7" s="54"/>
+      <c r="K7" s="54">
+        <v>6</v>
+      </c>
       <c r="L7" s="55"/>
       <c r="M7" s="56"/>
       <c r="N7" s="57"/>
-      <c r="O7" s="52"/>
+      <c r="O7" s="52">
+        <v>1</v>
+      </c>
       <c r="P7" s="53"/>
-      <c r="Q7" s="53"/>
+      <c r="Q7" s="53">
+        <v>1</v>
+      </c>
       <c r="R7" s="54"/>
       <c r="S7" s="55"/>
       <c r="T7" s="58">
         <f>H7+I7+J7+K7+N7+P7+R7</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="U7" s="58">
         <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
-        <v>0</v>
+        <v>825</v>
       </c>
       <c r="V7" s="58">
         <f>U7/24</f>
-        <v>0</v>
+        <v>34.375</v>
       </c>
       <c r="W7" s="50"/>
       <c r="AF7" s="12"/>
@@ -17737,7 +17748,10 @@
       <c r="B8" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="59"/>
+      <c r="C8" s="59">
+        <f>41+43</f>
+        <v>84</v>
+      </c>
       <c r="D8" s="59"/>
       <c r="E8" s="59"/>
       <c r="F8" s="59"/>
@@ -17747,24 +17761,32 @@
       <c r="J8" s="60"/>
       <c r="K8" s="61"/>
       <c r="L8" s="62"/>
-      <c r="M8" s="63"/>
+      <c r="M8" s="63">
+        <v>1</v>
+      </c>
       <c r="N8" s="64"/>
-      <c r="O8" s="65"/>
-      <c r="P8" s="66"/>
-      <c r="Q8" s="66"/>
+      <c r="O8" s="65">
+        <v>1</v>
+      </c>
+      <c r="P8" s="66">
+        <v>12</v>
+      </c>
+      <c r="Q8" s="66">
+        <v>1</v>
+      </c>
       <c r="R8" s="67"/>
       <c r="S8" s="62"/>
       <c r="T8" s="68">
         <f t="shared" ref="T8:T41" si="0">H8+I8+J8+K8+N8+P8+R8</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="U8" s="69">
         <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="V8" s="69">
         <f>U8/24</f>
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="W8" s="50"/>
       <c r="AF8" s="12"/>
@@ -17799,7 +17821,10 @@
       <c r="B9" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="70"/>
+      <c r="C9" s="70">
+        <f>62+30</f>
+        <v>92</v>
+      </c>
       <c r="D9" s="70"/>
       <c r="E9" s="70"/>
       <c r="F9" s="70"/>
@@ -17813,7 +17838,9 @@
       <c r="N9" s="74"/>
       <c r="O9" s="70"/>
       <c r="P9" s="71"/>
-      <c r="Q9" s="71"/>
+      <c r="Q9" s="71">
+        <v>1</v>
+      </c>
       <c r="R9" s="72"/>
       <c r="S9" s="55"/>
       <c r="T9" s="75">
@@ -17822,11 +17849,11 @@
       </c>
       <c r="U9" s="76">
         <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
-        <v>0</v>
+        <v>2232</v>
       </c>
       <c r="V9" s="76">
         <f t="shared" ref="V9:V11" si="3">U9/24</f>
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="W9" s="50"/>
       <c r="AF9" s="12"/>
@@ -17861,7 +17888,10 @@
       <c r="B10" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="C10" s="70"/>
+      <c r="C10" s="70">
+        <f>36+10</f>
+        <v>46</v>
+      </c>
       <c r="D10" s="70"/>
       <c r="E10" s="70"/>
       <c r="F10" s="70"/>
@@ -17875,7 +17905,9 @@
       <c r="N10" s="74"/>
       <c r="O10" s="70"/>
       <c r="P10" s="71"/>
-      <c r="Q10" s="71"/>
+      <c r="Q10" s="71">
+        <v>1</v>
+      </c>
       <c r="R10" s="72"/>
       <c r="S10" s="55"/>
       <c r="T10" s="58">
@@ -17884,11 +17916,11 @@
       </c>
       <c r="U10" s="58">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1128</v>
       </c>
       <c r="V10" s="58">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="W10" s="50"/>
       <c r="AF10" s="12"/>
@@ -17923,7 +17955,9 @@
       <c r="B11" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="70"/>
+      <c r="C11" s="70">
+        <v>9</v>
+      </c>
       <c r="D11" s="70"/>
       <c r="E11" s="70"/>
       <c r="F11" s="70"/>
@@ -17931,7 +17965,9 @@
       <c r="H11" s="70"/>
       <c r="I11" s="70"/>
       <c r="J11" s="71"/>
-      <c r="K11" s="72"/>
+      <c r="K11" s="72">
+        <v>2</v>
+      </c>
       <c r="L11" s="55"/>
       <c r="M11" s="73"/>
       <c r="N11" s="74"/>
@@ -17942,15 +17978,15 @@
       <c r="S11" s="55"/>
       <c r="T11" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U11" s="58">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="V11" s="58">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>9.0833333333333339</v>
       </c>
       <c r="AF11" s="12"/>
       <c r="AG11" s="12"/>
@@ -17983,7 +18019,10 @@
       <c r="B12" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="59"/>
+      <c r="C12" s="59">
+        <f>1224+53+1080+8+1080+29</f>
+        <v>3474</v>
+      </c>
       <c r="D12" s="59"/>
       <c r="E12" s="59"/>
       <c r="F12" s="59"/>
@@ -17993,24 +18032,34 @@
       <c r="J12" s="60"/>
       <c r="K12" s="61"/>
       <c r="L12" s="62"/>
-      <c r="M12" s="63"/>
+      <c r="M12" s="63">
+        <v>8</v>
+      </c>
       <c r="N12" s="64"/>
-      <c r="O12" s="65"/>
-      <c r="P12" s="66"/>
-      <c r="Q12" s="66"/>
-      <c r="R12" s="67"/>
+      <c r="O12" s="65">
+        <v>10</v>
+      </c>
+      <c r="P12" s="66">
+        <v>5</v>
+      </c>
+      <c r="Q12" s="66">
+        <v>16</v>
+      </c>
+      <c r="R12" s="67">
+        <v>12</v>
+      </c>
       <c r="S12" s="62"/>
       <c r="T12" s="69">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="U12" s="69">
         <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
-        <v>0</v>
+        <v>84209</v>
       </c>
       <c r="V12" s="69">
         <f>U12/24</f>
-        <v>0</v>
+        <v>3508.7083333333335</v>
       </c>
       <c r="W12" s="9"/>
       <c r="X12" s="9"/>
@@ -18052,12 +18101,16 @@
       <c r="B13" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="70"/>
+      <c r="C13" s="70">
+        <v>2</v>
+      </c>
       <c r="D13" s="70"/>
       <c r="E13" s="70"/>
       <c r="F13" s="70"/>
       <c r="G13" s="70"/>
-      <c r="H13" s="70"/>
+      <c r="H13" s="70">
+        <v>16</v>
+      </c>
       <c r="I13" s="70"/>
       <c r="J13" s="71"/>
       <c r="K13" s="72"/>
@@ -18071,15 +18124,15 @@
       <c r="S13" s="55"/>
       <c r="T13" s="76">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="U13" s="76">
         <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="V13" s="76">
         <f>U13/24</f>
-        <v>0</v>
+        <v>2.6666666666666665</v>
       </c>
       <c r="AF13" s="12"/>
       <c r="AG13" s="12"/>
@@ -18113,7 +18166,9 @@
       <c r="B14" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="70"/>
+      <c r="C14" s="70">
+        <v>2</v>
+      </c>
       <c r="D14" s="70"/>
       <c r="E14" s="70"/>
       <c r="F14" s="70"/>
@@ -18136,11 +18191,11 @@
       </c>
       <c r="U14" s="75">
         <f t="shared" ref="U14:U36" si="4">C14*24+M14*24+O14*24+Q14*24+T14</f>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V14" s="75">
         <f t="shared" ref="V14:V36" si="5">U14/24</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF14" s="12"/>
       <c r="AG14" s="12"/>
@@ -18301,7 +18356,10 @@
       <c r="E17" s="70"/>
       <c r="F17" s="70"/>
       <c r="G17" s="70"/>
-      <c r="H17" s="70"/>
+      <c r="H17" s="70">
+        <f>24*3</f>
+        <v>72</v>
+      </c>
       <c r="I17" s="70"/>
       <c r="J17" s="71"/>
       <c r="K17" s="72"/>
@@ -18315,15 +18373,15 @@
       <c r="S17" s="55"/>
       <c r="T17" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="U17" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="V17" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF17" s="12"/>
       <c r="AG17" s="12"/>
@@ -18417,12 +18475,17 @@
       <c r="B19" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="C19" s="70"/>
+      <c r="C19" s="70">
+        <v>2</v>
+      </c>
       <c r="D19" s="70"/>
       <c r="E19" s="70"/>
       <c r="F19" s="70"/>
       <c r="G19" s="70"/>
-      <c r="H19" s="70"/>
+      <c r="H19" s="70">
+        <f>24+20</f>
+        <v>44</v>
+      </c>
       <c r="I19" s="70"/>
       <c r="J19" s="71"/>
       <c r="K19" s="72"/>
@@ -18436,15 +18499,15 @@
       <c r="S19" s="55"/>
       <c r="T19" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="U19" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="V19" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3.8333333333333335</v>
       </c>
       <c r="AF19" s="12"/>
       <c r="AG19" s="12"/>
@@ -18478,7 +18541,9 @@
       <c r="B20" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="70"/>
+      <c r="C20" s="70">
+        <v>5</v>
+      </c>
       <c r="D20" s="70"/>
       <c r="E20" s="70"/>
       <c r="F20" s="70"/>
@@ -18501,11 +18566,11 @@
       </c>
       <c r="U20" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="V20" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AF20" s="12"/>
       <c r="AG20" s="12"/>
@@ -18544,7 +18609,10 @@
       <c r="E21" s="70"/>
       <c r="F21" s="70"/>
       <c r="G21" s="70"/>
-      <c r="H21" s="70"/>
+      <c r="H21" s="70">
+        <f>24*2</f>
+        <v>48</v>
+      </c>
       <c r="I21" s="70"/>
       <c r="J21" s="71"/>
       <c r="K21" s="72"/>
@@ -18558,15 +18626,15 @@
       <c r="S21" s="55"/>
       <c r="T21" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="U21" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V21" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF21" s="12"/>
       <c r="AG21" s="12"/>
@@ -18600,13 +18668,17 @@
       <c r="B22" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="C22" s="70"/>
+      <c r="C22" s="70">
+        <v>2</v>
+      </c>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
       <c r="G22" s="70"/>
       <c r="H22" s="70"/>
-      <c r="I22" s="70"/>
+      <c r="I22" s="70">
+        <v>20</v>
+      </c>
       <c r="J22" s="71"/>
       <c r="K22" s="72"/>
       <c r="L22" s="55"/>
@@ -18619,15 +18691,15 @@
       <c r="S22" s="55"/>
       <c r="T22" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="U22" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="V22" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2.8333333333333335</v>
       </c>
       <c r="W22" s="9"/>
       <c r="X22" s="9"/>
@@ -18675,7 +18747,10 @@
       <c r="E23" s="70"/>
       <c r="F23" s="70"/>
       <c r="G23" s="70"/>
-      <c r="H23" s="70"/>
+      <c r="H23" s="70">
+        <f>37*24+19</f>
+        <v>907</v>
+      </c>
       <c r="I23" s="70"/>
       <c r="J23" s="71"/>
       <c r="K23" s="72"/>
@@ -18689,15 +18764,15 @@
       <c r="S23" s="55"/>
       <c r="T23" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>907</v>
       </c>
       <c r="U23" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>907</v>
       </c>
       <c r="V23" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>37.791666666666664</v>
       </c>
       <c r="W23" s="9"/>
       <c r="X23" s="9"/>
@@ -18740,12 +18815,17 @@
       <c r="B24" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="C24" s="70"/>
+      <c r="C24" s="70">
+        <v>2</v>
+      </c>
       <c r="D24" s="70"/>
       <c r="E24" s="70"/>
       <c r="F24" s="70"/>
       <c r="G24" s="70"/>
-      <c r="H24" s="70"/>
+      <c r="H24" s="70">
+        <f>24*3</f>
+        <v>72</v>
+      </c>
       <c r="I24" s="70"/>
       <c r="J24" s="71"/>
       <c r="K24" s="72"/>
@@ -18759,15 +18839,15 @@
       <c r="S24" s="55"/>
       <c r="T24" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="U24" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="V24" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AF24" s="12"/>
       <c r="AG24" s="12"/>
@@ -18801,34 +18881,44 @@
       <c r="B25" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="C25" s="70"/>
+      <c r="C25" s="70">
+        <v>51</v>
+      </c>
       <c r="D25" s="70"/>
       <c r="E25" s="70"/>
       <c r="F25" s="70"/>
       <c r="G25" s="70"/>
       <c r="H25" s="70"/>
       <c r="I25" s="70"/>
-      <c r="J25" s="71"/>
+      <c r="J25" s="71">
+        <v>1</v>
+      </c>
       <c r="K25" s="72"/>
       <c r="L25" s="55"/>
-      <c r="M25" s="73"/>
+      <c r="M25" s="73">
+        <v>1</v>
+      </c>
       <c r="N25" s="74"/>
-      <c r="O25" s="70"/>
+      <c r="O25" s="70">
+        <v>1</v>
+      </c>
       <c r="P25" s="71"/>
-      <c r="Q25" s="71"/>
+      <c r="Q25" s="71">
+        <v>2</v>
+      </c>
       <c r="R25" s="72"/>
       <c r="S25" s="55"/>
       <c r="T25" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U25" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1321</v>
       </c>
       <c r="V25" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>55.041666666666664</v>
       </c>
       <c r="AY25" s="14" t="e">
         <f>#REF!-AY24</f>
@@ -18890,7 +18980,9 @@
       <c r="B27" s="26" t="s">
         <v>69</v>
       </c>
-      <c r="C27" s="70"/>
+      <c r="C27" s="70">
+        <v>4</v>
+      </c>
       <c r="D27" s="70"/>
       <c r="E27" s="70"/>
       <c r="F27" s="70"/>
@@ -18913,11 +19005,11 @@
       </c>
       <c r="U27" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V27" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W27" s="9"/>
       <c r="X27" s="9"/>
@@ -18937,7 +19029,9 @@
       <c r="B28" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="C28" s="70"/>
+      <c r="C28" s="70">
+        <v>5</v>
+      </c>
       <c r="D28" s="70"/>
       <c r="E28" s="70"/>
       <c r="F28" s="70"/>
@@ -18947,11 +19041,17 @@
       <c r="J28" s="71"/>
       <c r="K28" s="72"/>
       <c r="L28" s="55"/>
-      <c r="M28" s="73"/>
+      <c r="M28" s="73">
+        <v>2</v>
+      </c>
       <c r="N28" s="74"/>
-      <c r="O28" s="70"/>
+      <c r="O28" s="70">
+        <v>1</v>
+      </c>
       <c r="P28" s="71"/>
-      <c r="Q28" s="71"/>
+      <c r="Q28" s="71">
+        <v>6</v>
+      </c>
       <c r="R28" s="72"/>
       <c r="S28" s="55"/>
       <c r="T28" s="58">
@@ -18960,11 +19060,11 @@
       </c>
       <c r="U28" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>336</v>
       </c>
       <c r="V28" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="W28" s="9"/>
       <c r="X28" s="9"/>
@@ -18984,34 +19084,42 @@
       <c r="B29" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="C29" s="70"/>
+      <c r="C29" s="70">
+        <v>27</v>
+      </c>
       <c r="D29" s="70"/>
       <c r="E29" s="70"/>
       <c r="F29" s="70"/>
       <c r="G29" s="70"/>
       <c r="H29" s="70"/>
       <c r="I29" s="70"/>
-      <c r="J29" s="71"/>
+      <c r="J29" s="71">
+        <v>5</v>
+      </c>
       <c r="K29" s="72"/>
       <c r="L29" s="55"/>
       <c r="M29" s="73"/>
       <c r="N29" s="74"/>
-      <c r="O29" s="70"/>
+      <c r="O29" s="70">
+        <v>1</v>
+      </c>
       <c r="P29" s="71"/>
-      <c r="Q29" s="71"/>
+      <c r="Q29" s="71">
+        <v>1</v>
+      </c>
       <c r="R29" s="72"/>
       <c r="S29" s="55"/>
       <c r="T29" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U29" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>701</v>
       </c>
       <c r="V29" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>29.208333333333332</v>
       </c>
     </row>
     <row r="30" spans="1:54" x14ac:dyDescent="0.25">
@@ -19022,7 +19130,9 @@
       <c r="B30" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="C30" s="70"/>
+      <c r="C30" s="70">
+        <v>13</v>
+      </c>
       <c r="D30" s="70"/>
       <c r="E30" s="70"/>
       <c r="F30" s="70"/>
@@ -19034,9 +19144,13 @@
       <c r="L30" s="55"/>
       <c r="M30" s="73"/>
       <c r="N30" s="74"/>
-      <c r="O30" s="70"/>
+      <c r="O30" s="70">
+        <v>1</v>
+      </c>
       <c r="P30" s="71"/>
-      <c r="Q30" s="71"/>
+      <c r="Q30" s="71">
+        <v>1</v>
+      </c>
       <c r="R30" s="72"/>
       <c r="S30" s="55"/>
       <c r="T30" s="58">
@@ -19045,11 +19159,11 @@
       </c>
       <c r="U30" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="V30" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31" spans="1:54" x14ac:dyDescent="0.25">
@@ -19060,7 +19174,9 @@
       <c r="B31" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="C31" s="70"/>
+      <c r="C31" s="70">
+        <v>2</v>
+      </c>
       <c r="D31" s="70"/>
       <c r="E31" s="70"/>
       <c r="F31" s="70"/>
@@ -19083,11 +19199,11 @@
       </c>
       <c r="U31" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V31" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:54" x14ac:dyDescent="0.25">
@@ -19136,7 +19252,9 @@
       <c r="B33" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="C33" s="70"/>
+      <c r="C33" s="70">
+        <v>2</v>
+      </c>
       <c r="D33" s="70"/>
       <c r="E33" s="70"/>
       <c r="F33" s="70"/>
@@ -19159,11 +19277,11 @@
       </c>
       <c r="U33" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V33" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:23" x14ac:dyDescent="0.25">
@@ -19174,34 +19292,45 @@
       <c r="B34" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="C34" s="70"/>
+      <c r="C34" s="70">
+        <f>144+55</f>
+        <v>199</v>
+      </c>
       <c r="D34" s="70"/>
       <c r="E34" s="70"/>
       <c r="F34" s="70"/>
       <c r="G34" s="70"/>
       <c r="H34" s="70"/>
-      <c r="I34" s="70"/>
+      <c r="I34" s="70">
+        <v>1</v>
+      </c>
       <c r="J34" s="71"/>
-      <c r="K34" s="72"/>
+      <c r="K34" s="72">
+        <v>1</v>
+      </c>
       <c r="L34" s="55"/>
       <c r="M34" s="73"/>
       <c r="N34" s="74"/>
-      <c r="O34" s="70"/>
+      <c r="O34" s="70">
+        <v>2</v>
+      </c>
       <c r="P34" s="71"/>
-      <c r="Q34" s="71"/>
+      <c r="Q34" s="71">
+        <v>2</v>
+      </c>
       <c r="R34" s="72"/>
       <c r="S34" s="55"/>
       <c r="T34" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U34" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4874</v>
       </c>
       <c r="V34" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>203.08333333333334</v>
       </c>
     </row>
     <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -19288,34 +19417,52 @@
       <c r="B37" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="C37" s="59"/>
+      <c r="C37" s="59">
+        <f>30+648+3132+94</f>
+        <v>3904</v>
+      </c>
       <c r="D37" s="59"/>
       <c r="E37" s="59"/>
       <c r="F37" s="59"/>
       <c r="G37" s="59"/>
-      <c r="H37" s="59"/>
-      <c r="I37" s="59"/>
-      <c r="J37" s="60"/>
-      <c r="K37" s="61"/>
+      <c r="H37" s="59">
+        <v>2</v>
+      </c>
+      <c r="I37" s="59">
+        <v>2</v>
+      </c>
+      <c r="J37" s="60">
+        <v>1</v>
+      </c>
+      <c r="K37" s="61">
+        <f>6+2</f>
+        <v>8</v>
+      </c>
       <c r="L37" s="62"/>
-      <c r="M37" s="63"/>
+      <c r="M37" s="63">
+        <v>15</v>
+      </c>
       <c r="N37" s="64"/>
-      <c r="O37" s="65"/>
+      <c r="O37" s="65">
+        <v>24</v>
+      </c>
       <c r="P37" s="66"/>
-      <c r="Q37" s="66"/>
+      <c r="Q37" s="66">
+        <v>109</v>
+      </c>
       <c r="R37" s="67"/>
       <c r="S37" s="62"/>
       <c r="T37" s="77">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="U37" s="77">
         <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
-        <v>0</v>
+        <v>24325</v>
       </c>
       <c r="V37" s="77">
         <f>U37/6</f>
-        <v>0</v>
+        <v>4054.1666666666665</v>
       </c>
       <c r="W37" s="50"/>
     </row>
@@ -19403,7 +19550,10 @@
       <c r="B40" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="C40" s="59"/>
+      <c r="C40" s="59">
+        <f>63+50</f>
+        <v>113</v>
+      </c>
       <c r="D40" s="59"/>
       <c r="E40" s="59"/>
       <c r="F40" s="59"/>
@@ -19411,26 +19561,34 @@
       <c r="H40" s="59"/>
       <c r="I40" s="59"/>
       <c r="J40" s="60"/>
-      <c r="K40" s="61"/>
+      <c r="K40" s="61">
+        <v>20</v>
+      </c>
       <c r="L40" s="62"/>
-      <c r="M40" s="63"/>
+      <c r="M40" s="63">
+        <v>2</v>
+      </c>
       <c r="N40" s="64"/>
-      <c r="O40" s="65"/>
+      <c r="O40" s="65">
+        <v>2</v>
+      </c>
       <c r="P40" s="66"/>
-      <c r="Q40" s="66"/>
+      <c r="Q40" s="66">
+        <v>4</v>
+      </c>
       <c r="R40" s="67"/>
       <c r="S40" s="62"/>
       <c r="T40" s="77">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="U40" s="77">
         <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
-        <v>0</v>
+        <v>2924</v>
       </c>
       <c r="V40" s="77">
         <f>U40/24</f>
-        <v>0</v>
+        <v>121.83333333333333</v>
       </c>
     </row>
     <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -19441,7 +19599,9 @@
       <c r="B41" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="C41" s="82"/>
+      <c r="C41" s="82">
+        <v>40</v>
+      </c>
       <c r="D41" s="82"/>
       <c r="E41" s="82"/>
       <c r="F41" s="82"/>
@@ -19451,11 +19611,17 @@
       <c r="J41" s="83"/>
       <c r="K41" s="84"/>
       <c r="L41" s="85"/>
-      <c r="M41" s="86"/>
+      <c r="M41" s="86">
+        <v>10</v>
+      </c>
       <c r="N41" s="87"/>
-      <c r="O41" s="82"/>
+      <c r="O41" s="82">
+        <v>12</v>
+      </c>
       <c r="P41" s="83"/>
-      <c r="Q41" s="83"/>
+      <c r="Q41" s="83">
+        <v>20</v>
+      </c>
       <c r="R41" s="84"/>
       <c r="S41" s="85"/>
       <c r="T41" s="88">
@@ -19464,11 +19630,11 @@
       </c>
       <c r="U41" s="88">
         <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
-        <v>0</v>
+        <v>984</v>
       </c>
       <c r="V41" s="88">
         <f>U41/12</f>
-        <v>0</v>
+        <v>82</v>
       </c>
     </row>
     <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -19508,34 +19674,53 @@
       <c r="B43" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="C43" s="65"/>
+      <c r="C43" s="65">
+        <f>11610+19764+10260</f>
+        <v>41634</v>
+      </c>
       <c r="D43" s="65"/>
       <c r="E43" s="65"/>
       <c r="F43" s="65"/>
       <c r="G43" s="65"/>
-      <c r="H43" s="65"/>
-      <c r="I43" s="65"/>
-      <c r="J43" s="66"/>
-      <c r="K43" s="67"/>
+      <c r="H43" s="65">
+        <v>5</v>
+      </c>
+      <c r="I43" s="65">
+        <v>12</v>
+      </c>
+      <c r="J43" s="66">
+        <f>6*8</f>
+        <v>48</v>
+      </c>
+      <c r="K43" s="67">
+        <f>71*6+2</f>
+        <v>428</v>
+      </c>
       <c r="L43" s="62"/>
-      <c r="M43" s="63"/>
+      <c r="M43" s="63">
+        <v>336</v>
+      </c>
       <c r="N43" s="64"/>
-      <c r="O43" s="65"/>
+      <c r="O43" s="65">
+        <v>412</v>
+      </c>
       <c r="P43" s="66"/>
-      <c r="Q43" s="66"/>
+      <c r="Q43" s="66">
+        <v>475</v>
+      </c>
       <c r="R43" s="67"/>
       <c r="S43" s="62"/>
       <c r="T43" s="77">
         <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
-        <v>0</v>
+        <v>493</v>
       </c>
       <c r="U43" s="77">
         <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
-        <v>0</v>
+        <v>257635</v>
       </c>
       <c r="V43" s="77">
         <f>U43/6</f>
-        <v>0</v>
+        <v>42939.166666666664</v>
       </c>
     </row>
     <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -19651,34 +19836,49 @@
       <c r="B47" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="C47" s="65"/>
+      <c r="C47" s="65">
+        <f>106+648+324+88+540+103+324+432+106</f>
+        <v>2671</v>
+      </c>
       <c r="D47" s="65"/>
       <c r="E47" s="65"/>
       <c r="F47" s="65"/>
       <c r="G47" s="65"/>
-      <c r="H47" s="65"/>
+      <c r="H47" s="65">
+        <v>1</v>
+      </c>
       <c r="I47" s="65"/>
       <c r="J47" s="66"/>
-      <c r="K47" s="67"/>
+      <c r="K47" s="67">
+        <v>5</v>
+      </c>
       <c r="L47" s="62"/>
-      <c r="M47" s="63"/>
+      <c r="M47" s="63">
+        <v>9</v>
+      </c>
       <c r="N47" s="64"/>
-      <c r="O47" s="65"/>
+      <c r="O47" s="65">
+        <v>16</v>
+      </c>
       <c r="P47" s="66"/>
-      <c r="Q47" s="66"/>
-      <c r="R47" s="67"/>
+      <c r="Q47" s="66">
+        <v>5</v>
+      </c>
+      <c r="R47" s="67">
+        <v>3</v>
+      </c>
       <c r="S47" s="62"/>
       <c r="T47" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="U47" s="77">
         <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
-        <v>0</v>
+        <v>16215</v>
       </c>
       <c r="V47" s="77">
         <f>U47/6</f>
-        <v>0</v>
+        <v>2702.5</v>
       </c>
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.25">
@@ -19694,7 +19894,9 @@
       <c r="E48" s="70"/>
       <c r="F48" s="70"/>
       <c r="G48" s="70"/>
-      <c r="H48" s="70"/>
+      <c r="H48" s="70">
+        <v>24</v>
+      </c>
       <c r="I48" s="70"/>
       <c r="J48" s="71"/>
       <c r="K48" s="72"/>
@@ -19708,15 +19910,15 @@
       <c r="S48" s="55"/>
       <c r="T48" s="75">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="U48" s="75">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V48" s="75">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.25">
@@ -19727,7 +19929,9 @@
       <c r="B49" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="C49" s="70"/>
+      <c r="C49" s="70">
+        <v>10</v>
+      </c>
       <c r="D49" s="70"/>
       <c r="E49" s="70"/>
       <c r="F49" s="70"/>
@@ -19750,11 +19954,11 @@
       </c>
       <c r="U49" s="75">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="V49" s="75">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="50" spans="1:22" x14ac:dyDescent="0.25">
@@ -19803,7 +20007,9 @@
       <c r="B51" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="C51" s="65"/>
+      <c r="C51" s="65">
+        <v>34</v>
+      </c>
       <c r="D51" s="65"/>
       <c r="E51" s="65"/>
       <c r="F51" s="65"/>
@@ -19826,11 +20032,11 @@
       </c>
       <c r="U51" s="77">
         <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="V51" s="77">
         <f>U51/6</f>
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.25">
@@ -19879,7 +20085,9 @@
       <c r="B53" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C53" s="70"/>
+      <c r="C53" s="70">
+        <v>6</v>
+      </c>
       <c r="D53" s="70"/>
       <c r="E53" s="70"/>
       <c r="F53" s="70"/>
@@ -19893,7 +20101,9 @@
       <c r="N53" s="74"/>
       <c r="O53" s="70"/>
       <c r="P53" s="71"/>
-      <c r="Q53" s="71"/>
+      <c r="Q53" s="71">
+        <v>1</v>
+      </c>
       <c r="R53" s="72"/>
       <c r="S53" s="55"/>
       <c r="T53" s="75">
@@ -19902,11 +20112,11 @@
       </c>
       <c r="U53" s="75">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="V53" s="75">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.25">
@@ -20032,7 +20242,7 @@
       </c>
       <c r="C58" s="2">
         <f>SUM(C7:C57)</f>
-        <v>0</v>
+        <v>52467</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" s="2"/>
@@ -20046,23 +20256,23 @@
       </c>
       <c r="H58" s="2">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1191</v>
       </c>
       <c r="I58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="J58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="K58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>470</v>
       </c>
       <c r="M58" s="5">
         <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
-        <v>0</v>
+        <v>384</v>
       </c>
       <c r="N58" s="5">
         <f t="shared" si="12"/>
@@ -20070,32 +20280,32 @@
       </c>
       <c r="O58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>484</v>
       </c>
       <c r="P58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Q58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>646</v>
       </c>
       <c r="R58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="S58" s="55"/>
       <c r="T58" s="4">
         <f>SUM(T7:T57)</f>
-        <v>0</v>
+        <v>1786</v>
       </c>
       <c r="U58" s="90">
         <f>SUM(U7:U57)</f>
-        <v>0</v>
+        <v>402754</v>
       </c>
       <c r="V58" s="4">
         <f>SUM(V7:V57)</f>
-        <v>0</v>
+        <v>54119.791666666664</v>
       </c>
     </row>
     <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -20365,13 +20575,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
     <mergeCell ref="C60:K60"/>
     <mergeCell ref="I1:U1"/>
     <mergeCell ref="C4:K4"/>
     <mergeCell ref="T4:T5"/>
     <mergeCell ref="U4:U5"/>
-    <mergeCell ref="V4:V5"/>
-    <mergeCell ref="J5:K5"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -23304,13 +23514,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
     <mergeCell ref="C60:K60"/>
     <mergeCell ref="I1:U1"/>
     <mergeCell ref="C4:K4"/>
     <mergeCell ref="T4:T5"/>
     <mergeCell ref="U4:U5"/>
-    <mergeCell ref="V4:V5"/>
-    <mergeCell ref="J5:K5"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -26243,13 +26453,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
     <mergeCell ref="C60:K60"/>
     <mergeCell ref="I1:U1"/>
     <mergeCell ref="C4:K4"/>
     <mergeCell ref="T4:T5"/>
     <mergeCell ref="U4:U5"/>
-    <mergeCell ref="V4:V5"/>
-    <mergeCell ref="J5:K5"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -29182,13 +29392,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
     <mergeCell ref="C60:K60"/>
     <mergeCell ref="I1:U1"/>
     <mergeCell ref="C4:K4"/>
     <mergeCell ref="T4:T5"/>
     <mergeCell ref="U4:U5"/>
-    <mergeCell ref="V4:V5"/>
-    <mergeCell ref="J5:K5"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>

--- a/GBDS AUGUST FILES 2026/INVENTORY COUNT SHEET - AUGUST 2026.xlsx
+++ b/GBDS AUGUST FILES 2026/INVENTORY COUNT SHEET - AUGUST 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS AUGUST FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28D3A955-1D33-4EDC-81D2-073AF1DB8406}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED7CCFBA-0612-4086-BE77-BA01ED64C524}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="5" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="6" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
   </bookViews>
   <sheets>
     <sheet name="SAMPLE" sheetId="32" r:id="rId1"/>
@@ -19,9 +19,9 @@
     <sheet name="08-05-2026" sheetId="71" r:id="rId4"/>
     <sheet name="08-06-2026" sheetId="72" r:id="rId5"/>
     <sheet name="08-07-2026" sheetId="73" r:id="rId6"/>
-    <sheet name="08-08-2026" sheetId="74" r:id="rId7"/>
-    <sheet name="08-09-2026" sheetId="75" r:id="rId8"/>
-    <sheet name="08-10-2026" sheetId="76" r:id="rId9"/>
+    <sheet name="08-10-2026" sheetId="76" r:id="rId7"/>
+    <sheet name="08-08-2026" sheetId="74" r:id="rId8"/>
+    <sheet name="08-09-2026" sheetId="75" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'08-03-2026'!$A$1:$W$59</definedName>
@@ -29,9 +29,9 @@
     <definedName name="_xlnm.Print_Area" localSheetId="3">'08-05-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'08-06-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'08-07-2026'!$A$1:$W$59</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'08-08-2026'!$A$1:$W$59</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="7">'08-09-2026'!$A$1:$W$59</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="8">'08-10-2026'!$A$1:$W$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">'08-08-2026'!$A$1:$W$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="8">'08-09-2026'!$A$1:$W$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'08-10-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">SAMPLE!$A$1:$W$85</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -20593,7 +20593,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7D7CD48-36B7-4216-A88E-17673474B053}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{650CA8C6-0E34-4041-83EB-8BD8B22ACF90}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -20650,7 +20650,7 @@
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -20824,34 +20824,44 @@
       <c r="B7" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="52"/>
+      <c r="C7" s="52">
+        <v>32</v>
+      </c>
       <c r="D7" s="52"/>
       <c r="E7" s="52"/>
       <c r="F7" s="52"/>
       <c r="G7" s="52"/>
       <c r="H7" s="52"/>
-      <c r="I7" s="52"/>
+      <c r="I7" s="52">
+        <v>3</v>
+      </c>
       <c r="J7" s="53"/>
-      <c r="K7" s="54"/>
+      <c r="K7" s="54">
+        <v>6</v>
+      </c>
       <c r="L7" s="55"/>
       <c r="M7" s="56"/>
       <c r="N7" s="57"/>
-      <c r="O7" s="52"/>
+      <c r="O7" s="52">
+        <v>1</v>
+      </c>
       <c r="P7" s="53"/>
-      <c r="Q7" s="53"/>
+      <c r="Q7" s="53">
+        <v>1</v>
+      </c>
       <c r="R7" s="54"/>
       <c r="S7" s="55"/>
       <c r="T7" s="58">
         <f>H7+I7+J7+K7+N7+P7+R7</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="U7" s="58">
         <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
-        <v>0</v>
+        <v>825</v>
       </c>
       <c r="V7" s="58">
         <f>U7/24</f>
-        <v>0</v>
+        <v>34.375</v>
       </c>
       <c r="W7" s="50"/>
       <c r="AF7" s="12"/>
@@ -20886,7 +20896,10 @@
       <c r="B8" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="59"/>
+      <c r="C8" s="59">
+        <f>41+43</f>
+        <v>84</v>
+      </c>
       <c r="D8" s="59"/>
       <c r="E8" s="59"/>
       <c r="F8" s="59"/>
@@ -20896,24 +20909,32 @@
       <c r="J8" s="60"/>
       <c r="K8" s="61"/>
       <c r="L8" s="62"/>
-      <c r="M8" s="63"/>
+      <c r="M8" s="63">
+        <v>1</v>
+      </c>
       <c r="N8" s="64"/>
-      <c r="O8" s="65"/>
-      <c r="P8" s="66"/>
-      <c r="Q8" s="66"/>
+      <c r="O8" s="65">
+        <v>1</v>
+      </c>
+      <c r="P8" s="66">
+        <v>12</v>
+      </c>
+      <c r="Q8" s="66">
+        <v>1</v>
+      </c>
       <c r="R8" s="67"/>
       <c r="S8" s="62"/>
       <c r="T8" s="68">
         <f t="shared" ref="T8:T41" si="0">H8+I8+J8+K8+N8+P8+R8</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="U8" s="69">
         <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="V8" s="69">
         <f>U8/24</f>
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="W8" s="50"/>
       <c r="AF8" s="12"/>
@@ -20948,7 +20969,10 @@
       <c r="B9" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="70"/>
+      <c r="C9" s="70">
+        <f>62+30</f>
+        <v>92</v>
+      </c>
       <c r="D9" s="70"/>
       <c r="E9" s="70"/>
       <c r="F9" s="70"/>
@@ -20971,11 +20995,11 @@
       </c>
       <c r="U9" s="76">
         <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
-        <v>0</v>
+        <v>2208</v>
       </c>
       <c r="V9" s="76">
         <f t="shared" ref="V9:V11" si="3">U9/24</f>
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="W9" s="50"/>
       <c r="AF9" s="12"/>
@@ -21010,7 +21034,10 @@
       <c r="B10" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="C10" s="70"/>
+      <c r="C10" s="70">
+        <f>36+10</f>
+        <v>46</v>
+      </c>
       <c r="D10" s="70"/>
       <c r="E10" s="70"/>
       <c r="F10" s="70"/>
@@ -21033,11 +21060,11 @@
       </c>
       <c r="U10" s="58">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1104</v>
       </c>
       <c r="V10" s="58">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="W10" s="50"/>
       <c r="AF10" s="12"/>
@@ -21072,7 +21099,9 @@
       <c r="B11" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="70"/>
+      <c r="C11" s="70">
+        <v>9</v>
+      </c>
       <c r="D11" s="70"/>
       <c r="E11" s="70"/>
       <c r="F11" s="70"/>
@@ -21080,7 +21109,9 @@
       <c r="H11" s="70"/>
       <c r="I11" s="70"/>
       <c r="J11" s="71"/>
-      <c r="K11" s="72"/>
+      <c r="K11" s="72">
+        <v>2</v>
+      </c>
       <c r="L11" s="55"/>
       <c r="M11" s="73"/>
       <c r="N11" s="74"/>
@@ -21091,15 +21122,15 @@
       <c r="S11" s="55"/>
       <c r="T11" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U11" s="58">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="V11" s="58">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>9.0833333333333339</v>
       </c>
       <c r="AF11" s="12"/>
       <c r="AG11" s="12"/>
@@ -21132,7 +21163,10 @@
       <c r="B12" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="59"/>
+      <c r="C12" s="59">
+        <f>1224+53+1008+23+1080+29</f>
+        <v>3417</v>
+      </c>
       <c r="D12" s="59"/>
       <c r="E12" s="59"/>
       <c r="F12" s="59"/>
@@ -21142,24 +21176,34 @@
       <c r="J12" s="60"/>
       <c r="K12" s="61"/>
       <c r="L12" s="62"/>
-      <c r="M12" s="63"/>
-      <c r="N12" s="64"/>
-      <c r="O12" s="65"/>
+      <c r="M12" s="63">
+        <v>19</v>
+      </c>
+      <c r="N12" s="64">
+        <v>7</v>
+      </c>
+      <c r="O12" s="65">
+        <v>6</v>
+      </c>
       <c r="P12" s="66"/>
-      <c r="Q12" s="66"/>
-      <c r="R12" s="67"/>
+      <c r="Q12" s="66">
+        <v>20</v>
+      </c>
+      <c r="R12" s="67">
+        <v>7</v>
+      </c>
       <c r="S12" s="62"/>
       <c r="T12" s="69">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="U12" s="69">
         <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
-        <v>0</v>
+        <v>83102</v>
       </c>
       <c r="V12" s="69">
         <f>U12/24</f>
-        <v>0</v>
+        <v>3462.5833333333335</v>
       </c>
       <c r="W12" s="9"/>
       <c r="X12" s="9"/>
@@ -21201,12 +21245,16 @@
       <c r="B13" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="70"/>
+      <c r="C13" s="70">
+        <v>2</v>
+      </c>
       <c r="D13" s="70"/>
       <c r="E13" s="70"/>
       <c r="F13" s="70"/>
       <c r="G13" s="70"/>
-      <c r="H13" s="70"/>
+      <c r="H13" s="70">
+        <v>16</v>
+      </c>
       <c r="I13" s="70"/>
       <c r="J13" s="71"/>
       <c r="K13" s="72"/>
@@ -21220,15 +21268,15 @@
       <c r="S13" s="55"/>
       <c r="T13" s="76">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="U13" s="76">
         <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="V13" s="76">
         <f>U13/24</f>
-        <v>0</v>
+        <v>2.6666666666666665</v>
       </c>
       <c r="AF13" s="12"/>
       <c r="AG13" s="12"/>
@@ -21262,7 +21310,9 @@
       <c r="B14" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="70"/>
+      <c r="C14" s="70">
+        <v>2</v>
+      </c>
       <c r="D14" s="70"/>
       <c r="E14" s="70"/>
       <c r="F14" s="70"/>
@@ -21285,11 +21335,11 @@
       </c>
       <c r="U14" s="75">
         <f t="shared" ref="U14:U36" si="4">C14*24+M14*24+O14*24+Q14*24+T14</f>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V14" s="75">
         <f t="shared" ref="V14:V36" si="5">U14/24</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF14" s="12"/>
       <c r="AG14" s="12"/>
@@ -21450,7 +21500,9 @@
       <c r="E17" s="70"/>
       <c r="F17" s="70"/>
       <c r="G17" s="70"/>
-      <c r="H17" s="70"/>
+      <c r="H17" s="70">
+        <v>72</v>
+      </c>
       <c r="I17" s="70"/>
       <c r="J17" s="71"/>
       <c r="K17" s="72"/>
@@ -21464,15 +21516,15 @@
       <c r="S17" s="55"/>
       <c r="T17" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="U17" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="V17" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF17" s="12"/>
       <c r="AG17" s="12"/>
@@ -21566,12 +21618,16 @@
       <c r="B19" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="C19" s="70"/>
+      <c r="C19" s="70">
+        <v>2</v>
+      </c>
       <c r="D19" s="70"/>
       <c r="E19" s="70"/>
       <c r="F19" s="70"/>
       <c r="G19" s="70"/>
-      <c r="H19" s="70"/>
+      <c r="H19" s="70">
+        <v>44</v>
+      </c>
       <c r="I19" s="70"/>
       <c r="J19" s="71"/>
       <c r="K19" s="72"/>
@@ -21585,15 +21641,15 @@
       <c r="S19" s="55"/>
       <c r="T19" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="U19" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="V19" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3.8333333333333335</v>
       </c>
       <c r="AF19" s="12"/>
       <c r="AG19" s="12"/>
@@ -21627,7 +21683,9 @@
       <c r="B20" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="70"/>
+      <c r="C20" s="70">
+        <v>5</v>
+      </c>
       <c r="D20" s="70"/>
       <c r="E20" s="70"/>
       <c r="F20" s="70"/>
@@ -21650,11 +21708,11 @@
       </c>
       <c r="U20" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="V20" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AF20" s="12"/>
       <c r="AG20" s="12"/>
@@ -21693,7 +21751,9 @@
       <c r="E21" s="70"/>
       <c r="F21" s="70"/>
       <c r="G21" s="70"/>
-      <c r="H21" s="70"/>
+      <c r="H21" s="70">
+        <v>48</v>
+      </c>
       <c r="I21" s="70"/>
       <c r="J21" s="71"/>
       <c r="K21" s="72"/>
@@ -21707,15 +21767,15 @@
       <c r="S21" s="55"/>
       <c r="T21" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="U21" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V21" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF21" s="12"/>
       <c r="AG21" s="12"/>
@@ -21749,13 +21809,17 @@
       <c r="B22" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="C22" s="70"/>
+      <c r="C22" s="70">
+        <v>2</v>
+      </c>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
       <c r="G22" s="70"/>
       <c r="H22" s="70"/>
-      <c r="I22" s="70"/>
+      <c r="I22" s="70">
+        <v>20</v>
+      </c>
       <c r="J22" s="71"/>
       <c r="K22" s="72"/>
       <c r="L22" s="55"/>
@@ -21768,15 +21832,15 @@
       <c r="S22" s="55"/>
       <c r="T22" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="U22" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="V22" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2.8333333333333335</v>
       </c>
       <c r="W22" s="9"/>
       <c r="X22" s="9"/>
@@ -21824,7 +21888,9 @@
       <c r="E23" s="70"/>
       <c r="F23" s="70"/>
       <c r="G23" s="70"/>
-      <c r="H23" s="70"/>
+      <c r="H23" s="70">
+        <v>907</v>
+      </c>
       <c r="I23" s="70"/>
       <c r="J23" s="71"/>
       <c r="K23" s="72"/>
@@ -21838,15 +21904,15 @@
       <c r="S23" s="55"/>
       <c r="T23" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>907</v>
       </c>
       <c r="U23" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>907</v>
       </c>
       <c r="V23" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>37.791666666666664</v>
       </c>
       <c r="W23" s="9"/>
       <c r="X23" s="9"/>
@@ -21889,12 +21955,16 @@
       <c r="B24" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="C24" s="70"/>
+      <c r="C24" s="70">
+        <v>2</v>
+      </c>
       <c r="D24" s="70"/>
       <c r="E24" s="70"/>
       <c r="F24" s="70"/>
       <c r="G24" s="70"/>
-      <c r="H24" s="70"/>
+      <c r="H24" s="70">
+        <v>72</v>
+      </c>
       <c r="I24" s="70"/>
       <c r="J24" s="71"/>
       <c r="K24" s="72"/>
@@ -21908,15 +21978,15 @@
       <c r="S24" s="55"/>
       <c r="T24" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="U24" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="V24" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AF24" s="12"/>
       <c r="AG24" s="12"/>
@@ -21950,34 +22020,44 @@
       <c r="B25" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="C25" s="70"/>
+      <c r="C25" s="70">
+        <v>51</v>
+      </c>
       <c r="D25" s="70"/>
       <c r="E25" s="70"/>
       <c r="F25" s="70"/>
       <c r="G25" s="70"/>
       <c r="H25" s="70"/>
       <c r="I25" s="70"/>
-      <c r="J25" s="71"/>
+      <c r="J25" s="71">
+        <v>1</v>
+      </c>
       <c r="K25" s="72"/>
       <c r="L25" s="55"/>
-      <c r="M25" s="73"/>
+      <c r="M25" s="73">
+        <v>1</v>
+      </c>
       <c r="N25" s="74"/>
-      <c r="O25" s="70"/>
+      <c r="O25" s="70">
+        <v>1</v>
+      </c>
       <c r="P25" s="71"/>
-      <c r="Q25" s="71"/>
+      <c r="Q25" s="71">
+        <v>2</v>
+      </c>
       <c r="R25" s="72"/>
       <c r="S25" s="55"/>
       <c r="T25" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U25" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1321</v>
       </c>
       <c r="V25" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>55.041666666666664</v>
       </c>
       <c r="AY25" s="14" t="e">
         <f>#REF!-AY24</f>
@@ -22039,7 +22119,9 @@
       <c r="B27" s="26" t="s">
         <v>69</v>
       </c>
-      <c r="C27" s="70"/>
+      <c r="C27" s="70">
+        <v>4</v>
+      </c>
       <c r="D27" s="70"/>
       <c r="E27" s="70"/>
       <c r="F27" s="70"/>
@@ -22062,11 +22144,11 @@
       </c>
       <c r="U27" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V27" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W27" s="9"/>
       <c r="X27" s="9"/>
@@ -22086,7 +22168,9 @@
       <c r="B28" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="C28" s="70"/>
+      <c r="C28" s="70">
+        <v>5</v>
+      </c>
       <c r="D28" s="70"/>
       <c r="E28" s="70"/>
       <c r="F28" s="70"/>
@@ -22096,11 +22180,17 @@
       <c r="J28" s="71"/>
       <c r="K28" s="72"/>
       <c r="L28" s="55"/>
-      <c r="M28" s="73"/>
+      <c r="M28" s="73">
+        <v>2</v>
+      </c>
       <c r="N28" s="74"/>
-      <c r="O28" s="70"/>
+      <c r="O28" s="70">
+        <v>1</v>
+      </c>
       <c r="P28" s="71"/>
-      <c r="Q28" s="71"/>
+      <c r="Q28" s="71">
+        <v>4</v>
+      </c>
       <c r="R28" s="72"/>
       <c r="S28" s="55"/>
       <c r="T28" s="58">
@@ -22109,11 +22199,11 @@
       </c>
       <c r="U28" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>288</v>
       </c>
       <c r="V28" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="W28" s="9"/>
       <c r="X28" s="9"/>
@@ -22133,34 +22223,42 @@
       <c r="B29" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="C29" s="70"/>
+      <c r="C29" s="70">
+        <v>27</v>
+      </c>
       <c r="D29" s="70"/>
       <c r="E29" s="70"/>
       <c r="F29" s="70"/>
       <c r="G29" s="70"/>
       <c r="H29" s="70"/>
       <c r="I29" s="70"/>
-      <c r="J29" s="71"/>
+      <c r="J29" s="71">
+        <v>5</v>
+      </c>
       <c r="K29" s="72"/>
       <c r="L29" s="55"/>
       <c r="M29" s="73"/>
       <c r="N29" s="74"/>
-      <c r="O29" s="70"/>
+      <c r="O29" s="70">
+        <v>1</v>
+      </c>
       <c r="P29" s="71"/>
-      <c r="Q29" s="71"/>
+      <c r="Q29" s="71">
+        <v>1</v>
+      </c>
       <c r="R29" s="72"/>
       <c r="S29" s="55"/>
       <c r="T29" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U29" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>701</v>
       </c>
       <c r="V29" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>29.208333333333332</v>
       </c>
     </row>
     <row r="30" spans="1:54" x14ac:dyDescent="0.25">
@@ -22171,7 +22269,9 @@
       <c r="B30" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="C30" s="70"/>
+      <c r="C30" s="70">
+        <v>13</v>
+      </c>
       <c r="D30" s="70"/>
       <c r="E30" s="70"/>
       <c r="F30" s="70"/>
@@ -22183,9 +22283,13 @@
       <c r="L30" s="55"/>
       <c r="M30" s="73"/>
       <c r="N30" s="74"/>
-      <c r="O30" s="70"/>
+      <c r="O30" s="70">
+        <v>1</v>
+      </c>
       <c r="P30" s="71"/>
-      <c r="Q30" s="71"/>
+      <c r="Q30" s="71">
+        <v>1</v>
+      </c>
       <c r="R30" s="72"/>
       <c r="S30" s="55"/>
       <c r="T30" s="58">
@@ -22194,11 +22298,11 @@
       </c>
       <c r="U30" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="V30" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31" spans="1:54" x14ac:dyDescent="0.25">
@@ -22209,7 +22313,9 @@
       <c r="B31" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="C31" s="70"/>
+      <c r="C31" s="70">
+        <v>2</v>
+      </c>
       <c r="D31" s="70"/>
       <c r="E31" s="70"/>
       <c r="F31" s="70"/>
@@ -22232,11 +22338,11 @@
       </c>
       <c r="U31" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V31" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:54" x14ac:dyDescent="0.25">
@@ -22285,7 +22391,9 @@
       <c r="B33" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="C33" s="70"/>
+      <c r="C33" s="70">
+        <v>2</v>
+      </c>
       <c r="D33" s="70"/>
       <c r="E33" s="70"/>
       <c r="F33" s="70"/>
@@ -22308,11 +22416,11 @@
       </c>
       <c r="U33" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V33" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:23" x14ac:dyDescent="0.25">
@@ -22323,34 +22431,47 @@
       <c r="B34" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="C34" s="70"/>
+      <c r="C34" s="70">
+        <f>144+48</f>
+        <v>192</v>
+      </c>
       <c r="D34" s="70"/>
       <c r="E34" s="70"/>
       <c r="F34" s="70"/>
       <c r="G34" s="70"/>
-      <c r="H34" s="70"/>
+      <c r="H34" s="70">
+        <v>1</v>
+      </c>
       <c r="I34" s="70"/>
       <c r="J34" s="71"/>
-      <c r="K34" s="72"/>
+      <c r="K34" s="72">
+        <v>1</v>
+      </c>
       <c r="L34" s="55"/>
-      <c r="M34" s="73"/>
+      <c r="M34" s="73">
+        <v>2</v>
+      </c>
       <c r="N34" s="74"/>
-      <c r="O34" s="70"/>
+      <c r="O34" s="70">
+        <v>2</v>
+      </c>
       <c r="P34" s="71"/>
-      <c r="Q34" s="71"/>
+      <c r="Q34" s="71">
+        <v>2</v>
+      </c>
       <c r="R34" s="72"/>
       <c r="S34" s="55"/>
       <c r="T34" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U34" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4754</v>
       </c>
       <c r="V34" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>198.08333333333334</v>
       </c>
     </row>
     <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -22437,34 +22558,52 @@
       <c r="B37" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="C37" s="59"/>
+      <c r="C37" s="59">
+        <f>101+324+3132+94</f>
+        <v>3651</v>
+      </c>
       <c r="D37" s="59"/>
       <c r="E37" s="59"/>
       <c r="F37" s="59"/>
       <c r="G37" s="59"/>
-      <c r="H37" s="59"/>
-      <c r="I37" s="59"/>
-      <c r="J37" s="60"/>
-      <c r="K37" s="61"/>
+      <c r="H37" s="59">
+        <v>2</v>
+      </c>
+      <c r="I37" s="59">
+        <v>2</v>
+      </c>
+      <c r="J37" s="60">
+        <v>1</v>
+      </c>
+      <c r="K37" s="61">
+        <f>6+2</f>
+        <v>8</v>
+      </c>
       <c r="L37" s="62"/>
-      <c r="M37" s="63"/>
+      <c r="M37" s="63">
+        <v>8</v>
+      </c>
       <c r="N37" s="64"/>
-      <c r="O37" s="65"/>
+      <c r="O37" s="65">
+        <v>10</v>
+      </c>
       <c r="P37" s="66"/>
-      <c r="Q37" s="66"/>
+      <c r="Q37" s="66">
+        <v>94</v>
+      </c>
       <c r="R37" s="67"/>
       <c r="S37" s="62"/>
       <c r="T37" s="77">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="U37" s="77">
         <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
-        <v>0</v>
+        <v>22591</v>
       </c>
       <c r="V37" s="77">
         <f>U37/6</f>
-        <v>0</v>
+        <v>3765.1666666666665</v>
       </c>
       <c r="W37" s="50"/>
     </row>
@@ -22552,7 +22691,10 @@
       <c r="B40" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="C40" s="59"/>
+      <c r="C40" s="59">
+        <f>63+50</f>
+        <v>113</v>
+      </c>
       <c r="D40" s="59"/>
       <c r="E40" s="59"/>
       <c r="F40" s="59"/>
@@ -22560,26 +22702,34 @@
       <c r="H40" s="59"/>
       <c r="I40" s="59"/>
       <c r="J40" s="60"/>
-      <c r="K40" s="61"/>
+      <c r="K40" s="61">
+        <v>20</v>
+      </c>
       <c r="L40" s="62"/>
-      <c r="M40" s="63"/>
+      <c r="M40" s="63">
+        <v>2</v>
+      </c>
       <c r="N40" s="64"/>
-      <c r="O40" s="65"/>
+      <c r="O40" s="65">
+        <v>2</v>
+      </c>
       <c r="P40" s="66"/>
-      <c r="Q40" s="66"/>
+      <c r="Q40" s="66">
+        <v>3</v>
+      </c>
       <c r="R40" s="67"/>
       <c r="S40" s="62"/>
       <c r="T40" s="77">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="U40" s="77">
         <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
-        <v>0</v>
+        <v>2900</v>
       </c>
       <c r="V40" s="77">
         <f>U40/24</f>
-        <v>0</v>
+        <v>120.83333333333333</v>
       </c>
     </row>
     <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -22600,11 +22750,17 @@
       <c r="J41" s="83"/>
       <c r="K41" s="84"/>
       <c r="L41" s="85"/>
-      <c r="M41" s="86"/>
+      <c r="M41" s="86">
+        <v>5</v>
+      </c>
       <c r="N41" s="87"/>
-      <c r="O41" s="82"/>
+      <c r="O41" s="82">
+        <v>5</v>
+      </c>
       <c r="P41" s="83"/>
-      <c r="Q41" s="83"/>
+      <c r="Q41" s="83">
+        <v>26</v>
+      </c>
       <c r="R41" s="84"/>
       <c r="S41" s="85"/>
       <c r="T41" s="88">
@@ -22613,11 +22769,11 @@
       </c>
       <c r="U41" s="88">
         <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
-        <v>0</v>
+        <v>432</v>
       </c>
       <c r="V41" s="88">
         <f>U41/12</f>
-        <v>0</v>
+        <v>36</v>
       </c>
     </row>
     <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -22657,34 +22813,53 @@
       <c r="B43" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="C43" s="65"/>
+      <c r="C43" s="65">
+        <f>9828+19764+10260</f>
+        <v>39852</v>
+      </c>
       <c r="D43" s="65"/>
       <c r="E43" s="65"/>
       <c r="F43" s="65"/>
       <c r="G43" s="65"/>
-      <c r="H43" s="65"/>
-      <c r="I43" s="65"/>
-      <c r="J43" s="66"/>
-      <c r="K43" s="67"/>
+      <c r="H43" s="65">
+        <v>6</v>
+      </c>
+      <c r="I43" s="65">
+        <v>12</v>
+      </c>
+      <c r="J43" s="66">
+        <f>13*6+2</f>
+        <v>80</v>
+      </c>
+      <c r="K43" s="67">
+        <f>71*6+2</f>
+        <v>428</v>
+      </c>
       <c r="L43" s="62"/>
-      <c r="M43" s="63"/>
+      <c r="M43" s="63">
+        <v>444</v>
+      </c>
       <c r="N43" s="64"/>
-      <c r="O43" s="65"/>
+      <c r="O43" s="65">
+        <v>199</v>
+      </c>
       <c r="P43" s="66"/>
-      <c r="Q43" s="66"/>
+      <c r="Q43" s="66">
+        <v>561</v>
+      </c>
       <c r="R43" s="67"/>
       <c r="S43" s="62"/>
       <c r="T43" s="77">
         <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
-        <v>0</v>
+        <v>526</v>
       </c>
       <c r="U43" s="77">
         <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
-        <v>0</v>
+        <v>246862</v>
       </c>
       <c r="V43" s="77">
         <f>U43/6</f>
-        <v>0</v>
+        <v>41143.666666666664</v>
       </c>
     </row>
     <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -22800,34 +22975,49 @@
       <c r="B47" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="C47" s="65"/>
+      <c r="C47" s="65">
+        <f>106+648+324+88+540+103+324+432+106</f>
+        <v>2671</v>
+      </c>
       <c r="D47" s="65"/>
       <c r="E47" s="65"/>
       <c r="F47" s="65"/>
       <c r="G47" s="65"/>
-      <c r="H47" s="65"/>
+      <c r="H47" s="65">
+        <v>1</v>
+      </c>
       <c r="I47" s="65"/>
       <c r="J47" s="66"/>
-      <c r="K47" s="67"/>
+      <c r="K47" s="67">
+        <v>5</v>
+      </c>
       <c r="L47" s="62"/>
-      <c r="M47" s="63"/>
+      <c r="M47" s="63">
+        <v>9</v>
+      </c>
       <c r="N47" s="64"/>
-      <c r="O47" s="65"/>
+      <c r="O47" s="65">
+        <v>16</v>
+      </c>
       <c r="P47" s="66"/>
-      <c r="Q47" s="66"/>
-      <c r="R47" s="67"/>
+      <c r="Q47" s="66">
+        <v>5</v>
+      </c>
+      <c r="R47" s="67">
+        <v>3</v>
+      </c>
       <c r="S47" s="62"/>
       <c r="T47" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="U47" s="77">
         <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
-        <v>0</v>
+        <v>16215</v>
       </c>
       <c r="V47" s="77">
         <f>U47/6</f>
-        <v>0</v>
+        <v>2702.5</v>
       </c>
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.25">
@@ -22843,7 +23033,9 @@
       <c r="E48" s="70"/>
       <c r="F48" s="70"/>
       <c r="G48" s="70"/>
-      <c r="H48" s="70"/>
+      <c r="H48" s="70">
+        <v>24</v>
+      </c>
       <c r="I48" s="70"/>
       <c r="J48" s="71"/>
       <c r="K48" s="72"/>
@@ -22857,15 +23049,15 @@
       <c r="S48" s="55"/>
       <c r="T48" s="75">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="U48" s="75">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V48" s="75">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.25">
@@ -22876,7 +23068,9 @@
       <c r="B49" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="C49" s="70"/>
+      <c r="C49" s="70">
+        <v>10</v>
+      </c>
       <c r="D49" s="70"/>
       <c r="E49" s="70"/>
       <c r="F49" s="70"/>
@@ -22899,11 +23093,11 @@
       </c>
       <c r="U49" s="75">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="V49" s="75">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="50" spans="1:22" x14ac:dyDescent="0.25">
@@ -22952,7 +23146,9 @@
       <c r="B51" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="C51" s="65"/>
+      <c r="C51" s="65">
+        <v>34</v>
+      </c>
       <c r="D51" s="65"/>
       <c r="E51" s="65"/>
       <c r="F51" s="65"/>
@@ -22975,11 +23171,11 @@
       </c>
       <c r="U51" s="77">
         <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="V51" s="77">
         <f>U51/6</f>
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.25">
@@ -23028,7 +23224,9 @@
       <c r="B53" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C53" s="70"/>
+      <c r="C53" s="70">
+        <v>6</v>
+      </c>
       <c r="D53" s="70"/>
       <c r="E53" s="70"/>
       <c r="F53" s="70"/>
@@ -23042,7 +23240,9 @@
       <c r="N53" s="74"/>
       <c r="O53" s="70"/>
       <c r="P53" s="71"/>
-      <c r="Q53" s="71"/>
+      <c r="Q53" s="71">
+        <v>1</v>
+      </c>
       <c r="R53" s="72"/>
       <c r="S53" s="55"/>
       <c r="T53" s="75">
@@ -23051,11 +23251,11 @@
       </c>
       <c r="U53" s="75">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="V53" s="75">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.25">
@@ -23181,7 +23381,7 @@
       </c>
       <c r="C58" s="2">
         <f>SUM(C7:C57)</f>
-        <v>0</v>
+        <v>50328</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" s="2"/>
@@ -23195,56 +23395,56 @@
       </c>
       <c r="H58" s="2">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1193</v>
       </c>
       <c r="I58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="J58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="K58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>470</v>
       </c>
       <c r="M58" s="5">
         <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
-        <v>0</v>
+        <v>493</v>
       </c>
       <c r="N58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>246</v>
       </c>
       <c r="P58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>722</v>
       </c>
       <c r="R58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S58" s="55"/>
       <c r="T58" s="4">
         <f>SUM(T7:T57)</f>
-        <v>0</v>
+        <v>1816</v>
       </c>
       <c r="U58" s="90">
         <f>SUM(U7:U57)</f>
-        <v>0</v>
+        <v>388348</v>
       </c>
       <c r="V58" s="4">
         <f>SUM(V7:V57)</f>
-        <v>0</v>
+        <v>51933.166666666664</v>
       </c>
     </row>
     <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -23532,7 +23732,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E90C1C8C-E747-496B-BE70-EA58545B1CAD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7D7CD48-36B7-4216-A88E-17673474B053}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -23589,7 +23789,7 @@
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -26471,7 +26671,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{650CA8C6-0E34-4041-83EB-8BD8B22ACF90}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E90C1C8C-E747-496B-BE70-EA58545B1CAD}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -26528,7 +26728,7 @@
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>

--- a/GBDS AUGUST FILES 2026/INVENTORY COUNT SHEET - AUGUST 2026.xlsx
+++ b/GBDS AUGUST FILES 2026/INVENTORY COUNT SHEET - AUGUST 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS AUGUST FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E66F9281-EDAB-48DE-B770-542CE2C2687C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B9CAC04-B304-49B3-991A-3E29C7E97859}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="3" activeTab="7" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="3" activeTab="9" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
   </bookViews>
   <sheets>
     <sheet name="SAMPLE" sheetId="32" r:id="rId1"/>
@@ -7852,13 +7852,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
     <mergeCell ref="C60:K60"/>
     <mergeCell ref="I1:U1"/>
     <mergeCell ref="C4:K4"/>
     <mergeCell ref="T4:T5"/>
     <mergeCell ref="U4:U5"/>
-    <mergeCell ref="V4:V5"/>
-    <mergeCell ref="J5:K5"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -10791,13 +10791,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
     <mergeCell ref="C60:K60"/>
     <mergeCell ref="I1:U1"/>
     <mergeCell ref="C4:K4"/>
     <mergeCell ref="T4:T5"/>
     <mergeCell ref="U4:U5"/>
-    <mergeCell ref="V4:V5"/>
-    <mergeCell ref="J5:K5"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -13730,13 +13730,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
     <mergeCell ref="C60:K60"/>
     <mergeCell ref="I1:U1"/>
     <mergeCell ref="C4:K4"/>
     <mergeCell ref="T4:T5"/>
     <mergeCell ref="U4:U5"/>
-    <mergeCell ref="V4:V5"/>
-    <mergeCell ref="J5:K5"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -16669,13 +16669,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
     <mergeCell ref="C60:K60"/>
     <mergeCell ref="I1:U1"/>
     <mergeCell ref="C4:K4"/>
     <mergeCell ref="T4:T5"/>
     <mergeCell ref="U4:U5"/>
-    <mergeCell ref="V4:V5"/>
-    <mergeCell ref="J5:K5"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -38878,34 +38878,44 @@
       <c r="B7" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="52"/>
+      <c r="C7" s="52">
+        <v>32</v>
+      </c>
       <c r="D7" s="52"/>
       <c r="E7" s="52"/>
       <c r="F7" s="52"/>
       <c r="G7" s="52"/>
       <c r="H7" s="52"/>
-      <c r="I7" s="52"/>
+      <c r="I7" s="52">
+        <v>3</v>
+      </c>
       <c r="J7" s="53"/>
-      <c r="K7" s="54"/>
+      <c r="K7" s="54">
+        <v>6</v>
+      </c>
       <c r="L7" s="55"/>
       <c r="M7" s="56"/>
       <c r="N7" s="57"/>
-      <c r="O7" s="52"/>
+      <c r="O7" s="52">
+        <v>1</v>
+      </c>
       <c r="P7" s="53"/>
-      <c r="Q7" s="53"/>
+      <c r="Q7" s="53">
+        <v>1</v>
+      </c>
       <c r="R7" s="54"/>
       <c r="S7" s="55"/>
       <c r="T7" s="58">
         <f>H7+I7+J7+K7+N7+P7+R7</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="U7" s="58">
         <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
-        <v>0</v>
+        <v>825</v>
       </c>
       <c r="V7" s="58">
         <f>U7/24</f>
-        <v>0</v>
+        <v>34.375</v>
       </c>
       <c r="W7" s="50"/>
       <c r="AF7" s="12"/>
@@ -38940,7 +38950,10 @@
       <c r="B8" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="59"/>
+      <c r="C8" s="59">
+        <f>41+43</f>
+        <v>84</v>
+      </c>
       <c r="D8" s="59"/>
       <c r="E8" s="59"/>
       <c r="F8" s="59"/>
@@ -38950,24 +38963,32 @@
       <c r="J8" s="60"/>
       <c r="K8" s="61"/>
       <c r="L8" s="62"/>
-      <c r="M8" s="63"/>
+      <c r="M8" s="63">
+        <v>1</v>
+      </c>
       <c r="N8" s="64"/>
-      <c r="O8" s="65"/>
-      <c r="P8" s="66"/>
-      <c r="Q8" s="66"/>
+      <c r="O8" s="65">
+        <v>1</v>
+      </c>
+      <c r="P8" s="66">
+        <v>12</v>
+      </c>
+      <c r="Q8" s="66">
+        <v>1</v>
+      </c>
       <c r="R8" s="67"/>
       <c r="S8" s="62"/>
       <c r="T8" s="68">
         <f t="shared" ref="T8:T41" si="0">H8+I8+J8+K8+N8+P8+R8</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="U8" s="69">
         <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="V8" s="69">
         <f>U8/24</f>
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="W8" s="50"/>
       <c r="AF8" s="12"/>
@@ -39002,7 +39023,10 @@
       <c r="B9" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="70"/>
+      <c r="C9" s="70">
+        <f>60+30</f>
+        <v>90</v>
+      </c>
       <c r="D9" s="70"/>
       <c r="E9" s="70"/>
       <c r="F9" s="70"/>
@@ -39014,7 +39038,9 @@
       <c r="L9" s="55"/>
       <c r="M9" s="73"/>
       <c r="N9" s="74"/>
-      <c r="O9" s="70"/>
+      <c r="O9" s="70">
+        <v>1</v>
+      </c>
       <c r="P9" s="71"/>
       <c r="Q9" s="71"/>
       <c r="R9" s="72"/>
@@ -39025,11 +39051,11 @@
       </c>
       <c r="U9" s="76">
         <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
-        <v>0</v>
+        <v>2184</v>
       </c>
       <c r="V9" s="76">
         <f t="shared" ref="V9:V11" si="3">U9/24</f>
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="W9" s="50"/>
       <c r="AF9" s="12"/>
@@ -39064,7 +39090,10 @@
       <c r="B10" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="C10" s="70"/>
+      <c r="C10" s="70">
+        <f>36+10</f>
+        <v>46</v>
+      </c>
       <c r="D10" s="70"/>
       <c r="E10" s="70"/>
       <c r="F10" s="70"/>
@@ -39087,11 +39116,11 @@
       </c>
       <c r="U10" s="58">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1104</v>
       </c>
       <c r="V10" s="58">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="W10" s="50"/>
       <c r="AF10" s="12"/>
@@ -39126,7 +39155,9 @@
       <c r="B11" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="70"/>
+      <c r="C11" s="70">
+        <v>9</v>
+      </c>
       <c r="D11" s="70"/>
       <c r="E11" s="70"/>
       <c r="F11" s="70"/>
@@ -39134,7 +39165,9 @@
       <c r="H11" s="70"/>
       <c r="I11" s="70"/>
       <c r="J11" s="71"/>
-      <c r="K11" s="72"/>
+      <c r="K11" s="72">
+        <v>2</v>
+      </c>
       <c r="L11" s="55"/>
       <c r="M11" s="73"/>
       <c r="N11" s="74"/>
@@ -39145,15 +39178,15 @@
       <c r="S11" s="55"/>
       <c r="T11" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U11" s="58">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="V11" s="58">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>9.0833333333333339</v>
       </c>
       <c r="AF11" s="12"/>
       <c r="AG11" s="12"/>
@@ -39186,7 +39219,10 @@
       <c r="B12" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="59"/>
+      <c r="C12" s="59">
+        <f>1224+53+936+33+1080+29</f>
+        <v>3355</v>
+      </c>
       <c r="D12" s="59"/>
       <c r="E12" s="59"/>
       <c r="F12" s="59"/>
@@ -39196,24 +39232,36 @@
       <c r="J12" s="60"/>
       <c r="K12" s="61"/>
       <c r="L12" s="62"/>
-      <c r="M12" s="63"/>
-      <c r="N12" s="64"/>
-      <c r="O12" s="65"/>
-      <c r="P12" s="66"/>
-      <c r="Q12" s="66"/>
-      <c r="R12" s="67"/>
+      <c r="M12" s="63">
+        <v>9</v>
+      </c>
+      <c r="N12" s="64">
+        <v>10</v>
+      </c>
+      <c r="O12" s="65">
+        <v>10</v>
+      </c>
+      <c r="P12" s="66">
+        <v>13</v>
+      </c>
+      <c r="Q12" s="66">
+        <v>18</v>
+      </c>
+      <c r="R12" s="67">
+        <v>1</v>
+      </c>
       <c r="S12" s="62"/>
       <c r="T12" s="69">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="U12" s="69">
         <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
-        <v>0</v>
+        <v>81432</v>
       </c>
       <c r="V12" s="69">
         <f>U12/24</f>
-        <v>0</v>
+        <v>3393</v>
       </c>
       <c r="W12" s="9"/>
       <c r="X12" s="9"/>
@@ -39255,12 +39303,16 @@
       <c r="B13" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="70"/>
+      <c r="C13" s="70">
+        <v>2</v>
+      </c>
       <c r="D13" s="70"/>
       <c r="E13" s="70"/>
       <c r="F13" s="70"/>
       <c r="G13" s="70"/>
-      <c r="H13" s="70"/>
+      <c r="H13" s="70">
+        <v>16</v>
+      </c>
       <c r="I13" s="70"/>
       <c r="J13" s="71"/>
       <c r="K13" s="72"/>
@@ -39274,15 +39326,15 @@
       <c r="S13" s="55"/>
       <c r="T13" s="76">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="U13" s="76">
         <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="V13" s="76">
         <f>U13/24</f>
-        <v>0</v>
+        <v>2.6666666666666665</v>
       </c>
       <c r="AF13" s="12"/>
       <c r="AG13" s="12"/>
@@ -39316,7 +39368,9 @@
       <c r="B14" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="70"/>
+      <c r="C14" s="70">
+        <v>2</v>
+      </c>
       <c r="D14" s="70"/>
       <c r="E14" s="70"/>
       <c r="F14" s="70"/>
@@ -39339,11 +39393,11 @@
       </c>
       <c r="U14" s="75">
         <f t="shared" ref="U14:U36" si="4">C14*24+M14*24+O14*24+Q14*24+T14</f>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V14" s="75">
         <f t="shared" ref="V14:V36" si="5">U14/24</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF14" s="12"/>
       <c r="AG14" s="12"/>
@@ -39504,7 +39558,10 @@
       <c r="E17" s="70"/>
       <c r="F17" s="70"/>
       <c r="G17" s="70"/>
-      <c r="H17" s="70"/>
+      <c r="H17" s="70">
+        <f>24*3</f>
+        <v>72</v>
+      </c>
       <c r="I17" s="70"/>
       <c r="J17" s="71"/>
       <c r="K17" s="72"/>
@@ -39518,15 +39575,15 @@
       <c r="S17" s="55"/>
       <c r="T17" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="U17" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="V17" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF17" s="12"/>
       <c r="AG17" s="12"/>
@@ -39620,12 +39677,17 @@
       <c r="B19" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="C19" s="70"/>
+      <c r="C19" s="70">
+        <v>2</v>
+      </c>
       <c r="D19" s="70"/>
       <c r="E19" s="70"/>
       <c r="F19" s="70"/>
       <c r="G19" s="70"/>
-      <c r="H19" s="70"/>
+      <c r="H19" s="70">
+        <f>24+20</f>
+        <v>44</v>
+      </c>
       <c r="I19" s="70"/>
       <c r="J19" s="71"/>
       <c r="K19" s="72"/>
@@ -39639,15 +39701,15 @@
       <c r="S19" s="55"/>
       <c r="T19" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="U19" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="V19" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3.8333333333333335</v>
       </c>
       <c r="AF19" s="12"/>
       <c r="AG19" s="12"/>
@@ -39681,7 +39743,9 @@
       <c r="B20" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="70"/>
+      <c r="C20" s="70">
+        <v>5</v>
+      </c>
       <c r="D20" s="70"/>
       <c r="E20" s="70"/>
       <c r="F20" s="70"/>
@@ -39704,11 +39768,11 @@
       </c>
       <c r="U20" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="V20" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AF20" s="12"/>
       <c r="AG20" s="12"/>
@@ -39747,7 +39811,10 @@
       <c r="E21" s="70"/>
       <c r="F21" s="70"/>
       <c r="G21" s="70"/>
-      <c r="H21" s="70"/>
+      <c r="H21" s="70">
+        <f>24*2</f>
+        <v>48</v>
+      </c>
       <c r="I21" s="70"/>
       <c r="J21" s="71"/>
       <c r="K21" s="72"/>
@@ -39761,15 +39828,15 @@
       <c r="S21" s="55"/>
       <c r="T21" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="U21" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V21" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF21" s="12"/>
       <c r="AG21" s="12"/>
@@ -39803,13 +39870,17 @@
       <c r="B22" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="C22" s="70"/>
+      <c r="C22" s="70">
+        <v>2</v>
+      </c>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
       <c r="G22" s="70"/>
       <c r="H22" s="70"/>
-      <c r="I22" s="70"/>
+      <c r="I22" s="70">
+        <v>20</v>
+      </c>
       <c r="J22" s="71"/>
       <c r="K22" s="72"/>
       <c r="L22" s="55"/>
@@ -39822,15 +39893,15 @@
       <c r="S22" s="55"/>
       <c r="T22" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="U22" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="V22" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2.8333333333333335</v>
       </c>
       <c r="W22" s="9"/>
       <c r="X22" s="9"/>
@@ -39878,7 +39949,10 @@
       <c r="E23" s="70"/>
       <c r="F23" s="70"/>
       <c r="G23" s="70"/>
-      <c r="H23" s="70"/>
+      <c r="H23" s="70">
+        <f>37*24+19</f>
+        <v>907</v>
+      </c>
       <c r="I23" s="70"/>
       <c r="J23" s="71"/>
       <c r="K23" s="72"/>
@@ -39892,15 +39966,15 @@
       <c r="S23" s="55"/>
       <c r="T23" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>907</v>
       </c>
       <c r="U23" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>907</v>
       </c>
       <c r="V23" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>37.791666666666664</v>
       </c>
       <c r="W23" s="9"/>
       <c r="X23" s="9"/>
@@ -39943,12 +40017,17 @@
       <c r="B24" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="C24" s="70"/>
+      <c r="C24" s="70">
+        <v>2</v>
+      </c>
       <c r="D24" s="70"/>
       <c r="E24" s="70"/>
       <c r="F24" s="70"/>
       <c r="G24" s="70"/>
-      <c r="H24" s="70"/>
+      <c r="H24" s="70">
+        <f>24*3</f>
+        <v>72</v>
+      </c>
       <c r="I24" s="70"/>
       <c r="J24" s="71"/>
       <c r="K24" s="72"/>
@@ -39962,15 +40041,15 @@
       <c r="S24" s="55"/>
       <c r="T24" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="U24" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="V24" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AF24" s="12"/>
       <c r="AG24" s="12"/>
@@ -40004,34 +40083,44 @@
       <c r="B25" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="C25" s="70"/>
+      <c r="C25" s="70">
+        <v>51</v>
+      </c>
       <c r="D25" s="70"/>
       <c r="E25" s="70"/>
       <c r="F25" s="70"/>
       <c r="G25" s="70"/>
       <c r="H25" s="70"/>
       <c r="I25" s="70"/>
-      <c r="J25" s="71"/>
+      <c r="J25" s="71">
+        <v>1</v>
+      </c>
       <c r="K25" s="72"/>
       <c r="L25" s="55"/>
-      <c r="M25" s="73"/>
+      <c r="M25" s="73">
+        <v>1</v>
+      </c>
       <c r="N25" s="74"/>
-      <c r="O25" s="70"/>
+      <c r="O25" s="70">
+        <v>1</v>
+      </c>
       <c r="P25" s="71"/>
-      <c r="Q25" s="71"/>
+      <c r="Q25" s="71">
+        <v>2</v>
+      </c>
       <c r="R25" s="72"/>
       <c r="S25" s="55"/>
       <c r="T25" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U25" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1321</v>
       </c>
       <c r="V25" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>55.041666666666664</v>
       </c>
       <c r="AY25" s="14" t="e">
         <f>#REF!-AY24</f>
@@ -40051,7 +40140,10 @@
       <c r="E26" s="70"/>
       <c r="F26" s="70"/>
       <c r="G26" s="70"/>
-      <c r="H26" s="70"/>
+      <c r="H26" s="70">
+        <f>5*24</f>
+        <v>120</v>
+      </c>
       <c r="I26" s="70"/>
       <c r="J26" s="71"/>
       <c r="K26" s="72"/>
@@ -40065,15 +40157,15 @@
       <c r="S26" s="55"/>
       <c r="T26" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="U26" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="V26" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W26" s="9"/>
       <c r="X26" s="9"/>
@@ -40093,7 +40185,9 @@
       <c r="B27" s="26" t="s">
         <v>69</v>
       </c>
-      <c r="C27" s="70"/>
+      <c r="C27" s="70">
+        <v>3</v>
+      </c>
       <c r="D27" s="70"/>
       <c r="E27" s="70"/>
       <c r="F27" s="70"/>
@@ -40116,11 +40210,11 @@
       </c>
       <c r="U27" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="V27" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W27" s="9"/>
       <c r="X27" s="9"/>
@@ -40154,7 +40248,9 @@
       <c r="N28" s="74"/>
       <c r="O28" s="70"/>
       <c r="P28" s="71"/>
-      <c r="Q28" s="71"/>
+      <c r="Q28" s="71">
+        <v>3</v>
+      </c>
       <c r="R28" s="72"/>
       <c r="S28" s="55"/>
       <c r="T28" s="58">
@@ -40163,11 +40259,11 @@
       </c>
       <c r="U28" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="V28" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W28" s="9"/>
       <c r="X28" s="9"/>
@@ -40187,13 +40283,17 @@
       <c r="B29" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="C29" s="70"/>
+      <c r="C29" s="70">
+        <v>27</v>
+      </c>
       <c r="D29" s="70"/>
       <c r="E29" s="70"/>
       <c r="F29" s="70"/>
       <c r="G29" s="70"/>
       <c r="H29" s="70"/>
-      <c r="I29" s="70"/>
+      <c r="I29" s="70">
+        <v>5</v>
+      </c>
       <c r="J29" s="71"/>
       <c r="K29" s="72"/>
       <c r="L29" s="55"/>
@@ -40201,20 +40301,22 @@
       <c r="N29" s="74"/>
       <c r="O29" s="70"/>
       <c r="P29" s="71"/>
-      <c r="Q29" s="71"/>
+      <c r="Q29" s="71">
+        <v>1</v>
+      </c>
       <c r="R29" s="72"/>
       <c r="S29" s="55"/>
       <c r="T29" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U29" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>677</v>
       </c>
       <c r="V29" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>28.208333333333332</v>
       </c>
     </row>
     <row r="30" spans="1:54" x14ac:dyDescent="0.25">
@@ -40225,7 +40327,9 @@
       <c r="B30" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="C30" s="70"/>
+      <c r="C30" s="70">
+        <v>13</v>
+      </c>
       <c r="D30" s="70"/>
       <c r="E30" s="70"/>
       <c r="F30" s="70"/>
@@ -40237,9 +40341,13 @@
       <c r="L30" s="55"/>
       <c r="M30" s="73"/>
       <c r="N30" s="74"/>
-      <c r="O30" s="70"/>
+      <c r="O30" s="70">
+        <v>1</v>
+      </c>
       <c r="P30" s="71"/>
-      <c r="Q30" s="71"/>
+      <c r="Q30" s="71">
+        <v>1</v>
+      </c>
       <c r="R30" s="72"/>
       <c r="S30" s="55"/>
       <c r="T30" s="58">
@@ -40248,11 +40356,11 @@
       </c>
       <c r="U30" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="V30" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31" spans="1:54" x14ac:dyDescent="0.25">
@@ -40263,7 +40371,9 @@
       <c r="B31" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="C31" s="70"/>
+      <c r="C31" s="70">
+        <v>2</v>
+      </c>
       <c r="D31" s="70"/>
       <c r="E31" s="70"/>
       <c r="F31" s="70"/>
@@ -40286,11 +40396,11 @@
       </c>
       <c r="U31" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V31" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:54" x14ac:dyDescent="0.25">
@@ -40339,7 +40449,9 @@
       <c r="B33" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="C33" s="70"/>
+      <c r="C33" s="70">
+        <v>1</v>
+      </c>
       <c r="D33" s="70"/>
       <c r="E33" s="70"/>
       <c r="F33" s="70"/>
@@ -40349,7 +40461,9 @@
       <c r="J33" s="71"/>
       <c r="K33" s="72"/>
       <c r="L33" s="55"/>
-      <c r="M33" s="73"/>
+      <c r="M33" s="73">
+        <v>1</v>
+      </c>
       <c r="N33" s="74"/>
       <c r="O33" s="70"/>
       <c r="P33" s="71"/>
@@ -40362,11 +40476,11 @@
       </c>
       <c r="U33" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V33" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:23" x14ac:dyDescent="0.25">
@@ -40377,34 +40491,45 @@
       <c r="B34" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="C34" s="70"/>
+      <c r="C34" s="70">
+        <f>144+46</f>
+        <v>190</v>
+      </c>
       <c r="D34" s="70"/>
       <c r="E34" s="70"/>
       <c r="F34" s="70"/>
       <c r="G34" s="70"/>
       <c r="H34" s="70"/>
-      <c r="I34" s="70"/>
+      <c r="I34" s="70">
+        <v>1</v>
+      </c>
       <c r="J34" s="71"/>
-      <c r="K34" s="72"/>
+      <c r="K34" s="72">
+        <v>1</v>
+      </c>
       <c r="L34" s="55"/>
       <c r="M34" s="73"/>
       <c r="N34" s="74"/>
-      <c r="O34" s="70"/>
+      <c r="O34" s="70">
+        <v>2</v>
+      </c>
       <c r="P34" s="71"/>
-      <c r="Q34" s="71"/>
+      <c r="Q34" s="71">
+        <v>2</v>
+      </c>
       <c r="R34" s="72"/>
       <c r="S34" s="55"/>
       <c r="T34" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U34" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4658</v>
       </c>
       <c r="V34" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>194.08333333333334</v>
       </c>
     </row>
     <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -40491,34 +40616,52 @@
       <c r="B37" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="C37" s="59"/>
+      <c r="C37" s="59">
+        <f>108+3132+94</f>
+        <v>3334</v>
+      </c>
       <c r="D37" s="59"/>
       <c r="E37" s="59"/>
       <c r="F37" s="59"/>
       <c r="G37" s="59"/>
-      <c r="H37" s="59"/>
-      <c r="I37" s="59"/>
-      <c r="J37" s="60"/>
-      <c r="K37" s="61"/>
+      <c r="H37" s="59">
+        <v>1</v>
+      </c>
+      <c r="I37" s="59">
+        <v>2</v>
+      </c>
+      <c r="J37" s="60">
+        <v>2</v>
+      </c>
+      <c r="K37" s="61">
+        <f>6+2</f>
+        <v>8</v>
+      </c>
       <c r="L37" s="62"/>
-      <c r="M37" s="63"/>
+      <c r="M37" s="63">
+        <v>20</v>
+      </c>
       <c r="N37" s="64"/>
-      <c r="O37" s="65"/>
+      <c r="O37" s="65">
+        <v>36</v>
+      </c>
       <c r="P37" s="66"/>
-      <c r="Q37" s="66"/>
+      <c r="Q37" s="66">
+        <v>65</v>
+      </c>
       <c r="R37" s="67"/>
       <c r="S37" s="62"/>
       <c r="T37" s="77">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="U37" s="77">
         <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
-        <v>0</v>
+        <v>20743</v>
       </c>
       <c r="V37" s="77">
         <f>U37/6</f>
-        <v>0</v>
+        <v>3457.1666666666665</v>
       </c>
       <c r="W37" s="50"/>
     </row>
@@ -40535,7 +40678,10 @@
       <c r="E38" s="70"/>
       <c r="F38" s="70"/>
       <c r="G38" s="70"/>
-      <c r="H38" s="70"/>
+      <c r="H38" s="70">
+        <f>24*5</f>
+        <v>120</v>
+      </c>
       <c r="I38" s="70"/>
       <c r="J38" s="71"/>
       <c r="K38" s="72"/>
@@ -40549,15 +40695,15 @@
       <c r="S38" s="55"/>
       <c r="T38" s="75">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="U38" s="75">
         <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="V38" s="75">
         <f>U38/24</f>
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39" spans="1:23" x14ac:dyDescent="0.25">
@@ -40606,34 +40752,46 @@
       <c r="B40" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="C40" s="59"/>
+      <c r="C40" s="59">
+        <f>63+50</f>
+        <v>113</v>
+      </c>
       <c r="D40" s="59"/>
       <c r="E40" s="59"/>
       <c r="F40" s="59"/>
       <c r="G40" s="59"/>
-      <c r="H40" s="59"/>
+      <c r="H40" s="59">
+        <f>252*24</f>
+        <v>6048</v>
+      </c>
       <c r="I40" s="59"/>
       <c r="J40" s="60"/>
-      <c r="K40" s="61"/>
+      <c r="K40" s="61">
+        <v>20</v>
+      </c>
       <c r="L40" s="62"/>
       <c r="M40" s="63"/>
       <c r="N40" s="64"/>
-      <c r="O40" s="65"/>
+      <c r="O40" s="65">
+        <v>2</v>
+      </c>
       <c r="P40" s="66"/>
-      <c r="Q40" s="66"/>
+      <c r="Q40" s="66">
+        <v>3</v>
+      </c>
       <c r="R40" s="67"/>
       <c r="S40" s="62"/>
       <c r="T40" s="77">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>6068</v>
       </c>
       <c r="U40" s="77">
         <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
-        <v>0</v>
+        <v>8900</v>
       </c>
       <c r="V40" s="77">
         <f>U40/24</f>
-        <v>0</v>
+        <v>370.83333333333331</v>
       </c>
     </row>
     <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -40649,7 +40807,10 @@
       <c r="E41" s="82"/>
       <c r="F41" s="82"/>
       <c r="G41" s="82"/>
-      <c r="H41" s="82"/>
+      <c r="H41" s="82">
+        <f>576*12</f>
+        <v>6912</v>
+      </c>
       <c r="I41" s="82"/>
       <c r="J41" s="83"/>
       <c r="K41" s="84"/>
@@ -40663,15 +40824,15 @@
       <c r="S41" s="85"/>
       <c r="T41" s="88">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>6912</v>
       </c>
       <c r="U41" s="88">
         <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
-        <v>0</v>
+        <v>6912</v>
       </c>
       <c r="V41" s="88">
         <f>U41/12</f>
-        <v>0</v>
+        <v>576</v>
       </c>
     </row>
     <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -40711,34 +40872,53 @@
       <c r="B43" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="C43" s="65"/>
+      <c r="C43" s="65">
+        <f>49+7344+19764+10260+756</f>
+        <v>38173</v>
+      </c>
       <c r="D43" s="65"/>
       <c r="E43" s="65"/>
       <c r="F43" s="65"/>
       <c r="G43" s="65"/>
-      <c r="H43" s="65"/>
-      <c r="I43" s="65"/>
-      <c r="J43" s="66"/>
-      <c r="K43" s="67"/>
+      <c r="H43" s="65">
+        <v>13</v>
+      </c>
+      <c r="I43" s="65">
+        <v>12</v>
+      </c>
+      <c r="J43" s="66">
+        <f>17*6</f>
+        <v>102</v>
+      </c>
+      <c r="K43" s="67">
+        <f>71*6+2</f>
+        <v>428</v>
+      </c>
       <c r="L43" s="62"/>
-      <c r="M43" s="63"/>
+      <c r="M43" s="63">
+        <v>350</v>
+      </c>
       <c r="N43" s="64"/>
-      <c r="O43" s="65"/>
+      <c r="O43" s="65">
+        <v>430</v>
+      </c>
       <c r="P43" s="66"/>
-      <c r="Q43" s="66"/>
+      <c r="Q43" s="66">
+        <v>522</v>
+      </c>
       <c r="R43" s="67"/>
       <c r="S43" s="62"/>
       <c r="T43" s="77">
         <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
-        <v>0</v>
+        <v>555</v>
       </c>
       <c r="U43" s="77">
         <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
-        <v>0</v>
+        <v>237405</v>
       </c>
       <c r="V43" s="77">
         <f>U43/6</f>
-        <v>0</v>
+        <v>39567.5</v>
       </c>
     </row>
     <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -40783,7 +40963,10 @@
       <c r="E45" s="70"/>
       <c r="F45" s="70"/>
       <c r="G45" s="70"/>
-      <c r="H45" s="70"/>
+      <c r="H45" s="70">
+        <f>5*24</f>
+        <v>120</v>
+      </c>
       <c r="I45" s="70"/>
       <c r="J45" s="71"/>
       <c r="K45" s="72"/>
@@ -40797,15 +40980,15 @@
       <c r="S45" s="55"/>
       <c r="T45" s="75">
         <f t="shared" ref="T45:T54" si="7">H45+I45+J45+K45+N45+P45+R45</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="U45" s="75">
         <f>C45*24+M45*24+O45*24+Q45*24+T45</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="V45" s="75">
         <f>U45/24</f>
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46" spans="1:23" x14ac:dyDescent="0.25">
@@ -40854,34 +41037,49 @@
       <c r="B47" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="C47" s="65"/>
+      <c r="C47" s="65">
+        <f>106+648+324+88+540+103+324+432+106</f>
+        <v>2671</v>
+      </c>
       <c r="D47" s="65"/>
       <c r="E47" s="65"/>
       <c r="F47" s="65"/>
       <c r="G47" s="65"/>
-      <c r="H47" s="65"/>
+      <c r="H47" s="65">
+        <v>1</v>
+      </c>
       <c r="I47" s="65"/>
       <c r="J47" s="66"/>
-      <c r="K47" s="67"/>
+      <c r="K47" s="67">
+        <v>5</v>
+      </c>
       <c r="L47" s="62"/>
-      <c r="M47" s="63"/>
+      <c r="M47" s="63">
+        <v>3</v>
+      </c>
       <c r="N47" s="64"/>
-      <c r="O47" s="65"/>
+      <c r="O47" s="65">
+        <v>16</v>
+      </c>
       <c r="P47" s="66"/>
-      <c r="Q47" s="66"/>
-      <c r="R47" s="67"/>
+      <c r="Q47" s="66">
+        <v>5</v>
+      </c>
+      <c r="R47" s="67">
+        <v>3</v>
+      </c>
       <c r="S47" s="62"/>
       <c r="T47" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="U47" s="77">
         <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
-        <v>0</v>
+        <v>16179</v>
       </c>
       <c r="V47" s="77">
         <f>U47/6</f>
-        <v>0</v>
+        <v>2696.5</v>
       </c>
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.25">
@@ -40897,7 +41095,9 @@
       <c r="E48" s="70"/>
       <c r="F48" s="70"/>
       <c r="G48" s="70"/>
-      <c r="H48" s="70"/>
+      <c r="H48" s="70">
+        <v>24</v>
+      </c>
       <c r="I48" s="70"/>
       <c r="J48" s="71"/>
       <c r="K48" s="72"/>
@@ -40911,15 +41111,15 @@
       <c r="S48" s="55"/>
       <c r="T48" s="75">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="U48" s="75">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V48" s="75">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.25">
@@ -40930,7 +41130,9 @@
       <c r="B49" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="C49" s="70"/>
+      <c r="C49" s="70">
+        <v>10</v>
+      </c>
       <c r="D49" s="70"/>
       <c r="E49" s="70"/>
       <c r="F49" s="70"/>
@@ -40953,11 +41155,11 @@
       </c>
       <c r="U49" s="75">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="V49" s="75">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="50" spans="1:22" x14ac:dyDescent="0.25">
@@ -41006,7 +41208,9 @@
       <c r="B51" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="C51" s="65"/>
+      <c r="C51" s="65">
+        <v>34</v>
+      </c>
       <c r="D51" s="65"/>
       <c r="E51" s="65"/>
       <c r="F51" s="65"/>
@@ -41029,11 +41233,11 @@
       </c>
       <c r="U51" s="77">
         <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="V51" s="77">
         <f>U51/6</f>
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.25">
@@ -41082,7 +41286,10 @@
       <c r="B53" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C53" s="70"/>
+      <c r="C53" s="70">
+        <f>6+1</f>
+        <v>7</v>
+      </c>
       <c r="D53" s="70"/>
       <c r="E53" s="70"/>
       <c r="F53" s="70"/>
@@ -41105,11 +41312,11 @@
       </c>
       <c r="U53" s="75">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="V53" s="75">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.25">
@@ -41235,7 +41442,7 @@
       </c>
       <c r="C58" s="2">
         <f>SUM(C7:C57)</f>
-        <v>0</v>
+        <v>48260</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" s="2"/>
@@ -41249,56 +41456,56 @@
       </c>
       <c r="H58" s="2">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>14518</v>
       </c>
       <c r="I58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="J58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="K58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>470</v>
       </c>
       <c r="M58" s="5">
         <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
-        <v>0</v>
+        <v>385</v>
       </c>
       <c r="N58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>501</v>
       </c>
       <c r="P58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="Q58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>624</v>
       </c>
       <c r="R58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S58" s="55"/>
       <c r="T58" s="4">
         <f>SUM(T7:T57)</f>
-        <v>0</v>
+        <v>15175</v>
       </c>
       <c r="U58" s="90">
         <f>SUM(U7:U57)</f>
-        <v>0</v>
+        <v>387793</v>
       </c>
       <c r="V58" s="4">
         <f>SUM(V7:V57)</f>
-        <v>0</v>
+        <v>50762.416666666672</v>
       </c>
     </row>
     <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>

--- a/GBDS AUGUST FILES 2026/INVENTORY COUNT SHEET - AUGUST 2026.xlsx
+++ b/GBDS AUGUST FILES 2026/INVENTORY COUNT SHEET - AUGUST 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS AUGUST FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B9CAC04-B304-49B3-991A-3E29C7E97859}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EFD1ACB-6144-4C6C-8039-8981B06D792A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="3" activeTab="9" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
   </bookViews>
@@ -5162,34 +5162,42 @@
       <c r="B7" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="52"/>
+      <c r="C7" s="52">
+        <v>32</v>
+      </c>
       <c r="D7" s="52"/>
       <c r="E7" s="52"/>
       <c r="F7" s="52"/>
       <c r="G7" s="52"/>
       <c r="H7" s="52"/>
-      <c r="I7" s="52"/>
+      <c r="I7" s="52">
+        <v>3</v>
+      </c>
       <c r="J7" s="53"/>
-      <c r="K7" s="54"/>
+      <c r="K7" s="54">
+        <v>6</v>
+      </c>
       <c r="L7" s="55"/>
       <c r="M7" s="56"/>
       <c r="N7" s="57"/>
-      <c r="O7" s="52"/>
+      <c r="O7" s="52">
+        <v>1</v>
+      </c>
       <c r="P7" s="53"/>
       <c r="Q7" s="53"/>
       <c r="R7" s="54"/>
       <c r="S7" s="55"/>
       <c r="T7" s="58">
         <f>H7+I7+J7+K7+N7+P7+R7</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="U7" s="58">
         <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
-        <v>0</v>
+        <v>801</v>
       </c>
       <c r="V7" s="58">
         <f>U7/24</f>
-        <v>0</v>
+        <v>33.375</v>
       </c>
       <c r="W7" s="50"/>
       <c r="AF7" s="12"/>
@@ -5224,7 +5232,10 @@
       <c r="B8" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="59"/>
+      <c r="C8" s="59">
+        <f>41+43</f>
+        <v>84</v>
+      </c>
       <c r="D8" s="59"/>
       <c r="E8" s="59"/>
       <c r="F8" s="59"/>
@@ -5234,24 +5245,32 @@
       <c r="J8" s="60"/>
       <c r="K8" s="61"/>
       <c r="L8" s="62"/>
-      <c r="M8" s="63"/>
+      <c r="M8" s="63">
+        <v>1</v>
+      </c>
       <c r="N8" s="64"/>
-      <c r="O8" s="65"/>
-      <c r="P8" s="66"/>
-      <c r="Q8" s="66"/>
+      <c r="O8" s="65">
+        <v>1</v>
+      </c>
+      <c r="P8" s="66">
+        <v>12</v>
+      </c>
+      <c r="Q8" s="66">
+        <v>1</v>
+      </c>
       <c r="R8" s="67"/>
       <c r="S8" s="62"/>
       <c r="T8" s="68">
         <f t="shared" ref="T8:T41" si="0">H8+I8+J8+K8+N8+P8+R8</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="U8" s="69">
         <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="V8" s="69">
         <f>U8/24</f>
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="W8" s="50"/>
       <c r="AF8" s="12"/>
@@ -5286,7 +5305,10 @@
       <c r="B9" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="70"/>
+      <c r="C9" s="70">
+        <f>60+30</f>
+        <v>90</v>
+      </c>
       <c r="D9" s="70"/>
       <c r="E9" s="70"/>
       <c r="F9" s="70"/>
@@ -5298,7 +5320,9 @@
       <c r="L9" s="55"/>
       <c r="M9" s="73"/>
       <c r="N9" s="74"/>
-      <c r="O9" s="70"/>
+      <c r="O9" s="70">
+        <v>1</v>
+      </c>
       <c r="P9" s="71"/>
       <c r="Q9" s="71"/>
       <c r="R9" s="72"/>
@@ -5309,11 +5333,11 @@
       </c>
       <c r="U9" s="76">
         <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
-        <v>0</v>
+        <v>2184</v>
       </c>
       <c r="V9" s="76">
         <f t="shared" ref="V9:V11" si="3">U9/24</f>
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="W9" s="50"/>
       <c r="AF9" s="12"/>
@@ -5348,7 +5372,10 @@
       <c r="B10" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="C10" s="70"/>
+      <c r="C10" s="70">
+        <f>34+10</f>
+        <v>44</v>
+      </c>
       <c r="D10" s="70"/>
       <c r="E10" s="70"/>
       <c r="F10" s="70"/>
@@ -5362,7 +5389,9 @@
       <c r="N10" s="74"/>
       <c r="O10" s="70"/>
       <c r="P10" s="71"/>
-      <c r="Q10" s="71"/>
+      <c r="Q10" s="71">
+        <v>2</v>
+      </c>
       <c r="R10" s="72"/>
       <c r="S10" s="55"/>
       <c r="T10" s="58">
@@ -5371,11 +5400,11 @@
       </c>
       <c r="U10" s="58">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1104</v>
       </c>
       <c r="V10" s="58">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="W10" s="50"/>
       <c r="AF10" s="12"/>
@@ -5410,7 +5439,9 @@
       <c r="B11" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="70"/>
+      <c r="C11" s="70">
+        <v>9</v>
+      </c>
       <c r="D11" s="70"/>
       <c r="E11" s="70"/>
       <c r="F11" s="70"/>
@@ -5418,7 +5449,9 @@
       <c r="H11" s="70"/>
       <c r="I11" s="70"/>
       <c r="J11" s="71"/>
-      <c r="K11" s="72"/>
+      <c r="K11" s="72">
+        <v>2</v>
+      </c>
       <c r="L11" s="55"/>
       <c r="M11" s="73"/>
       <c r="N11" s="74"/>
@@ -5429,15 +5462,15 @@
       <c r="S11" s="55"/>
       <c r="T11" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U11" s="58">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="V11" s="58">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>9.0833333333333339</v>
       </c>
       <c r="AF11" s="12"/>
       <c r="AG11" s="12"/>
@@ -5470,7 +5503,10 @@
       <c r="B12" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="59"/>
+      <c r="C12" s="59">
+        <f>1224+53+3+936+1080+29</f>
+        <v>3325</v>
+      </c>
       <c r="D12" s="59"/>
       <c r="E12" s="59"/>
       <c r="F12" s="59"/>
@@ -5480,24 +5516,32 @@
       <c r="J12" s="60"/>
       <c r="K12" s="61"/>
       <c r="L12" s="62"/>
-      <c r="M12" s="63"/>
+      <c r="M12" s="63">
+        <v>10</v>
+      </c>
       <c r="N12" s="64"/>
-      <c r="O12" s="65"/>
+      <c r="O12" s="65">
+        <v>10</v>
+      </c>
       <c r="P12" s="66"/>
-      <c r="Q12" s="66"/>
-      <c r="R12" s="67"/>
+      <c r="Q12" s="66">
+        <v>20</v>
+      </c>
+      <c r="R12" s="67">
+        <v>13</v>
+      </c>
       <c r="S12" s="62"/>
       <c r="T12" s="69">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="U12" s="69">
         <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
-        <v>0</v>
+        <v>80773</v>
       </c>
       <c r="V12" s="69">
         <f>U12/24</f>
-        <v>0</v>
+        <v>3365.5416666666665</v>
       </c>
       <c r="W12" s="9"/>
       <c r="X12" s="9"/>
@@ -5539,12 +5583,16 @@
       <c r="B13" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="70"/>
+      <c r="C13" s="70">
+        <v>2</v>
+      </c>
       <c r="D13" s="70"/>
       <c r="E13" s="70"/>
       <c r="F13" s="70"/>
       <c r="G13" s="70"/>
-      <c r="H13" s="70"/>
+      <c r="H13" s="70">
+        <v>16</v>
+      </c>
       <c r="I13" s="70"/>
       <c r="J13" s="71"/>
       <c r="K13" s="72"/>
@@ -5558,15 +5606,15 @@
       <c r="S13" s="55"/>
       <c r="T13" s="76">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="U13" s="76">
         <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="V13" s="76">
         <f>U13/24</f>
-        <v>0</v>
+        <v>2.6666666666666665</v>
       </c>
       <c r="AF13" s="12"/>
       <c r="AG13" s="12"/>
@@ -5600,7 +5648,9 @@
       <c r="B14" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="70"/>
+      <c r="C14" s="70">
+        <v>2</v>
+      </c>
       <c r="D14" s="70"/>
       <c r="E14" s="70"/>
       <c r="F14" s="70"/>
@@ -5623,11 +5673,11 @@
       </c>
       <c r="U14" s="75">
         <f t="shared" ref="U14:U36" si="4">C14*24+M14*24+O14*24+Q14*24+T14</f>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V14" s="75">
         <f t="shared" ref="V14:V36" si="5">U14/24</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF14" s="12"/>
       <c r="AG14" s="12"/>
@@ -5788,7 +5838,10 @@
       <c r="E17" s="70"/>
       <c r="F17" s="70"/>
       <c r="G17" s="70"/>
-      <c r="H17" s="70"/>
+      <c r="H17" s="70">
+        <f>3*24</f>
+        <v>72</v>
+      </c>
       <c r="I17" s="70"/>
       <c r="J17" s="71"/>
       <c r="K17" s="72"/>
@@ -5802,15 +5855,15 @@
       <c r="S17" s="55"/>
       <c r="T17" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="U17" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="V17" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF17" s="12"/>
       <c r="AG17" s="12"/>
@@ -5904,12 +5957,17 @@
       <c r="B19" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="C19" s="70"/>
+      <c r="C19" s="70">
+        <v>2</v>
+      </c>
       <c r="D19" s="70"/>
       <c r="E19" s="70"/>
       <c r="F19" s="70"/>
       <c r="G19" s="70"/>
-      <c r="H19" s="70"/>
+      <c r="H19" s="70">
+        <f>24+20</f>
+        <v>44</v>
+      </c>
       <c r="I19" s="70"/>
       <c r="J19" s="71"/>
       <c r="K19" s="72"/>
@@ -5923,15 +5981,15 @@
       <c r="S19" s="55"/>
       <c r="T19" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="U19" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="V19" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3.8333333333333335</v>
       </c>
       <c r="AF19" s="12"/>
       <c r="AG19" s="12"/>
@@ -5965,7 +6023,9 @@
       <c r="B20" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="70"/>
+      <c r="C20" s="70">
+        <v>5</v>
+      </c>
       <c r="D20" s="70"/>
       <c r="E20" s="70"/>
       <c r="F20" s="70"/>
@@ -5988,11 +6048,11 @@
       </c>
       <c r="U20" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="V20" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AF20" s="12"/>
       <c r="AG20" s="12"/>
@@ -6031,7 +6091,10 @@
       <c r="E21" s="70"/>
       <c r="F21" s="70"/>
       <c r="G21" s="70"/>
-      <c r="H21" s="70"/>
+      <c r="H21" s="70">
+        <f>24*2</f>
+        <v>48</v>
+      </c>
       <c r="I21" s="70"/>
       <c r="J21" s="71"/>
       <c r="K21" s="72"/>
@@ -6045,15 +6108,15 @@
       <c r="S21" s="55"/>
       <c r="T21" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="U21" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V21" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF21" s="12"/>
       <c r="AG21" s="12"/>
@@ -6087,13 +6150,17 @@
       <c r="B22" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="C22" s="70"/>
+      <c r="C22" s="70">
+        <v>2</v>
+      </c>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
       <c r="G22" s="70"/>
       <c r="H22" s="70"/>
-      <c r="I22" s="70"/>
+      <c r="I22" s="70">
+        <v>20</v>
+      </c>
       <c r="J22" s="71"/>
       <c r="K22" s="72"/>
       <c r="L22" s="55"/>
@@ -6106,15 +6173,15 @@
       <c r="S22" s="55"/>
       <c r="T22" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="U22" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="V22" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2.8333333333333335</v>
       </c>
       <c r="W22" s="9"/>
       <c r="X22" s="9"/>
@@ -6162,7 +6229,10 @@
       <c r="E23" s="70"/>
       <c r="F23" s="70"/>
       <c r="G23" s="70"/>
-      <c r="H23" s="70"/>
+      <c r="H23" s="70">
+        <f>37*24+19</f>
+        <v>907</v>
+      </c>
       <c r="I23" s="70"/>
       <c r="J23" s="71"/>
       <c r="K23" s="72"/>
@@ -6176,15 +6246,15 @@
       <c r="S23" s="55"/>
       <c r="T23" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>907</v>
       </c>
       <c r="U23" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>907</v>
       </c>
       <c r="V23" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>37.791666666666664</v>
       </c>
       <c r="W23" s="9"/>
       <c r="X23" s="9"/>
@@ -6227,12 +6297,17 @@
       <c r="B24" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="C24" s="70"/>
+      <c r="C24" s="70">
+        <v>2</v>
+      </c>
       <c r="D24" s="70"/>
       <c r="E24" s="70"/>
       <c r="F24" s="70"/>
       <c r="G24" s="70"/>
-      <c r="H24" s="70"/>
+      <c r="H24" s="70">
+        <f>24*3</f>
+        <v>72</v>
+      </c>
       <c r="I24" s="70"/>
       <c r="J24" s="71"/>
       <c r="K24" s="72"/>
@@ -6246,15 +6321,15 @@
       <c r="S24" s="55"/>
       <c r="T24" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="U24" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="V24" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AF24" s="12"/>
       <c r="AG24" s="12"/>
@@ -6288,34 +6363,44 @@
       <c r="B25" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="C25" s="70"/>
+      <c r="C25" s="70">
+        <v>49</v>
+      </c>
       <c r="D25" s="70"/>
       <c r="E25" s="70"/>
       <c r="F25" s="70"/>
       <c r="G25" s="70"/>
       <c r="H25" s="70"/>
       <c r="I25" s="70"/>
-      <c r="J25" s="71"/>
+      <c r="J25" s="71">
+        <v>1</v>
+      </c>
       <c r="K25" s="72"/>
       <c r="L25" s="55"/>
-      <c r="M25" s="73"/>
+      <c r="M25" s="73">
+        <v>1</v>
+      </c>
       <c r="N25" s="74"/>
-      <c r="O25" s="70"/>
+      <c r="O25" s="70">
+        <v>1</v>
+      </c>
       <c r="P25" s="71"/>
-      <c r="Q25" s="71"/>
+      <c r="Q25" s="71">
+        <v>2</v>
+      </c>
       <c r="R25" s="72"/>
       <c r="S25" s="55"/>
       <c r="T25" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U25" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1273</v>
       </c>
       <c r="V25" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>53.041666666666664</v>
       </c>
       <c r="AY25" s="14" t="e">
         <f>#REF!-AY24</f>
@@ -6330,7 +6415,9 @@
       <c r="B26" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="C26" s="70"/>
+      <c r="C26" s="70">
+        <v>5</v>
+      </c>
       <c r="D26" s="70"/>
       <c r="E26" s="70"/>
       <c r="F26" s="70"/>
@@ -6353,11 +6440,11 @@
       </c>
       <c r="U26" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="V26" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W26" s="9"/>
       <c r="X26" s="9"/>
@@ -6377,7 +6464,9 @@
       <c r="B27" s="26" t="s">
         <v>69</v>
       </c>
-      <c r="C27" s="70"/>
+      <c r="C27" s="70">
+        <v>3</v>
+      </c>
       <c r="D27" s="70"/>
       <c r="E27" s="70"/>
       <c r="F27" s="70"/>
@@ -6400,11 +6489,11 @@
       </c>
       <c r="U27" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="V27" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W27" s="9"/>
       <c r="X27" s="9"/>
@@ -6471,17 +6560,25 @@
       <c r="B29" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="C29" s="70"/>
+      <c r="C29" s="70">
+        <v>26</v>
+      </c>
       <c r="D29" s="70"/>
       <c r="E29" s="70"/>
       <c r="F29" s="70"/>
       <c r="G29" s="70"/>
       <c r="H29" s="70"/>
       <c r="I29" s="70"/>
-      <c r="J29" s="71"/>
+      <c r="J29" s="71">
+        <v>5</v>
+      </c>
       <c r="K29" s="72"/>
-      <c r="L29" s="55"/>
-      <c r="M29" s="73"/>
+      <c r="L29" s="55">
+        <v>1</v>
+      </c>
+      <c r="M29" s="73">
+        <v>1</v>
+      </c>
       <c r="N29" s="74"/>
       <c r="O29" s="70"/>
       <c r="P29" s="71"/>
@@ -6490,15 +6587,15 @@
       <c r="S29" s="55"/>
       <c r="T29" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U29" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>653</v>
       </c>
       <c r="V29" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>27.208333333333332</v>
       </c>
     </row>
     <row r="30" spans="1:54" x14ac:dyDescent="0.25">
@@ -6509,7 +6606,9 @@
       <c r="B30" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="C30" s="70"/>
+      <c r="C30" s="70">
+        <v>13</v>
+      </c>
       <c r="D30" s="70"/>
       <c r="E30" s="70"/>
       <c r="F30" s="70"/>
@@ -6521,7 +6620,9 @@
       <c r="L30" s="55"/>
       <c r="M30" s="73"/>
       <c r="N30" s="74"/>
-      <c r="O30" s="70"/>
+      <c r="O30" s="70">
+        <v>1</v>
+      </c>
       <c r="P30" s="71"/>
       <c r="Q30" s="71"/>
       <c r="R30" s="72"/>
@@ -6532,11 +6633,11 @@
       </c>
       <c r="U30" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>336</v>
       </c>
       <c r="V30" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="31" spans="1:54" x14ac:dyDescent="0.25">
@@ -6547,7 +6648,9 @@
       <c r="B31" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="C31" s="70"/>
+      <c r="C31" s="70">
+        <v>1</v>
+      </c>
       <c r="D31" s="70"/>
       <c r="E31" s="70"/>
       <c r="F31" s="70"/>
@@ -6561,7 +6664,9 @@
       <c r="N31" s="74"/>
       <c r="O31" s="70"/>
       <c r="P31" s="71"/>
-      <c r="Q31" s="71"/>
+      <c r="Q31" s="71">
+        <v>1</v>
+      </c>
       <c r="R31" s="72"/>
       <c r="S31" s="55"/>
       <c r="T31" s="58">
@@ -6570,11 +6675,11 @@
       </c>
       <c r="U31" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V31" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:54" x14ac:dyDescent="0.25">
@@ -6623,7 +6728,9 @@
       <c r="B33" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="C33" s="70"/>
+      <c r="C33" s="70">
+        <v>1</v>
+      </c>
       <c r="D33" s="70"/>
       <c r="E33" s="70"/>
       <c r="F33" s="70"/>
@@ -6633,7 +6740,9 @@
       <c r="J33" s="71"/>
       <c r="K33" s="72"/>
       <c r="L33" s="55"/>
-      <c r="M33" s="73"/>
+      <c r="M33" s="73">
+        <v>1</v>
+      </c>
       <c r="N33" s="74"/>
       <c r="O33" s="70"/>
       <c r="P33" s="71"/>
@@ -6646,11 +6755,11 @@
       </c>
       <c r="U33" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V33" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:23" x14ac:dyDescent="0.25">
@@ -6661,34 +6770,47 @@
       <c r="B34" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="C34" s="70"/>
+      <c r="C34" s="70">
+        <f>45+144</f>
+        <v>189</v>
+      </c>
       <c r="D34" s="70"/>
       <c r="E34" s="70"/>
       <c r="F34" s="70"/>
       <c r="G34" s="70"/>
       <c r="H34" s="70"/>
-      <c r="I34" s="70"/>
+      <c r="I34" s="70">
+        <v>1</v>
+      </c>
       <c r="J34" s="71"/>
-      <c r="K34" s="72"/>
+      <c r="K34" s="72">
+        <v>1</v>
+      </c>
       <c r="L34" s="55"/>
-      <c r="M34" s="73"/>
+      <c r="M34" s="73">
+        <v>1</v>
+      </c>
       <c r="N34" s="74"/>
-      <c r="O34" s="70"/>
+      <c r="O34" s="70">
+        <v>2</v>
+      </c>
       <c r="P34" s="71"/>
-      <c r="Q34" s="71"/>
+      <c r="Q34" s="71">
+        <v>2</v>
+      </c>
       <c r="R34" s="72"/>
       <c r="S34" s="55"/>
       <c r="T34" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U34" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4658</v>
       </c>
       <c r="V34" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>194.08333333333334</v>
       </c>
     </row>
     <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -6775,34 +6897,52 @@
       <c r="B37" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="C37" s="59"/>
+      <c r="C37" s="59">
+        <f>3132+62</f>
+        <v>3194</v>
+      </c>
       <c r="D37" s="59"/>
       <c r="E37" s="59"/>
       <c r="F37" s="59"/>
       <c r="G37" s="59"/>
-      <c r="H37" s="59"/>
-      <c r="I37" s="59"/>
-      <c r="J37" s="60"/>
-      <c r="K37" s="61"/>
+      <c r="H37" s="59">
+        <v>4</v>
+      </c>
+      <c r="I37" s="59">
+        <v>2</v>
+      </c>
+      <c r="J37" s="60">
+        <v>5</v>
+      </c>
+      <c r="K37" s="61">
+        <f>6+2</f>
+        <v>8</v>
+      </c>
       <c r="L37" s="62"/>
-      <c r="M37" s="63"/>
+      <c r="M37" s="63">
+        <v>20</v>
+      </c>
       <c r="N37" s="64"/>
-      <c r="O37" s="65"/>
+      <c r="O37" s="65">
+        <v>26</v>
+      </c>
       <c r="P37" s="66"/>
-      <c r="Q37" s="66"/>
+      <c r="Q37" s="66">
+        <v>121</v>
+      </c>
       <c r="R37" s="67"/>
       <c r="S37" s="62"/>
       <c r="T37" s="77">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="U37" s="77">
         <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
-        <v>0</v>
+        <v>20185</v>
       </c>
       <c r="V37" s="77">
         <f>U37/6</f>
-        <v>0</v>
+        <v>3364.1666666666665</v>
       </c>
       <c r="W37" s="50"/>
     </row>
@@ -6814,7 +6954,9 @@
       <c r="B38" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="C38" s="70"/>
+      <c r="C38" s="70">
+        <v>3</v>
+      </c>
       <c r="D38" s="70"/>
       <c r="E38" s="70"/>
       <c r="F38" s="70"/>
@@ -6828,7 +6970,9 @@
       <c r="N38" s="74"/>
       <c r="O38" s="70"/>
       <c r="P38" s="71"/>
-      <c r="Q38" s="71"/>
+      <c r="Q38" s="71">
+        <v>2</v>
+      </c>
       <c r="R38" s="72"/>
       <c r="S38" s="55"/>
       <c r="T38" s="75">
@@ -6837,11 +6981,11 @@
       </c>
       <c r="U38" s="75">
         <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="V38" s="75">
         <f>U38/24</f>
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39" spans="1:23" x14ac:dyDescent="0.25">
@@ -6890,7 +7034,10 @@
       <c r="B40" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="C40" s="59"/>
+      <c r="C40" s="59">
+        <f>50+315</f>
+        <v>365</v>
+      </c>
       <c r="D40" s="59"/>
       <c r="E40" s="59"/>
       <c r="F40" s="59"/>
@@ -6898,26 +7045,32 @@
       <c r="H40" s="59"/>
       <c r="I40" s="59"/>
       <c r="J40" s="60"/>
-      <c r="K40" s="61"/>
+      <c r="K40" s="61">
+        <v>20</v>
+      </c>
       <c r="L40" s="62"/>
       <c r="M40" s="63"/>
       <c r="N40" s="64"/>
-      <c r="O40" s="65"/>
+      <c r="O40" s="65">
+        <v>2</v>
+      </c>
       <c r="P40" s="66"/>
-      <c r="Q40" s="66"/>
+      <c r="Q40" s="66">
+        <v>1</v>
+      </c>
       <c r="R40" s="67"/>
       <c r="S40" s="62"/>
       <c r="T40" s="77">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="U40" s="77">
         <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
-        <v>0</v>
+        <v>8852</v>
       </c>
       <c r="V40" s="77">
         <f>U40/24</f>
-        <v>0</v>
+        <v>368.83333333333331</v>
       </c>
     </row>
     <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -6928,7 +7081,10 @@
       <c r="B41" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="C41" s="82"/>
+      <c r="C41" s="82">
+        <f>480+51</f>
+        <v>531</v>
+      </c>
       <c r="D41" s="82"/>
       <c r="E41" s="82"/>
       <c r="F41" s="82"/>
@@ -6938,11 +7094,17 @@
       <c r="J41" s="83"/>
       <c r="K41" s="84"/>
       <c r="L41" s="85"/>
-      <c r="M41" s="86"/>
+      <c r="M41" s="86">
+        <v>5</v>
+      </c>
       <c r="N41" s="87"/>
-      <c r="O41" s="82"/>
+      <c r="O41" s="82">
+        <v>10</v>
+      </c>
       <c r="P41" s="83"/>
-      <c r="Q41" s="83"/>
+      <c r="Q41" s="83">
+        <v>20</v>
+      </c>
       <c r="R41" s="84"/>
       <c r="S41" s="85"/>
       <c r="T41" s="88">
@@ -6951,11 +7113,11 @@
       </c>
       <c r="U41" s="88">
         <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
-        <v>0</v>
+        <v>6792</v>
       </c>
       <c r="V41" s="88">
         <f>U41/12</f>
-        <v>0</v>
+        <v>566</v>
       </c>
     </row>
     <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -6995,34 +7157,53 @@
       <c r="B43" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="C43" s="65"/>
+      <c r="C43" s="65">
+        <f>50+6912+19764+10260</f>
+        <v>36986</v>
+      </c>
       <c r="D43" s="65"/>
       <c r="E43" s="65"/>
       <c r="F43" s="65"/>
       <c r="G43" s="65"/>
-      <c r="H43" s="65"/>
-      <c r="I43" s="65"/>
-      <c r="J43" s="66"/>
-      <c r="K43" s="67"/>
+      <c r="H43" s="65">
+        <v>1</v>
+      </c>
+      <c r="I43" s="65">
+        <v>12</v>
+      </c>
+      <c r="J43" s="66">
+        <f>18*6</f>
+        <v>108</v>
+      </c>
+      <c r="K43" s="67">
+        <f>71*6+2</f>
+        <v>428</v>
+      </c>
       <c r="L43" s="62"/>
-      <c r="M43" s="63"/>
+      <c r="M43" s="63">
+        <v>366</v>
+      </c>
       <c r="N43" s="64"/>
-      <c r="O43" s="65"/>
+      <c r="O43" s="65">
+        <v>392</v>
+      </c>
       <c r="P43" s="66"/>
-      <c r="Q43" s="66"/>
+      <c r="Q43" s="66">
+        <v>446</v>
+      </c>
       <c r="R43" s="67"/>
       <c r="S43" s="62"/>
       <c r="T43" s="77">
         <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
-        <v>0</v>
+        <v>549</v>
       </c>
       <c r="U43" s="77">
         <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
-        <v>0</v>
+        <v>229689</v>
       </c>
       <c r="V43" s="77">
         <f>U43/6</f>
-        <v>0</v>
+        <v>38281.5</v>
       </c>
     </row>
     <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -7062,7 +7243,9 @@
       <c r="B45" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="C45" s="70"/>
+      <c r="C45" s="70">
+        <v>4</v>
+      </c>
       <c r="D45" s="70"/>
       <c r="E45" s="70"/>
       <c r="F45" s="70"/>
@@ -7076,7 +7259,9 @@
       <c r="N45" s="74"/>
       <c r="O45" s="70"/>
       <c r="P45" s="71"/>
-      <c r="Q45" s="71"/>
+      <c r="Q45" s="71">
+        <v>1</v>
+      </c>
       <c r="R45" s="72"/>
       <c r="S45" s="55"/>
       <c r="T45" s="75">
@@ -7085,11 +7270,11 @@
       </c>
       <c r="U45" s="75">
         <f>C45*24+M45*24+O45*24+Q45*24+T45</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="V45" s="75">
         <f>U45/24</f>
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46" spans="1:23" x14ac:dyDescent="0.25">
@@ -7138,34 +7323,47 @@
       <c r="B47" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="C47" s="65"/>
+      <c r="C47" s="65">
+        <f>104+648+324+88+540+103+324+432+106</f>
+        <v>2669</v>
+      </c>
       <c r="D47" s="65"/>
       <c r="E47" s="65"/>
       <c r="F47" s="65"/>
       <c r="G47" s="65"/>
-      <c r="H47" s="65"/>
+      <c r="H47" s="65">
+        <v>1</v>
+      </c>
       <c r="I47" s="65"/>
       <c r="J47" s="66"/>
-      <c r="K47" s="67"/>
+      <c r="K47" s="67">
+        <v>5</v>
+      </c>
       <c r="L47" s="62"/>
       <c r="M47" s="63"/>
       <c r="N47" s="64"/>
-      <c r="O47" s="65"/>
+      <c r="O47" s="65">
+        <v>16</v>
+      </c>
       <c r="P47" s="66"/>
-      <c r="Q47" s="66"/>
-      <c r="R47" s="67"/>
+      <c r="Q47" s="66">
+        <v>5</v>
+      </c>
+      <c r="R47" s="67">
+        <v>3</v>
+      </c>
       <c r="S47" s="62"/>
       <c r="T47" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="U47" s="77">
         <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
-        <v>0</v>
+        <v>16149</v>
       </c>
       <c r="V47" s="77">
         <f>U47/6</f>
-        <v>0</v>
+        <v>2691.5</v>
       </c>
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.25">
@@ -7181,7 +7379,9 @@
       <c r="E48" s="70"/>
       <c r="F48" s="70"/>
       <c r="G48" s="70"/>
-      <c r="H48" s="70"/>
+      <c r="H48" s="70">
+        <v>24</v>
+      </c>
       <c r="I48" s="70"/>
       <c r="J48" s="71"/>
       <c r="K48" s="72"/>
@@ -7195,15 +7395,15 @@
       <c r="S48" s="55"/>
       <c r="T48" s="75">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="U48" s="75">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V48" s="75">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.25">
@@ -7228,7 +7428,9 @@
       <c r="N49" s="74"/>
       <c r="O49" s="70"/>
       <c r="P49" s="71"/>
-      <c r="Q49" s="71"/>
+      <c r="Q49" s="71">
+        <v>10</v>
+      </c>
       <c r="R49" s="72"/>
       <c r="S49" s="55"/>
       <c r="T49" s="75">
@@ -7237,11 +7439,11 @@
       </c>
       <c r="U49" s="75">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="V49" s="75">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="50" spans="1:22" x14ac:dyDescent="0.25">
@@ -7290,7 +7492,9 @@
       <c r="B51" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="C51" s="65"/>
+      <c r="C51" s="65">
+        <v>34</v>
+      </c>
       <c r="D51" s="65"/>
       <c r="E51" s="65"/>
       <c r="F51" s="65"/>
@@ -7313,11 +7517,11 @@
       </c>
       <c r="U51" s="77">
         <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="V51" s="77">
         <f>U51/6</f>
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.25">
@@ -7366,7 +7570,9 @@
       <c r="B53" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C53" s="70"/>
+      <c r="C53" s="70">
+        <v>7</v>
+      </c>
       <c r="D53" s="70"/>
       <c r="E53" s="70"/>
       <c r="F53" s="70"/>
@@ -7389,11 +7595,11 @@
       </c>
       <c r="U53" s="75">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="V53" s="75">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.25">
@@ -7519,7 +7725,7 @@
       </c>
       <c r="C58" s="2">
         <f>SUM(C7:C57)</f>
-        <v>0</v>
+        <v>47679</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" s="2"/>
@@ -7533,23 +7739,23 @@
       </c>
       <c r="H58" s="2">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1189</v>
       </c>
       <c r="I58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="J58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="K58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>470</v>
       </c>
       <c r="M58" s="5">
         <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
-        <v>0</v>
+        <v>406</v>
       </c>
       <c r="N58" s="5">
         <f t="shared" si="12"/>
@@ -7557,32 +7763,32 @@
       </c>
       <c r="O58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>463</v>
       </c>
       <c r="P58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>634</v>
       </c>
       <c r="R58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="S58" s="55"/>
       <c r="T58" s="4">
         <f>SUM(T7:T57)</f>
-        <v>0</v>
+        <v>1844</v>
       </c>
       <c r="U58" s="90">
         <f>SUM(U7:U57)</f>
-        <v>0</v>
+        <v>378470</v>
       </c>
       <c r="V58" s="4">
         <f>SUM(V7:V57)</f>
-        <v>0</v>
+        <v>49330.958333333328</v>
       </c>
     </row>
     <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>

--- a/GBDS AUGUST FILES 2026/INVENTORY COUNT SHEET - AUGUST 2026.xlsx
+++ b/GBDS AUGUST FILES 2026/INVENTORY COUNT SHEET - AUGUST 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS AUGUST FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EFD1ACB-6144-4C6C-8039-8981B06D792A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{380D70AC-84DD-4F16-A9DB-A5613DF33D00}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="3" activeTab="9" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="3" activeTab="10" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
   </bookViews>
   <sheets>
     <sheet name="SAMPLE" sheetId="32" r:id="rId1"/>
@@ -8307,34 +8307,42 @@
       <c r="B7" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="52"/>
+      <c r="C7" s="52">
+        <v>32</v>
+      </c>
       <c r="D7" s="52"/>
       <c r="E7" s="52"/>
       <c r="F7" s="52"/>
       <c r="G7" s="52"/>
       <c r="H7" s="52"/>
-      <c r="I7" s="52"/>
+      <c r="I7" s="52">
+        <v>3</v>
+      </c>
       <c r="J7" s="53"/>
-      <c r="K7" s="54"/>
+      <c r="K7" s="54">
+        <v>6</v>
+      </c>
       <c r="L7" s="55"/>
       <c r="M7" s="56"/>
       <c r="N7" s="57"/>
-      <c r="O7" s="52"/>
+      <c r="O7" s="52">
+        <v>1</v>
+      </c>
       <c r="P7" s="53"/>
       <c r="Q7" s="53"/>
       <c r="R7" s="54"/>
       <c r="S7" s="55"/>
       <c r="T7" s="58">
         <f>H7+I7+J7+K7+N7+P7+R7</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="U7" s="58">
         <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
-        <v>0</v>
+        <v>801</v>
       </c>
       <c r="V7" s="58">
         <f>U7/24</f>
-        <v>0</v>
+        <v>33.375</v>
       </c>
       <c r="W7" s="50"/>
       <c r="AF7" s="12"/>
@@ -8369,7 +8377,10 @@
       <c r="B8" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="59"/>
+      <c r="C8" s="59">
+        <f>41+43</f>
+        <v>84</v>
+      </c>
       <c r="D8" s="59"/>
       <c r="E8" s="59"/>
       <c r="F8" s="59"/>
@@ -8379,24 +8390,32 @@
       <c r="J8" s="60"/>
       <c r="K8" s="61"/>
       <c r="L8" s="62"/>
-      <c r="M8" s="63"/>
+      <c r="M8" s="63">
+        <v>1</v>
+      </c>
       <c r="N8" s="64"/>
-      <c r="O8" s="65"/>
-      <c r="P8" s="66"/>
-      <c r="Q8" s="66"/>
+      <c r="O8" s="65">
+        <v>1</v>
+      </c>
+      <c r="P8" s="66">
+        <v>12</v>
+      </c>
+      <c r="Q8" s="66">
+        <v>1</v>
+      </c>
       <c r="R8" s="67"/>
       <c r="S8" s="62"/>
       <c r="T8" s="68">
         <f t="shared" ref="T8:T41" si="0">H8+I8+J8+K8+N8+P8+R8</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="U8" s="69">
         <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="V8" s="69">
         <f>U8/24</f>
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="W8" s="50"/>
       <c r="AF8" s="12"/>
@@ -8431,7 +8450,10 @@
       <c r="B9" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="70"/>
+      <c r="C9" s="70">
+        <f>59+30</f>
+        <v>89</v>
+      </c>
       <c r="D9" s="70"/>
       <c r="E9" s="70"/>
       <c r="F9" s="70"/>
@@ -8443,9 +8465,13 @@
       <c r="L9" s="55"/>
       <c r="M9" s="73"/>
       <c r="N9" s="74"/>
-      <c r="O9" s="70"/>
+      <c r="O9" s="70">
+        <v>1</v>
+      </c>
       <c r="P9" s="71"/>
-      <c r="Q9" s="71"/>
+      <c r="Q9" s="71">
+        <v>1</v>
+      </c>
       <c r="R9" s="72"/>
       <c r="S9" s="55"/>
       <c r="T9" s="75">
@@ -8454,11 +8480,11 @@
       </c>
       <c r="U9" s="76">
         <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
-        <v>0</v>
+        <v>2184</v>
       </c>
       <c r="V9" s="76">
         <f t="shared" ref="V9:V11" si="3">U9/24</f>
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="W9" s="50"/>
       <c r="AF9" s="12"/>
@@ -8493,7 +8519,10 @@
       <c r="B10" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="C10" s="70"/>
+      <c r="C10" s="70">
+        <f>33+10</f>
+        <v>43</v>
+      </c>
       <c r="D10" s="70"/>
       <c r="E10" s="70"/>
       <c r="F10" s="70"/>
@@ -8507,7 +8536,9 @@
       <c r="N10" s="74"/>
       <c r="O10" s="70"/>
       <c r="P10" s="71"/>
-      <c r="Q10" s="71"/>
+      <c r="Q10" s="71">
+        <v>1</v>
+      </c>
       <c r="R10" s="72"/>
       <c r="S10" s="55"/>
       <c r="T10" s="58">
@@ -8516,11 +8547,11 @@
       </c>
       <c r="U10" s="58">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1056</v>
       </c>
       <c r="V10" s="58">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="W10" s="50"/>
       <c r="AF10" s="12"/>
@@ -8555,7 +8586,9 @@
       <c r="B11" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="70"/>
+      <c r="C11" s="70">
+        <v>9</v>
+      </c>
       <c r="D11" s="70"/>
       <c r="E11" s="70"/>
       <c r="F11" s="70"/>
@@ -8563,7 +8596,9 @@
       <c r="H11" s="70"/>
       <c r="I11" s="70"/>
       <c r="J11" s="71"/>
-      <c r="K11" s="72"/>
+      <c r="K11" s="72">
+        <v>2</v>
+      </c>
       <c r="L11" s="55"/>
       <c r="M11" s="73"/>
       <c r="N11" s="74"/>
@@ -8574,15 +8609,15 @@
       <c r="S11" s="55"/>
       <c r="T11" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U11" s="58">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="V11" s="58">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>9.0833333333333339</v>
       </c>
       <c r="AF11" s="12"/>
       <c r="AG11" s="12"/>
@@ -8615,7 +8650,10 @@
       <c r="B12" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="59"/>
+      <c r="C12" s="59">
+        <f>1224+53+864+50+1080+29</f>
+        <v>3300</v>
+      </c>
       <c r="D12" s="59"/>
       <c r="E12" s="59"/>
       <c r="F12" s="59"/>
@@ -8625,24 +8663,34 @@
       <c r="J12" s="60"/>
       <c r="K12" s="61"/>
       <c r="L12" s="62"/>
-      <c r="M12" s="63"/>
+      <c r="M12" s="63">
+        <v>7</v>
+      </c>
       <c r="N12" s="64"/>
-      <c r="O12" s="65"/>
-      <c r="P12" s="66"/>
-      <c r="Q12" s="66"/>
-      <c r="R12" s="67"/>
+      <c r="O12" s="65">
+        <v>11</v>
+      </c>
+      <c r="P12" s="66">
+        <v>14</v>
+      </c>
+      <c r="Q12" s="66">
+        <v>19</v>
+      </c>
+      <c r="R12" s="67">
+        <v>11</v>
+      </c>
       <c r="S12" s="62"/>
       <c r="T12" s="69">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="U12" s="69">
         <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
-        <v>0</v>
+        <v>80113</v>
       </c>
       <c r="V12" s="69">
         <f>U12/24</f>
-        <v>0</v>
+        <v>3338.0416666666665</v>
       </c>
       <c r="W12" s="9"/>
       <c r="X12" s="9"/>
@@ -8684,12 +8732,16 @@
       <c r="B13" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="70"/>
+      <c r="C13" s="70">
+        <v>2</v>
+      </c>
       <c r="D13" s="70"/>
       <c r="E13" s="70"/>
       <c r="F13" s="70"/>
       <c r="G13" s="70"/>
-      <c r="H13" s="70"/>
+      <c r="H13" s="70">
+        <v>16</v>
+      </c>
       <c r="I13" s="70"/>
       <c r="J13" s="71"/>
       <c r="K13" s="72"/>
@@ -8703,15 +8755,15 @@
       <c r="S13" s="55"/>
       <c r="T13" s="76">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="U13" s="76">
         <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="V13" s="76">
         <f>U13/24</f>
-        <v>0</v>
+        <v>2.6666666666666665</v>
       </c>
       <c r="AF13" s="12"/>
       <c r="AG13" s="12"/>
@@ -8745,7 +8797,9 @@
       <c r="B14" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="70"/>
+      <c r="C14" s="70">
+        <v>2</v>
+      </c>
       <c r="D14" s="70"/>
       <c r="E14" s="70"/>
       <c r="F14" s="70"/>
@@ -8768,11 +8822,11 @@
       </c>
       <c r="U14" s="75">
         <f t="shared" ref="U14:U36" si="4">C14*24+M14*24+O14*24+Q14*24+T14</f>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V14" s="75">
         <f t="shared" ref="V14:V36" si="5">U14/24</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF14" s="12"/>
       <c r="AG14" s="12"/>
@@ -8933,7 +8987,10 @@
       <c r="E17" s="70"/>
       <c r="F17" s="70"/>
       <c r="G17" s="70"/>
-      <c r="H17" s="70"/>
+      <c r="H17" s="70">
+        <f>3*24</f>
+        <v>72</v>
+      </c>
       <c r="I17" s="70"/>
       <c r="J17" s="71"/>
       <c r="K17" s="72"/>
@@ -8947,15 +9004,15 @@
       <c r="S17" s="55"/>
       <c r="T17" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="U17" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="V17" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF17" s="12"/>
       <c r="AG17" s="12"/>
@@ -9049,12 +9106,17 @@
       <c r="B19" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="C19" s="70"/>
+      <c r="C19" s="70">
+        <v>2</v>
+      </c>
       <c r="D19" s="70"/>
       <c r="E19" s="70"/>
       <c r="F19" s="70"/>
       <c r="G19" s="70"/>
-      <c r="H19" s="70"/>
+      <c r="H19" s="70">
+        <f>24+20</f>
+        <v>44</v>
+      </c>
       <c r="I19" s="70"/>
       <c r="J19" s="71"/>
       <c r="K19" s="72"/>
@@ -9068,15 +9130,15 @@
       <c r="S19" s="55"/>
       <c r="T19" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="U19" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="V19" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3.8333333333333335</v>
       </c>
       <c r="AF19" s="12"/>
       <c r="AG19" s="12"/>
@@ -9110,7 +9172,9 @@
       <c r="B20" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="70"/>
+      <c r="C20" s="70">
+        <v>5</v>
+      </c>
       <c r="D20" s="70"/>
       <c r="E20" s="70"/>
       <c r="F20" s="70"/>
@@ -9133,11 +9197,11 @@
       </c>
       <c r="U20" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="V20" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AF20" s="12"/>
       <c r="AG20" s="12"/>
@@ -9176,7 +9240,10 @@
       <c r="E21" s="70"/>
       <c r="F21" s="70"/>
       <c r="G21" s="70"/>
-      <c r="H21" s="70"/>
+      <c r="H21" s="70">
+        <f>24*2</f>
+        <v>48</v>
+      </c>
       <c r="I21" s="70"/>
       <c r="J21" s="71"/>
       <c r="K21" s="72"/>
@@ -9190,15 +9257,15 @@
       <c r="S21" s="55"/>
       <c r="T21" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="U21" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V21" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF21" s="12"/>
       <c r="AG21" s="12"/>
@@ -9232,13 +9299,17 @@
       <c r="B22" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="C22" s="70"/>
+      <c r="C22" s="70">
+        <v>2</v>
+      </c>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
       <c r="G22" s="70"/>
       <c r="H22" s="70"/>
-      <c r="I22" s="70"/>
+      <c r="I22" s="70">
+        <v>20</v>
+      </c>
       <c r="J22" s="71"/>
       <c r="K22" s="72"/>
       <c r="L22" s="55"/>
@@ -9251,15 +9322,15 @@
       <c r="S22" s="55"/>
       <c r="T22" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="U22" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="V22" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2.8333333333333335</v>
       </c>
       <c r="W22" s="9"/>
       <c r="X22" s="9"/>
@@ -9307,7 +9378,10 @@
       <c r="E23" s="70"/>
       <c r="F23" s="70"/>
       <c r="G23" s="70"/>
-      <c r="H23" s="70"/>
+      <c r="H23" s="70">
+        <f>37*24+19</f>
+        <v>907</v>
+      </c>
       <c r="I23" s="70"/>
       <c r="J23" s="71"/>
       <c r="K23" s="72"/>
@@ -9321,15 +9395,15 @@
       <c r="S23" s="55"/>
       <c r="T23" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>907</v>
       </c>
       <c r="U23" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>907</v>
       </c>
       <c r="V23" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>37.791666666666664</v>
       </c>
       <c r="W23" s="9"/>
       <c r="X23" s="9"/>
@@ -9372,12 +9446,17 @@
       <c r="B24" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="C24" s="70"/>
+      <c r="C24" s="70">
+        <v>2</v>
+      </c>
       <c r="D24" s="70"/>
       <c r="E24" s="70"/>
       <c r="F24" s="70"/>
       <c r="G24" s="70"/>
-      <c r="H24" s="70"/>
+      <c r="H24" s="70">
+        <f>3*24</f>
+        <v>72</v>
+      </c>
       <c r="I24" s="70"/>
       <c r="J24" s="71"/>
       <c r="K24" s="72"/>
@@ -9391,15 +9470,15 @@
       <c r="S24" s="55"/>
       <c r="T24" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="U24" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="V24" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AF24" s="12"/>
       <c r="AG24" s="12"/>
@@ -9433,7 +9512,9 @@
       <c r="B25" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="C25" s="70"/>
+      <c r="C25" s="70">
+        <v>47</v>
+      </c>
       <c r="D25" s="70"/>
       <c r="E25" s="70"/>
       <c r="F25" s="70"/>
@@ -9441,26 +9522,32 @@
       <c r="H25" s="70"/>
       <c r="I25" s="70"/>
       <c r="J25" s="71"/>
-      <c r="K25" s="72"/>
+      <c r="K25" s="72">
+        <v>1</v>
+      </c>
       <c r="L25" s="55"/>
-      <c r="M25" s="73"/>
+      <c r="M25" s="73">
+        <v>1</v>
+      </c>
       <c r="N25" s="74"/>
-      <c r="O25" s="70"/>
+      <c r="O25" s="70">
+        <v>1</v>
+      </c>
       <c r="P25" s="71"/>
       <c r="Q25" s="71"/>
       <c r="R25" s="72"/>
       <c r="S25" s="55"/>
       <c r="T25" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U25" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1177</v>
       </c>
       <c r="V25" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>49.041666666666664</v>
       </c>
       <c r="AY25" s="14" t="e">
         <f>#REF!-AY24</f>
@@ -9475,7 +9562,9 @@
       <c r="B26" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="C26" s="70"/>
+      <c r="C26" s="70">
+        <v>1</v>
+      </c>
       <c r="D26" s="70"/>
       <c r="E26" s="70"/>
       <c r="F26" s="70"/>
@@ -9487,9 +9576,13 @@
       <c r="L26" s="55"/>
       <c r="M26" s="73"/>
       <c r="N26" s="74"/>
-      <c r="O26" s="70"/>
+      <c r="O26" s="70">
+        <v>1</v>
+      </c>
       <c r="P26" s="71"/>
-      <c r="Q26" s="71"/>
+      <c r="Q26" s="71">
+        <v>3</v>
+      </c>
       <c r="R26" s="72"/>
       <c r="S26" s="55"/>
       <c r="T26" s="58">
@@ -9498,11 +9591,11 @@
       </c>
       <c r="U26" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="V26" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W26" s="9"/>
       <c r="X26" s="9"/>
@@ -9522,7 +9615,9 @@
       <c r="B27" s="26" t="s">
         <v>69</v>
       </c>
-      <c r="C27" s="70"/>
+      <c r="C27" s="70">
+        <v>3</v>
+      </c>
       <c r="D27" s="70"/>
       <c r="E27" s="70"/>
       <c r="F27" s="70"/>
@@ -9545,11 +9640,11 @@
       </c>
       <c r="U27" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="V27" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W27" s="9"/>
       <c r="X27" s="9"/>
@@ -9616,34 +9711,40 @@
       <c r="B29" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="C29" s="70"/>
+      <c r="C29" s="70">
+        <v>25</v>
+      </c>
       <c r="D29" s="70"/>
       <c r="E29" s="70"/>
       <c r="F29" s="70"/>
       <c r="G29" s="70"/>
       <c r="H29" s="70"/>
-      <c r="I29" s="70"/>
+      <c r="I29" s="70">
+        <v>5</v>
+      </c>
       <c r="J29" s="71"/>
       <c r="K29" s="72"/>
       <c r="L29" s="55"/>
       <c r="M29" s="73"/>
       <c r="N29" s="74"/>
-      <c r="O29" s="70"/>
+      <c r="O29" s="70">
+        <v>1</v>
+      </c>
       <c r="P29" s="71"/>
       <c r="Q29" s="71"/>
       <c r="R29" s="72"/>
       <c r="S29" s="55"/>
       <c r="T29" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U29" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>629</v>
       </c>
       <c r="V29" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>26.208333333333332</v>
       </c>
     </row>
     <row r="30" spans="1:54" x14ac:dyDescent="0.25">
@@ -9654,7 +9755,9 @@
       <c r="B30" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="C30" s="70"/>
+      <c r="C30" s="70">
+        <v>11</v>
+      </c>
       <c r="D30" s="70"/>
       <c r="E30" s="70"/>
       <c r="F30" s="70"/>
@@ -9666,7 +9769,9 @@
       <c r="L30" s="55"/>
       <c r="M30" s="73"/>
       <c r="N30" s="74"/>
-      <c r="O30" s="70"/>
+      <c r="O30" s="70">
+        <v>1</v>
+      </c>
       <c r="P30" s="71"/>
       <c r="Q30" s="71"/>
       <c r="R30" s="72"/>
@@ -9677,11 +9782,11 @@
       </c>
       <c r="U30" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>288</v>
       </c>
       <c r="V30" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="31" spans="1:54" x14ac:dyDescent="0.25">
@@ -9702,7 +9807,9 @@
       <c r="J31" s="71"/>
       <c r="K31" s="72"/>
       <c r="L31" s="55"/>
-      <c r="M31" s="73"/>
+      <c r="M31" s="73">
+        <v>1</v>
+      </c>
       <c r="N31" s="74"/>
       <c r="O31" s="70"/>
       <c r="P31" s="71"/>
@@ -9715,11 +9822,11 @@
       </c>
       <c r="U31" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V31" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:54" x14ac:dyDescent="0.25">
@@ -9768,7 +9875,9 @@
       <c r="B33" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="C33" s="70"/>
+      <c r="C33" s="70">
+        <v>1</v>
+      </c>
       <c r="D33" s="70"/>
       <c r="E33" s="70"/>
       <c r="F33" s="70"/>
@@ -9778,7 +9887,9 @@
       <c r="J33" s="71"/>
       <c r="K33" s="72"/>
       <c r="L33" s="55"/>
-      <c r="M33" s="73"/>
+      <c r="M33" s="73">
+        <v>1</v>
+      </c>
       <c r="N33" s="74"/>
       <c r="O33" s="70"/>
       <c r="P33" s="71"/>
@@ -9791,11 +9902,11 @@
       </c>
       <c r="U33" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V33" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:23" x14ac:dyDescent="0.25">
@@ -9806,34 +9917,45 @@
       <c r="B34" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="C34" s="70"/>
+      <c r="C34" s="70">
+        <f>42+144</f>
+        <v>186</v>
+      </c>
       <c r="D34" s="70"/>
       <c r="E34" s="70"/>
       <c r="F34" s="70"/>
       <c r="G34" s="70"/>
       <c r="H34" s="70"/>
-      <c r="I34" s="70"/>
+      <c r="I34" s="70">
+        <v>1</v>
+      </c>
       <c r="J34" s="71"/>
-      <c r="K34" s="72"/>
+      <c r="K34" s="72">
+        <v>1</v>
+      </c>
       <c r="L34" s="55"/>
       <c r="M34" s="73"/>
       <c r="N34" s="74"/>
-      <c r="O34" s="70"/>
+      <c r="O34" s="70">
+        <v>2</v>
+      </c>
       <c r="P34" s="71"/>
-      <c r="Q34" s="71"/>
+      <c r="Q34" s="71">
+        <v>2</v>
+      </c>
       <c r="R34" s="72"/>
       <c r="S34" s="55"/>
       <c r="T34" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U34" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4562</v>
       </c>
       <c r="V34" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>190.08333333333334</v>
       </c>
     </row>
     <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -9920,34 +10042,52 @@
       <c r="B37" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="C37" s="59"/>
+      <c r="C37" s="59">
+        <f>3024+22</f>
+        <v>3046</v>
+      </c>
       <c r="D37" s="59"/>
       <c r="E37" s="59"/>
       <c r="F37" s="59"/>
       <c r="G37" s="59"/>
-      <c r="H37" s="59"/>
-      <c r="I37" s="59"/>
-      <c r="J37" s="60"/>
-      <c r="K37" s="61"/>
+      <c r="H37" s="59">
+        <v>4</v>
+      </c>
+      <c r="I37" s="59">
+        <v>2</v>
+      </c>
+      <c r="J37" s="60">
+        <v>5</v>
+      </c>
+      <c r="K37" s="61">
+        <f>1*6+2</f>
+        <v>8</v>
+      </c>
       <c r="L37" s="62"/>
-      <c r="M37" s="63"/>
+      <c r="M37" s="63">
+        <v>20</v>
+      </c>
       <c r="N37" s="64"/>
-      <c r="O37" s="65"/>
+      <c r="O37" s="65">
+        <v>20</v>
+      </c>
       <c r="P37" s="66"/>
-      <c r="Q37" s="66"/>
+      <c r="Q37" s="66">
+        <v>121</v>
+      </c>
       <c r="R37" s="67"/>
       <c r="S37" s="62"/>
       <c r="T37" s="77">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="U37" s="77">
         <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
-        <v>0</v>
+        <v>19261</v>
       </c>
       <c r="V37" s="77">
         <f>U37/6</f>
-        <v>0</v>
+        <v>3210.1666666666665</v>
       </c>
       <c r="W37" s="50"/>
     </row>
@@ -9971,9 +10111,13 @@
       <c r="L38" s="55"/>
       <c r="M38" s="73"/>
       <c r="N38" s="74"/>
-      <c r="O38" s="70"/>
+      <c r="O38" s="70">
+        <v>1</v>
+      </c>
       <c r="P38" s="71"/>
-      <c r="Q38" s="71"/>
+      <c r="Q38" s="71">
+        <v>3</v>
+      </c>
       <c r="R38" s="72"/>
       <c r="S38" s="55"/>
       <c r="T38" s="75">
@@ -9982,11 +10126,11 @@
       </c>
       <c r="U38" s="75">
         <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V38" s="75">
         <f>U38/24</f>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39" spans="1:23" x14ac:dyDescent="0.25">
@@ -10035,7 +10179,10 @@
       <c r="B40" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="C40" s="59"/>
+      <c r="C40" s="59">
+        <f>252+58</f>
+        <v>310</v>
+      </c>
       <c r="D40" s="59"/>
       <c r="E40" s="59"/>
       <c r="F40" s="59"/>
@@ -10043,26 +10190,32 @@
       <c r="H40" s="59"/>
       <c r="I40" s="59"/>
       <c r="J40" s="60"/>
-      <c r="K40" s="61"/>
+      <c r="K40" s="61">
+        <v>20</v>
+      </c>
       <c r="L40" s="62"/>
       <c r="M40" s="63"/>
       <c r="N40" s="64"/>
-      <c r="O40" s="65"/>
+      <c r="O40" s="65">
+        <v>2</v>
+      </c>
       <c r="P40" s="66"/>
-      <c r="Q40" s="66"/>
+      <c r="Q40" s="66">
+        <v>1</v>
+      </c>
       <c r="R40" s="67"/>
       <c r="S40" s="62"/>
       <c r="T40" s="77">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="U40" s="77">
         <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
-        <v>0</v>
+        <v>7532</v>
       </c>
       <c r="V40" s="77">
         <f>U40/24</f>
-        <v>0</v>
+        <v>313.83333333333331</v>
       </c>
     </row>
     <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -10073,7 +10226,10 @@
       <c r="B41" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="C41" s="82"/>
+      <c r="C41" s="82">
+        <f>480+11</f>
+        <v>491</v>
+      </c>
       <c r="D41" s="82"/>
       <c r="E41" s="82"/>
       <c r="F41" s="82"/>
@@ -10083,11 +10239,17 @@
       <c r="J41" s="83"/>
       <c r="K41" s="84"/>
       <c r="L41" s="85"/>
-      <c r="M41" s="86"/>
+      <c r="M41" s="86">
+        <v>10</v>
+      </c>
       <c r="N41" s="87"/>
-      <c r="O41" s="82"/>
+      <c r="O41" s="82">
+        <v>10</v>
+      </c>
       <c r="P41" s="83"/>
-      <c r="Q41" s="83"/>
+      <c r="Q41" s="83">
+        <v>25</v>
+      </c>
       <c r="R41" s="84"/>
       <c r="S41" s="85"/>
       <c r="T41" s="88">
@@ -10096,11 +10258,11 @@
       </c>
       <c r="U41" s="88">
         <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
-        <v>0</v>
+        <v>6432</v>
       </c>
       <c r="V41" s="88">
         <f>U41/12</f>
-        <v>0</v>
+        <v>536</v>
       </c>
     </row>
     <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -10140,34 +10302,53 @@
       <c r="B43" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="C43" s="65"/>
+      <c r="C43" s="65">
+        <f>5832+19764+10260+29</f>
+        <v>35885</v>
+      </c>
       <c r="D43" s="65"/>
       <c r="E43" s="65"/>
       <c r="F43" s="65"/>
       <c r="G43" s="65"/>
-      <c r="H43" s="65"/>
-      <c r="I43" s="65"/>
-      <c r="J43" s="66"/>
-      <c r="K43" s="67"/>
+      <c r="H43" s="65">
+        <v>1</v>
+      </c>
+      <c r="I43" s="65">
+        <v>12</v>
+      </c>
+      <c r="J43" s="66">
+        <f>19*6</f>
+        <v>114</v>
+      </c>
+      <c r="K43" s="67">
+        <f>71*6+2</f>
+        <v>428</v>
+      </c>
       <c r="L43" s="62"/>
-      <c r="M43" s="63"/>
+      <c r="M43" s="63">
+        <v>364</v>
+      </c>
       <c r="N43" s="64"/>
-      <c r="O43" s="65"/>
+      <c r="O43" s="65">
+        <v>371</v>
+      </c>
       <c r="P43" s="66"/>
-      <c r="Q43" s="66"/>
+      <c r="Q43" s="66">
+        <v>508</v>
+      </c>
       <c r="R43" s="67"/>
       <c r="S43" s="62"/>
       <c r="T43" s="77">
         <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
-        <v>0</v>
+        <v>555</v>
       </c>
       <c r="U43" s="77">
         <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
-        <v>0</v>
+        <v>223323</v>
       </c>
       <c r="V43" s="77">
         <f>U43/6</f>
-        <v>0</v>
+        <v>37220.5</v>
       </c>
     </row>
     <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -10217,11 +10398,17 @@
       <c r="J45" s="71"/>
       <c r="K45" s="72"/>
       <c r="L45" s="55"/>
-      <c r="M45" s="73"/>
+      <c r="M45" s="73">
+        <v>1</v>
+      </c>
       <c r="N45" s="74"/>
-      <c r="O45" s="70"/>
+      <c r="O45" s="70">
+        <v>1</v>
+      </c>
       <c r="P45" s="71"/>
-      <c r="Q45" s="71"/>
+      <c r="Q45" s="71">
+        <v>3</v>
+      </c>
       <c r="R45" s="72"/>
       <c r="S45" s="55"/>
       <c r="T45" s="75">
@@ -10230,11 +10417,11 @@
       </c>
       <c r="U45" s="75">
         <f>C45*24+M45*24+O45*24+Q45*24+T45</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="V45" s="75">
         <f>U45/24</f>
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46" spans="1:23" x14ac:dyDescent="0.25">
@@ -10283,34 +10470,49 @@
       <c r="B47" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="C47" s="65"/>
+      <c r="C47" s="65">
+        <f>99+648+324+88+540+103+324+432+106</f>
+        <v>2664</v>
+      </c>
       <c r="D47" s="65"/>
       <c r="E47" s="65"/>
       <c r="F47" s="65"/>
       <c r="G47" s="65"/>
-      <c r="H47" s="65"/>
+      <c r="H47" s="65">
+        <v>1</v>
+      </c>
       <c r="I47" s="65"/>
       <c r="J47" s="66"/>
-      <c r="K47" s="67"/>
+      <c r="K47" s="67">
+        <v>5</v>
+      </c>
       <c r="L47" s="62"/>
-      <c r="M47" s="63"/>
+      <c r="M47" s="63">
+        <v>5</v>
+      </c>
       <c r="N47" s="64"/>
-      <c r="O47" s="65"/>
+      <c r="O47" s="65">
+        <v>16</v>
+      </c>
       <c r="P47" s="66"/>
-      <c r="Q47" s="66"/>
-      <c r="R47" s="67"/>
+      <c r="Q47" s="66">
+        <v>5</v>
+      </c>
+      <c r="R47" s="67">
+        <v>3</v>
+      </c>
       <c r="S47" s="62"/>
       <c r="T47" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="U47" s="77">
         <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
-        <v>0</v>
+        <v>16149</v>
       </c>
       <c r="V47" s="77">
         <f>U47/6</f>
-        <v>0</v>
+        <v>2691.5</v>
       </c>
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.25">
@@ -10326,7 +10528,9 @@
       <c r="E48" s="70"/>
       <c r="F48" s="70"/>
       <c r="G48" s="70"/>
-      <c r="H48" s="70"/>
+      <c r="H48" s="70">
+        <v>24</v>
+      </c>
       <c r="I48" s="70"/>
       <c r="J48" s="71"/>
       <c r="K48" s="72"/>
@@ -10340,15 +10544,15 @@
       <c r="S48" s="55"/>
       <c r="T48" s="75">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="U48" s="75">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V48" s="75">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.25">
@@ -10435,7 +10639,9 @@
       <c r="B51" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="C51" s="65"/>
+      <c r="C51" s="65">
+        <v>34</v>
+      </c>
       <c r="D51" s="65"/>
       <c r="E51" s="65"/>
       <c r="F51" s="65"/>
@@ -10458,11 +10664,11 @@
       </c>
       <c r="U51" s="77">
         <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="V51" s="77">
         <f>U51/6</f>
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.25">
@@ -10511,7 +10717,9 @@
       <c r="B53" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C53" s="70"/>
+      <c r="C53" s="70">
+        <v>7</v>
+      </c>
       <c r="D53" s="70"/>
       <c r="E53" s="70"/>
       <c r="F53" s="70"/>
@@ -10534,11 +10742,11 @@
       </c>
       <c r="U53" s="75">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="V53" s="75">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.25">
@@ -10664,7 +10872,7 @@
       </c>
       <c r="C58" s="2">
         <f>SUM(C7:C57)</f>
-        <v>0</v>
+        <v>46283</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" s="2"/>
@@ -10678,23 +10886,23 @@
       </c>
       <c r="H58" s="2">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1189</v>
       </c>
       <c r="I58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="J58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="K58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>471</v>
       </c>
       <c r="M58" s="5">
         <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
-        <v>0</v>
+        <v>411</v>
       </c>
       <c r="N58" s="5">
         <f t="shared" si="12"/>
@@ -10702,32 +10910,32 @@
       </c>
       <c r="O58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>441</v>
       </c>
       <c r="P58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="Q58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>693</v>
       </c>
       <c r="R58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="S58" s="55"/>
       <c r="T58" s="4">
         <f>SUM(T7:T57)</f>
-        <v>0</v>
+        <v>1862</v>
       </c>
       <c r="U58" s="90">
         <f>SUM(U7:U57)</f>
-        <v>0</v>
+        <v>368240</v>
       </c>
       <c r="V58" s="4">
         <f>SUM(V7:V57)</f>
-        <v>0</v>
+        <v>47978.458333333336</v>
       </c>
     </row>
     <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>

--- a/GBDS AUGUST FILES 2026/INVENTORY COUNT SHEET - AUGUST 2026.xlsx
+++ b/GBDS AUGUST FILES 2026/INVENTORY COUNT SHEET - AUGUST 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS AUGUST FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{380D70AC-84DD-4F16-A9DB-A5613DF33D00}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E7F079B-DA87-406D-BCF5-E48E9AB07271}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="3" activeTab="10" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="3" activeTab="11" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
   </bookViews>
   <sheets>
     <sheet name="SAMPLE" sheetId="32" r:id="rId1"/>
@@ -11454,34 +11454,42 @@
       <c r="B7" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="52"/>
+      <c r="C7" s="52">
+        <v>32</v>
+      </c>
       <c r="D7" s="52"/>
       <c r="E7" s="52"/>
       <c r="F7" s="52"/>
       <c r="G7" s="52"/>
       <c r="H7" s="52"/>
-      <c r="I7" s="52"/>
+      <c r="I7" s="52">
+        <v>3</v>
+      </c>
       <c r="J7" s="53"/>
-      <c r="K7" s="54"/>
+      <c r="K7" s="54">
+        <v>6</v>
+      </c>
       <c r="L7" s="55"/>
       <c r="M7" s="56"/>
       <c r="N7" s="57"/>
-      <c r="O7" s="52"/>
+      <c r="O7" s="52">
+        <v>1</v>
+      </c>
       <c r="P7" s="53"/>
       <c r="Q7" s="53"/>
       <c r="R7" s="54"/>
       <c r="S7" s="55"/>
       <c r="T7" s="58">
         <f>H7+I7+J7+K7+N7+P7+R7</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="U7" s="58">
         <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
-        <v>0</v>
+        <v>801</v>
       </c>
       <c r="V7" s="58">
         <f>U7/24</f>
-        <v>0</v>
+        <v>33.375</v>
       </c>
       <c r="W7" s="50"/>
       <c r="AF7" s="12"/>
@@ -11516,7 +11524,10 @@
       <c r="B8" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="59"/>
+      <c r="C8" s="59">
+        <f>41+43</f>
+        <v>84</v>
+      </c>
       <c r="D8" s="59"/>
       <c r="E8" s="59"/>
       <c r="F8" s="59"/>
@@ -11528,22 +11539,28 @@
       <c r="L8" s="62"/>
       <c r="M8" s="63"/>
       <c r="N8" s="64"/>
-      <c r="O8" s="65"/>
-      <c r="P8" s="66"/>
-      <c r="Q8" s="66"/>
+      <c r="O8" s="65">
+        <v>1</v>
+      </c>
+      <c r="P8" s="66">
+        <v>12</v>
+      </c>
+      <c r="Q8" s="66">
+        <v>1</v>
+      </c>
       <c r="R8" s="67"/>
       <c r="S8" s="62"/>
       <c r="T8" s="68">
         <f t="shared" ref="T8:T41" si="0">H8+I8+J8+K8+N8+P8+R8</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="U8" s="69">
         <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
-        <v>0</v>
+        <v>2076</v>
       </c>
       <c r="V8" s="69">
         <f>U8/24</f>
-        <v>0</v>
+        <v>86.5</v>
       </c>
       <c r="W8" s="50"/>
       <c r="AF8" s="12"/>
@@ -11578,7 +11595,10 @@
       <c r="B9" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="70"/>
+      <c r="C9" s="70">
+        <f>59+30</f>
+        <v>89</v>
+      </c>
       <c r="D9" s="70"/>
       <c r="E9" s="70"/>
       <c r="F9" s="70"/>
@@ -11590,9 +11610,13 @@
       <c r="L9" s="55"/>
       <c r="M9" s="73"/>
       <c r="N9" s="74"/>
-      <c r="O9" s="70"/>
+      <c r="O9" s="70">
+        <v>1</v>
+      </c>
       <c r="P9" s="71"/>
-      <c r="Q9" s="71"/>
+      <c r="Q9" s="71">
+        <v>1</v>
+      </c>
       <c r="R9" s="72"/>
       <c r="S9" s="55"/>
       <c r="T9" s="75">
@@ -11601,11 +11625,11 @@
       </c>
       <c r="U9" s="76">
         <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
-        <v>0</v>
+        <v>2184</v>
       </c>
       <c r="V9" s="76">
         <f t="shared" ref="V9:V11" si="3">U9/24</f>
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="W9" s="50"/>
       <c r="AF9" s="12"/>
@@ -11640,7 +11664,10 @@
       <c r="B10" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="C10" s="70"/>
+      <c r="C10" s="70">
+        <f>31+10</f>
+        <v>41</v>
+      </c>
       <c r="D10" s="70"/>
       <c r="E10" s="70"/>
       <c r="F10" s="70"/>
@@ -11663,11 +11690,11 @@
       </c>
       <c r="U10" s="58">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>984</v>
       </c>
       <c r="V10" s="58">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="W10" s="50"/>
       <c r="AF10" s="12"/>
@@ -11702,7 +11729,9 @@
       <c r="B11" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="70"/>
+      <c r="C11" s="70">
+        <v>9</v>
+      </c>
       <c r="D11" s="70"/>
       <c r="E11" s="70"/>
       <c r="F11" s="70"/>
@@ -11710,7 +11739,9 @@
       <c r="H11" s="70"/>
       <c r="I11" s="70"/>
       <c r="J11" s="71"/>
-      <c r="K11" s="72"/>
+      <c r="K11" s="72">
+        <v>2</v>
+      </c>
       <c r="L11" s="55"/>
       <c r="M11" s="73"/>
       <c r="N11" s="74"/>
@@ -11721,15 +11752,15 @@
       <c r="S11" s="55"/>
       <c r="T11" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U11" s="58">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="V11" s="58">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>9.0833333333333339</v>
       </c>
       <c r="AF11" s="12"/>
       <c r="AG11" s="12"/>
@@ -11762,7 +11793,10 @@
       <c r="B12" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="59"/>
+      <c r="C12" s="59">
+        <f>1224+53+1080+29+864+26</f>
+        <v>3276</v>
+      </c>
       <c r="D12" s="59"/>
       <c r="E12" s="59"/>
       <c r="F12" s="59"/>
@@ -11772,24 +11806,36 @@
       <c r="J12" s="60"/>
       <c r="K12" s="61"/>
       <c r="L12" s="62"/>
-      <c r="M12" s="63"/>
-      <c r="N12" s="64"/>
-      <c r="O12" s="65"/>
-      <c r="P12" s="66"/>
-      <c r="Q12" s="66"/>
-      <c r="R12" s="67"/>
+      <c r="M12" s="63">
+        <v>4</v>
+      </c>
+      <c r="N12" s="64">
+        <v>9</v>
+      </c>
+      <c r="O12" s="65">
+        <v>2</v>
+      </c>
+      <c r="P12" s="66">
+        <v>12</v>
+      </c>
+      <c r="Q12" s="66">
+        <v>26</v>
+      </c>
+      <c r="R12" s="67">
+        <v>6</v>
+      </c>
       <c r="S12" s="62"/>
       <c r="T12" s="69">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="U12" s="69">
         <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
-        <v>0</v>
+        <v>79419</v>
       </c>
       <c r="V12" s="69">
         <f>U12/24</f>
-        <v>0</v>
+        <v>3309.125</v>
       </c>
       <c r="W12" s="9"/>
       <c r="X12" s="9"/>
@@ -11831,12 +11877,17 @@
       <c r="B13" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="70"/>
+      <c r="C13" s="70">
+        <v>2</v>
+      </c>
       <c r="D13" s="70"/>
       <c r="E13" s="70"/>
       <c r="F13" s="70"/>
       <c r="G13" s="70"/>
-      <c r="H13" s="70"/>
+      <c r="H13" s="70">
+        <f>16</f>
+        <v>16</v>
+      </c>
       <c r="I13" s="70"/>
       <c r="J13" s="71"/>
       <c r="K13" s="72"/>
@@ -11850,15 +11901,15 @@
       <c r="S13" s="55"/>
       <c r="T13" s="76">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="U13" s="76">
         <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="V13" s="76">
         <f>U13/24</f>
-        <v>0</v>
+        <v>2.6666666666666665</v>
       </c>
       <c r="AF13" s="12"/>
       <c r="AG13" s="12"/>
@@ -11892,7 +11943,9 @@
       <c r="B14" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="70"/>
+      <c r="C14" s="70">
+        <v>2</v>
+      </c>
       <c r="D14" s="70"/>
       <c r="E14" s="70"/>
       <c r="F14" s="70"/>
@@ -11915,11 +11968,11 @@
       </c>
       <c r="U14" s="75">
         <f t="shared" ref="U14:U36" si="4">C14*24+M14*24+O14*24+Q14*24+T14</f>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V14" s="75">
         <f t="shared" ref="V14:V36" si="5">U14/24</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF14" s="12"/>
       <c r="AG14" s="12"/>
@@ -12080,7 +12133,10 @@
       <c r="E17" s="70"/>
       <c r="F17" s="70"/>
       <c r="G17" s="70"/>
-      <c r="H17" s="70"/>
+      <c r="H17" s="70">
+        <f>3*24</f>
+        <v>72</v>
+      </c>
       <c r="I17" s="70"/>
       <c r="J17" s="71"/>
       <c r="K17" s="72"/>
@@ -12094,15 +12150,15 @@
       <c r="S17" s="55"/>
       <c r="T17" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="U17" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="V17" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF17" s="12"/>
       <c r="AG17" s="12"/>
@@ -12196,12 +12252,17 @@
       <c r="B19" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="C19" s="70"/>
+      <c r="C19" s="70">
+        <v>2</v>
+      </c>
       <c r="D19" s="70"/>
       <c r="E19" s="70"/>
       <c r="F19" s="70"/>
       <c r="G19" s="70"/>
-      <c r="H19" s="70"/>
+      <c r="H19" s="70">
+        <f>20+24</f>
+        <v>44</v>
+      </c>
       <c r="I19" s="70"/>
       <c r="J19" s="71"/>
       <c r="K19" s="72"/>
@@ -12215,15 +12276,15 @@
       <c r="S19" s="55"/>
       <c r="T19" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="U19" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="V19" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3.8333333333333335</v>
       </c>
       <c r="AF19" s="12"/>
       <c r="AG19" s="12"/>
@@ -12257,7 +12318,9 @@
       <c r="B20" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="70"/>
+      <c r="C20" s="70">
+        <v>5</v>
+      </c>
       <c r="D20" s="70"/>
       <c r="E20" s="70"/>
       <c r="F20" s="70"/>
@@ -12280,11 +12343,11 @@
       </c>
       <c r="U20" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="V20" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AF20" s="12"/>
       <c r="AG20" s="12"/>
@@ -12323,7 +12386,10 @@
       <c r="E21" s="70"/>
       <c r="F21" s="70"/>
       <c r="G21" s="70"/>
-      <c r="H21" s="70"/>
+      <c r="H21" s="70">
+        <f>2*24</f>
+        <v>48</v>
+      </c>
       <c r="I21" s="70"/>
       <c r="J21" s="71"/>
       <c r="K21" s="72"/>
@@ -12337,15 +12403,15 @@
       <c r="S21" s="55"/>
       <c r="T21" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="U21" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V21" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF21" s="12"/>
       <c r="AG21" s="12"/>
@@ -12379,13 +12445,17 @@
       <c r="B22" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="C22" s="70"/>
+      <c r="C22" s="70">
+        <v>2</v>
+      </c>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
       <c r="G22" s="70"/>
       <c r="H22" s="70"/>
-      <c r="I22" s="70"/>
+      <c r="I22" s="70">
+        <v>20</v>
+      </c>
       <c r="J22" s="71"/>
       <c r="K22" s="72"/>
       <c r="L22" s="55"/>
@@ -12398,15 +12468,15 @@
       <c r="S22" s="55"/>
       <c r="T22" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="U22" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="V22" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2.8333333333333335</v>
       </c>
       <c r="W22" s="9"/>
       <c r="X22" s="9"/>
@@ -12454,7 +12524,10 @@
       <c r="E23" s="70"/>
       <c r="F23" s="70"/>
       <c r="G23" s="70"/>
-      <c r="H23" s="70"/>
+      <c r="H23" s="70">
+        <f>37*24+19</f>
+        <v>907</v>
+      </c>
       <c r="I23" s="70"/>
       <c r="J23" s="71"/>
       <c r="K23" s="72"/>
@@ -12468,15 +12541,15 @@
       <c r="S23" s="55"/>
       <c r="T23" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>907</v>
       </c>
       <c r="U23" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>907</v>
       </c>
       <c r="V23" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>37.791666666666664</v>
       </c>
       <c r="W23" s="9"/>
       <c r="X23" s="9"/>
@@ -12519,12 +12592,17 @@
       <c r="B24" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="C24" s="70"/>
+      <c r="C24" s="70">
+        <v>2</v>
+      </c>
       <c r="D24" s="70"/>
       <c r="E24" s="70"/>
       <c r="F24" s="70"/>
       <c r="G24" s="70"/>
-      <c r="H24" s="70"/>
+      <c r="H24" s="70">
+        <f>3*24</f>
+        <v>72</v>
+      </c>
       <c r="I24" s="70"/>
       <c r="J24" s="71"/>
       <c r="K24" s="72"/>
@@ -12538,15 +12616,15 @@
       <c r="S24" s="55"/>
       <c r="T24" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="U24" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="V24" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AF24" s="12"/>
       <c r="AG24" s="12"/>
@@ -12580,34 +12658,44 @@
       <c r="B25" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="C25" s="70"/>
+      <c r="C25" s="70">
+        <v>42</v>
+      </c>
       <c r="D25" s="70"/>
       <c r="E25" s="70"/>
       <c r="F25" s="70"/>
       <c r="G25" s="70"/>
       <c r="H25" s="70"/>
-      <c r="I25" s="70"/>
+      <c r="I25" s="70">
+        <v>1</v>
+      </c>
       <c r="J25" s="71"/>
       <c r="K25" s="72"/>
       <c r="L25" s="55"/>
-      <c r="M25" s="73"/>
+      <c r="M25" s="73">
+        <v>1</v>
+      </c>
       <c r="N25" s="74"/>
-      <c r="O25" s="70"/>
+      <c r="O25" s="70">
+        <v>1</v>
+      </c>
       <c r="P25" s="71"/>
-      <c r="Q25" s="71"/>
+      <c r="Q25" s="71">
+        <v>5</v>
+      </c>
       <c r="R25" s="72"/>
       <c r="S25" s="55"/>
       <c r="T25" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U25" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1177</v>
       </c>
       <c r="V25" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>49.041666666666664</v>
       </c>
       <c r="AY25" s="14" t="e">
         <f>#REF!-AY24</f>
@@ -12622,7 +12710,9 @@
       <c r="B26" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="C26" s="70"/>
+      <c r="C26" s="70">
+        <v>1</v>
+      </c>
       <c r="D26" s="70"/>
       <c r="E26" s="70"/>
       <c r="F26" s="70"/>
@@ -12634,7 +12724,9 @@
       <c r="L26" s="55"/>
       <c r="M26" s="73"/>
       <c r="N26" s="74"/>
-      <c r="O26" s="70"/>
+      <c r="O26" s="70">
+        <v>1</v>
+      </c>
       <c r="P26" s="71"/>
       <c r="Q26" s="71"/>
       <c r="R26" s="72"/>
@@ -12645,11 +12737,11 @@
       </c>
       <c r="U26" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V26" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W26" s="9"/>
       <c r="X26" s="9"/>
@@ -12669,7 +12761,9 @@
       <c r="B27" s="26" t="s">
         <v>69</v>
       </c>
-      <c r="C27" s="70"/>
+      <c r="C27" s="70">
+        <v>3</v>
+      </c>
       <c r="D27" s="70"/>
       <c r="E27" s="70"/>
       <c r="F27" s="70"/>
@@ -12692,11 +12786,11 @@
       </c>
       <c r="U27" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="V27" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W27" s="9"/>
       <c r="X27" s="9"/>
@@ -12763,34 +12857,42 @@
       <c r="B29" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="C29" s="70"/>
+      <c r="C29" s="70">
+        <v>23</v>
+      </c>
       <c r="D29" s="70"/>
       <c r="E29" s="70"/>
       <c r="F29" s="70"/>
       <c r="G29" s="70"/>
       <c r="H29" s="70"/>
-      <c r="I29" s="70"/>
+      <c r="I29" s="70">
+        <v>5</v>
+      </c>
       <c r="J29" s="71"/>
       <c r="K29" s="72"/>
       <c r="L29" s="55"/>
       <c r="M29" s="73"/>
       <c r="N29" s="74"/>
-      <c r="O29" s="70"/>
+      <c r="O29" s="70">
+        <v>1</v>
+      </c>
       <c r="P29" s="71"/>
-      <c r="Q29" s="71"/>
+      <c r="Q29" s="71">
+        <v>2</v>
+      </c>
       <c r="R29" s="72"/>
       <c r="S29" s="55"/>
       <c r="T29" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U29" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>629</v>
       </c>
       <c r="V29" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>26.208333333333332</v>
       </c>
     </row>
     <row r="30" spans="1:54" x14ac:dyDescent="0.25">
@@ -12801,7 +12903,9 @@
       <c r="B30" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="C30" s="70"/>
+      <c r="C30" s="70">
+        <v>9</v>
+      </c>
       <c r="D30" s="70"/>
       <c r="E30" s="70"/>
       <c r="F30" s="70"/>
@@ -12813,9 +12917,13 @@
       <c r="L30" s="55"/>
       <c r="M30" s="73"/>
       <c r="N30" s="74"/>
-      <c r="O30" s="70"/>
+      <c r="O30" s="70">
+        <v>1</v>
+      </c>
       <c r="P30" s="71"/>
-      <c r="Q30" s="71"/>
+      <c r="Q30" s="71">
+        <v>2</v>
+      </c>
       <c r="R30" s="72"/>
       <c r="S30" s="55"/>
       <c r="T30" s="58">
@@ -12824,11 +12932,11 @@
       </c>
       <c r="U30" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>288</v>
       </c>
       <c r="V30" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="31" spans="1:54" x14ac:dyDescent="0.25">
@@ -12915,7 +13023,9 @@
       <c r="B33" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="C33" s="70"/>
+      <c r="C33" s="70">
+        <v>1</v>
+      </c>
       <c r="D33" s="70"/>
       <c r="E33" s="70"/>
       <c r="F33" s="70"/>
@@ -12925,7 +13035,9 @@
       <c r="J33" s="71"/>
       <c r="K33" s="72"/>
       <c r="L33" s="55"/>
-      <c r="M33" s="73"/>
+      <c r="M33" s="73">
+        <v>1</v>
+      </c>
       <c r="N33" s="74"/>
       <c r="O33" s="70"/>
       <c r="P33" s="71"/>
@@ -12938,11 +13050,11 @@
       </c>
       <c r="U33" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V33" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:23" x14ac:dyDescent="0.25">
@@ -12953,34 +13065,45 @@
       <c r="B34" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="C34" s="70"/>
+      <c r="C34" s="70">
+        <f>42+144</f>
+        <v>186</v>
+      </c>
       <c r="D34" s="70"/>
       <c r="E34" s="70"/>
       <c r="F34" s="70"/>
       <c r="G34" s="70"/>
       <c r="H34" s="70"/>
-      <c r="I34" s="70"/>
+      <c r="I34" s="70">
+        <v>1</v>
+      </c>
       <c r="J34" s="71"/>
-      <c r="K34" s="72"/>
+      <c r="K34" s="72">
+        <v>1</v>
+      </c>
       <c r="L34" s="55"/>
       <c r="M34" s="73"/>
       <c r="N34" s="74"/>
-      <c r="O34" s="70"/>
+      <c r="O34" s="70">
+        <v>2</v>
+      </c>
       <c r="P34" s="71"/>
-      <c r="Q34" s="71"/>
+      <c r="Q34" s="71">
+        <v>1</v>
+      </c>
       <c r="R34" s="72"/>
       <c r="S34" s="55"/>
       <c r="T34" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U34" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4538</v>
       </c>
       <c r="V34" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>189.08333333333334</v>
       </c>
     </row>
     <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -13067,34 +13190,52 @@
       <c r="B37" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="C37" s="59"/>
+      <c r="C37" s="59">
+        <f>22+3024</f>
+        <v>3046</v>
+      </c>
       <c r="D37" s="59"/>
       <c r="E37" s="59"/>
       <c r="F37" s="59"/>
       <c r="G37" s="59"/>
-      <c r="H37" s="59"/>
-      <c r="I37" s="59"/>
-      <c r="J37" s="60"/>
-      <c r="K37" s="61"/>
+      <c r="H37" s="59">
+        <v>4</v>
+      </c>
+      <c r="I37" s="59">
+        <v>2</v>
+      </c>
+      <c r="J37" s="60">
+        <v>5</v>
+      </c>
+      <c r="K37" s="61">
+        <f>6+2</f>
+        <v>8</v>
+      </c>
       <c r="L37" s="62"/>
-      <c r="M37" s="63"/>
+      <c r="M37" s="63">
+        <v>6</v>
+      </c>
       <c r="N37" s="64"/>
-      <c r="O37" s="65"/>
+      <c r="O37" s="65">
+        <v>10</v>
+      </c>
       <c r="P37" s="66"/>
-      <c r="Q37" s="66"/>
+      <c r="Q37" s="66">
+        <v>41</v>
+      </c>
       <c r="R37" s="67"/>
       <c r="S37" s="62"/>
       <c r="T37" s="77">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="U37" s="77">
         <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
-        <v>0</v>
+        <v>18637</v>
       </c>
       <c r="V37" s="77">
         <f>U37/6</f>
-        <v>0</v>
+        <v>3106.1666666666665</v>
       </c>
       <c r="W37" s="50"/>
     </row>
@@ -13118,7 +13259,9 @@
       <c r="L38" s="55"/>
       <c r="M38" s="73"/>
       <c r="N38" s="74"/>
-      <c r="O38" s="70"/>
+      <c r="O38" s="70">
+        <v>1</v>
+      </c>
       <c r="P38" s="71"/>
       <c r="Q38" s="71"/>
       <c r="R38" s="72"/>
@@ -13129,11 +13272,11 @@
       </c>
       <c r="U38" s="75">
         <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V38" s="75">
         <f>U38/24</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:23" x14ac:dyDescent="0.25">
@@ -13182,7 +13325,10 @@
       <c r="B40" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="C40" s="59"/>
+      <c r="C40" s="59">
+        <f>252+58</f>
+        <v>310</v>
+      </c>
       <c r="D40" s="59"/>
       <c r="E40" s="59"/>
       <c r="F40" s="59"/>
@@ -13190,26 +13336,30 @@
       <c r="H40" s="59"/>
       <c r="I40" s="59"/>
       <c r="J40" s="60"/>
-      <c r="K40" s="61"/>
+      <c r="K40" s="61">
+        <v>20</v>
+      </c>
       <c r="L40" s="62"/>
       <c r="M40" s="63"/>
       <c r="N40" s="64"/>
-      <c r="O40" s="65"/>
+      <c r="O40" s="65">
+        <v>2</v>
+      </c>
       <c r="P40" s="66"/>
       <c r="Q40" s="66"/>
       <c r="R40" s="67"/>
       <c r="S40" s="62"/>
       <c r="T40" s="77">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="U40" s="77">
         <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
-        <v>0</v>
+        <v>7508</v>
       </c>
       <c r="V40" s="77">
         <f>U40/24</f>
-        <v>0</v>
+        <v>312.83333333333331</v>
       </c>
     </row>
     <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -13220,7 +13370,10 @@
       <c r="B41" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="C41" s="82"/>
+      <c r="C41" s="82">
+        <f>384+59</f>
+        <v>443</v>
+      </c>
       <c r="D41" s="82"/>
       <c r="E41" s="82"/>
       <c r="F41" s="82"/>
@@ -13232,9 +13385,13 @@
       <c r="L41" s="85"/>
       <c r="M41" s="86"/>
       <c r="N41" s="87"/>
-      <c r="O41" s="82"/>
+      <c r="O41" s="82">
+        <v>8</v>
+      </c>
       <c r="P41" s="83"/>
-      <c r="Q41" s="83"/>
+      <c r="Q41" s="83">
+        <v>48</v>
+      </c>
       <c r="R41" s="84"/>
       <c r="S41" s="85"/>
       <c r="T41" s="88">
@@ -13243,11 +13400,11 @@
       </c>
       <c r="U41" s="88">
         <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
-        <v>0</v>
+        <v>5988</v>
       </c>
       <c r="V41" s="88">
         <f>U41/12</f>
-        <v>0</v>
+        <v>499</v>
       </c>
     </row>
     <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -13287,34 +13444,53 @@
       <c r="B43" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="C43" s="65"/>
+      <c r="C43" s="65">
+        <f>29+5076+19764+10260</f>
+        <v>35129</v>
+      </c>
       <c r="D43" s="65"/>
       <c r="E43" s="65"/>
       <c r="F43" s="65"/>
       <c r="G43" s="65"/>
-      <c r="H43" s="65"/>
-      <c r="I43" s="65"/>
-      <c r="J43" s="66"/>
-      <c r="K43" s="67"/>
+      <c r="H43" s="65">
+        <v>7</v>
+      </c>
+      <c r="I43" s="65">
+        <v>12</v>
+      </c>
+      <c r="J43" s="66">
+        <f>20*6</f>
+        <v>120</v>
+      </c>
+      <c r="K43" s="67">
+        <f>71*6+2</f>
+        <v>428</v>
+      </c>
       <c r="L43" s="62"/>
-      <c r="M43" s="63"/>
+      <c r="M43" s="63">
+        <v>59</v>
+      </c>
       <c r="N43" s="64"/>
-      <c r="O43" s="65"/>
+      <c r="O43" s="65">
+        <v>83</v>
+      </c>
       <c r="P43" s="66"/>
-      <c r="Q43" s="66"/>
+      <c r="Q43" s="66">
+        <v>649</v>
+      </c>
       <c r="R43" s="67"/>
       <c r="S43" s="62"/>
       <c r="T43" s="77">
         <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
-        <v>0</v>
+        <v>567</v>
       </c>
       <c r="U43" s="77">
         <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
-        <v>0</v>
+        <v>216087</v>
       </c>
       <c r="V43" s="77">
         <f>U43/6</f>
-        <v>0</v>
+        <v>36014.5</v>
       </c>
     </row>
     <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -13366,7 +13542,9 @@
       <c r="L45" s="55"/>
       <c r="M45" s="73"/>
       <c r="N45" s="74"/>
-      <c r="O45" s="70"/>
+      <c r="O45" s="70">
+        <v>1</v>
+      </c>
       <c r="P45" s="71"/>
       <c r="Q45" s="71"/>
       <c r="R45" s="72"/>
@@ -13377,11 +13555,11 @@
       </c>
       <c r="U45" s="75">
         <f>C45*24+M45*24+O45*24+Q45*24+T45</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V45" s="75">
         <f>U45/24</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:23" x14ac:dyDescent="0.25">
@@ -13430,34 +13608,47 @@
       <c r="B47" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="C47" s="65"/>
+      <c r="C47" s="65">
+        <f>99+648+324+88+540+103+324+432+106</f>
+        <v>2664</v>
+      </c>
       <c r="D47" s="65"/>
       <c r="E47" s="65"/>
       <c r="F47" s="65"/>
       <c r="G47" s="65"/>
-      <c r="H47" s="65"/>
+      <c r="H47" s="65">
+        <v>1</v>
+      </c>
       <c r="I47" s="65"/>
       <c r="J47" s="66"/>
-      <c r="K47" s="67"/>
+      <c r="K47" s="67">
+        <v>5</v>
+      </c>
       <c r="L47" s="62"/>
       <c r="M47" s="63"/>
       <c r="N47" s="64"/>
-      <c r="O47" s="65"/>
+      <c r="O47" s="65">
+        <v>16</v>
+      </c>
       <c r="P47" s="66"/>
-      <c r="Q47" s="66"/>
-      <c r="R47" s="67"/>
+      <c r="Q47" s="66">
+        <v>5</v>
+      </c>
+      <c r="R47" s="67">
+        <v>3</v>
+      </c>
       <c r="S47" s="62"/>
       <c r="T47" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="U47" s="77">
         <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
-        <v>0</v>
+        <v>16119</v>
       </c>
       <c r="V47" s="77">
         <f>U47/6</f>
-        <v>0</v>
+        <v>2686.5</v>
       </c>
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.25">
@@ -13473,7 +13664,9 @@
       <c r="E48" s="70"/>
       <c r="F48" s="70"/>
       <c r="G48" s="70"/>
-      <c r="H48" s="70"/>
+      <c r="H48" s="70">
+        <v>24</v>
+      </c>
       <c r="I48" s="70"/>
       <c r="J48" s="71"/>
       <c r="K48" s="72"/>
@@ -13487,15 +13680,15 @@
       <c r="S48" s="55"/>
       <c r="T48" s="75">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="U48" s="75">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V48" s="75">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.25">
@@ -13582,7 +13775,9 @@
       <c r="B51" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="C51" s="65"/>
+      <c r="C51" s="65">
+        <v>34</v>
+      </c>
       <c r="D51" s="65"/>
       <c r="E51" s="65"/>
       <c r="F51" s="65"/>
@@ -13605,11 +13800,11 @@
       </c>
       <c r="U51" s="77">
         <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="V51" s="77">
         <f>U51/6</f>
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.25">
@@ -13658,7 +13853,9 @@
       <c r="B53" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C53" s="70"/>
+      <c r="C53" s="70">
+        <v>7</v>
+      </c>
       <c r="D53" s="70"/>
       <c r="E53" s="70"/>
       <c r="F53" s="70"/>
@@ -13681,11 +13878,11 @@
       </c>
       <c r="U53" s="75">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="V53" s="75">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.25">
@@ -13811,7 +14008,7 @@
       </c>
       <c r="C58" s="2">
         <f>SUM(C7:C57)</f>
-        <v>0</v>
+        <v>45444</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" s="2"/>
@@ -13825,56 +14022,56 @@
       </c>
       <c r="H58" s="2">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1195</v>
       </c>
       <c r="I58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="J58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="K58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>470</v>
       </c>
       <c r="M58" s="5">
         <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="N58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="P58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>781</v>
       </c>
       <c r="R58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="S58" s="55"/>
       <c r="T58" s="4">
         <f>SUM(T7:T57)</f>
-        <v>0</v>
+        <v>1876</v>
       </c>
       <c r="U58" s="90">
         <f>SUM(U7:U57)</f>
-        <v>0</v>
+        <v>358804</v>
       </c>
       <c r="V58" s="4">
         <f>SUM(V7:V57)</f>
-        <v>0</v>
+        <v>46580.541666666664</v>
       </c>
     </row>
     <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>

--- a/GBDS AUGUST FILES 2026/INVENTORY COUNT SHEET - AUGUST 2026.xlsx
+++ b/GBDS AUGUST FILES 2026/INVENTORY COUNT SHEET - AUGUST 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS AUGUST FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E7F079B-DA87-406D-BCF5-E48E9AB07271}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C079CEF0-0243-4EFD-A26C-11C3141D692E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="3" activeTab="11" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="3" activeTab="12" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
   </bookViews>
   <sheets>
     <sheet name="SAMPLE" sheetId="32" r:id="rId1"/>
@@ -14590,34 +14590,42 @@
       <c r="B7" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="52"/>
+      <c r="C7" s="52">
+        <v>32</v>
+      </c>
       <c r="D7" s="52"/>
       <c r="E7" s="52"/>
       <c r="F7" s="52"/>
       <c r="G7" s="52"/>
       <c r="H7" s="52"/>
-      <c r="I7" s="52"/>
+      <c r="I7" s="52">
+        <v>3</v>
+      </c>
       <c r="J7" s="53"/>
-      <c r="K7" s="54"/>
+      <c r="K7" s="54">
+        <v>6</v>
+      </c>
       <c r="L7" s="55"/>
       <c r="M7" s="56"/>
       <c r="N7" s="57"/>
-      <c r="O7" s="52"/>
+      <c r="O7" s="52">
+        <v>1</v>
+      </c>
       <c r="P7" s="53"/>
       <c r="Q7" s="53"/>
       <c r="R7" s="54"/>
       <c r="S7" s="55"/>
       <c r="T7" s="58">
         <f>H7+I7+J7+K7+N7+P7+R7</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="U7" s="58">
         <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
-        <v>0</v>
+        <v>801</v>
       </c>
       <c r="V7" s="58">
         <f>U7/24</f>
-        <v>0</v>
+        <v>33.375</v>
       </c>
       <c r="W7" s="50"/>
       <c r="AF7" s="12"/>
@@ -14652,7 +14660,10 @@
       <c r="B8" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="59"/>
+      <c r="C8" s="59">
+        <f>41+43</f>
+        <v>84</v>
+      </c>
       <c r="D8" s="59"/>
       <c r="E8" s="59"/>
       <c r="F8" s="59"/>
@@ -14664,22 +14675,28 @@
       <c r="L8" s="62"/>
       <c r="M8" s="63"/>
       <c r="N8" s="64"/>
-      <c r="O8" s="65"/>
-      <c r="P8" s="66"/>
-      <c r="Q8" s="66"/>
+      <c r="O8" s="65">
+        <v>1</v>
+      </c>
+      <c r="P8" s="66">
+        <v>12</v>
+      </c>
+      <c r="Q8" s="66">
+        <v>1</v>
+      </c>
       <c r="R8" s="67"/>
       <c r="S8" s="62"/>
       <c r="T8" s="68">
         <f t="shared" ref="T8:T41" si="0">H8+I8+J8+K8+N8+P8+R8</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="U8" s="69">
         <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
-        <v>0</v>
+        <v>2076</v>
       </c>
       <c r="V8" s="69">
         <f>U8/24</f>
-        <v>0</v>
+        <v>86.5</v>
       </c>
       <c r="W8" s="50"/>
       <c r="AF8" s="12"/>
@@ -14714,7 +14731,10 @@
       <c r="B9" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="70"/>
+      <c r="C9" s="70">
+        <f>59+30</f>
+        <v>89</v>
+      </c>
       <c r="D9" s="70"/>
       <c r="E9" s="70"/>
       <c r="F9" s="70"/>
@@ -14726,9 +14746,13 @@
       <c r="L9" s="55"/>
       <c r="M9" s="73"/>
       <c r="N9" s="74"/>
-      <c r="O9" s="70"/>
+      <c r="O9" s="70">
+        <v>1</v>
+      </c>
       <c r="P9" s="71"/>
-      <c r="Q9" s="71"/>
+      <c r="Q9" s="71">
+        <v>1</v>
+      </c>
       <c r="R9" s="72"/>
       <c r="S9" s="55"/>
       <c r="T9" s="75">
@@ -14737,11 +14761,11 @@
       </c>
       <c r="U9" s="76">
         <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
-        <v>0</v>
+        <v>2184</v>
       </c>
       <c r="V9" s="76">
         <f t="shared" ref="V9:V11" si="3">U9/24</f>
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="W9" s="50"/>
       <c r="AF9" s="12"/>
@@ -14776,7 +14800,10 @@
       <c r="B10" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="C10" s="70"/>
+      <c r="C10" s="70">
+        <f>31+10</f>
+        <v>41</v>
+      </c>
       <c r="D10" s="70"/>
       <c r="E10" s="70"/>
       <c r="F10" s="70"/>
@@ -14799,11 +14826,11 @@
       </c>
       <c r="U10" s="58">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>984</v>
       </c>
       <c r="V10" s="58">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="W10" s="50"/>
       <c r="AF10" s="12"/>
@@ -14838,7 +14865,9 @@
       <c r="B11" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="70"/>
+      <c r="C11" s="70">
+        <v>9</v>
+      </c>
       <c r="D11" s="70"/>
       <c r="E11" s="70"/>
       <c r="F11" s="70"/>
@@ -14846,7 +14875,9 @@
       <c r="H11" s="70"/>
       <c r="I11" s="70"/>
       <c r="J11" s="71"/>
-      <c r="K11" s="72"/>
+      <c r="K11" s="72">
+        <v>2</v>
+      </c>
       <c r="L11" s="55"/>
       <c r="M11" s="73"/>
       <c r="N11" s="74"/>
@@ -14857,15 +14888,15 @@
       <c r="S11" s="55"/>
       <c r="T11" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U11" s="58">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="V11" s="58">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>9.0833333333333339</v>
       </c>
       <c r="AF11" s="12"/>
       <c r="AG11" s="12"/>
@@ -14898,7 +14929,10 @@
       <c r="B12" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="59"/>
+      <c r="C12" s="59">
+        <f>1224+53+1080+29+864+26</f>
+        <v>3276</v>
+      </c>
       <c r="D12" s="59"/>
       <c r="E12" s="59"/>
       <c r="F12" s="59"/>
@@ -14908,24 +14942,36 @@
       <c r="J12" s="60"/>
       <c r="K12" s="61"/>
       <c r="L12" s="62"/>
-      <c r="M12" s="63"/>
-      <c r="N12" s="64"/>
-      <c r="O12" s="65"/>
-      <c r="P12" s="66"/>
-      <c r="Q12" s="66"/>
-      <c r="R12" s="67"/>
+      <c r="M12" s="63">
+        <v>4</v>
+      </c>
+      <c r="N12" s="64">
+        <v>9</v>
+      </c>
+      <c r="O12" s="65">
+        <v>2</v>
+      </c>
+      <c r="P12" s="66">
+        <v>12</v>
+      </c>
+      <c r="Q12" s="66">
+        <v>26</v>
+      </c>
+      <c r="R12" s="67">
+        <v>6</v>
+      </c>
       <c r="S12" s="62"/>
       <c r="T12" s="69">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="U12" s="69">
         <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
-        <v>0</v>
+        <v>79419</v>
       </c>
       <c r="V12" s="69">
         <f>U12/24</f>
-        <v>0</v>
+        <v>3309.125</v>
       </c>
       <c r="W12" s="9"/>
       <c r="X12" s="9"/>
@@ -14967,12 +15013,16 @@
       <c r="B13" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="70"/>
+      <c r="C13" s="70">
+        <v>2</v>
+      </c>
       <c r="D13" s="70"/>
       <c r="E13" s="70"/>
       <c r="F13" s="70"/>
       <c r="G13" s="70"/>
-      <c r="H13" s="70"/>
+      <c r="H13" s="70">
+        <v>16</v>
+      </c>
       <c r="I13" s="70"/>
       <c r="J13" s="71"/>
       <c r="K13" s="72"/>
@@ -14986,15 +15036,15 @@
       <c r="S13" s="55"/>
       <c r="T13" s="76">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="U13" s="76">
         <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="V13" s="76">
         <f>U13/24</f>
-        <v>0</v>
+        <v>2.6666666666666665</v>
       </c>
       <c r="AF13" s="12"/>
       <c r="AG13" s="12"/>
@@ -15028,7 +15078,9 @@
       <c r="B14" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="70"/>
+      <c r="C14" s="70">
+        <v>2</v>
+      </c>
       <c r="D14" s="70"/>
       <c r="E14" s="70"/>
       <c r="F14" s="70"/>
@@ -15051,11 +15103,11 @@
       </c>
       <c r="U14" s="75">
         <f t="shared" ref="U14:U36" si="4">C14*24+M14*24+O14*24+Q14*24+T14</f>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V14" s="75">
         <f t="shared" ref="V14:V36" si="5">U14/24</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF14" s="12"/>
       <c r="AG14" s="12"/>
@@ -15216,7 +15268,10 @@
       <c r="E17" s="70"/>
       <c r="F17" s="70"/>
       <c r="G17" s="70"/>
-      <c r="H17" s="70"/>
+      <c r="H17" s="70">
+        <f>3*24</f>
+        <v>72</v>
+      </c>
       <c r="I17" s="70"/>
       <c r="J17" s="71"/>
       <c r="K17" s="72"/>
@@ -15230,15 +15285,15 @@
       <c r="S17" s="55"/>
       <c r="T17" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="U17" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="V17" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF17" s="12"/>
       <c r="AG17" s="12"/>
@@ -15332,12 +15387,17 @@
       <c r="B19" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="C19" s="70"/>
+      <c r="C19" s="70">
+        <v>2</v>
+      </c>
       <c r="D19" s="70"/>
       <c r="E19" s="70"/>
       <c r="F19" s="70"/>
       <c r="G19" s="70"/>
-      <c r="H19" s="70"/>
+      <c r="H19" s="70">
+        <f>20+24</f>
+        <v>44</v>
+      </c>
       <c r="I19" s="70"/>
       <c r="J19" s="71"/>
       <c r="K19" s="72"/>
@@ -15351,15 +15411,15 @@
       <c r="S19" s="55"/>
       <c r="T19" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="U19" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="V19" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3.8333333333333335</v>
       </c>
       <c r="AF19" s="12"/>
       <c r="AG19" s="12"/>
@@ -15393,7 +15453,9 @@
       <c r="B20" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="70"/>
+      <c r="C20" s="70">
+        <v>5</v>
+      </c>
       <c r="D20" s="70"/>
       <c r="E20" s="70"/>
       <c r="F20" s="70"/>
@@ -15416,11 +15478,11 @@
       </c>
       <c r="U20" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="V20" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AF20" s="12"/>
       <c r="AG20" s="12"/>
@@ -15459,7 +15521,10 @@
       <c r="E21" s="70"/>
       <c r="F21" s="70"/>
       <c r="G21" s="70"/>
-      <c r="H21" s="70"/>
+      <c r="H21" s="70">
+        <f>2*24</f>
+        <v>48</v>
+      </c>
       <c r="I21" s="70"/>
       <c r="J21" s="71"/>
       <c r="K21" s="72"/>
@@ -15473,15 +15538,15 @@
       <c r="S21" s="55"/>
       <c r="T21" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="U21" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V21" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF21" s="12"/>
       <c r="AG21" s="12"/>
@@ -15515,13 +15580,17 @@
       <c r="B22" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="C22" s="70"/>
+      <c r="C22" s="70">
+        <v>2</v>
+      </c>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
       <c r="G22" s="70"/>
       <c r="H22" s="70"/>
-      <c r="I22" s="70"/>
+      <c r="I22" s="70">
+        <v>20</v>
+      </c>
       <c r="J22" s="71"/>
       <c r="K22" s="72"/>
       <c r="L22" s="55"/>
@@ -15534,15 +15603,15 @@
       <c r="S22" s="55"/>
       <c r="T22" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="U22" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="V22" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2.8333333333333335</v>
       </c>
       <c r="W22" s="9"/>
       <c r="X22" s="9"/>
@@ -15590,7 +15659,10 @@
       <c r="E23" s="70"/>
       <c r="F23" s="70"/>
       <c r="G23" s="70"/>
-      <c r="H23" s="70"/>
+      <c r="H23" s="70">
+        <f>37*24+19</f>
+        <v>907</v>
+      </c>
       <c r="I23" s="70"/>
       <c r="J23" s="71"/>
       <c r="K23" s="72"/>
@@ -15604,15 +15676,15 @@
       <c r="S23" s="55"/>
       <c r="T23" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>907</v>
       </c>
       <c r="U23" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>907</v>
       </c>
       <c r="V23" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>37.791666666666664</v>
       </c>
       <c r="W23" s="9"/>
       <c r="X23" s="9"/>
@@ -15655,12 +15727,17 @@
       <c r="B24" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="C24" s="70"/>
+      <c r="C24" s="70">
+        <v>2</v>
+      </c>
       <c r="D24" s="70"/>
       <c r="E24" s="70"/>
       <c r="F24" s="70"/>
       <c r="G24" s="70"/>
-      <c r="H24" s="70"/>
+      <c r="H24" s="70">
+        <f>3*24</f>
+        <v>72</v>
+      </c>
       <c r="I24" s="70"/>
       <c r="J24" s="71"/>
       <c r="K24" s="72"/>
@@ -15674,15 +15751,15 @@
       <c r="S24" s="55"/>
       <c r="T24" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="U24" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="V24" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AF24" s="12"/>
       <c r="AG24" s="12"/>
@@ -15716,34 +15793,44 @@
       <c r="B25" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="C25" s="70"/>
+      <c r="C25" s="70">
+        <v>42</v>
+      </c>
       <c r="D25" s="70"/>
       <c r="E25" s="70"/>
       <c r="F25" s="70"/>
       <c r="G25" s="70"/>
       <c r="H25" s="70"/>
-      <c r="I25" s="70"/>
+      <c r="I25" s="70">
+        <v>1</v>
+      </c>
       <c r="J25" s="71"/>
       <c r="K25" s="72"/>
       <c r="L25" s="55"/>
-      <c r="M25" s="73"/>
+      <c r="M25" s="73">
+        <v>1</v>
+      </c>
       <c r="N25" s="74"/>
-      <c r="O25" s="70"/>
+      <c r="O25" s="70">
+        <v>1</v>
+      </c>
       <c r="P25" s="71"/>
-      <c r="Q25" s="71"/>
+      <c r="Q25" s="71">
+        <v>5</v>
+      </c>
       <c r="R25" s="72"/>
       <c r="S25" s="55"/>
       <c r="T25" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U25" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1177</v>
       </c>
       <c r="V25" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>49.041666666666664</v>
       </c>
       <c r="AY25" s="14" t="e">
         <f>#REF!-AY24</f>
@@ -15758,7 +15845,9 @@
       <c r="B26" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="C26" s="70"/>
+      <c r="C26" s="70">
+        <v>1</v>
+      </c>
       <c r="D26" s="70"/>
       <c r="E26" s="70"/>
       <c r="F26" s="70"/>
@@ -15770,7 +15859,9 @@
       <c r="L26" s="55"/>
       <c r="M26" s="73"/>
       <c r="N26" s="74"/>
-      <c r="O26" s="70"/>
+      <c r="O26" s="70">
+        <v>1</v>
+      </c>
       <c r="P26" s="71"/>
       <c r="Q26" s="71"/>
       <c r="R26" s="72"/>
@@ -15781,11 +15872,11 @@
       </c>
       <c r="U26" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V26" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W26" s="9"/>
       <c r="X26" s="9"/>
@@ -15805,7 +15896,9 @@
       <c r="B27" s="26" t="s">
         <v>69</v>
       </c>
-      <c r="C27" s="70"/>
+      <c r="C27" s="70">
+        <v>3</v>
+      </c>
       <c r="D27" s="70"/>
       <c r="E27" s="70"/>
       <c r="F27" s="70"/>
@@ -15828,11 +15921,11 @@
       </c>
       <c r="U27" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="V27" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W27" s="9"/>
       <c r="X27" s="9"/>
@@ -15899,34 +15992,42 @@
       <c r="B29" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="C29" s="70"/>
+      <c r="C29" s="70">
+        <v>23</v>
+      </c>
       <c r="D29" s="70"/>
       <c r="E29" s="70"/>
       <c r="F29" s="70"/>
       <c r="G29" s="70"/>
       <c r="H29" s="70"/>
-      <c r="I29" s="70"/>
+      <c r="I29" s="70">
+        <v>5</v>
+      </c>
       <c r="J29" s="71"/>
       <c r="K29" s="72"/>
       <c r="L29" s="55"/>
       <c r="M29" s="73"/>
       <c r="N29" s="74"/>
-      <c r="O29" s="70"/>
+      <c r="O29" s="70">
+        <v>1</v>
+      </c>
       <c r="P29" s="71"/>
-      <c r="Q29" s="71"/>
+      <c r="Q29" s="71">
+        <v>2</v>
+      </c>
       <c r="R29" s="72"/>
       <c r="S29" s="55"/>
       <c r="T29" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U29" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>629</v>
       </c>
       <c r="V29" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>26.208333333333332</v>
       </c>
     </row>
     <row r="30" spans="1:54" x14ac:dyDescent="0.25">
@@ -15937,7 +16038,9 @@
       <c r="B30" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="C30" s="70"/>
+      <c r="C30" s="70">
+        <v>9</v>
+      </c>
       <c r="D30" s="70"/>
       <c r="E30" s="70"/>
       <c r="F30" s="70"/>
@@ -15949,9 +16052,13 @@
       <c r="L30" s="55"/>
       <c r="M30" s="73"/>
       <c r="N30" s="74"/>
-      <c r="O30" s="70"/>
+      <c r="O30" s="70">
+        <v>1</v>
+      </c>
       <c r="P30" s="71"/>
-      <c r="Q30" s="71"/>
+      <c r="Q30" s="71">
+        <v>2</v>
+      </c>
       <c r="R30" s="72"/>
       <c r="S30" s="55"/>
       <c r="T30" s="58">
@@ -15960,11 +16067,11 @@
       </c>
       <c r="U30" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>288</v>
       </c>
       <c r="V30" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="31" spans="1:54" x14ac:dyDescent="0.25">
@@ -16051,7 +16158,9 @@
       <c r="B33" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="C33" s="70"/>
+      <c r="C33" s="70">
+        <v>1</v>
+      </c>
       <c r="D33" s="70"/>
       <c r="E33" s="70"/>
       <c r="F33" s="70"/>
@@ -16061,7 +16170,9 @@
       <c r="J33" s="71"/>
       <c r="K33" s="72"/>
       <c r="L33" s="55"/>
-      <c r="M33" s="73"/>
+      <c r="M33" s="73">
+        <v>1</v>
+      </c>
       <c r="N33" s="74"/>
       <c r="O33" s="70"/>
       <c r="P33" s="71"/>
@@ -16074,11 +16185,11 @@
       </c>
       <c r="U33" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V33" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:23" x14ac:dyDescent="0.25">
@@ -16089,34 +16200,45 @@
       <c r="B34" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="C34" s="70"/>
+      <c r="C34" s="70">
+        <f>42+144</f>
+        <v>186</v>
+      </c>
       <c r="D34" s="70"/>
       <c r="E34" s="70"/>
       <c r="F34" s="70"/>
       <c r="G34" s="70"/>
       <c r="H34" s="70"/>
-      <c r="I34" s="70"/>
+      <c r="I34" s="70">
+        <v>1</v>
+      </c>
       <c r="J34" s="71"/>
-      <c r="K34" s="72"/>
+      <c r="K34" s="72">
+        <v>1</v>
+      </c>
       <c r="L34" s="55"/>
       <c r="M34" s="73"/>
       <c r="N34" s="74"/>
-      <c r="O34" s="70"/>
+      <c r="O34" s="70">
+        <v>2</v>
+      </c>
       <c r="P34" s="71"/>
-      <c r="Q34" s="71"/>
+      <c r="Q34" s="71">
+        <v>1</v>
+      </c>
       <c r="R34" s="72"/>
       <c r="S34" s="55"/>
       <c r="T34" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U34" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4538</v>
       </c>
       <c r="V34" s="75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>189.08333333333334</v>
       </c>
     </row>
     <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -16203,34 +16325,52 @@
       <c r="B37" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="C37" s="59"/>
+      <c r="C37" s="59">
+        <f>22+3024</f>
+        <v>3046</v>
+      </c>
       <c r="D37" s="59"/>
       <c r="E37" s="59"/>
       <c r="F37" s="59"/>
       <c r="G37" s="59"/>
-      <c r="H37" s="59"/>
-      <c r="I37" s="59"/>
-      <c r="J37" s="60"/>
-      <c r="K37" s="61"/>
+      <c r="H37" s="59">
+        <v>4</v>
+      </c>
+      <c r="I37" s="59">
+        <v>2</v>
+      </c>
+      <c r="J37" s="60">
+        <v>5</v>
+      </c>
+      <c r="K37" s="61">
+        <f>6+2</f>
+        <v>8</v>
+      </c>
       <c r="L37" s="62"/>
-      <c r="M37" s="63"/>
+      <c r="M37" s="63">
+        <v>6</v>
+      </c>
       <c r="N37" s="64"/>
-      <c r="O37" s="65"/>
+      <c r="O37" s="65">
+        <v>10</v>
+      </c>
       <c r="P37" s="66"/>
-      <c r="Q37" s="66"/>
+      <c r="Q37" s="66">
+        <v>41</v>
+      </c>
       <c r="R37" s="67"/>
       <c r="S37" s="62"/>
       <c r="T37" s="77">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="U37" s="77">
         <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
-        <v>0</v>
+        <v>18637</v>
       </c>
       <c r="V37" s="77">
         <f>U37/6</f>
-        <v>0</v>
+        <v>3106.1666666666665</v>
       </c>
       <c r="W37" s="50"/>
     </row>
@@ -16254,7 +16394,9 @@
       <c r="L38" s="55"/>
       <c r="M38" s="73"/>
       <c r="N38" s="74"/>
-      <c r="O38" s="70"/>
+      <c r="O38" s="70">
+        <v>1</v>
+      </c>
       <c r="P38" s="71"/>
       <c r="Q38" s="71"/>
       <c r="R38" s="72"/>
@@ -16265,11 +16407,11 @@
       </c>
       <c r="U38" s="75">
         <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V38" s="75">
         <f>U38/24</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:23" x14ac:dyDescent="0.25">
@@ -16318,7 +16460,10 @@
       <c r="B40" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="C40" s="59"/>
+      <c r="C40" s="59">
+        <f>252+58</f>
+        <v>310</v>
+      </c>
       <c r="D40" s="59"/>
       <c r="E40" s="59"/>
       <c r="F40" s="59"/>
@@ -16326,26 +16471,30 @@
       <c r="H40" s="59"/>
       <c r="I40" s="59"/>
       <c r="J40" s="60"/>
-      <c r="K40" s="61"/>
+      <c r="K40" s="61">
+        <v>20</v>
+      </c>
       <c r="L40" s="62"/>
       <c r="M40" s="63"/>
       <c r="N40" s="64"/>
-      <c r="O40" s="65"/>
+      <c r="O40" s="65">
+        <v>2</v>
+      </c>
       <c r="P40" s="66"/>
       <c r="Q40" s="66"/>
       <c r="R40" s="67"/>
       <c r="S40" s="62"/>
       <c r="T40" s="77">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="U40" s="77">
         <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
-        <v>0</v>
+        <v>7508</v>
       </c>
       <c r="V40" s="77">
         <f>U40/24</f>
-        <v>0</v>
+        <v>312.83333333333331</v>
       </c>
     </row>
     <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -16356,7 +16505,10 @@
       <c r="B41" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="C41" s="82"/>
+      <c r="C41" s="82">
+        <f>384+59</f>
+        <v>443</v>
+      </c>
       <c r="D41" s="82"/>
       <c r="E41" s="82"/>
       <c r="F41" s="82"/>
@@ -16368,9 +16520,13 @@
       <c r="L41" s="85"/>
       <c r="M41" s="86"/>
       <c r="N41" s="87"/>
-      <c r="O41" s="82"/>
+      <c r="O41" s="82">
+        <v>8</v>
+      </c>
       <c r="P41" s="83"/>
-      <c r="Q41" s="83"/>
+      <c r="Q41" s="83">
+        <v>48</v>
+      </c>
       <c r="R41" s="84"/>
       <c r="S41" s="85"/>
       <c r="T41" s="88">
@@ -16379,11 +16535,11 @@
       </c>
       <c r="U41" s="88">
         <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
-        <v>0</v>
+        <v>5988</v>
       </c>
       <c r="V41" s="88">
         <f>U41/12</f>
-        <v>0</v>
+        <v>499</v>
       </c>
     </row>
     <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -16423,34 +16579,53 @@
       <c r="B43" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="C43" s="65"/>
+      <c r="C43" s="65">
+        <f>29+5076+19764+10260</f>
+        <v>35129</v>
+      </c>
       <c r="D43" s="65"/>
       <c r="E43" s="65"/>
       <c r="F43" s="65"/>
       <c r="G43" s="65"/>
-      <c r="H43" s="65"/>
-      <c r="I43" s="65"/>
-      <c r="J43" s="66"/>
-      <c r="K43" s="67"/>
+      <c r="H43" s="65">
+        <v>7</v>
+      </c>
+      <c r="I43" s="65">
+        <v>12</v>
+      </c>
+      <c r="J43" s="66">
+        <f>20*6</f>
+        <v>120</v>
+      </c>
+      <c r="K43" s="67">
+        <f>71*6+2</f>
+        <v>428</v>
+      </c>
       <c r="L43" s="62"/>
-      <c r="M43" s="63"/>
+      <c r="M43" s="63">
+        <v>59</v>
+      </c>
       <c r="N43" s="64"/>
-      <c r="O43" s="65"/>
+      <c r="O43" s="65">
+        <v>83</v>
+      </c>
       <c r="P43" s="66"/>
-      <c r="Q43" s="66"/>
+      <c r="Q43" s="66">
+        <v>649</v>
+      </c>
       <c r="R43" s="67"/>
       <c r="S43" s="62"/>
       <c r="T43" s="77">
         <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
-        <v>0</v>
+        <v>567</v>
       </c>
       <c r="U43" s="77">
         <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
-        <v>0</v>
+        <v>216087</v>
       </c>
       <c r="V43" s="77">
         <f>U43/6</f>
-        <v>0</v>
+        <v>36014.5</v>
       </c>
     </row>
     <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -16502,7 +16677,9 @@
       <c r="L45" s="55"/>
       <c r="M45" s="73"/>
       <c r="N45" s="74"/>
-      <c r="O45" s="70"/>
+      <c r="O45" s="70">
+        <v>1</v>
+      </c>
       <c r="P45" s="71"/>
       <c r="Q45" s="71"/>
       <c r="R45" s="72"/>
@@ -16513,11 +16690,11 @@
       </c>
       <c r="U45" s="75">
         <f>C45*24+M45*24+O45*24+Q45*24+T45</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V45" s="75">
         <f>U45/24</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:23" x14ac:dyDescent="0.25">
@@ -16566,34 +16743,47 @@
       <c r="B47" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="C47" s="65"/>
+      <c r="C47" s="65">
+        <f>99+648+324+88+540+103+324+432+106</f>
+        <v>2664</v>
+      </c>
       <c r="D47" s="65"/>
       <c r="E47" s="65"/>
       <c r="F47" s="65"/>
       <c r="G47" s="65"/>
-      <c r="H47" s="65"/>
+      <c r="H47" s="65">
+        <v>1</v>
+      </c>
       <c r="I47" s="65"/>
       <c r="J47" s="66"/>
-      <c r="K47" s="67"/>
+      <c r="K47" s="67">
+        <v>5</v>
+      </c>
       <c r="L47" s="62"/>
       <c r="M47" s="63"/>
       <c r="N47" s="64"/>
-      <c r="O47" s="65"/>
+      <c r="O47" s="65">
+        <v>16</v>
+      </c>
       <c r="P47" s="66"/>
-      <c r="Q47" s="66"/>
-      <c r="R47" s="67"/>
+      <c r="Q47" s="66">
+        <v>5</v>
+      </c>
+      <c r="R47" s="67">
+        <v>3</v>
+      </c>
       <c r="S47" s="62"/>
       <c r="T47" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="U47" s="77">
         <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
-        <v>0</v>
+        <v>16119</v>
       </c>
       <c r="V47" s="77">
         <f>U47/6</f>
-        <v>0</v>
+        <v>2686.5</v>
       </c>
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.25">
@@ -16609,7 +16799,9 @@
       <c r="E48" s="70"/>
       <c r="F48" s="70"/>
       <c r="G48" s="70"/>
-      <c r="H48" s="70"/>
+      <c r="H48" s="70">
+        <v>24</v>
+      </c>
       <c r="I48" s="70"/>
       <c r="J48" s="71"/>
       <c r="K48" s="72"/>
@@ -16623,15 +16815,15 @@
       <c r="S48" s="55"/>
       <c r="T48" s="75">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="U48" s="75">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V48" s="75">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.25">
@@ -16718,7 +16910,9 @@
       <c r="B51" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="C51" s="65"/>
+      <c r="C51" s="65">
+        <v>34</v>
+      </c>
       <c r="D51" s="65"/>
       <c r="E51" s="65"/>
       <c r="F51" s="65"/>
@@ -16741,11 +16935,11 @@
       </c>
       <c r="U51" s="77">
         <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="V51" s="77">
         <f>U51/6</f>
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.25">
@@ -16794,7 +16988,9 @@
       <c r="B53" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C53" s="70"/>
+      <c r="C53" s="70">
+        <v>7</v>
+      </c>
       <c r="D53" s="70"/>
       <c r="E53" s="70"/>
       <c r="F53" s="70"/>
@@ -16817,11 +17013,11 @@
       </c>
       <c r="U53" s="75">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="V53" s="75">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.25">
@@ -16947,7 +17143,7 @@
       </c>
       <c r="C58" s="2">
         <f>SUM(C7:C57)</f>
-        <v>0</v>
+        <v>45444</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" s="2"/>
@@ -16961,56 +17157,56 @@
       </c>
       <c r="H58" s="2">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1195</v>
       </c>
       <c r="I58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="J58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="K58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>470</v>
       </c>
       <c r="M58" s="5">
         <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="N58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="P58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>781</v>
       </c>
       <c r="R58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="S58" s="55"/>
       <c r="T58" s="4">
         <f>SUM(T7:T57)</f>
-        <v>0</v>
+        <v>1876</v>
       </c>
       <c r="U58" s="90">
         <f>SUM(U7:U57)</f>
-        <v>0</v>
+        <v>358804</v>
       </c>
       <c r="V58" s="4">
         <f>SUM(V7:V57)</f>
-        <v>0</v>
+        <v>46580.541666666664</v>
       </c>
     </row>
     <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>

--- a/GBDS AUGUST FILES 2026/INVENTORY COUNT SHEET - AUGUST 2026.xlsx
+++ b/GBDS AUGUST FILES 2026/INVENTORY COUNT SHEET - AUGUST 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS AUGUST FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C079CEF0-0243-4EFD-A26C-11C3141D692E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA2026D2-12F8-49FD-B39B-7DE611B9B015}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="3" activeTab="12" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="4" activeTab="13" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
   </bookViews>
   <sheets>
     <sheet name="SAMPLE" sheetId="32" r:id="rId1"/>
@@ -26,6 +26,7 @@
     <sheet name="08-14-2026" sheetId="78" r:id="rId11"/>
     <sheet name="08-15-2026" sheetId="79" r:id="rId12"/>
     <sheet name="08-17-2026" sheetId="80" r:id="rId13"/>
+    <sheet name="08-18-2026" sheetId="81" r:id="rId14"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'08-03-2026'!$A$1:$W$59</definedName>
@@ -40,6 +41,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="10">'08-14-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="11">'08-15-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="12">'08-17-2026'!$A$1:$W$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="13">'08-18-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">SAMPLE!$A$1:$W$85</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -58,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1092" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1176" uniqueCount="83">
   <si>
     <t>ROUTE 1</t>
   </si>
@@ -1294,7 +1296,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="119">
+  <cellXfs count="120">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1580,6 +1582,9 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="63" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2005,21 +2010,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="107" t="s">
+      <c r="I1" s="108" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="107"/>
-      <c r="K1" s="107"/>
-      <c r="L1" s="107"/>
-      <c r="M1" s="107"/>
-      <c r="N1" s="107"/>
-      <c r="O1" s="107"/>
-      <c r="P1" s="107"/>
-      <c r="Q1" s="107"/>
-      <c r="R1" s="107"/>
-      <c r="S1" s="107"/>
-      <c r="T1" s="107"/>
-      <c r="U1" s="107"/>
+      <c r="J1" s="108"/>
+      <c r="K1" s="108"/>
+      <c r="L1" s="108"/>
+      <c r="M1" s="108"/>
+      <c r="N1" s="108"/>
+      <c r="O1" s="108"/>
+      <c r="P1" s="108"/>
+      <c r="Q1" s="108"/>
+      <c r="R1" s="108"/>
+      <c r="S1" s="108"/>
+      <c r="T1" s="108"/>
+      <c r="U1" s="108"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -2031,17 +2036,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="108" t="s">
+      <c r="C4" s="109" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="108"/>
-      <c r="E4" s="108"/>
-      <c r="F4" s="108"/>
-      <c r="G4" s="108"/>
-      <c r="H4" s="108"/>
-      <c r="I4" s="108"/>
-      <c r="J4" s="109"/>
-      <c r="K4" s="110"/>
+      <c r="D4" s="109"/>
+      <c r="E4" s="109"/>
+      <c r="F4" s="109"/>
+      <c r="G4" s="109"/>
+      <c r="H4" s="109"/>
+      <c r="I4" s="109"/>
+      <c r="J4" s="110"/>
+      <c r="K4" s="111"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -2061,13 +2066,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="111" t="s">
+      <c r="T4" s="112" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="113" t="s">
+      <c r="U4" s="114" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="100" t="s">
+      <c r="V4" s="101" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -2107,10 +2112,10 @@
       <c r="I5" s="93" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="102" t="s">
+      <c r="J5" s="103" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="103"/>
+      <c r="K5" s="104"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -2118,9 +2123,9 @@
       <c r="Q5" s="89"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="112"/>
-      <c r="U5" s="114"/>
-      <c r="V5" s="101"/>
+      <c r="T5" s="113"/>
+      <c r="U5" s="115"/>
+      <c r="V5" s="102"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -4651,17 +4656,17 @@
       <c r="B62" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C62" s="104" t="s">
+      <c r="C62" s="105" t="s">
         <v>41</v>
       </c>
-      <c r="D62" s="105"/>
-      <c r="E62" s="105"/>
-      <c r="F62" s="105"/>
-      <c r="G62" s="105"/>
-      <c r="H62" s="105"/>
-      <c r="I62" s="105"/>
-      <c r="J62" s="105"/>
-      <c r="K62" s="106"/>
+      <c r="D62" s="106"/>
+      <c r="E62" s="106"/>
+      <c r="F62" s="106"/>
+      <c r="G62" s="106"/>
+      <c r="H62" s="106"/>
+      <c r="I62" s="106"/>
+      <c r="J62" s="106"/>
+      <c r="K62" s="107"/>
       <c r="U62" s="24" t="s">
         <v>51</v>
       </c>
@@ -4970,21 +4975,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="107" t="s">
+      <c r="I1" s="108" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="107"/>
-      <c r="K1" s="107"/>
-      <c r="L1" s="107"/>
-      <c r="M1" s="107"/>
-      <c r="N1" s="107"/>
-      <c r="O1" s="107"/>
-      <c r="P1" s="107"/>
-      <c r="Q1" s="107"/>
-      <c r="R1" s="107"/>
-      <c r="S1" s="107"/>
-      <c r="T1" s="107"/>
-      <c r="U1" s="107"/>
+      <c r="J1" s="108"/>
+      <c r="K1" s="108"/>
+      <c r="L1" s="108"/>
+      <c r="M1" s="108"/>
+      <c r="N1" s="108"/>
+      <c r="O1" s="108"/>
+      <c r="P1" s="108"/>
+      <c r="Q1" s="108"/>
+      <c r="R1" s="108"/>
+      <c r="S1" s="108"/>
+      <c r="T1" s="108"/>
+      <c r="U1" s="108"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -4996,17 +5001,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="108" t="s">
+      <c r="C4" s="109" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="108"/>
-      <c r="E4" s="108"/>
-      <c r="F4" s="108"/>
-      <c r="G4" s="108"/>
-      <c r="H4" s="108"/>
-      <c r="I4" s="108"/>
-      <c r="J4" s="109"/>
-      <c r="K4" s="110"/>
+      <c r="D4" s="109"/>
+      <c r="E4" s="109"/>
+      <c r="F4" s="109"/>
+      <c r="G4" s="109"/>
+      <c r="H4" s="109"/>
+      <c r="I4" s="109"/>
+      <c r="J4" s="110"/>
+      <c r="K4" s="111"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -5026,13 +5031,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="111" t="s">
+      <c r="T4" s="112" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="117" t="s">
+      <c r="U4" s="118" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="100" t="s">
+      <c r="V4" s="101" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -5072,10 +5077,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="115" t="s">
+      <c r="J5" s="116" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="116"/>
+      <c r="K5" s="117"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -5083,9 +5088,9 @@
       <c r="Q5" s="99"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="112"/>
-      <c r="U5" s="118"/>
-      <c r="V5" s="101"/>
+      <c r="T5" s="113"/>
+      <c r="U5" s="119"/>
+      <c r="V5" s="102"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -7796,17 +7801,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="104" t="s">
+      <c r="C60" s="105" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="105"/>
-      <c r="E60" s="105"/>
-      <c r="F60" s="105"/>
-      <c r="G60" s="105"/>
-      <c r="H60" s="105"/>
-      <c r="I60" s="105"/>
-      <c r="J60" s="105"/>
-      <c r="K60" s="106"/>
+      <c r="D60" s="106"/>
+      <c r="E60" s="106"/>
+      <c r="F60" s="106"/>
+      <c r="G60" s="106"/>
+      <c r="H60" s="106"/>
+      <c r="I60" s="106"/>
+      <c r="J60" s="106"/>
+      <c r="K60" s="107"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -8115,21 +8120,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="107" t="s">
+      <c r="I1" s="108" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="107"/>
-      <c r="K1" s="107"/>
-      <c r="L1" s="107"/>
-      <c r="M1" s="107"/>
-      <c r="N1" s="107"/>
-      <c r="O1" s="107"/>
-      <c r="P1" s="107"/>
-      <c r="Q1" s="107"/>
-      <c r="R1" s="107"/>
-      <c r="S1" s="107"/>
-      <c r="T1" s="107"/>
-      <c r="U1" s="107"/>
+      <c r="J1" s="108"/>
+      <c r="K1" s="108"/>
+      <c r="L1" s="108"/>
+      <c r="M1" s="108"/>
+      <c r="N1" s="108"/>
+      <c r="O1" s="108"/>
+      <c r="P1" s="108"/>
+      <c r="Q1" s="108"/>
+      <c r="R1" s="108"/>
+      <c r="S1" s="108"/>
+      <c r="T1" s="108"/>
+      <c r="U1" s="108"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -8141,17 +8146,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="108" t="s">
+      <c r="C4" s="109" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="108"/>
-      <c r="E4" s="108"/>
-      <c r="F4" s="108"/>
-      <c r="G4" s="108"/>
-      <c r="H4" s="108"/>
-      <c r="I4" s="108"/>
-      <c r="J4" s="109"/>
-      <c r="K4" s="110"/>
+      <c r="D4" s="109"/>
+      <c r="E4" s="109"/>
+      <c r="F4" s="109"/>
+      <c r="G4" s="109"/>
+      <c r="H4" s="109"/>
+      <c r="I4" s="109"/>
+      <c r="J4" s="110"/>
+      <c r="K4" s="111"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -8171,13 +8176,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="111" t="s">
+      <c r="T4" s="112" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="117" t="s">
+      <c r="U4" s="118" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="100" t="s">
+      <c r="V4" s="101" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -8217,10 +8222,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="115" t="s">
+      <c r="J5" s="116" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="116"/>
+      <c r="K5" s="117"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -8228,9 +8233,9 @@
       <c r="Q5" s="99"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="112"/>
-      <c r="U5" s="118"/>
-      <c r="V5" s="101"/>
+      <c r="T5" s="113"/>
+      <c r="U5" s="119"/>
+      <c r="V5" s="102"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -10943,17 +10948,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="104" t="s">
+      <c r="C60" s="105" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="105"/>
-      <c r="E60" s="105"/>
-      <c r="F60" s="105"/>
-      <c r="G60" s="105"/>
-      <c r="H60" s="105"/>
-      <c r="I60" s="105"/>
-      <c r="J60" s="105"/>
-      <c r="K60" s="106"/>
+      <c r="D60" s="106"/>
+      <c r="E60" s="106"/>
+      <c r="F60" s="106"/>
+      <c r="G60" s="106"/>
+      <c r="H60" s="106"/>
+      <c r="I60" s="106"/>
+      <c r="J60" s="106"/>
+      <c r="K60" s="107"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -11262,21 +11267,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="107" t="s">
+      <c r="I1" s="108" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="107"/>
-      <c r="K1" s="107"/>
-      <c r="L1" s="107"/>
-      <c r="M1" s="107"/>
-      <c r="N1" s="107"/>
-      <c r="O1" s="107"/>
-      <c r="P1" s="107"/>
-      <c r="Q1" s="107"/>
-      <c r="R1" s="107"/>
-      <c r="S1" s="107"/>
-      <c r="T1" s="107"/>
-      <c r="U1" s="107"/>
+      <c r="J1" s="108"/>
+      <c r="K1" s="108"/>
+      <c r="L1" s="108"/>
+      <c r="M1" s="108"/>
+      <c r="N1" s="108"/>
+      <c r="O1" s="108"/>
+      <c r="P1" s="108"/>
+      <c r="Q1" s="108"/>
+      <c r="R1" s="108"/>
+      <c r="S1" s="108"/>
+      <c r="T1" s="108"/>
+      <c r="U1" s="108"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -11288,17 +11293,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="108" t="s">
+      <c r="C4" s="109" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="108"/>
-      <c r="E4" s="108"/>
-      <c r="F4" s="108"/>
-      <c r="G4" s="108"/>
-      <c r="H4" s="108"/>
-      <c r="I4" s="108"/>
-      <c r="J4" s="109"/>
-      <c r="K4" s="110"/>
+      <c r="D4" s="109"/>
+      <c r="E4" s="109"/>
+      <c r="F4" s="109"/>
+      <c r="G4" s="109"/>
+      <c r="H4" s="109"/>
+      <c r="I4" s="109"/>
+      <c r="J4" s="110"/>
+      <c r="K4" s="111"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -11318,13 +11323,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="111" t="s">
+      <c r="T4" s="112" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="117" t="s">
+      <c r="U4" s="118" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="100" t="s">
+      <c r="V4" s="101" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -11364,10 +11369,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="115" t="s">
+      <c r="J5" s="116" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="116"/>
+      <c r="K5" s="117"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -11375,9 +11380,9 @@
       <c r="Q5" s="99"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="112"/>
-      <c r="U5" s="118"/>
-      <c r="V5" s="101"/>
+      <c r="T5" s="113"/>
+      <c r="U5" s="119"/>
+      <c r="V5" s="102"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -14079,17 +14084,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="104" t="s">
+      <c r="C60" s="105" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="105"/>
-      <c r="E60" s="105"/>
-      <c r="F60" s="105"/>
-      <c r="G60" s="105"/>
-      <c r="H60" s="105"/>
-      <c r="I60" s="105"/>
-      <c r="J60" s="105"/>
-      <c r="K60" s="106"/>
+      <c r="D60" s="106"/>
+      <c r="E60" s="106"/>
+      <c r="F60" s="106"/>
+      <c r="G60" s="106"/>
+      <c r="H60" s="106"/>
+      <c r="I60" s="106"/>
+      <c r="J60" s="106"/>
+      <c r="K60" s="107"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -14398,21 +14403,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="107" t="s">
+      <c r="I1" s="108" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="107"/>
-      <c r="K1" s="107"/>
-      <c r="L1" s="107"/>
-      <c r="M1" s="107"/>
-      <c r="N1" s="107"/>
-      <c r="O1" s="107"/>
-      <c r="P1" s="107"/>
-      <c r="Q1" s="107"/>
-      <c r="R1" s="107"/>
-      <c r="S1" s="107"/>
-      <c r="T1" s="107"/>
-      <c r="U1" s="107"/>
+      <c r="J1" s="108"/>
+      <c r="K1" s="108"/>
+      <c r="L1" s="108"/>
+      <c r="M1" s="108"/>
+      <c r="N1" s="108"/>
+      <c r="O1" s="108"/>
+      <c r="P1" s="108"/>
+      <c r="Q1" s="108"/>
+      <c r="R1" s="108"/>
+      <c r="S1" s="108"/>
+      <c r="T1" s="108"/>
+      <c r="U1" s="108"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -14424,17 +14429,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="108" t="s">
+      <c r="C4" s="109" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="108"/>
-      <c r="E4" s="108"/>
-      <c r="F4" s="108"/>
-      <c r="G4" s="108"/>
-      <c r="H4" s="108"/>
-      <c r="I4" s="108"/>
-      <c r="J4" s="109"/>
-      <c r="K4" s="110"/>
+      <c r="D4" s="109"/>
+      <c r="E4" s="109"/>
+      <c r="F4" s="109"/>
+      <c r="G4" s="109"/>
+      <c r="H4" s="109"/>
+      <c r="I4" s="109"/>
+      <c r="J4" s="110"/>
+      <c r="K4" s="111"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -14454,13 +14459,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="111" t="s">
+      <c r="T4" s="112" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="117" t="s">
+      <c r="U4" s="118" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="100" t="s">
+      <c r="V4" s="101" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -14500,10 +14505,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="115" t="s">
+      <c r="J5" s="116" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="116"/>
+      <c r="K5" s="117"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -14511,9 +14516,9 @@
       <c r="Q5" s="99"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="112"/>
-      <c r="U5" s="118"/>
-      <c r="V5" s="101"/>
+      <c r="T5" s="113"/>
+      <c r="U5" s="119"/>
+      <c r="V5" s="102"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -17214,17 +17219,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="104" t="s">
+      <c r="C60" s="105" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="105"/>
-      <c r="E60" s="105"/>
-      <c r="F60" s="105"/>
-      <c r="G60" s="105"/>
-      <c r="H60" s="105"/>
-      <c r="I60" s="105"/>
-      <c r="J60" s="105"/>
-      <c r="K60" s="106"/>
+      <c r="D60" s="106"/>
+      <c r="E60" s="106"/>
+      <c r="F60" s="106"/>
+      <c r="G60" s="106"/>
+      <c r="H60" s="106"/>
+      <c r="I60" s="106"/>
+      <c r="J60" s="106"/>
+      <c r="K60" s="107"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -17483,6 +17488,3135 @@
     <mergeCell ref="C4:K4"/>
     <mergeCell ref="T4:T5"/>
     <mergeCell ref="U4:U5"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
+  <pageSetup paperSize="14" scale="70" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="24" max="80" man="1"/>
+  </colBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10404419-184F-4CE3-BF04-EDA1B752AE66}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BB81"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="28" customWidth="1"/>
+    <col min="3" max="6" width="10" style="9" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" style="9" customWidth="1"/>
+    <col min="8" max="8" width="7.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.85546875" style="9" customWidth="1"/>
+    <col min="11" max="11" width="7.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.42578125" style="9" customWidth="1"/>
+    <col min="13" max="13" width="10" style="9" customWidth="1"/>
+    <col min="14" max="14" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" style="9" customWidth="1"/>
+    <col min="16" max="16" width="5.5703125" style="9" customWidth="1"/>
+    <col min="17" max="17" width="10" style="9" customWidth="1"/>
+    <col min="18" max="18" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="1.42578125" style="9" customWidth="1"/>
+    <col min="20" max="20" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="9" customWidth="1"/>
+    <col min="22" max="22" width="19.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="23" max="49" width="7.28515625" style="9" customWidth="1"/>
+    <col min="50" max="50" width="1.5703125" style="9" customWidth="1"/>
+    <col min="51" max="51" width="9.42578125" style="9" customWidth="1"/>
+    <col min="52" max="52" width="1.28515625" style="9" customWidth="1"/>
+    <col min="53" max="53" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="10.28515625" style="9" bestFit="1" customWidth="1"/>
+    <col min="55" max="16384" width="9.140625" style="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="108" t="s">
+        <v>43</v>
+      </c>
+      <c r="J1" s="108"/>
+      <c r="K1" s="108"/>
+      <c r="L1" s="108"/>
+      <c r="M1" s="108"/>
+      <c r="N1" s="108"/>
+      <c r="O1" s="108"/>
+      <c r="P1" s="108"/>
+      <c r="Q1" s="108"/>
+      <c r="R1" s="108"/>
+      <c r="S1" s="108"/>
+      <c r="T1" s="108"/>
+      <c r="U1" s="108"/>
+    </row>
+    <row r="2" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="B2" s="28" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B4" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="109" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="109"/>
+      <c r="E4" s="109"/>
+      <c r="F4" s="109"/>
+      <c r="G4" s="109"/>
+      <c r="H4" s="109"/>
+      <c r="I4" s="109"/>
+      <c r="J4" s="110"/>
+      <c r="K4" s="111"/>
+      <c r="M4" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="N4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="O4" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="P4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q4" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="R4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="S4" s="9"/>
+      <c r="T4" s="112" t="s">
+        <v>68</v>
+      </c>
+      <c r="U4" s="118" t="s">
+        <v>67</v>
+      </c>
+      <c r="V4" s="101" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF4" s="11"/>
+      <c r="AG4" s="11"/>
+      <c r="AH4" s="11"/>
+      <c r="AI4" s="11"/>
+      <c r="AJ4" s="11"/>
+      <c r="AK4" s="11"/>
+      <c r="AL4" s="11"/>
+      <c r="AM4" s="11"/>
+      <c r="AN4" s="11"/>
+      <c r="AO4" s="11"/>
+      <c r="AP4" s="11"/>
+      <c r="AQ4" s="11"/>
+      <c r="AR4" s="11"/>
+      <c r="AS4" s="11"/>
+      <c r="AT4" s="11"/>
+      <c r="AU4" s="11"/>
+      <c r="AV4" s="11"/>
+      <c r="AW4" s="11"/>
+      <c r="AX4" s="11"/>
+      <c r="AY4" s="11"/>
+      <c r="AZ4" s="11"/>
+      <c r="BA4" s="11"/>
+      <c r="BB4" s="11"/>
+    </row>
+    <row r="5" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="37"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40" t="s">
+        <v>64</v>
+      </c>
+      <c r="I5" s="40" t="s">
+        <v>60</v>
+      </c>
+      <c r="J5" s="116" t="s">
+        <v>65</v>
+      </c>
+      <c r="K5" s="117"/>
+      <c r="M5" s="37"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="40"/>
+      <c r="P5" s="100"/>
+      <c r="Q5" s="100"/>
+      <c r="R5" s="38"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="113"/>
+      <c r="U5" s="119"/>
+      <c r="V5" s="102"/>
+      <c r="AF5" s="11"/>
+      <c r="AG5" s="11"/>
+      <c r="AH5" s="11"/>
+      <c r="AI5" s="11"/>
+      <c r="AJ5" s="11"/>
+      <c r="AK5" s="11"/>
+      <c r="AL5" s="11"/>
+      <c r="AM5" s="11"/>
+      <c r="AN5" s="11"/>
+      <c r="AO5" s="11"/>
+      <c r="AP5" s="11"/>
+      <c r="AQ5" s="11"/>
+      <c r="AR5" s="11"/>
+      <c r="AS5" s="11"/>
+      <c r="AT5" s="11"/>
+      <c r="AU5" s="11"/>
+      <c r="AV5" s="11"/>
+      <c r="AW5" s="11"/>
+      <c r="AX5" s="11"/>
+      <c r="AY5" s="11"/>
+      <c r="AZ5" s="11"/>
+      <c r="BA5" s="11"/>
+      <c r="BB5" s="11"/>
+    </row>
+    <row r="6" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="37"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="100"/>
+      <c r="K6" s="38"/>
+      <c r="M6" s="37"/>
+      <c r="N6" s="49"/>
+      <c r="O6" s="40"/>
+      <c r="P6" s="100"/>
+      <c r="Q6" s="100"/>
+      <c r="R6" s="38"/>
+      <c r="S6" s="9"/>
+      <c r="T6" s="39"/>
+      <c r="U6" s="39"/>
+      <c r="V6" s="39"/>
+      <c r="AF6" s="11"/>
+      <c r="AG6" s="11"/>
+      <c r="AH6" s="11"/>
+      <c r="AI6" s="11"/>
+      <c r="AJ6" s="11"/>
+      <c r="AK6" s="11"/>
+      <c r="AL6" s="11"/>
+      <c r="AM6" s="11"/>
+      <c r="AN6" s="11"/>
+      <c r="AO6" s="11"/>
+      <c r="AP6" s="11"/>
+      <c r="AQ6" s="11"/>
+      <c r="AR6" s="11"/>
+      <c r="AS6" s="11"/>
+      <c r="AT6" s="11"/>
+      <c r="AU6" s="11"/>
+      <c r="AV6" s="11"/>
+      <c r="AW6" s="11"/>
+      <c r="AX6" s="11"/>
+      <c r="AY6" s="11"/>
+      <c r="AZ6" s="11"/>
+      <c r="BA6" s="11"/>
+      <c r="BB6" s="11"/>
+    </row>
+    <row r="7" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A7" s="27">
+        <v>1</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="52">
+        <v>32</v>
+      </c>
+      <c r="D7" s="52"/>
+      <c r="E7" s="52"/>
+      <c r="F7" s="52"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="52"/>
+      <c r="I7" s="52">
+        <v>3</v>
+      </c>
+      <c r="J7" s="53"/>
+      <c r="K7" s="54">
+        <v>6</v>
+      </c>
+      <c r="L7" s="55"/>
+      <c r="M7" s="56"/>
+      <c r="N7" s="57"/>
+      <c r="O7" s="52">
+        <v>1</v>
+      </c>
+      <c r="P7" s="53"/>
+      <c r="Q7" s="53"/>
+      <c r="R7" s="54"/>
+      <c r="S7" s="55"/>
+      <c r="T7" s="58">
+        <f>H7+I7+J7+K7+N7+P7+R7</f>
+        <v>9</v>
+      </c>
+      <c r="U7" s="58">
+        <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
+        <v>801</v>
+      </c>
+      <c r="V7" s="58">
+        <f>U7/24</f>
+        <v>33.375</v>
+      </c>
+      <c r="W7" s="50"/>
+      <c r="AF7" s="12"/>
+      <c r="AG7" s="12"/>
+      <c r="AH7" s="12"/>
+      <c r="AI7" s="12"/>
+      <c r="AJ7" s="12"/>
+      <c r="AK7" s="12"/>
+      <c r="AL7" s="12"/>
+      <c r="AM7" s="12"/>
+      <c r="AN7" s="12"/>
+      <c r="AO7" s="12"/>
+      <c r="AP7" s="12"/>
+      <c r="AQ7" s="12"/>
+      <c r="AR7" s="12"/>
+      <c r="AS7" s="12"/>
+      <c r="AT7" s="12"/>
+      <c r="AU7" s="12"/>
+      <c r="AV7" s="12"/>
+      <c r="AW7" s="12"/>
+      <c r="AX7" s="12"/>
+      <c r="AY7" s="12"/>
+      <c r="AZ7" s="12"/>
+      <c r="BA7" s="12"/>
+      <c r="BB7" s="12"/>
+    </row>
+    <row r="8" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="27">
+        <f>A7+1</f>
+        <v>2</v>
+      </c>
+      <c r="B8" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="59">
+        <f>40+37</f>
+        <v>77</v>
+      </c>
+      <c r="D8" s="59"/>
+      <c r="E8" s="59"/>
+      <c r="F8" s="59"/>
+      <c r="G8" s="59"/>
+      <c r="H8" s="59"/>
+      <c r="I8" s="59"/>
+      <c r="J8" s="60"/>
+      <c r="K8" s="61"/>
+      <c r="L8" s="62"/>
+      <c r="M8" s="63"/>
+      <c r="N8" s="64"/>
+      <c r="O8" s="65">
+        <v>1</v>
+      </c>
+      <c r="P8" s="66">
+        <v>12</v>
+      </c>
+      <c r="Q8" s="66">
+        <v>2</v>
+      </c>
+      <c r="R8" s="67"/>
+      <c r="S8" s="62"/>
+      <c r="T8" s="68">
+        <f t="shared" ref="T8:T41" si="0">H8+I8+J8+K8+N8+P8+R8</f>
+        <v>12</v>
+      </c>
+      <c r="U8" s="69">
+        <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
+        <v>1932</v>
+      </c>
+      <c r="V8" s="69">
+        <f>U8/24</f>
+        <v>80.5</v>
+      </c>
+      <c r="W8" s="50"/>
+      <c r="AF8" s="12"/>
+      <c r="AG8" s="12"/>
+      <c r="AH8" s="12"/>
+      <c r="AI8" s="12"/>
+      <c r="AJ8" s="12"/>
+      <c r="AK8" s="12"/>
+      <c r="AL8" s="12"/>
+      <c r="AM8" s="12"/>
+      <c r="AN8" s="12"/>
+      <c r="AO8" s="12"/>
+      <c r="AP8" s="12"/>
+      <c r="AQ8" s="12"/>
+      <c r="AR8" s="12"/>
+      <c r="AS8" s="12"/>
+      <c r="AT8" s="12"/>
+      <c r="AU8" s="12"/>
+      <c r="AV8" s="12"/>
+      <c r="AW8" s="12"/>
+      <c r="AX8" s="12"/>
+      <c r="AY8" s="12"/>
+      <c r="AZ8" s="12"/>
+      <c r="BA8" s="12"/>
+      <c r="BB8" s="12"/>
+    </row>
+    <row r="9" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A9" s="27">
+        <f t="shared" ref="A9:A57" si="1">A8+1</f>
+        <v>3</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="70">
+        <f>57+30</f>
+        <v>87</v>
+      </c>
+      <c r="D9" s="70"/>
+      <c r="E9" s="70"/>
+      <c r="F9" s="70"/>
+      <c r="G9" s="70"/>
+      <c r="H9" s="70"/>
+      <c r="I9" s="70"/>
+      <c r="J9" s="71"/>
+      <c r="K9" s="72"/>
+      <c r="L9" s="55"/>
+      <c r="M9" s="73"/>
+      <c r="N9" s="74"/>
+      <c r="O9" s="70">
+        <v>1</v>
+      </c>
+      <c r="P9" s="71"/>
+      <c r="Q9" s="71"/>
+      <c r="R9" s="72"/>
+      <c r="S9" s="55"/>
+      <c r="T9" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U9" s="76">
+        <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
+        <v>2112</v>
+      </c>
+      <c r="V9" s="76">
+        <f t="shared" ref="V9:V11" si="3">U9/24</f>
+        <v>88</v>
+      </c>
+      <c r="W9" s="50"/>
+      <c r="AF9" s="12"/>
+      <c r="AG9" s="12"/>
+      <c r="AH9" s="12"/>
+      <c r="AI9" s="12"/>
+      <c r="AJ9" s="12"/>
+      <c r="AK9" s="12"/>
+      <c r="AL9" s="12"/>
+      <c r="AM9" s="12"/>
+      <c r="AN9" s="12"/>
+      <c r="AO9" s="12"/>
+      <c r="AP9" s="12"/>
+      <c r="AQ9" s="12"/>
+      <c r="AR9" s="12"/>
+      <c r="AS9" s="12"/>
+      <c r="AT9" s="12"/>
+      <c r="AU9" s="12"/>
+      <c r="AV9" s="12"/>
+      <c r="AW9" s="12"/>
+      <c r="AX9" s="12"/>
+      <c r="AY9" s="12"/>
+      <c r="AZ9" s="12"/>
+      <c r="BA9" s="12"/>
+      <c r="BB9" s="12"/>
+    </row>
+    <row r="10" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A10" s="27">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="70">
+        <f>26+10</f>
+        <v>36</v>
+      </c>
+      <c r="D10" s="70"/>
+      <c r="E10" s="70"/>
+      <c r="F10" s="70"/>
+      <c r="G10" s="70"/>
+      <c r="H10" s="70"/>
+      <c r="I10" s="70"/>
+      <c r="J10" s="71"/>
+      <c r="K10" s="72"/>
+      <c r="L10" s="55"/>
+      <c r="M10" s="73"/>
+      <c r="N10" s="74"/>
+      <c r="O10" s="70">
+        <v>1</v>
+      </c>
+      <c r="P10" s="71"/>
+      <c r="Q10" s="71">
+        <v>1</v>
+      </c>
+      <c r="R10" s="72"/>
+      <c r="S10" s="55"/>
+      <c r="T10" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U10" s="58">
+        <f t="shared" si="2"/>
+        <v>912</v>
+      </c>
+      <c r="V10" s="58">
+        <f t="shared" si="3"/>
+        <v>38</v>
+      </c>
+      <c r="W10" s="50"/>
+      <c r="AF10" s="12"/>
+      <c r="AG10" s="12"/>
+      <c r="AH10" s="12"/>
+      <c r="AI10" s="12"/>
+      <c r="AJ10" s="12"/>
+      <c r="AK10" s="12"/>
+      <c r="AL10" s="12"/>
+      <c r="AM10" s="12"/>
+      <c r="AN10" s="12"/>
+      <c r="AO10" s="12"/>
+      <c r="AP10" s="12"/>
+      <c r="AQ10" s="12"/>
+      <c r="AR10" s="12"/>
+      <c r="AS10" s="12"/>
+      <c r="AT10" s="12"/>
+      <c r="AU10" s="12"/>
+      <c r="AV10" s="12"/>
+      <c r="AW10" s="12"/>
+      <c r="AX10" s="12"/>
+      <c r="AY10" s="12"/>
+      <c r="AZ10" s="12"/>
+      <c r="BA10" s="12"/>
+      <c r="BB10" s="12"/>
+    </row>
+    <row r="11" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A11" s="27">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="70">
+        <v>9</v>
+      </c>
+      <c r="D11" s="70"/>
+      <c r="E11" s="70"/>
+      <c r="F11" s="70"/>
+      <c r="G11" s="70"/>
+      <c r="H11" s="70"/>
+      <c r="I11" s="70"/>
+      <c r="J11" s="71"/>
+      <c r="K11" s="72">
+        <v>2</v>
+      </c>
+      <c r="L11" s="55"/>
+      <c r="M11" s="73"/>
+      <c r="N11" s="74"/>
+      <c r="O11" s="70"/>
+      <c r="P11" s="71"/>
+      <c r="Q11" s="71"/>
+      <c r="R11" s="72"/>
+      <c r="S11" s="55"/>
+      <c r="T11" s="58">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="U11" s="58">
+        <f t="shared" si="2"/>
+        <v>218</v>
+      </c>
+      <c r="V11" s="58">
+        <f t="shared" si="3"/>
+        <v>9.0833333333333339</v>
+      </c>
+      <c r="AF11" s="12"/>
+      <c r="AG11" s="12"/>
+      <c r="AH11" s="12"/>
+      <c r="AI11" s="12"/>
+      <c r="AJ11" s="12"/>
+      <c r="AK11" s="12"/>
+      <c r="AL11" s="12"/>
+      <c r="AM11" s="12"/>
+      <c r="AN11" s="12"/>
+      <c r="AO11" s="12"/>
+      <c r="AP11" s="12"/>
+      <c r="AQ11" s="12"/>
+      <c r="AR11" s="12"/>
+      <c r="AS11" s="12"/>
+      <c r="AT11" s="12"/>
+      <c r="AU11" s="12"/>
+      <c r="AV11" s="12"/>
+      <c r="AW11" s="12"/>
+      <c r="AX11" s="12"/>
+      <c r="AY11" s="12"/>
+      <c r="AZ11" s="12"/>
+      <c r="BA11" s="12"/>
+      <c r="BB11" s="12"/>
+    </row>
+    <row r="12" spans="1:54" s="13" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="27">
+        <v>7</v>
+      </c>
+      <c r="B12" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="59">
+        <f>1224+53+792+7+1080+29</f>
+        <v>3185</v>
+      </c>
+      <c r="D12" s="59"/>
+      <c r="E12" s="59"/>
+      <c r="F12" s="59"/>
+      <c r="G12" s="59"/>
+      <c r="H12" s="59"/>
+      <c r="I12" s="59"/>
+      <c r="J12" s="60"/>
+      <c r="K12" s="61"/>
+      <c r="L12" s="62"/>
+      <c r="M12" s="63">
+        <v>25</v>
+      </c>
+      <c r="N12" s="64">
+        <v>4</v>
+      </c>
+      <c r="O12" s="65">
+        <v>10</v>
+      </c>
+      <c r="P12" s="66">
+        <v>18</v>
+      </c>
+      <c r="Q12" s="66">
+        <v>24</v>
+      </c>
+      <c r="R12" s="67">
+        <v>5</v>
+      </c>
+      <c r="S12" s="62"/>
+      <c r="T12" s="69">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="U12" s="69">
+        <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
+        <v>77883</v>
+      </c>
+      <c r="V12" s="69">
+        <f>U12/24</f>
+        <v>3245.125</v>
+      </c>
+      <c r="W12" s="9"/>
+      <c r="X12" s="9"/>
+      <c r="Y12" s="9"/>
+      <c r="Z12" s="9"/>
+      <c r="AA12" s="9"/>
+      <c r="AB12" s="9"/>
+      <c r="AC12" s="9"/>
+      <c r="AD12" s="9"/>
+      <c r="AE12" s="9"/>
+      <c r="AF12" s="12"/>
+      <c r="AG12" s="12"/>
+      <c r="AH12" s="12"/>
+      <c r="AI12" s="12"/>
+      <c r="AJ12" s="12"/>
+      <c r="AK12" s="12"/>
+      <c r="AL12" s="12"/>
+      <c r="AM12" s="12"/>
+      <c r="AN12" s="12"/>
+      <c r="AO12" s="12"/>
+      <c r="AP12" s="12"/>
+      <c r="AQ12" s="12"/>
+      <c r="AR12" s="12"/>
+      <c r="AS12" s="12"/>
+      <c r="AT12" s="12"/>
+      <c r="AU12" s="12"/>
+      <c r="AV12" s="12"/>
+      <c r="AW12" s="12"/>
+      <c r="AX12" s="12"/>
+      <c r="AY12" s="12"/>
+      <c r="AZ12" s="12"/>
+      <c r="BA12" s="12"/>
+      <c r="BB12" s="12"/>
+    </row>
+    <row r="13" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A13" s="27">
+        <v>11</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="70">
+        <v>2</v>
+      </c>
+      <c r="D13" s="70"/>
+      <c r="E13" s="70"/>
+      <c r="F13" s="70"/>
+      <c r="G13" s="70"/>
+      <c r="H13" s="70">
+        <v>16</v>
+      </c>
+      <c r="I13" s="70"/>
+      <c r="J13" s="71"/>
+      <c r="K13" s="72"/>
+      <c r="L13" s="55"/>
+      <c r="M13" s="73"/>
+      <c r="N13" s="74"/>
+      <c r="O13" s="70"/>
+      <c r="P13" s="71"/>
+      <c r="Q13" s="71"/>
+      <c r="R13" s="72"/>
+      <c r="S13" s="55"/>
+      <c r="T13" s="76">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="U13" s="76">
+        <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
+        <v>64</v>
+      </c>
+      <c r="V13" s="76">
+        <f>U13/24</f>
+        <v>2.6666666666666665</v>
+      </c>
+      <c r="AF13" s="12"/>
+      <c r="AG13" s="12"/>
+      <c r="AH13" s="12"/>
+      <c r="AI13" s="12"/>
+      <c r="AJ13" s="12"/>
+      <c r="AK13" s="12"/>
+      <c r="AL13" s="12"/>
+      <c r="AM13" s="12"/>
+      <c r="AN13" s="12"/>
+      <c r="AO13" s="12"/>
+      <c r="AP13" s="12"/>
+      <c r="AQ13" s="12"/>
+      <c r="AR13" s="12"/>
+      <c r="AS13" s="12"/>
+      <c r="AT13" s="12"/>
+      <c r="AU13" s="12"/>
+      <c r="AV13" s="12"/>
+      <c r="AW13" s="12"/>
+      <c r="AX13" s="12"/>
+      <c r="AY13" s="12"/>
+      <c r="AZ13" s="12"/>
+      <c r="BA13" s="12"/>
+      <c r="BB13" s="12"/>
+    </row>
+    <row r="14" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A14" s="27">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="70">
+        <v>2</v>
+      </c>
+      <c r="D14" s="70"/>
+      <c r="E14" s="70"/>
+      <c r="F14" s="70"/>
+      <c r="G14" s="70"/>
+      <c r="H14" s="70"/>
+      <c r="I14" s="70"/>
+      <c r="J14" s="71"/>
+      <c r="K14" s="72"/>
+      <c r="L14" s="55"/>
+      <c r="M14" s="73"/>
+      <c r="N14" s="74"/>
+      <c r="O14" s="70"/>
+      <c r="P14" s="71"/>
+      <c r="Q14" s="71"/>
+      <c r="R14" s="72"/>
+      <c r="S14" s="55"/>
+      <c r="T14" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U14" s="75">
+        <f t="shared" ref="U14:U36" si="4">C14*24+M14*24+O14*24+Q14*24+T14</f>
+        <v>48</v>
+      </c>
+      <c r="V14" s="75">
+        <f t="shared" ref="V14:V36" si="5">U14/24</f>
+        <v>2</v>
+      </c>
+      <c r="AF14" s="12"/>
+      <c r="AG14" s="12"/>
+      <c r="AH14" s="12"/>
+      <c r="AI14" s="12"/>
+      <c r="AJ14" s="12"/>
+      <c r="AK14" s="12"/>
+      <c r="AL14" s="12"/>
+      <c r="AM14" s="12"/>
+      <c r="AN14" s="12"/>
+      <c r="AO14" s="12"/>
+      <c r="AP14" s="12"/>
+      <c r="AQ14" s="12"/>
+      <c r="AR14" s="12"/>
+      <c r="AS14" s="12"/>
+      <c r="AT14" s="12"/>
+      <c r="AU14" s="12"/>
+      <c r="AV14" s="12"/>
+      <c r="AW14" s="12"/>
+      <c r="AX14" s="12"/>
+      <c r="AY14" s="12"/>
+      <c r="AZ14" s="12"/>
+      <c r="BA14" s="12"/>
+      <c r="BB14" s="12"/>
+    </row>
+    <row r="15" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A15" s="27">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="70"/>
+      <c r="D15" s="70"/>
+      <c r="E15" s="70"/>
+      <c r="F15" s="70"/>
+      <c r="G15" s="70"/>
+      <c r="H15" s="70"/>
+      <c r="I15" s="70"/>
+      <c r="J15" s="71"/>
+      <c r="K15" s="72"/>
+      <c r="L15" s="55"/>
+      <c r="M15" s="73"/>
+      <c r="N15" s="74"/>
+      <c r="O15" s="70"/>
+      <c r="P15" s="71"/>
+      <c r="Q15" s="71"/>
+      <c r="R15" s="72"/>
+      <c r="S15" s="55"/>
+      <c r="T15" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U15" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF15" s="12"/>
+      <c r="AG15" s="12"/>
+      <c r="AH15" s="12"/>
+      <c r="AI15" s="12"/>
+      <c r="AJ15" s="12"/>
+      <c r="AK15" s="12"/>
+      <c r="AL15" s="12"/>
+      <c r="AM15" s="12"/>
+      <c r="AN15" s="12"/>
+      <c r="AO15" s="12"/>
+      <c r="AP15" s="12"/>
+      <c r="AQ15" s="12"/>
+      <c r="AR15" s="12"/>
+      <c r="AS15" s="12"/>
+      <c r="AT15" s="12"/>
+      <c r="AU15" s="12"/>
+      <c r="AV15" s="12"/>
+      <c r="AW15" s="12"/>
+      <c r="AX15" s="12"/>
+      <c r="AY15" s="12"/>
+      <c r="AZ15" s="12"/>
+      <c r="BA15" s="12"/>
+      <c r="BB15" s="12"/>
+    </row>
+    <row r="16" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A16" s="27">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="70"/>
+      <c r="D16" s="70"/>
+      <c r="E16" s="70"/>
+      <c r="F16" s="70"/>
+      <c r="G16" s="70"/>
+      <c r="H16" s="70"/>
+      <c r="I16" s="70"/>
+      <c r="J16" s="71"/>
+      <c r="K16" s="72"/>
+      <c r="L16" s="55"/>
+      <c r="M16" s="73"/>
+      <c r="N16" s="74"/>
+      <c r="O16" s="70"/>
+      <c r="P16" s="71"/>
+      <c r="Q16" s="71"/>
+      <c r="R16" s="72"/>
+      <c r="S16" s="55"/>
+      <c r="T16" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U16" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF16" s="12"/>
+      <c r="AG16" s="12"/>
+      <c r="AH16" s="12"/>
+      <c r="AI16" s="12"/>
+      <c r="AJ16" s="12"/>
+      <c r="AK16" s="12"/>
+      <c r="AL16" s="12"/>
+      <c r="AM16" s="12"/>
+      <c r="AN16" s="12"/>
+      <c r="AO16" s="12"/>
+      <c r="AP16" s="12"/>
+      <c r="AQ16" s="12"/>
+      <c r="AR16" s="12"/>
+      <c r="AS16" s="12"/>
+      <c r="AT16" s="12"/>
+      <c r="AU16" s="12"/>
+      <c r="AV16" s="12"/>
+      <c r="AW16" s="12"/>
+      <c r="AX16" s="12"/>
+      <c r="AY16" s="12"/>
+      <c r="AZ16" s="12"/>
+      <c r="BA16" s="12"/>
+      <c r="BB16" s="12"/>
+    </row>
+    <row r="17" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A17" s="27">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="70"/>
+      <c r="D17" s="70"/>
+      <c r="E17" s="70"/>
+      <c r="F17" s="70"/>
+      <c r="G17" s="70"/>
+      <c r="H17" s="70">
+        <f>3*24</f>
+        <v>72</v>
+      </c>
+      <c r="I17" s="70"/>
+      <c r="J17" s="71"/>
+      <c r="K17" s="72"/>
+      <c r="L17" s="55"/>
+      <c r="M17" s="73"/>
+      <c r="N17" s="74"/>
+      <c r="O17" s="70"/>
+      <c r="P17" s="71"/>
+      <c r="Q17" s="71"/>
+      <c r="R17" s="72"/>
+      <c r="S17" s="55"/>
+      <c r="T17" s="58">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="U17" s="75">
+        <f t="shared" si="4"/>
+        <v>72</v>
+      </c>
+      <c r="V17" s="75">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="AF17" s="12"/>
+      <c r="AG17" s="12"/>
+      <c r="AH17" s="12"/>
+      <c r="AI17" s="12"/>
+      <c r="AJ17" s="12"/>
+      <c r="AK17" s="12"/>
+      <c r="AL17" s="12"/>
+      <c r="AM17" s="12"/>
+      <c r="AN17" s="12"/>
+      <c r="AO17" s="12"/>
+      <c r="AP17" s="12"/>
+      <c r="AQ17" s="12"/>
+      <c r="AR17" s="12"/>
+      <c r="AS17" s="12"/>
+      <c r="AT17" s="12"/>
+      <c r="AU17" s="12"/>
+      <c r="AV17" s="12"/>
+      <c r="AW17" s="12"/>
+      <c r="AX17" s="12"/>
+      <c r="AY17" s="12"/>
+      <c r="AZ17" s="12"/>
+      <c r="BA17" s="12"/>
+      <c r="BB17" s="12"/>
+    </row>
+    <row r="18" spans="1:54" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="27">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="70"/>
+      <c r="D18" s="70"/>
+      <c r="E18" s="70"/>
+      <c r="F18" s="70"/>
+      <c r="G18" s="70"/>
+      <c r="H18" s="70"/>
+      <c r="I18" s="70"/>
+      <c r="J18" s="71"/>
+      <c r="K18" s="72"/>
+      <c r="L18" s="55"/>
+      <c r="M18" s="73"/>
+      <c r="N18" s="74"/>
+      <c r="O18" s="70"/>
+      <c r="P18" s="71"/>
+      <c r="Q18" s="71"/>
+      <c r="R18" s="72"/>
+      <c r="S18" s="55"/>
+      <c r="T18" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U18" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF18" s="12"/>
+      <c r="AG18" s="12"/>
+      <c r="AH18" s="12"/>
+      <c r="AI18" s="12"/>
+      <c r="AJ18" s="12"/>
+      <c r="AK18" s="12"/>
+      <c r="AL18" s="12"/>
+      <c r="AM18" s="12"/>
+      <c r="AN18" s="12"/>
+      <c r="AO18" s="12"/>
+      <c r="AP18" s="12"/>
+      <c r="AQ18" s="12"/>
+      <c r="AR18" s="12"/>
+      <c r="AS18" s="12"/>
+      <c r="AT18" s="12"/>
+      <c r="AU18" s="12"/>
+      <c r="AV18" s="12"/>
+      <c r="AW18" s="12"/>
+      <c r="AX18" s="12"/>
+      <c r="AY18" s="12"/>
+      <c r="AZ18" s="12"/>
+      <c r="BA18" s="12"/>
+      <c r="BB18" s="12"/>
+    </row>
+    <row r="19" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A19" s="27">
+        <v>16</v>
+      </c>
+      <c r="B19" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="70">
+        <v>2</v>
+      </c>
+      <c r="D19" s="70"/>
+      <c r="E19" s="70"/>
+      <c r="F19" s="70"/>
+      <c r="G19" s="70"/>
+      <c r="H19" s="70">
+        <f>20+24</f>
+        <v>44</v>
+      </c>
+      <c r="I19" s="70"/>
+      <c r="J19" s="71"/>
+      <c r="K19" s="72"/>
+      <c r="L19" s="55"/>
+      <c r="M19" s="73"/>
+      <c r="N19" s="74"/>
+      <c r="O19" s="70"/>
+      <c r="P19" s="71"/>
+      <c r="Q19" s="71"/>
+      <c r="R19" s="72"/>
+      <c r="S19" s="55"/>
+      <c r="T19" s="58">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="U19" s="75">
+        <f t="shared" si="4"/>
+        <v>92</v>
+      </c>
+      <c r="V19" s="75">
+        <f t="shared" si="5"/>
+        <v>3.8333333333333335</v>
+      </c>
+      <c r="AF19" s="12"/>
+      <c r="AG19" s="12"/>
+      <c r="AH19" s="12"/>
+      <c r="AI19" s="12"/>
+      <c r="AJ19" s="12"/>
+      <c r="AK19" s="12"/>
+      <c r="AL19" s="12"/>
+      <c r="AM19" s="12"/>
+      <c r="AN19" s="12"/>
+      <c r="AO19" s="12"/>
+      <c r="AP19" s="12"/>
+      <c r="AQ19" s="12"/>
+      <c r="AR19" s="12"/>
+      <c r="AS19" s="12"/>
+      <c r="AT19" s="12"/>
+      <c r="AU19" s="12"/>
+      <c r="AV19" s="12"/>
+      <c r="AW19" s="12"/>
+      <c r="AX19" s="12"/>
+      <c r="AY19" s="12"/>
+      <c r="AZ19" s="12"/>
+      <c r="BA19" s="12"/>
+      <c r="BB19" s="12"/>
+    </row>
+    <row r="20" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A20" s="27">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="B20" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="70">
+        <v>5</v>
+      </c>
+      <c r="D20" s="70"/>
+      <c r="E20" s="70"/>
+      <c r="F20" s="70"/>
+      <c r="G20" s="70"/>
+      <c r="H20" s="70"/>
+      <c r="I20" s="70"/>
+      <c r="J20" s="71"/>
+      <c r="K20" s="72"/>
+      <c r="L20" s="55"/>
+      <c r="M20" s="73"/>
+      <c r="N20" s="74"/>
+      <c r="O20" s="70"/>
+      <c r="P20" s="71"/>
+      <c r="Q20" s="71"/>
+      <c r="R20" s="72"/>
+      <c r="S20" s="55"/>
+      <c r="T20" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U20" s="75">
+        <f t="shared" si="4"/>
+        <v>120</v>
+      </c>
+      <c r="V20" s="75">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="AF20" s="12"/>
+      <c r="AG20" s="12"/>
+      <c r="AH20" s="12"/>
+      <c r="AI20" s="12"/>
+      <c r="AJ20" s="12"/>
+      <c r="AK20" s="12"/>
+      <c r="AL20" s="12"/>
+      <c r="AM20" s="12"/>
+      <c r="AN20" s="12"/>
+      <c r="AO20" s="12"/>
+      <c r="AP20" s="12"/>
+      <c r="AQ20" s="12"/>
+      <c r="AR20" s="12"/>
+      <c r="AS20" s="12"/>
+      <c r="AT20" s="12"/>
+      <c r="AU20" s="12"/>
+      <c r="AV20" s="12"/>
+      <c r="AW20" s="12"/>
+      <c r="AX20" s="12"/>
+      <c r="AY20" s="12"/>
+      <c r="AZ20" s="12"/>
+      <c r="BA20" s="12"/>
+      <c r="BB20" s="12"/>
+    </row>
+    <row r="21" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A21" s="27">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="B21" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="70"/>
+      <c r="D21" s="70"/>
+      <c r="E21" s="70"/>
+      <c r="F21" s="70"/>
+      <c r="G21" s="70"/>
+      <c r="H21" s="70">
+        <f>2*24</f>
+        <v>48</v>
+      </c>
+      <c r="I21" s="70"/>
+      <c r="J21" s="71"/>
+      <c r="K21" s="72"/>
+      <c r="L21" s="55"/>
+      <c r="M21" s="73"/>
+      <c r="N21" s="74"/>
+      <c r="O21" s="70"/>
+      <c r="P21" s="71"/>
+      <c r="Q21" s="71"/>
+      <c r="R21" s="72"/>
+      <c r="S21" s="55"/>
+      <c r="T21" s="58">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+      <c r="U21" s="75">
+        <f t="shared" si="4"/>
+        <v>48</v>
+      </c>
+      <c r="V21" s="75">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="AF21" s="12"/>
+      <c r="AG21" s="12"/>
+      <c r="AH21" s="12"/>
+      <c r="AI21" s="12"/>
+      <c r="AJ21" s="12"/>
+      <c r="AK21" s="12"/>
+      <c r="AL21" s="12"/>
+      <c r="AM21" s="12"/>
+      <c r="AN21" s="12"/>
+      <c r="AO21" s="12"/>
+      <c r="AP21" s="12"/>
+      <c r="AQ21" s="12"/>
+      <c r="AR21" s="12"/>
+      <c r="AS21" s="12"/>
+      <c r="AT21" s="12"/>
+      <c r="AU21" s="12"/>
+      <c r="AV21" s="12"/>
+      <c r="AW21" s="12"/>
+      <c r="AX21" s="12"/>
+      <c r="AY21" s="12"/>
+      <c r="AZ21" s="12"/>
+      <c r="BA21" s="12"/>
+      <c r="BB21" s="12"/>
+    </row>
+    <row r="22" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="27">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="B22" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="70">
+        <v>2</v>
+      </c>
+      <c r="D22" s="70"/>
+      <c r="E22" s="70"/>
+      <c r="F22" s="70"/>
+      <c r="G22" s="70"/>
+      <c r="H22" s="70"/>
+      <c r="I22" s="70">
+        <v>20</v>
+      </c>
+      <c r="J22" s="71"/>
+      <c r="K22" s="72"/>
+      <c r="L22" s="55"/>
+      <c r="M22" s="73"/>
+      <c r="N22" s="74"/>
+      <c r="O22" s="70"/>
+      <c r="P22" s="71"/>
+      <c r="Q22" s="71"/>
+      <c r="R22" s="72"/>
+      <c r="S22" s="55"/>
+      <c r="T22" s="58">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="U22" s="75">
+        <f t="shared" si="4"/>
+        <v>68</v>
+      </c>
+      <c r="V22" s="75">
+        <f t="shared" si="5"/>
+        <v>2.8333333333333335</v>
+      </c>
+      <c r="W22" s="9"/>
+      <c r="X22" s="9"/>
+      <c r="Y22" s="9"/>
+      <c r="Z22" s="9"/>
+      <c r="AA22" s="9"/>
+      <c r="AB22" s="9"/>
+      <c r="AC22" s="9"/>
+      <c r="AD22" s="9"/>
+      <c r="AE22" s="9"/>
+      <c r="AF22" s="12"/>
+      <c r="AG22" s="12"/>
+      <c r="AH22" s="12"/>
+      <c r="AI22" s="12"/>
+      <c r="AJ22" s="12"/>
+      <c r="AK22" s="12"/>
+      <c r="AL22" s="12"/>
+      <c r="AM22" s="12"/>
+      <c r="AN22" s="12"/>
+      <c r="AO22" s="12"/>
+      <c r="AP22" s="12"/>
+      <c r="AQ22" s="12"/>
+      <c r="AR22" s="12"/>
+      <c r="AS22" s="12"/>
+      <c r="AT22" s="12"/>
+      <c r="AU22" s="12"/>
+      <c r="AV22" s="12"/>
+      <c r="AW22" s="12"/>
+      <c r="AX22" s="12"/>
+      <c r="AY22" s="12"/>
+      <c r="AZ22" s="12"/>
+      <c r="BA22" s="12"/>
+      <c r="BB22" s="12"/>
+    </row>
+    <row r="23" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="27">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="B23" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="70"/>
+      <c r="D23" s="70"/>
+      <c r="E23" s="70"/>
+      <c r="F23" s="70"/>
+      <c r="G23" s="70"/>
+      <c r="H23" s="70">
+        <f>37*24+19</f>
+        <v>907</v>
+      </c>
+      <c r="I23" s="70"/>
+      <c r="J23" s="71"/>
+      <c r="K23" s="72"/>
+      <c r="L23" s="55"/>
+      <c r="M23" s="73"/>
+      <c r="N23" s="74"/>
+      <c r="O23" s="70"/>
+      <c r="P23" s="71"/>
+      <c r="Q23" s="71"/>
+      <c r="R23" s="72"/>
+      <c r="S23" s="55"/>
+      <c r="T23" s="58">
+        <f t="shared" si="0"/>
+        <v>907</v>
+      </c>
+      <c r="U23" s="75">
+        <f t="shared" si="4"/>
+        <v>907</v>
+      </c>
+      <c r="V23" s="75">
+        <f t="shared" si="5"/>
+        <v>37.791666666666664</v>
+      </c>
+      <c r="W23" s="9"/>
+      <c r="X23" s="9"/>
+      <c r="Y23" s="9"/>
+      <c r="Z23" s="9"/>
+      <c r="AA23" s="9"/>
+      <c r="AB23" s="9"/>
+      <c r="AC23" s="9"/>
+      <c r="AD23" s="9"/>
+      <c r="AE23" s="9"/>
+      <c r="AF23" s="12"/>
+      <c r="AG23" s="12"/>
+      <c r="AH23" s="12"/>
+      <c r="AI23" s="12"/>
+      <c r="AJ23" s="12"/>
+      <c r="AK23" s="12"/>
+      <c r="AL23" s="12"/>
+      <c r="AM23" s="12"/>
+      <c r="AN23" s="12"/>
+      <c r="AO23" s="12"/>
+      <c r="AP23" s="12"/>
+      <c r="AQ23" s="12"/>
+      <c r="AR23" s="12"/>
+      <c r="AS23" s="12"/>
+      <c r="AT23" s="12"/>
+      <c r="AU23" s="12"/>
+      <c r="AV23" s="12"/>
+      <c r="AW23" s="12"/>
+      <c r="AX23" s="12"/>
+      <c r="AY23" s="12"/>
+      <c r="AZ23" s="12"/>
+      <c r="BA23" s="12"/>
+      <c r="BB23" s="12"/>
+    </row>
+    <row r="24" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A24" s="27">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="B24" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" s="70">
+        <v>2</v>
+      </c>
+      <c r="D24" s="70"/>
+      <c r="E24" s="70"/>
+      <c r="F24" s="70"/>
+      <c r="G24" s="70"/>
+      <c r="H24" s="70">
+        <f>3*24</f>
+        <v>72</v>
+      </c>
+      <c r="I24" s="70"/>
+      <c r="J24" s="71"/>
+      <c r="K24" s="72"/>
+      <c r="L24" s="55"/>
+      <c r="M24" s="73"/>
+      <c r="N24" s="74"/>
+      <c r="O24" s="70"/>
+      <c r="P24" s="71"/>
+      <c r="Q24" s="71"/>
+      <c r="R24" s="72"/>
+      <c r="S24" s="55"/>
+      <c r="T24" s="58">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="U24" s="75">
+        <f t="shared" si="4"/>
+        <v>120</v>
+      </c>
+      <c r="V24" s="75">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="AF24" s="12"/>
+      <c r="AG24" s="12"/>
+      <c r="AH24" s="12"/>
+      <c r="AI24" s="12"/>
+      <c r="AJ24" s="12"/>
+      <c r="AK24" s="12"/>
+      <c r="AL24" s="12"/>
+      <c r="AM24" s="12"/>
+      <c r="AN24" s="12"/>
+      <c r="AO24" s="12"/>
+      <c r="AP24" s="12"/>
+      <c r="AQ24" s="12"/>
+      <c r="AR24" s="12"/>
+      <c r="AS24" s="12"/>
+      <c r="AT24" s="12"/>
+      <c r="AU24" s="12"/>
+      <c r="AV24" s="12"/>
+      <c r="AW24" s="12"/>
+      <c r="AX24" s="12"/>
+      <c r="AY24" s="12"/>
+      <c r="AZ24" s="12"/>
+      <c r="BA24" s="12"/>
+      <c r="BB24" s="12"/>
+    </row>
+    <row r="25" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A25" s="27">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="70">
+        <v>41</v>
+      </c>
+      <c r="D25" s="70"/>
+      <c r="E25" s="70"/>
+      <c r="F25" s="70"/>
+      <c r="G25" s="70"/>
+      <c r="H25" s="70"/>
+      <c r="I25" s="70">
+        <v>1</v>
+      </c>
+      <c r="J25" s="71"/>
+      <c r="K25" s="72"/>
+      <c r="L25" s="55"/>
+      <c r="M25" s="73">
+        <v>1</v>
+      </c>
+      <c r="N25" s="74"/>
+      <c r="O25" s="70">
+        <v>1</v>
+      </c>
+      <c r="P25" s="71"/>
+      <c r="Q25" s="71"/>
+      <c r="R25" s="72"/>
+      <c r="S25" s="55"/>
+      <c r="T25" s="58">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="U25" s="75">
+        <f t="shared" si="4"/>
+        <v>1033</v>
+      </c>
+      <c r="V25" s="75">
+        <f t="shared" si="5"/>
+        <v>43.041666666666664</v>
+      </c>
+      <c r="AY25" s="14" t="e">
+        <f>#REF!-AY24</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="27">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="B26" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="70"/>
+      <c r="D26" s="70"/>
+      <c r="E26" s="70"/>
+      <c r="F26" s="70"/>
+      <c r="G26" s="70"/>
+      <c r="H26" s="70"/>
+      <c r="I26" s="70"/>
+      <c r="J26" s="71"/>
+      <c r="K26" s="72"/>
+      <c r="L26" s="55"/>
+      <c r="M26" s="73"/>
+      <c r="N26" s="74"/>
+      <c r="O26" s="70"/>
+      <c r="P26" s="71"/>
+      <c r="Q26" s="71">
+        <v>1</v>
+      </c>
+      <c r="R26" s="72"/>
+      <c r="S26" s="55"/>
+      <c r="T26" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U26" s="75">
+        <f t="shared" si="4"/>
+        <v>24</v>
+      </c>
+      <c r="V26" s="75">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="W26" s="9"/>
+      <c r="X26" s="9"/>
+      <c r="Y26" s="9"/>
+      <c r="Z26" s="9"/>
+      <c r="AA26" s="9"/>
+      <c r="AB26" s="9"/>
+      <c r="AC26" s="9"/>
+      <c r="AD26" s="9"/>
+      <c r="AE26" s="9"/>
+    </row>
+    <row r="27" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="27">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="B27" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27" s="70">
+        <v>3</v>
+      </c>
+      <c r="D27" s="70"/>
+      <c r="E27" s="70"/>
+      <c r="F27" s="70"/>
+      <c r="G27" s="70"/>
+      <c r="H27" s="70"/>
+      <c r="I27" s="70"/>
+      <c r="J27" s="71"/>
+      <c r="K27" s="72"/>
+      <c r="L27" s="55"/>
+      <c r="M27" s="73"/>
+      <c r="N27" s="74"/>
+      <c r="O27" s="70"/>
+      <c r="P27" s="71"/>
+      <c r="Q27" s="71"/>
+      <c r="R27" s="72"/>
+      <c r="S27" s="55"/>
+      <c r="T27" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U27" s="75">
+        <f t="shared" si="4"/>
+        <v>72</v>
+      </c>
+      <c r="V27" s="75">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="W27" s="9"/>
+      <c r="X27" s="9"/>
+      <c r="Y27" s="9"/>
+      <c r="Z27" s="9"/>
+      <c r="AA27" s="9"/>
+      <c r="AB27" s="9"/>
+      <c r="AC27" s="9"/>
+      <c r="AD27" s="9"/>
+      <c r="AE27" s="9"/>
+    </row>
+    <row r="28" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="27">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="B28" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="70"/>
+      <c r="D28" s="70"/>
+      <c r="E28" s="70"/>
+      <c r="F28" s="70"/>
+      <c r="G28" s="70"/>
+      <c r="H28" s="70"/>
+      <c r="I28" s="70"/>
+      <c r="J28" s="71"/>
+      <c r="K28" s="72"/>
+      <c r="L28" s="55"/>
+      <c r="M28" s="73"/>
+      <c r="N28" s="74"/>
+      <c r="O28" s="70"/>
+      <c r="P28" s="71"/>
+      <c r="Q28" s="71"/>
+      <c r="R28" s="72"/>
+      <c r="S28" s="55"/>
+      <c r="T28" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U28" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V28" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W28" s="9"/>
+      <c r="X28" s="9"/>
+      <c r="Y28" s="9"/>
+      <c r="Z28" s="9"/>
+      <c r="AA28" s="9"/>
+      <c r="AB28" s="9"/>
+      <c r="AC28" s="9"/>
+      <c r="AD28" s="9"/>
+      <c r="AE28" s="9"/>
+    </row>
+    <row r="29" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A29" s="27">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="B29" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" s="70">
+        <v>21</v>
+      </c>
+      <c r="D29" s="70"/>
+      <c r="E29" s="70"/>
+      <c r="F29" s="70"/>
+      <c r="G29" s="70"/>
+      <c r="H29" s="70"/>
+      <c r="I29" s="70">
+        <v>5</v>
+      </c>
+      <c r="J29" s="71"/>
+      <c r="K29" s="72"/>
+      <c r="L29" s="55"/>
+      <c r="M29" s="73"/>
+      <c r="N29" s="74"/>
+      <c r="O29" s="70">
+        <v>1</v>
+      </c>
+      <c r="P29" s="71"/>
+      <c r="Q29" s="71">
+        <v>1</v>
+      </c>
+      <c r="R29" s="72"/>
+      <c r="S29" s="55"/>
+      <c r="T29" s="58">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="U29" s="75">
+        <f t="shared" si="4"/>
+        <v>557</v>
+      </c>
+      <c r="V29" s="75">
+        <f t="shared" si="5"/>
+        <v>23.208333333333332</v>
+      </c>
+    </row>
+    <row r="30" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A30" s="27">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="B30" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="70">
+        <v>9</v>
+      </c>
+      <c r="D30" s="70"/>
+      <c r="E30" s="70"/>
+      <c r="F30" s="70"/>
+      <c r="G30" s="70"/>
+      <c r="H30" s="70"/>
+      <c r="I30" s="70"/>
+      <c r="J30" s="71"/>
+      <c r="K30" s="72"/>
+      <c r="L30" s="55"/>
+      <c r="M30" s="73"/>
+      <c r="N30" s="74"/>
+      <c r="O30" s="70">
+        <v>1</v>
+      </c>
+      <c r="P30" s="71"/>
+      <c r="Q30" s="71">
+        <v>1</v>
+      </c>
+      <c r="R30" s="72"/>
+      <c r="S30" s="55"/>
+      <c r="T30" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U30" s="75">
+        <f t="shared" si="4"/>
+        <v>264</v>
+      </c>
+      <c r="V30" s="75">
+        <f t="shared" si="5"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="31" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A31" s="27">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="B31" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" s="70"/>
+      <c r="D31" s="70"/>
+      <c r="E31" s="70"/>
+      <c r="F31" s="70"/>
+      <c r="G31" s="70"/>
+      <c r="H31" s="70"/>
+      <c r="I31" s="70"/>
+      <c r="J31" s="71"/>
+      <c r="K31" s="72"/>
+      <c r="L31" s="55"/>
+      <c r="M31" s="73"/>
+      <c r="N31" s="74"/>
+      <c r="O31" s="70"/>
+      <c r="P31" s="71"/>
+      <c r="Q31" s="71"/>
+      <c r="R31" s="72"/>
+      <c r="S31" s="55"/>
+      <c r="T31" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U31" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V31" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A32" s="27">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="B32" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" s="70"/>
+      <c r="D32" s="70"/>
+      <c r="E32" s="70"/>
+      <c r="F32" s="70"/>
+      <c r="G32" s="70"/>
+      <c r="H32" s="70"/>
+      <c r="I32" s="70"/>
+      <c r="J32" s="71"/>
+      <c r="K32" s="72"/>
+      <c r="L32" s="55"/>
+      <c r="M32" s="73"/>
+      <c r="N32" s="74"/>
+      <c r="O32" s="70"/>
+      <c r="P32" s="71"/>
+      <c r="Q32" s="71"/>
+      <c r="R32" s="72"/>
+      <c r="S32" s="55"/>
+      <c r="T32" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U32" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V32" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A33" s="27">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="B33" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" s="70"/>
+      <c r="D33" s="70"/>
+      <c r="E33" s="70"/>
+      <c r="F33" s="70"/>
+      <c r="G33" s="70"/>
+      <c r="H33" s="70"/>
+      <c r="I33" s="70"/>
+      <c r="J33" s="71"/>
+      <c r="K33" s="72"/>
+      <c r="L33" s="55"/>
+      <c r="M33" s="73">
+        <v>1</v>
+      </c>
+      <c r="N33" s="74"/>
+      <c r="O33" s="70"/>
+      <c r="P33" s="71"/>
+      <c r="Q33" s="71"/>
+      <c r="R33" s="72"/>
+      <c r="S33" s="55"/>
+      <c r="T33" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U33" s="75">
+        <f t="shared" si="4"/>
+        <v>24</v>
+      </c>
+      <c r="V33" s="75">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A34" s="27">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="B34" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" s="70">
+        <f>144+36</f>
+        <v>180</v>
+      </c>
+      <c r="D34" s="70"/>
+      <c r="E34" s="70"/>
+      <c r="F34" s="70"/>
+      <c r="G34" s="70"/>
+      <c r="H34" s="70"/>
+      <c r="I34" s="70">
+        <v>1</v>
+      </c>
+      <c r="J34" s="71"/>
+      <c r="K34" s="72">
+        <v>1</v>
+      </c>
+      <c r="L34" s="55"/>
+      <c r="M34" s="73"/>
+      <c r="N34" s="74"/>
+      <c r="O34" s="70">
+        <v>2</v>
+      </c>
+      <c r="P34" s="71"/>
+      <c r="Q34" s="71"/>
+      <c r="R34" s="72"/>
+      <c r="S34" s="55"/>
+      <c r="T34" s="58">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="U34" s="75">
+        <f t="shared" si="4"/>
+        <v>4370</v>
+      </c>
+      <c r="V34" s="75">
+        <f t="shared" si="5"/>
+        <v>182.08333333333334</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="27">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="B35" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="C35" s="70"/>
+      <c r="D35" s="70"/>
+      <c r="E35" s="70"/>
+      <c r="F35" s="70"/>
+      <c r="G35" s="70"/>
+      <c r="H35" s="70"/>
+      <c r="I35" s="70"/>
+      <c r="J35" s="71"/>
+      <c r="K35" s="72"/>
+      <c r="L35" s="55"/>
+      <c r="M35" s="73"/>
+      <c r="N35" s="74"/>
+      <c r="O35" s="70"/>
+      <c r="P35" s="71"/>
+      <c r="Q35" s="71"/>
+      <c r="R35" s="72"/>
+      <c r="S35" s="55"/>
+      <c r="T35" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U35" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V35" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A36" s="27">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+      <c r="B36" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="70"/>
+      <c r="D36" s="70"/>
+      <c r="E36" s="70"/>
+      <c r="F36" s="70"/>
+      <c r="G36" s="70"/>
+      <c r="H36" s="70"/>
+      <c r="I36" s="70"/>
+      <c r="J36" s="71"/>
+      <c r="K36" s="72"/>
+      <c r="L36" s="55"/>
+      <c r="M36" s="73"/>
+      <c r="N36" s="74"/>
+      <c r="O36" s="70"/>
+      <c r="P36" s="71"/>
+      <c r="Q36" s="71"/>
+      <c r="R36" s="72"/>
+      <c r="S36" s="55"/>
+      <c r="T36" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U36" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="27">
+        <f t="shared" si="1"/>
+        <v>34</v>
+      </c>
+      <c r="B37" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="C37" s="59">
+        <f>2592+79</f>
+        <v>2671</v>
+      </c>
+      <c r="D37" s="59"/>
+      <c r="E37" s="59"/>
+      <c r="F37" s="59"/>
+      <c r="G37" s="59"/>
+      <c r="H37" s="59">
+        <v>4</v>
+      </c>
+      <c r="I37" s="59">
+        <v>2</v>
+      </c>
+      <c r="J37" s="60">
+        <v>5</v>
+      </c>
+      <c r="K37" s="61">
+        <f>1*6+2</f>
+        <v>8</v>
+      </c>
+      <c r="L37" s="62"/>
+      <c r="M37" s="63">
+        <v>40</v>
+      </c>
+      <c r="N37" s="64"/>
+      <c r="O37" s="65">
+        <v>29</v>
+      </c>
+      <c r="P37" s="66"/>
+      <c r="Q37" s="66">
+        <v>101</v>
+      </c>
+      <c r="R37" s="67"/>
+      <c r="S37" s="62"/>
+      <c r="T37" s="77">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="U37" s="77">
+        <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
+        <v>17065</v>
+      </c>
+      <c r="V37" s="77">
+        <f>U37/6</f>
+        <v>2844.1666666666665</v>
+      </c>
+      <c r="W37" s="50"/>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A38" s="27">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="B38" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" s="70"/>
+      <c r="D38" s="70"/>
+      <c r="E38" s="70"/>
+      <c r="F38" s="70"/>
+      <c r="G38" s="70"/>
+      <c r="H38" s="70"/>
+      <c r="I38" s="70"/>
+      <c r="J38" s="71"/>
+      <c r="K38" s="72"/>
+      <c r="L38" s="55"/>
+      <c r="M38" s="73"/>
+      <c r="N38" s="74"/>
+      <c r="O38" s="70"/>
+      <c r="P38" s="71"/>
+      <c r="Q38" s="71"/>
+      <c r="R38" s="72"/>
+      <c r="S38" s="55"/>
+      <c r="T38" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U38" s="75">
+        <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
+        <v>0</v>
+      </c>
+      <c r="V38" s="75">
+        <f>U38/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A39" s="27">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="B39" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="C39" s="78"/>
+      <c r="D39" s="78"/>
+      <c r="E39" s="78"/>
+      <c r="F39" s="78"/>
+      <c r="G39" s="78"/>
+      <c r="H39" s="78"/>
+      <c r="I39" s="78"/>
+      <c r="J39" s="79"/>
+      <c r="K39" s="80"/>
+      <c r="L39" s="55"/>
+      <c r="M39" s="73"/>
+      <c r="N39" s="74"/>
+      <c r="O39" s="70"/>
+      <c r="P39" s="71"/>
+      <c r="Q39" s="71"/>
+      <c r="R39" s="72"/>
+      <c r="S39" s="95"/>
+      <c r="T39" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U39" s="75">
+        <f>C39*24+M39*24+O39*24+Q39*24+T39</f>
+        <v>0</v>
+      </c>
+      <c r="V39" s="75">
+        <f>U39/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="27">
+        <f t="shared" si="1"/>
+        <v>37</v>
+      </c>
+      <c r="B40" s="42" t="s">
+        <v>21</v>
+      </c>
+      <c r="C40" s="59">
+        <f>252+53</f>
+        <v>305</v>
+      </c>
+      <c r="D40" s="59"/>
+      <c r="E40" s="59"/>
+      <c r="F40" s="59"/>
+      <c r="G40" s="59"/>
+      <c r="H40" s="59"/>
+      <c r="I40" s="59"/>
+      <c r="J40" s="60"/>
+      <c r="K40" s="61">
+        <v>20</v>
+      </c>
+      <c r="L40" s="62"/>
+      <c r="M40" s="63"/>
+      <c r="N40" s="64"/>
+      <c r="O40" s="65">
+        <v>2</v>
+      </c>
+      <c r="P40" s="66"/>
+      <c r="Q40" s="66"/>
+      <c r="R40" s="67"/>
+      <c r="S40" s="62"/>
+      <c r="T40" s="77">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="U40" s="77">
+        <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
+        <v>7388</v>
+      </c>
+      <c r="V40" s="77">
+        <f>U40/24</f>
+        <v>307.83333333333331</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="27">
+        <f t="shared" si="1"/>
+        <v>38</v>
+      </c>
+      <c r="B41" s="43" t="s">
+        <v>22</v>
+      </c>
+      <c r="C41" s="82">
+        <f>384+27</f>
+        <v>411</v>
+      </c>
+      <c r="D41" s="82"/>
+      <c r="E41" s="82"/>
+      <c r="F41" s="82"/>
+      <c r="G41" s="82"/>
+      <c r="H41" s="82"/>
+      <c r="I41" s="82"/>
+      <c r="J41" s="83"/>
+      <c r="K41" s="84"/>
+      <c r="L41" s="85"/>
+      <c r="M41" s="86">
+        <v>7</v>
+      </c>
+      <c r="N41" s="87"/>
+      <c r="O41" s="82">
+        <v>8</v>
+      </c>
+      <c r="P41" s="83"/>
+      <c r="Q41" s="83">
+        <v>20</v>
+      </c>
+      <c r="R41" s="84"/>
+      <c r="S41" s="85"/>
+      <c r="T41" s="88">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U41" s="88">
+        <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
+        <v>5352</v>
+      </c>
+      <c r="V41" s="88">
+        <f>U41/12</f>
+        <v>446</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="27">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+      <c r="B42" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C42" s="70"/>
+      <c r="D42" s="70"/>
+      <c r="E42" s="70"/>
+      <c r="F42" s="70"/>
+      <c r="G42" s="70"/>
+      <c r="H42" s="70"/>
+      <c r="I42" s="70"/>
+      <c r="J42" s="71"/>
+      <c r="K42" s="72"/>
+      <c r="L42" s="55"/>
+      <c r="M42" s="73"/>
+      <c r="N42" s="74"/>
+      <c r="O42" s="70"/>
+      <c r="P42" s="71"/>
+      <c r="Q42" s="71"/>
+      <c r="R42" s="72"/>
+      <c r="S42" s="55"/>
+      <c r="T42" s="75"/>
+      <c r="U42" s="75"/>
+      <c r="V42" s="75"/>
+    </row>
+    <row r="43" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="27">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="B43" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="C43" s="65">
+        <f>5832+19764+10260</f>
+        <v>35856</v>
+      </c>
+      <c r="D43" s="65"/>
+      <c r="E43" s="65"/>
+      <c r="F43" s="65"/>
+      <c r="G43" s="65"/>
+      <c r="H43" s="65">
+        <v>10</v>
+      </c>
+      <c r="I43" s="65">
+        <v>12</v>
+      </c>
+      <c r="J43" s="66">
+        <f>22*6+3</f>
+        <v>135</v>
+      </c>
+      <c r="K43" s="67">
+        <f>71*6+2</f>
+        <v>428</v>
+      </c>
+      <c r="L43" s="62"/>
+      <c r="M43" s="63">
+        <v>759</v>
+      </c>
+      <c r="N43" s="64"/>
+      <c r="O43" s="65">
+        <v>444</v>
+      </c>
+      <c r="P43" s="66"/>
+      <c r="Q43" s="66">
+        <v>506</v>
+      </c>
+      <c r="R43" s="67"/>
+      <c r="S43" s="62"/>
+      <c r="T43" s="77">
+        <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
+        <v>585</v>
+      </c>
+      <c r="U43" s="77">
+        <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
+        <v>225975</v>
+      </c>
+      <c r="V43" s="77">
+        <f>U43/6</f>
+        <v>37662.5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="27">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+      <c r="B44" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="70"/>
+      <c r="D44" s="70"/>
+      <c r="E44" s="70"/>
+      <c r="F44" s="70"/>
+      <c r="G44" s="70"/>
+      <c r="H44" s="70"/>
+      <c r="I44" s="70"/>
+      <c r="J44" s="71"/>
+      <c r="K44" s="72"/>
+      <c r="L44" s="55"/>
+      <c r="M44" s="73"/>
+      <c r="N44" s="74"/>
+      <c r="O44" s="70"/>
+      <c r="P44" s="71"/>
+      <c r="Q44" s="71"/>
+      <c r="R44" s="72"/>
+      <c r="S44" s="55"/>
+      <c r="T44" s="75"/>
+      <c r="U44" s="75"/>
+      <c r="V44" s="75"/>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A45" s="27">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="B45" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="70"/>
+      <c r="D45" s="70"/>
+      <c r="E45" s="70"/>
+      <c r="F45" s="70"/>
+      <c r="G45" s="70"/>
+      <c r="H45" s="70"/>
+      <c r="I45" s="70"/>
+      <c r="J45" s="71"/>
+      <c r="K45" s="72"/>
+      <c r="L45" s="55"/>
+      <c r="M45" s="73"/>
+      <c r="N45" s="74"/>
+      <c r="O45" s="70"/>
+      <c r="P45" s="71"/>
+      <c r="Q45" s="71"/>
+      <c r="R45" s="72"/>
+      <c r="S45" s="55"/>
+      <c r="T45" s="75">
+        <f t="shared" ref="T45:T54" si="7">H45+I45+J45+K45+N45+P45+R45</f>
+        <v>0</v>
+      </c>
+      <c r="U45" s="75">
+        <f>C45*24+M45*24+O45*24+Q45*24+T45</f>
+        <v>0</v>
+      </c>
+      <c r="V45" s="75">
+        <f>U45/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A46" s="27">
+        <f t="shared" si="1"/>
+        <v>43</v>
+      </c>
+      <c r="B46" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="C46" s="70"/>
+      <c r="D46" s="70"/>
+      <c r="E46" s="70"/>
+      <c r="F46" s="70"/>
+      <c r="G46" s="70"/>
+      <c r="H46" s="70"/>
+      <c r="I46" s="70"/>
+      <c r="J46" s="71"/>
+      <c r="K46" s="72"/>
+      <c r="L46" s="55"/>
+      <c r="M46" s="73"/>
+      <c r="N46" s="74"/>
+      <c r="O46" s="70"/>
+      <c r="P46" s="71"/>
+      <c r="Q46" s="71"/>
+      <c r="R46" s="72"/>
+      <c r="S46" s="55"/>
+      <c r="T46" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U46" s="75">
+        <f t="shared" ref="U46:U50" si="8">C46*24+M46*24+O46*24+Q46*24+T46</f>
+        <v>0</v>
+      </c>
+      <c r="V46" s="75">
+        <f t="shared" ref="V46:V54" si="9">U46/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="27">
+        <f t="shared" si="1"/>
+        <v>44</v>
+      </c>
+      <c r="B47" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="C47" s="65">
+        <f>94+648+324+88+540+103+324+432+106</f>
+        <v>2659</v>
+      </c>
+      <c r="D47" s="65"/>
+      <c r="E47" s="65"/>
+      <c r="F47" s="65"/>
+      <c r="G47" s="65"/>
+      <c r="H47" s="65">
+        <v>1</v>
+      </c>
+      <c r="I47" s="65"/>
+      <c r="J47" s="66"/>
+      <c r="K47" s="67">
+        <v>5</v>
+      </c>
+      <c r="L47" s="62"/>
+      <c r="M47" s="63">
+        <v>5</v>
+      </c>
+      <c r="N47" s="64"/>
+      <c r="O47" s="65">
+        <v>16</v>
+      </c>
+      <c r="P47" s="66"/>
+      <c r="Q47" s="66">
+        <v>5</v>
+      </c>
+      <c r="R47" s="67">
+        <v>3</v>
+      </c>
+      <c r="S47" s="62"/>
+      <c r="T47" s="77">
+        <f t="shared" si="7"/>
+        <v>9</v>
+      </c>
+      <c r="U47" s="77">
+        <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
+        <v>16119</v>
+      </c>
+      <c r="V47" s="77">
+        <f>U47/6</f>
+        <v>2686.5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A48" s="27">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="B48" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C48" s="70"/>
+      <c r="D48" s="70"/>
+      <c r="E48" s="70"/>
+      <c r="F48" s="70"/>
+      <c r="G48" s="70"/>
+      <c r="H48" s="70">
+        <v>24</v>
+      </c>
+      <c r="I48" s="70"/>
+      <c r="J48" s="71"/>
+      <c r="K48" s="72"/>
+      <c r="L48" s="55"/>
+      <c r="M48" s="73"/>
+      <c r="N48" s="74"/>
+      <c r="O48" s="70"/>
+      <c r="P48" s="71"/>
+      <c r="Q48" s="71"/>
+      <c r="R48" s="72"/>
+      <c r="S48" s="55"/>
+      <c r="T48" s="75">
+        <f t="shared" si="7"/>
+        <v>24</v>
+      </c>
+      <c r="U48" s="75">
+        <f t="shared" si="8"/>
+        <v>24</v>
+      </c>
+      <c r="V48" s="75">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A49" s="27">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="B49" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C49" s="70"/>
+      <c r="D49" s="70"/>
+      <c r="E49" s="70"/>
+      <c r="F49" s="70"/>
+      <c r="G49" s="70"/>
+      <c r="H49" s="70"/>
+      <c r="I49" s="70"/>
+      <c r="J49" s="71"/>
+      <c r="K49" s="72"/>
+      <c r="L49" s="55"/>
+      <c r="M49" s="73"/>
+      <c r="N49" s="74"/>
+      <c r="O49" s="70"/>
+      <c r="P49" s="71"/>
+      <c r="Q49" s="71"/>
+      <c r="R49" s="72"/>
+      <c r="S49" s="55"/>
+      <c r="T49" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U49" s="75">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V49" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A50" s="27">
+        <f t="shared" si="1"/>
+        <v>47</v>
+      </c>
+      <c r="B50" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="C50" s="70"/>
+      <c r="D50" s="70"/>
+      <c r="E50" s="70"/>
+      <c r="F50" s="70"/>
+      <c r="G50" s="70"/>
+      <c r="H50" s="70"/>
+      <c r="I50" s="70"/>
+      <c r="J50" s="71"/>
+      <c r="K50" s="72"/>
+      <c r="L50" s="55"/>
+      <c r="M50" s="73"/>
+      <c r="N50" s="74"/>
+      <c r="O50" s="70"/>
+      <c r="P50" s="71"/>
+      <c r="Q50" s="71"/>
+      <c r="R50" s="72"/>
+      <c r="S50" s="55"/>
+      <c r="T50" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U50" s="75">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V50" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="27">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+      <c r="B51" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="C51" s="65">
+        <v>34</v>
+      </c>
+      <c r="D51" s="65"/>
+      <c r="E51" s="65"/>
+      <c r="F51" s="65"/>
+      <c r="G51" s="65"/>
+      <c r="H51" s="65"/>
+      <c r="I51" s="65"/>
+      <c r="J51" s="66"/>
+      <c r="K51" s="67"/>
+      <c r="L51" s="62"/>
+      <c r="M51" s="63"/>
+      <c r="N51" s="64"/>
+      <c r="O51" s="65"/>
+      <c r="P51" s="66"/>
+      <c r="Q51" s="66"/>
+      <c r="R51" s="67"/>
+      <c r="S51" s="62"/>
+      <c r="T51" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U51" s="77">
+        <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
+        <v>204</v>
+      </c>
+      <c r="V51" s="77">
+        <f>U51/6</f>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A52" s="27">
+        <f t="shared" si="1"/>
+        <v>49</v>
+      </c>
+      <c r="B52" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="C52" s="70"/>
+      <c r="D52" s="70"/>
+      <c r="E52" s="70"/>
+      <c r="F52" s="70"/>
+      <c r="G52" s="70"/>
+      <c r="H52" s="70"/>
+      <c r="I52" s="70"/>
+      <c r="J52" s="71"/>
+      <c r="K52" s="72"/>
+      <c r="L52" s="55"/>
+      <c r="M52" s="73"/>
+      <c r="N52" s="74"/>
+      <c r="O52" s="70"/>
+      <c r="P52" s="71"/>
+      <c r="Q52" s="71"/>
+      <c r="R52" s="72"/>
+      <c r="S52" s="55"/>
+      <c r="T52" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U52" s="75">
+        <f t="shared" ref="U52:U54" si="10">C52*24+M52*24+O52*24+Q52*24+T52</f>
+        <v>0</v>
+      </c>
+      <c r="V52" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A53" s="27">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="B53" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C53" s="70">
+        <v>7</v>
+      </c>
+      <c r="D53" s="70"/>
+      <c r="E53" s="70"/>
+      <c r="F53" s="70"/>
+      <c r="G53" s="70"/>
+      <c r="H53" s="70"/>
+      <c r="I53" s="70"/>
+      <c r="J53" s="71"/>
+      <c r="K53" s="72"/>
+      <c r="L53" s="55"/>
+      <c r="M53" s="73"/>
+      <c r="N53" s="74"/>
+      <c r="O53" s="70"/>
+      <c r="P53" s="71"/>
+      <c r="Q53" s="71"/>
+      <c r="R53" s="72"/>
+      <c r="S53" s="55"/>
+      <c r="T53" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U53" s="75">
+        <f t="shared" si="10"/>
+        <v>168</v>
+      </c>
+      <c r="V53" s="75">
+        <f t="shared" si="9"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A54" s="27">
+        <f t="shared" si="1"/>
+        <v>51</v>
+      </c>
+      <c r="B54" s="26"/>
+      <c r="C54" s="70"/>
+      <c r="D54" s="70"/>
+      <c r="E54" s="70"/>
+      <c r="F54" s="70"/>
+      <c r="G54" s="70"/>
+      <c r="H54" s="70"/>
+      <c r="I54" s="70"/>
+      <c r="J54" s="71"/>
+      <c r="K54" s="72"/>
+      <c r="L54" s="55"/>
+      <c r="M54" s="73"/>
+      <c r="N54" s="74"/>
+      <c r="O54" s="70"/>
+      <c r="P54" s="71"/>
+      <c r="Q54" s="71"/>
+      <c r="R54" s="72"/>
+      <c r="S54" s="55"/>
+      <c r="T54" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U54" s="75">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V54" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A55" s="27">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="B55" s="26"/>
+      <c r="C55" s="70"/>
+      <c r="D55" s="70"/>
+      <c r="E55" s="70"/>
+      <c r="F55" s="70"/>
+      <c r="G55" s="70"/>
+      <c r="H55" s="70"/>
+      <c r="I55" s="70"/>
+      <c r="J55" s="71"/>
+      <c r="K55" s="72"/>
+      <c r="L55" s="55"/>
+      <c r="M55" s="73"/>
+      <c r="N55" s="74"/>
+      <c r="O55" s="70"/>
+      <c r="P55" s="71"/>
+      <c r="Q55" s="71"/>
+      <c r="R55" s="72"/>
+      <c r="S55" s="55"/>
+      <c r="T55" s="75"/>
+      <c r="U55" s="75"/>
+      <c r="V55" s="75"/>
+    </row>
+    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A56" s="27">
+        <f t="shared" si="1"/>
+        <v>53</v>
+      </c>
+      <c r="B56" s="26"/>
+      <c r="C56" s="70"/>
+      <c r="D56" s="70"/>
+      <c r="E56" s="70"/>
+      <c r="F56" s="70"/>
+      <c r="G56" s="70"/>
+      <c r="H56" s="70"/>
+      <c r="I56" s="70"/>
+      <c r="J56" s="71"/>
+      <c r="K56" s="72"/>
+      <c r="L56" s="55"/>
+      <c r="M56" s="73"/>
+      <c r="N56" s="74"/>
+      <c r="O56" s="70"/>
+      <c r="P56" s="71"/>
+      <c r="Q56" s="71"/>
+      <c r="R56" s="72"/>
+      <c r="S56" s="55"/>
+      <c r="T56" s="75"/>
+      <c r="U56" s="75"/>
+      <c r="V56" s="75"/>
+    </row>
+    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A57" s="27">
+        <f t="shared" si="1"/>
+        <v>54</v>
+      </c>
+      <c r="B57" s="26"/>
+      <c r="C57" s="70"/>
+      <c r="D57" s="70"/>
+      <c r="E57" s="70"/>
+      <c r="F57" s="70"/>
+      <c r="G57" s="70"/>
+      <c r="H57" s="70"/>
+      <c r="I57" s="70"/>
+      <c r="J57" s="71"/>
+      <c r="K57" s="72"/>
+      <c r="L57" s="55"/>
+      <c r="M57" s="73"/>
+      <c r="N57" s="74"/>
+      <c r="O57" s="70"/>
+      <c r="P57" s="71"/>
+      <c r="Q57" s="71"/>
+      <c r="R57" s="72"/>
+      <c r="S57" s="55"/>
+      <c r="T57" s="75"/>
+      <c r="U57" s="75"/>
+      <c r="V57" s="75"/>
+    </row>
+    <row r="58" spans="1:22" s="15" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B58" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="C58" s="2">
+        <f>SUM(C7:C57)</f>
+        <v>45638</v>
+      </c>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2">
+        <f t="shared" ref="F58:K58" si="11">SUM(F7:F57)</f>
+        <v>0</v>
+      </c>
+      <c r="G58" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="H58" s="2">
+        <f t="shared" si="11"/>
+        <v>1198</v>
+      </c>
+      <c r="I58" s="6">
+        <f t="shared" si="11"/>
+        <v>44</v>
+      </c>
+      <c r="J58" s="6">
+        <f t="shared" si="11"/>
+        <v>140</v>
+      </c>
+      <c r="K58" s="6">
+        <f t="shared" si="11"/>
+        <v>470</v>
+      </c>
+      <c r="M58" s="5">
+        <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
+        <v>838</v>
+      </c>
+      <c r="N58" s="5">
+        <f t="shared" si="12"/>
+        <v>4</v>
+      </c>
+      <c r="O58" s="5">
+        <f t="shared" si="12"/>
+        <v>518</v>
+      </c>
+      <c r="P58" s="5">
+        <f t="shared" si="12"/>
+        <v>30</v>
+      </c>
+      <c r="Q58" s="5">
+        <f t="shared" si="12"/>
+        <v>662</v>
+      </c>
+      <c r="R58" s="5">
+        <f t="shared" si="12"/>
+        <v>8</v>
+      </c>
+      <c r="S58" s="55"/>
+      <c r="T58" s="4">
+        <f>SUM(T7:T57)</f>
+        <v>1894</v>
+      </c>
+      <c r="U58" s="90">
+        <f>SUM(U7:U57)</f>
+        <v>364036</v>
+      </c>
+      <c r="V58" s="4">
+        <f>SUM(V7:V57)</f>
+        <v>47811.541666666664</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="60" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="C60" s="105" t="s">
+        <v>41</v>
+      </c>
+      <c r="D60" s="106"/>
+      <c r="E60" s="106"/>
+      <c r="F60" s="106"/>
+      <c r="G60" s="106"/>
+      <c r="H60" s="106"/>
+      <c r="I60" s="106"/>
+      <c r="J60" s="106"/>
+      <c r="K60" s="107"/>
+      <c r="U60" s="24" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B61" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="C61" s="19"/>
+      <c r="D61" s="19"/>
+      <c r="E61" s="19"/>
+      <c r="F61" s="19"/>
+      <c r="G61" s="19"/>
+      <c r="H61" s="19"/>
+      <c r="I61" s="19"/>
+      <c r="J61" s="45"/>
+      <c r="K61" s="20"/>
+      <c r="U61" s="7"/>
+    </row>
+    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B62" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+      <c r="J62" s="44"/>
+      <c r="K62" s="21"/>
+      <c r="U62" s="3"/>
+    </row>
+    <row r="63" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B63" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C63" s="22"/>
+      <c r="D63" s="22"/>
+      <c r="E63" s="22"/>
+      <c r="F63" s="22"/>
+      <c r="G63" s="22"/>
+      <c r="H63" s="22"/>
+      <c r="I63" s="22"/>
+      <c r="J63" s="46"/>
+      <c r="K63" s="23"/>
+      <c r="U63" s="8"/>
+    </row>
+    <row r="64" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B65" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="C65" s="19"/>
+      <c r="D65" s="19"/>
+      <c r="E65" s="19"/>
+      <c r="F65" s="19"/>
+      <c r="G65" s="19"/>
+      <c r="H65" s="19"/>
+      <c r="I65" s="19"/>
+      <c r="J65" s="45"/>
+      <c r="K65" s="20"/>
+      <c r="U65" s="7"/>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B66" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C66" s="1"/>
+      <c r="D66" s="1"/>
+      <c r="E66" s="1"/>
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="J66" s="44"/>
+      <c r="K66" s="21"/>
+      <c r="U66" s="3"/>
+    </row>
+    <row r="67" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B67" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C67" s="22"/>
+      <c r="D67" s="22"/>
+      <c r="E67" s="22"/>
+      <c r="F67" s="22"/>
+      <c r="G67" s="22"/>
+      <c r="H67" s="22"/>
+      <c r="I67" s="22"/>
+      <c r="J67" s="46"/>
+      <c r="K67" s="23"/>
+      <c r="U67" s="8"/>
+    </row>
+    <row r="68" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B69" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="C69" s="19"/>
+      <c r="D69" s="19"/>
+      <c r="E69" s="19"/>
+      <c r="F69" s="19"/>
+      <c r="G69" s="19"/>
+      <c r="H69" s="19"/>
+      <c r="I69" s="19"/>
+      <c r="J69" s="45"/>
+      <c r="K69" s="20"/>
+      <c r="U69" s="7"/>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B70" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="J70" s="44"/>
+      <c r="K70" s="21"/>
+      <c r="U70" s="3"/>
+    </row>
+    <row r="71" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B71" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C71" s="22"/>
+      <c r="D71" s="22"/>
+      <c r="E71" s="22"/>
+      <c r="F71" s="22"/>
+      <c r="G71" s="22"/>
+      <c r="H71" s="22"/>
+      <c r="I71" s="22"/>
+      <c r="J71" s="46"/>
+      <c r="K71" s="23"/>
+      <c r="U71" s="8"/>
+    </row>
+    <row r="72" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B73" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="C73" s="19"/>
+      <c r="D73" s="19"/>
+      <c r="E73" s="19"/>
+      <c r="F73" s="19"/>
+      <c r="G73" s="19"/>
+      <c r="H73" s="19"/>
+      <c r="I73" s="19"/>
+      <c r="J73" s="45"/>
+      <c r="K73" s="20"/>
+      <c r="U73" s="7"/>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B74" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C74" s="1"/>
+      <c r="D74" s="1"/>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1"/>
+      <c r="J74" s="44"/>
+      <c r="K74" s="21"/>
+      <c r="U74" s="3"/>
+    </row>
+    <row r="75" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B75" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C75" s="22"/>
+      <c r="D75" s="22"/>
+      <c r="E75" s="22"/>
+      <c r="F75" s="22"/>
+      <c r="G75" s="22"/>
+      <c r="H75" s="22"/>
+      <c r="I75" s="22"/>
+      <c r="J75" s="46"/>
+      <c r="K75" s="23"/>
+      <c r="U75" s="8"/>
+    </row>
+    <row r="76" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B77" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="C77" s="19"/>
+      <c r="D77" s="19"/>
+      <c r="E77" s="19"/>
+      <c r="F77" s="19"/>
+      <c r="G77" s="19"/>
+      <c r="H77" s="19"/>
+      <c r="I77" s="19"/>
+      <c r="J77" s="45"/>
+      <c r="K77" s="20"/>
+      <c r="U77" s="7"/>
+    </row>
+    <row r="78" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B78" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C78" s="1"/>
+      <c r="D78" s="1"/>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+      <c r="J78" s="44"/>
+      <c r="K78" s="21"/>
+      <c r="U78" s="3"/>
+    </row>
+    <row r="79" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B79" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C79" s="22"/>
+      <c r="D79" s="22"/>
+      <c r="E79" s="22"/>
+      <c r="F79" s="22"/>
+      <c r="G79" s="22"/>
+      <c r="H79" s="22"/>
+      <c r="I79" s="22"/>
+      <c r="J79" s="46"/>
+      <c r="K79" s="23"/>
+      <c r="U79" s="8"/>
+    </row>
+    <row r="80" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="81" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B81" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="C81" s="17"/>
+      <c r="D81" s="17"/>
+      <c r="E81" s="17"/>
+      <c r="F81" s="17"/>
+      <c r="G81" s="17"/>
+      <c r="H81" s="17"/>
+      <c r="I81" s="17"/>
+      <c r="J81" s="47"/>
+      <c r="K81" s="18"/>
+      <c r="U81" s="16"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="C60:K60"/>
+    <mergeCell ref="I1:U1"/>
+    <mergeCell ref="C4:K4"/>
+    <mergeCell ref="T4:T5"/>
+    <mergeCell ref="U4:U5"/>
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -17533,21 +20667,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="107" t="s">
+      <c r="I1" s="108" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="107"/>
-      <c r="K1" s="107"/>
-      <c r="L1" s="107"/>
-      <c r="M1" s="107"/>
-      <c r="N1" s="107"/>
-      <c r="O1" s="107"/>
-      <c r="P1" s="107"/>
-      <c r="Q1" s="107"/>
-      <c r="R1" s="107"/>
-      <c r="S1" s="107"/>
-      <c r="T1" s="107"/>
-      <c r="U1" s="107"/>
+      <c r="J1" s="108"/>
+      <c r="K1" s="108"/>
+      <c r="L1" s="108"/>
+      <c r="M1" s="108"/>
+      <c r="N1" s="108"/>
+      <c r="O1" s="108"/>
+      <c r="P1" s="108"/>
+      <c r="Q1" s="108"/>
+      <c r="R1" s="108"/>
+      <c r="S1" s="108"/>
+      <c r="T1" s="108"/>
+      <c r="U1" s="108"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -17559,17 +20693,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="108" t="s">
+      <c r="C4" s="109" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="108"/>
-      <c r="E4" s="108"/>
-      <c r="F4" s="108"/>
-      <c r="G4" s="108"/>
-      <c r="H4" s="108"/>
-      <c r="I4" s="108"/>
-      <c r="J4" s="109"/>
-      <c r="K4" s="110"/>
+      <c r="D4" s="109"/>
+      <c r="E4" s="109"/>
+      <c r="F4" s="109"/>
+      <c r="G4" s="109"/>
+      <c r="H4" s="109"/>
+      <c r="I4" s="109"/>
+      <c r="J4" s="110"/>
+      <c r="K4" s="111"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -17589,13 +20723,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="111" t="s">
+      <c r="T4" s="112" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="117" t="s">
+      <c r="U4" s="118" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="100" t="s">
+      <c r="V4" s="101" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -17635,10 +20769,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="115" t="s">
+      <c r="J5" s="116" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="116"/>
+      <c r="K5" s="117"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -17646,9 +20780,9 @@
       <c r="Q5" s="96"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="112"/>
-      <c r="U5" s="118"/>
-      <c r="V5" s="101"/>
+      <c r="T5" s="113"/>
+      <c r="U5" s="119"/>
+      <c r="V5" s="102"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -20358,17 +23492,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="104" t="s">
+      <c r="C60" s="105" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="105"/>
-      <c r="E60" s="105"/>
-      <c r="F60" s="105"/>
-      <c r="G60" s="105"/>
-      <c r="H60" s="105"/>
-      <c r="I60" s="105"/>
-      <c r="J60" s="105"/>
-      <c r="K60" s="106"/>
+      <c r="D60" s="106"/>
+      <c r="E60" s="106"/>
+      <c r="F60" s="106"/>
+      <c r="G60" s="106"/>
+      <c r="H60" s="106"/>
+      <c r="I60" s="106"/>
+      <c r="J60" s="106"/>
+      <c r="K60" s="107"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -20677,21 +23811,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="107" t="s">
+      <c r="I1" s="108" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="107"/>
-      <c r="K1" s="107"/>
-      <c r="L1" s="107"/>
-      <c r="M1" s="107"/>
-      <c r="N1" s="107"/>
-      <c r="O1" s="107"/>
-      <c r="P1" s="107"/>
-      <c r="Q1" s="107"/>
-      <c r="R1" s="107"/>
-      <c r="S1" s="107"/>
-      <c r="T1" s="107"/>
-      <c r="U1" s="107"/>
+      <c r="J1" s="108"/>
+      <c r="K1" s="108"/>
+      <c r="L1" s="108"/>
+      <c r="M1" s="108"/>
+      <c r="N1" s="108"/>
+      <c r="O1" s="108"/>
+      <c r="P1" s="108"/>
+      <c r="Q1" s="108"/>
+      <c r="R1" s="108"/>
+      <c r="S1" s="108"/>
+      <c r="T1" s="108"/>
+      <c r="U1" s="108"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -20703,17 +23837,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="108" t="s">
+      <c r="C4" s="109" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="108"/>
-      <c r="E4" s="108"/>
-      <c r="F4" s="108"/>
-      <c r="G4" s="108"/>
-      <c r="H4" s="108"/>
-      <c r="I4" s="108"/>
-      <c r="J4" s="109"/>
-      <c r="K4" s="110"/>
+      <c r="D4" s="109"/>
+      <c r="E4" s="109"/>
+      <c r="F4" s="109"/>
+      <c r="G4" s="109"/>
+      <c r="H4" s="109"/>
+      <c r="I4" s="109"/>
+      <c r="J4" s="110"/>
+      <c r="K4" s="111"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -20733,13 +23867,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="111" t="s">
+      <c r="T4" s="112" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="117" t="s">
+      <c r="U4" s="118" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="100" t="s">
+      <c r="V4" s="101" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -20779,10 +23913,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="115" t="s">
+      <c r="J5" s="116" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="116"/>
+      <c r="K5" s="117"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -20790,9 +23924,9 @@
       <c r="Q5" s="97"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="112"/>
-      <c r="U5" s="118"/>
-      <c r="V5" s="101"/>
+      <c r="T5" s="113"/>
+      <c r="U5" s="119"/>
+      <c r="V5" s="102"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -23492,17 +26626,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="104" t="s">
+      <c r="C60" s="105" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="105"/>
-      <c r="E60" s="105"/>
-      <c r="F60" s="105"/>
-      <c r="G60" s="105"/>
-      <c r="H60" s="105"/>
-      <c r="I60" s="105"/>
-      <c r="J60" s="105"/>
-      <c r="K60" s="106"/>
+      <c r="D60" s="106"/>
+      <c r="E60" s="106"/>
+      <c r="F60" s="106"/>
+      <c r="G60" s="106"/>
+      <c r="H60" s="106"/>
+      <c r="I60" s="106"/>
+      <c r="J60" s="106"/>
+      <c r="K60" s="107"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -23811,21 +26945,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="107" t="s">
+      <c r="I1" s="108" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="107"/>
-      <c r="K1" s="107"/>
-      <c r="L1" s="107"/>
-      <c r="M1" s="107"/>
-      <c r="N1" s="107"/>
-      <c r="O1" s="107"/>
-      <c r="P1" s="107"/>
-      <c r="Q1" s="107"/>
-      <c r="R1" s="107"/>
-      <c r="S1" s="107"/>
-      <c r="T1" s="107"/>
-      <c r="U1" s="107"/>
+      <c r="J1" s="108"/>
+      <c r="K1" s="108"/>
+      <c r="L1" s="108"/>
+      <c r="M1" s="108"/>
+      <c r="N1" s="108"/>
+      <c r="O1" s="108"/>
+      <c r="P1" s="108"/>
+      <c r="Q1" s="108"/>
+      <c r="R1" s="108"/>
+      <c r="S1" s="108"/>
+      <c r="T1" s="108"/>
+      <c r="U1" s="108"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -23837,17 +26971,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="108" t="s">
+      <c r="C4" s="109" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="108"/>
-      <c r="E4" s="108"/>
-      <c r="F4" s="108"/>
-      <c r="G4" s="108"/>
-      <c r="H4" s="108"/>
-      <c r="I4" s="108"/>
-      <c r="J4" s="109"/>
-      <c r="K4" s="110"/>
+      <c r="D4" s="109"/>
+      <c r="E4" s="109"/>
+      <c r="F4" s="109"/>
+      <c r="G4" s="109"/>
+      <c r="H4" s="109"/>
+      <c r="I4" s="109"/>
+      <c r="J4" s="110"/>
+      <c r="K4" s="111"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -23867,13 +27001,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="111" t="s">
+      <c r="T4" s="112" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="117" t="s">
+      <c r="U4" s="118" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="100" t="s">
+      <c r="V4" s="101" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -23913,10 +27047,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="115" t="s">
+      <c r="J5" s="116" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="116"/>
+      <c r="K5" s="117"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -23924,9 +27058,9 @@
       <c r="Q5" s="97"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="112"/>
-      <c r="U5" s="118"/>
-      <c r="V5" s="101"/>
+      <c r="T5" s="113"/>
+      <c r="U5" s="119"/>
+      <c r="V5" s="102"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -26626,17 +29760,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="104" t="s">
+      <c r="C60" s="105" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="105"/>
-      <c r="E60" s="105"/>
-      <c r="F60" s="105"/>
-      <c r="G60" s="105"/>
-      <c r="H60" s="105"/>
-      <c r="I60" s="105"/>
-      <c r="J60" s="105"/>
-      <c r="K60" s="106"/>
+      <c r="D60" s="106"/>
+      <c r="E60" s="106"/>
+      <c r="F60" s="106"/>
+      <c r="G60" s="106"/>
+      <c r="H60" s="106"/>
+      <c r="I60" s="106"/>
+      <c r="J60" s="106"/>
+      <c r="K60" s="107"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -26945,21 +30079,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="107" t="s">
+      <c r="I1" s="108" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="107"/>
-      <c r="K1" s="107"/>
-      <c r="L1" s="107"/>
-      <c r="M1" s="107"/>
-      <c r="N1" s="107"/>
-      <c r="O1" s="107"/>
-      <c r="P1" s="107"/>
-      <c r="Q1" s="107"/>
-      <c r="R1" s="107"/>
-      <c r="S1" s="107"/>
-      <c r="T1" s="107"/>
-      <c r="U1" s="107"/>
+      <c r="J1" s="108"/>
+      <c r="K1" s="108"/>
+      <c r="L1" s="108"/>
+      <c r="M1" s="108"/>
+      <c r="N1" s="108"/>
+      <c r="O1" s="108"/>
+      <c r="P1" s="108"/>
+      <c r="Q1" s="108"/>
+      <c r="R1" s="108"/>
+      <c r="S1" s="108"/>
+      <c r="T1" s="108"/>
+      <c r="U1" s="108"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -26971,17 +30105,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="108" t="s">
+      <c r="C4" s="109" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="108"/>
-      <c r="E4" s="108"/>
-      <c r="F4" s="108"/>
-      <c r="G4" s="108"/>
-      <c r="H4" s="108"/>
-      <c r="I4" s="108"/>
-      <c r="J4" s="109"/>
-      <c r="K4" s="110"/>
+      <c r="D4" s="109"/>
+      <c r="E4" s="109"/>
+      <c r="F4" s="109"/>
+      <c r="G4" s="109"/>
+      <c r="H4" s="109"/>
+      <c r="I4" s="109"/>
+      <c r="J4" s="110"/>
+      <c r="K4" s="111"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -27001,13 +30135,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="111" t="s">
+      <c r="T4" s="112" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="117" t="s">
+      <c r="U4" s="118" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="100" t="s">
+      <c r="V4" s="101" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -27047,10 +30181,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="115" t="s">
+      <c r="J5" s="116" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="116"/>
+      <c r="K5" s="117"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -27058,9 +30192,9 @@
       <c r="Q5" s="97"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="112"/>
-      <c r="U5" s="118"/>
-      <c r="V5" s="101"/>
+      <c r="T5" s="113"/>
+      <c r="U5" s="119"/>
+      <c r="V5" s="102"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -29750,17 +32884,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="104" t="s">
+      <c r="C60" s="105" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="105"/>
-      <c r="E60" s="105"/>
-      <c r="F60" s="105"/>
-      <c r="G60" s="105"/>
-      <c r="H60" s="105"/>
-      <c r="I60" s="105"/>
-      <c r="J60" s="105"/>
-      <c r="K60" s="106"/>
+      <c r="D60" s="106"/>
+      <c r="E60" s="106"/>
+      <c r="F60" s="106"/>
+      <c r="G60" s="106"/>
+      <c r="H60" s="106"/>
+      <c r="I60" s="106"/>
+      <c r="J60" s="106"/>
+      <c r="K60" s="107"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -30069,21 +33203,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="107" t="s">
+      <c r="I1" s="108" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="107"/>
-      <c r="K1" s="107"/>
-      <c r="L1" s="107"/>
-      <c r="M1" s="107"/>
-      <c r="N1" s="107"/>
-      <c r="O1" s="107"/>
-      <c r="P1" s="107"/>
-      <c r="Q1" s="107"/>
-      <c r="R1" s="107"/>
-      <c r="S1" s="107"/>
-      <c r="T1" s="107"/>
-      <c r="U1" s="107"/>
+      <c r="J1" s="108"/>
+      <c r="K1" s="108"/>
+      <c r="L1" s="108"/>
+      <c r="M1" s="108"/>
+      <c r="N1" s="108"/>
+      <c r="O1" s="108"/>
+      <c r="P1" s="108"/>
+      <c r="Q1" s="108"/>
+      <c r="R1" s="108"/>
+      <c r="S1" s="108"/>
+      <c r="T1" s="108"/>
+      <c r="U1" s="108"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -30095,17 +33229,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="108" t="s">
+      <c r="C4" s="109" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="108"/>
-      <c r="E4" s="108"/>
-      <c r="F4" s="108"/>
-      <c r="G4" s="108"/>
-      <c r="H4" s="108"/>
-      <c r="I4" s="108"/>
-      <c r="J4" s="109"/>
-      <c r="K4" s="110"/>
+      <c r="D4" s="109"/>
+      <c r="E4" s="109"/>
+      <c r="F4" s="109"/>
+      <c r="G4" s="109"/>
+      <c r="H4" s="109"/>
+      <c r="I4" s="109"/>
+      <c r="J4" s="110"/>
+      <c r="K4" s="111"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -30125,13 +33259,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="111" t="s">
+      <c r="T4" s="112" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="117" t="s">
+      <c r="U4" s="118" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="100" t="s">
+      <c r="V4" s="101" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -30171,10 +33305,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="115" t="s">
+      <c r="J5" s="116" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="116"/>
+      <c r="K5" s="117"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -30182,9 +33316,9 @@
       <c r="Q5" s="98"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="112"/>
-      <c r="U5" s="118"/>
-      <c r="V5" s="101"/>
+      <c r="T5" s="113"/>
+      <c r="U5" s="119"/>
+      <c r="V5" s="102"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -32899,17 +36033,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="104" t="s">
+      <c r="C60" s="105" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="105"/>
-      <c r="E60" s="105"/>
-      <c r="F60" s="105"/>
-      <c r="G60" s="105"/>
-      <c r="H60" s="105"/>
-      <c r="I60" s="105"/>
-      <c r="J60" s="105"/>
-      <c r="K60" s="106"/>
+      <c r="D60" s="106"/>
+      <c r="E60" s="106"/>
+      <c r="F60" s="106"/>
+      <c r="G60" s="106"/>
+      <c r="H60" s="106"/>
+      <c r="I60" s="106"/>
+      <c r="J60" s="106"/>
+      <c r="K60" s="107"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -33218,21 +36352,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="107" t="s">
+      <c r="I1" s="108" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="107"/>
-      <c r="K1" s="107"/>
-      <c r="L1" s="107"/>
-      <c r="M1" s="107"/>
-      <c r="N1" s="107"/>
-      <c r="O1" s="107"/>
-      <c r="P1" s="107"/>
-      <c r="Q1" s="107"/>
-      <c r="R1" s="107"/>
-      <c r="S1" s="107"/>
-      <c r="T1" s="107"/>
-      <c r="U1" s="107"/>
+      <c r="J1" s="108"/>
+      <c r="K1" s="108"/>
+      <c r="L1" s="108"/>
+      <c r="M1" s="108"/>
+      <c r="N1" s="108"/>
+      <c r="O1" s="108"/>
+      <c r="P1" s="108"/>
+      <c r="Q1" s="108"/>
+      <c r="R1" s="108"/>
+      <c r="S1" s="108"/>
+      <c r="T1" s="108"/>
+      <c r="U1" s="108"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -33244,17 +36378,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="108" t="s">
+      <c r="C4" s="109" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="108"/>
-      <c r="E4" s="108"/>
-      <c r="F4" s="108"/>
-      <c r="G4" s="108"/>
-      <c r="H4" s="108"/>
-      <c r="I4" s="108"/>
-      <c r="J4" s="109"/>
-      <c r="K4" s="110"/>
+      <c r="D4" s="109"/>
+      <c r="E4" s="109"/>
+      <c r="F4" s="109"/>
+      <c r="G4" s="109"/>
+      <c r="H4" s="109"/>
+      <c r="I4" s="109"/>
+      <c r="J4" s="110"/>
+      <c r="K4" s="111"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -33274,13 +36408,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="111" t="s">
+      <c r="T4" s="112" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="117" t="s">
+      <c r="U4" s="118" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="100" t="s">
+      <c r="V4" s="101" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -33320,10 +36454,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="115" t="s">
+      <c r="J5" s="116" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="116"/>
+      <c r="K5" s="117"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -33331,9 +36465,9 @@
       <c r="Q5" s="98"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="112"/>
-      <c r="U5" s="118"/>
-      <c r="V5" s="101"/>
+      <c r="T5" s="113"/>
+      <c r="U5" s="119"/>
+      <c r="V5" s="102"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -36038,17 +39172,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="104" t="s">
+      <c r="C60" s="105" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="105"/>
-      <c r="E60" s="105"/>
-      <c r="F60" s="105"/>
-      <c r="G60" s="105"/>
-      <c r="H60" s="105"/>
-      <c r="I60" s="105"/>
-      <c r="J60" s="105"/>
-      <c r="K60" s="106"/>
+      <c r="D60" s="106"/>
+      <c r="E60" s="106"/>
+      <c r="F60" s="106"/>
+      <c r="G60" s="106"/>
+      <c r="H60" s="106"/>
+      <c r="I60" s="106"/>
+      <c r="J60" s="106"/>
+      <c r="K60" s="107"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -36357,21 +39491,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="107" t="s">
+      <c r="I1" s="108" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="107"/>
-      <c r="K1" s="107"/>
-      <c r="L1" s="107"/>
-      <c r="M1" s="107"/>
-      <c r="N1" s="107"/>
-      <c r="O1" s="107"/>
-      <c r="P1" s="107"/>
-      <c r="Q1" s="107"/>
-      <c r="R1" s="107"/>
-      <c r="S1" s="107"/>
-      <c r="T1" s="107"/>
-      <c r="U1" s="107"/>
+      <c r="J1" s="108"/>
+      <c r="K1" s="108"/>
+      <c r="L1" s="108"/>
+      <c r="M1" s="108"/>
+      <c r="N1" s="108"/>
+      <c r="O1" s="108"/>
+      <c r="P1" s="108"/>
+      <c r="Q1" s="108"/>
+      <c r="R1" s="108"/>
+      <c r="S1" s="108"/>
+      <c r="T1" s="108"/>
+      <c r="U1" s="108"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -36383,17 +39517,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="108" t="s">
+      <c r="C4" s="109" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="108"/>
-      <c r="E4" s="108"/>
-      <c r="F4" s="108"/>
-      <c r="G4" s="108"/>
-      <c r="H4" s="108"/>
-      <c r="I4" s="108"/>
-      <c r="J4" s="109"/>
-      <c r="K4" s="110"/>
+      <c r="D4" s="109"/>
+      <c r="E4" s="109"/>
+      <c r="F4" s="109"/>
+      <c r="G4" s="109"/>
+      <c r="H4" s="109"/>
+      <c r="I4" s="109"/>
+      <c r="J4" s="110"/>
+      <c r="K4" s="111"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -36413,13 +39547,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="111" t="s">
+      <c r="T4" s="112" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="117" t="s">
+      <c r="U4" s="118" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="100" t="s">
+      <c r="V4" s="101" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -36459,10 +39593,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="115" t="s">
+      <c r="J5" s="116" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="116"/>
+      <c r="K5" s="117"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -36470,9 +39604,9 @@
       <c r="Q5" s="98"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="112"/>
-      <c r="U5" s="118"/>
-      <c r="V5" s="101"/>
+      <c r="T5" s="113"/>
+      <c r="U5" s="119"/>
+      <c r="V5" s="102"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -39174,17 +42308,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="104" t="s">
+      <c r="C60" s="105" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="105"/>
-      <c r="E60" s="105"/>
-      <c r="F60" s="105"/>
-      <c r="G60" s="105"/>
-      <c r="H60" s="105"/>
-      <c r="I60" s="105"/>
-      <c r="J60" s="105"/>
-      <c r="K60" s="106"/>
+      <c r="D60" s="106"/>
+      <c r="E60" s="106"/>
+      <c r="F60" s="106"/>
+      <c r="G60" s="106"/>
+      <c r="H60" s="106"/>
+      <c r="I60" s="106"/>
+      <c r="J60" s="106"/>
+      <c r="K60" s="107"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -39493,21 +42627,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="107" t="s">
+      <c r="I1" s="108" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="107"/>
-      <c r="K1" s="107"/>
-      <c r="L1" s="107"/>
-      <c r="M1" s="107"/>
-      <c r="N1" s="107"/>
-      <c r="O1" s="107"/>
-      <c r="P1" s="107"/>
-      <c r="Q1" s="107"/>
-      <c r="R1" s="107"/>
-      <c r="S1" s="107"/>
-      <c r="T1" s="107"/>
-      <c r="U1" s="107"/>
+      <c r="J1" s="108"/>
+      <c r="K1" s="108"/>
+      <c r="L1" s="108"/>
+      <c r="M1" s="108"/>
+      <c r="N1" s="108"/>
+      <c r="O1" s="108"/>
+      <c r="P1" s="108"/>
+      <c r="Q1" s="108"/>
+      <c r="R1" s="108"/>
+      <c r="S1" s="108"/>
+      <c r="T1" s="108"/>
+      <c r="U1" s="108"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -39519,17 +42653,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="108" t="s">
+      <c r="C4" s="109" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="108"/>
-      <c r="E4" s="108"/>
-      <c r="F4" s="108"/>
-      <c r="G4" s="108"/>
-      <c r="H4" s="108"/>
-      <c r="I4" s="108"/>
-      <c r="J4" s="109"/>
-      <c r="K4" s="110"/>
+      <c r="D4" s="109"/>
+      <c r="E4" s="109"/>
+      <c r="F4" s="109"/>
+      <c r="G4" s="109"/>
+      <c r="H4" s="109"/>
+      <c r="I4" s="109"/>
+      <c r="J4" s="110"/>
+      <c r="K4" s="111"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -39549,13 +42683,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="111" t="s">
+      <c r="T4" s="112" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="117" t="s">
+      <c r="U4" s="118" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="100" t="s">
+      <c r="V4" s="101" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -39595,10 +42729,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="115" t="s">
+      <c r="J5" s="116" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="116"/>
+      <c r="K5" s="117"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -39606,9 +42740,9 @@
       <c r="Q5" s="98"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="112"/>
-      <c r="U5" s="118"/>
-      <c r="V5" s="101"/>
+      <c r="T5" s="113"/>
+      <c r="U5" s="119"/>
+      <c r="V5" s="102"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -42320,17 +45454,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="104" t="s">
+      <c r="C60" s="105" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="105"/>
-      <c r="E60" s="105"/>
-      <c r="F60" s="105"/>
-      <c r="G60" s="105"/>
-      <c r="H60" s="105"/>
-      <c r="I60" s="105"/>
-      <c r="J60" s="105"/>
-      <c r="K60" s="106"/>
+      <c r="D60" s="106"/>
+      <c r="E60" s="106"/>
+      <c r="F60" s="106"/>
+      <c r="G60" s="106"/>
+      <c r="H60" s="106"/>
+      <c r="I60" s="106"/>
+      <c r="J60" s="106"/>
+      <c r="K60" s="107"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>

--- a/GBDS AUGUST FILES 2026/INVENTORY COUNT SHEET - AUGUST 2026.xlsx
+++ b/GBDS AUGUST FILES 2026/INVENTORY COUNT SHEET - AUGUST 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS AUGUST FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA2026D2-12F8-49FD-B39B-7DE611B9B015}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46E6EEEB-A172-4BB2-AC72-76B1FEA93262}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="4" activeTab="13" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="5" activeTab="14" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
   </bookViews>
   <sheets>
     <sheet name="SAMPLE" sheetId="32" r:id="rId1"/>
@@ -27,6 +27,7 @@
     <sheet name="08-15-2026" sheetId="79" r:id="rId12"/>
     <sheet name="08-17-2026" sheetId="80" r:id="rId13"/>
     <sheet name="08-18-2026" sheetId="81" r:id="rId14"/>
+    <sheet name="08-19-2026" sheetId="82" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'08-03-2026'!$A$1:$W$59</definedName>
@@ -42,6 +43,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="11">'08-15-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="12">'08-17-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="13">'08-18-2026'!$A$1:$W$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="14">'08-19-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">SAMPLE!$A$1:$W$85</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -60,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1176" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1260" uniqueCount="83">
   <si>
     <t>ROUTE 1</t>
   </si>
@@ -1296,7 +1298,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="120">
+  <cellXfs count="121">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1582,6 +1584,9 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="63" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2010,21 +2015,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="108" t="s">
+      <c r="I1" s="109" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="108"/>
-      <c r="K1" s="108"/>
-      <c r="L1" s="108"/>
-      <c r="M1" s="108"/>
-      <c r="N1" s="108"/>
-      <c r="O1" s="108"/>
-      <c r="P1" s="108"/>
-      <c r="Q1" s="108"/>
-      <c r="R1" s="108"/>
-      <c r="S1" s="108"/>
-      <c r="T1" s="108"/>
-      <c r="U1" s="108"/>
+      <c r="J1" s="109"/>
+      <c r="K1" s="109"/>
+      <c r="L1" s="109"/>
+      <c r="M1" s="109"/>
+      <c r="N1" s="109"/>
+      <c r="O1" s="109"/>
+      <c r="P1" s="109"/>
+      <c r="Q1" s="109"/>
+      <c r="R1" s="109"/>
+      <c r="S1" s="109"/>
+      <c r="T1" s="109"/>
+      <c r="U1" s="109"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -2036,17 +2041,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="109" t="s">
+      <c r="C4" s="110" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="109"/>
-      <c r="E4" s="109"/>
-      <c r="F4" s="109"/>
-      <c r="G4" s="109"/>
-      <c r="H4" s="109"/>
-      <c r="I4" s="109"/>
-      <c r="J4" s="110"/>
-      <c r="K4" s="111"/>
+      <c r="D4" s="110"/>
+      <c r="E4" s="110"/>
+      <c r="F4" s="110"/>
+      <c r="G4" s="110"/>
+      <c r="H4" s="110"/>
+      <c r="I4" s="110"/>
+      <c r="J4" s="111"/>
+      <c r="K4" s="112"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -2066,13 +2071,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="112" t="s">
+      <c r="T4" s="113" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="114" t="s">
+      <c r="U4" s="115" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="101" t="s">
+      <c r="V4" s="102" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -2112,10 +2117,10 @@
       <c r="I5" s="93" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="103" t="s">
+      <c r="J5" s="104" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="104"/>
+      <c r="K5" s="105"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -2123,9 +2128,9 @@
       <c r="Q5" s="89"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="113"/>
-      <c r="U5" s="115"/>
-      <c r="V5" s="102"/>
+      <c r="T5" s="114"/>
+      <c r="U5" s="116"/>
+      <c r="V5" s="103"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -4656,17 +4661,17 @@
       <c r="B62" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C62" s="105" t="s">
+      <c r="C62" s="106" t="s">
         <v>41</v>
       </c>
-      <c r="D62" s="106"/>
-      <c r="E62" s="106"/>
-      <c r="F62" s="106"/>
-      <c r="G62" s="106"/>
-      <c r="H62" s="106"/>
-      <c r="I62" s="106"/>
-      <c r="J62" s="106"/>
-      <c r="K62" s="107"/>
+      <c r="D62" s="107"/>
+      <c r="E62" s="107"/>
+      <c r="F62" s="107"/>
+      <c r="G62" s="107"/>
+      <c r="H62" s="107"/>
+      <c r="I62" s="107"/>
+      <c r="J62" s="107"/>
+      <c r="K62" s="108"/>
       <c r="U62" s="24" t="s">
         <v>51</v>
       </c>
@@ -4975,21 +4980,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="108" t="s">
+      <c r="I1" s="109" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="108"/>
-      <c r="K1" s="108"/>
-      <c r="L1" s="108"/>
-      <c r="M1" s="108"/>
-      <c r="N1" s="108"/>
-      <c r="O1" s="108"/>
-      <c r="P1" s="108"/>
-      <c r="Q1" s="108"/>
-      <c r="R1" s="108"/>
-      <c r="S1" s="108"/>
-      <c r="T1" s="108"/>
-      <c r="U1" s="108"/>
+      <c r="J1" s="109"/>
+      <c r="K1" s="109"/>
+      <c r="L1" s="109"/>
+      <c r="M1" s="109"/>
+      <c r="N1" s="109"/>
+      <c r="O1" s="109"/>
+      <c r="P1" s="109"/>
+      <c r="Q1" s="109"/>
+      <c r="R1" s="109"/>
+      <c r="S1" s="109"/>
+      <c r="T1" s="109"/>
+      <c r="U1" s="109"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -5001,17 +5006,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="109" t="s">
+      <c r="C4" s="110" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="109"/>
-      <c r="E4" s="109"/>
-      <c r="F4" s="109"/>
-      <c r="G4" s="109"/>
-      <c r="H4" s="109"/>
-      <c r="I4" s="109"/>
-      <c r="J4" s="110"/>
-      <c r="K4" s="111"/>
+      <c r="D4" s="110"/>
+      <c r="E4" s="110"/>
+      <c r="F4" s="110"/>
+      <c r="G4" s="110"/>
+      <c r="H4" s="110"/>
+      <c r="I4" s="110"/>
+      <c r="J4" s="111"/>
+      <c r="K4" s="112"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -5031,13 +5036,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="112" t="s">
+      <c r="T4" s="113" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="118" t="s">
+      <c r="U4" s="119" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="101" t="s">
+      <c r="V4" s="102" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -5077,10 +5082,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="116" t="s">
+      <c r="J5" s="117" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="117"/>
+      <c r="K5" s="118"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -5088,9 +5093,9 @@
       <c r="Q5" s="99"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="113"/>
-      <c r="U5" s="119"/>
-      <c r="V5" s="102"/>
+      <c r="T5" s="114"/>
+      <c r="U5" s="120"/>
+      <c r="V5" s="103"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -7801,17 +7806,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="105" t="s">
+      <c r="C60" s="106" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="106"/>
-      <c r="E60" s="106"/>
-      <c r="F60" s="106"/>
-      <c r="G60" s="106"/>
-      <c r="H60" s="106"/>
-      <c r="I60" s="106"/>
-      <c r="J60" s="106"/>
-      <c r="K60" s="107"/>
+      <c r="D60" s="107"/>
+      <c r="E60" s="107"/>
+      <c r="F60" s="107"/>
+      <c r="G60" s="107"/>
+      <c r="H60" s="107"/>
+      <c r="I60" s="107"/>
+      <c r="J60" s="107"/>
+      <c r="K60" s="108"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -8120,21 +8125,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="108" t="s">
+      <c r="I1" s="109" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="108"/>
-      <c r="K1" s="108"/>
-      <c r="L1" s="108"/>
-      <c r="M1" s="108"/>
-      <c r="N1" s="108"/>
-      <c r="O1" s="108"/>
-      <c r="P1" s="108"/>
-      <c r="Q1" s="108"/>
-      <c r="R1" s="108"/>
-      <c r="S1" s="108"/>
-      <c r="T1" s="108"/>
-      <c r="U1" s="108"/>
+      <c r="J1" s="109"/>
+      <c r="K1" s="109"/>
+      <c r="L1" s="109"/>
+      <c r="M1" s="109"/>
+      <c r="N1" s="109"/>
+      <c r="O1" s="109"/>
+      <c r="P1" s="109"/>
+      <c r="Q1" s="109"/>
+      <c r="R1" s="109"/>
+      <c r="S1" s="109"/>
+      <c r="T1" s="109"/>
+      <c r="U1" s="109"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -8146,17 +8151,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="109" t="s">
+      <c r="C4" s="110" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="109"/>
-      <c r="E4" s="109"/>
-      <c r="F4" s="109"/>
-      <c r="G4" s="109"/>
-      <c r="H4" s="109"/>
-      <c r="I4" s="109"/>
-      <c r="J4" s="110"/>
-      <c r="K4" s="111"/>
+      <c r="D4" s="110"/>
+      <c r="E4" s="110"/>
+      <c r="F4" s="110"/>
+      <c r="G4" s="110"/>
+      <c r="H4" s="110"/>
+      <c r="I4" s="110"/>
+      <c r="J4" s="111"/>
+      <c r="K4" s="112"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -8176,13 +8181,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="112" t="s">
+      <c r="T4" s="113" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="118" t="s">
+      <c r="U4" s="119" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="101" t="s">
+      <c r="V4" s="102" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -8222,10 +8227,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="116" t="s">
+      <c r="J5" s="117" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="117"/>
+      <c r="K5" s="118"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -8233,9 +8238,9 @@
       <c r="Q5" s="99"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="113"/>
-      <c r="U5" s="119"/>
-      <c r="V5" s="102"/>
+      <c r="T5" s="114"/>
+      <c r="U5" s="120"/>
+      <c r="V5" s="103"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -10948,17 +10953,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="105" t="s">
+      <c r="C60" s="106" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="106"/>
-      <c r="E60" s="106"/>
-      <c r="F60" s="106"/>
-      <c r="G60" s="106"/>
-      <c r="H60" s="106"/>
-      <c r="I60" s="106"/>
-      <c r="J60" s="106"/>
-      <c r="K60" s="107"/>
+      <c r="D60" s="107"/>
+      <c r="E60" s="107"/>
+      <c r="F60" s="107"/>
+      <c r="G60" s="107"/>
+      <c r="H60" s="107"/>
+      <c r="I60" s="107"/>
+      <c r="J60" s="107"/>
+      <c r="K60" s="108"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -11267,21 +11272,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="108" t="s">
+      <c r="I1" s="109" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="108"/>
-      <c r="K1" s="108"/>
-      <c r="L1" s="108"/>
-      <c r="M1" s="108"/>
-      <c r="N1" s="108"/>
-      <c r="O1" s="108"/>
-      <c r="P1" s="108"/>
-      <c r="Q1" s="108"/>
-      <c r="R1" s="108"/>
-      <c r="S1" s="108"/>
-      <c r="T1" s="108"/>
-      <c r="U1" s="108"/>
+      <c r="J1" s="109"/>
+      <c r="K1" s="109"/>
+      <c r="L1" s="109"/>
+      <c r="M1" s="109"/>
+      <c r="N1" s="109"/>
+      <c r="O1" s="109"/>
+      <c r="P1" s="109"/>
+      <c r="Q1" s="109"/>
+      <c r="R1" s="109"/>
+      <c r="S1" s="109"/>
+      <c r="T1" s="109"/>
+      <c r="U1" s="109"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -11293,17 +11298,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="109" t="s">
+      <c r="C4" s="110" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="109"/>
-      <c r="E4" s="109"/>
-      <c r="F4" s="109"/>
-      <c r="G4" s="109"/>
-      <c r="H4" s="109"/>
-      <c r="I4" s="109"/>
-      <c r="J4" s="110"/>
-      <c r="K4" s="111"/>
+      <c r="D4" s="110"/>
+      <c r="E4" s="110"/>
+      <c r="F4" s="110"/>
+      <c r="G4" s="110"/>
+      <c r="H4" s="110"/>
+      <c r="I4" s="110"/>
+      <c r="J4" s="111"/>
+      <c r="K4" s="112"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -11323,13 +11328,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="112" t="s">
+      <c r="T4" s="113" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="118" t="s">
+      <c r="U4" s="119" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="101" t="s">
+      <c r="V4" s="102" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -11369,10 +11374,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="116" t="s">
+      <c r="J5" s="117" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="117"/>
+      <c r="K5" s="118"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -11380,9 +11385,9 @@
       <c r="Q5" s="99"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="113"/>
-      <c r="U5" s="119"/>
-      <c r="V5" s="102"/>
+      <c r="T5" s="114"/>
+      <c r="U5" s="120"/>
+      <c r="V5" s="103"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -14084,17 +14089,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="105" t="s">
+      <c r="C60" s="106" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="106"/>
-      <c r="E60" s="106"/>
-      <c r="F60" s="106"/>
-      <c r="G60" s="106"/>
-      <c r="H60" s="106"/>
-      <c r="I60" s="106"/>
-      <c r="J60" s="106"/>
-      <c r="K60" s="107"/>
+      <c r="D60" s="107"/>
+      <c r="E60" s="107"/>
+      <c r="F60" s="107"/>
+      <c r="G60" s="107"/>
+      <c r="H60" s="107"/>
+      <c r="I60" s="107"/>
+      <c r="J60" s="107"/>
+      <c r="K60" s="108"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -14403,21 +14408,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="108" t="s">
+      <c r="I1" s="109" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="108"/>
-      <c r="K1" s="108"/>
-      <c r="L1" s="108"/>
-      <c r="M1" s="108"/>
-      <c r="N1" s="108"/>
-      <c r="O1" s="108"/>
-      <c r="P1" s="108"/>
-      <c r="Q1" s="108"/>
-      <c r="R1" s="108"/>
-      <c r="S1" s="108"/>
-      <c r="T1" s="108"/>
-      <c r="U1" s="108"/>
+      <c r="J1" s="109"/>
+      <c r="K1" s="109"/>
+      <c r="L1" s="109"/>
+      <c r="M1" s="109"/>
+      <c r="N1" s="109"/>
+      <c r="O1" s="109"/>
+      <c r="P1" s="109"/>
+      <c r="Q1" s="109"/>
+      <c r="R1" s="109"/>
+      <c r="S1" s="109"/>
+      <c r="T1" s="109"/>
+      <c r="U1" s="109"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -14429,17 +14434,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="109" t="s">
+      <c r="C4" s="110" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="109"/>
-      <c r="E4" s="109"/>
-      <c r="F4" s="109"/>
-      <c r="G4" s="109"/>
-      <c r="H4" s="109"/>
-      <c r="I4" s="109"/>
-      <c r="J4" s="110"/>
-      <c r="K4" s="111"/>
+      <c r="D4" s="110"/>
+      <c r="E4" s="110"/>
+      <c r="F4" s="110"/>
+      <c r="G4" s="110"/>
+      <c r="H4" s="110"/>
+      <c r="I4" s="110"/>
+      <c r="J4" s="111"/>
+      <c r="K4" s="112"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -14459,13 +14464,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="112" t="s">
+      <c r="T4" s="113" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="118" t="s">
+      <c r="U4" s="119" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="101" t="s">
+      <c r="V4" s="102" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -14505,10 +14510,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="116" t="s">
+      <c r="J5" s="117" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="117"/>
+      <c r="K5" s="118"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -14516,9 +14521,9 @@
       <c r="Q5" s="99"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="113"/>
-      <c r="U5" s="119"/>
-      <c r="V5" s="102"/>
+      <c r="T5" s="114"/>
+      <c r="U5" s="120"/>
+      <c r="V5" s="103"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -17219,17 +17224,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="105" t="s">
+      <c r="C60" s="106" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="106"/>
-      <c r="E60" s="106"/>
-      <c r="F60" s="106"/>
-      <c r="G60" s="106"/>
-      <c r="H60" s="106"/>
-      <c r="I60" s="106"/>
-      <c r="J60" s="106"/>
-      <c r="K60" s="107"/>
+      <c r="D60" s="107"/>
+      <c r="E60" s="107"/>
+      <c r="F60" s="107"/>
+      <c r="G60" s="107"/>
+      <c r="H60" s="107"/>
+      <c r="I60" s="107"/>
+      <c r="J60" s="107"/>
+      <c r="K60" s="108"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -17538,21 +17543,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="108" t="s">
+      <c r="I1" s="109" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="108"/>
-      <c r="K1" s="108"/>
-      <c r="L1" s="108"/>
-      <c r="M1" s="108"/>
-      <c r="N1" s="108"/>
-      <c r="O1" s="108"/>
-      <c r="P1" s="108"/>
-      <c r="Q1" s="108"/>
-      <c r="R1" s="108"/>
-      <c r="S1" s="108"/>
-      <c r="T1" s="108"/>
-      <c r="U1" s="108"/>
+      <c r="J1" s="109"/>
+      <c r="K1" s="109"/>
+      <c r="L1" s="109"/>
+      <c r="M1" s="109"/>
+      <c r="N1" s="109"/>
+      <c r="O1" s="109"/>
+      <c r="P1" s="109"/>
+      <c r="Q1" s="109"/>
+      <c r="R1" s="109"/>
+      <c r="S1" s="109"/>
+      <c r="T1" s="109"/>
+      <c r="U1" s="109"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -17564,17 +17569,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="109" t="s">
+      <c r="C4" s="110" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="109"/>
-      <c r="E4" s="109"/>
-      <c r="F4" s="109"/>
-      <c r="G4" s="109"/>
-      <c r="H4" s="109"/>
-      <c r="I4" s="109"/>
-      <c r="J4" s="110"/>
-      <c r="K4" s="111"/>
+      <c r="D4" s="110"/>
+      <c r="E4" s="110"/>
+      <c r="F4" s="110"/>
+      <c r="G4" s="110"/>
+      <c r="H4" s="110"/>
+      <c r="I4" s="110"/>
+      <c r="J4" s="111"/>
+      <c r="K4" s="112"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -17594,13 +17599,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="112" t="s">
+      <c r="T4" s="113" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="118" t="s">
+      <c r="U4" s="119" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="101" t="s">
+      <c r="V4" s="102" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -17640,10 +17645,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="116" t="s">
+      <c r="J5" s="117" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="117"/>
+      <c r="K5" s="118"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -17651,9 +17656,9 @@
       <c r="Q5" s="100"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="113"/>
-      <c r="U5" s="119"/>
-      <c r="V5" s="102"/>
+      <c r="T5" s="114"/>
+      <c r="U5" s="120"/>
+      <c r="V5" s="103"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -20348,17 +20353,3142 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="105" t="s">
+      <c r="C60" s="106" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="106"/>
-      <c r="E60" s="106"/>
-      <c r="F60" s="106"/>
-      <c r="G60" s="106"/>
-      <c r="H60" s="106"/>
-      <c r="I60" s="106"/>
-      <c r="J60" s="106"/>
-      <c r="K60" s="107"/>
+      <c r="D60" s="107"/>
+      <c r="E60" s="107"/>
+      <c r="F60" s="107"/>
+      <c r="G60" s="107"/>
+      <c r="H60" s="107"/>
+      <c r="I60" s="107"/>
+      <c r="J60" s="107"/>
+      <c r="K60" s="108"/>
+      <c r="U60" s="24" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B61" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="C61" s="19"/>
+      <c r="D61" s="19"/>
+      <c r="E61" s="19"/>
+      <c r="F61" s="19"/>
+      <c r="G61" s="19"/>
+      <c r="H61" s="19"/>
+      <c r="I61" s="19"/>
+      <c r="J61" s="45"/>
+      <c r="K61" s="20"/>
+      <c r="U61" s="7"/>
+    </row>
+    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B62" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+      <c r="J62" s="44"/>
+      <c r="K62" s="21"/>
+      <c r="U62" s="3"/>
+    </row>
+    <row r="63" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B63" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C63" s="22"/>
+      <c r="D63" s="22"/>
+      <c r="E63" s="22"/>
+      <c r="F63" s="22"/>
+      <c r="G63" s="22"/>
+      <c r="H63" s="22"/>
+      <c r="I63" s="22"/>
+      <c r="J63" s="46"/>
+      <c r="K63" s="23"/>
+      <c r="U63" s="8"/>
+    </row>
+    <row r="64" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B65" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="C65" s="19"/>
+      <c r="D65" s="19"/>
+      <c r="E65" s="19"/>
+      <c r="F65" s="19"/>
+      <c r="G65" s="19"/>
+      <c r="H65" s="19"/>
+      <c r="I65" s="19"/>
+      <c r="J65" s="45"/>
+      <c r="K65" s="20"/>
+      <c r="U65" s="7"/>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B66" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C66" s="1"/>
+      <c r="D66" s="1"/>
+      <c r="E66" s="1"/>
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="J66" s="44"/>
+      <c r="K66" s="21"/>
+      <c r="U66" s="3"/>
+    </row>
+    <row r="67" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B67" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C67" s="22"/>
+      <c r="D67" s="22"/>
+      <c r="E67" s="22"/>
+      <c r="F67" s="22"/>
+      <c r="G67" s="22"/>
+      <c r="H67" s="22"/>
+      <c r="I67" s="22"/>
+      <c r="J67" s="46"/>
+      <c r="K67" s="23"/>
+      <c r="U67" s="8"/>
+    </row>
+    <row r="68" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B69" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="C69" s="19"/>
+      <c r="D69" s="19"/>
+      <c r="E69" s="19"/>
+      <c r="F69" s="19"/>
+      <c r="G69" s="19"/>
+      <c r="H69" s="19"/>
+      <c r="I69" s="19"/>
+      <c r="J69" s="45"/>
+      <c r="K69" s="20"/>
+      <c r="U69" s="7"/>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B70" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="J70" s="44"/>
+      <c r="K70" s="21"/>
+      <c r="U70" s="3"/>
+    </row>
+    <row r="71" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B71" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C71" s="22"/>
+      <c r="D71" s="22"/>
+      <c r="E71" s="22"/>
+      <c r="F71" s="22"/>
+      <c r="G71" s="22"/>
+      <c r="H71" s="22"/>
+      <c r="I71" s="22"/>
+      <c r="J71" s="46"/>
+      <c r="K71" s="23"/>
+      <c r="U71" s="8"/>
+    </row>
+    <row r="72" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B73" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="C73" s="19"/>
+      <c r="D73" s="19"/>
+      <c r="E73" s="19"/>
+      <c r="F73" s="19"/>
+      <c r="G73" s="19"/>
+      <c r="H73" s="19"/>
+      <c r="I73" s="19"/>
+      <c r="J73" s="45"/>
+      <c r="K73" s="20"/>
+      <c r="U73" s="7"/>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B74" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C74" s="1"/>
+      <c r="D74" s="1"/>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1"/>
+      <c r="J74" s="44"/>
+      <c r="K74" s="21"/>
+      <c r="U74" s="3"/>
+    </row>
+    <row r="75" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B75" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C75" s="22"/>
+      <c r="D75" s="22"/>
+      <c r="E75" s="22"/>
+      <c r="F75" s="22"/>
+      <c r="G75" s="22"/>
+      <c r="H75" s="22"/>
+      <c r="I75" s="22"/>
+      <c r="J75" s="46"/>
+      <c r="K75" s="23"/>
+      <c r="U75" s="8"/>
+    </row>
+    <row r="76" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B77" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="C77" s="19"/>
+      <c r="D77" s="19"/>
+      <c r="E77" s="19"/>
+      <c r="F77" s="19"/>
+      <c r="G77" s="19"/>
+      <c r="H77" s="19"/>
+      <c r="I77" s="19"/>
+      <c r="J77" s="45"/>
+      <c r="K77" s="20"/>
+      <c r="U77" s="7"/>
+    </row>
+    <row r="78" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B78" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C78" s="1"/>
+      <c r="D78" s="1"/>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+      <c r="J78" s="44"/>
+      <c r="K78" s="21"/>
+      <c r="U78" s="3"/>
+    </row>
+    <row r="79" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B79" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C79" s="22"/>
+      <c r="D79" s="22"/>
+      <c r="E79" s="22"/>
+      <c r="F79" s="22"/>
+      <c r="G79" s="22"/>
+      <c r="H79" s="22"/>
+      <c r="I79" s="22"/>
+      <c r="J79" s="46"/>
+      <c r="K79" s="23"/>
+      <c r="U79" s="8"/>
+    </row>
+    <row r="80" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="81" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B81" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="C81" s="17"/>
+      <c r="D81" s="17"/>
+      <c r="E81" s="17"/>
+      <c r="F81" s="17"/>
+      <c r="G81" s="17"/>
+      <c r="H81" s="17"/>
+      <c r="I81" s="17"/>
+      <c r="J81" s="47"/>
+      <c r="K81" s="18"/>
+      <c r="U81" s="16"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="C60:K60"/>
+    <mergeCell ref="I1:U1"/>
+    <mergeCell ref="C4:K4"/>
+    <mergeCell ref="T4:T5"/>
+    <mergeCell ref="U4:U5"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
+  <pageSetup paperSize="14" scale="70" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="24" max="80" man="1"/>
+  </colBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6785A562-FC08-4F6D-8F24-EB56A0E8599E}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BB81"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="28" customWidth="1"/>
+    <col min="3" max="6" width="10" style="9" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" style="9" customWidth="1"/>
+    <col min="8" max="8" width="7.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.85546875" style="9" customWidth="1"/>
+    <col min="11" max="11" width="7.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.42578125" style="9" customWidth="1"/>
+    <col min="13" max="13" width="10" style="9" customWidth="1"/>
+    <col min="14" max="14" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" style="9" customWidth="1"/>
+    <col min="16" max="16" width="5.5703125" style="9" customWidth="1"/>
+    <col min="17" max="17" width="10" style="9" customWidth="1"/>
+    <col min="18" max="18" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="1.42578125" style="9" customWidth="1"/>
+    <col min="20" max="20" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="9" customWidth="1"/>
+    <col min="22" max="22" width="19.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="23" max="49" width="7.28515625" style="9" customWidth="1"/>
+    <col min="50" max="50" width="1.5703125" style="9" customWidth="1"/>
+    <col min="51" max="51" width="9.42578125" style="9" customWidth="1"/>
+    <col min="52" max="52" width="1.28515625" style="9" customWidth="1"/>
+    <col min="53" max="53" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="10.28515625" style="9" bestFit="1" customWidth="1"/>
+    <col min="55" max="16384" width="9.140625" style="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="109" t="s">
+        <v>43</v>
+      </c>
+      <c r="J1" s="109"/>
+      <c r="K1" s="109"/>
+      <c r="L1" s="109"/>
+      <c r="M1" s="109"/>
+      <c r="N1" s="109"/>
+      <c r="O1" s="109"/>
+      <c r="P1" s="109"/>
+      <c r="Q1" s="109"/>
+      <c r="R1" s="109"/>
+      <c r="S1" s="109"/>
+      <c r="T1" s="109"/>
+      <c r="U1" s="109"/>
+    </row>
+    <row r="2" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="B2" s="28" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B4" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="110" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="110"/>
+      <c r="E4" s="110"/>
+      <c r="F4" s="110"/>
+      <c r="G4" s="110"/>
+      <c r="H4" s="110"/>
+      <c r="I4" s="110"/>
+      <c r="J4" s="111"/>
+      <c r="K4" s="112"/>
+      <c r="M4" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="N4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="O4" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="P4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q4" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="R4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="S4" s="9"/>
+      <c r="T4" s="113" t="s">
+        <v>68</v>
+      </c>
+      <c r="U4" s="119" t="s">
+        <v>67</v>
+      </c>
+      <c r="V4" s="102" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF4" s="11"/>
+      <c r="AG4" s="11"/>
+      <c r="AH4" s="11"/>
+      <c r="AI4" s="11"/>
+      <c r="AJ4" s="11"/>
+      <c r="AK4" s="11"/>
+      <c r="AL4" s="11"/>
+      <c r="AM4" s="11"/>
+      <c r="AN4" s="11"/>
+      <c r="AO4" s="11"/>
+      <c r="AP4" s="11"/>
+      <c r="AQ4" s="11"/>
+      <c r="AR4" s="11"/>
+      <c r="AS4" s="11"/>
+      <c r="AT4" s="11"/>
+      <c r="AU4" s="11"/>
+      <c r="AV4" s="11"/>
+      <c r="AW4" s="11"/>
+      <c r="AX4" s="11"/>
+      <c r="AY4" s="11"/>
+      <c r="AZ4" s="11"/>
+      <c r="BA4" s="11"/>
+      <c r="BB4" s="11"/>
+    </row>
+    <row r="5" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="37"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40" t="s">
+        <v>64</v>
+      </c>
+      <c r="I5" s="40" t="s">
+        <v>60</v>
+      </c>
+      <c r="J5" s="117" t="s">
+        <v>65</v>
+      </c>
+      <c r="K5" s="118"/>
+      <c r="M5" s="37"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="40"/>
+      <c r="P5" s="101"/>
+      <c r="Q5" s="101"/>
+      <c r="R5" s="38"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="114"/>
+      <c r="U5" s="120"/>
+      <c r="V5" s="103"/>
+      <c r="AF5" s="11"/>
+      <c r="AG5" s="11"/>
+      <c r="AH5" s="11"/>
+      <c r="AI5" s="11"/>
+      <c r="AJ5" s="11"/>
+      <c r="AK5" s="11"/>
+      <c r="AL5" s="11"/>
+      <c r="AM5" s="11"/>
+      <c r="AN5" s="11"/>
+      <c r="AO5" s="11"/>
+      <c r="AP5" s="11"/>
+      <c r="AQ5" s="11"/>
+      <c r="AR5" s="11"/>
+      <c r="AS5" s="11"/>
+      <c r="AT5" s="11"/>
+      <c r="AU5" s="11"/>
+      <c r="AV5" s="11"/>
+      <c r="AW5" s="11"/>
+      <c r="AX5" s="11"/>
+      <c r="AY5" s="11"/>
+      <c r="AZ5" s="11"/>
+      <c r="BA5" s="11"/>
+      <c r="BB5" s="11"/>
+    </row>
+    <row r="6" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="37"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="101"/>
+      <c r="K6" s="38"/>
+      <c r="M6" s="37"/>
+      <c r="N6" s="49"/>
+      <c r="O6" s="40"/>
+      <c r="P6" s="101"/>
+      <c r="Q6" s="101"/>
+      <c r="R6" s="38"/>
+      <c r="S6" s="9"/>
+      <c r="T6" s="39"/>
+      <c r="U6" s="39"/>
+      <c r="V6" s="39"/>
+      <c r="AF6" s="11"/>
+      <c r="AG6" s="11"/>
+      <c r="AH6" s="11"/>
+      <c r="AI6" s="11"/>
+      <c r="AJ6" s="11"/>
+      <c r="AK6" s="11"/>
+      <c r="AL6" s="11"/>
+      <c r="AM6" s="11"/>
+      <c r="AN6" s="11"/>
+      <c r="AO6" s="11"/>
+      <c r="AP6" s="11"/>
+      <c r="AQ6" s="11"/>
+      <c r="AR6" s="11"/>
+      <c r="AS6" s="11"/>
+      <c r="AT6" s="11"/>
+      <c r="AU6" s="11"/>
+      <c r="AV6" s="11"/>
+      <c r="AW6" s="11"/>
+      <c r="AX6" s="11"/>
+      <c r="AY6" s="11"/>
+      <c r="AZ6" s="11"/>
+      <c r="BA6" s="11"/>
+      <c r="BB6" s="11"/>
+    </row>
+    <row r="7" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A7" s="27">
+        <v>1</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="52">
+        <v>31</v>
+      </c>
+      <c r="D7" s="52"/>
+      <c r="E7" s="52"/>
+      <c r="F7" s="52"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="52"/>
+      <c r="I7" s="52">
+        <v>3</v>
+      </c>
+      <c r="J7" s="53"/>
+      <c r="K7" s="54">
+        <v>6</v>
+      </c>
+      <c r="L7" s="55"/>
+      <c r="M7" s="56"/>
+      <c r="N7" s="57"/>
+      <c r="O7" s="52">
+        <v>1</v>
+      </c>
+      <c r="P7" s="53"/>
+      <c r="Q7" s="53"/>
+      <c r="R7" s="54"/>
+      <c r="S7" s="55"/>
+      <c r="T7" s="58">
+        <f>H7+I7+J7+K7+N7+P7+R7</f>
+        <v>9</v>
+      </c>
+      <c r="U7" s="58">
+        <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
+        <v>777</v>
+      </c>
+      <c r="V7" s="58">
+        <f>U7/24</f>
+        <v>32.375</v>
+      </c>
+      <c r="W7" s="50"/>
+      <c r="AF7" s="12"/>
+      <c r="AG7" s="12"/>
+      <c r="AH7" s="12"/>
+      <c r="AI7" s="12"/>
+      <c r="AJ7" s="12"/>
+      <c r="AK7" s="12"/>
+      <c r="AL7" s="12"/>
+      <c r="AM7" s="12"/>
+      <c r="AN7" s="12"/>
+      <c r="AO7" s="12"/>
+      <c r="AP7" s="12"/>
+      <c r="AQ7" s="12"/>
+      <c r="AR7" s="12"/>
+      <c r="AS7" s="12"/>
+      <c r="AT7" s="12"/>
+      <c r="AU7" s="12"/>
+      <c r="AV7" s="12"/>
+      <c r="AW7" s="12"/>
+      <c r="AX7" s="12"/>
+      <c r="AY7" s="12"/>
+      <c r="AZ7" s="12"/>
+      <c r="BA7" s="12"/>
+      <c r="BB7" s="12"/>
+    </row>
+    <row r="8" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="27">
+        <f>A7+1</f>
+        <v>2</v>
+      </c>
+      <c r="B8" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="59">
+        <f>40+37</f>
+        <v>77</v>
+      </c>
+      <c r="D8" s="59"/>
+      <c r="E8" s="59"/>
+      <c r="F8" s="59"/>
+      <c r="G8" s="59"/>
+      <c r="H8" s="59"/>
+      <c r="I8" s="59"/>
+      <c r="J8" s="60"/>
+      <c r="K8" s="61"/>
+      <c r="L8" s="62"/>
+      <c r="M8" s="63"/>
+      <c r="N8" s="64"/>
+      <c r="O8" s="65">
+        <v>1</v>
+      </c>
+      <c r="P8" s="66">
+        <v>12</v>
+      </c>
+      <c r="Q8" s="66">
+        <v>2</v>
+      </c>
+      <c r="R8" s="67"/>
+      <c r="S8" s="62"/>
+      <c r="T8" s="68">
+        <f t="shared" ref="T8:T41" si="0">H8+I8+J8+K8+N8+P8+R8</f>
+        <v>12</v>
+      </c>
+      <c r="U8" s="69">
+        <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
+        <v>1932</v>
+      </c>
+      <c r="V8" s="69">
+        <f>U8/24</f>
+        <v>80.5</v>
+      </c>
+      <c r="W8" s="50"/>
+      <c r="AF8" s="12"/>
+      <c r="AG8" s="12"/>
+      <c r="AH8" s="12"/>
+      <c r="AI8" s="12"/>
+      <c r="AJ8" s="12"/>
+      <c r="AK8" s="12"/>
+      <c r="AL8" s="12"/>
+      <c r="AM8" s="12"/>
+      <c r="AN8" s="12"/>
+      <c r="AO8" s="12"/>
+      <c r="AP8" s="12"/>
+      <c r="AQ8" s="12"/>
+      <c r="AR8" s="12"/>
+      <c r="AS8" s="12"/>
+      <c r="AT8" s="12"/>
+      <c r="AU8" s="12"/>
+      <c r="AV8" s="12"/>
+      <c r="AW8" s="12"/>
+      <c r="AX8" s="12"/>
+      <c r="AY8" s="12"/>
+      <c r="AZ8" s="12"/>
+      <c r="BA8" s="12"/>
+      <c r="BB8" s="12"/>
+    </row>
+    <row r="9" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A9" s="27">
+        <f t="shared" ref="A9:A57" si="1">A8+1</f>
+        <v>3</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="70">
+        <f>56+30</f>
+        <v>86</v>
+      </c>
+      <c r="D9" s="70"/>
+      <c r="E9" s="70"/>
+      <c r="F9" s="70"/>
+      <c r="G9" s="70"/>
+      <c r="H9" s="70"/>
+      <c r="I9" s="70"/>
+      <c r="J9" s="71"/>
+      <c r="K9" s="72"/>
+      <c r="L9" s="55"/>
+      <c r="M9" s="73">
+        <v>1</v>
+      </c>
+      <c r="N9" s="74"/>
+      <c r="O9" s="70"/>
+      <c r="P9" s="71"/>
+      <c r="Q9" s="71"/>
+      <c r="R9" s="72"/>
+      <c r="S9" s="55"/>
+      <c r="T9" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U9" s="76">
+        <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
+        <v>2088</v>
+      </c>
+      <c r="V9" s="76">
+        <f t="shared" ref="V9:V11" si="3">U9/24</f>
+        <v>87</v>
+      </c>
+      <c r="W9" s="50"/>
+      <c r="AF9" s="12"/>
+      <c r="AG9" s="12"/>
+      <c r="AH9" s="12"/>
+      <c r="AI9" s="12"/>
+      <c r="AJ9" s="12"/>
+      <c r="AK9" s="12"/>
+      <c r="AL9" s="12"/>
+      <c r="AM9" s="12"/>
+      <c r="AN9" s="12"/>
+      <c r="AO9" s="12"/>
+      <c r="AP9" s="12"/>
+      <c r="AQ9" s="12"/>
+      <c r="AR9" s="12"/>
+      <c r="AS9" s="12"/>
+      <c r="AT9" s="12"/>
+      <c r="AU9" s="12"/>
+      <c r="AV9" s="12"/>
+      <c r="AW9" s="12"/>
+      <c r="AX9" s="12"/>
+      <c r="AY9" s="12"/>
+      <c r="AZ9" s="12"/>
+      <c r="BA9" s="12"/>
+      <c r="BB9" s="12"/>
+    </row>
+    <row r="10" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A10" s="27">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="70">
+        <f>25+10</f>
+        <v>35</v>
+      </c>
+      <c r="D10" s="70"/>
+      <c r="E10" s="70"/>
+      <c r="F10" s="70"/>
+      <c r="G10" s="70"/>
+      <c r="H10" s="70"/>
+      <c r="I10" s="70"/>
+      <c r="J10" s="71"/>
+      <c r="K10" s="72"/>
+      <c r="L10" s="55"/>
+      <c r="M10" s="73">
+        <v>1</v>
+      </c>
+      <c r="N10" s="74"/>
+      <c r="O10" s="70"/>
+      <c r="P10" s="71"/>
+      <c r="Q10" s="71"/>
+      <c r="R10" s="72"/>
+      <c r="S10" s="55"/>
+      <c r="T10" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U10" s="58">
+        <f t="shared" si="2"/>
+        <v>864</v>
+      </c>
+      <c r="V10" s="58">
+        <f t="shared" si="3"/>
+        <v>36</v>
+      </c>
+      <c r="W10" s="50"/>
+      <c r="AF10" s="12"/>
+      <c r="AG10" s="12"/>
+      <c r="AH10" s="12"/>
+      <c r="AI10" s="12"/>
+      <c r="AJ10" s="12"/>
+      <c r="AK10" s="12"/>
+      <c r="AL10" s="12"/>
+      <c r="AM10" s="12"/>
+      <c r="AN10" s="12"/>
+      <c r="AO10" s="12"/>
+      <c r="AP10" s="12"/>
+      <c r="AQ10" s="12"/>
+      <c r="AR10" s="12"/>
+      <c r="AS10" s="12"/>
+      <c r="AT10" s="12"/>
+      <c r="AU10" s="12"/>
+      <c r="AV10" s="12"/>
+      <c r="AW10" s="12"/>
+      <c r="AX10" s="12"/>
+      <c r="AY10" s="12"/>
+      <c r="AZ10" s="12"/>
+      <c r="BA10" s="12"/>
+      <c r="BB10" s="12"/>
+    </row>
+    <row r="11" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A11" s="27">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="70">
+        <v>9</v>
+      </c>
+      <c r="D11" s="70"/>
+      <c r="E11" s="70"/>
+      <c r="F11" s="70"/>
+      <c r="G11" s="70"/>
+      <c r="H11" s="70"/>
+      <c r="I11" s="70"/>
+      <c r="J11" s="71"/>
+      <c r="K11" s="72">
+        <v>2</v>
+      </c>
+      <c r="L11" s="55"/>
+      <c r="M11" s="73"/>
+      <c r="N11" s="74"/>
+      <c r="O11" s="70"/>
+      <c r="P11" s="71"/>
+      <c r="Q11" s="71"/>
+      <c r="R11" s="72"/>
+      <c r="S11" s="55"/>
+      <c r="T11" s="58">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="U11" s="58">
+        <f t="shared" si="2"/>
+        <v>218</v>
+      </c>
+      <c r="V11" s="58">
+        <f t="shared" si="3"/>
+        <v>9.0833333333333339</v>
+      </c>
+      <c r="AF11" s="12"/>
+      <c r="AG11" s="12"/>
+      <c r="AH11" s="12"/>
+      <c r="AI11" s="12"/>
+      <c r="AJ11" s="12"/>
+      <c r="AK11" s="12"/>
+      <c r="AL11" s="12"/>
+      <c r="AM11" s="12"/>
+      <c r="AN11" s="12"/>
+      <c r="AO11" s="12"/>
+      <c r="AP11" s="12"/>
+      <c r="AQ11" s="12"/>
+      <c r="AR11" s="12"/>
+      <c r="AS11" s="12"/>
+      <c r="AT11" s="12"/>
+      <c r="AU11" s="12"/>
+      <c r="AV11" s="12"/>
+      <c r="AW11" s="12"/>
+      <c r="AX11" s="12"/>
+      <c r="AY11" s="12"/>
+      <c r="AZ11" s="12"/>
+      <c r="BA11" s="12"/>
+      <c r="BB11" s="12"/>
+    </row>
+    <row r="12" spans="1:54" s="13" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="27">
+        <v>7</v>
+      </c>
+      <c r="B12" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="59">
+        <f>1224+53+720+69+1080+29</f>
+        <v>3175</v>
+      </c>
+      <c r="D12" s="59"/>
+      <c r="E12" s="59"/>
+      <c r="F12" s="59"/>
+      <c r="G12" s="59"/>
+      <c r="H12" s="59"/>
+      <c r="I12" s="59"/>
+      <c r="J12" s="60"/>
+      <c r="K12" s="61"/>
+      <c r="L12" s="62"/>
+      <c r="M12" s="63">
+        <v>15</v>
+      </c>
+      <c r="N12" s="64"/>
+      <c r="O12" s="65">
+        <v>12</v>
+      </c>
+      <c r="P12" s="66">
+        <v>21</v>
+      </c>
+      <c r="Q12" s="66">
+        <v>15</v>
+      </c>
+      <c r="R12" s="67">
+        <v>5</v>
+      </c>
+      <c r="S12" s="62"/>
+      <c r="T12" s="69">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="U12" s="69">
+        <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
+        <v>77234</v>
+      </c>
+      <c r="V12" s="69">
+        <f>U12/24</f>
+        <v>3218.0833333333335</v>
+      </c>
+      <c r="W12" s="9"/>
+      <c r="X12" s="9"/>
+      <c r="Y12" s="9"/>
+      <c r="Z12" s="9"/>
+      <c r="AA12" s="9"/>
+      <c r="AB12" s="9"/>
+      <c r="AC12" s="9"/>
+      <c r="AD12" s="9"/>
+      <c r="AE12" s="9"/>
+      <c r="AF12" s="12"/>
+      <c r="AG12" s="12"/>
+      <c r="AH12" s="12"/>
+      <c r="AI12" s="12"/>
+      <c r="AJ12" s="12"/>
+      <c r="AK12" s="12"/>
+      <c r="AL12" s="12"/>
+      <c r="AM12" s="12"/>
+      <c r="AN12" s="12"/>
+      <c r="AO12" s="12"/>
+      <c r="AP12" s="12"/>
+      <c r="AQ12" s="12"/>
+      <c r="AR12" s="12"/>
+      <c r="AS12" s="12"/>
+      <c r="AT12" s="12"/>
+      <c r="AU12" s="12"/>
+      <c r="AV12" s="12"/>
+      <c r="AW12" s="12"/>
+      <c r="AX12" s="12"/>
+      <c r="AY12" s="12"/>
+      <c r="AZ12" s="12"/>
+      <c r="BA12" s="12"/>
+      <c r="BB12" s="12"/>
+    </row>
+    <row r="13" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A13" s="27">
+        <v>11</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="70">
+        <v>2</v>
+      </c>
+      <c r="D13" s="70"/>
+      <c r="E13" s="70"/>
+      <c r="F13" s="70"/>
+      <c r="G13" s="70"/>
+      <c r="H13" s="70">
+        <v>16</v>
+      </c>
+      <c r="I13" s="70"/>
+      <c r="J13" s="71"/>
+      <c r="K13" s="72"/>
+      <c r="L13" s="55"/>
+      <c r="M13" s="73"/>
+      <c r="N13" s="74"/>
+      <c r="O13" s="70"/>
+      <c r="P13" s="71"/>
+      <c r="Q13" s="71"/>
+      <c r="R13" s="72"/>
+      <c r="S13" s="55"/>
+      <c r="T13" s="76">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="U13" s="76">
+        <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
+        <v>64</v>
+      </c>
+      <c r="V13" s="76">
+        <f>U13/24</f>
+        <v>2.6666666666666665</v>
+      </c>
+      <c r="AF13" s="12"/>
+      <c r="AG13" s="12"/>
+      <c r="AH13" s="12"/>
+      <c r="AI13" s="12"/>
+      <c r="AJ13" s="12"/>
+      <c r="AK13" s="12"/>
+      <c r="AL13" s="12"/>
+      <c r="AM13" s="12"/>
+      <c r="AN13" s="12"/>
+      <c r="AO13" s="12"/>
+      <c r="AP13" s="12"/>
+      <c r="AQ13" s="12"/>
+      <c r="AR13" s="12"/>
+      <c r="AS13" s="12"/>
+      <c r="AT13" s="12"/>
+      <c r="AU13" s="12"/>
+      <c r="AV13" s="12"/>
+      <c r="AW13" s="12"/>
+      <c r="AX13" s="12"/>
+      <c r="AY13" s="12"/>
+      <c r="AZ13" s="12"/>
+      <c r="BA13" s="12"/>
+      <c r="BB13" s="12"/>
+    </row>
+    <row r="14" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A14" s="27">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="70">
+        <v>2</v>
+      </c>
+      <c r="D14" s="70"/>
+      <c r="E14" s="70"/>
+      <c r="F14" s="70"/>
+      <c r="G14" s="70"/>
+      <c r="H14" s="70"/>
+      <c r="I14" s="70"/>
+      <c r="J14" s="71"/>
+      <c r="K14" s="72"/>
+      <c r="L14" s="55"/>
+      <c r="M14" s="73"/>
+      <c r="N14" s="74"/>
+      <c r="O14" s="70"/>
+      <c r="P14" s="71"/>
+      <c r="Q14" s="71"/>
+      <c r="R14" s="72"/>
+      <c r="S14" s="55"/>
+      <c r="T14" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U14" s="75">
+        <f t="shared" ref="U14:U36" si="4">C14*24+M14*24+O14*24+Q14*24+T14</f>
+        <v>48</v>
+      </c>
+      <c r="V14" s="75">
+        <f t="shared" ref="V14:V36" si="5">U14/24</f>
+        <v>2</v>
+      </c>
+      <c r="AF14" s="12"/>
+      <c r="AG14" s="12"/>
+      <c r="AH14" s="12"/>
+      <c r="AI14" s="12"/>
+      <c r="AJ14" s="12"/>
+      <c r="AK14" s="12"/>
+      <c r="AL14" s="12"/>
+      <c r="AM14" s="12"/>
+      <c r="AN14" s="12"/>
+      <c r="AO14" s="12"/>
+      <c r="AP14" s="12"/>
+      <c r="AQ14" s="12"/>
+      <c r="AR14" s="12"/>
+      <c r="AS14" s="12"/>
+      <c r="AT14" s="12"/>
+      <c r="AU14" s="12"/>
+      <c r="AV14" s="12"/>
+      <c r="AW14" s="12"/>
+      <c r="AX14" s="12"/>
+      <c r="AY14" s="12"/>
+      <c r="AZ14" s="12"/>
+      <c r="BA14" s="12"/>
+      <c r="BB14" s="12"/>
+    </row>
+    <row r="15" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A15" s="27">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="70"/>
+      <c r="D15" s="70"/>
+      <c r="E15" s="70"/>
+      <c r="F15" s="70"/>
+      <c r="G15" s="70"/>
+      <c r="H15" s="70"/>
+      <c r="I15" s="70"/>
+      <c r="J15" s="71"/>
+      <c r="K15" s="72"/>
+      <c r="L15" s="55"/>
+      <c r="M15" s="73"/>
+      <c r="N15" s="74"/>
+      <c r="O15" s="70"/>
+      <c r="P15" s="71"/>
+      <c r="Q15" s="71"/>
+      <c r="R15" s="72"/>
+      <c r="S15" s="55"/>
+      <c r="T15" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U15" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF15" s="12"/>
+      <c r="AG15" s="12"/>
+      <c r="AH15" s="12"/>
+      <c r="AI15" s="12"/>
+      <c r="AJ15" s="12"/>
+      <c r="AK15" s="12"/>
+      <c r="AL15" s="12"/>
+      <c r="AM15" s="12"/>
+      <c r="AN15" s="12"/>
+      <c r="AO15" s="12"/>
+      <c r="AP15" s="12"/>
+      <c r="AQ15" s="12"/>
+      <c r="AR15" s="12"/>
+      <c r="AS15" s="12"/>
+      <c r="AT15" s="12"/>
+      <c r="AU15" s="12"/>
+      <c r="AV15" s="12"/>
+      <c r="AW15" s="12"/>
+      <c r="AX15" s="12"/>
+      <c r="AY15" s="12"/>
+      <c r="AZ15" s="12"/>
+      <c r="BA15" s="12"/>
+      <c r="BB15" s="12"/>
+    </row>
+    <row r="16" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A16" s="27">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="70"/>
+      <c r="D16" s="70"/>
+      <c r="E16" s="70"/>
+      <c r="F16" s="70"/>
+      <c r="G16" s="70"/>
+      <c r="H16" s="70"/>
+      <c r="I16" s="70"/>
+      <c r="J16" s="71"/>
+      <c r="K16" s="72"/>
+      <c r="L16" s="55"/>
+      <c r="M16" s="73"/>
+      <c r="N16" s="74"/>
+      <c r="O16" s="70"/>
+      <c r="P16" s="71"/>
+      <c r="Q16" s="71"/>
+      <c r="R16" s="72"/>
+      <c r="S16" s="55"/>
+      <c r="T16" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U16" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF16" s="12"/>
+      <c r="AG16" s="12"/>
+      <c r="AH16" s="12"/>
+      <c r="AI16" s="12"/>
+      <c r="AJ16" s="12"/>
+      <c r="AK16" s="12"/>
+      <c r="AL16" s="12"/>
+      <c r="AM16" s="12"/>
+      <c r="AN16" s="12"/>
+      <c r="AO16" s="12"/>
+      <c r="AP16" s="12"/>
+      <c r="AQ16" s="12"/>
+      <c r="AR16" s="12"/>
+      <c r="AS16" s="12"/>
+      <c r="AT16" s="12"/>
+      <c r="AU16" s="12"/>
+      <c r="AV16" s="12"/>
+      <c r="AW16" s="12"/>
+      <c r="AX16" s="12"/>
+      <c r="AY16" s="12"/>
+      <c r="AZ16" s="12"/>
+      <c r="BA16" s="12"/>
+      <c r="BB16" s="12"/>
+    </row>
+    <row r="17" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A17" s="27">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="70"/>
+      <c r="D17" s="70"/>
+      <c r="E17" s="70"/>
+      <c r="F17" s="70"/>
+      <c r="G17" s="70"/>
+      <c r="H17" s="70">
+        <f>3*24</f>
+        <v>72</v>
+      </c>
+      <c r="I17" s="70"/>
+      <c r="J17" s="71"/>
+      <c r="K17" s="72"/>
+      <c r="L17" s="55"/>
+      <c r="M17" s="73"/>
+      <c r="N17" s="74"/>
+      <c r="O17" s="70"/>
+      <c r="P17" s="71"/>
+      <c r="Q17" s="71"/>
+      <c r="R17" s="72"/>
+      <c r="S17" s="55"/>
+      <c r="T17" s="58">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="U17" s="75">
+        <f t="shared" si="4"/>
+        <v>72</v>
+      </c>
+      <c r="V17" s="75">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="AF17" s="12"/>
+      <c r="AG17" s="12"/>
+      <c r="AH17" s="12"/>
+      <c r="AI17" s="12"/>
+      <c r="AJ17" s="12"/>
+      <c r="AK17" s="12"/>
+      <c r="AL17" s="12"/>
+      <c r="AM17" s="12"/>
+      <c r="AN17" s="12"/>
+      <c r="AO17" s="12"/>
+      <c r="AP17" s="12"/>
+      <c r="AQ17" s="12"/>
+      <c r="AR17" s="12"/>
+      <c r="AS17" s="12"/>
+      <c r="AT17" s="12"/>
+      <c r="AU17" s="12"/>
+      <c r="AV17" s="12"/>
+      <c r="AW17" s="12"/>
+      <c r="AX17" s="12"/>
+      <c r="AY17" s="12"/>
+      <c r="AZ17" s="12"/>
+      <c r="BA17" s="12"/>
+      <c r="BB17" s="12"/>
+    </row>
+    <row r="18" spans="1:54" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="27">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="70"/>
+      <c r="D18" s="70"/>
+      <c r="E18" s="70"/>
+      <c r="F18" s="70"/>
+      <c r="G18" s="70"/>
+      <c r="H18" s="70"/>
+      <c r="I18" s="70"/>
+      <c r="J18" s="71"/>
+      <c r="K18" s="72"/>
+      <c r="L18" s="55"/>
+      <c r="M18" s="73"/>
+      <c r="N18" s="74"/>
+      <c r="O18" s="70"/>
+      <c r="P18" s="71"/>
+      <c r="Q18" s="71"/>
+      <c r="R18" s="72"/>
+      <c r="S18" s="55"/>
+      <c r="T18" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U18" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF18" s="12"/>
+      <c r="AG18" s="12"/>
+      <c r="AH18" s="12"/>
+      <c r="AI18" s="12"/>
+      <c r="AJ18" s="12"/>
+      <c r="AK18" s="12"/>
+      <c r="AL18" s="12"/>
+      <c r="AM18" s="12"/>
+      <c r="AN18" s="12"/>
+      <c r="AO18" s="12"/>
+      <c r="AP18" s="12"/>
+      <c r="AQ18" s="12"/>
+      <c r="AR18" s="12"/>
+      <c r="AS18" s="12"/>
+      <c r="AT18" s="12"/>
+      <c r="AU18" s="12"/>
+      <c r="AV18" s="12"/>
+      <c r="AW18" s="12"/>
+      <c r="AX18" s="12"/>
+      <c r="AY18" s="12"/>
+      <c r="AZ18" s="12"/>
+      <c r="BA18" s="12"/>
+      <c r="BB18" s="12"/>
+    </row>
+    <row r="19" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A19" s="27">
+        <v>16</v>
+      </c>
+      <c r="B19" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="70">
+        <v>2</v>
+      </c>
+      <c r="D19" s="70"/>
+      <c r="E19" s="70"/>
+      <c r="F19" s="70"/>
+      <c r="G19" s="70"/>
+      <c r="H19" s="70">
+        <f>20+24</f>
+        <v>44</v>
+      </c>
+      <c r="I19" s="70"/>
+      <c r="J19" s="71"/>
+      <c r="K19" s="72"/>
+      <c r="L19" s="55"/>
+      <c r="M19" s="73"/>
+      <c r="N19" s="74"/>
+      <c r="O19" s="70"/>
+      <c r="P19" s="71"/>
+      <c r="Q19" s="71"/>
+      <c r="R19" s="72"/>
+      <c r="S19" s="55"/>
+      <c r="T19" s="58">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="U19" s="75">
+        <f t="shared" si="4"/>
+        <v>92</v>
+      </c>
+      <c r="V19" s="75">
+        <f t="shared" si="5"/>
+        <v>3.8333333333333335</v>
+      </c>
+      <c r="AF19" s="12"/>
+      <c r="AG19" s="12"/>
+      <c r="AH19" s="12"/>
+      <c r="AI19" s="12"/>
+      <c r="AJ19" s="12"/>
+      <c r="AK19" s="12"/>
+      <c r="AL19" s="12"/>
+      <c r="AM19" s="12"/>
+      <c r="AN19" s="12"/>
+      <c r="AO19" s="12"/>
+      <c r="AP19" s="12"/>
+      <c r="AQ19" s="12"/>
+      <c r="AR19" s="12"/>
+      <c r="AS19" s="12"/>
+      <c r="AT19" s="12"/>
+      <c r="AU19" s="12"/>
+      <c r="AV19" s="12"/>
+      <c r="AW19" s="12"/>
+      <c r="AX19" s="12"/>
+      <c r="AY19" s="12"/>
+      <c r="AZ19" s="12"/>
+      <c r="BA19" s="12"/>
+      <c r="BB19" s="12"/>
+    </row>
+    <row r="20" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A20" s="27">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="B20" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="70">
+        <v>5</v>
+      </c>
+      <c r="D20" s="70"/>
+      <c r="E20" s="70"/>
+      <c r="F20" s="70"/>
+      <c r="G20" s="70"/>
+      <c r="H20" s="70"/>
+      <c r="I20" s="70"/>
+      <c r="J20" s="71"/>
+      <c r="K20" s="72"/>
+      <c r="L20" s="55"/>
+      <c r="M20" s="73"/>
+      <c r="N20" s="74"/>
+      <c r="O20" s="70"/>
+      <c r="P20" s="71"/>
+      <c r="Q20" s="71"/>
+      <c r="R20" s="72"/>
+      <c r="S20" s="55"/>
+      <c r="T20" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U20" s="75">
+        <f t="shared" si="4"/>
+        <v>120</v>
+      </c>
+      <c r="V20" s="75">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="AF20" s="12"/>
+      <c r="AG20" s="12"/>
+      <c r="AH20" s="12"/>
+      <c r="AI20" s="12"/>
+      <c r="AJ20" s="12"/>
+      <c r="AK20" s="12"/>
+      <c r="AL20" s="12"/>
+      <c r="AM20" s="12"/>
+      <c r="AN20" s="12"/>
+      <c r="AO20" s="12"/>
+      <c r="AP20" s="12"/>
+      <c r="AQ20" s="12"/>
+      <c r="AR20" s="12"/>
+      <c r="AS20" s="12"/>
+      <c r="AT20" s="12"/>
+      <c r="AU20" s="12"/>
+      <c r="AV20" s="12"/>
+      <c r="AW20" s="12"/>
+      <c r="AX20" s="12"/>
+      <c r="AY20" s="12"/>
+      <c r="AZ20" s="12"/>
+      <c r="BA20" s="12"/>
+      <c r="BB20" s="12"/>
+    </row>
+    <row r="21" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A21" s="27">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="B21" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="70"/>
+      <c r="D21" s="70"/>
+      <c r="E21" s="70"/>
+      <c r="F21" s="70"/>
+      <c r="G21" s="70"/>
+      <c r="H21" s="70">
+        <f>2*24</f>
+        <v>48</v>
+      </c>
+      <c r="I21" s="70"/>
+      <c r="J21" s="71"/>
+      <c r="K21" s="72"/>
+      <c r="L21" s="55"/>
+      <c r="M21" s="73"/>
+      <c r="N21" s="74"/>
+      <c r="O21" s="70"/>
+      <c r="P21" s="71"/>
+      <c r="Q21" s="71"/>
+      <c r="R21" s="72"/>
+      <c r="S21" s="55"/>
+      <c r="T21" s="58">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+      <c r="U21" s="75">
+        <f t="shared" si="4"/>
+        <v>48</v>
+      </c>
+      <c r="V21" s="75">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="AF21" s="12"/>
+      <c r="AG21" s="12"/>
+      <c r="AH21" s="12"/>
+      <c r="AI21" s="12"/>
+      <c r="AJ21" s="12"/>
+      <c r="AK21" s="12"/>
+      <c r="AL21" s="12"/>
+      <c r="AM21" s="12"/>
+      <c r="AN21" s="12"/>
+      <c r="AO21" s="12"/>
+      <c r="AP21" s="12"/>
+      <c r="AQ21" s="12"/>
+      <c r="AR21" s="12"/>
+      <c r="AS21" s="12"/>
+      <c r="AT21" s="12"/>
+      <c r="AU21" s="12"/>
+      <c r="AV21" s="12"/>
+      <c r="AW21" s="12"/>
+      <c r="AX21" s="12"/>
+      <c r="AY21" s="12"/>
+      <c r="AZ21" s="12"/>
+      <c r="BA21" s="12"/>
+      <c r="BB21" s="12"/>
+    </row>
+    <row r="22" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="27">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="B22" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="70">
+        <v>2</v>
+      </c>
+      <c r="D22" s="70"/>
+      <c r="E22" s="70"/>
+      <c r="F22" s="70"/>
+      <c r="G22" s="70"/>
+      <c r="H22" s="70"/>
+      <c r="I22" s="70">
+        <v>20</v>
+      </c>
+      <c r="J22" s="71"/>
+      <c r="K22" s="72"/>
+      <c r="L22" s="55"/>
+      <c r="M22" s="73"/>
+      <c r="N22" s="74"/>
+      <c r="O22" s="70"/>
+      <c r="P22" s="71"/>
+      <c r="Q22" s="71"/>
+      <c r="R22" s="72"/>
+      <c r="S22" s="55"/>
+      <c r="T22" s="58">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="U22" s="75">
+        <f t="shared" si="4"/>
+        <v>68</v>
+      </c>
+      <c r="V22" s="75">
+        <f t="shared" si="5"/>
+        <v>2.8333333333333335</v>
+      </c>
+      <c r="W22" s="9"/>
+      <c r="X22" s="9"/>
+      <c r="Y22" s="9"/>
+      <c r="Z22" s="9"/>
+      <c r="AA22" s="9"/>
+      <c r="AB22" s="9"/>
+      <c r="AC22" s="9"/>
+      <c r="AD22" s="9"/>
+      <c r="AE22" s="9"/>
+      <c r="AF22" s="12"/>
+      <c r="AG22" s="12"/>
+      <c r="AH22" s="12"/>
+      <c r="AI22" s="12"/>
+      <c r="AJ22" s="12"/>
+      <c r="AK22" s="12"/>
+      <c r="AL22" s="12"/>
+      <c r="AM22" s="12"/>
+      <c r="AN22" s="12"/>
+      <c r="AO22" s="12"/>
+      <c r="AP22" s="12"/>
+      <c r="AQ22" s="12"/>
+      <c r="AR22" s="12"/>
+      <c r="AS22" s="12"/>
+      <c r="AT22" s="12"/>
+      <c r="AU22" s="12"/>
+      <c r="AV22" s="12"/>
+      <c r="AW22" s="12"/>
+      <c r="AX22" s="12"/>
+      <c r="AY22" s="12"/>
+      <c r="AZ22" s="12"/>
+      <c r="BA22" s="12"/>
+      <c r="BB22" s="12"/>
+    </row>
+    <row r="23" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="27">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="B23" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="70"/>
+      <c r="D23" s="70"/>
+      <c r="E23" s="70"/>
+      <c r="F23" s="70"/>
+      <c r="G23" s="70"/>
+      <c r="H23" s="70">
+        <f>37*24+19</f>
+        <v>907</v>
+      </c>
+      <c r="I23" s="70"/>
+      <c r="J23" s="71"/>
+      <c r="K23" s="72"/>
+      <c r="L23" s="55"/>
+      <c r="M23" s="73"/>
+      <c r="N23" s="74"/>
+      <c r="O23" s="70"/>
+      <c r="P23" s="71"/>
+      <c r="Q23" s="71"/>
+      <c r="R23" s="72"/>
+      <c r="S23" s="55"/>
+      <c r="T23" s="58">
+        <f t="shared" si="0"/>
+        <v>907</v>
+      </c>
+      <c r="U23" s="75">
+        <f t="shared" si="4"/>
+        <v>907</v>
+      </c>
+      <c r="V23" s="75">
+        <f t="shared" si="5"/>
+        <v>37.791666666666664</v>
+      </c>
+      <c r="W23" s="9"/>
+      <c r="X23" s="9"/>
+      <c r="Y23" s="9"/>
+      <c r="Z23" s="9"/>
+      <c r="AA23" s="9"/>
+      <c r="AB23" s="9"/>
+      <c r="AC23" s="9"/>
+      <c r="AD23" s="9"/>
+      <c r="AE23" s="9"/>
+      <c r="AF23" s="12"/>
+      <c r="AG23" s="12"/>
+      <c r="AH23" s="12"/>
+      <c r="AI23" s="12"/>
+      <c r="AJ23" s="12"/>
+      <c r="AK23" s="12"/>
+      <c r="AL23" s="12"/>
+      <c r="AM23" s="12"/>
+      <c r="AN23" s="12"/>
+      <c r="AO23" s="12"/>
+      <c r="AP23" s="12"/>
+      <c r="AQ23" s="12"/>
+      <c r="AR23" s="12"/>
+      <c r="AS23" s="12"/>
+      <c r="AT23" s="12"/>
+      <c r="AU23" s="12"/>
+      <c r="AV23" s="12"/>
+      <c r="AW23" s="12"/>
+      <c r="AX23" s="12"/>
+      <c r="AY23" s="12"/>
+      <c r="AZ23" s="12"/>
+      <c r="BA23" s="12"/>
+      <c r="BB23" s="12"/>
+    </row>
+    <row r="24" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A24" s="27">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="B24" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" s="70">
+        <v>2</v>
+      </c>
+      <c r="D24" s="70"/>
+      <c r="E24" s="70"/>
+      <c r="F24" s="70"/>
+      <c r="G24" s="70"/>
+      <c r="H24" s="70">
+        <f>3*24</f>
+        <v>72</v>
+      </c>
+      <c r="I24" s="70"/>
+      <c r="J24" s="71"/>
+      <c r="K24" s="72"/>
+      <c r="L24" s="55"/>
+      <c r="M24" s="73"/>
+      <c r="N24" s="74"/>
+      <c r="O24" s="70"/>
+      <c r="P24" s="71"/>
+      <c r="Q24" s="71"/>
+      <c r="R24" s="72"/>
+      <c r="S24" s="55"/>
+      <c r="T24" s="58">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="U24" s="75">
+        <f t="shared" si="4"/>
+        <v>120</v>
+      </c>
+      <c r="V24" s="75">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="AF24" s="12"/>
+      <c r="AG24" s="12"/>
+      <c r="AH24" s="12"/>
+      <c r="AI24" s="12"/>
+      <c r="AJ24" s="12"/>
+      <c r="AK24" s="12"/>
+      <c r="AL24" s="12"/>
+      <c r="AM24" s="12"/>
+      <c r="AN24" s="12"/>
+      <c r="AO24" s="12"/>
+      <c r="AP24" s="12"/>
+      <c r="AQ24" s="12"/>
+      <c r="AR24" s="12"/>
+      <c r="AS24" s="12"/>
+      <c r="AT24" s="12"/>
+      <c r="AU24" s="12"/>
+      <c r="AV24" s="12"/>
+      <c r="AW24" s="12"/>
+      <c r="AX24" s="12"/>
+      <c r="AY24" s="12"/>
+      <c r="AZ24" s="12"/>
+      <c r="BA24" s="12"/>
+      <c r="BB24" s="12"/>
+    </row>
+    <row r="25" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A25" s="27">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="70">
+        <v>39</v>
+      </c>
+      <c r="D25" s="70"/>
+      <c r="E25" s="70"/>
+      <c r="F25" s="70"/>
+      <c r="G25" s="70"/>
+      <c r="H25" s="70"/>
+      <c r="I25" s="70">
+        <v>1</v>
+      </c>
+      <c r="J25" s="71"/>
+      <c r="K25" s="72"/>
+      <c r="L25" s="55"/>
+      <c r="M25" s="73">
+        <v>1</v>
+      </c>
+      <c r="N25" s="74"/>
+      <c r="O25" s="70">
+        <v>1</v>
+      </c>
+      <c r="P25" s="71"/>
+      <c r="Q25" s="71">
+        <v>2</v>
+      </c>
+      <c r="R25" s="72"/>
+      <c r="S25" s="55"/>
+      <c r="T25" s="58">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="U25" s="75">
+        <f t="shared" si="4"/>
+        <v>1033</v>
+      </c>
+      <c r="V25" s="75">
+        <f t="shared" si="5"/>
+        <v>43.041666666666664</v>
+      </c>
+      <c r="AY25" s="14" t="e">
+        <f>#REF!-AY24</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="27">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="B26" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="70"/>
+      <c r="D26" s="70"/>
+      <c r="E26" s="70"/>
+      <c r="F26" s="70"/>
+      <c r="G26" s="70"/>
+      <c r="H26" s="70"/>
+      <c r="I26" s="70"/>
+      <c r="J26" s="71"/>
+      <c r="K26" s="72"/>
+      <c r="L26" s="55"/>
+      <c r="M26" s="73"/>
+      <c r="N26" s="74"/>
+      <c r="O26" s="70"/>
+      <c r="P26" s="71"/>
+      <c r="Q26" s="71"/>
+      <c r="R26" s="72"/>
+      <c r="S26" s="55"/>
+      <c r="T26" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U26" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V26" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W26" s="9"/>
+      <c r="X26" s="9"/>
+      <c r="Y26" s="9"/>
+      <c r="Z26" s="9"/>
+      <c r="AA26" s="9"/>
+      <c r="AB26" s="9"/>
+      <c r="AC26" s="9"/>
+      <c r="AD26" s="9"/>
+      <c r="AE26" s="9"/>
+    </row>
+    <row r="27" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="27">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="B27" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27" s="70">
+        <v>3</v>
+      </c>
+      <c r="D27" s="70"/>
+      <c r="E27" s="70"/>
+      <c r="F27" s="70"/>
+      <c r="G27" s="70"/>
+      <c r="H27" s="70"/>
+      <c r="I27" s="70"/>
+      <c r="J27" s="71"/>
+      <c r="K27" s="72"/>
+      <c r="L27" s="55"/>
+      <c r="M27" s="73"/>
+      <c r="N27" s="74"/>
+      <c r="O27" s="70"/>
+      <c r="P27" s="71"/>
+      <c r="Q27" s="71"/>
+      <c r="R27" s="72"/>
+      <c r="S27" s="55"/>
+      <c r="T27" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U27" s="75">
+        <f t="shared" si="4"/>
+        <v>72</v>
+      </c>
+      <c r="V27" s="75">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="W27" s="9"/>
+      <c r="X27" s="9"/>
+      <c r="Y27" s="9"/>
+      <c r="Z27" s="9"/>
+      <c r="AA27" s="9"/>
+      <c r="AB27" s="9"/>
+      <c r="AC27" s="9"/>
+      <c r="AD27" s="9"/>
+      <c r="AE27" s="9"/>
+    </row>
+    <row r="28" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="27">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="B28" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="70"/>
+      <c r="D28" s="70"/>
+      <c r="E28" s="70"/>
+      <c r="F28" s="70"/>
+      <c r="G28" s="70"/>
+      <c r="H28" s="70"/>
+      <c r="I28" s="70"/>
+      <c r="J28" s="71"/>
+      <c r="K28" s="72"/>
+      <c r="L28" s="55"/>
+      <c r="M28" s="73"/>
+      <c r="N28" s="74"/>
+      <c r="O28" s="70"/>
+      <c r="P28" s="71"/>
+      <c r="Q28" s="71"/>
+      <c r="R28" s="72"/>
+      <c r="S28" s="55"/>
+      <c r="T28" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U28" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V28" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W28" s="9"/>
+      <c r="X28" s="9"/>
+      <c r="Y28" s="9"/>
+      <c r="Z28" s="9"/>
+      <c r="AA28" s="9"/>
+      <c r="AB28" s="9"/>
+      <c r="AC28" s="9"/>
+      <c r="AD28" s="9"/>
+      <c r="AE28" s="9"/>
+    </row>
+    <row r="29" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A29" s="27">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="B29" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" s="70">
+        <v>21</v>
+      </c>
+      <c r="D29" s="70"/>
+      <c r="E29" s="70"/>
+      <c r="F29" s="70"/>
+      <c r="G29" s="70"/>
+      <c r="H29" s="70"/>
+      <c r="I29" s="70">
+        <v>5</v>
+      </c>
+      <c r="J29" s="71"/>
+      <c r="K29" s="72"/>
+      <c r="L29" s="55"/>
+      <c r="M29" s="73"/>
+      <c r="N29" s="74"/>
+      <c r="O29" s="70">
+        <v>1</v>
+      </c>
+      <c r="P29" s="71"/>
+      <c r="Q29" s="71">
+        <v>1</v>
+      </c>
+      <c r="R29" s="72"/>
+      <c r="S29" s="55"/>
+      <c r="T29" s="58">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="U29" s="75">
+        <f t="shared" si="4"/>
+        <v>557</v>
+      </c>
+      <c r="V29" s="75">
+        <f t="shared" si="5"/>
+        <v>23.208333333333332</v>
+      </c>
+    </row>
+    <row r="30" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A30" s="27">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="B30" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="70">
+        <v>9</v>
+      </c>
+      <c r="D30" s="70"/>
+      <c r="E30" s="70"/>
+      <c r="F30" s="70"/>
+      <c r="G30" s="70"/>
+      <c r="H30" s="70"/>
+      <c r="I30" s="70"/>
+      <c r="J30" s="71"/>
+      <c r="K30" s="72"/>
+      <c r="L30" s="55"/>
+      <c r="M30" s="73"/>
+      <c r="N30" s="74"/>
+      <c r="O30" s="70"/>
+      <c r="P30" s="71"/>
+      <c r="Q30" s="71">
+        <v>1</v>
+      </c>
+      <c r="R30" s="72"/>
+      <c r="S30" s="55"/>
+      <c r="T30" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U30" s="75">
+        <f t="shared" si="4"/>
+        <v>240</v>
+      </c>
+      <c r="V30" s="75">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A31" s="27">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="B31" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" s="70"/>
+      <c r="D31" s="70"/>
+      <c r="E31" s="70"/>
+      <c r="F31" s="70"/>
+      <c r="G31" s="70"/>
+      <c r="H31" s="70"/>
+      <c r="I31" s="70"/>
+      <c r="J31" s="71"/>
+      <c r="K31" s="72"/>
+      <c r="L31" s="55"/>
+      <c r="M31" s="73"/>
+      <c r="N31" s="74"/>
+      <c r="O31" s="70"/>
+      <c r="P31" s="71"/>
+      <c r="Q31" s="71"/>
+      <c r="R31" s="72"/>
+      <c r="S31" s="55"/>
+      <c r="T31" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U31" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V31" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A32" s="27">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="B32" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" s="70"/>
+      <c r="D32" s="70"/>
+      <c r="E32" s="70"/>
+      <c r="F32" s="70"/>
+      <c r="G32" s="70"/>
+      <c r="H32" s="70"/>
+      <c r="I32" s="70"/>
+      <c r="J32" s="71"/>
+      <c r="K32" s="72"/>
+      <c r="L32" s="55"/>
+      <c r="M32" s="73"/>
+      <c r="N32" s="74"/>
+      <c r="O32" s="70"/>
+      <c r="P32" s="71"/>
+      <c r="Q32" s="71"/>
+      <c r="R32" s="72"/>
+      <c r="S32" s="55"/>
+      <c r="T32" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U32" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V32" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A33" s="27">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="B33" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" s="70"/>
+      <c r="D33" s="70"/>
+      <c r="E33" s="70"/>
+      <c r="F33" s="70"/>
+      <c r="G33" s="70"/>
+      <c r="H33" s="70"/>
+      <c r="I33" s="70"/>
+      <c r="J33" s="71"/>
+      <c r="K33" s="72"/>
+      <c r="L33" s="55"/>
+      <c r="M33" s="73">
+        <v>1</v>
+      </c>
+      <c r="N33" s="74"/>
+      <c r="O33" s="70"/>
+      <c r="P33" s="71"/>
+      <c r="Q33" s="71"/>
+      <c r="R33" s="72"/>
+      <c r="S33" s="55"/>
+      <c r="T33" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U33" s="75">
+        <f t="shared" si="4"/>
+        <v>24</v>
+      </c>
+      <c r="V33" s="75">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A34" s="27">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="B34" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" s="70">
+        <f>144+34</f>
+        <v>178</v>
+      </c>
+      <c r="D34" s="70"/>
+      <c r="E34" s="70"/>
+      <c r="F34" s="70"/>
+      <c r="G34" s="70"/>
+      <c r="H34" s="70"/>
+      <c r="I34" s="70">
+        <v>1</v>
+      </c>
+      <c r="J34" s="71"/>
+      <c r="K34" s="72">
+        <v>1</v>
+      </c>
+      <c r="L34" s="55"/>
+      <c r="M34" s="73"/>
+      <c r="N34" s="74"/>
+      <c r="O34" s="70">
+        <v>2</v>
+      </c>
+      <c r="P34" s="71"/>
+      <c r="Q34" s="71">
+        <v>2</v>
+      </c>
+      <c r="R34" s="72"/>
+      <c r="S34" s="55"/>
+      <c r="T34" s="58">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="U34" s="75">
+        <f t="shared" si="4"/>
+        <v>4370</v>
+      </c>
+      <c r="V34" s="75">
+        <f t="shared" si="5"/>
+        <v>182.08333333333334</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="27">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="B35" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="C35" s="70"/>
+      <c r="D35" s="70"/>
+      <c r="E35" s="70"/>
+      <c r="F35" s="70"/>
+      <c r="G35" s="70"/>
+      <c r="H35" s="70"/>
+      <c r="I35" s="70"/>
+      <c r="J35" s="71"/>
+      <c r="K35" s="72"/>
+      <c r="L35" s="55"/>
+      <c r="M35" s="73"/>
+      <c r="N35" s="74"/>
+      <c r="O35" s="70"/>
+      <c r="P35" s="71"/>
+      <c r="Q35" s="71"/>
+      <c r="R35" s="72"/>
+      <c r="S35" s="55"/>
+      <c r="T35" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U35" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V35" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A36" s="27">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+      <c r="B36" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="70"/>
+      <c r="D36" s="70"/>
+      <c r="E36" s="70"/>
+      <c r="F36" s="70"/>
+      <c r="G36" s="70"/>
+      <c r="H36" s="70"/>
+      <c r="I36" s="70"/>
+      <c r="J36" s="71"/>
+      <c r="K36" s="72"/>
+      <c r="L36" s="55"/>
+      <c r="M36" s="73"/>
+      <c r="N36" s="74"/>
+      <c r="O36" s="70"/>
+      <c r="P36" s="71"/>
+      <c r="Q36" s="71"/>
+      <c r="R36" s="72"/>
+      <c r="S36" s="55"/>
+      <c r="T36" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U36" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="27">
+        <f t="shared" si="1"/>
+        <v>34</v>
+      </c>
+      <c r="B37" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="C37" s="59">
+        <f>2592+60</f>
+        <v>2652</v>
+      </c>
+      <c r="D37" s="59"/>
+      <c r="E37" s="59"/>
+      <c r="F37" s="59"/>
+      <c r="G37" s="59"/>
+      <c r="H37" s="59">
+        <v>4</v>
+      </c>
+      <c r="I37" s="59">
+        <v>2</v>
+      </c>
+      <c r="J37" s="60">
+        <v>5</v>
+      </c>
+      <c r="K37" s="61">
+        <f>1*6+2</f>
+        <v>8</v>
+      </c>
+      <c r="L37" s="62"/>
+      <c r="M37" s="63">
+        <v>50</v>
+      </c>
+      <c r="N37" s="64"/>
+      <c r="O37" s="65">
+        <v>15</v>
+      </c>
+      <c r="P37" s="66"/>
+      <c r="Q37" s="66">
+        <v>66</v>
+      </c>
+      <c r="R37" s="67"/>
+      <c r="S37" s="62"/>
+      <c r="T37" s="77">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="U37" s="77">
+        <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
+        <v>16717</v>
+      </c>
+      <c r="V37" s="77">
+        <f>U37/6</f>
+        <v>2786.1666666666665</v>
+      </c>
+      <c r="W37" s="50"/>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A38" s="27">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="B38" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" s="70"/>
+      <c r="D38" s="70"/>
+      <c r="E38" s="70"/>
+      <c r="F38" s="70"/>
+      <c r="G38" s="70"/>
+      <c r="H38" s="70"/>
+      <c r="I38" s="70"/>
+      <c r="J38" s="71"/>
+      <c r="K38" s="72"/>
+      <c r="L38" s="55"/>
+      <c r="M38" s="73"/>
+      <c r="N38" s="74"/>
+      <c r="O38" s="70"/>
+      <c r="P38" s="71"/>
+      <c r="Q38" s="71"/>
+      <c r="R38" s="72"/>
+      <c r="S38" s="55"/>
+      <c r="T38" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U38" s="75">
+        <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
+        <v>0</v>
+      </c>
+      <c r="V38" s="75">
+        <f>U38/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A39" s="27">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="B39" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="C39" s="78"/>
+      <c r="D39" s="78"/>
+      <c r="E39" s="78"/>
+      <c r="F39" s="78"/>
+      <c r="G39" s="78"/>
+      <c r="H39" s="78"/>
+      <c r="I39" s="78"/>
+      <c r="J39" s="79"/>
+      <c r="K39" s="80"/>
+      <c r="L39" s="55"/>
+      <c r="M39" s="73"/>
+      <c r="N39" s="74"/>
+      <c r="O39" s="70"/>
+      <c r="P39" s="71"/>
+      <c r="Q39" s="71"/>
+      <c r="R39" s="72"/>
+      <c r="S39" s="95"/>
+      <c r="T39" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U39" s="75">
+        <f>C39*24+M39*24+O39*24+Q39*24+T39</f>
+        <v>0</v>
+      </c>
+      <c r="V39" s="75">
+        <f>U39/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="27">
+        <f t="shared" si="1"/>
+        <v>37</v>
+      </c>
+      <c r="B40" s="42" t="s">
+        <v>21</v>
+      </c>
+      <c r="C40" s="59">
+        <f>51+252</f>
+        <v>303</v>
+      </c>
+      <c r="D40" s="59"/>
+      <c r="E40" s="59"/>
+      <c r="F40" s="59"/>
+      <c r="G40" s="59"/>
+      <c r="H40" s="59"/>
+      <c r="I40" s="59"/>
+      <c r="J40" s="60"/>
+      <c r="K40" s="61">
+        <v>20</v>
+      </c>
+      <c r="L40" s="62"/>
+      <c r="M40" s="63"/>
+      <c r="N40" s="64"/>
+      <c r="O40" s="65">
+        <v>2</v>
+      </c>
+      <c r="P40" s="66"/>
+      <c r="Q40" s="66">
+        <v>2</v>
+      </c>
+      <c r="R40" s="67"/>
+      <c r="S40" s="62"/>
+      <c r="T40" s="77">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="U40" s="77">
+        <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
+        <v>7388</v>
+      </c>
+      <c r="V40" s="77">
+        <f>U40/24</f>
+        <v>307.83333333333331</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="27">
+        <f t="shared" si="1"/>
+        <v>38</v>
+      </c>
+      <c r="B41" s="43" t="s">
+        <v>22</v>
+      </c>
+      <c r="C41" s="82">
+        <f>384+9</f>
+        <v>393</v>
+      </c>
+      <c r="D41" s="82"/>
+      <c r="E41" s="82"/>
+      <c r="F41" s="82"/>
+      <c r="G41" s="82"/>
+      <c r="H41" s="82"/>
+      <c r="I41" s="82"/>
+      <c r="J41" s="83"/>
+      <c r="K41" s="84"/>
+      <c r="L41" s="85"/>
+      <c r="M41" s="86">
+        <v>10</v>
+      </c>
+      <c r="N41" s="87"/>
+      <c r="O41" s="82">
+        <v>8</v>
+      </c>
+      <c r="P41" s="83"/>
+      <c r="Q41" s="83">
+        <v>19</v>
+      </c>
+      <c r="R41" s="84"/>
+      <c r="S41" s="85"/>
+      <c r="T41" s="88">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U41" s="88">
+        <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
+        <v>5160</v>
+      </c>
+      <c r="V41" s="88">
+        <f>U41/12</f>
+        <v>430</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="27">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+      <c r="B42" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C42" s="70"/>
+      <c r="D42" s="70"/>
+      <c r="E42" s="70"/>
+      <c r="F42" s="70"/>
+      <c r="G42" s="70"/>
+      <c r="H42" s="70"/>
+      <c r="I42" s="70"/>
+      <c r="J42" s="71"/>
+      <c r="K42" s="72"/>
+      <c r="L42" s="55"/>
+      <c r="M42" s="73"/>
+      <c r="N42" s="74"/>
+      <c r="O42" s="70"/>
+      <c r="P42" s="71"/>
+      <c r="Q42" s="71"/>
+      <c r="R42" s="72"/>
+      <c r="S42" s="55"/>
+      <c r="T42" s="75"/>
+      <c r="U42" s="75"/>
+      <c r="V42" s="75"/>
+    </row>
+    <row r="43" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="27">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="B43" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="C43" s="65">
+        <f>6971+19764+10260</f>
+        <v>36995</v>
+      </c>
+      <c r="D43" s="65"/>
+      <c r="E43" s="65"/>
+      <c r="F43" s="65"/>
+      <c r="G43" s="65"/>
+      <c r="H43" s="65">
+        <v>8</v>
+      </c>
+      <c r="I43" s="65">
+        <v>12</v>
+      </c>
+      <c r="J43" s="66">
+        <f>22*6+5</f>
+        <v>137</v>
+      </c>
+      <c r="K43" s="67">
+        <f>69*6+1</f>
+        <v>415</v>
+      </c>
+      <c r="L43" s="62"/>
+      <c r="M43" s="63">
+        <v>302</v>
+      </c>
+      <c r="N43" s="64"/>
+      <c r="O43" s="65">
+        <v>450</v>
+      </c>
+      <c r="P43" s="66"/>
+      <c r="Q43" s="66">
+        <v>448</v>
+      </c>
+      <c r="R43" s="67"/>
+      <c r="S43" s="62"/>
+      <c r="T43" s="77">
+        <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
+        <v>572</v>
+      </c>
+      <c r="U43" s="77">
+        <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
+        <v>229742</v>
+      </c>
+      <c r="V43" s="77">
+        <f>U43/6</f>
+        <v>38290.333333333336</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="27">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+      <c r="B44" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="70"/>
+      <c r="D44" s="70"/>
+      <c r="E44" s="70"/>
+      <c r="F44" s="70"/>
+      <c r="G44" s="70"/>
+      <c r="H44" s="70"/>
+      <c r="I44" s="70"/>
+      <c r="J44" s="71"/>
+      <c r="K44" s="72"/>
+      <c r="L44" s="55"/>
+      <c r="M44" s="73"/>
+      <c r="N44" s="74"/>
+      <c r="O44" s="70"/>
+      <c r="P44" s="71"/>
+      <c r="Q44" s="71"/>
+      <c r="R44" s="72"/>
+      <c r="S44" s="55"/>
+      <c r="T44" s="75"/>
+      <c r="U44" s="75"/>
+      <c r="V44" s="75"/>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A45" s="27">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="B45" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="70"/>
+      <c r="D45" s="70"/>
+      <c r="E45" s="70"/>
+      <c r="F45" s="70"/>
+      <c r="G45" s="70"/>
+      <c r="H45" s="70"/>
+      <c r="I45" s="70"/>
+      <c r="J45" s="71"/>
+      <c r="K45" s="72"/>
+      <c r="L45" s="55"/>
+      <c r="M45" s="73"/>
+      <c r="N45" s="74"/>
+      <c r="O45" s="70"/>
+      <c r="P45" s="71"/>
+      <c r="Q45" s="71"/>
+      <c r="R45" s="72"/>
+      <c r="S45" s="55"/>
+      <c r="T45" s="75">
+        <f t="shared" ref="T45:T54" si="7">H45+I45+J45+K45+N45+P45+R45</f>
+        <v>0</v>
+      </c>
+      <c r="U45" s="75">
+        <f>C45*24+M45*24+O45*24+Q45*24+T45</f>
+        <v>0</v>
+      </c>
+      <c r="V45" s="75">
+        <f>U45/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A46" s="27">
+        <f t="shared" si="1"/>
+        <v>43</v>
+      </c>
+      <c r="B46" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="C46" s="70"/>
+      <c r="D46" s="70"/>
+      <c r="E46" s="70"/>
+      <c r="F46" s="70"/>
+      <c r="G46" s="70"/>
+      <c r="H46" s="70"/>
+      <c r="I46" s="70"/>
+      <c r="J46" s="71"/>
+      <c r="K46" s="72"/>
+      <c r="L46" s="55"/>
+      <c r="M46" s="73"/>
+      <c r="N46" s="74"/>
+      <c r="O46" s="70"/>
+      <c r="P46" s="71"/>
+      <c r="Q46" s="71"/>
+      <c r="R46" s="72"/>
+      <c r="S46" s="55"/>
+      <c r="T46" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U46" s="75">
+        <f t="shared" ref="U46:U50" si="8">C46*24+M46*24+O46*24+Q46*24+T46</f>
+        <v>0</v>
+      </c>
+      <c r="V46" s="75">
+        <f t="shared" ref="V46:V54" si="9">U46/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="27">
+        <f t="shared" si="1"/>
+        <v>44</v>
+      </c>
+      <c r="B47" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="C47" s="65">
+        <f>94+648+324+88+540+103+324+432+106</f>
+        <v>2659</v>
+      </c>
+      <c r="D47" s="65"/>
+      <c r="E47" s="65"/>
+      <c r="F47" s="65"/>
+      <c r="G47" s="65"/>
+      <c r="H47" s="65">
+        <v>1</v>
+      </c>
+      <c r="I47" s="65"/>
+      <c r="J47" s="66"/>
+      <c r="K47" s="67">
+        <v>5</v>
+      </c>
+      <c r="L47" s="62"/>
+      <c r="M47" s="63"/>
+      <c r="N47" s="64"/>
+      <c r="O47" s="65">
+        <v>15</v>
+      </c>
+      <c r="P47" s="66"/>
+      <c r="Q47" s="66">
+        <v>5</v>
+      </c>
+      <c r="R47" s="67">
+        <v>3</v>
+      </c>
+      <c r="S47" s="62"/>
+      <c r="T47" s="77">
+        <f t="shared" si="7"/>
+        <v>9</v>
+      </c>
+      <c r="U47" s="77">
+        <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
+        <v>16083</v>
+      </c>
+      <c r="V47" s="77">
+        <f>U47/6</f>
+        <v>2680.5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A48" s="27">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="B48" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C48" s="70"/>
+      <c r="D48" s="70"/>
+      <c r="E48" s="70"/>
+      <c r="F48" s="70"/>
+      <c r="G48" s="70"/>
+      <c r="H48" s="70">
+        <v>24</v>
+      </c>
+      <c r="I48" s="70"/>
+      <c r="J48" s="71"/>
+      <c r="K48" s="72"/>
+      <c r="L48" s="55"/>
+      <c r="M48" s="73"/>
+      <c r="N48" s="74"/>
+      <c r="O48" s="70"/>
+      <c r="P48" s="71"/>
+      <c r="Q48" s="71"/>
+      <c r="R48" s="72"/>
+      <c r="S48" s="55"/>
+      <c r="T48" s="75">
+        <f t="shared" si="7"/>
+        <v>24</v>
+      </c>
+      <c r="U48" s="75">
+        <f t="shared" si="8"/>
+        <v>24</v>
+      </c>
+      <c r="V48" s="75">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A49" s="27">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="B49" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C49" s="70"/>
+      <c r="D49" s="70"/>
+      <c r="E49" s="70"/>
+      <c r="F49" s="70"/>
+      <c r="G49" s="70"/>
+      <c r="H49" s="70"/>
+      <c r="I49" s="70"/>
+      <c r="J49" s="71"/>
+      <c r="K49" s="72"/>
+      <c r="L49" s="55"/>
+      <c r="M49" s="73"/>
+      <c r="N49" s="74"/>
+      <c r="O49" s="70"/>
+      <c r="P49" s="71"/>
+      <c r="Q49" s="71"/>
+      <c r="R49" s="72"/>
+      <c r="S49" s="55"/>
+      <c r="T49" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U49" s="75">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V49" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A50" s="27">
+        <f t="shared" si="1"/>
+        <v>47</v>
+      </c>
+      <c r="B50" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="C50" s="70"/>
+      <c r="D50" s="70"/>
+      <c r="E50" s="70"/>
+      <c r="F50" s="70"/>
+      <c r="G50" s="70"/>
+      <c r="H50" s="70"/>
+      <c r="I50" s="70"/>
+      <c r="J50" s="71"/>
+      <c r="K50" s="72"/>
+      <c r="L50" s="55"/>
+      <c r="M50" s="73"/>
+      <c r="N50" s="74"/>
+      <c r="O50" s="70"/>
+      <c r="P50" s="71"/>
+      <c r="Q50" s="71"/>
+      <c r="R50" s="72"/>
+      <c r="S50" s="55"/>
+      <c r="T50" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U50" s="75">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V50" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="27">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+      <c r="B51" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="C51" s="65">
+        <v>34</v>
+      </c>
+      <c r="D51" s="65"/>
+      <c r="E51" s="65"/>
+      <c r="F51" s="65"/>
+      <c r="G51" s="65"/>
+      <c r="H51" s="65"/>
+      <c r="I51" s="65"/>
+      <c r="J51" s="66"/>
+      <c r="K51" s="67"/>
+      <c r="L51" s="62"/>
+      <c r="M51" s="63"/>
+      <c r="N51" s="64"/>
+      <c r="O51" s="65"/>
+      <c r="P51" s="66"/>
+      <c r="Q51" s="66"/>
+      <c r="R51" s="67"/>
+      <c r="S51" s="62"/>
+      <c r="T51" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U51" s="77">
+        <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
+        <v>204</v>
+      </c>
+      <c r="V51" s="77">
+        <f>U51/6</f>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A52" s="27">
+        <f t="shared" si="1"/>
+        <v>49</v>
+      </c>
+      <c r="B52" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="C52" s="70"/>
+      <c r="D52" s="70"/>
+      <c r="E52" s="70"/>
+      <c r="F52" s="70"/>
+      <c r="G52" s="70"/>
+      <c r="H52" s="70"/>
+      <c r="I52" s="70"/>
+      <c r="J52" s="71"/>
+      <c r="K52" s="72"/>
+      <c r="L52" s="55"/>
+      <c r="M52" s="73"/>
+      <c r="N52" s="74"/>
+      <c r="O52" s="70"/>
+      <c r="P52" s="71"/>
+      <c r="Q52" s="71"/>
+      <c r="R52" s="72"/>
+      <c r="S52" s="55"/>
+      <c r="T52" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U52" s="75">
+        <f t="shared" ref="U52:U54" si="10">C52*24+M52*24+O52*24+Q52*24+T52</f>
+        <v>0</v>
+      </c>
+      <c r="V52" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A53" s="27">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="B53" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C53" s="70">
+        <v>7</v>
+      </c>
+      <c r="D53" s="70"/>
+      <c r="E53" s="70"/>
+      <c r="F53" s="70"/>
+      <c r="G53" s="70"/>
+      <c r="H53" s="70"/>
+      <c r="I53" s="70"/>
+      <c r="J53" s="71"/>
+      <c r="K53" s="72"/>
+      <c r="L53" s="55"/>
+      <c r="M53" s="73"/>
+      <c r="N53" s="74"/>
+      <c r="O53" s="70"/>
+      <c r="P53" s="71"/>
+      <c r="Q53" s="71"/>
+      <c r="R53" s="72"/>
+      <c r="S53" s="55"/>
+      <c r="T53" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U53" s="75">
+        <f t="shared" si="10"/>
+        <v>168</v>
+      </c>
+      <c r="V53" s="75">
+        <f t="shared" si="9"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A54" s="27">
+        <f t="shared" si="1"/>
+        <v>51</v>
+      </c>
+      <c r="B54" s="26"/>
+      <c r="C54" s="70"/>
+      <c r="D54" s="70"/>
+      <c r="E54" s="70"/>
+      <c r="F54" s="70"/>
+      <c r="G54" s="70"/>
+      <c r="H54" s="70"/>
+      <c r="I54" s="70"/>
+      <c r="J54" s="71"/>
+      <c r="K54" s="72"/>
+      <c r="L54" s="55"/>
+      <c r="M54" s="73"/>
+      <c r="N54" s="74"/>
+      <c r="O54" s="70"/>
+      <c r="P54" s="71"/>
+      <c r="Q54" s="71"/>
+      <c r="R54" s="72"/>
+      <c r="S54" s="55"/>
+      <c r="T54" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U54" s="75">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V54" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A55" s="27">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="B55" s="26"/>
+      <c r="C55" s="70"/>
+      <c r="D55" s="70"/>
+      <c r="E55" s="70"/>
+      <c r="F55" s="70"/>
+      <c r="G55" s="70"/>
+      <c r="H55" s="70"/>
+      <c r="I55" s="70"/>
+      <c r="J55" s="71"/>
+      <c r="K55" s="72"/>
+      <c r="L55" s="55"/>
+      <c r="M55" s="73"/>
+      <c r="N55" s="74"/>
+      <c r="O55" s="70"/>
+      <c r="P55" s="71"/>
+      <c r="Q55" s="71"/>
+      <c r="R55" s="72"/>
+      <c r="S55" s="55"/>
+      <c r="T55" s="75"/>
+      <c r="U55" s="75"/>
+      <c r="V55" s="75"/>
+    </row>
+    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A56" s="27">
+        <f t="shared" si="1"/>
+        <v>53</v>
+      </c>
+      <c r="B56" s="26"/>
+      <c r="C56" s="70"/>
+      <c r="D56" s="70"/>
+      <c r="E56" s="70"/>
+      <c r="F56" s="70"/>
+      <c r="G56" s="70"/>
+      <c r="H56" s="70"/>
+      <c r="I56" s="70"/>
+      <c r="J56" s="71"/>
+      <c r="K56" s="72"/>
+      <c r="L56" s="55"/>
+      <c r="M56" s="73"/>
+      <c r="N56" s="74"/>
+      <c r="O56" s="70"/>
+      <c r="P56" s="71"/>
+      <c r="Q56" s="71"/>
+      <c r="R56" s="72"/>
+      <c r="S56" s="55"/>
+      <c r="T56" s="75"/>
+      <c r="U56" s="75"/>
+      <c r="V56" s="75"/>
+    </row>
+    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A57" s="27">
+        <f t="shared" si="1"/>
+        <v>54</v>
+      </c>
+      <c r="B57" s="26"/>
+      <c r="C57" s="70"/>
+      <c r="D57" s="70"/>
+      <c r="E57" s="70"/>
+      <c r="F57" s="70"/>
+      <c r="G57" s="70"/>
+      <c r="H57" s="70"/>
+      <c r="I57" s="70"/>
+      <c r="J57" s="71"/>
+      <c r="K57" s="72"/>
+      <c r="L57" s="55"/>
+      <c r="M57" s="73"/>
+      <c r="N57" s="74"/>
+      <c r="O57" s="70"/>
+      <c r="P57" s="71"/>
+      <c r="Q57" s="71"/>
+      <c r="R57" s="72"/>
+      <c r="S57" s="55"/>
+      <c r="T57" s="75"/>
+      <c r="U57" s="75"/>
+      <c r="V57" s="75"/>
+    </row>
+    <row r="58" spans="1:22" s="15" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B58" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="C58" s="2">
+        <f>SUM(C7:C57)</f>
+        <v>46721</v>
+      </c>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2">
+        <f t="shared" ref="F58:K58" si="11">SUM(F7:F57)</f>
+        <v>0</v>
+      </c>
+      <c r="G58" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="H58" s="2">
+        <f t="shared" si="11"/>
+        <v>1196</v>
+      </c>
+      <c r="I58" s="6">
+        <f t="shared" si="11"/>
+        <v>44</v>
+      </c>
+      <c r="J58" s="6">
+        <f t="shared" si="11"/>
+        <v>142</v>
+      </c>
+      <c r="K58" s="6">
+        <f t="shared" si="11"/>
+        <v>457</v>
+      </c>
+      <c r="M58" s="5">
+        <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
+        <v>381</v>
+      </c>
+      <c r="N58" s="5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="O58" s="5">
+        <f t="shared" si="12"/>
+        <v>508</v>
+      </c>
+      <c r="P58" s="5">
+        <f t="shared" si="12"/>
+        <v>33</v>
+      </c>
+      <c r="Q58" s="5">
+        <f t="shared" si="12"/>
+        <v>563</v>
+      </c>
+      <c r="R58" s="5">
+        <f t="shared" si="12"/>
+        <v>8</v>
+      </c>
+      <c r="S58" s="55"/>
+      <c r="T58" s="4">
+        <f>SUM(T7:T57)</f>
+        <v>1880</v>
+      </c>
+      <c r="U58" s="90">
+        <f>SUM(U7:U57)</f>
+        <v>366434</v>
+      </c>
+      <c r="V58" s="4">
+        <f>SUM(V7:V57)</f>
+        <v>48326.333333333336</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="60" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="C60" s="106" t="s">
+        <v>41</v>
+      </c>
+      <c r="D60" s="107"/>
+      <c r="E60" s="107"/>
+      <c r="F60" s="107"/>
+      <c r="G60" s="107"/>
+      <c r="H60" s="107"/>
+      <c r="I60" s="107"/>
+      <c r="J60" s="107"/>
+      <c r="K60" s="108"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -20667,21 +23797,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="108" t="s">
+      <c r="I1" s="109" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="108"/>
-      <c r="K1" s="108"/>
-      <c r="L1" s="108"/>
-      <c r="M1" s="108"/>
-      <c r="N1" s="108"/>
-      <c r="O1" s="108"/>
-      <c r="P1" s="108"/>
-      <c r="Q1" s="108"/>
-      <c r="R1" s="108"/>
-      <c r="S1" s="108"/>
-      <c r="T1" s="108"/>
-      <c r="U1" s="108"/>
+      <c r="J1" s="109"/>
+      <c r="K1" s="109"/>
+      <c r="L1" s="109"/>
+      <c r="M1" s="109"/>
+      <c r="N1" s="109"/>
+      <c r="O1" s="109"/>
+      <c r="P1" s="109"/>
+      <c r="Q1" s="109"/>
+      <c r="R1" s="109"/>
+      <c r="S1" s="109"/>
+      <c r="T1" s="109"/>
+      <c r="U1" s="109"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -20693,17 +23823,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="109" t="s">
+      <c r="C4" s="110" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="109"/>
-      <c r="E4" s="109"/>
-      <c r="F4" s="109"/>
-      <c r="G4" s="109"/>
-      <c r="H4" s="109"/>
-      <c r="I4" s="109"/>
-      <c r="J4" s="110"/>
-      <c r="K4" s="111"/>
+      <c r="D4" s="110"/>
+      <c r="E4" s="110"/>
+      <c r="F4" s="110"/>
+      <c r="G4" s="110"/>
+      <c r="H4" s="110"/>
+      <c r="I4" s="110"/>
+      <c r="J4" s="111"/>
+      <c r="K4" s="112"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -20723,13 +23853,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="112" t="s">
+      <c r="T4" s="113" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="118" t="s">
+      <c r="U4" s="119" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="101" t="s">
+      <c r="V4" s="102" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -20769,10 +23899,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="116" t="s">
+      <c r="J5" s="117" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="117"/>
+      <c r="K5" s="118"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -20780,9 +23910,9 @@
       <c r="Q5" s="96"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="113"/>
-      <c r="U5" s="119"/>
-      <c r="V5" s="102"/>
+      <c r="T5" s="114"/>
+      <c r="U5" s="120"/>
+      <c r="V5" s="103"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -23492,17 +26622,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="105" t="s">
+      <c r="C60" s="106" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="106"/>
-      <c r="E60" s="106"/>
-      <c r="F60" s="106"/>
-      <c r="G60" s="106"/>
-      <c r="H60" s="106"/>
-      <c r="I60" s="106"/>
-      <c r="J60" s="106"/>
-      <c r="K60" s="107"/>
+      <c r="D60" s="107"/>
+      <c r="E60" s="107"/>
+      <c r="F60" s="107"/>
+      <c r="G60" s="107"/>
+      <c r="H60" s="107"/>
+      <c r="I60" s="107"/>
+      <c r="J60" s="107"/>
+      <c r="K60" s="108"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -23811,21 +26941,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="108" t="s">
+      <c r="I1" s="109" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="108"/>
-      <c r="K1" s="108"/>
-      <c r="L1" s="108"/>
-      <c r="M1" s="108"/>
-      <c r="N1" s="108"/>
-      <c r="O1" s="108"/>
-      <c r="P1" s="108"/>
-      <c r="Q1" s="108"/>
-      <c r="R1" s="108"/>
-      <c r="S1" s="108"/>
-      <c r="T1" s="108"/>
-      <c r="U1" s="108"/>
+      <c r="J1" s="109"/>
+      <c r="K1" s="109"/>
+      <c r="L1" s="109"/>
+      <c r="M1" s="109"/>
+      <c r="N1" s="109"/>
+      <c r="O1" s="109"/>
+      <c r="P1" s="109"/>
+      <c r="Q1" s="109"/>
+      <c r="R1" s="109"/>
+      <c r="S1" s="109"/>
+      <c r="T1" s="109"/>
+      <c r="U1" s="109"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -23837,17 +26967,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="109" t="s">
+      <c r="C4" s="110" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="109"/>
-      <c r="E4" s="109"/>
-      <c r="F4" s="109"/>
-      <c r="G4" s="109"/>
-      <c r="H4" s="109"/>
-      <c r="I4" s="109"/>
-      <c r="J4" s="110"/>
-      <c r="K4" s="111"/>
+      <c r="D4" s="110"/>
+      <c r="E4" s="110"/>
+      <c r="F4" s="110"/>
+      <c r="G4" s="110"/>
+      <c r="H4" s="110"/>
+      <c r="I4" s="110"/>
+      <c r="J4" s="111"/>
+      <c r="K4" s="112"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -23867,13 +26997,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="112" t="s">
+      <c r="T4" s="113" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="118" t="s">
+      <c r="U4" s="119" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="101" t="s">
+      <c r="V4" s="102" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -23913,10 +27043,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="116" t="s">
+      <c r="J5" s="117" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="117"/>
+      <c r="K5" s="118"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -23924,9 +27054,9 @@
       <c r="Q5" s="97"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="113"/>
-      <c r="U5" s="119"/>
-      <c r="V5" s="102"/>
+      <c r="T5" s="114"/>
+      <c r="U5" s="120"/>
+      <c r="V5" s="103"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -26626,17 +29756,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="105" t="s">
+      <c r="C60" s="106" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="106"/>
-      <c r="E60" s="106"/>
-      <c r="F60" s="106"/>
-      <c r="G60" s="106"/>
-      <c r="H60" s="106"/>
-      <c r="I60" s="106"/>
-      <c r="J60" s="106"/>
-      <c r="K60" s="107"/>
+      <c r="D60" s="107"/>
+      <c r="E60" s="107"/>
+      <c r="F60" s="107"/>
+      <c r="G60" s="107"/>
+      <c r="H60" s="107"/>
+      <c r="I60" s="107"/>
+      <c r="J60" s="107"/>
+      <c r="K60" s="108"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -26945,21 +30075,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="108" t="s">
+      <c r="I1" s="109" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="108"/>
-      <c r="K1" s="108"/>
-      <c r="L1" s="108"/>
-      <c r="M1" s="108"/>
-      <c r="N1" s="108"/>
-      <c r="O1" s="108"/>
-      <c r="P1" s="108"/>
-      <c r="Q1" s="108"/>
-      <c r="R1" s="108"/>
-      <c r="S1" s="108"/>
-      <c r="T1" s="108"/>
-      <c r="U1" s="108"/>
+      <c r="J1" s="109"/>
+      <c r="K1" s="109"/>
+      <c r="L1" s="109"/>
+      <c r="M1" s="109"/>
+      <c r="N1" s="109"/>
+      <c r="O1" s="109"/>
+      <c r="P1" s="109"/>
+      <c r="Q1" s="109"/>
+      <c r="R1" s="109"/>
+      <c r="S1" s="109"/>
+      <c r="T1" s="109"/>
+      <c r="U1" s="109"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -26971,17 +30101,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="109" t="s">
+      <c r="C4" s="110" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="109"/>
-      <c r="E4" s="109"/>
-      <c r="F4" s="109"/>
-      <c r="G4" s="109"/>
-      <c r="H4" s="109"/>
-      <c r="I4" s="109"/>
-      <c r="J4" s="110"/>
-      <c r="K4" s="111"/>
+      <c r="D4" s="110"/>
+      <c r="E4" s="110"/>
+      <c r="F4" s="110"/>
+      <c r="G4" s="110"/>
+      <c r="H4" s="110"/>
+      <c r="I4" s="110"/>
+      <c r="J4" s="111"/>
+      <c r="K4" s="112"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -27001,13 +30131,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="112" t="s">
+      <c r="T4" s="113" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="118" t="s">
+      <c r="U4" s="119" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="101" t="s">
+      <c r="V4" s="102" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -27047,10 +30177,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="116" t="s">
+      <c r="J5" s="117" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="117"/>
+      <c r="K5" s="118"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -27058,9 +30188,9 @@
       <c r="Q5" s="97"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="113"/>
-      <c r="U5" s="119"/>
-      <c r="V5" s="102"/>
+      <c r="T5" s="114"/>
+      <c r="U5" s="120"/>
+      <c r="V5" s="103"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -29760,17 +32890,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="105" t="s">
+      <c r="C60" s="106" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="106"/>
-      <c r="E60" s="106"/>
-      <c r="F60" s="106"/>
-      <c r="G60" s="106"/>
-      <c r="H60" s="106"/>
-      <c r="I60" s="106"/>
-      <c r="J60" s="106"/>
-      <c r="K60" s="107"/>
+      <c r="D60" s="107"/>
+      <c r="E60" s="107"/>
+      <c r="F60" s="107"/>
+      <c r="G60" s="107"/>
+      <c r="H60" s="107"/>
+      <c r="I60" s="107"/>
+      <c r="J60" s="107"/>
+      <c r="K60" s="108"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -30079,21 +33209,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="108" t="s">
+      <c r="I1" s="109" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="108"/>
-      <c r="K1" s="108"/>
-      <c r="L1" s="108"/>
-      <c r="M1" s="108"/>
-      <c r="N1" s="108"/>
-      <c r="O1" s="108"/>
-      <c r="P1" s="108"/>
-      <c r="Q1" s="108"/>
-      <c r="R1" s="108"/>
-      <c r="S1" s="108"/>
-      <c r="T1" s="108"/>
-      <c r="U1" s="108"/>
+      <c r="J1" s="109"/>
+      <c r="K1" s="109"/>
+      <c r="L1" s="109"/>
+      <c r="M1" s="109"/>
+      <c r="N1" s="109"/>
+      <c r="O1" s="109"/>
+      <c r="P1" s="109"/>
+      <c r="Q1" s="109"/>
+      <c r="R1" s="109"/>
+      <c r="S1" s="109"/>
+      <c r="T1" s="109"/>
+      <c r="U1" s="109"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -30105,17 +33235,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="109" t="s">
+      <c r="C4" s="110" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="109"/>
-      <c r="E4" s="109"/>
-      <c r="F4" s="109"/>
-      <c r="G4" s="109"/>
-      <c r="H4" s="109"/>
-      <c r="I4" s="109"/>
-      <c r="J4" s="110"/>
-      <c r="K4" s="111"/>
+      <c r="D4" s="110"/>
+      <c r="E4" s="110"/>
+      <c r="F4" s="110"/>
+      <c r="G4" s="110"/>
+      <c r="H4" s="110"/>
+      <c r="I4" s="110"/>
+      <c r="J4" s="111"/>
+      <c r="K4" s="112"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -30135,13 +33265,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="112" t="s">
+      <c r="T4" s="113" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="118" t="s">
+      <c r="U4" s="119" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="101" t="s">
+      <c r="V4" s="102" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -30181,10 +33311,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="116" t="s">
+      <c r="J5" s="117" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="117"/>
+      <c r="K5" s="118"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -30192,9 +33322,9 @@
       <c r="Q5" s="97"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="113"/>
-      <c r="U5" s="119"/>
-      <c r="V5" s="102"/>
+      <c r="T5" s="114"/>
+      <c r="U5" s="120"/>
+      <c r="V5" s="103"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -32884,17 +36014,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="105" t="s">
+      <c r="C60" s="106" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="106"/>
-      <c r="E60" s="106"/>
-      <c r="F60" s="106"/>
-      <c r="G60" s="106"/>
-      <c r="H60" s="106"/>
-      <c r="I60" s="106"/>
-      <c r="J60" s="106"/>
-      <c r="K60" s="107"/>
+      <c r="D60" s="107"/>
+      <c r="E60" s="107"/>
+      <c r="F60" s="107"/>
+      <c r="G60" s="107"/>
+      <c r="H60" s="107"/>
+      <c r="I60" s="107"/>
+      <c r="J60" s="107"/>
+      <c r="K60" s="108"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -33203,21 +36333,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="108" t="s">
+      <c r="I1" s="109" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="108"/>
-      <c r="K1" s="108"/>
-      <c r="L1" s="108"/>
-      <c r="M1" s="108"/>
-      <c r="N1" s="108"/>
-      <c r="O1" s="108"/>
-      <c r="P1" s="108"/>
-      <c r="Q1" s="108"/>
-      <c r="R1" s="108"/>
-      <c r="S1" s="108"/>
-      <c r="T1" s="108"/>
-      <c r="U1" s="108"/>
+      <c r="J1" s="109"/>
+      <c r="K1" s="109"/>
+      <c r="L1" s="109"/>
+      <c r="M1" s="109"/>
+      <c r="N1" s="109"/>
+      <c r="O1" s="109"/>
+      <c r="P1" s="109"/>
+      <c r="Q1" s="109"/>
+      <c r="R1" s="109"/>
+      <c r="S1" s="109"/>
+      <c r="T1" s="109"/>
+      <c r="U1" s="109"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -33229,17 +36359,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="109" t="s">
+      <c r="C4" s="110" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="109"/>
-      <c r="E4" s="109"/>
-      <c r="F4" s="109"/>
-      <c r="G4" s="109"/>
-      <c r="H4" s="109"/>
-      <c r="I4" s="109"/>
-      <c r="J4" s="110"/>
-      <c r="K4" s="111"/>
+      <c r="D4" s="110"/>
+      <c r="E4" s="110"/>
+      <c r="F4" s="110"/>
+      <c r="G4" s="110"/>
+      <c r="H4" s="110"/>
+      <c r="I4" s="110"/>
+      <c r="J4" s="111"/>
+      <c r="K4" s="112"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -33259,13 +36389,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="112" t="s">
+      <c r="T4" s="113" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="118" t="s">
+      <c r="U4" s="119" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="101" t="s">
+      <c r="V4" s="102" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -33305,10 +36435,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="116" t="s">
+      <c r="J5" s="117" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="117"/>
+      <c r="K5" s="118"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -33316,9 +36446,9 @@
       <c r="Q5" s="98"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="113"/>
-      <c r="U5" s="119"/>
-      <c r="V5" s="102"/>
+      <c r="T5" s="114"/>
+      <c r="U5" s="120"/>
+      <c r="V5" s="103"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -36033,17 +39163,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="105" t="s">
+      <c r="C60" s="106" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="106"/>
-      <c r="E60" s="106"/>
-      <c r="F60" s="106"/>
-      <c r="G60" s="106"/>
-      <c r="H60" s="106"/>
-      <c r="I60" s="106"/>
-      <c r="J60" s="106"/>
-      <c r="K60" s="107"/>
+      <c r="D60" s="107"/>
+      <c r="E60" s="107"/>
+      <c r="F60" s="107"/>
+      <c r="G60" s="107"/>
+      <c r="H60" s="107"/>
+      <c r="I60" s="107"/>
+      <c r="J60" s="107"/>
+      <c r="K60" s="108"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -36352,21 +39482,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="108" t="s">
+      <c r="I1" s="109" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="108"/>
-      <c r="K1" s="108"/>
-      <c r="L1" s="108"/>
-      <c r="M1" s="108"/>
-      <c r="N1" s="108"/>
-      <c r="O1" s="108"/>
-      <c r="P1" s="108"/>
-      <c r="Q1" s="108"/>
-      <c r="R1" s="108"/>
-      <c r="S1" s="108"/>
-      <c r="T1" s="108"/>
-      <c r="U1" s="108"/>
+      <c r="J1" s="109"/>
+      <c r="K1" s="109"/>
+      <c r="L1" s="109"/>
+      <c r="M1" s="109"/>
+      <c r="N1" s="109"/>
+      <c r="O1" s="109"/>
+      <c r="P1" s="109"/>
+      <c r="Q1" s="109"/>
+      <c r="R1" s="109"/>
+      <c r="S1" s="109"/>
+      <c r="T1" s="109"/>
+      <c r="U1" s="109"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -36378,17 +39508,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="109" t="s">
+      <c r="C4" s="110" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="109"/>
-      <c r="E4" s="109"/>
-      <c r="F4" s="109"/>
-      <c r="G4" s="109"/>
-      <c r="H4" s="109"/>
-      <c r="I4" s="109"/>
-      <c r="J4" s="110"/>
-      <c r="K4" s="111"/>
+      <c r="D4" s="110"/>
+      <c r="E4" s="110"/>
+      <c r="F4" s="110"/>
+      <c r="G4" s="110"/>
+      <c r="H4" s="110"/>
+      <c r="I4" s="110"/>
+      <c r="J4" s="111"/>
+      <c r="K4" s="112"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -36408,13 +39538,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="112" t="s">
+      <c r="T4" s="113" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="118" t="s">
+      <c r="U4" s="119" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="101" t="s">
+      <c r="V4" s="102" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -36454,10 +39584,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="116" t="s">
+      <c r="J5" s="117" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="117"/>
+      <c r="K5" s="118"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -36465,9 +39595,9 @@
       <c r="Q5" s="98"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="113"/>
-      <c r="U5" s="119"/>
-      <c r="V5" s="102"/>
+      <c r="T5" s="114"/>
+      <c r="U5" s="120"/>
+      <c r="V5" s="103"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -39172,17 +42302,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="105" t="s">
+      <c r="C60" s="106" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="106"/>
-      <c r="E60" s="106"/>
-      <c r="F60" s="106"/>
-      <c r="G60" s="106"/>
-      <c r="H60" s="106"/>
-      <c r="I60" s="106"/>
-      <c r="J60" s="106"/>
-      <c r="K60" s="107"/>
+      <c r="D60" s="107"/>
+      <c r="E60" s="107"/>
+      <c r="F60" s="107"/>
+      <c r="G60" s="107"/>
+      <c r="H60" s="107"/>
+      <c r="I60" s="107"/>
+      <c r="J60" s="107"/>
+      <c r="K60" s="108"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -39491,21 +42621,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="108" t="s">
+      <c r="I1" s="109" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="108"/>
-      <c r="K1" s="108"/>
-      <c r="L1" s="108"/>
-      <c r="M1" s="108"/>
-      <c r="N1" s="108"/>
-      <c r="O1" s="108"/>
-      <c r="P1" s="108"/>
-      <c r="Q1" s="108"/>
-      <c r="R1" s="108"/>
-      <c r="S1" s="108"/>
-      <c r="T1" s="108"/>
-      <c r="U1" s="108"/>
+      <c r="J1" s="109"/>
+      <c r="K1" s="109"/>
+      <c r="L1" s="109"/>
+      <c r="M1" s="109"/>
+      <c r="N1" s="109"/>
+      <c r="O1" s="109"/>
+      <c r="P1" s="109"/>
+      <c r="Q1" s="109"/>
+      <c r="R1" s="109"/>
+      <c r="S1" s="109"/>
+      <c r="T1" s="109"/>
+      <c r="U1" s="109"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -39517,17 +42647,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="109" t="s">
+      <c r="C4" s="110" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="109"/>
-      <c r="E4" s="109"/>
-      <c r="F4" s="109"/>
-      <c r="G4" s="109"/>
-      <c r="H4" s="109"/>
-      <c r="I4" s="109"/>
-      <c r="J4" s="110"/>
-      <c r="K4" s="111"/>
+      <c r="D4" s="110"/>
+      <c r="E4" s="110"/>
+      <c r="F4" s="110"/>
+      <c r="G4" s="110"/>
+      <c r="H4" s="110"/>
+      <c r="I4" s="110"/>
+      <c r="J4" s="111"/>
+      <c r="K4" s="112"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -39547,13 +42677,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="112" t="s">
+      <c r="T4" s="113" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="118" t="s">
+      <c r="U4" s="119" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="101" t="s">
+      <c r="V4" s="102" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -39593,10 +42723,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="116" t="s">
+      <c r="J5" s="117" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="117"/>
+      <c r="K5" s="118"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -39604,9 +42734,9 @@
       <c r="Q5" s="98"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="113"/>
-      <c r="U5" s="119"/>
-      <c r="V5" s="102"/>
+      <c r="T5" s="114"/>
+      <c r="U5" s="120"/>
+      <c r="V5" s="103"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -42308,17 +45438,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="105" t="s">
+      <c r="C60" s="106" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="106"/>
-      <c r="E60" s="106"/>
-      <c r="F60" s="106"/>
-      <c r="G60" s="106"/>
-      <c r="H60" s="106"/>
-      <c r="I60" s="106"/>
-      <c r="J60" s="106"/>
-      <c r="K60" s="107"/>
+      <c r="D60" s="107"/>
+      <c r="E60" s="107"/>
+      <c r="F60" s="107"/>
+      <c r="G60" s="107"/>
+      <c r="H60" s="107"/>
+      <c r="I60" s="107"/>
+      <c r="J60" s="107"/>
+      <c r="K60" s="108"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -42627,21 +45757,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="108" t="s">
+      <c r="I1" s="109" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="108"/>
-      <c r="K1" s="108"/>
-      <c r="L1" s="108"/>
-      <c r="M1" s="108"/>
-      <c r="N1" s="108"/>
-      <c r="O1" s="108"/>
-      <c r="P1" s="108"/>
-      <c r="Q1" s="108"/>
-      <c r="R1" s="108"/>
-      <c r="S1" s="108"/>
-      <c r="T1" s="108"/>
-      <c r="U1" s="108"/>
+      <c r="J1" s="109"/>
+      <c r="K1" s="109"/>
+      <c r="L1" s="109"/>
+      <c r="M1" s="109"/>
+      <c r="N1" s="109"/>
+      <c r="O1" s="109"/>
+      <c r="P1" s="109"/>
+      <c r="Q1" s="109"/>
+      <c r="R1" s="109"/>
+      <c r="S1" s="109"/>
+      <c r="T1" s="109"/>
+      <c r="U1" s="109"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -42653,17 +45783,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="109" t="s">
+      <c r="C4" s="110" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="109"/>
-      <c r="E4" s="109"/>
-      <c r="F4" s="109"/>
-      <c r="G4" s="109"/>
-      <c r="H4" s="109"/>
-      <c r="I4" s="109"/>
-      <c r="J4" s="110"/>
-      <c r="K4" s="111"/>
+      <c r="D4" s="110"/>
+      <c r="E4" s="110"/>
+      <c r="F4" s="110"/>
+      <c r="G4" s="110"/>
+      <c r="H4" s="110"/>
+      <c r="I4" s="110"/>
+      <c r="J4" s="111"/>
+      <c r="K4" s="112"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -42683,13 +45813,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="112" t="s">
+      <c r="T4" s="113" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="118" t="s">
+      <c r="U4" s="119" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="101" t="s">
+      <c r="V4" s="102" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -42729,10 +45859,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="116" t="s">
+      <c r="J5" s="117" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="117"/>
+      <c r="K5" s="118"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -42740,9 +45870,9 @@
       <c r="Q5" s="98"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="113"/>
-      <c r="U5" s="119"/>
-      <c r="V5" s="102"/>
+      <c r="T5" s="114"/>
+      <c r="U5" s="120"/>
+      <c r="V5" s="103"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -45454,17 +48584,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="105" t="s">
+      <c r="C60" s="106" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="106"/>
-      <c r="E60" s="106"/>
-      <c r="F60" s="106"/>
-      <c r="G60" s="106"/>
-      <c r="H60" s="106"/>
-      <c r="I60" s="106"/>
-      <c r="J60" s="106"/>
-      <c r="K60" s="107"/>
+      <c r="D60" s="107"/>
+      <c r="E60" s="107"/>
+      <c r="F60" s="107"/>
+      <c r="G60" s="107"/>
+      <c r="H60" s="107"/>
+      <c r="I60" s="107"/>
+      <c r="J60" s="107"/>
+      <c r="K60" s="108"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>

--- a/GBDS AUGUST FILES 2026/INVENTORY COUNT SHEET - AUGUST 2026.xlsx
+++ b/GBDS AUGUST FILES 2026/INVENTORY COUNT SHEET - AUGUST 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS AUGUST FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46E6EEEB-A172-4BB2-AC72-76B1FEA93262}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F79B0F49-671B-440B-82EF-E317E23A2229}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="5" activeTab="14" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="6" activeTab="15" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
   </bookViews>
   <sheets>
     <sheet name="SAMPLE" sheetId="32" r:id="rId1"/>
@@ -28,6 +28,7 @@
     <sheet name="08-17-2026" sheetId="80" r:id="rId13"/>
     <sheet name="08-18-2026" sheetId="81" r:id="rId14"/>
     <sheet name="08-19-2026" sheetId="82" r:id="rId15"/>
+    <sheet name="08-20-2026" sheetId="83" r:id="rId16"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'08-03-2026'!$A$1:$W$59</definedName>
@@ -44,6 +45,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="12">'08-17-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="13">'08-18-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="14">'08-19-2026'!$A$1:$W$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="15">'08-20-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">SAMPLE!$A$1:$W$85</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -62,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1260" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1344" uniqueCount="86">
   <si>
     <t>ROUTE 1</t>
   </si>
@@ -312,6 +314,15 @@
   </si>
   <si>
     <t>DATE: 08/17/2026</t>
+  </si>
+  <si>
+    <t>DATE: 08/20/2026</t>
+  </si>
+  <si>
+    <t>DATE: 08/19/2026</t>
+  </si>
+  <si>
+    <t>DATE: 08/18/2026</t>
   </si>
 </sst>
 </file>
@@ -1298,7 +1309,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="121">
+  <cellXfs count="122">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1584,6 +1595,9 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="63" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2015,21 +2029,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="109" t="s">
+      <c r="I1" s="110" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="109"/>
-      <c r="K1" s="109"/>
-      <c r="L1" s="109"/>
-      <c r="M1" s="109"/>
-      <c r="N1" s="109"/>
-      <c r="O1" s="109"/>
-      <c r="P1" s="109"/>
-      <c r="Q1" s="109"/>
-      <c r="R1" s="109"/>
-      <c r="S1" s="109"/>
-      <c r="T1" s="109"/>
-      <c r="U1" s="109"/>
+      <c r="J1" s="110"/>
+      <c r="K1" s="110"/>
+      <c r="L1" s="110"/>
+      <c r="M1" s="110"/>
+      <c r="N1" s="110"/>
+      <c r="O1" s="110"/>
+      <c r="P1" s="110"/>
+      <c r="Q1" s="110"/>
+      <c r="R1" s="110"/>
+      <c r="S1" s="110"/>
+      <c r="T1" s="110"/>
+      <c r="U1" s="110"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -2041,17 +2055,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="110" t="s">
+      <c r="C4" s="111" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="110"/>
-      <c r="E4" s="110"/>
-      <c r="F4" s="110"/>
-      <c r="G4" s="110"/>
-      <c r="H4" s="110"/>
-      <c r="I4" s="110"/>
-      <c r="J4" s="111"/>
-      <c r="K4" s="112"/>
+      <c r="D4" s="111"/>
+      <c r="E4" s="111"/>
+      <c r="F4" s="111"/>
+      <c r="G4" s="111"/>
+      <c r="H4" s="111"/>
+      <c r="I4" s="111"/>
+      <c r="J4" s="112"/>
+      <c r="K4" s="113"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -2071,13 +2085,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="113" t="s">
+      <c r="T4" s="114" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="115" t="s">
+      <c r="U4" s="116" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="102" t="s">
+      <c r="V4" s="103" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -2117,10 +2131,10 @@
       <c r="I5" s="93" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="104" t="s">
+      <c r="J5" s="105" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="105"/>
+      <c r="K5" s="106"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -2128,9 +2142,9 @@
       <c r="Q5" s="89"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="114"/>
-      <c r="U5" s="116"/>
-      <c r="V5" s="103"/>
+      <c r="T5" s="115"/>
+      <c r="U5" s="117"/>
+      <c r="V5" s="104"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -4661,17 +4675,17 @@
       <c r="B62" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C62" s="106" t="s">
+      <c r="C62" s="107" t="s">
         <v>41</v>
       </c>
-      <c r="D62" s="107"/>
-      <c r="E62" s="107"/>
-      <c r="F62" s="107"/>
-      <c r="G62" s="107"/>
-      <c r="H62" s="107"/>
-      <c r="I62" s="107"/>
-      <c r="J62" s="107"/>
-      <c r="K62" s="108"/>
+      <c r="D62" s="108"/>
+      <c r="E62" s="108"/>
+      <c r="F62" s="108"/>
+      <c r="G62" s="108"/>
+      <c r="H62" s="108"/>
+      <c r="I62" s="108"/>
+      <c r="J62" s="108"/>
+      <c r="K62" s="109"/>
       <c r="U62" s="24" t="s">
         <v>51</v>
       </c>
@@ -4980,21 +4994,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="109" t="s">
+      <c r="I1" s="110" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="109"/>
-      <c r="K1" s="109"/>
-      <c r="L1" s="109"/>
-      <c r="M1" s="109"/>
-      <c r="N1" s="109"/>
-      <c r="O1" s="109"/>
-      <c r="P1" s="109"/>
-      <c r="Q1" s="109"/>
-      <c r="R1" s="109"/>
-      <c r="S1" s="109"/>
-      <c r="T1" s="109"/>
-      <c r="U1" s="109"/>
+      <c r="J1" s="110"/>
+      <c r="K1" s="110"/>
+      <c r="L1" s="110"/>
+      <c r="M1" s="110"/>
+      <c r="N1" s="110"/>
+      <c r="O1" s="110"/>
+      <c r="P1" s="110"/>
+      <c r="Q1" s="110"/>
+      <c r="R1" s="110"/>
+      <c r="S1" s="110"/>
+      <c r="T1" s="110"/>
+      <c r="U1" s="110"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -5006,17 +5020,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="110" t="s">
+      <c r="C4" s="111" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="110"/>
-      <c r="E4" s="110"/>
-      <c r="F4" s="110"/>
-      <c r="G4" s="110"/>
-      <c r="H4" s="110"/>
-      <c r="I4" s="110"/>
-      <c r="J4" s="111"/>
-      <c r="K4" s="112"/>
+      <c r="D4" s="111"/>
+      <c r="E4" s="111"/>
+      <c r="F4" s="111"/>
+      <c r="G4" s="111"/>
+      <c r="H4" s="111"/>
+      <c r="I4" s="111"/>
+      <c r="J4" s="112"/>
+      <c r="K4" s="113"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -5036,13 +5050,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="113" t="s">
+      <c r="T4" s="114" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="119" t="s">
+      <c r="U4" s="120" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="102" t="s">
+      <c r="V4" s="103" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -5082,10 +5096,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="117" t="s">
+      <c r="J5" s="118" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="118"/>
+      <c r="K5" s="119"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -5093,9 +5107,9 @@
       <c r="Q5" s="99"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="114"/>
-      <c r="U5" s="120"/>
-      <c r="V5" s="103"/>
+      <c r="T5" s="115"/>
+      <c r="U5" s="121"/>
+      <c r="V5" s="104"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -7806,17 +7820,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="106" t="s">
+      <c r="C60" s="107" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="107"/>
-      <c r="E60" s="107"/>
-      <c r="F60" s="107"/>
-      <c r="G60" s="107"/>
-      <c r="H60" s="107"/>
-      <c r="I60" s="107"/>
-      <c r="J60" s="107"/>
-      <c r="K60" s="108"/>
+      <c r="D60" s="108"/>
+      <c r="E60" s="108"/>
+      <c r="F60" s="108"/>
+      <c r="G60" s="108"/>
+      <c r="H60" s="108"/>
+      <c r="I60" s="108"/>
+      <c r="J60" s="108"/>
+      <c r="K60" s="109"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -8125,21 +8139,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="109" t="s">
+      <c r="I1" s="110" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="109"/>
-      <c r="K1" s="109"/>
-      <c r="L1" s="109"/>
-      <c r="M1" s="109"/>
-      <c r="N1" s="109"/>
-      <c r="O1" s="109"/>
-      <c r="P1" s="109"/>
-      <c r="Q1" s="109"/>
-      <c r="R1" s="109"/>
-      <c r="S1" s="109"/>
-      <c r="T1" s="109"/>
-      <c r="U1" s="109"/>
+      <c r="J1" s="110"/>
+      <c r="K1" s="110"/>
+      <c r="L1" s="110"/>
+      <c r="M1" s="110"/>
+      <c r="N1" s="110"/>
+      <c r="O1" s="110"/>
+      <c r="P1" s="110"/>
+      <c r="Q1" s="110"/>
+      <c r="R1" s="110"/>
+      <c r="S1" s="110"/>
+      <c r="T1" s="110"/>
+      <c r="U1" s="110"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -8151,17 +8165,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="110" t="s">
+      <c r="C4" s="111" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="110"/>
-      <c r="E4" s="110"/>
-      <c r="F4" s="110"/>
-      <c r="G4" s="110"/>
-      <c r="H4" s="110"/>
-      <c r="I4" s="110"/>
-      <c r="J4" s="111"/>
-      <c r="K4" s="112"/>
+      <c r="D4" s="111"/>
+      <c r="E4" s="111"/>
+      <c r="F4" s="111"/>
+      <c r="G4" s="111"/>
+      <c r="H4" s="111"/>
+      <c r="I4" s="111"/>
+      <c r="J4" s="112"/>
+      <c r="K4" s="113"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -8181,13 +8195,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="113" t="s">
+      <c r="T4" s="114" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="119" t="s">
+      <c r="U4" s="120" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="102" t="s">
+      <c r="V4" s="103" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -8227,10 +8241,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="117" t="s">
+      <c r="J5" s="118" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="118"/>
+      <c r="K5" s="119"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -8238,9 +8252,9 @@
       <c r="Q5" s="99"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="114"/>
-      <c r="U5" s="120"/>
-      <c r="V5" s="103"/>
+      <c r="T5" s="115"/>
+      <c r="U5" s="121"/>
+      <c r="V5" s="104"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -10953,17 +10967,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="106" t="s">
+      <c r="C60" s="107" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="107"/>
-      <c r="E60" s="107"/>
-      <c r="F60" s="107"/>
-      <c r="G60" s="107"/>
-      <c r="H60" s="107"/>
-      <c r="I60" s="107"/>
-      <c r="J60" s="107"/>
-      <c r="K60" s="108"/>
+      <c r="D60" s="108"/>
+      <c r="E60" s="108"/>
+      <c r="F60" s="108"/>
+      <c r="G60" s="108"/>
+      <c r="H60" s="108"/>
+      <c r="I60" s="108"/>
+      <c r="J60" s="108"/>
+      <c r="K60" s="109"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -11272,21 +11286,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="109" t="s">
+      <c r="I1" s="110" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="109"/>
-      <c r="K1" s="109"/>
-      <c r="L1" s="109"/>
-      <c r="M1" s="109"/>
-      <c r="N1" s="109"/>
-      <c r="O1" s="109"/>
-      <c r="P1" s="109"/>
-      <c r="Q1" s="109"/>
-      <c r="R1" s="109"/>
-      <c r="S1" s="109"/>
-      <c r="T1" s="109"/>
-      <c r="U1" s="109"/>
+      <c r="J1" s="110"/>
+      <c r="K1" s="110"/>
+      <c r="L1" s="110"/>
+      <c r="M1" s="110"/>
+      <c r="N1" s="110"/>
+      <c r="O1" s="110"/>
+      <c r="P1" s="110"/>
+      <c r="Q1" s="110"/>
+      <c r="R1" s="110"/>
+      <c r="S1" s="110"/>
+      <c r="T1" s="110"/>
+      <c r="U1" s="110"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -11298,17 +11312,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="110" t="s">
+      <c r="C4" s="111" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="110"/>
-      <c r="E4" s="110"/>
-      <c r="F4" s="110"/>
-      <c r="G4" s="110"/>
-      <c r="H4" s="110"/>
-      <c r="I4" s="110"/>
-      <c r="J4" s="111"/>
-      <c r="K4" s="112"/>
+      <c r="D4" s="111"/>
+      <c r="E4" s="111"/>
+      <c r="F4" s="111"/>
+      <c r="G4" s="111"/>
+      <c r="H4" s="111"/>
+      <c r="I4" s="111"/>
+      <c r="J4" s="112"/>
+      <c r="K4" s="113"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -11328,13 +11342,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="113" t="s">
+      <c r="T4" s="114" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="119" t="s">
+      <c r="U4" s="120" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="102" t="s">
+      <c r="V4" s="103" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -11374,10 +11388,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="117" t="s">
+      <c r="J5" s="118" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="118"/>
+      <c r="K5" s="119"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -11385,9 +11399,9 @@
       <c r="Q5" s="99"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="114"/>
-      <c r="U5" s="120"/>
-      <c r="V5" s="103"/>
+      <c r="T5" s="115"/>
+      <c r="U5" s="121"/>
+      <c r="V5" s="104"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -14089,17 +14103,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="106" t="s">
+      <c r="C60" s="107" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="107"/>
-      <c r="E60" s="107"/>
-      <c r="F60" s="107"/>
-      <c r="G60" s="107"/>
-      <c r="H60" s="107"/>
-      <c r="I60" s="107"/>
-      <c r="J60" s="107"/>
-      <c r="K60" s="108"/>
+      <c r="D60" s="108"/>
+      <c r="E60" s="108"/>
+      <c r="F60" s="108"/>
+      <c r="G60" s="108"/>
+      <c r="H60" s="108"/>
+      <c r="I60" s="108"/>
+      <c r="J60" s="108"/>
+      <c r="K60" s="109"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -14408,21 +14422,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="109" t="s">
+      <c r="I1" s="110" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="109"/>
-      <c r="K1" s="109"/>
-      <c r="L1" s="109"/>
-      <c r="M1" s="109"/>
-      <c r="N1" s="109"/>
-      <c r="O1" s="109"/>
-      <c r="P1" s="109"/>
-      <c r="Q1" s="109"/>
-      <c r="R1" s="109"/>
-      <c r="S1" s="109"/>
-      <c r="T1" s="109"/>
-      <c r="U1" s="109"/>
+      <c r="J1" s="110"/>
+      <c r="K1" s="110"/>
+      <c r="L1" s="110"/>
+      <c r="M1" s="110"/>
+      <c r="N1" s="110"/>
+      <c r="O1" s="110"/>
+      <c r="P1" s="110"/>
+      <c r="Q1" s="110"/>
+      <c r="R1" s="110"/>
+      <c r="S1" s="110"/>
+      <c r="T1" s="110"/>
+      <c r="U1" s="110"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -14434,17 +14448,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="110" t="s">
+      <c r="C4" s="111" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="110"/>
-      <c r="E4" s="110"/>
-      <c r="F4" s="110"/>
-      <c r="G4" s="110"/>
-      <c r="H4" s="110"/>
-      <c r="I4" s="110"/>
-      <c r="J4" s="111"/>
-      <c r="K4" s="112"/>
+      <c r="D4" s="111"/>
+      <c r="E4" s="111"/>
+      <c r="F4" s="111"/>
+      <c r="G4" s="111"/>
+      <c r="H4" s="111"/>
+      <c r="I4" s="111"/>
+      <c r="J4" s="112"/>
+      <c r="K4" s="113"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -14464,13 +14478,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="113" t="s">
+      <c r="T4" s="114" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="119" t="s">
+      <c r="U4" s="120" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="102" t="s">
+      <c r="V4" s="103" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -14510,10 +14524,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="117" t="s">
+      <c r="J5" s="118" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="118"/>
+      <c r="K5" s="119"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -14521,9 +14535,9 @@
       <c r="Q5" s="99"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="114"/>
-      <c r="U5" s="120"/>
-      <c r="V5" s="103"/>
+      <c r="T5" s="115"/>
+      <c r="U5" s="121"/>
+      <c r="V5" s="104"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -17224,17 +17238,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="106" t="s">
+      <c r="C60" s="107" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="107"/>
-      <c r="E60" s="107"/>
-      <c r="F60" s="107"/>
-      <c r="G60" s="107"/>
-      <c r="H60" s="107"/>
-      <c r="I60" s="107"/>
-      <c r="J60" s="107"/>
-      <c r="K60" s="108"/>
+      <c r="D60" s="108"/>
+      <c r="E60" s="108"/>
+      <c r="F60" s="108"/>
+      <c r="G60" s="108"/>
+      <c r="H60" s="108"/>
+      <c r="I60" s="108"/>
+      <c r="J60" s="108"/>
+      <c r="K60" s="109"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -17543,25 +17557,25 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="109" t="s">
+      <c r="I1" s="110" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="109"/>
-      <c r="K1" s="109"/>
-      <c r="L1" s="109"/>
-      <c r="M1" s="109"/>
-      <c r="N1" s="109"/>
-      <c r="O1" s="109"/>
-      <c r="P1" s="109"/>
-      <c r="Q1" s="109"/>
-      <c r="R1" s="109"/>
-      <c r="S1" s="109"/>
-      <c r="T1" s="109"/>
-      <c r="U1" s="109"/>
+      <c r="J1" s="110"/>
+      <c r="K1" s="110"/>
+      <c r="L1" s="110"/>
+      <c r="M1" s="110"/>
+      <c r="N1" s="110"/>
+      <c r="O1" s="110"/>
+      <c r="P1" s="110"/>
+      <c r="Q1" s="110"/>
+      <c r="R1" s="110"/>
+      <c r="S1" s="110"/>
+      <c r="T1" s="110"/>
+      <c r="U1" s="110"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -17569,17 +17583,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="110" t="s">
+      <c r="C4" s="111" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="110"/>
-      <c r="E4" s="110"/>
-      <c r="F4" s="110"/>
-      <c r="G4" s="110"/>
-      <c r="H4" s="110"/>
-      <c r="I4" s="110"/>
-      <c r="J4" s="111"/>
-      <c r="K4" s="112"/>
+      <c r="D4" s="111"/>
+      <c r="E4" s="111"/>
+      <c r="F4" s="111"/>
+      <c r="G4" s="111"/>
+      <c r="H4" s="111"/>
+      <c r="I4" s="111"/>
+      <c r="J4" s="112"/>
+      <c r="K4" s="113"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -17599,13 +17613,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="113" t="s">
+      <c r="T4" s="114" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="119" t="s">
+      <c r="U4" s="120" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="102" t="s">
+      <c r="V4" s="103" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -17645,10 +17659,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="117" t="s">
+      <c r="J5" s="118" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="118"/>
+      <c r="K5" s="119"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -17656,9 +17670,9 @@
       <c r="Q5" s="100"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="114"/>
-      <c r="U5" s="120"/>
-      <c r="V5" s="103"/>
+      <c r="T5" s="115"/>
+      <c r="U5" s="121"/>
+      <c r="V5" s="104"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -20353,17 +20367,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="106" t="s">
+      <c r="C60" s="107" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="107"/>
-      <c r="E60" s="107"/>
-      <c r="F60" s="107"/>
-      <c r="G60" s="107"/>
-      <c r="H60" s="107"/>
-      <c r="I60" s="107"/>
-      <c r="J60" s="107"/>
-      <c r="K60" s="108"/>
+      <c r="D60" s="108"/>
+      <c r="E60" s="108"/>
+      <c r="F60" s="108"/>
+      <c r="G60" s="108"/>
+      <c r="H60" s="108"/>
+      <c r="I60" s="108"/>
+      <c r="J60" s="108"/>
+      <c r="K60" s="109"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -20672,25 +20686,25 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="109" t="s">
+      <c r="I1" s="110" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="109"/>
-      <c r="K1" s="109"/>
-      <c r="L1" s="109"/>
-      <c r="M1" s="109"/>
-      <c r="N1" s="109"/>
-      <c r="O1" s="109"/>
-      <c r="P1" s="109"/>
-      <c r="Q1" s="109"/>
-      <c r="R1" s="109"/>
-      <c r="S1" s="109"/>
-      <c r="T1" s="109"/>
-      <c r="U1" s="109"/>
+      <c r="J1" s="110"/>
+      <c r="K1" s="110"/>
+      <c r="L1" s="110"/>
+      <c r="M1" s="110"/>
+      <c r="N1" s="110"/>
+      <c r="O1" s="110"/>
+      <c r="P1" s="110"/>
+      <c r="Q1" s="110"/>
+      <c r="R1" s="110"/>
+      <c r="S1" s="110"/>
+      <c r="T1" s="110"/>
+      <c r="U1" s="110"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -20698,17 +20712,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="110" t="s">
+      <c r="C4" s="111" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="110"/>
-      <c r="E4" s="110"/>
-      <c r="F4" s="110"/>
-      <c r="G4" s="110"/>
-      <c r="H4" s="110"/>
-      <c r="I4" s="110"/>
-      <c r="J4" s="111"/>
-      <c r="K4" s="112"/>
+      <c r="D4" s="111"/>
+      <c r="E4" s="111"/>
+      <c r="F4" s="111"/>
+      <c r="G4" s="111"/>
+      <c r="H4" s="111"/>
+      <c r="I4" s="111"/>
+      <c r="J4" s="112"/>
+      <c r="K4" s="113"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -20728,13 +20742,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="113" t="s">
+      <c r="T4" s="114" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="119" t="s">
+      <c r="U4" s="120" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="102" t="s">
+      <c r="V4" s="103" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -20774,10 +20788,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="117" t="s">
+      <c r="J5" s="118" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="118"/>
+      <c r="K5" s="119"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -20785,9 +20799,9 @@
       <c r="Q5" s="101"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="114"/>
-      <c r="U5" s="120"/>
-      <c r="V5" s="103"/>
+      <c r="T5" s="115"/>
+      <c r="U5" s="121"/>
+      <c r="V5" s="104"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -23478,17 +23492,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="106" t="s">
+      <c r="C60" s="107" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="107"/>
-      <c r="E60" s="107"/>
-      <c r="F60" s="107"/>
-      <c r="G60" s="107"/>
-      <c r="H60" s="107"/>
-      <c r="I60" s="107"/>
-      <c r="J60" s="107"/>
-      <c r="K60" s="108"/>
+      <c r="D60" s="108"/>
+      <c r="E60" s="108"/>
+      <c r="F60" s="108"/>
+      <c r="G60" s="108"/>
+      <c r="H60" s="108"/>
+      <c r="I60" s="108"/>
+      <c r="J60" s="108"/>
+      <c r="K60" s="109"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -23740,13 +23754,3155 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
     <mergeCell ref="C60:K60"/>
     <mergeCell ref="I1:U1"/>
     <mergeCell ref="C4:K4"/>
     <mergeCell ref="T4:T5"/>
     <mergeCell ref="U4:U5"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
+  <pageSetup paperSize="14" scale="70" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="24" max="80" man="1"/>
+  </colBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A53ACD1-5C40-4744-844F-FD1ECB768037}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BB81"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="28" customWidth="1"/>
+    <col min="3" max="6" width="10" style="9" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" style="9" customWidth="1"/>
+    <col min="8" max="8" width="7.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.85546875" style="9" customWidth="1"/>
+    <col min="11" max="11" width="7.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.42578125" style="9" customWidth="1"/>
+    <col min="13" max="13" width="10" style="9" customWidth="1"/>
+    <col min="14" max="14" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" style="9" customWidth="1"/>
+    <col min="16" max="16" width="5.5703125" style="9" customWidth="1"/>
+    <col min="17" max="17" width="10" style="9" customWidth="1"/>
+    <col min="18" max="18" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="1.42578125" style="9" customWidth="1"/>
+    <col min="20" max="20" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="9" customWidth="1"/>
+    <col min="22" max="22" width="19.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="23" max="49" width="7.28515625" style="9" customWidth="1"/>
+    <col min="50" max="50" width="1.5703125" style="9" customWidth="1"/>
+    <col min="51" max="51" width="9.42578125" style="9" customWidth="1"/>
+    <col min="52" max="52" width="1.28515625" style="9" customWidth="1"/>
+    <col min="53" max="53" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="10.28515625" style="9" bestFit="1" customWidth="1"/>
+    <col min="55" max="16384" width="9.140625" style="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="110" t="s">
+        <v>43</v>
+      </c>
+      <c r="J1" s="110"/>
+      <c r="K1" s="110"/>
+      <c r="L1" s="110"/>
+      <c r="M1" s="110"/>
+      <c r="N1" s="110"/>
+      <c r="O1" s="110"/>
+      <c r="P1" s="110"/>
+      <c r="Q1" s="110"/>
+      <c r="R1" s="110"/>
+      <c r="S1" s="110"/>
+      <c r="T1" s="110"/>
+      <c r="U1" s="110"/>
+    </row>
+    <row r="2" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="B2" s="28" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B4" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="111" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="111"/>
+      <c r="E4" s="111"/>
+      <c r="F4" s="111"/>
+      <c r="G4" s="111"/>
+      <c r="H4" s="111"/>
+      <c r="I4" s="111"/>
+      <c r="J4" s="112"/>
+      <c r="K4" s="113"/>
+      <c r="M4" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="N4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="O4" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="P4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q4" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="R4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="S4" s="9"/>
+      <c r="T4" s="114" t="s">
+        <v>68</v>
+      </c>
+      <c r="U4" s="120" t="s">
+        <v>67</v>
+      </c>
+      <c r="V4" s="103" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF4" s="11"/>
+      <c r="AG4" s="11"/>
+      <c r="AH4" s="11"/>
+      <c r="AI4" s="11"/>
+      <c r="AJ4" s="11"/>
+      <c r="AK4" s="11"/>
+      <c r="AL4" s="11"/>
+      <c r="AM4" s="11"/>
+      <c r="AN4" s="11"/>
+      <c r="AO4" s="11"/>
+      <c r="AP4" s="11"/>
+      <c r="AQ4" s="11"/>
+      <c r="AR4" s="11"/>
+      <c r="AS4" s="11"/>
+      <c r="AT4" s="11"/>
+      <c r="AU4" s="11"/>
+      <c r="AV4" s="11"/>
+      <c r="AW4" s="11"/>
+      <c r="AX4" s="11"/>
+      <c r="AY4" s="11"/>
+      <c r="AZ4" s="11"/>
+      <c r="BA4" s="11"/>
+      <c r="BB4" s="11"/>
+    </row>
+    <row r="5" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="37"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40" t="s">
+        <v>64</v>
+      </c>
+      <c r="I5" s="40" t="s">
+        <v>60</v>
+      </c>
+      <c r="J5" s="118" t="s">
+        <v>65</v>
+      </c>
+      <c r="K5" s="119"/>
+      <c r="M5" s="37"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="40"/>
+      <c r="P5" s="102"/>
+      <c r="Q5" s="102"/>
+      <c r="R5" s="38"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="115"/>
+      <c r="U5" s="121"/>
+      <c r="V5" s="104"/>
+      <c r="AF5" s="11"/>
+      <c r="AG5" s="11"/>
+      <c r="AH5" s="11"/>
+      <c r="AI5" s="11"/>
+      <c r="AJ5" s="11"/>
+      <c r="AK5" s="11"/>
+      <c r="AL5" s="11"/>
+      <c r="AM5" s="11"/>
+      <c r="AN5" s="11"/>
+      <c r="AO5" s="11"/>
+      <c r="AP5" s="11"/>
+      <c r="AQ5" s="11"/>
+      <c r="AR5" s="11"/>
+      <c r="AS5" s="11"/>
+      <c r="AT5" s="11"/>
+      <c r="AU5" s="11"/>
+      <c r="AV5" s="11"/>
+      <c r="AW5" s="11"/>
+      <c r="AX5" s="11"/>
+      <c r="AY5" s="11"/>
+      <c r="AZ5" s="11"/>
+      <c r="BA5" s="11"/>
+      <c r="BB5" s="11"/>
+    </row>
+    <row r="6" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="37"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="102"/>
+      <c r="K6" s="38"/>
+      <c r="M6" s="37"/>
+      <c r="N6" s="49"/>
+      <c r="O6" s="40"/>
+      <c r="P6" s="102"/>
+      <c r="Q6" s="102"/>
+      <c r="R6" s="38"/>
+      <c r="S6" s="9"/>
+      <c r="T6" s="39"/>
+      <c r="U6" s="39"/>
+      <c r="V6" s="39"/>
+      <c r="AF6" s="11"/>
+      <c r="AG6" s="11"/>
+      <c r="AH6" s="11"/>
+      <c r="AI6" s="11"/>
+      <c r="AJ6" s="11"/>
+      <c r="AK6" s="11"/>
+      <c r="AL6" s="11"/>
+      <c r="AM6" s="11"/>
+      <c r="AN6" s="11"/>
+      <c r="AO6" s="11"/>
+      <c r="AP6" s="11"/>
+      <c r="AQ6" s="11"/>
+      <c r="AR6" s="11"/>
+      <c r="AS6" s="11"/>
+      <c r="AT6" s="11"/>
+      <c r="AU6" s="11"/>
+      <c r="AV6" s="11"/>
+      <c r="AW6" s="11"/>
+      <c r="AX6" s="11"/>
+      <c r="AY6" s="11"/>
+      <c r="AZ6" s="11"/>
+      <c r="BA6" s="11"/>
+      <c r="BB6" s="11"/>
+    </row>
+    <row r="7" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A7" s="27">
+        <v>1</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="52">
+        <v>31</v>
+      </c>
+      <c r="D7" s="52"/>
+      <c r="E7" s="52"/>
+      <c r="F7" s="52"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="52"/>
+      <c r="I7" s="52">
+        <v>3</v>
+      </c>
+      <c r="J7" s="53"/>
+      <c r="K7" s="54">
+        <v>6</v>
+      </c>
+      <c r="L7" s="55"/>
+      <c r="M7" s="56"/>
+      <c r="N7" s="57"/>
+      <c r="O7" s="52">
+        <v>1</v>
+      </c>
+      <c r="P7" s="53"/>
+      <c r="Q7" s="53"/>
+      <c r="R7" s="54"/>
+      <c r="S7" s="55"/>
+      <c r="T7" s="58">
+        <f>H7+I7+J7+K7+N7+P7+R7</f>
+        <v>9</v>
+      </c>
+      <c r="U7" s="58">
+        <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
+        <v>777</v>
+      </c>
+      <c r="V7" s="58">
+        <f>U7/24</f>
+        <v>32.375</v>
+      </c>
+      <c r="W7" s="50"/>
+      <c r="AF7" s="12"/>
+      <c r="AG7" s="12"/>
+      <c r="AH7" s="12"/>
+      <c r="AI7" s="12"/>
+      <c r="AJ7" s="12"/>
+      <c r="AK7" s="12"/>
+      <c r="AL7" s="12"/>
+      <c r="AM7" s="12"/>
+      <c r="AN7" s="12"/>
+      <c r="AO7" s="12"/>
+      <c r="AP7" s="12"/>
+      <c r="AQ7" s="12"/>
+      <c r="AR7" s="12"/>
+      <c r="AS7" s="12"/>
+      <c r="AT7" s="12"/>
+      <c r="AU7" s="12"/>
+      <c r="AV7" s="12"/>
+      <c r="AW7" s="12"/>
+      <c r="AX7" s="12"/>
+      <c r="AY7" s="12"/>
+      <c r="AZ7" s="12"/>
+      <c r="BA7" s="12"/>
+      <c r="BB7" s="12"/>
+    </row>
+    <row r="8" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="27">
+        <f>A7+1</f>
+        <v>2</v>
+      </c>
+      <c r="B8" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="59">
+        <f>35+38</f>
+        <v>73</v>
+      </c>
+      <c r="D8" s="59"/>
+      <c r="E8" s="59"/>
+      <c r="F8" s="59"/>
+      <c r="G8" s="59"/>
+      <c r="H8" s="59"/>
+      <c r="I8" s="59"/>
+      <c r="J8" s="60"/>
+      <c r="K8" s="61"/>
+      <c r="L8" s="62"/>
+      <c r="M8" s="63">
+        <v>4</v>
+      </c>
+      <c r="N8" s="64"/>
+      <c r="O8" s="65">
+        <v>1</v>
+      </c>
+      <c r="P8" s="66">
+        <v>12</v>
+      </c>
+      <c r="Q8" s="66">
+        <v>1</v>
+      </c>
+      <c r="R8" s="67"/>
+      <c r="S8" s="62"/>
+      <c r="T8" s="68">
+        <f t="shared" ref="T8:T41" si="0">H8+I8+J8+K8+N8+P8+R8</f>
+        <v>12</v>
+      </c>
+      <c r="U8" s="69">
+        <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
+        <v>1908</v>
+      </c>
+      <c r="V8" s="69">
+        <f>U8/24</f>
+        <v>79.5</v>
+      </c>
+      <c r="W8" s="50"/>
+      <c r="AF8" s="12"/>
+      <c r="AG8" s="12"/>
+      <c r="AH8" s="12"/>
+      <c r="AI8" s="12"/>
+      <c r="AJ8" s="12"/>
+      <c r="AK8" s="12"/>
+      <c r="AL8" s="12"/>
+      <c r="AM8" s="12"/>
+      <c r="AN8" s="12"/>
+      <c r="AO8" s="12"/>
+      <c r="AP8" s="12"/>
+      <c r="AQ8" s="12"/>
+      <c r="AR8" s="12"/>
+      <c r="AS8" s="12"/>
+      <c r="AT8" s="12"/>
+      <c r="AU8" s="12"/>
+      <c r="AV8" s="12"/>
+      <c r="AW8" s="12"/>
+      <c r="AX8" s="12"/>
+      <c r="AY8" s="12"/>
+      <c r="AZ8" s="12"/>
+      <c r="BA8" s="12"/>
+      <c r="BB8" s="12"/>
+    </row>
+    <row r="9" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A9" s="27">
+        <f t="shared" ref="A9:A57" si="1">A8+1</f>
+        <v>3</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="70">
+        <f>30+41</f>
+        <v>71</v>
+      </c>
+      <c r="D9" s="70"/>
+      <c r="E9" s="70"/>
+      <c r="F9" s="70"/>
+      <c r="G9" s="70"/>
+      <c r="H9" s="70"/>
+      <c r="I9" s="70"/>
+      <c r="J9" s="71"/>
+      <c r="K9" s="72"/>
+      <c r="L9" s="55"/>
+      <c r="M9" s="73">
+        <v>10</v>
+      </c>
+      <c r="N9" s="74"/>
+      <c r="O9" s="70"/>
+      <c r="P9" s="71"/>
+      <c r="Q9" s="71"/>
+      <c r="R9" s="72"/>
+      <c r="S9" s="55"/>
+      <c r="T9" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U9" s="76">
+        <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
+        <v>1944</v>
+      </c>
+      <c r="V9" s="76">
+        <f t="shared" ref="V9:V11" si="3">U9/24</f>
+        <v>81</v>
+      </c>
+      <c r="W9" s="50"/>
+      <c r="AF9" s="12"/>
+      <c r="AG9" s="12"/>
+      <c r="AH9" s="12"/>
+      <c r="AI9" s="12"/>
+      <c r="AJ9" s="12"/>
+      <c r="AK9" s="12"/>
+      <c r="AL9" s="12"/>
+      <c r="AM9" s="12"/>
+      <c r="AN9" s="12"/>
+      <c r="AO9" s="12"/>
+      <c r="AP9" s="12"/>
+      <c r="AQ9" s="12"/>
+      <c r="AR9" s="12"/>
+      <c r="AS9" s="12"/>
+      <c r="AT9" s="12"/>
+      <c r="AU9" s="12"/>
+      <c r="AV9" s="12"/>
+      <c r="AW9" s="12"/>
+      <c r="AX9" s="12"/>
+      <c r="AY9" s="12"/>
+      <c r="AZ9" s="12"/>
+      <c r="BA9" s="12"/>
+      <c r="BB9" s="12"/>
+    </row>
+    <row r="10" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A10" s="27">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="70">
+        <f>10+10</f>
+        <v>20</v>
+      </c>
+      <c r="D10" s="70"/>
+      <c r="E10" s="70"/>
+      <c r="F10" s="70"/>
+      <c r="G10" s="70"/>
+      <c r="H10" s="70"/>
+      <c r="I10" s="70"/>
+      <c r="J10" s="71"/>
+      <c r="K10" s="72"/>
+      <c r="L10" s="55"/>
+      <c r="M10" s="73">
+        <v>10</v>
+      </c>
+      <c r="N10" s="74"/>
+      <c r="O10" s="70"/>
+      <c r="P10" s="71"/>
+      <c r="Q10" s="71"/>
+      <c r="R10" s="72"/>
+      <c r="S10" s="55"/>
+      <c r="T10" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U10" s="58">
+        <f t="shared" si="2"/>
+        <v>720</v>
+      </c>
+      <c r="V10" s="58">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+      <c r="W10" s="50"/>
+      <c r="AF10" s="12"/>
+      <c r="AG10" s="12"/>
+      <c r="AH10" s="12"/>
+      <c r="AI10" s="12"/>
+      <c r="AJ10" s="12"/>
+      <c r="AK10" s="12"/>
+      <c r="AL10" s="12"/>
+      <c r="AM10" s="12"/>
+      <c r="AN10" s="12"/>
+      <c r="AO10" s="12"/>
+      <c r="AP10" s="12"/>
+      <c r="AQ10" s="12"/>
+      <c r="AR10" s="12"/>
+      <c r="AS10" s="12"/>
+      <c r="AT10" s="12"/>
+      <c r="AU10" s="12"/>
+      <c r="AV10" s="12"/>
+      <c r="AW10" s="12"/>
+      <c r="AX10" s="12"/>
+      <c r="AY10" s="12"/>
+      <c r="AZ10" s="12"/>
+      <c r="BA10" s="12"/>
+      <c r="BB10" s="12"/>
+    </row>
+    <row r="11" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A11" s="27">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="70"/>
+      <c r="D11" s="70"/>
+      <c r="E11" s="70"/>
+      <c r="F11" s="70"/>
+      <c r="G11" s="70"/>
+      <c r="H11" s="70"/>
+      <c r="I11" s="70"/>
+      <c r="J11" s="71"/>
+      <c r="K11" s="72">
+        <v>2</v>
+      </c>
+      <c r="L11" s="55"/>
+      <c r="M11" s="73">
+        <v>9</v>
+      </c>
+      <c r="N11" s="74"/>
+      <c r="O11" s="70"/>
+      <c r="P11" s="71"/>
+      <c r="Q11" s="71"/>
+      <c r="R11" s="72"/>
+      <c r="S11" s="55"/>
+      <c r="T11" s="58">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="U11" s="58">
+        <f t="shared" si="2"/>
+        <v>218</v>
+      </c>
+      <c r="V11" s="58">
+        <f t="shared" si="3"/>
+        <v>9.0833333333333339</v>
+      </c>
+      <c r="AF11" s="12"/>
+      <c r="AG11" s="12"/>
+      <c r="AH11" s="12"/>
+      <c r="AI11" s="12"/>
+      <c r="AJ11" s="12"/>
+      <c r="AK11" s="12"/>
+      <c r="AL11" s="12"/>
+      <c r="AM11" s="12"/>
+      <c r="AN11" s="12"/>
+      <c r="AO11" s="12"/>
+      <c r="AP11" s="12"/>
+      <c r="AQ11" s="12"/>
+      <c r="AR11" s="12"/>
+      <c r="AS11" s="12"/>
+      <c r="AT11" s="12"/>
+      <c r="AU11" s="12"/>
+      <c r="AV11" s="12"/>
+      <c r="AW11" s="12"/>
+      <c r="AX11" s="12"/>
+      <c r="AY11" s="12"/>
+      <c r="AZ11" s="12"/>
+      <c r="BA11" s="12"/>
+      <c r="BB11" s="12"/>
+    </row>
+    <row r="12" spans="1:54" s="13" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="27">
+        <v>7</v>
+      </c>
+      <c r="B12" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="59">
+        <f>1224+53+720+43+1080+29</f>
+        <v>3149</v>
+      </c>
+      <c r="D12" s="59"/>
+      <c r="E12" s="59"/>
+      <c r="F12" s="59"/>
+      <c r="G12" s="59"/>
+      <c r="H12" s="59"/>
+      <c r="I12" s="59"/>
+      <c r="J12" s="60"/>
+      <c r="K12" s="61"/>
+      <c r="L12" s="62"/>
+      <c r="M12" s="63">
+        <v>12</v>
+      </c>
+      <c r="N12" s="64">
+        <v>20</v>
+      </c>
+      <c r="O12" s="65">
+        <v>11</v>
+      </c>
+      <c r="P12" s="66">
+        <v>18</v>
+      </c>
+      <c r="Q12" s="66">
+        <v>21</v>
+      </c>
+      <c r="R12" s="67"/>
+      <c r="S12" s="62"/>
+      <c r="T12" s="69">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="U12" s="69">
+        <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
+        <v>76670</v>
+      </c>
+      <c r="V12" s="69">
+        <f>U12/24</f>
+        <v>3194.5833333333335</v>
+      </c>
+      <c r="W12" s="9"/>
+      <c r="X12" s="9"/>
+      <c r="Y12" s="9"/>
+      <c r="Z12" s="9"/>
+      <c r="AA12" s="9"/>
+      <c r="AB12" s="9"/>
+      <c r="AC12" s="9"/>
+      <c r="AD12" s="9"/>
+      <c r="AE12" s="9"/>
+      <c r="AF12" s="12"/>
+      <c r="AG12" s="12"/>
+      <c r="AH12" s="12"/>
+      <c r="AI12" s="12"/>
+      <c r="AJ12" s="12"/>
+      <c r="AK12" s="12"/>
+      <c r="AL12" s="12"/>
+      <c r="AM12" s="12"/>
+      <c r="AN12" s="12"/>
+      <c r="AO12" s="12"/>
+      <c r="AP12" s="12"/>
+      <c r="AQ12" s="12"/>
+      <c r="AR12" s="12"/>
+      <c r="AS12" s="12"/>
+      <c r="AT12" s="12"/>
+      <c r="AU12" s="12"/>
+      <c r="AV12" s="12"/>
+      <c r="AW12" s="12"/>
+      <c r="AX12" s="12"/>
+      <c r="AY12" s="12"/>
+      <c r="AZ12" s="12"/>
+      <c r="BA12" s="12"/>
+      <c r="BB12" s="12"/>
+    </row>
+    <row r="13" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A13" s="27">
+        <v>11</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="70">
+        <v>2</v>
+      </c>
+      <c r="D13" s="70"/>
+      <c r="E13" s="70"/>
+      <c r="F13" s="70"/>
+      <c r="G13" s="70"/>
+      <c r="H13" s="70">
+        <v>16</v>
+      </c>
+      <c r="I13" s="70"/>
+      <c r="J13" s="71"/>
+      <c r="K13" s="72"/>
+      <c r="L13" s="55"/>
+      <c r="M13" s="73"/>
+      <c r="N13" s="74"/>
+      <c r="O13" s="70"/>
+      <c r="P13" s="71"/>
+      <c r="Q13" s="71"/>
+      <c r="R13" s="72"/>
+      <c r="S13" s="55"/>
+      <c r="T13" s="76">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="U13" s="76">
+        <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
+        <v>64</v>
+      </c>
+      <c r="V13" s="76">
+        <f>U13/24</f>
+        <v>2.6666666666666665</v>
+      </c>
+      <c r="AF13" s="12"/>
+      <c r="AG13" s="12"/>
+      <c r="AH13" s="12"/>
+      <c r="AI13" s="12"/>
+      <c r="AJ13" s="12"/>
+      <c r="AK13" s="12"/>
+      <c r="AL13" s="12"/>
+      <c r="AM13" s="12"/>
+      <c r="AN13" s="12"/>
+      <c r="AO13" s="12"/>
+      <c r="AP13" s="12"/>
+      <c r="AQ13" s="12"/>
+      <c r="AR13" s="12"/>
+      <c r="AS13" s="12"/>
+      <c r="AT13" s="12"/>
+      <c r="AU13" s="12"/>
+      <c r="AV13" s="12"/>
+      <c r="AW13" s="12"/>
+      <c r="AX13" s="12"/>
+      <c r="AY13" s="12"/>
+      <c r="AZ13" s="12"/>
+      <c r="BA13" s="12"/>
+      <c r="BB13" s="12"/>
+    </row>
+    <row r="14" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A14" s="27">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="70">
+        <v>2</v>
+      </c>
+      <c r="D14" s="70"/>
+      <c r="E14" s="70"/>
+      <c r="F14" s="70"/>
+      <c r="G14" s="70"/>
+      <c r="H14" s="70"/>
+      <c r="I14" s="70"/>
+      <c r="J14" s="71"/>
+      <c r="K14" s="72"/>
+      <c r="L14" s="55"/>
+      <c r="M14" s="73"/>
+      <c r="N14" s="74"/>
+      <c r="O14" s="70"/>
+      <c r="P14" s="71"/>
+      <c r="Q14" s="71"/>
+      <c r="R14" s="72"/>
+      <c r="S14" s="55"/>
+      <c r="T14" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U14" s="75">
+        <f t="shared" ref="U14:U36" si="4">C14*24+M14*24+O14*24+Q14*24+T14</f>
+        <v>48</v>
+      </c>
+      <c r="V14" s="75">
+        <f t="shared" ref="V14:V36" si="5">U14/24</f>
+        <v>2</v>
+      </c>
+      <c r="AF14" s="12"/>
+      <c r="AG14" s="12"/>
+      <c r="AH14" s="12"/>
+      <c r="AI14" s="12"/>
+      <c r="AJ14" s="12"/>
+      <c r="AK14" s="12"/>
+      <c r="AL14" s="12"/>
+      <c r="AM14" s="12"/>
+      <c r="AN14" s="12"/>
+      <c r="AO14" s="12"/>
+      <c r="AP14" s="12"/>
+      <c r="AQ14" s="12"/>
+      <c r="AR14" s="12"/>
+      <c r="AS14" s="12"/>
+      <c r="AT14" s="12"/>
+      <c r="AU14" s="12"/>
+      <c r="AV14" s="12"/>
+      <c r="AW14" s="12"/>
+      <c r="AX14" s="12"/>
+      <c r="AY14" s="12"/>
+      <c r="AZ14" s="12"/>
+      <c r="BA14" s="12"/>
+      <c r="BB14" s="12"/>
+    </row>
+    <row r="15" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A15" s="27">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="70"/>
+      <c r="D15" s="70"/>
+      <c r="E15" s="70"/>
+      <c r="F15" s="70"/>
+      <c r="G15" s="70"/>
+      <c r="H15" s="70"/>
+      <c r="I15" s="70"/>
+      <c r="J15" s="71"/>
+      <c r="K15" s="72"/>
+      <c r="L15" s="55"/>
+      <c r="M15" s="73"/>
+      <c r="N15" s="74"/>
+      <c r="O15" s="70"/>
+      <c r="P15" s="71"/>
+      <c r="Q15" s="71"/>
+      <c r="R15" s="72"/>
+      <c r="S15" s="55"/>
+      <c r="T15" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U15" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF15" s="12"/>
+      <c r="AG15" s="12"/>
+      <c r="AH15" s="12"/>
+      <c r="AI15" s="12"/>
+      <c r="AJ15" s="12"/>
+      <c r="AK15" s="12"/>
+      <c r="AL15" s="12"/>
+      <c r="AM15" s="12"/>
+      <c r="AN15" s="12"/>
+      <c r="AO15" s="12"/>
+      <c r="AP15" s="12"/>
+      <c r="AQ15" s="12"/>
+      <c r="AR15" s="12"/>
+      <c r="AS15" s="12"/>
+      <c r="AT15" s="12"/>
+      <c r="AU15" s="12"/>
+      <c r="AV15" s="12"/>
+      <c r="AW15" s="12"/>
+      <c r="AX15" s="12"/>
+      <c r="AY15" s="12"/>
+      <c r="AZ15" s="12"/>
+      <c r="BA15" s="12"/>
+      <c r="BB15" s="12"/>
+    </row>
+    <row r="16" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A16" s="27">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="70"/>
+      <c r="D16" s="70"/>
+      <c r="E16" s="70"/>
+      <c r="F16" s="70"/>
+      <c r="G16" s="70"/>
+      <c r="H16" s="70"/>
+      <c r="I16" s="70"/>
+      <c r="J16" s="71"/>
+      <c r="K16" s="72"/>
+      <c r="L16" s="55"/>
+      <c r="M16" s="73"/>
+      <c r="N16" s="74"/>
+      <c r="O16" s="70"/>
+      <c r="P16" s="71"/>
+      <c r="Q16" s="71"/>
+      <c r="R16" s="72"/>
+      <c r="S16" s="55"/>
+      <c r="T16" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U16" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF16" s="12"/>
+      <c r="AG16" s="12"/>
+      <c r="AH16" s="12"/>
+      <c r="AI16" s="12"/>
+      <c r="AJ16" s="12"/>
+      <c r="AK16" s="12"/>
+      <c r="AL16" s="12"/>
+      <c r="AM16" s="12"/>
+      <c r="AN16" s="12"/>
+      <c r="AO16" s="12"/>
+      <c r="AP16" s="12"/>
+      <c r="AQ16" s="12"/>
+      <c r="AR16" s="12"/>
+      <c r="AS16" s="12"/>
+      <c r="AT16" s="12"/>
+      <c r="AU16" s="12"/>
+      <c r="AV16" s="12"/>
+      <c r="AW16" s="12"/>
+      <c r="AX16" s="12"/>
+      <c r="AY16" s="12"/>
+      <c r="AZ16" s="12"/>
+      <c r="BA16" s="12"/>
+      <c r="BB16" s="12"/>
+    </row>
+    <row r="17" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A17" s="27">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="70"/>
+      <c r="D17" s="70"/>
+      <c r="E17" s="70"/>
+      <c r="F17" s="70"/>
+      <c r="G17" s="70"/>
+      <c r="H17" s="70">
+        <f>3*24</f>
+        <v>72</v>
+      </c>
+      <c r="I17" s="70"/>
+      <c r="J17" s="71"/>
+      <c r="K17" s="72"/>
+      <c r="L17" s="55"/>
+      <c r="M17" s="73"/>
+      <c r="N17" s="74"/>
+      <c r="O17" s="70"/>
+      <c r="P17" s="71"/>
+      <c r="Q17" s="71"/>
+      <c r="R17" s="72"/>
+      <c r="S17" s="55"/>
+      <c r="T17" s="58">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="U17" s="75">
+        <f t="shared" si="4"/>
+        <v>72</v>
+      </c>
+      <c r="V17" s="75">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="AF17" s="12"/>
+      <c r="AG17" s="12"/>
+      <c r="AH17" s="12"/>
+      <c r="AI17" s="12"/>
+      <c r="AJ17" s="12"/>
+      <c r="AK17" s="12"/>
+      <c r="AL17" s="12"/>
+      <c r="AM17" s="12"/>
+      <c r="AN17" s="12"/>
+      <c r="AO17" s="12"/>
+      <c r="AP17" s="12"/>
+      <c r="AQ17" s="12"/>
+      <c r="AR17" s="12"/>
+      <c r="AS17" s="12"/>
+      <c r="AT17" s="12"/>
+      <c r="AU17" s="12"/>
+      <c r="AV17" s="12"/>
+      <c r="AW17" s="12"/>
+      <c r="AX17" s="12"/>
+      <c r="AY17" s="12"/>
+      <c r="AZ17" s="12"/>
+      <c r="BA17" s="12"/>
+      <c r="BB17" s="12"/>
+    </row>
+    <row r="18" spans="1:54" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="27">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="70"/>
+      <c r="D18" s="70"/>
+      <c r="E18" s="70"/>
+      <c r="F18" s="70"/>
+      <c r="G18" s="70"/>
+      <c r="H18" s="70"/>
+      <c r="I18" s="70"/>
+      <c r="J18" s="71"/>
+      <c r="K18" s="72"/>
+      <c r="L18" s="55"/>
+      <c r="M18" s="73"/>
+      <c r="N18" s="74"/>
+      <c r="O18" s="70"/>
+      <c r="P18" s="71"/>
+      <c r="Q18" s="71"/>
+      <c r="R18" s="72"/>
+      <c r="S18" s="55"/>
+      <c r="T18" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U18" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF18" s="12"/>
+      <c r="AG18" s="12"/>
+      <c r="AH18" s="12"/>
+      <c r="AI18" s="12"/>
+      <c r="AJ18" s="12"/>
+      <c r="AK18" s="12"/>
+      <c r="AL18" s="12"/>
+      <c r="AM18" s="12"/>
+      <c r="AN18" s="12"/>
+      <c r="AO18" s="12"/>
+      <c r="AP18" s="12"/>
+      <c r="AQ18" s="12"/>
+      <c r="AR18" s="12"/>
+      <c r="AS18" s="12"/>
+      <c r="AT18" s="12"/>
+      <c r="AU18" s="12"/>
+      <c r="AV18" s="12"/>
+      <c r="AW18" s="12"/>
+      <c r="AX18" s="12"/>
+      <c r="AY18" s="12"/>
+      <c r="AZ18" s="12"/>
+      <c r="BA18" s="12"/>
+      <c r="BB18" s="12"/>
+    </row>
+    <row r="19" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A19" s="27">
+        <v>16</v>
+      </c>
+      <c r="B19" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="70">
+        <v>1</v>
+      </c>
+      <c r="D19" s="70"/>
+      <c r="E19" s="70"/>
+      <c r="F19" s="70"/>
+      <c r="G19" s="70"/>
+      <c r="H19" s="70">
+        <f>1*24+20</f>
+        <v>44</v>
+      </c>
+      <c r="I19" s="70"/>
+      <c r="J19" s="71"/>
+      <c r="K19" s="72"/>
+      <c r="L19" s="55"/>
+      <c r="M19" s="73">
+        <v>1</v>
+      </c>
+      <c r="N19" s="74"/>
+      <c r="O19" s="70"/>
+      <c r="P19" s="71"/>
+      <c r="Q19" s="71"/>
+      <c r="R19" s="72"/>
+      <c r="S19" s="55"/>
+      <c r="T19" s="58">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="U19" s="75">
+        <f t="shared" si="4"/>
+        <v>92</v>
+      </c>
+      <c r="V19" s="75">
+        <f t="shared" si="5"/>
+        <v>3.8333333333333335</v>
+      </c>
+      <c r="AF19" s="12"/>
+      <c r="AG19" s="12"/>
+      <c r="AH19" s="12"/>
+      <c r="AI19" s="12"/>
+      <c r="AJ19" s="12"/>
+      <c r="AK19" s="12"/>
+      <c r="AL19" s="12"/>
+      <c r="AM19" s="12"/>
+      <c r="AN19" s="12"/>
+      <c r="AO19" s="12"/>
+      <c r="AP19" s="12"/>
+      <c r="AQ19" s="12"/>
+      <c r="AR19" s="12"/>
+      <c r="AS19" s="12"/>
+      <c r="AT19" s="12"/>
+      <c r="AU19" s="12"/>
+      <c r="AV19" s="12"/>
+      <c r="AW19" s="12"/>
+      <c r="AX19" s="12"/>
+      <c r="AY19" s="12"/>
+      <c r="AZ19" s="12"/>
+      <c r="BA19" s="12"/>
+      <c r="BB19" s="12"/>
+    </row>
+    <row r="20" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A20" s="27">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="B20" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="70">
+        <v>5</v>
+      </c>
+      <c r="D20" s="70"/>
+      <c r="E20" s="70"/>
+      <c r="F20" s="70"/>
+      <c r="G20" s="70"/>
+      <c r="H20" s="70"/>
+      <c r="I20" s="70"/>
+      <c r="J20" s="71"/>
+      <c r="K20" s="72"/>
+      <c r="L20" s="55"/>
+      <c r="M20" s="73"/>
+      <c r="N20" s="74"/>
+      <c r="O20" s="70"/>
+      <c r="P20" s="71"/>
+      <c r="Q20" s="71"/>
+      <c r="R20" s="72"/>
+      <c r="S20" s="55"/>
+      <c r="T20" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U20" s="75">
+        <f t="shared" si="4"/>
+        <v>120</v>
+      </c>
+      <c r="V20" s="75">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="AF20" s="12"/>
+      <c r="AG20" s="12"/>
+      <c r="AH20" s="12"/>
+      <c r="AI20" s="12"/>
+      <c r="AJ20" s="12"/>
+      <c r="AK20" s="12"/>
+      <c r="AL20" s="12"/>
+      <c r="AM20" s="12"/>
+      <c r="AN20" s="12"/>
+      <c r="AO20" s="12"/>
+      <c r="AP20" s="12"/>
+      <c r="AQ20" s="12"/>
+      <c r="AR20" s="12"/>
+      <c r="AS20" s="12"/>
+      <c r="AT20" s="12"/>
+      <c r="AU20" s="12"/>
+      <c r="AV20" s="12"/>
+      <c r="AW20" s="12"/>
+      <c r="AX20" s="12"/>
+      <c r="AY20" s="12"/>
+      <c r="AZ20" s="12"/>
+      <c r="BA20" s="12"/>
+      <c r="BB20" s="12"/>
+    </row>
+    <row r="21" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A21" s="27">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="B21" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="70"/>
+      <c r="D21" s="70"/>
+      <c r="E21" s="70"/>
+      <c r="F21" s="70"/>
+      <c r="G21" s="70"/>
+      <c r="H21" s="70">
+        <f>2*24</f>
+        <v>48</v>
+      </c>
+      <c r="I21" s="70"/>
+      <c r="J21" s="71"/>
+      <c r="K21" s="72"/>
+      <c r="L21" s="55"/>
+      <c r="M21" s="73"/>
+      <c r="N21" s="74"/>
+      <c r="O21" s="70"/>
+      <c r="P21" s="71"/>
+      <c r="Q21" s="71"/>
+      <c r="R21" s="72"/>
+      <c r="S21" s="55"/>
+      <c r="T21" s="58">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+      <c r="U21" s="75">
+        <f t="shared" si="4"/>
+        <v>48</v>
+      </c>
+      <c r="V21" s="75">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="AF21" s="12"/>
+      <c r="AG21" s="12"/>
+      <c r="AH21" s="12"/>
+      <c r="AI21" s="12"/>
+      <c r="AJ21" s="12"/>
+      <c r="AK21" s="12"/>
+      <c r="AL21" s="12"/>
+      <c r="AM21" s="12"/>
+      <c r="AN21" s="12"/>
+      <c r="AO21" s="12"/>
+      <c r="AP21" s="12"/>
+      <c r="AQ21" s="12"/>
+      <c r="AR21" s="12"/>
+      <c r="AS21" s="12"/>
+      <c r="AT21" s="12"/>
+      <c r="AU21" s="12"/>
+      <c r="AV21" s="12"/>
+      <c r="AW21" s="12"/>
+      <c r="AX21" s="12"/>
+      <c r="AY21" s="12"/>
+      <c r="AZ21" s="12"/>
+      <c r="BA21" s="12"/>
+      <c r="BB21" s="12"/>
+    </row>
+    <row r="22" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="27">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="B22" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="70">
+        <v>1</v>
+      </c>
+      <c r="D22" s="70"/>
+      <c r="E22" s="70"/>
+      <c r="F22" s="70"/>
+      <c r="G22" s="70"/>
+      <c r="H22" s="70"/>
+      <c r="I22" s="70">
+        <v>20</v>
+      </c>
+      <c r="J22" s="71"/>
+      <c r="K22" s="72"/>
+      <c r="L22" s="55"/>
+      <c r="M22" s="73">
+        <v>1</v>
+      </c>
+      <c r="N22" s="74"/>
+      <c r="O22" s="70"/>
+      <c r="P22" s="71"/>
+      <c r="Q22" s="71"/>
+      <c r="R22" s="72"/>
+      <c r="S22" s="55"/>
+      <c r="T22" s="58">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="U22" s="75">
+        <f t="shared" si="4"/>
+        <v>68</v>
+      </c>
+      <c r="V22" s="75">
+        <f t="shared" si="5"/>
+        <v>2.8333333333333335</v>
+      </c>
+      <c r="W22" s="9"/>
+      <c r="X22" s="9"/>
+      <c r="Y22" s="9"/>
+      <c r="Z22" s="9"/>
+      <c r="AA22" s="9"/>
+      <c r="AB22" s="9"/>
+      <c r="AC22" s="9"/>
+      <c r="AD22" s="9"/>
+      <c r="AE22" s="9"/>
+      <c r="AF22" s="12"/>
+      <c r="AG22" s="12"/>
+      <c r="AH22" s="12"/>
+      <c r="AI22" s="12"/>
+      <c r="AJ22" s="12"/>
+      <c r="AK22" s="12"/>
+      <c r="AL22" s="12"/>
+      <c r="AM22" s="12"/>
+      <c r="AN22" s="12"/>
+      <c r="AO22" s="12"/>
+      <c r="AP22" s="12"/>
+      <c r="AQ22" s="12"/>
+      <c r="AR22" s="12"/>
+      <c r="AS22" s="12"/>
+      <c r="AT22" s="12"/>
+      <c r="AU22" s="12"/>
+      <c r="AV22" s="12"/>
+      <c r="AW22" s="12"/>
+      <c r="AX22" s="12"/>
+      <c r="AY22" s="12"/>
+      <c r="AZ22" s="12"/>
+      <c r="BA22" s="12"/>
+      <c r="BB22" s="12"/>
+    </row>
+    <row r="23" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="27">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="B23" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="70"/>
+      <c r="D23" s="70"/>
+      <c r="E23" s="70"/>
+      <c r="F23" s="70"/>
+      <c r="G23" s="70"/>
+      <c r="H23" s="70">
+        <f>37*24+19</f>
+        <v>907</v>
+      </c>
+      <c r="I23" s="70"/>
+      <c r="J23" s="71"/>
+      <c r="K23" s="72"/>
+      <c r="L23" s="55"/>
+      <c r="M23" s="73"/>
+      <c r="N23" s="74"/>
+      <c r="O23" s="70"/>
+      <c r="P23" s="71"/>
+      <c r="Q23" s="71"/>
+      <c r="R23" s="72"/>
+      <c r="S23" s="55"/>
+      <c r="T23" s="58">
+        <f t="shared" si="0"/>
+        <v>907</v>
+      </c>
+      <c r="U23" s="75">
+        <f t="shared" si="4"/>
+        <v>907</v>
+      </c>
+      <c r="V23" s="75">
+        <f t="shared" si="5"/>
+        <v>37.791666666666664</v>
+      </c>
+      <c r="W23" s="9"/>
+      <c r="X23" s="9"/>
+      <c r="Y23" s="9"/>
+      <c r="Z23" s="9"/>
+      <c r="AA23" s="9"/>
+      <c r="AB23" s="9"/>
+      <c r="AC23" s="9"/>
+      <c r="AD23" s="9"/>
+      <c r="AE23" s="9"/>
+      <c r="AF23" s="12"/>
+      <c r="AG23" s="12"/>
+      <c r="AH23" s="12"/>
+      <c r="AI23" s="12"/>
+      <c r="AJ23" s="12"/>
+      <c r="AK23" s="12"/>
+      <c r="AL23" s="12"/>
+      <c r="AM23" s="12"/>
+      <c r="AN23" s="12"/>
+      <c r="AO23" s="12"/>
+      <c r="AP23" s="12"/>
+      <c r="AQ23" s="12"/>
+      <c r="AR23" s="12"/>
+      <c r="AS23" s="12"/>
+      <c r="AT23" s="12"/>
+      <c r="AU23" s="12"/>
+      <c r="AV23" s="12"/>
+      <c r="AW23" s="12"/>
+      <c r="AX23" s="12"/>
+      <c r="AY23" s="12"/>
+      <c r="AZ23" s="12"/>
+      <c r="BA23" s="12"/>
+      <c r="BB23" s="12"/>
+    </row>
+    <row r="24" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A24" s="27">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="B24" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" s="70">
+        <v>2</v>
+      </c>
+      <c r="D24" s="70"/>
+      <c r="E24" s="70"/>
+      <c r="F24" s="70"/>
+      <c r="G24" s="70"/>
+      <c r="H24" s="70">
+        <f>3*24</f>
+        <v>72</v>
+      </c>
+      <c r="I24" s="70"/>
+      <c r="J24" s="71"/>
+      <c r="K24" s="72"/>
+      <c r="L24" s="55"/>
+      <c r="M24" s="73"/>
+      <c r="N24" s="74"/>
+      <c r="O24" s="70"/>
+      <c r="P24" s="71"/>
+      <c r="Q24" s="71"/>
+      <c r="R24" s="72"/>
+      <c r="S24" s="55"/>
+      <c r="T24" s="58">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="U24" s="75">
+        <f t="shared" si="4"/>
+        <v>120</v>
+      </c>
+      <c r="V24" s="75">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="AF24" s="12"/>
+      <c r="AG24" s="12"/>
+      <c r="AH24" s="12"/>
+      <c r="AI24" s="12"/>
+      <c r="AJ24" s="12"/>
+      <c r="AK24" s="12"/>
+      <c r="AL24" s="12"/>
+      <c r="AM24" s="12"/>
+      <c r="AN24" s="12"/>
+      <c r="AO24" s="12"/>
+      <c r="AP24" s="12"/>
+      <c r="AQ24" s="12"/>
+      <c r="AR24" s="12"/>
+      <c r="AS24" s="12"/>
+      <c r="AT24" s="12"/>
+      <c r="AU24" s="12"/>
+      <c r="AV24" s="12"/>
+      <c r="AW24" s="12"/>
+      <c r="AX24" s="12"/>
+      <c r="AY24" s="12"/>
+      <c r="AZ24" s="12"/>
+      <c r="BA24" s="12"/>
+      <c r="BB24" s="12"/>
+    </row>
+    <row r="25" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A25" s="27">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="70">
+        <f>35+126</f>
+        <v>161</v>
+      </c>
+      <c r="D25" s="70"/>
+      <c r="E25" s="70"/>
+      <c r="F25" s="70"/>
+      <c r="G25" s="70"/>
+      <c r="H25" s="70"/>
+      <c r="I25" s="70">
+        <v>1</v>
+      </c>
+      <c r="J25" s="71"/>
+      <c r="K25" s="72"/>
+      <c r="L25" s="55"/>
+      <c r="M25" s="73">
+        <v>2</v>
+      </c>
+      <c r="N25" s="74"/>
+      <c r="O25" s="70">
+        <v>1</v>
+      </c>
+      <c r="P25" s="71"/>
+      <c r="Q25" s="71">
+        <v>2</v>
+      </c>
+      <c r="R25" s="72"/>
+      <c r="S25" s="55"/>
+      <c r="T25" s="58">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="U25" s="75">
+        <f t="shared" si="4"/>
+        <v>3985</v>
+      </c>
+      <c r="V25" s="75">
+        <f t="shared" si="5"/>
+        <v>166.04166666666666</v>
+      </c>
+      <c r="AY25" s="14" t="e">
+        <f>#REF!-AY24</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="27">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="B26" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="70"/>
+      <c r="D26" s="70"/>
+      <c r="E26" s="70"/>
+      <c r="F26" s="70"/>
+      <c r="G26" s="70"/>
+      <c r="H26" s="70"/>
+      <c r="I26" s="70"/>
+      <c r="J26" s="71"/>
+      <c r="K26" s="72"/>
+      <c r="L26" s="55"/>
+      <c r="M26" s="73"/>
+      <c r="N26" s="74"/>
+      <c r="O26" s="70"/>
+      <c r="P26" s="71"/>
+      <c r="Q26" s="71"/>
+      <c r="R26" s="72"/>
+      <c r="S26" s="55"/>
+      <c r="T26" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U26" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V26" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W26" s="9"/>
+      <c r="X26" s="9"/>
+      <c r="Y26" s="9"/>
+      <c r="Z26" s="9"/>
+      <c r="AA26" s="9"/>
+      <c r="AB26" s="9"/>
+      <c r="AC26" s="9"/>
+      <c r="AD26" s="9"/>
+      <c r="AE26" s="9"/>
+    </row>
+    <row r="27" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="27">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="B27" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27" s="70">
+        <v>2</v>
+      </c>
+      <c r="D27" s="70"/>
+      <c r="E27" s="70"/>
+      <c r="F27" s="70"/>
+      <c r="G27" s="70"/>
+      <c r="H27" s="70"/>
+      <c r="I27" s="70"/>
+      <c r="J27" s="71"/>
+      <c r="K27" s="72"/>
+      <c r="L27" s="55"/>
+      <c r="M27" s="73">
+        <v>1</v>
+      </c>
+      <c r="N27" s="74"/>
+      <c r="O27" s="70"/>
+      <c r="P27" s="71"/>
+      <c r="Q27" s="71"/>
+      <c r="R27" s="72"/>
+      <c r="S27" s="55"/>
+      <c r="T27" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U27" s="75">
+        <f t="shared" si="4"/>
+        <v>72</v>
+      </c>
+      <c r="V27" s="75">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="W27" s="9"/>
+      <c r="X27" s="9"/>
+      <c r="Y27" s="9"/>
+      <c r="Z27" s="9"/>
+      <c r="AA27" s="9"/>
+      <c r="AB27" s="9"/>
+      <c r="AC27" s="9"/>
+      <c r="AD27" s="9"/>
+      <c r="AE27" s="9"/>
+    </row>
+    <row r="28" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="27">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="B28" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="70"/>
+      <c r="D28" s="70"/>
+      <c r="E28" s="70"/>
+      <c r="F28" s="70"/>
+      <c r="G28" s="70"/>
+      <c r="H28" s="70"/>
+      <c r="I28" s="70"/>
+      <c r="J28" s="71"/>
+      <c r="K28" s="72"/>
+      <c r="L28" s="55"/>
+      <c r="M28" s="73"/>
+      <c r="N28" s="74"/>
+      <c r="O28" s="70"/>
+      <c r="P28" s="71"/>
+      <c r="Q28" s="71"/>
+      <c r="R28" s="72"/>
+      <c r="S28" s="55"/>
+      <c r="T28" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U28" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V28" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W28" s="9"/>
+      <c r="X28" s="9"/>
+      <c r="Y28" s="9"/>
+      <c r="Z28" s="9"/>
+      <c r="AA28" s="9"/>
+      <c r="AB28" s="9"/>
+      <c r="AC28" s="9"/>
+      <c r="AD28" s="9"/>
+      <c r="AE28" s="9"/>
+    </row>
+    <row r="29" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A29" s="27">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="B29" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" s="70">
+        <v>9</v>
+      </c>
+      <c r="D29" s="70"/>
+      <c r="E29" s="70"/>
+      <c r="F29" s="70"/>
+      <c r="G29" s="70"/>
+      <c r="H29" s="70"/>
+      <c r="I29" s="70">
+        <v>5</v>
+      </c>
+      <c r="J29" s="71"/>
+      <c r="K29" s="72"/>
+      <c r="L29" s="55"/>
+      <c r="M29" s="73">
+        <v>11</v>
+      </c>
+      <c r="N29" s="74"/>
+      <c r="O29" s="70">
+        <v>1</v>
+      </c>
+      <c r="P29" s="71"/>
+      <c r="Q29" s="71">
+        <v>1</v>
+      </c>
+      <c r="R29" s="72"/>
+      <c r="S29" s="55"/>
+      <c r="T29" s="58">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="U29" s="75">
+        <f t="shared" si="4"/>
+        <v>533</v>
+      </c>
+      <c r="V29" s="75">
+        <f t="shared" si="5"/>
+        <v>22.208333333333332</v>
+      </c>
+    </row>
+    <row r="30" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A30" s="27">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="B30" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="70">
+        <v>4</v>
+      </c>
+      <c r="D30" s="70"/>
+      <c r="E30" s="70"/>
+      <c r="F30" s="70"/>
+      <c r="G30" s="70"/>
+      <c r="H30" s="70"/>
+      <c r="I30" s="70"/>
+      <c r="J30" s="71"/>
+      <c r="K30" s="72"/>
+      <c r="L30" s="55"/>
+      <c r="M30" s="73">
+        <v>3</v>
+      </c>
+      <c r="N30" s="74"/>
+      <c r="O30" s="70"/>
+      <c r="P30" s="71"/>
+      <c r="Q30" s="71">
+        <v>1</v>
+      </c>
+      <c r="R30" s="72"/>
+      <c r="S30" s="55"/>
+      <c r="T30" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U30" s="75">
+        <f t="shared" si="4"/>
+        <v>192</v>
+      </c>
+      <c r="V30" s="75">
+        <f t="shared" si="5"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A31" s="27">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="B31" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" s="70"/>
+      <c r="D31" s="70"/>
+      <c r="E31" s="70"/>
+      <c r="F31" s="70"/>
+      <c r="G31" s="70"/>
+      <c r="H31" s="70"/>
+      <c r="I31" s="70"/>
+      <c r="J31" s="71"/>
+      <c r="K31" s="72"/>
+      <c r="L31" s="55"/>
+      <c r="M31" s="73"/>
+      <c r="N31" s="74"/>
+      <c r="O31" s="70"/>
+      <c r="P31" s="71"/>
+      <c r="Q31" s="71"/>
+      <c r="R31" s="72"/>
+      <c r="S31" s="55"/>
+      <c r="T31" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U31" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V31" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A32" s="27">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="B32" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" s="70"/>
+      <c r="D32" s="70"/>
+      <c r="E32" s="70"/>
+      <c r="F32" s="70"/>
+      <c r="G32" s="70"/>
+      <c r="H32" s="70"/>
+      <c r="I32" s="70"/>
+      <c r="J32" s="71"/>
+      <c r="K32" s="72"/>
+      <c r="L32" s="55"/>
+      <c r="M32" s="73"/>
+      <c r="N32" s="74"/>
+      <c r="O32" s="70"/>
+      <c r="P32" s="71"/>
+      <c r="Q32" s="71"/>
+      <c r="R32" s="72"/>
+      <c r="S32" s="55"/>
+      <c r="T32" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U32" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V32" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A33" s="27">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="B33" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" s="70"/>
+      <c r="D33" s="70"/>
+      <c r="E33" s="70"/>
+      <c r="F33" s="70"/>
+      <c r="G33" s="70"/>
+      <c r="H33" s="70"/>
+      <c r="I33" s="70"/>
+      <c r="J33" s="71"/>
+      <c r="K33" s="72"/>
+      <c r="L33" s="55"/>
+      <c r="M33" s="73"/>
+      <c r="N33" s="74"/>
+      <c r="O33" s="70"/>
+      <c r="P33" s="71"/>
+      <c r="Q33" s="71"/>
+      <c r="R33" s="72"/>
+      <c r="S33" s="55"/>
+      <c r="T33" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U33" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V33" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A34" s="27">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="B34" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" s="70">
+        <f>144+23</f>
+        <v>167</v>
+      </c>
+      <c r="D34" s="70"/>
+      <c r="E34" s="70"/>
+      <c r="F34" s="70"/>
+      <c r="G34" s="70"/>
+      <c r="H34" s="70"/>
+      <c r="I34" s="70">
+        <v>1</v>
+      </c>
+      <c r="J34" s="71"/>
+      <c r="K34" s="72">
+        <v>1</v>
+      </c>
+      <c r="L34" s="55"/>
+      <c r="M34" s="73">
+        <v>11</v>
+      </c>
+      <c r="N34" s="74"/>
+      <c r="O34" s="70">
+        <v>2</v>
+      </c>
+      <c r="P34" s="71"/>
+      <c r="Q34" s="71">
+        <v>1</v>
+      </c>
+      <c r="R34" s="72"/>
+      <c r="S34" s="55"/>
+      <c r="T34" s="58">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="U34" s="75">
+        <f t="shared" si="4"/>
+        <v>4346</v>
+      </c>
+      <c r="V34" s="75">
+        <f t="shared" si="5"/>
+        <v>181.08333333333334</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="27">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="B35" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="C35" s="70"/>
+      <c r="D35" s="70"/>
+      <c r="E35" s="70"/>
+      <c r="F35" s="70"/>
+      <c r="G35" s="70"/>
+      <c r="H35" s="70"/>
+      <c r="I35" s="70"/>
+      <c r="J35" s="71"/>
+      <c r="K35" s="72"/>
+      <c r="L35" s="55"/>
+      <c r="M35" s="73"/>
+      <c r="N35" s="74"/>
+      <c r="O35" s="70"/>
+      <c r="P35" s="71"/>
+      <c r="Q35" s="71"/>
+      <c r="R35" s="72"/>
+      <c r="S35" s="55"/>
+      <c r="T35" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U35" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V35" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A36" s="27">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+      <c r="B36" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="70"/>
+      <c r="D36" s="70"/>
+      <c r="E36" s="70"/>
+      <c r="F36" s="70"/>
+      <c r="G36" s="70"/>
+      <c r="H36" s="70"/>
+      <c r="I36" s="70"/>
+      <c r="J36" s="71"/>
+      <c r="K36" s="72"/>
+      <c r="L36" s="55"/>
+      <c r="M36" s="73"/>
+      <c r="N36" s="74"/>
+      <c r="O36" s="70"/>
+      <c r="P36" s="71"/>
+      <c r="Q36" s="71"/>
+      <c r="R36" s="72"/>
+      <c r="S36" s="55"/>
+      <c r="T36" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U36" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="27">
+        <f t="shared" si="1"/>
+        <v>34</v>
+      </c>
+      <c r="B37" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="C37" s="59">
+        <f>64+864+2376</f>
+        <v>3304</v>
+      </c>
+      <c r="D37" s="59"/>
+      <c r="E37" s="59"/>
+      <c r="F37" s="59"/>
+      <c r="G37" s="59"/>
+      <c r="H37" s="59">
+        <v>3</v>
+      </c>
+      <c r="I37" s="59">
+        <v>2</v>
+      </c>
+      <c r="J37" s="60">
+        <v>6</v>
+      </c>
+      <c r="K37" s="61">
+        <f>6+2</f>
+        <v>8</v>
+      </c>
+      <c r="L37" s="62"/>
+      <c r="M37" s="63">
+        <v>35</v>
+      </c>
+      <c r="N37" s="64"/>
+      <c r="O37" s="65">
+        <v>25</v>
+      </c>
+      <c r="P37" s="66"/>
+      <c r="Q37" s="66">
+        <v>157</v>
+      </c>
+      <c r="R37" s="67"/>
+      <c r="S37" s="62"/>
+      <c r="T37" s="77">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="U37" s="77">
+        <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
+        <v>21145</v>
+      </c>
+      <c r="V37" s="77">
+        <f>U37/6</f>
+        <v>3524.1666666666665</v>
+      </c>
+      <c r="W37" s="50"/>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A38" s="27">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="B38" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" s="70"/>
+      <c r="D38" s="70"/>
+      <c r="E38" s="70"/>
+      <c r="F38" s="70"/>
+      <c r="G38" s="70"/>
+      <c r="H38" s="70"/>
+      <c r="I38" s="70"/>
+      <c r="J38" s="71"/>
+      <c r="K38" s="72"/>
+      <c r="L38" s="55"/>
+      <c r="M38" s="73"/>
+      <c r="N38" s="74"/>
+      <c r="O38" s="70"/>
+      <c r="P38" s="71"/>
+      <c r="Q38" s="71"/>
+      <c r="R38" s="72"/>
+      <c r="S38" s="55"/>
+      <c r="T38" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U38" s="75">
+        <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
+        <v>0</v>
+      </c>
+      <c r="V38" s="75">
+        <f>U38/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A39" s="27">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="B39" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="C39" s="78"/>
+      <c r="D39" s="78"/>
+      <c r="E39" s="78"/>
+      <c r="F39" s="78"/>
+      <c r="G39" s="78"/>
+      <c r="H39" s="78"/>
+      <c r="I39" s="78"/>
+      <c r="J39" s="79"/>
+      <c r="K39" s="80"/>
+      <c r="L39" s="55"/>
+      <c r="M39" s="73"/>
+      <c r="N39" s="74"/>
+      <c r="O39" s="70"/>
+      <c r="P39" s="71"/>
+      <c r="Q39" s="71"/>
+      <c r="R39" s="72"/>
+      <c r="S39" s="95"/>
+      <c r="T39" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U39" s="75">
+        <f>C39*24+M39*24+O39*24+Q39*24+T39</f>
+        <v>0</v>
+      </c>
+      <c r="V39" s="75">
+        <f>U39/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="27">
+        <f t="shared" si="1"/>
+        <v>37</v>
+      </c>
+      <c r="B40" s="42" t="s">
+        <v>21</v>
+      </c>
+      <c r="C40" s="59">
+        <f>189+66</f>
+        <v>255</v>
+      </c>
+      <c r="D40" s="59"/>
+      <c r="E40" s="59"/>
+      <c r="F40" s="59"/>
+      <c r="G40" s="59"/>
+      <c r="H40" s="59"/>
+      <c r="I40" s="59"/>
+      <c r="J40" s="60"/>
+      <c r="K40" s="61">
+        <v>20</v>
+      </c>
+      <c r="L40" s="62"/>
+      <c r="M40" s="63">
+        <v>1</v>
+      </c>
+      <c r="N40" s="64"/>
+      <c r="O40" s="65">
+        <v>2</v>
+      </c>
+      <c r="P40" s="66"/>
+      <c r="Q40" s="66">
+        <v>2</v>
+      </c>
+      <c r="R40" s="67"/>
+      <c r="S40" s="62"/>
+      <c r="T40" s="77">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="U40" s="77">
+        <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
+        <v>6260</v>
+      </c>
+      <c r="V40" s="77">
+        <f>U40/24</f>
+        <v>260.83333333333331</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="27">
+        <f t="shared" si="1"/>
+        <v>38</v>
+      </c>
+      <c r="B41" s="43" t="s">
+        <v>22</v>
+      </c>
+      <c r="C41" s="82">
+        <f>288+39</f>
+        <v>327</v>
+      </c>
+      <c r="D41" s="82"/>
+      <c r="E41" s="82"/>
+      <c r="F41" s="82"/>
+      <c r="G41" s="82"/>
+      <c r="H41" s="82"/>
+      <c r="I41" s="82"/>
+      <c r="J41" s="83"/>
+      <c r="K41" s="84"/>
+      <c r="L41" s="85"/>
+      <c r="M41" s="86">
+        <v>25</v>
+      </c>
+      <c r="N41" s="87"/>
+      <c r="O41" s="82">
+        <v>9</v>
+      </c>
+      <c r="P41" s="83"/>
+      <c r="Q41" s="83">
+        <v>44</v>
+      </c>
+      <c r="R41" s="84"/>
+      <c r="S41" s="85"/>
+      <c r="T41" s="88">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U41" s="88">
+        <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
+        <v>4860</v>
+      </c>
+      <c r="V41" s="88">
+        <f>U41/12</f>
+        <v>405</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="27">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+      <c r="B42" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C42" s="70"/>
+      <c r="D42" s="70"/>
+      <c r="E42" s="70"/>
+      <c r="F42" s="70"/>
+      <c r="G42" s="70"/>
+      <c r="H42" s="70"/>
+      <c r="I42" s="70"/>
+      <c r="J42" s="71"/>
+      <c r="K42" s="72"/>
+      <c r="L42" s="55"/>
+      <c r="M42" s="73"/>
+      <c r="N42" s="74"/>
+      <c r="O42" s="70"/>
+      <c r="P42" s="71"/>
+      <c r="Q42" s="71"/>
+      <c r="R42" s="72"/>
+      <c r="S42" s="55"/>
+      <c r="T42" s="75"/>
+      <c r="U42" s="75"/>
+      <c r="V42" s="75"/>
+    </row>
+    <row r="43" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="27">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="B43" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="C43" s="65">
+        <f>8856+9720+19764</f>
+        <v>38340</v>
+      </c>
+      <c r="D43" s="65"/>
+      <c r="E43" s="65"/>
+      <c r="F43" s="65"/>
+      <c r="G43" s="65"/>
+      <c r="H43" s="65">
+        <v>9</v>
+      </c>
+      <c r="I43" s="65">
+        <v>12</v>
+      </c>
+      <c r="J43" s="66">
+        <f>26*6+4</f>
+        <v>160</v>
+      </c>
+      <c r="K43" s="67">
+        <f>69*6+1</f>
+        <v>415</v>
+      </c>
+      <c r="L43" s="62"/>
+      <c r="M43" s="63">
+        <v>422</v>
+      </c>
+      <c r="N43" s="64"/>
+      <c r="O43" s="65">
+        <v>443</v>
+      </c>
+      <c r="P43" s="66"/>
+      <c r="Q43" s="66">
+        <v>563</v>
+      </c>
+      <c r="R43" s="67"/>
+      <c r="S43" s="62"/>
+      <c r="T43" s="77">
+        <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
+        <v>596</v>
+      </c>
+      <c r="U43" s="77">
+        <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
+        <v>239204</v>
+      </c>
+      <c r="V43" s="77">
+        <f>U43/6</f>
+        <v>39867.333333333336</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="27">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+      <c r="B44" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="70"/>
+      <c r="D44" s="70"/>
+      <c r="E44" s="70"/>
+      <c r="F44" s="70"/>
+      <c r="G44" s="70"/>
+      <c r="H44" s="70"/>
+      <c r="I44" s="70"/>
+      <c r="J44" s="71"/>
+      <c r="K44" s="72"/>
+      <c r="L44" s="55"/>
+      <c r="M44" s="73"/>
+      <c r="N44" s="74"/>
+      <c r="O44" s="70"/>
+      <c r="P44" s="71"/>
+      <c r="Q44" s="71"/>
+      <c r="R44" s="72"/>
+      <c r="S44" s="55"/>
+      <c r="T44" s="75"/>
+      <c r="U44" s="75"/>
+      <c r="V44" s="75"/>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A45" s="27">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="B45" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="70"/>
+      <c r="D45" s="70"/>
+      <c r="E45" s="70"/>
+      <c r="F45" s="70"/>
+      <c r="G45" s="70"/>
+      <c r="H45" s="70"/>
+      <c r="I45" s="70"/>
+      <c r="J45" s="71"/>
+      <c r="K45" s="72"/>
+      <c r="L45" s="55"/>
+      <c r="M45" s="73"/>
+      <c r="N45" s="74"/>
+      <c r="O45" s="70"/>
+      <c r="P45" s="71"/>
+      <c r="Q45" s="71"/>
+      <c r="R45" s="72"/>
+      <c r="S45" s="55"/>
+      <c r="T45" s="75">
+        <f t="shared" ref="T45:T54" si="7">H45+I45+J45+K45+N45+P45+R45</f>
+        <v>0</v>
+      </c>
+      <c r="U45" s="75">
+        <f>C45*24+M45*24+O45*24+Q45*24+T45</f>
+        <v>0</v>
+      </c>
+      <c r="V45" s="75">
+        <f>U45/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A46" s="27">
+        <f t="shared" si="1"/>
+        <v>43</v>
+      </c>
+      <c r="B46" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="C46" s="70"/>
+      <c r="D46" s="70"/>
+      <c r="E46" s="70"/>
+      <c r="F46" s="70"/>
+      <c r="G46" s="70"/>
+      <c r="H46" s="70"/>
+      <c r="I46" s="70"/>
+      <c r="J46" s="71"/>
+      <c r="K46" s="72"/>
+      <c r="L46" s="55"/>
+      <c r="M46" s="73"/>
+      <c r="N46" s="74"/>
+      <c r="O46" s="70"/>
+      <c r="P46" s="71"/>
+      <c r="Q46" s="71"/>
+      <c r="R46" s="72"/>
+      <c r="S46" s="55"/>
+      <c r="T46" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U46" s="75">
+        <f t="shared" ref="U46:U50" si="8">C46*24+M46*24+O46*24+Q46*24+T46</f>
+        <v>0</v>
+      </c>
+      <c r="V46" s="75">
+        <f t="shared" ref="V46:V54" si="9">U46/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="27">
+        <f t="shared" si="1"/>
+        <v>44</v>
+      </c>
+      <c r="B47" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="C47" s="65">
+        <f>89+648+324+88+432+98+103+324+432+106</f>
+        <v>2644</v>
+      </c>
+      <c r="D47" s="65"/>
+      <c r="E47" s="65"/>
+      <c r="F47" s="65"/>
+      <c r="G47" s="65"/>
+      <c r="H47" s="65">
+        <v>1</v>
+      </c>
+      <c r="I47" s="65"/>
+      <c r="J47" s="66"/>
+      <c r="K47" s="67">
+        <v>5</v>
+      </c>
+      <c r="L47" s="62"/>
+      <c r="M47" s="63">
+        <v>15</v>
+      </c>
+      <c r="N47" s="64"/>
+      <c r="O47" s="65">
+        <v>15</v>
+      </c>
+      <c r="P47" s="66"/>
+      <c r="Q47" s="66">
+        <v>5</v>
+      </c>
+      <c r="R47" s="67">
+        <v>3</v>
+      </c>
+      <c r="S47" s="62"/>
+      <c r="T47" s="77">
+        <f t="shared" si="7"/>
+        <v>9</v>
+      </c>
+      <c r="U47" s="77">
+        <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
+        <v>16083</v>
+      </c>
+      <c r="V47" s="77">
+        <f>U47/6</f>
+        <v>2680.5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A48" s="27">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="B48" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C48" s="70"/>
+      <c r="D48" s="70"/>
+      <c r="E48" s="70"/>
+      <c r="F48" s="70"/>
+      <c r="G48" s="70"/>
+      <c r="H48" s="70">
+        <v>24</v>
+      </c>
+      <c r="I48" s="70"/>
+      <c r="J48" s="71"/>
+      <c r="K48" s="72"/>
+      <c r="L48" s="55"/>
+      <c r="M48" s="73"/>
+      <c r="N48" s="74"/>
+      <c r="O48" s="70"/>
+      <c r="P48" s="71"/>
+      <c r="Q48" s="71"/>
+      <c r="R48" s="72"/>
+      <c r="S48" s="55"/>
+      <c r="T48" s="75">
+        <f t="shared" si="7"/>
+        <v>24</v>
+      </c>
+      <c r="U48" s="75">
+        <f t="shared" si="8"/>
+        <v>24</v>
+      </c>
+      <c r="V48" s="75">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A49" s="27">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="B49" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C49" s="70"/>
+      <c r="D49" s="70"/>
+      <c r="E49" s="70"/>
+      <c r="F49" s="70"/>
+      <c r="G49" s="70"/>
+      <c r="H49" s="70"/>
+      <c r="I49" s="70"/>
+      <c r="J49" s="71"/>
+      <c r="K49" s="72"/>
+      <c r="L49" s="55"/>
+      <c r="M49" s="73"/>
+      <c r="N49" s="74"/>
+      <c r="O49" s="70"/>
+      <c r="P49" s="71"/>
+      <c r="Q49" s="71"/>
+      <c r="R49" s="72"/>
+      <c r="S49" s="55"/>
+      <c r="T49" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U49" s="75">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V49" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A50" s="27">
+        <f t="shared" si="1"/>
+        <v>47</v>
+      </c>
+      <c r="B50" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="C50" s="70"/>
+      <c r="D50" s="70"/>
+      <c r="E50" s="70"/>
+      <c r="F50" s="70"/>
+      <c r="G50" s="70"/>
+      <c r="H50" s="70"/>
+      <c r="I50" s="70"/>
+      <c r="J50" s="71"/>
+      <c r="K50" s="72"/>
+      <c r="L50" s="55"/>
+      <c r="M50" s="73"/>
+      <c r="N50" s="74"/>
+      <c r="O50" s="70"/>
+      <c r="P50" s="71"/>
+      <c r="Q50" s="71"/>
+      <c r="R50" s="72"/>
+      <c r="S50" s="55"/>
+      <c r="T50" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U50" s="75">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V50" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="27">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+      <c r="B51" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="C51" s="65">
+        <v>34</v>
+      </c>
+      <c r="D51" s="65"/>
+      <c r="E51" s="65"/>
+      <c r="F51" s="65"/>
+      <c r="G51" s="65"/>
+      <c r="H51" s="65"/>
+      <c r="I51" s="65"/>
+      <c r="J51" s="66"/>
+      <c r="K51" s="67"/>
+      <c r="L51" s="62"/>
+      <c r="M51" s="63"/>
+      <c r="N51" s="64"/>
+      <c r="O51" s="65"/>
+      <c r="P51" s="66"/>
+      <c r="Q51" s="66"/>
+      <c r="R51" s="67"/>
+      <c r="S51" s="62"/>
+      <c r="T51" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U51" s="77">
+        <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
+        <v>204</v>
+      </c>
+      <c r="V51" s="77">
+        <f>U51/6</f>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A52" s="27">
+        <f t="shared" si="1"/>
+        <v>49</v>
+      </c>
+      <c r="B52" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="C52" s="70"/>
+      <c r="D52" s="70"/>
+      <c r="E52" s="70"/>
+      <c r="F52" s="70"/>
+      <c r="G52" s="70"/>
+      <c r="H52" s="70"/>
+      <c r="I52" s="70"/>
+      <c r="J52" s="71"/>
+      <c r="K52" s="72"/>
+      <c r="L52" s="55"/>
+      <c r="M52" s="73"/>
+      <c r="N52" s="74"/>
+      <c r="O52" s="70"/>
+      <c r="P52" s="71"/>
+      <c r="Q52" s="71"/>
+      <c r="R52" s="72"/>
+      <c r="S52" s="55"/>
+      <c r="T52" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U52" s="75">
+        <f t="shared" ref="U52:U54" si="10">C52*24+M52*24+O52*24+Q52*24+T52</f>
+        <v>0</v>
+      </c>
+      <c r="V52" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A53" s="27">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="B53" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C53" s="70">
+        <v>7</v>
+      </c>
+      <c r="D53" s="70"/>
+      <c r="E53" s="70"/>
+      <c r="F53" s="70"/>
+      <c r="G53" s="70"/>
+      <c r="H53" s="70"/>
+      <c r="I53" s="70"/>
+      <c r="J53" s="71"/>
+      <c r="K53" s="72"/>
+      <c r="L53" s="55"/>
+      <c r="M53" s="73"/>
+      <c r="N53" s="74"/>
+      <c r="O53" s="70"/>
+      <c r="P53" s="71"/>
+      <c r="Q53" s="71"/>
+      <c r="R53" s="72"/>
+      <c r="S53" s="55"/>
+      <c r="T53" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U53" s="75">
+        <f t="shared" si="10"/>
+        <v>168</v>
+      </c>
+      <c r="V53" s="75">
+        <f t="shared" si="9"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A54" s="27">
+        <f t="shared" si="1"/>
+        <v>51</v>
+      </c>
+      <c r="B54" s="26"/>
+      <c r="C54" s="70"/>
+      <c r="D54" s="70"/>
+      <c r="E54" s="70"/>
+      <c r="F54" s="70"/>
+      <c r="G54" s="70"/>
+      <c r="H54" s="70"/>
+      <c r="I54" s="70"/>
+      <c r="J54" s="71"/>
+      <c r="K54" s="72"/>
+      <c r="L54" s="55"/>
+      <c r="M54" s="73"/>
+      <c r="N54" s="74"/>
+      <c r="O54" s="70"/>
+      <c r="P54" s="71"/>
+      <c r="Q54" s="71"/>
+      <c r="R54" s="72"/>
+      <c r="S54" s="55"/>
+      <c r="T54" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U54" s="75">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V54" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A55" s="27">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="B55" s="26"/>
+      <c r="C55" s="70"/>
+      <c r="D55" s="70"/>
+      <c r="E55" s="70"/>
+      <c r="F55" s="70"/>
+      <c r="G55" s="70"/>
+      <c r="H55" s="70"/>
+      <c r="I55" s="70"/>
+      <c r="J55" s="71"/>
+      <c r="K55" s="72"/>
+      <c r="L55" s="55"/>
+      <c r="M55" s="73"/>
+      <c r="N55" s="74"/>
+      <c r="O55" s="70"/>
+      <c r="P55" s="71"/>
+      <c r="Q55" s="71"/>
+      <c r="R55" s="72"/>
+      <c r="S55" s="55"/>
+      <c r="T55" s="75"/>
+      <c r="U55" s="75"/>
+      <c r="V55" s="75"/>
+    </row>
+    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A56" s="27">
+        <f t="shared" si="1"/>
+        <v>53</v>
+      </c>
+      <c r="B56" s="26"/>
+      <c r="C56" s="70"/>
+      <c r="D56" s="70"/>
+      <c r="E56" s="70"/>
+      <c r="F56" s="70"/>
+      <c r="G56" s="70"/>
+      <c r="H56" s="70"/>
+      <c r="I56" s="70"/>
+      <c r="J56" s="71"/>
+      <c r="K56" s="72"/>
+      <c r="L56" s="55"/>
+      <c r="M56" s="73"/>
+      <c r="N56" s="74"/>
+      <c r="O56" s="70"/>
+      <c r="P56" s="71"/>
+      <c r="Q56" s="71"/>
+      <c r="R56" s="72"/>
+      <c r="S56" s="55"/>
+      <c r="T56" s="75"/>
+      <c r="U56" s="75"/>
+      <c r="V56" s="75"/>
+    </row>
+    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A57" s="27">
+        <f t="shared" si="1"/>
+        <v>54</v>
+      </c>
+      <c r="B57" s="26"/>
+      <c r="C57" s="70"/>
+      <c r="D57" s="70"/>
+      <c r="E57" s="70"/>
+      <c r="F57" s="70"/>
+      <c r="G57" s="70"/>
+      <c r="H57" s="70"/>
+      <c r="I57" s="70"/>
+      <c r="J57" s="71"/>
+      <c r="K57" s="72"/>
+      <c r="L57" s="55"/>
+      <c r="M57" s="73"/>
+      <c r="N57" s="74"/>
+      <c r="O57" s="70"/>
+      <c r="P57" s="71"/>
+      <c r="Q57" s="71"/>
+      <c r="R57" s="72"/>
+      <c r="S57" s="55"/>
+      <c r="T57" s="75"/>
+      <c r="U57" s="75"/>
+      <c r="V57" s="75"/>
+    </row>
+    <row r="58" spans="1:22" s="15" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B58" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="C58" s="2">
+        <f>SUM(C7:C57)</f>
+        <v>48611</v>
+      </c>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2">
+        <f t="shared" ref="F58:K58" si="11">SUM(F7:F57)</f>
+        <v>0</v>
+      </c>
+      <c r="G58" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="H58" s="2">
+        <f t="shared" si="11"/>
+        <v>1196</v>
+      </c>
+      <c r="I58" s="6">
+        <f t="shared" si="11"/>
+        <v>44</v>
+      </c>
+      <c r="J58" s="6">
+        <f t="shared" si="11"/>
+        <v>166</v>
+      </c>
+      <c r="K58" s="6">
+        <f t="shared" si="11"/>
+        <v>457</v>
+      </c>
+      <c r="M58" s="5">
+        <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
+        <v>573</v>
+      </c>
+      <c r="N58" s="5">
+        <f t="shared" si="12"/>
+        <v>20</v>
+      </c>
+      <c r="O58" s="5">
+        <f t="shared" si="12"/>
+        <v>511</v>
+      </c>
+      <c r="P58" s="5">
+        <f t="shared" si="12"/>
+        <v>30</v>
+      </c>
+      <c r="Q58" s="5">
+        <f t="shared" si="12"/>
+        <v>798</v>
+      </c>
+      <c r="R58" s="5">
+        <f t="shared" si="12"/>
+        <v>3</v>
+      </c>
+      <c r="S58" s="55"/>
+      <c r="T58" s="4">
+        <f>SUM(T7:T57)</f>
+        <v>1916</v>
+      </c>
+      <c r="U58" s="90">
+        <f>SUM(U7:U57)</f>
+        <v>380852</v>
+      </c>
+      <c r="V58" s="4">
+        <f>SUM(V7:V57)</f>
+        <v>50650.833333333336</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="60" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="C60" s="107" t="s">
+        <v>41</v>
+      </c>
+      <c r="D60" s="108"/>
+      <c r="E60" s="108"/>
+      <c r="F60" s="108"/>
+      <c r="G60" s="108"/>
+      <c r="H60" s="108"/>
+      <c r="I60" s="108"/>
+      <c r="J60" s="108"/>
+      <c r="K60" s="109"/>
+      <c r="U60" s="24" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B61" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="C61" s="19"/>
+      <c r="D61" s="19"/>
+      <c r="E61" s="19"/>
+      <c r="F61" s="19"/>
+      <c r="G61" s="19"/>
+      <c r="H61" s="19"/>
+      <c r="I61" s="19"/>
+      <c r="J61" s="45"/>
+      <c r="K61" s="20"/>
+      <c r="U61" s="7"/>
+    </row>
+    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B62" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+      <c r="J62" s="44"/>
+      <c r="K62" s="21"/>
+      <c r="U62" s="3"/>
+    </row>
+    <row r="63" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B63" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C63" s="22"/>
+      <c r="D63" s="22"/>
+      <c r="E63" s="22"/>
+      <c r="F63" s="22"/>
+      <c r="G63" s="22"/>
+      <c r="H63" s="22"/>
+      <c r="I63" s="22"/>
+      <c r="J63" s="46"/>
+      <c r="K63" s="23"/>
+      <c r="U63" s="8"/>
+    </row>
+    <row r="64" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B65" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="C65" s="19"/>
+      <c r="D65" s="19"/>
+      <c r="E65" s="19"/>
+      <c r="F65" s="19"/>
+      <c r="G65" s="19"/>
+      <c r="H65" s="19"/>
+      <c r="I65" s="19"/>
+      <c r="J65" s="45"/>
+      <c r="K65" s="20"/>
+      <c r="U65" s="7"/>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B66" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C66" s="1"/>
+      <c r="D66" s="1"/>
+      <c r="E66" s="1"/>
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="J66" s="44"/>
+      <c r="K66" s="21"/>
+      <c r="U66" s="3"/>
+    </row>
+    <row r="67" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B67" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C67" s="22"/>
+      <c r="D67" s="22"/>
+      <c r="E67" s="22"/>
+      <c r="F67" s="22"/>
+      <c r="G67" s="22"/>
+      <c r="H67" s="22"/>
+      <c r="I67" s="22"/>
+      <c r="J67" s="46"/>
+      <c r="K67" s="23"/>
+      <c r="U67" s="8"/>
+    </row>
+    <row r="68" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B69" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="C69" s="19"/>
+      <c r="D69" s="19"/>
+      <c r="E69" s="19"/>
+      <c r="F69" s="19"/>
+      <c r="G69" s="19"/>
+      <c r="H69" s="19"/>
+      <c r="I69" s="19"/>
+      <c r="J69" s="45"/>
+      <c r="K69" s="20"/>
+      <c r="U69" s="7"/>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B70" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="J70" s="44"/>
+      <c r="K70" s="21"/>
+      <c r="U70" s="3"/>
+    </row>
+    <row r="71" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B71" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C71" s="22"/>
+      <c r="D71" s="22"/>
+      <c r="E71" s="22"/>
+      <c r="F71" s="22"/>
+      <c r="G71" s="22"/>
+      <c r="H71" s="22"/>
+      <c r="I71" s="22"/>
+      <c r="J71" s="46"/>
+      <c r="K71" s="23"/>
+      <c r="U71" s="8"/>
+    </row>
+    <row r="72" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B73" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="C73" s="19"/>
+      <c r="D73" s="19"/>
+      <c r="E73" s="19"/>
+      <c r="F73" s="19"/>
+      <c r="G73" s="19"/>
+      <c r="H73" s="19"/>
+      <c r="I73" s="19"/>
+      <c r="J73" s="45"/>
+      <c r="K73" s="20"/>
+      <c r="U73" s="7"/>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B74" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C74" s="1"/>
+      <c r="D74" s="1"/>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1"/>
+      <c r="J74" s="44"/>
+      <c r="K74" s="21"/>
+      <c r="U74" s="3"/>
+    </row>
+    <row r="75" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B75" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C75" s="22"/>
+      <c r="D75" s="22"/>
+      <c r="E75" s="22"/>
+      <c r="F75" s="22"/>
+      <c r="G75" s="22"/>
+      <c r="H75" s="22"/>
+      <c r="I75" s="22"/>
+      <c r="J75" s="46"/>
+      <c r="K75" s="23"/>
+      <c r="U75" s="8"/>
+    </row>
+    <row r="76" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B77" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="C77" s="19"/>
+      <c r="D77" s="19"/>
+      <c r="E77" s="19"/>
+      <c r="F77" s="19"/>
+      <c r="G77" s="19"/>
+      <c r="H77" s="19"/>
+      <c r="I77" s="19"/>
+      <c r="J77" s="45"/>
+      <c r="K77" s="20"/>
+      <c r="U77" s="7"/>
+    </row>
+    <row r="78" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B78" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C78" s="1"/>
+      <c r="D78" s="1"/>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+      <c r="J78" s="44"/>
+      <c r="K78" s="21"/>
+      <c r="U78" s="3"/>
+    </row>
+    <row r="79" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B79" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C79" s="22"/>
+      <c r="D79" s="22"/>
+      <c r="E79" s="22"/>
+      <c r="F79" s="22"/>
+      <c r="G79" s="22"/>
+      <c r="H79" s="22"/>
+      <c r="I79" s="22"/>
+      <c r="J79" s="46"/>
+      <c r="K79" s="23"/>
+      <c r="U79" s="8"/>
+    </row>
+    <row r="80" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="81" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B81" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="C81" s="17"/>
+      <c r="D81" s="17"/>
+      <c r="E81" s="17"/>
+      <c r="F81" s="17"/>
+      <c r="G81" s="17"/>
+      <c r="H81" s="17"/>
+      <c r="I81" s="17"/>
+      <c r="J81" s="47"/>
+      <c r="K81" s="18"/>
+      <c r="U81" s="16"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
     <mergeCell ref="V4:V5"/>
     <mergeCell ref="J5:K5"/>
+    <mergeCell ref="C60:K60"/>
+    <mergeCell ref="I1:U1"/>
+    <mergeCell ref="C4:K4"/>
+    <mergeCell ref="T4:T5"/>
+    <mergeCell ref="U4:U5"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -23797,21 +26953,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="109" t="s">
+      <c r="I1" s="110" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="109"/>
-      <c r="K1" s="109"/>
-      <c r="L1" s="109"/>
-      <c r="M1" s="109"/>
-      <c r="N1" s="109"/>
-      <c r="O1" s="109"/>
-      <c r="P1" s="109"/>
-      <c r="Q1" s="109"/>
-      <c r="R1" s="109"/>
-      <c r="S1" s="109"/>
-      <c r="T1" s="109"/>
-      <c r="U1" s="109"/>
+      <c r="J1" s="110"/>
+      <c r="K1" s="110"/>
+      <c r="L1" s="110"/>
+      <c r="M1" s="110"/>
+      <c r="N1" s="110"/>
+      <c r="O1" s="110"/>
+      <c r="P1" s="110"/>
+      <c r="Q1" s="110"/>
+      <c r="R1" s="110"/>
+      <c r="S1" s="110"/>
+      <c r="T1" s="110"/>
+      <c r="U1" s="110"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -23823,17 +26979,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="110" t="s">
+      <c r="C4" s="111" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="110"/>
-      <c r="E4" s="110"/>
-      <c r="F4" s="110"/>
-      <c r="G4" s="110"/>
-      <c r="H4" s="110"/>
-      <c r="I4" s="110"/>
-      <c r="J4" s="111"/>
-      <c r="K4" s="112"/>
+      <c r="D4" s="111"/>
+      <c r="E4" s="111"/>
+      <c r="F4" s="111"/>
+      <c r="G4" s="111"/>
+      <c r="H4" s="111"/>
+      <c r="I4" s="111"/>
+      <c r="J4" s="112"/>
+      <c r="K4" s="113"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -23853,13 +27009,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="113" t="s">
+      <c r="T4" s="114" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="119" t="s">
+      <c r="U4" s="120" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="102" t="s">
+      <c r="V4" s="103" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -23899,10 +27055,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="117" t="s">
+      <c r="J5" s="118" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="118"/>
+      <c r="K5" s="119"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -23910,9 +27066,9 @@
       <c r="Q5" s="96"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="114"/>
-      <c r="U5" s="120"/>
-      <c r="V5" s="103"/>
+      <c r="T5" s="115"/>
+      <c r="U5" s="121"/>
+      <c r="V5" s="104"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -26622,17 +29778,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="106" t="s">
+      <c r="C60" s="107" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="107"/>
-      <c r="E60" s="107"/>
-      <c r="F60" s="107"/>
-      <c r="G60" s="107"/>
-      <c r="H60" s="107"/>
-      <c r="I60" s="107"/>
-      <c r="J60" s="107"/>
-      <c r="K60" s="108"/>
+      <c r="D60" s="108"/>
+      <c r="E60" s="108"/>
+      <c r="F60" s="108"/>
+      <c r="G60" s="108"/>
+      <c r="H60" s="108"/>
+      <c r="I60" s="108"/>
+      <c r="J60" s="108"/>
+      <c r="K60" s="109"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -26941,21 +30097,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="109" t="s">
+      <c r="I1" s="110" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="109"/>
-      <c r="K1" s="109"/>
-      <c r="L1" s="109"/>
-      <c r="M1" s="109"/>
-      <c r="N1" s="109"/>
-      <c r="O1" s="109"/>
-      <c r="P1" s="109"/>
-      <c r="Q1" s="109"/>
-      <c r="R1" s="109"/>
-      <c r="S1" s="109"/>
-      <c r="T1" s="109"/>
-      <c r="U1" s="109"/>
+      <c r="J1" s="110"/>
+      <c r="K1" s="110"/>
+      <c r="L1" s="110"/>
+      <c r="M1" s="110"/>
+      <c r="N1" s="110"/>
+      <c r="O1" s="110"/>
+      <c r="P1" s="110"/>
+      <c r="Q1" s="110"/>
+      <c r="R1" s="110"/>
+      <c r="S1" s="110"/>
+      <c r="T1" s="110"/>
+      <c r="U1" s="110"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -26967,17 +30123,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="110" t="s">
+      <c r="C4" s="111" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="110"/>
-      <c r="E4" s="110"/>
-      <c r="F4" s="110"/>
-      <c r="G4" s="110"/>
-      <c r="H4" s="110"/>
-      <c r="I4" s="110"/>
-      <c r="J4" s="111"/>
-      <c r="K4" s="112"/>
+      <c r="D4" s="111"/>
+      <c r="E4" s="111"/>
+      <c r="F4" s="111"/>
+      <c r="G4" s="111"/>
+      <c r="H4" s="111"/>
+      <c r="I4" s="111"/>
+      <c r="J4" s="112"/>
+      <c r="K4" s="113"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -26997,13 +30153,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="113" t="s">
+      <c r="T4" s="114" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="119" t="s">
+      <c r="U4" s="120" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="102" t="s">
+      <c r="V4" s="103" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -27043,10 +30199,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="117" t="s">
+      <c r="J5" s="118" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="118"/>
+      <c r="K5" s="119"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -27054,9 +30210,9 @@
       <c r="Q5" s="97"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="114"/>
-      <c r="U5" s="120"/>
-      <c r="V5" s="103"/>
+      <c r="T5" s="115"/>
+      <c r="U5" s="121"/>
+      <c r="V5" s="104"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -29756,17 +32912,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="106" t="s">
+      <c r="C60" s="107" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="107"/>
-      <c r="E60" s="107"/>
-      <c r="F60" s="107"/>
-      <c r="G60" s="107"/>
-      <c r="H60" s="107"/>
-      <c r="I60" s="107"/>
-      <c r="J60" s="107"/>
-      <c r="K60" s="108"/>
+      <c r="D60" s="108"/>
+      <c r="E60" s="108"/>
+      <c r="F60" s="108"/>
+      <c r="G60" s="108"/>
+      <c r="H60" s="108"/>
+      <c r="I60" s="108"/>
+      <c r="J60" s="108"/>
+      <c r="K60" s="109"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -30075,21 +33231,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="109" t="s">
+      <c r="I1" s="110" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="109"/>
-      <c r="K1" s="109"/>
-      <c r="L1" s="109"/>
-      <c r="M1" s="109"/>
-      <c r="N1" s="109"/>
-      <c r="O1" s="109"/>
-      <c r="P1" s="109"/>
-      <c r="Q1" s="109"/>
-      <c r="R1" s="109"/>
-      <c r="S1" s="109"/>
-      <c r="T1" s="109"/>
-      <c r="U1" s="109"/>
+      <c r="J1" s="110"/>
+      <c r="K1" s="110"/>
+      <c r="L1" s="110"/>
+      <c r="M1" s="110"/>
+      <c r="N1" s="110"/>
+      <c r="O1" s="110"/>
+      <c r="P1" s="110"/>
+      <c r="Q1" s="110"/>
+      <c r="R1" s="110"/>
+      <c r="S1" s="110"/>
+      <c r="T1" s="110"/>
+      <c r="U1" s="110"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -30101,17 +33257,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="110" t="s">
+      <c r="C4" s="111" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="110"/>
-      <c r="E4" s="110"/>
-      <c r="F4" s="110"/>
-      <c r="G4" s="110"/>
-      <c r="H4" s="110"/>
-      <c r="I4" s="110"/>
-      <c r="J4" s="111"/>
-      <c r="K4" s="112"/>
+      <c r="D4" s="111"/>
+      <c r="E4" s="111"/>
+      <c r="F4" s="111"/>
+      <c r="G4" s="111"/>
+      <c r="H4" s="111"/>
+      <c r="I4" s="111"/>
+      <c r="J4" s="112"/>
+      <c r="K4" s="113"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -30131,13 +33287,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="113" t="s">
+      <c r="T4" s="114" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="119" t="s">
+      <c r="U4" s="120" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="102" t="s">
+      <c r="V4" s="103" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -30177,10 +33333,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="117" t="s">
+      <c r="J5" s="118" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="118"/>
+      <c r="K5" s="119"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -30188,9 +33344,9 @@
       <c r="Q5" s="97"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="114"/>
-      <c r="U5" s="120"/>
-      <c r="V5" s="103"/>
+      <c r="T5" s="115"/>
+      <c r="U5" s="121"/>
+      <c r="V5" s="104"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -32890,17 +36046,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="106" t="s">
+      <c r="C60" s="107" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="107"/>
-      <c r="E60" s="107"/>
-      <c r="F60" s="107"/>
-      <c r="G60" s="107"/>
-      <c r="H60" s="107"/>
-      <c r="I60" s="107"/>
-      <c r="J60" s="107"/>
-      <c r="K60" s="108"/>
+      <c r="D60" s="108"/>
+      <c r="E60" s="108"/>
+      <c r="F60" s="108"/>
+      <c r="G60" s="108"/>
+      <c r="H60" s="108"/>
+      <c r="I60" s="108"/>
+      <c r="J60" s="108"/>
+      <c r="K60" s="109"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -33209,21 +36365,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="109" t="s">
+      <c r="I1" s="110" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="109"/>
-      <c r="K1" s="109"/>
-      <c r="L1" s="109"/>
-      <c r="M1" s="109"/>
-      <c r="N1" s="109"/>
-      <c r="O1" s="109"/>
-      <c r="P1" s="109"/>
-      <c r="Q1" s="109"/>
-      <c r="R1" s="109"/>
-      <c r="S1" s="109"/>
-      <c r="T1" s="109"/>
-      <c r="U1" s="109"/>
+      <c r="J1" s="110"/>
+      <c r="K1" s="110"/>
+      <c r="L1" s="110"/>
+      <c r="M1" s="110"/>
+      <c r="N1" s="110"/>
+      <c r="O1" s="110"/>
+      <c r="P1" s="110"/>
+      <c r="Q1" s="110"/>
+      <c r="R1" s="110"/>
+      <c r="S1" s="110"/>
+      <c r="T1" s="110"/>
+      <c r="U1" s="110"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -33235,17 +36391,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="110" t="s">
+      <c r="C4" s="111" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="110"/>
-      <c r="E4" s="110"/>
-      <c r="F4" s="110"/>
-      <c r="G4" s="110"/>
-      <c r="H4" s="110"/>
-      <c r="I4" s="110"/>
-      <c r="J4" s="111"/>
-      <c r="K4" s="112"/>
+      <c r="D4" s="111"/>
+      <c r="E4" s="111"/>
+      <c r="F4" s="111"/>
+      <c r="G4" s="111"/>
+      <c r="H4" s="111"/>
+      <c r="I4" s="111"/>
+      <c r="J4" s="112"/>
+      <c r="K4" s="113"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -33265,13 +36421,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="113" t="s">
+      <c r="T4" s="114" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="119" t="s">
+      <c r="U4" s="120" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="102" t="s">
+      <c r="V4" s="103" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -33311,10 +36467,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="117" t="s">
+      <c r="J5" s="118" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="118"/>
+      <c r="K5" s="119"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -33322,9 +36478,9 @@
       <c r="Q5" s="97"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="114"/>
-      <c r="U5" s="120"/>
-      <c r="V5" s="103"/>
+      <c r="T5" s="115"/>
+      <c r="U5" s="121"/>
+      <c r="V5" s="104"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -36014,17 +39170,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="106" t="s">
+      <c r="C60" s="107" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="107"/>
-      <c r="E60" s="107"/>
-      <c r="F60" s="107"/>
-      <c r="G60" s="107"/>
-      <c r="H60" s="107"/>
-      <c r="I60" s="107"/>
-      <c r="J60" s="107"/>
-      <c r="K60" s="108"/>
+      <c r="D60" s="108"/>
+      <c r="E60" s="108"/>
+      <c r="F60" s="108"/>
+      <c r="G60" s="108"/>
+      <c r="H60" s="108"/>
+      <c r="I60" s="108"/>
+      <c r="J60" s="108"/>
+      <c r="K60" s="109"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -36333,21 +39489,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="109" t="s">
+      <c r="I1" s="110" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="109"/>
-      <c r="K1" s="109"/>
-      <c r="L1" s="109"/>
-      <c r="M1" s="109"/>
-      <c r="N1" s="109"/>
-      <c r="O1" s="109"/>
-      <c r="P1" s="109"/>
-      <c r="Q1" s="109"/>
-      <c r="R1" s="109"/>
-      <c r="S1" s="109"/>
-      <c r="T1" s="109"/>
-      <c r="U1" s="109"/>
+      <c r="J1" s="110"/>
+      <c r="K1" s="110"/>
+      <c r="L1" s="110"/>
+      <c r="M1" s="110"/>
+      <c r="N1" s="110"/>
+      <c r="O1" s="110"/>
+      <c r="P1" s="110"/>
+      <c r="Q1" s="110"/>
+      <c r="R1" s="110"/>
+      <c r="S1" s="110"/>
+      <c r="T1" s="110"/>
+      <c r="U1" s="110"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -36359,17 +39515,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="110" t="s">
+      <c r="C4" s="111" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="110"/>
-      <c r="E4" s="110"/>
-      <c r="F4" s="110"/>
-      <c r="G4" s="110"/>
-      <c r="H4" s="110"/>
-      <c r="I4" s="110"/>
-      <c r="J4" s="111"/>
-      <c r="K4" s="112"/>
+      <c r="D4" s="111"/>
+      <c r="E4" s="111"/>
+      <c r="F4" s="111"/>
+      <c r="G4" s="111"/>
+      <c r="H4" s="111"/>
+      <c r="I4" s="111"/>
+      <c r="J4" s="112"/>
+      <c r="K4" s="113"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -36389,13 +39545,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="113" t="s">
+      <c r="T4" s="114" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="119" t="s">
+      <c r="U4" s="120" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="102" t="s">
+      <c r="V4" s="103" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -36435,10 +39591,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="117" t="s">
+      <c r="J5" s="118" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="118"/>
+      <c r="K5" s="119"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -36446,9 +39602,9 @@
       <c r="Q5" s="98"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="114"/>
-      <c r="U5" s="120"/>
-      <c r="V5" s="103"/>
+      <c r="T5" s="115"/>
+      <c r="U5" s="121"/>
+      <c r="V5" s="104"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -39163,17 +42319,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="106" t="s">
+      <c r="C60" s="107" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="107"/>
-      <c r="E60" s="107"/>
-      <c r="F60" s="107"/>
-      <c r="G60" s="107"/>
-      <c r="H60" s="107"/>
-      <c r="I60" s="107"/>
-      <c r="J60" s="107"/>
-      <c r="K60" s="108"/>
+      <c r="D60" s="108"/>
+      <c r="E60" s="108"/>
+      <c r="F60" s="108"/>
+      <c r="G60" s="108"/>
+      <c r="H60" s="108"/>
+      <c r="I60" s="108"/>
+      <c r="J60" s="108"/>
+      <c r="K60" s="109"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -39482,21 +42638,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="109" t="s">
+      <c r="I1" s="110" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="109"/>
-      <c r="K1" s="109"/>
-      <c r="L1" s="109"/>
-      <c r="M1" s="109"/>
-      <c r="N1" s="109"/>
-      <c r="O1" s="109"/>
-      <c r="P1" s="109"/>
-      <c r="Q1" s="109"/>
-      <c r="R1" s="109"/>
-      <c r="S1" s="109"/>
-      <c r="T1" s="109"/>
-      <c r="U1" s="109"/>
+      <c r="J1" s="110"/>
+      <c r="K1" s="110"/>
+      <c r="L1" s="110"/>
+      <c r="M1" s="110"/>
+      <c r="N1" s="110"/>
+      <c r="O1" s="110"/>
+      <c r="P1" s="110"/>
+      <c r="Q1" s="110"/>
+      <c r="R1" s="110"/>
+      <c r="S1" s="110"/>
+      <c r="T1" s="110"/>
+      <c r="U1" s="110"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -39508,17 +42664,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="110" t="s">
+      <c r="C4" s="111" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="110"/>
-      <c r="E4" s="110"/>
-      <c r="F4" s="110"/>
-      <c r="G4" s="110"/>
-      <c r="H4" s="110"/>
-      <c r="I4" s="110"/>
-      <c r="J4" s="111"/>
-      <c r="K4" s="112"/>
+      <c r="D4" s="111"/>
+      <c r="E4" s="111"/>
+      <c r="F4" s="111"/>
+      <c r="G4" s="111"/>
+      <c r="H4" s="111"/>
+      <c r="I4" s="111"/>
+      <c r="J4" s="112"/>
+      <c r="K4" s="113"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -39538,13 +42694,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="113" t="s">
+      <c r="T4" s="114" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="119" t="s">
+      <c r="U4" s="120" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="102" t="s">
+      <c r="V4" s="103" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -39584,10 +42740,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="117" t="s">
+      <c r="J5" s="118" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="118"/>
+      <c r="K5" s="119"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -39595,9 +42751,9 @@
       <c r="Q5" s="98"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="114"/>
-      <c r="U5" s="120"/>
-      <c r="V5" s="103"/>
+      <c r="T5" s="115"/>
+      <c r="U5" s="121"/>
+      <c r="V5" s="104"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -42302,17 +45458,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="106" t="s">
+      <c r="C60" s="107" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="107"/>
-      <c r="E60" s="107"/>
-      <c r="F60" s="107"/>
-      <c r="G60" s="107"/>
-      <c r="H60" s="107"/>
-      <c r="I60" s="107"/>
-      <c r="J60" s="107"/>
-      <c r="K60" s="108"/>
+      <c r="D60" s="108"/>
+      <c r="E60" s="108"/>
+      <c r="F60" s="108"/>
+      <c r="G60" s="108"/>
+      <c r="H60" s="108"/>
+      <c r="I60" s="108"/>
+      <c r="J60" s="108"/>
+      <c r="K60" s="109"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -42621,21 +45777,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="109" t="s">
+      <c r="I1" s="110" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="109"/>
-      <c r="K1" s="109"/>
-      <c r="L1" s="109"/>
-      <c r="M1" s="109"/>
-      <c r="N1" s="109"/>
-      <c r="O1" s="109"/>
-      <c r="P1" s="109"/>
-      <c r="Q1" s="109"/>
-      <c r="R1" s="109"/>
-      <c r="S1" s="109"/>
-      <c r="T1" s="109"/>
-      <c r="U1" s="109"/>
+      <c r="J1" s="110"/>
+      <c r="K1" s="110"/>
+      <c r="L1" s="110"/>
+      <c r="M1" s="110"/>
+      <c r="N1" s="110"/>
+      <c r="O1" s="110"/>
+      <c r="P1" s="110"/>
+      <c r="Q1" s="110"/>
+      <c r="R1" s="110"/>
+      <c r="S1" s="110"/>
+      <c r="T1" s="110"/>
+      <c r="U1" s="110"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -42647,17 +45803,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="110" t="s">
+      <c r="C4" s="111" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="110"/>
-      <c r="E4" s="110"/>
-      <c r="F4" s="110"/>
-      <c r="G4" s="110"/>
-      <c r="H4" s="110"/>
-      <c r="I4" s="110"/>
-      <c r="J4" s="111"/>
-      <c r="K4" s="112"/>
+      <c r="D4" s="111"/>
+      <c r="E4" s="111"/>
+      <c r="F4" s="111"/>
+      <c r="G4" s="111"/>
+      <c r="H4" s="111"/>
+      <c r="I4" s="111"/>
+      <c r="J4" s="112"/>
+      <c r="K4" s="113"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -42677,13 +45833,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="113" t="s">
+      <c r="T4" s="114" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="119" t="s">
+      <c r="U4" s="120" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="102" t="s">
+      <c r="V4" s="103" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -42723,10 +45879,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="117" t="s">
+      <c r="J5" s="118" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="118"/>
+      <c r="K5" s="119"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -42734,9 +45890,9 @@
       <c r="Q5" s="98"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="114"/>
-      <c r="U5" s="120"/>
-      <c r="V5" s="103"/>
+      <c r="T5" s="115"/>
+      <c r="U5" s="121"/>
+      <c r="V5" s="104"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -45438,17 +48594,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="106" t="s">
+      <c r="C60" s="107" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="107"/>
-      <c r="E60" s="107"/>
-      <c r="F60" s="107"/>
-      <c r="G60" s="107"/>
-      <c r="H60" s="107"/>
-      <c r="I60" s="107"/>
-      <c r="J60" s="107"/>
-      <c r="K60" s="108"/>
+      <c r="D60" s="108"/>
+      <c r="E60" s="108"/>
+      <c r="F60" s="108"/>
+      <c r="G60" s="108"/>
+      <c r="H60" s="108"/>
+      <c r="I60" s="108"/>
+      <c r="J60" s="108"/>
+      <c r="K60" s="109"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -45757,21 +48913,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="109" t="s">
+      <c r="I1" s="110" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="109"/>
-      <c r="K1" s="109"/>
-      <c r="L1" s="109"/>
-      <c r="M1" s="109"/>
-      <c r="N1" s="109"/>
-      <c r="O1" s="109"/>
-      <c r="P1" s="109"/>
-      <c r="Q1" s="109"/>
-      <c r="R1" s="109"/>
-      <c r="S1" s="109"/>
-      <c r="T1" s="109"/>
-      <c r="U1" s="109"/>
+      <c r="J1" s="110"/>
+      <c r="K1" s="110"/>
+      <c r="L1" s="110"/>
+      <c r="M1" s="110"/>
+      <c r="N1" s="110"/>
+      <c r="O1" s="110"/>
+      <c r="P1" s="110"/>
+      <c r="Q1" s="110"/>
+      <c r="R1" s="110"/>
+      <c r="S1" s="110"/>
+      <c r="T1" s="110"/>
+      <c r="U1" s="110"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -45783,17 +48939,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="110" t="s">
+      <c r="C4" s="111" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="110"/>
-      <c r="E4" s="110"/>
-      <c r="F4" s="110"/>
-      <c r="G4" s="110"/>
-      <c r="H4" s="110"/>
-      <c r="I4" s="110"/>
-      <c r="J4" s="111"/>
-      <c r="K4" s="112"/>
+      <c r="D4" s="111"/>
+      <c r="E4" s="111"/>
+      <c r="F4" s="111"/>
+      <c r="G4" s="111"/>
+      <c r="H4" s="111"/>
+      <c r="I4" s="111"/>
+      <c r="J4" s="112"/>
+      <c r="K4" s="113"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -45813,13 +48969,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="113" t="s">
+      <c r="T4" s="114" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="119" t="s">
+      <c r="U4" s="120" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="102" t="s">
+      <c r="V4" s="103" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -45859,10 +49015,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="117" t="s">
+      <c r="J5" s="118" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="118"/>
+      <c r="K5" s="119"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -45870,9 +49026,9 @@
       <c r="Q5" s="98"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="114"/>
-      <c r="U5" s="120"/>
-      <c r="V5" s="103"/>
+      <c r="T5" s="115"/>
+      <c r="U5" s="121"/>
+      <c r="V5" s="104"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -48584,17 +51740,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="106" t="s">
+      <c r="C60" s="107" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="107"/>
-      <c r="E60" s="107"/>
-      <c r="F60" s="107"/>
-      <c r="G60" s="107"/>
-      <c r="H60" s="107"/>
-      <c r="I60" s="107"/>
-      <c r="J60" s="107"/>
-      <c r="K60" s="108"/>
+      <c r="D60" s="108"/>
+      <c r="E60" s="108"/>
+      <c r="F60" s="108"/>
+      <c r="G60" s="108"/>
+      <c r="H60" s="108"/>
+      <c r="I60" s="108"/>
+      <c r="J60" s="108"/>
+      <c r="K60" s="109"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>

--- a/GBDS AUGUST FILES 2026/INVENTORY COUNT SHEET - AUGUST 2026.xlsx
+++ b/GBDS AUGUST FILES 2026/INVENTORY COUNT SHEET - AUGUST 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS AUGUST FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F79B0F49-671B-440B-82EF-E317E23A2229}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB1D556D-AD9A-4983-92C9-9A4B9FCFC299}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="6" activeTab="15" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="7" activeTab="16" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
   </bookViews>
   <sheets>
     <sheet name="SAMPLE" sheetId="32" r:id="rId1"/>
@@ -29,6 +29,7 @@
     <sheet name="08-18-2026" sheetId="81" r:id="rId14"/>
     <sheet name="08-19-2026" sheetId="82" r:id="rId15"/>
     <sheet name="08-20-2026" sheetId="83" r:id="rId16"/>
+    <sheet name="08-21-2026" sheetId="84" r:id="rId17"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'08-03-2026'!$A$1:$W$59</definedName>
@@ -46,6 +47,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="13">'08-18-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="14">'08-19-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="15">'08-20-2026'!$A$1:$W$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="16">'08-21-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">SAMPLE!$A$1:$W$85</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -64,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1344" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1428" uniqueCount="87">
   <si>
     <t>ROUTE 1</t>
   </si>
@@ -323,6 +325,9 @@
   </si>
   <si>
     <t>DATE: 08/18/2026</t>
+  </si>
+  <si>
+    <t>DATE: 08/21/2026</t>
   </si>
 </sst>
 </file>
@@ -1309,7 +1314,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="122">
+  <cellXfs count="123">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1595,6 +1600,9 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="63" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2029,21 +2037,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="110" t="s">
+      <c r="I1" s="111" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="110"/>
-      <c r="K1" s="110"/>
-      <c r="L1" s="110"/>
-      <c r="M1" s="110"/>
-      <c r="N1" s="110"/>
-      <c r="O1" s="110"/>
-      <c r="P1" s="110"/>
-      <c r="Q1" s="110"/>
-      <c r="R1" s="110"/>
-      <c r="S1" s="110"/>
-      <c r="T1" s="110"/>
-      <c r="U1" s="110"/>
+      <c r="J1" s="111"/>
+      <c r="K1" s="111"/>
+      <c r="L1" s="111"/>
+      <c r="M1" s="111"/>
+      <c r="N1" s="111"/>
+      <c r="O1" s="111"/>
+      <c r="P1" s="111"/>
+      <c r="Q1" s="111"/>
+      <c r="R1" s="111"/>
+      <c r="S1" s="111"/>
+      <c r="T1" s="111"/>
+      <c r="U1" s="111"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -2055,17 +2063,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="111" t="s">
+      <c r="C4" s="112" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="111"/>
-      <c r="E4" s="111"/>
-      <c r="F4" s="111"/>
-      <c r="G4" s="111"/>
-      <c r="H4" s="111"/>
-      <c r="I4" s="111"/>
-      <c r="J4" s="112"/>
-      <c r="K4" s="113"/>
+      <c r="D4" s="112"/>
+      <c r="E4" s="112"/>
+      <c r="F4" s="112"/>
+      <c r="G4" s="112"/>
+      <c r="H4" s="112"/>
+      <c r="I4" s="112"/>
+      <c r="J4" s="113"/>
+      <c r="K4" s="114"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -2085,13 +2093,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="114" t="s">
+      <c r="T4" s="115" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="116" t="s">
+      <c r="U4" s="117" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="103" t="s">
+      <c r="V4" s="104" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -2131,10 +2139,10 @@
       <c r="I5" s="93" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="105" t="s">
+      <c r="J5" s="106" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="106"/>
+      <c r="K5" s="107"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -2142,9 +2150,9 @@
       <c r="Q5" s="89"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="115"/>
-      <c r="U5" s="117"/>
-      <c r="V5" s="104"/>
+      <c r="T5" s="116"/>
+      <c r="U5" s="118"/>
+      <c r="V5" s="105"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -4675,17 +4683,17 @@
       <c r="B62" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C62" s="107" t="s">
+      <c r="C62" s="108" t="s">
         <v>41</v>
       </c>
-      <c r="D62" s="108"/>
-      <c r="E62" s="108"/>
-      <c r="F62" s="108"/>
-      <c r="G62" s="108"/>
-      <c r="H62" s="108"/>
-      <c r="I62" s="108"/>
-      <c r="J62" s="108"/>
-      <c r="K62" s="109"/>
+      <c r="D62" s="109"/>
+      <c r="E62" s="109"/>
+      <c r="F62" s="109"/>
+      <c r="G62" s="109"/>
+      <c r="H62" s="109"/>
+      <c r="I62" s="109"/>
+      <c r="J62" s="109"/>
+      <c r="K62" s="110"/>
       <c r="U62" s="24" t="s">
         <v>51</v>
       </c>
@@ -4994,21 +5002,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="110" t="s">
+      <c r="I1" s="111" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="110"/>
-      <c r="K1" s="110"/>
-      <c r="L1" s="110"/>
-      <c r="M1" s="110"/>
-      <c r="N1" s="110"/>
-      <c r="O1" s="110"/>
-      <c r="P1" s="110"/>
-      <c r="Q1" s="110"/>
-      <c r="R1" s="110"/>
-      <c r="S1" s="110"/>
-      <c r="T1" s="110"/>
-      <c r="U1" s="110"/>
+      <c r="J1" s="111"/>
+      <c r="K1" s="111"/>
+      <c r="L1" s="111"/>
+      <c r="M1" s="111"/>
+      <c r="N1" s="111"/>
+      <c r="O1" s="111"/>
+      <c r="P1" s="111"/>
+      <c r="Q1" s="111"/>
+      <c r="R1" s="111"/>
+      <c r="S1" s="111"/>
+      <c r="T1" s="111"/>
+      <c r="U1" s="111"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -5020,17 +5028,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="111" t="s">
+      <c r="C4" s="112" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="111"/>
-      <c r="E4" s="111"/>
-      <c r="F4" s="111"/>
-      <c r="G4" s="111"/>
-      <c r="H4" s="111"/>
-      <c r="I4" s="111"/>
-      <c r="J4" s="112"/>
-      <c r="K4" s="113"/>
+      <c r="D4" s="112"/>
+      <c r="E4" s="112"/>
+      <c r="F4" s="112"/>
+      <c r="G4" s="112"/>
+      <c r="H4" s="112"/>
+      <c r="I4" s="112"/>
+      <c r="J4" s="113"/>
+      <c r="K4" s="114"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -5050,13 +5058,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="114" t="s">
+      <c r="T4" s="115" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="120" t="s">
+      <c r="U4" s="121" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="103" t="s">
+      <c r="V4" s="104" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -5096,10 +5104,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="118" t="s">
+      <c r="J5" s="119" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="119"/>
+      <c r="K5" s="120"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -5107,9 +5115,9 @@
       <c r="Q5" s="99"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="115"/>
-      <c r="U5" s="121"/>
-      <c r="V5" s="104"/>
+      <c r="T5" s="116"/>
+      <c r="U5" s="122"/>
+      <c r="V5" s="105"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -7820,17 +7828,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="107" t="s">
+      <c r="C60" s="108" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="108"/>
-      <c r="E60" s="108"/>
-      <c r="F60" s="108"/>
-      <c r="G60" s="108"/>
-      <c r="H60" s="108"/>
-      <c r="I60" s="108"/>
-      <c r="J60" s="108"/>
-      <c r="K60" s="109"/>
+      <c r="D60" s="109"/>
+      <c r="E60" s="109"/>
+      <c r="F60" s="109"/>
+      <c r="G60" s="109"/>
+      <c r="H60" s="109"/>
+      <c r="I60" s="109"/>
+      <c r="J60" s="109"/>
+      <c r="K60" s="110"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -8139,21 +8147,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="110" t="s">
+      <c r="I1" s="111" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="110"/>
-      <c r="K1" s="110"/>
-      <c r="L1" s="110"/>
-      <c r="M1" s="110"/>
-      <c r="N1" s="110"/>
-      <c r="O1" s="110"/>
-      <c r="P1" s="110"/>
-      <c r="Q1" s="110"/>
-      <c r="R1" s="110"/>
-      <c r="S1" s="110"/>
-      <c r="T1" s="110"/>
-      <c r="U1" s="110"/>
+      <c r="J1" s="111"/>
+      <c r="K1" s="111"/>
+      <c r="L1" s="111"/>
+      <c r="M1" s="111"/>
+      <c r="N1" s="111"/>
+      <c r="O1" s="111"/>
+      <c r="P1" s="111"/>
+      <c r="Q1" s="111"/>
+      <c r="R1" s="111"/>
+      <c r="S1" s="111"/>
+      <c r="T1" s="111"/>
+      <c r="U1" s="111"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -8165,17 +8173,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="111" t="s">
+      <c r="C4" s="112" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="111"/>
-      <c r="E4" s="111"/>
-      <c r="F4" s="111"/>
-      <c r="G4" s="111"/>
-      <c r="H4" s="111"/>
-      <c r="I4" s="111"/>
-      <c r="J4" s="112"/>
-      <c r="K4" s="113"/>
+      <c r="D4" s="112"/>
+      <c r="E4" s="112"/>
+      <c r="F4" s="112"/>
+      <c r="G4" s="112"/>
+      <c r="H4" s="112"/>
+      <c r="I4" s="112"/>
+      <c r="J4" s="113"/>
+      <c r="K4" s="114"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -8195,13 +8203,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="114" t="s">
+      <c r="T4" s="115" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="120" t="s">
+      <c r="U4" s="121" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="103" t="s">
+      <c r="V4" s="104" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -8241,10 +8249,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="118" t="s">
+      <c r="J5" s="119" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="119"/>
+      <c r="K5" s="120"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -8252,9 +8260,9 @@
       <c r="Q5" s="99"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="115"/>
-      <c r="U5" s="121"/>
-      <c r="V5" s="104"/>
+      <c r="T5" s="116"/>
+      <c r="U5" s="122"/>
+      <c r="V5" s="105"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -10967,17 +10975,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="107" t="s">
+      <c r="C60" s="108" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="108"/>
-      <c r="E60" s="108"/>
-      <c r="F60" s="108"/>
-      <c r="G60" s="108"/>
-      <c r="H60" s="108"/>
-      <c r="I60" s="108"/>
-      <c r="J60" s="108"/>
-      <c r="K60" s="109"/>
+      <c r="D60" s="109"/>
+      <c r="E60" s="109"/>
+      <c r="F60" s="109"/>
+      <c r="G60" s="109"/>
+      <c r="H60" s="109"/>
+      <c r="I60" s="109"/>
+      <c r="J60" s="109"/>
+      <c r="K60" s="110"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -11286,21 +11294,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="110" t="s">
+      <c r="I1" s="111" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="110"/>
-      <c r="K1" s="110"/>
-      <c r="L1" s="110"/>
-      <c r="M1" s="110"/>
-      <c r="N1" s="110"/>
-      <c r="O1" s="110"/>
-      <c r="P1" s="110"/>
-      <c r="Q1" s="110"/>
-      <c r="R1" s="110"/>
-      <c r="S1" s="110"/>
-      <c r="T1" s="110"/>
-      <c r="U1" s="110"/>
+      <c r="J1" s="111"/>
+      <c r="K1" s="111"/>
+      <c r="L1" s="111"/>
+      <c r="M1" s="111"/>
+      <c r="N1" s="111"/>
+      <c r="O1" s="111"/>
+      <c r="P1" s="111"/>
+      <c r="Q1" s="111"/>
+      <c r="R1" s="111"/>
+      <c r="S1" s="111"/>
+      <c r="T1" s="111"/>
+      <c r="U1" s="111"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -11312,17 +11320,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="111" t="s">
+      <c r="C4" s="112" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="111"/>
-      <c r="E4" s="111"/>
-      <c r="F4" s="111"/>
-      <c r="G4" s="111"/>
-      <c r="H4" s="111"/>
-      <c r="I4" s="111"/>
-      <c r="J4" s="112"/>
-      <c r="K4" s="113"/>
+      <c r="D4" s="112"/>
+      <c r="E4" s="112"/>
+      <c r="F4" s="112"/>
+      <c r="G4" s="112"/>
+      <c r="H4" s="112"/>
+      <c r="I4" s="112"/>
+      <c r="J4" s="113"/>
+      <c r="K4" s="114"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -11342,13 +11350,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="114" t="s">
+      <c r="T4" s="115" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="120" t="s">
+      <c r="U4" s="121" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="103" t="s">
+      <c r="V4" s="104" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -11388,10 +11396,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="118" t="s">
+      <c r="J5" s="119" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="119"/>
+      <c r="K5" s="120"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -11399,9 +11407,9 @@
       <c r="Q5" s="99"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="115"/>
-      <c r="U5" s="121"/>
-      <c r="V5" s="104"/>
+      <c r="T5" s="116"/>
+      <c r="U5" s="122"/>
+      <c r="V5" s="105"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -14103,17 +14111,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="107" t="s">
+      <c r="C60" s="108" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="108"/>
-      <c r="E60" s="108"/>
-      <c r="F60" s="108"/>
-      <c r="G60" s="108"/>
-      <c r="H60" s="108"/>
-      <c r="I60" s="108"/>
-      <c r="J60" s="108"/>
-      <c r="K60" s="109"/>
+      <c r="D60" s="109"/>
+      <c r="E60" s="109"/>
+      <c r="F60" s="109"/>
+      <c r="G60" s="109"/>
+      <c r="H60" s="109"/>
+      <c r="I60" s="109"/>
+      <c r="J60" s="109"/>
+      <c r="K60" s="110"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -14422,21 +14430,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="110" t="s">
+      <c r="I1" s="111" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="110"/>
-      <c r="K1" s="110"/>
-      <c r="L1" s="110"/>
-      <c r="M1" s="110"/>
-      <c r="N1" s="110"/>
-      <c r="O1" s="110"/>
-      <c r="P1" s="110"/>
-      <c r="Q1" s="110"/>
-      <c r="R1" s="110"/>
-      <c r="S1" s="110"/>
-      <c r="T1" s="110"/>
-      <c r="U1" s="110"/>
+      <c r="J1" s="111"/>
+      <c r="K1" s="111"/>
+      <c r="L1" s="111"/>
+      <c r="M1" s="111"/>
+      <c r="N1" s="111"/>
+      <c r="O1" s="111"/>
+      <c r="P1" s="111"/>
+      <c r="Q1" s="111"/>
+      <c r="R1" s="111"/>
+      <c r="S1" s="111"/>
+      <c r="T1" s="111"/>
+      <c r="U1" s="111"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -14448,17 +14456,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="111" t="s">
+      <c r="C4" s="112" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="111"/>
-      <c r="E4" s="111"/>
-      <c r="F4" s="111"/>
-      <c r="G4" s="111"/>
-      <c r="H4" s="111"/>
-      <c r="I4" s="111"/>
-      <c r="J4" s="112"/>
-      <c r="K4" s="113"/>
+      <c r="D4" s="112"/>
+      <c r="E4" s="112"/>
+      <c r="F4" s="112"/>
+      <c r="G4" s="112"/>
+      <c r="H4" s="112"/>
+      <c r="I4" s="112"/>
+      <c r="J4" s="113"/>
+      <c r="K4" s="114"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -14478,13 +14486,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="114" t="s">
+      <c r="T4" s="115" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="120" t="s">
+      <c r="U4" s="121" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="103" t="s">
+      <c r="V4" s="104" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -14524,10 +14532,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="118" t="s">
+      <c r="J5" s="119" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="119"/>
+      <c r="K5" s="120"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -14535,9 +14543,9 @@
       <c r="Q5" s="99"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="115"/>
-      <c r="U5" s="121"/>
-      <c r="V5" s="104"/>
+      <c r="T5" s="116"/>
+      <c r="U5" s="122"/>
+      <c r="V5" s="105"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -17238,17 +17246,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="107" t="s">
+      <c r="C60" s="108" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="108"/>
-      <c r="E60" s="108"/>
-      <c r="F60" s="108"/>
-      <c r="G60" s="108"/>
-      <c r="H60" s="108"/>
-      <c r="I60" s="108"/>
-      <c r="J60" s="108"/>
-      <c r="K60" s="109"/>
+      <c r="D60" s="109"/>
+      <c r="E60" s="109"/>
+      <c r="F60" s="109"/>
+      <c r="G60" s="109"/>
+      <c r="H60" s="109"/>
+      <c r="I60" s="109"/>
+      <c r="J60" s="109"/>
+      <c r="K60" s="110"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -17557,21 +17565,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="110" t="s">
+      <c r="I1" s="111" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="110"/>
-      <c r="K1" s="110"/>
-      <c r="L1" s="110"/>
-      <c r="M1" s="110"/>
-      <c r="N1" s="110"/>
-      <c r="O1" s="110"/>
-      <c r="P1" s="110"/>
-      <c r="Q1" s="110"/>
-      <c r="R1" s="110"/>
-      <c r="S1" s="110"/>
-      <c r="T1" s="110"/>
-      <c r="U1" s="110"/>
+      <c r="J1" s="111"/>
+      <c r="K1" s="111"/>
+      <c r="L1" s="111"/>
+      <c r="M1" s="111"/>
+      <c r="N1" s="111"/>
+      <c r="O1" s="111"/>
+      <c r="P1" s="111"/>
+      <c r="Q1" s="111"/>
+      <c r="R1" s="111"/>
+      <c r="S1" s="111"/>
+      <c r="T1" s="111"/>
+      <c r="U1" s="111"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -17583,17 +17591,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="111" t="s">
+      <c r="C4" s="112" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="111"/>
-      <c r="E4" s="111"/>
-      <c r="F4" s="111"/>
-      <c r="G4" s="111"/>
-      <c r="H4" s="111"/>
-      <c r="I4" s="111"/>
-      <c r="J4" s="112"/>
-      <c r="K4" s="113"/>
+      <c r="D4" s="112"/>
+      <c r="E4" s="112"/>
+      <c r="F4" s="112"/>
+      <c r="G4" s="112"/>
+      <c r="H4" s="112"/>
+      <c r="I4" s="112"/>
+      <c r="J4" s="113"/>
+      <c r="K4" s="114"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -17613,13 +17621,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="114" t="s">
+      <c r="T4" s="115" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="120" t="s">
+      <c r="U4" s="121" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="103" t="s">
+      <c r="V4" s="104" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -17659,10 +17667,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="118" t="s">
+      <c r="J5" s="119" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="119"/>
+      <c r="K5" s="120"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -17670,9 +17678,9 @@
       <c r="Q5" s="100"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="115"/>
-      <c r="U5" s="121"/>
-      <c r="V5" s="104"/>
+      <c r="T5" s="116"/>
+      <c r="U5" s="122"/>
+      <c r="V5" s="105"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -20367,17 +20375,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="107" t="s">
+      <c r="C60" s="108" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="108"/>
-      <c r="E60" s="108"/>
-      <c r="F60" s="108"/>
-      <c r="G60" s="108"/>
-      <c r="H60" s="108"/>
-      <c r="I60" s="108"/>
-      <c r="J60" s="108"/>
-      <c r="K60" s="109"/>
+      <c r="D60" s="109"/>
+      <c r="E60" s="109"/>
+      <c r="F60" s="109"/>
+      <c r="G60" s="109"/>
+      <c r="H60" s="109"/>
+      <c r="I60" s="109"/>
+      <c r="J60" s="109"/>
+      <c r="K60" s="110"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -20686,21 +20694,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="110" t="s">
+      <c r="I1" s="111" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="110"/>
-      <c r="K1" s="110"/>
-      <c r="L1" s="110"/>
-      <c r="M1" s="110"/>
-      <c r="N1" s="110"/>
-      <c r="O1" s="110"/>
-      <c r="P1" s="110"/>
-      <c r="Q1" s="110"/>
-      <c r="R1" s="110"/>
-      <c r="S1" s="110"/>
-      <c r="T1" s="110"/>
-      <c r="U1" s="110"/>
+      <c r="J1" s="111"/>
+      <c r="K1" s="111"/>
+      <c r="L1" s="111"/>
+      <c r="M1" s="111"/>
+      <c r="N1" s="111"/>
+      <c r="O1" s="111"/>
+      <c r="P1" s="111"/>
+      <c r="Q1" s="111"/>
+      <c r="R1" s="111"/>
+      <c r="S1" s="111"/>
+      <c r="T1" s="111"/>
+      <c r="U1" s="111"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -20712,17 +20720,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="111" t="s">
+      <c r="C4" s="112" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="111"/>
-      <c r="E4" s="111"/>
-      <c r="F4" s="111"/>
-      <c r="G4" s="111"/>
-      <c r="H4" s="111"/>
-      <c r="I4" s="111"/>
-      <c r="J4" s="112"/>
-      <c r="K4" s="113"/>
+      <c r="D4" s="112"/>
+      <c r="E4" s="112"/>
+      <c r="F4" s="112"/>
+      <c r="G4" s="112"/>
+      <c r="H4" s="112"/>
+      <c r="I4" s="112"/>
+      <c r="J4" s="113"/>
+      <c r="K4" s="114"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -20742,13 +20750,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="114" t="s">
+      <c r="T4" s="115" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="120" t="s">
+      <c r="U4" s="121" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="103" t="s">
+      <c r="V4" s="104" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -20788,10 +20796,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="118" t="s">
+      <c r="J5" s="119" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="119"/>
+      <c r="K5" s="120"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -20799,9 +20807,9 @@
       <c r="Q5" s="101"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="115"/>
-      <c r="U5" s="121"/>
-      <c r="V5" s="104"/>
+      <c r="T5" s="116"/>
+      <c r="U5" s="122"/>
+      <c r="V5" s="105"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -23492,17 +23500,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="107" t="s">
+      <c r="C60" s="108" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="108"/>
-      <c r="E60" s="108"/>
-      <c r="F60" s="108"/>
-      <c r="G60" s="108"/>
-      <c r="H60" s="108"/>
-      <c r="I60" s="108"/>
-      <c r="J60" s="108"/>
-      <c r="K60" s="109"/>
+      <c r="D60" s="109"/>
+      <c r="E60" s="109"/>
+      <c r="F60" s="109"/>
+      <c r="G60" s="109"/>
+      <c r="H60" s="109"/>
+      <c r="I60" s="109"/>
+      <c r="J60" s="109"/>
+      <c r="K60" s="110"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -23811,21 +23819,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="110" t="s">
+      <c r="I1" s="111" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="110"/>
-      <c r="K1" s="110"/>
-      <c r="L1" s="110"/>
-      <c r="M1" s="110"/>
-      <c r="N1" s="110"/>
-      <c r="O1" s="110"/>
-      <c r="P1" s="110"/>
-      <c r="Q1" s="110"/>
-      <c r="R1" s="110"/>
-      <c r="S1" s="110"/>
-      <c r="T1" s="110"/>
-      <c r="U1" s="110"/>
+      <c r="J1" s="111"/>
+      <c r="K1" s="111"/>
+      <c r="L1" s="111"/>
+      <c r="M1" s="111"/>
+      <c r="N1" s="111"/>
+      <c r="O1" s="111"/>
+      <c r="P1" s="111"/>
+      <c r="Q1" s="111"/>
+      <c r="R1" s="111"/>
+      <c r="S1" s="111"/>
+      <c r="T1" s="111"/>
+      <c r="U1" s="111"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -23837,17 +23845,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="111" t="s">
+      <c r="C4" s="112" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="111"/>
-      <c r="E4" s="111"/>
-      <c r="F4" s="111"/>
-      <c r="G4" s="111"/>
-      <c r="H4" s="111"/>
-      <c r="I4" s="111"/>
-      <c r="J4" s="112"/>
-      <c r="K4" s="113"/>
+      <c r="D4" s="112"/>
+      <c r="E4" s="112"/>
+      <c r="F4" s="112"/>
+      <c r="G4" s="112"/>
+      <c r="H4" s="112"/>
+      <c r="I4" s="112"/>
+      <c r="J4" s="113"/>
+      <c r="K4" s="114"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -23867,13 +23875,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="114" t="s">
+      <c r="T4" s="115" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="120" t="s">
+      <c r="U4" s="121" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="103" t="s">
+      <c r="V4" s="104" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -23913,10 +23921,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="118" t="s">
+      <c r="J5" s="119" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="119"/>
+      <c r="K5" s="120"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -23924,9 +23932,9 @@
       <c r="Q5" s="102"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="115"/>
-      <c r="U5" s="121"/>
-      <c r="V5" s="104"/>
+      <c r="T5" s="116"/>
+      <c r="U5" s="122"/>
+      <c r="V5" s="105"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -26634,17 +26642,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="107" t="s">
+      <c r="C60" s="108" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="108"/>
-      <c r="E60" s="108"/>
-      <c r="F60" s="108"/>
-      <c r="G60" s="108"/>
-      <c r="H60" s="108"/>
-      <c r="I60" s="108"/>
-      <c r="J60" s="108"/>
-      <c r="K60" s="109"/>
+      <c r="D60" s="109"/>
+      <c r="E60" s="109"/>
+      <c r="F60" s="109"/>
+      <c r="G60" s="109"/>
+      <c r="H60" s="109"/>
+      <c r="I60" s="109"/>
+      <c r="J60" s="109"/>
+      <c r="K60" s="110"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -26903,6 +26911,3124 @@
     <mergeCell ref="C4:K4"/>
     <mergeCell ref="T4:T5"/>
     <mergeCell ref="U4:U5"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
+  <pageSetup paperSize="14" scale="70" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="24" max="80" man="1"/>
+  </colBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D3F7594-9AC5-434F-A2F7-C87D7699469D}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BB81"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="28" customWidth="1"/>
+    <col min="3" max="6" width="10" style="9" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" style="9" customWidth="1"/>
+    <col min="8" max="8" width="7.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.85546875" style="9" customWidth="1"/>
+    <col min="11" max="11" width="7.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.42578125" style="9" customWidth="1"/>
+    <col min="13" max="13" width="10" style="9" customWidth="1"/>
+    <col min="14" max="14" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" style="9" customWidth="1"/>
+    <col min="16" max="16" width="5.5703125" style="9" customWidth="1"/>
+    <col min="17" max="17" width="10" style="9" customWidth="1"/>
+    <col min="18" max="18" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="1.42578125" style="9" customWidth="1"/>
+    <col min="20" max="20" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="9" customWidth="1"/>
+    <col min="22" max="22" width="19.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="23" max="49" width="7.28515625" style="9" customWidth="1"/>
+    <col min="50" max="50" width="1.5703125" style="9" customWidth="1"/>
+    <col min="51" max="51" width="9.42578125" style="9" customWidth="1"/>
+    <col min="52" max="52" width="1.28515625" style="9" customWidth="1"/>
+    <col min="53" max="53" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="10.28515625" style="9" bestFit="1" customWidth="1"/>
+    <col min="55" max="16384" width="9.140625" style="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="111" t="s">
+        <v>43</v>
+      </c>
+      <c r="J1" s="111"/>
+      <c r="K1" s="111"/>
+      <c r="L1" s="111"/>
+      <c r="M1" s="111"/>
+      <c r="N1" s="111"/>
+      <c r="O1" s="111"/>
+      <c r="P1" s="111"/>
+      <c r="Q1" s="111"/>
+      <c r="R1" s="111"/>
+      <c r="S1" s="111"/>
+      <c r="T1" s="111"/>
+      <c r="U1" s="111"/>
+    </row>
+    <row r="2" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="B2" s="28" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B4" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="112" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="112"/>
+      <c r="E4" s="112"/>
+      <c r="F4" s="112"/>
+      <c r="G4" s="112"/>
+      <c r="H4" s="112"/>
+      <c r="I4" s="112"/>
+      <c r="J4" s="113"/>
+      <c r="K4" s="114"/>
+      <c r="M4" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="N4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="O4" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="P4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q4" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="R4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="S4" s="9"/>
+      <c r="T4" s="115" t="s">
+        <v>68</v>
+      </c>
+      <c r="U4" s="121" t="s">
+        <v>67</v>
+      </c>
+      <c r="V4" s="104" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF4" s="11"/>
+      <c r="AG4" s="11"/>
+      <c r="AH4" s="11"/>
+      <c r="AI4" s="11"/>
+      <c r="AJ4" s="11"/>
+      <c r="AK4" s="11"/>
+      <c r="AL4" s="11"/>
+      <c r="AM4" s="11"/>
+      <c r="AN4" s="11"/>
+      <c r="AO4" s="11"/>
+      <c r="AP4" s="11"/>
+      <c r="AQ4" s="11"/>
+      <c r="AR4" s="11"/>
+      <c r="AS4" s="11"/>
+      <c r="AT4" s="11"/>
+      <c r="AU4" s="11"/>
+      <c r="AV4" s="11"/>
+      <c r="AW4" s="11"/>
+      <c r="AX4" s="11"/>
+      <c r="AY4" s="11"/>
+      <c r="AZ4" s="11"/>
+      <c r="BA4" s="11"/>
+      <c r="BB4" s="11"/>
+    </row>
+    <row r="5" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="37"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40" t="s">
+        <v>64</v>
+      </c>
+      <c r="I5" s="40" t="s">
+        <v>60</v>
+      </c>
+      <c r="J5" s="119" t="s">
+        <v>65</v>
+      </c>
+      <c r="K5" s="120"/>
+      <c r="M5" s="37"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="40"/>
+      <c r="P5" s="103"/>
+      <c r="Q5" s="103"/>
+      <c r="R5" s="38"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="116"/>
+      <c r="U5" s="122"/>
+      <c r="V5" s="105"/>
+      <c r="AF5" s="11"/>
+      <c r="AG5" s="11"/>
+      <c r="AH5" s="11"/>
+      <c r="AI5" s="11"/>
+      <c r="AJ5" s="11"/>
+      <c r="AK5" s="11"/>
+      <c r="AL5" s="11"/>
+      <c r="AM5" s="11"/>
+      <c r="AN5" s="11"/>
+      <c r="AO5" s="11"/>
+      <c r="AP5" s="11"/>
+      <c r="AQ5" s="11"/>
+      <c r="AR5" s="11"/>
+      <c r="AS5" s="11"/>
+      <c r="AT5" s="11"/>
+      <c r="AU5" s="11"/>
+      <c r="AV5" s="11"/>
+      <c r="AW5" s="11"/>
+      <c r="AX5" s="11"/>
+      <c r="AY5" s="11"/>
+      <c r="AZ5" s="11"/>
+      <c r="BA5" s="11"/>
+      <c r="BB5" s="11"/>
+    </row>
+    <row r="6" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="37"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="103"/>
+      <c r="K6" s="38"/>
+      <c r="M6" s="37"/>
+      <c r="N6" s="49"/>
+      <c r="O6" s="40"/>
+      <c r="P6" s="103"/>
+      <c r="Q6" s="103"/>
+      <c r="R6" s="38"/>
+      <c r="S6" s="9"/>
+      <c r="T6" s="39"/>
+      <c r="U6" s="39"/>
+      <c r="V6" s="39"/>
+      <c r="AF6" s="11"/>
+      <c r="AG6" s="11"/>
+      <c r="AH6" s="11"/>
+      <c r="AI6" s="11"/>
+      <c r="AJ6" s="11"/>
+      <c r="AK6" s="11"/>
+      <c r="AL6" s="11"/>
+      <c r="AM6" s="11"/>
+      <c r="AN6" s="11"/>
+      <c r="AO6" s="11"/>
+      <c r="AP6" s="11"/>
+      <c r="AQ6" s="11"/>
+      <c r="AR6" s="11"/>
+      <c r="AS6" s="11"/>
+      <c r="AT6" s="11"/>
+      <c r="AU6" s="11"/>
+      <c r="AV6" s="11"/>
+      <c r="AW6" s="11"/>
+      <c r="AX6" s="11"/>
+      <c r="AY6" s="11"/>
+      <c r="AZ6" s="11"/>
+      <c r="BA6" s="11"/>
+      <c r="BB6" s="11"/>
+    </row>
+    <row r="7" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A7" s="27">
+        <v>1</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="52">
+        <v>30</v>
+      </c>
+      <c r="D7" s="52"/>
+      <c r="E7" s="52"/>
+      <c r="F7" s="52"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="52"/>
+      <c r="I7" s="52">
+        <v>3</v>
+      </c>
+      <c r="J7" s="53"/>
+      <c r="K7" s="54">
+        <v>6</v>
+      </c>
+      <c r="L7" s="55"/>
+      <c r="M7" s="56"/>
+      <c r="N7" s="57"/>
+      <c r="O7" s="52">
+        <v>1</v>
+      </c>
+      <c r="P7" s="53"/>
+      <c r="Q7" s="53">
+        <v>1</v>
+      </c>
+      <c r="R7" s="54"/>
+      <c r="S7" s="55"/>
+      <c r="T7" s="58">
+        <f>H7+I7+J7+K7+N7+P7+R7</f>
+        <v>9</v>
+      </c>
+      <c r="U7" s="58">
+        <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
+        <v>777</v>
+      </c>
+      <c r="V7" s="58">
+        <f>U7/24</f>
+        <v>32.375</v>
+      </c>
+      <c r="W7" s="50"/>
+      <c r="AF7" s="12"/>
+      <c r="AG7" s="12"/>
+      <c r="AH7" s="12"/>
+      <c r="AI7" s="12"/>
+      <c r="AJ7" s="12"/>
+      <c r="AK7" s="12"/>
+      <c r="AL7" s="12"/>
+      <c r="AM7" s="12"/>
+      <c r="AN7" s="12"/>
+      <c r="AO7" s="12"/>
+      <c r="AP7" s="12"/>
+      <c r="AQ7" s="12"/>
+      <c r="AR7" s="12"/>
+      <c r="AS7" s="12"/>
+      <c r="AT7" s="12"/>
+      <c r="AU7" s="12"/>
+      <c r="AV7" s="12"/>
+      <c r="AW7" s="12"/>
+      <c r="AX7" s="12"/>
+      <c r="AY7" s="12"/>
+      <c r="AZ7" s="12"/>
+      <c r="BA7" s="12"/>
+      <c r="BB7" s="12"/>
+    </row>
+    <row r="8" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="27">
+        <f>A7+1</f>
+        <v>2</v>
+      </c>
+      <c r="B8" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="59">
+        <f>38+30</f>
+        <v>68</v>
+      </c>
+      <c r="D8" s="59"/>
+      <c r="E8" s="59"/>
+      <c r="F8" s="59"/>
+      <c r="G8" s="59"/>
+      <c r="H8" s="59"/>
+      <c r="I8" s="59"/>
+      <c r="J8" s="60"/>
+      <c r="K8" s="61"/>
+      <c r="L8" s="62"/>
+      <c r="M8" s="63">
+        <v>1</v>
+      </c>
+      <c r="N8" s="64"/>
+      <c r="O8" s="65">
+        <v>1</v>
+      </c>
+      <c r="P8" s="66">
+        <v>12</v>
+      </c>
+      <c r="Q8" s="66">
+        <v>6</v>
+      </c>
+      <c r="R8" s="67"/>
+      <c r="S8" s="62"/>
+      <c r="T8" s="68">
+        <f t="shared" ref="T8:T41" si="0">H8+I8+J8+K8+N8+P8+R8</f>
+        <v>12</v>
+      </c>
+      <c r="U8" s="69">
+        <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
+        <v>1836</v>
+      </c>
+      <c r="V8" s="69">
+        <f>U8/24</f>
+        <v>76.5</v>
+      </c>
+      <c r="W8" s="50"/>
+      <c r="AF8" s="12"/>
+      <c r="AG8" s="12"/>
+      <c r="AH8" s="12"/>
+      <c r="AI8" s="12"/>
+      <c r="AJ8" s="12"/>
+      <c r="AK8" s="12"/>
+      <c r="AL8" s="12"/>
+      <c r="AM8" s="12"/>
+      <c r="AN8" s="12"/>
+      <c r="AO8" s="12"/>
+      <c r="AP8" s="12"/>
+      <c r="AQ8" s="12"/>
+      <c r="AR8" s="12"/>
+      <c r="AS8" s="12"/>
+      <c r="AT8" s="12"/>
+      <c r="AU8" s="12"/>
+      <c r="AV8" s="12"/>
+      <c r="AW8" s="12"/>
+      <c r="AX8" s="12"/>
+      <c r="AY8" s="12"/>
+      <c r="AZ8" s="12"/>
+      <c r="BA8" s="12"/>
+      <c r="BB8" s="12"/>
+    </row>
+    <row r="9" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A9" s="27">
+        <f t="shared" ref="A9:A57" si="1">A8+1</f>
+        <v>3</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="70">
+        <f>26+30</f>
+        <v>56</v>
+      </c>
+      <c r="D9" s="70"/>
+      <c r="E9" s="70"/>
+      <c r="F9" s="70"/>
+      <c r="G9" s="70"/>
+      <c r="H9" s="70"/>
+      <c r="I9" s="70"/>
+      <c r="J9" s="71"/>
+      <c r="K9" s="72"/>
+      <c r="L9" s="55"/>
+      <c r="M9" s="73"/>
+      <c r="N9" s="74"/>
+      <c r="O9" s="70"/>
+      <c r="P9" s="71"/>
+      <c r="Q9" s="71">
+        <v>15</v>
+      </c>
+      <c r="R9" s="72"/>
+      <c r="S9" s="55"/>
+      <c r="T9" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U9" s="76">
+        <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
+        <v>1704</v>
+      </c>
+      <c r="V9" s="76">
+        <f t="shared" ref="V9:V11" si="3">U9/24</f>
+        <v>71</v>
+      </c>
+      <c r="W9" s="50"/>
+      <c r="AF9" s="12"/>
+      <c r="AG9" s="12"/>
+      <c r="AH9" s="12"/>
+      <c r="AI9" s="12"/>
+      <c r="AJ9" s="12"/>
+      <c r="AK9" s="12"/>
+      <c r="AL9" s="12"/>
+      <c r="AM9" s="12"/>
+      <c r="AN9" s="12"/>
+      <c r="AO9" s="12"/>
+      <c r="AP9" s="12"/>
+      <c r="AQ9" s="12"/>
+      <c r="AR9" s="12"/>
+      <c r="AS9" s="12"/>
+      <c r="AT9" s="12"/>
+      <c r="AU9" s="12"/>
+      <c r="AV9" s="12"/>
+      <c r="AW9" s="12"/>
+      <c r="AX9" s="12"/>
+      <c r="AY9" s="12"/>
+      <c r="AZ9" s="12"/>
+      <c r="BA9" s="12"/>
+      <c r="BB9" s="12"/>
+    </row>
+    <row r="10" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A10" s="27">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="70">
+        <f>5+10</f>
+        <v>15</v>
+      </c>
+      <c r="D10" s="70"/>
+      <c r="E10" s="70"/>
+      <c r="F10" s="70"/>
+      <c r="G10" s="70"/>
+      <c r="H10" s="70"/>
+      <c r="I10" s="70"/>
+      <c r="J10" s="71"/>
+      <c r="K10" s="72"/>
+      <c r="L10" s="55"/>
+      <c r="M10" s="73"/>
+      <c r="N10" s="74"/>
+      <c r="O10" s="70"/>
+      <c r="P10" s="71"/>
+      <c r="Q10" s="71">
+        <v>5</v>
+      </c>
+      <c r="R10" s="72"/>
+      <c r="S10" s="55"/>
+      <c r="T10" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U10" s="58">
+        <f t="shared" si="2"/>
+        <v>480</v>
+      </c>
+      <c r="V10" s="58">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="W10" s="50"/>
+      <c r="AF10" s="12"/>
+      <c r="AG10" s="12"/>
+      <c r="AH10" s="12"/>
+      <c r="AI10" s="12"/>
+      <c r="AJ10" s="12"/>
+      <c r="AK10" s="12"/>
+      <c r="AL10" s="12"/>
+      <c r="AM10" s="12"/>
+      <c r="AN10" s="12"/>
+      <c r="AO10" s="12"/>
+      <c r="AP10" s="12"/>
+      <c r="AQ10" s="12"/>
+      <c r="AR10" s="12"/>
+      <c r="AS10" s="12"/>
+      <c r="AT10" s="12"/>
+      <c r="AU10" s="12"/>
+      <c r="AV10" s="12"/>
+      <c r="AW10" s="12"/>
+      <c r="AX10" s="12"/>
+      <c r="AY10" s="12"/>
+      <c r="AZ10" s="12"/>
+      <c r="BA10" s="12"/>
+      <c r="BB10" s="12"/>
+    </row>
+    <row r="11" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A11" s="27">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="70"/>
+      <c r="D11" s="70"/>
+      <c r="E11" s="70"/>
+      <c r="F11" s="70"/>
+      <c r="G11" s="70"/>
+      <c r="H11" s="70"/>
+      <c r="I11" s="70"/>
+      <c r="J11" s="71"/>
+      <c r="K11" s="72">
+        <v>2</v>
+      </c>
+      <c r="L11" s="55"/>
+      <c r="M11" s="73"/>
+      <c r="N11" s="74"/>
+      <c r="O11" s="70"/>
+      <c r="P11" s="71"/>
+      <c r="Q11" s="71"/>
+      <c r="R11" s="72"/>
+      <c r="S11" s="55"/>
+      <c r="T11" s="58">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="U11" s="58">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="V11" s="58">
+        <f t="shared" si="3"/>
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="AF11" s="12"/>
+      <c r="AG11" s="12"/>
+      <c r="AH11" s="12"/>
+      <c r="AI11" s="12"/>
+      <c r="AJ11" s="12"/>
+      <c r="AK11" s="12"/>
+      <c r="AL11" s="12"/>
+      <c r="AM11" s="12"/>
+      <c r="AN11" s="12"/>
+      <c r="AO11" s="12"/>
+      <c r="AP11" s="12"/>
+      <c r="AQ11" s="12"/>
+      <c r="AR11" s="12"/>
+      <c r="AS11" s="12"/>
+      <c r="AT11" s="12"/>
+      <c r="AU11" s="12"/>
+      <c r="AV11" s="12"/>
+      <c r="AW11" s="12"/>
+      <c r="AX11" s="12"/>
+      <c r="AY11" s="12"/>
+      <c r="AZ11" s="12"/>
+      <c r="BA11" s="12"/>
+      <c r="BB11" s="12"/>
+    </row>
+    <row r="12" spans="1:54" s="13" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="27">
+        <v>7</v>
+      </c>
+      <c r="B12" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="59">
+        <f>1224+53+720+38+1080+29</f>
+        <v>3144</v>
+      </c>
+      <c r="D12" s="59"/>
+      <c r="E12" s="59"/>
+      <c r="F12" s="59"/>
+      <c r="G12" s="59"/>
+      <c r="H12" s="59"/>
+      <c r="I12" s="59"/>
+      <c r="J12" s="60"/>
+      <c r="K12" s="61"/>
+      <c r="L12" s="62"/>
+      <c r="M12" s="63"/>
+      <c r="N12" s="64">
+        <v>10</v>
+      </c>
+      <c r="O12" s="65">
+        <v>13</v>
+      </c>
+      <c r="P12" s="66">
+        <v>12</v>
+      </c>
+      <c r="Q12" s="66">
+        <v>2</v>
+      </c>
+      <c r="R12" s="67"/>
+      <c r="S12" s="62"/>
+      <c r="T12" s="69">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="U12" s="69">
+        <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
+        <v>75838</v>
+      </c>
+      <c r="V12" s="69">
+        <f>U12/24</f>
+        <v>3159.9166666666665</v>
+      </c>
+      <c r="W12" s="9"/>
+      <c r="X12" s="9"/>
+      <c r="Y12" s="9"/>
+      <c r="Z12" s="9"/>
+      <c r="AA12" s="9"/>
+      <c r="AB12" s="9"/>
+      <c r="AC12" s="9"/>
+      <c r="AD12" s="9"/>
+      <c r="AE12" s="9"/>
+      <c r="AF12" s="12"/>
+      <c r="AG12" s="12"/>
+      <c r="AH12" s="12"/>
+      <c r="AI12" s="12"/>
+      <c r="AJ12" s="12"/>
+      <c r="AK12" s="12"/>
+      <c r="AL12" s="12"/>
+      <c r="AM12" s="12"/>
+      <c r="AN12" s="12"/>
+      <c r="AO12" s="12"/>
+      <c r="AP12" s="12"/>
+      <c r="AQ12" s="12"/>
+      <c r="AR12" s="12"/>
+      <c r="AS12" s="12"/>
+      <c r="AT12" s="12"/>
+      <c r="AU12" s="12"/>
+      <c r="AV12" s="12"/>
+      <c r="AW12" s="12"/>
+      <c r="AX12" s="12"/>
+      <c r="AY12" s="12"/>
+      <c r="AZ12" s="12"/>
+      <c r="BA12" s="12"/>
+      <c r="BB12" s="12"/>
+    </row>
+    <row r="13" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A13" s="27">
+        <v>11</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="70">
+        <v>2</v>
+      </c>
+      <c r="D13" s="70"/>
+      <c r="E13" s="70"/>
+      <c r="F13" s="70"/>
+      <c r="G13" s="70"/>
+      <c r="H13" s="70">
+        <v>16</v>
+      </c>
+      <c r="I13" s="70"/>
+      <c r="J13" s="71"/>
+      <c r="K13" s="72"/>
+      <c r="L13" s="55"/>
+      <c r="M13" s="73"/>
+      <c r="N13" s="74"/>
+      <c r="O13" s="70"/>
+      <c r="P13" s="71"/>
+      <c r="Q13" s="71"/>
+      <c r="R13" s="72"/>
+      <c r="S13" s="55"/>
+      <c r="T13" s="76">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="U13" s="76">
+        <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
+        <v>64</v>
+      </c>
+      <c r="V13" s="76">
+        <f>U13/24</f>
+        <v>2.6666666666666665</v>
+      </c>
+      <c r="AF13" s="12"/>
+      <c r="AG13" s="12"/>
+      <c r="AH13" s="12"/>
+      <c r="AI13" s="12"/>
+      <c r="AJ13" s="12"/>
+      <c r="AK13" s="12"/>
+      <c r="AL13" s="12"/>
+      <c r="AM13" s="12"/>
+      <c r="AN13" s="12"/>
+      <c r="AO13" s="12"/>
+      <c r="AP13" s="12"/>
+      <c r="AQ13" s="12"/>
+      <c r="AR13" s="12"/>
+      <c r="AS13" s="12"/>
+      <c r="AT13" s="12"/>
+      <c r="AU13" s="12"/>
+      <c r="AV13" s="12"/>
+      <c r="AW13" s="12"/>
+      <c r="AX13" s="12"/>
+      <c r="AY13" s="12"/>
+      <c r="AZ13" s="12"/>
+      <c r="BA13" s="12"/>
+      <c r="BB13" s="12"/>
+    </row>
+    <row r="14" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A14" s="27">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="70">
+        <v>2</v>
+      </c>
+      <c r="D14" s="70"/>
+      <c r="E14" s="70"/>
+      <c r="F14" s="70"/>
+      <c r="G14" s="70"/>
+      <c r="H14" s="70"/>
+      <c r="I14" s="70"/>
+      <c r="J14" s="71"/>
+      <c r="K14" s="72"/>
+      <c r="L14" s="55"/>
+      <c r="M14" s="73"/>
+      <c r="N14" s="74"/>
+      <c r="O14" s="70"/>
+      <c r="P14" s="71"/>
+      <c r="Q14" s="71"/>
+      <c r="R14" s="72"/>
+      <c r="S14" s="55"/>
+      <c r="T14" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U14" s="75">
+        <f t="shared" ref="U14:U36" si="4">C14*24+M14*24+O14*24+Q14*24+T14</f>
+        <v>48</v>
+      </c>
+      <c r="V14" s="75">
+        <f t="shared" ref="V14:V36" si="5">U14/24</f>
+        <v>2</v>
+      </c>
+      <c r="AF14" s="12"/>
+      <c r="AG14" s="12"/>
+      <c r="AH14" s="12"/>
+      <c r="AI14" s="12"/>
+      <c r="AJ14" s="12"/>
+      <c r="AK14" s="12"/>
+      <c r="AL14" s="12"/>
+      <c r="AM14" s="12"/>
+      <c r="AN14" s="12"/>
+      <c r="AO14" s="12"/>
+      <c r="AP14" s="12"/>
+      <c r="AQ14" s="12"/>
+      <c r="AR14" s="12"/>
+      <c r="AS14" s="12"/>
+      <c r="AT14" s="12"/>
+      <c r="AU14" s="12"/>
+      <c r="AV14" s="12"/>
+      <c r="AW14" s="12"/>
+      <c r="AX14" s="12"/>
+      <c r="AY14" s="12"/>
+      <c r="AZ14" s="12"/>
+      <c r="BA14" s="12"/>
+      <c r="BB14" s="12"/>
+    </row>
+    <row r="15" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A15" s="27">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="70"/>
+      <c r="D15" s="70"/>
+      <c r="E15" s="70"/>
+      <c r="F15" s="70"/>
+      <c r="G15" s="70"/>
+      <c r="H15" s="70"/>
+      <c r="I15" s="70"/>
+      <c r="J15" s="71"/>
+      <c r="K15" s="72"/>
+      <c r="L15" s="55"/>
+      <c r="M15" s="73"/>
+      <c r="N15" s="74"/>
+      <c r="O15" s="70"/>
+      <c r="P15" s="71"/>
+      <c r="Q15" s="71"/>
+      <c r="R15" s="72"/>
+      <c r="S15" s="55"/>
+      <c r="T15" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U15" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF15" s="12"/>
+      <c r="AG15" s="12"/>
+      <c r="AH15" s="12"/>
+      <c r="AI15" s="12"/>
+      <c r="AJ15" s="12"/>
+      <c r="AK15" s="12"/>
+      <c r="AL15" s="12"/>
+      <c r="AM15" s="12"/>
+      <c r="AN15" s="12"/>
+      <c r="AO15" s="12"/>
+      <c r="AP15" s="12"/>
+      <c r="AQ15" s="12"/>
+      <c r="AR15" s="12"/>
+      <c r="AS15" s="12"/>
+      <c r="AT15" s="12"/>
+      <c r="AU15" s="12"/>
+      <c r="AV15" s="12"/>
+      <c r="AW15" s="12"/>
+      <c r="AX15" s="12"/>
+      <c r="AY15" s="12"/>
+      <c r="AZ15" s="12"/>
+      <c r="BA15" s="12"/>
+      <c r="BB15" s="12"/>
+    </row>
+    <row r="16" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A16" s="27">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="70"/>
+      <c r="D16" s="70"/>
+      <c r="E16" s="70"/>
+      <c r="F16" s="70"/>
+      <c r="G16" s="70"/>
+      <c r="H16" s="70"/>
+      <c r="I16" s="70"/>
+      <c r="J16" s="71"/>
+      <c r="K16" s="72"/>
+      <c r="L16" s="55"/>
+      <c r="M16" s="73"/>
+      <c r="N16" s="74"/>
+      <c r="O16" s="70"/>
+      <c r="P16" s="71"/>
+      <c r="Q16" s="71"/>
+      <c r="R16" s="72"/>
+      <c r="S16" s="55"/>
+      <c r="T16" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U16" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF16" s="12"/>
+      <c r="AG16" s="12"/>
+      <c r="AH16" s="12"/>
+      <c r="AI16" s="12"/>
+      <c r="AJ16" s="12"/>
+      <c r="AK16" s="12"/>
+      <c r="AL16" s="12"/>
+      <c r="AM16" s="12"/>
+      <c r="AN16" s="12"/>
+      <c r="AO16" s="12"/>
+      <c r="AP16" s="12"/>
+      <c r="AQ16" s="12"/>
+      <c r="AR16" s="12"/>
+      <c r="AS16" s="12"/>
+      <c r="AT16" s="12"/>
+      <c r="AU16" s="12"/>
+      <c r="AV16" s="12"/>
+      <c r="AW16" s="12"/>
+      <c r="AX16" s="12"/>
+      <c r="AY16" s="12"/>
+      <c r="AZ16" s="12"/>
+      <c r="BA16" s="12"/>
+      <c r="BB16" s="12"/>
+    </row>
+    <row r="17" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A17" s="27">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="70"/>
+      <c r="D17" s="70"/>
+      <c r="E17" s="70"/>
+      <c r="F17" s="70"/>
+      <c r="G17" s="70"/>
+      <c r="H17" s="70">
+        <f>3*24</f>
+        <v>72</v>
+      </c>
+      <c r="I17" s="70"/>
+      <c r="J17" s="71"/>
+      <c r="K17" s="72"/>
+      <c r="L17" s="55"/>
+      <c r="M17" s="73"/>
+      <c r="N17" s="74"/>
+      <c r="O17" s="70"/>
+      <c r="P17" s="71"/>
+      <c r="Q17" s="71"/>
+      <c r="R17" s="72"/>
+      <c r="S17" s="55"/>
+      <c r="T17" s="58">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="U17" s="75">
+        <f t="shared" si="4"/>
+        <v>72</v>
+      </c>
+      <c r="V17" s="75">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="AF17" s="12"/>
+      <c r="AG17" s="12"/>
+      <c r="AH17" s="12"/>
+      <c r="AI17" s="12"/>
+      <c r="AJ17" s="12"/>
+      <c r="AK17" s="12"/>
+      <c r="AL17" s="12"/>
+      <c r="AM17" s="12"/>
+      <c r="AN17" s="12"/>
+      <c r="AO17" s="12"/>
+      <c r="AP17" s="12"/>
+      <c r="AQ17" s="12"/>
+      <c r="AR17" s="12"/>
+      <c r="AS17" s="12"/>
+      <c r="AT17" s="12"/>
+      <c r="AU17" s="12"/>
+      <c r="AV17" s="12"/>
+      <c r="AW17" s="12"/>
+      <c r="AX17" s="12"/>
+      <c r="AY17" s="12"/>
+      <c r="AZ17" s="12"/>
+      <c r="BA17" s="12"/>
+      <c r="BB17" s="12"/>
+    </row>
+    <row r="18" spans="1:54" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="27">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="70"/>
+      <c r="D18" s="70"/>
+      <c r="E18" s="70"/>
+      <c r="F18" s="70"/>
+      <c r="G18" s="70"/>
+      <c r="H18" s="70"/>
+      <c r="I18" s="70"/>
+      <c r="J18" s="71"/>
+      <c r="K18" s="72"/>
+      <c r="L18" s="55"/>
+      <c r="M18" s="73"/>
+      <c r="N18" s="74"/>
+      <c r="O18" s="70"/>
+      <c r="P18" s="71"/>
+      <c r="Q18" s="71"/>
+      <c r="R18" s="72"/>
+      <c r="S18" s="55"/>
+      <c r="T18" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U18" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF18" s="12"/>
+      <c r="AG18" s="12"/>
+      <c r="AH18" s="12"/>
+      <c r="AI18" s="12"/>
+      <c r="AJ18" s="12"/>
+      <c r="AK18" s="12"/>
+      <c r="AL18" s="12"/>
+      <c r="AM18" s="12"/>
+      <c r="AN18" s="12"/>
+      <c r="AO18" s="12"/>
+      <c r="AP18" s="12"/>
+      <c r="AQ18" s="12"/>
+      <c r="AR18" s="12"/>
+      <c r="AS18" s="12"/>
+      <c r="AT18" s="12"/>
+      <c r="AU18" s="12"/>
+      <c r="AV18" s="12"/>
+      <c r="AW18" s="12"/>
+      <c r="AX18" s="12"/>
+      <c r="AY18" s="12"/>
+      <c r="AZ18" s="12"/>
+      <c r="BA18" s="12"/>
+      <c r="BB18" s="12"/>
+    </row>
+    <row r="19" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A19" s="27">
+        <v>16</v>
+      </c>
+      <c r="B19" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="70">
+        <v>1</v>
+      </c>
+      <c r="D19" s="70"/>
+      <c r="E19" s="70"/>
+      <c r="F19" s="70"/>
+      <c r="G19" s="70"/>
+      <c r="H19" s="70">
+        <f>20+24</f>
+        <v>44</v>
+      </c>
+      <c r="I19" s="70"/>
+      <c r="J19" s="71"/>
+      <c r="K19" s="72"/>
+      <c r="L19" s="55"/>
+      <c r="M19" s="73"/>
+      <c r="N19" s="74"/>
+      <c r="O19" s="70"/>
+      <c r="P19" s="71"/>
+      <c r="Q19" s="71"/>
+      <c r="R19" s="72"/>
+      <c r="S19" s="55"/>
+      <c r="T19" s="58">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="U19" s="75">
+        <f t="shared" si="4"/>
+        <v>68</v>
+      </c>
+      <c r="V19" s="75">
+        <f t="shared" si="5"/>
+        <v>2.8333333333333335</v>
+      </c>
+      <c r="AF19" s="12"/>
+      <c r="AG19" s="12"/>
+      <c r="AH19" s="12"/>
+      <c r="AI19" s="12"/>
+      <c r="AJ19" s="12"/>
+      <c r="AK19" s="12"/>
+      <c r="AL19" s="12"/>
+      <c r="AM19" s="12"/>
+      <c r="AN19" s="12"/>
+      <c r="AO19" s="12"/>
+      <c r="AP19" s="12"/>
+      <c r="AQ19" s="12"/>
+      <c r="AR19" s="12"/>
+      <c r="AS19" s="12"/>
+      <c r="AT19" s="12"/>
+      <c r="AU19" s="12"/>
+      <c r="AV19" s="12"/>
+      <c r="AW19" s="12"/>
+      <c r="AX19" s="12"/>
+      <c r="AY19" s="12"/>
+      <c r="AZ19" s="12"/>
+      <c r="BA19" s="12"/>
+      <c r="BB19" s="12"/>
+    </row>
+    <row r="20" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A20" s="27">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="B20" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="70">
+        <v>5</v>
+      </c>
+      <c r="D20" s="70"/>
+      <c r="E20" s="70"/>
+      <c r="F20" s="70"/>
+      <c r="G20" s="70"/>
+      <c r="H20" s="70"/>
+      <c r="I20" s="70"/>
+      <c r="J20" s="71"/>
+      <c r="K20" s="72"/>
+      <c r="L20" s="55"/>
+      <c r="M20" s="73"/>
+      <c r="N20" s="74"/>
+      <c r="O20" s="70"/>
+      <c r="P20" s="71"/>
+      <c r="Q20" s="71"/>
+      <c r="R20" s="72"/>
+      <c r="S20" s="55"/>
+      <c r="T20" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U20" s="75">
+        <f t="shared" si="4"/>
+        <v>120</v>
+      </c>
+      <c r="V20" s="75">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="AF20" s="12"/>
+      <c r="AG20" s="12"/>
+      <c r="AH20" s="12"/>
+      <c r="AI20" s="12"/>
+      <c r="AJ20" s="12"/>
+      <c r="AK20" s="12"/>
+      <c r="AL20" s="12"/>
+      <c r="AM20" s="12"/>
+      <c r="AN20" s="12"/>
+      <c r="AO20" s="12"/>
+      <c r="AP20" s="12"/>
+      <c r="AQ20" s="12"/>
+      <c r="AR20" s="12"/>
+      <c r="AS20" s="12"/>
+      <c r="AT20" s="12"/>
+      <c r="AU20" s="12"/>
+      <c r="AV20" s="12"/>
+      <c r="AW20" s="12"/>
+      <c r="AX20" s="12"/>
+      <c r="AY20" s="12"/>
+      <c r="AZ20" s="12"/>
+      <c r="BA20" s="12"/>
+      <c r="BB20" s="12"/>
+    </row>
+    <row r="21" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A21" s="27">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="B21" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="70"/>
+      <c r="D21" s="70"/>
+      <c r="E21" s="70"/>
+      <c r="F21" s="70"/>
+      <c r="G21" s="70"/>
+      <c r="H21" s="70">
+        <f>2*24</f>
+        <v>48</v>
+      </c>
+      <c r="I21" s="70"/>
+      <c r="J21" s="71"/>
+      <c r="K21" s="72"/>
+      <c r="L21" s="55"/>
+      <c r="M21" s="73"/>
+      <c r="N21" s="74"/>
+      <c r="O21" s="70"/>
+      <c r="P21" s="71"/>
+      <c r="Q21" s="71"/>
+      <c r="R21" s="72"/>
+      <c r="S21" s="55"/>
+      <c r="T21" s="58">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+      <c r="U21" s="75">
+        <f t="shared" si="4"/>
+        <v>48</v>
+      </c>
+      <c r="V21" s="75">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="AF21" s="12"/>
+      <c r="AG21" s="12"/>
+      <c r="AH21" s="12"/>
+      <c r="AI21" s="12"/>
+      <c r="AJ21" s="12"/>
+      <c r="AK21" s="12"/>
+      <c r="AL21" s="12"/>
+      <c r="AM21" s="12"/>
+      <c r="AN21" s="12"/>
+      <c r="AO21" s="12"/>
+      <c r="AP21" s="12"/>
+      <c r="AQ21" s="12"/>
+      <c r="AR21" s="12"/>
+      <c r="AS21" s="12"/>
+      <c r="AT21" s="12"/>
+      <c r="AU21" s="12"/>
+      <c r="AV21" s="12"/>
+      <c r="AW21" s="12"/>
+      <c r="AX21" s="12"/>
+      <c r="AY21" s="12"/>
+      <c r="AZ21" s="12"/>
+      <c r="BA21" s="12"/>
+      <c r="BB21" s="12"/>
+    </row>
+    <row r="22" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="27">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="B22" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="70">
+        <v>1</v>
+      </c>
+      <c r="D22" s="70"/>
+      <c r="E22" s="70"/>
+      <c r="F22" s="70"/>
+      <c r="G22" s="70"/>
+      <c r="H22" s="70"/>
+      <c r="I22" s="70">
+        <v>20</v>
+      </c>
+      <c r="J22" s="71"/>
+      <c r="K22" s="72"/>
+      <c r="L22" s="55"/>
+      <c r="M22" s="73"/>
+      <c r="N22" s="74"/>
+      <c r="O22" s="70"/>
+      <c r="P22" s="71"/>
+      <c r="Q22" s="71"/>
+      <c r="R22" s="72"/>
+      <c r="S22" s="55"/>
+      <c r="T22" s="58">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="U22" s="75">
+        <f t="shared" si="4"/>
+        <v>44</v>
+      </c>
+      <c r="V22" s="75">
+        <f t="shared" si="5"/>
+        <v>1.8333333333333333</v>
+      </c>
+      <c r="W22" s="9"/>
+      <c r="X22" s="9"/>
+      <c r="Y22" s="9"/>
+      <c r="Z22" s="9"/>
+      <c r="AA22" s="9"/>
+      <c r="AB22" s="9"/>
+      <c r="AC22" s="9"/>
+      <c r="AD22" s="9"/>
+      <c r="AE22" s="9"/>
+      <c r="AF22" s="12"/>
+      <c r="AG22" s="12"/>
+      <c r="AH22" s="12"/>
+      <c r="AI22" s="12"/>
+      <c r="AJ22" s="12"/>
+      <c r="AK22" s="12"/>
+      <c r="AL22" s="12"/>
+      <c r="AM22" s="12"/>
+      <c r="AN22" s="12"/>
+      <c r="AO22" s="12"/>
+      <c r="AP22" s="12"/>
+      <c r="AQ22" s="12"/>
+      <c r="AR22" s="12"/>
+      <c r="AS22" s="12"/>
+      <c r="AT22" s="12"/>
+      <c r="AU22" s="12"/>
+      <c r="AV22" s="12"/>
+      <c r="AW22" s="12"/>
+      <c r="AX22" s="12"/>
+      <c r="AY22" s="12"/>
+      <c r="AZ22" s="12"/>
+      <c r="BA22" s="12"/>
+      <c r="BB22" s="12"/>
+    </row>
+    <row r="23" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="27">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="B23" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="70"/>
+      <c r="D23" s="70"/>
+      <c r="E23" s="70"/>
+      <c r="F23" s="70"/>
+      <c r="G23" s="70"/>
+      <c r="H23" s="70">
+        <f>37*24+19</f>
+        <v>907</v>
+      </c>
+      <c r="I23" s="70"/>
+      <c r="J23" s="71"/>
+      <c r="K23" s="72"/>
+      <c r="L23" s="55"/>
+      <c r="M23" s="73"/>
+      <c r="N23" s="74"/>
+      <c r="O23" s="70"/>
+      <c r="P23" s="71"/>
+      <c r="Q23" s="71"/>
+      <c r="R23" s="72"/>
+      <c r="S23" s="55"/>
+      <c r="T23" s="58">
+        <f t="shared" si="0"/>
+        <v>907</v>
+      </c>
+      <c r="U23" s="75">
+        <f t="shared" si="4"/>
+        <v>907</v>
+      </c>
+      <c r="V23" s="75">
+        <f t="shared" si="5"/>
+        <v>37.791666666666664</v>
+      </c>
+      <c r="W23" s="9"/>
+      <c r="X23" s="9"/>
+      <c r="Y23" s="9"/>
+      <c r="Z23" s="9"/>
+      <c r="AA23" s="9"/>
+      <c r="AB23" s="9"/>
+      <c r="AC23" s="9"/>
+      <c r="AD23" s="9"/>
+      <c r="AE23" s="9"/>
+      <c r="AF23" s="12"/>
+      <c r="AG23" s="12"/>
+      <c r="AH23" s="12"/>
+      <c r="AI23" s="12"/>
+      <c r="AJ23" s="12"/>
+      <c r="AK23" s="12"/>
+      <c r="AL23" s="12"/>
+      <c r="AM23" s="12"/>
+      <c r="AN23" s="12"/>
+      <c r="AO23" s="12"/>
+      <c r="AP23" s="12"/>
+      <c r="AQ23" s="12"/>
+      <c r="AR23" s="12"/>
+      <c r="AS23" s="12"/>
+      <c r="AT23" s="12"/>
+      <c r="AU23" s="12"/>
+      <c r="AV23" s="12"/>
+      <c r="AW23" s="12"/>
+      <c r="AX23" s="12"/>
+      <c r="AY23" s="12"/>
+      <c r="AZ23" s="12"/>
+      <c r="BA23" s="12"/>
+      <c r="BB23" s="12"/>
+    </row>
+    <row r="24" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A24" s="27">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="B24" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" s="70">
+        <v>2</v>
+      </c>
+      <c r="D24" s="70"/>
+      <c r="E24" s="70"/>
+      <c r="F24" s="70"/>
+      <c r="G24" s="70"/>
+      <c r="H24" s="70">
+        <f>3*24</f>
+        <v>72</v>
+      </c>
+      <c r="I24" s="70"/>
+      <c r="J24" s="71"/>
+      <c r="K24" s="72"/>
+      <c r="L24" s="55"/>
+      <c r="M24" s="73"/>
+      <c r="N24" s="74"/>
+      <c r="O24" s="70"/>
+      <c r="P24" s="71"/>
+      <c r="Q24" s="71"/>
+      <c r="R24" s="72"/>
+      <c r="S24" s="55"/>
+      <c r="T24" s="58">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="U24" s="75">
+        <f t="shared" si="4"/>
+        <v>120</v>
+      </c>
+      <c r="V24" s="75">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="AF24" s="12"/>
+      <c r="AG24" s="12"/>
+      <c r="AH24" s="12"/>
+      <c r="AI24" s="12"/>
+      <c r="AJ24" s="12"/>
+      <c r="AK24" s="12"/>
+      <c r="AL24" s="12"/>
+      <c r="AM24" s="12"/>
+      <c r="AN24" s="12"/>
+      <c r="AO24" s="12"/>
+      <c r="AP24" s="12"/>
+      <c r="AQ24" s="12"/>
+      <c r="AR24" s="12"/>
+      <c r="AS24" s="12"/>
+      <c r="AT24" s="12"/>
+      <c r="AU24" s="12"/>
+      <c r="AV24" s="12"/>
+      <c r="AW24" s="12"/>
+      <c r="AX24" s="12"/>
+      <c r="AY24" s="12"/>
+      <c r="AZ24" s="12"/>
+      <c r="BA24" s="12"/>
+      <c r="BB24" s="12"/>
+    </row>
+    <row r="25" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A25" s="27">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="70">
+        <f>126+25</f>
+        <v>151</v>
+      </c>
+      <c r="D25" s="70"/>
+      <c r="E25" s="70"/>
+      <c r="F25" s="70"/>
+      <c r="G25" s="70"/>
+      <c r="H25" s="70"/>
+      <c r="I25" s="70">
+        <v>1</v>
+      </c>
+      <c r="J25" s="71"/>
+      <c r="K25" s="72"/>
+      <c r="L25" s="55"/>
+      <c r="M25" s="73"/>
+      <c r="N25" s="74"/>
+      <c r="O25" s="70">
+        <v>1</v>
+      </c>
+      <c r="P25" s="71"/>
+      <c r="Q25" s="71">
+        <v>10</v>
+      </c>
+      <c r="R25" s="72"/>
+      <c r="S25" s="55"/>
+      <c r="T25" s="58">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="U25" s="75">
+        <f t="shared" si="4"/>
+        <v>3889</v>
+      </c>
+      <c r="V25" s="75">
+        <f t="shared" si="5"/>
+        <v>162.04166666666666</v>
+      </c>
+      <c r="AY25" s="14" t="e">
+        <f>#REF!-AY24</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="27">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="B26" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="70"/>
+      <c r="D26" s="70"/>
+      <c r="E26" s="70"/>
+      <c r="F26" s="70"/>
+      <c r="G26" s="70"/>
+      <c r="H26" s="70"/>
+      <c r="I26" s="70"/>
+      <c r="J26" s="71"/>
+      <c r="K26" s="72"/>
+      <c r="L26" s="55"/>
+      <c r="M26" s="73"/>
+      <c r="N26" s="74"/>
+      <c r="O26" s="70"/>
+      <c r="P26" s="71"/>
+      <c r="Q26" s="71"/>
+      <c r="R26" s="72"/>
+      <c r="S26" s="55"/>
+      <c r="T26" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U26" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V26" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W26" s="9"/>
+      <c r="X26" s="9"/>
+      <c r="Y26" s="9"/>
+      <c r="Z26" s="9"/>
+      <c r="AA26" s="9"/>
+      <c r="AB26" s="9"/>
+      <c r="AC26" s="9"/>
+      <c r="AD26" s="9"/>
+      <c r="AE26" s="9"/>
+    </row>
+    <row r="27" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="27">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="B27" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27" s="70">
+        <v>1</v>
+      </c>
+      <c r="D27" s="70"/>
+      <c r="E27" s="70"/>
+      <c r="F27" s="70"/>
+      <c r="G27" s="70"/>
+      <c r="H27" s="70"/>
+      <c r="I27" s="70"/>
+      <c r="J27" s="71"/>
+      <c r="K27" s="72"/>
+      <c r="L27" s="55"/>
+      <c r="M27" s="73"/>
+      <c r="N27" s="74"/>
+      <c r="O27" s="70"/>
+      <c r="P27" s="71"/>
+      <c r="Q27" s="71">
+        <v>1</v>
+      </c>
+      <c r="R27" s="72"/>
+      <c r="S27" s="55"/>
+      <c r="T27" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U27" s="75">
+        <f t="shared" si="4"/>
+        <v>48</v>
+      </c>
+      <c r="V27" s="75">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="W27" s="9"/>
+      <c r="X27" s="9"/>
+      <c r="Y27" s="9"/>
+      <c r="Z27" s="9"/>
+      <c r="AA27" s="9"/>
+      <c r="AB27" s="9"/>
+      <c r="AC27" s="9"/>
+      <c r="AD27" s="9"/>
+      <c r="AE27" s="9"/>
+    </row>
+    <row r="28" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="27">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="B28" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="70"/>
+      <c r="D28" s="70"/>
+      <c r="E28" s="70"/>
+      <c r="F28" s="70"/>
+      <c r="G28" s="70"/>
+      <c r="H28" s="70"/>
+      <c r="I28" s="70"/>
+      <c r="J28" s="71"/>
+      <c r="K28" s="72"/>
+      <c r="L28" s="55"/>
+      <c r="M28" s="73"/>
+      <c r="N28" s="74"/>
+      <c r="O28" s="70"/>
+      <c r="P28" s="71"/>
+      <c r="Q28" s="71"/>
+      <c r="R28" s="72"/>
+      <c r="S28" s="55"/>
+      <c r="T28" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U28" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V28" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W28" s="9"/>
+      <c r="X28" s="9"/>
+      <c r="Y28" s="9"/>
+      <c r="Z28" s="9"/>
+      <c r="AA28" s="9"/>
+      <c r="AB28" s="9"/>
+      <c r="AC28" s="9"/>
+      <c r="AD28" s="9"/>
+      <c r="AE28" s="9"/>
+    </row>
+    <row r="29" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A29" s="27">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="B29" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" s="70"/>
+      <c r="D29" s="70"/>
+      <c r="E29" s="70"/>
+      <c r="F29" s="70"/>
+      <c r="G29" s="70"/>
+      <c r="H29" s="70"/>
+      <c r="I29" s="70">
+        <v>5</v>
+      </c>
+      <c r="J29" s="71"/>
+      <c r="K29" s="72"/>
+      <c r="L29" s="55"/>
+      <c r="M29" s="73"/>
+      <c r="N29" s="74"/>
+      <c r="O29" s="70"/>
+      <c r="P29" s="71"/>
+      <c r="Q29" s="71">
+        <v>8</v>
+      </c>
+      <c r="R29" s="72"/>
+      <c r="S29" s="55"/>
+      <c r="T29" s="58">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="U29" s="75">
+        <f t="shared" si="4"/>
+        <v>197</v>
+      </c>
+      <c r="V29" s="75">
+        <f t="shared" si="5"/>
+        <v>8.2083333333333339</v>
+      </c>
+    </row>
+    <row r="30" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A30" s="27">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="B30" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="70">
+        <v>2</v>
+      </c>
+      <c r="D30" s="70"/>
+      <c r="E30" s="70"/>
+      <c r="F30" s="70"/>
+      <c r="G30" s="70"/>
+      <c r="H30" s="70"/>
+      <c r="I30" s="70"/>
+      <c r="J30" s="71"/>
+      <c r="K30" s="72"/>
+      <c r="L30" s="55"/>
+      <c r="M30" s="73"/>
+      <c r="N30" s="74"/>
+      <c r="O30" s="70"/>
+      <c r="P30" s="71"/>
+      <c r="Q30" s="71">
+        <v>2</v>
+      </c>
+      <c r="R30" s="72"/>
+      <c r="S30" s="55"/>
+      <c r="T30" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U30" s="75">
+        <f t="shared" si="4"/>
+        <v>96</v>
+      </c>
+      <c r="V30" s="75">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A31" s="27">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="B31" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" s="70"/>
+      <c r="D31" s="70"/>
+      <c r="E31" s="70"/>
+      <c r="F31" s="70"/>
+      <c r="G31" s="70"/>
+      <c r="H31" s="70"/>
+      <c r="I31" s="70"/>
+      <c r="J31" s="71"/>
+      <c r="K31" s="72"/>
+      <c r="L31" s="55"/>
+      <c r="M31" s="73"/>
+      <c r="N31" s="74"/>
+      <c r="O31" s="70"/>
+      <c r="P31" s="71"/>
+      <c r="Q31" s="71"/>
+      <c r="R31" s="72"/>
+      <c r="S31" s="55"/>
+      <c r="T31" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U31" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V31" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A32" s="27">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="B32" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" s="70"/>
+      <c r="D32" s="70"/>
+      <c r="E32" s="70"/>
+      <c r="F32" s="70"/>
+      <c r="G32" s="70"/>
+      <c r="H32" s="70"/>
+      <c r="I32" s="70"/>
+      <c r="J32" s="71"/>
+      <c r="K32" s="72"/>
+      <c r="L32" s="55"/>
+      <c r="M32" s="73"/>
+      <c r="N32" s="74"/>
+      <c r="O32" s="70"/>
+      <c r="P32" s="71"/>
+      <c r="Q32" s="71"/>
+      <c r="R32" s="72"/>
+      <c r="S32" s="55"/>
+      <c r="T32" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U32" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V32" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A33" s="27">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="B33" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" s="70"/>
+      <c r="D33" s="70"/>
+      <c r="E33" s="70"/>
+      <c r="F33" s="70"/>
+      <c r="G33" s="70"/>
+      <c r="H33" s="70"/>
+      <c r="I33" s="70"/>
+      <c r="J33" s="71"/>
+      <c r="K33" s="72"/>
+      <c r="L33" s="55"/>
+      <c r="M33" s="73"/>
+      <c r="N33" s="74"/>
+      <c r="O33" s="70"/>
+      <c r="P33" s="71"/>
+      <c r="Q33" s="71"/>
+      <c r="R33" s="72"/>
+      <c r="S33" s="55"/>
+      <c r="T33" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U33" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V33" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A34" s="27">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="B34" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" s="70">
+        <f>68+72</f>
+        <v>140</v>
+      </c>
+      <c r="D34" s="70"/>
+      <c r="E34" s="70"/>
+      <c r="F34" s="70"/>
+      <c r="G34" s="70"/>
+      <c r="H34" s="70"/>
+      <c r="I34" s="70">
+        <v>1</v>
+      </c>
+      <c r="J34" s="71"/>
+      <c r="K34" s="72">
+        <v>1</v>
+      </c>
+      <c r="L34" s="55"/>
+      <c r="M34" s="73"/>
+      <c r="N34" s="74"/>
+      <c r="O34" s="70">
+        <v>5</v>
+      </c>
+      <c r="P34" s="71"/>
+      <c r="Q34" s="71">
+        <v>23</v>
+      </c>
+      <c r="R34" s="72"/>
+      <c r="S34" s="55"/>
+      <c r="T34" s="58">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="U34" s="75">
+        <f t="shared" si="4"/>
+        <v>4034</v>
+      </c>
+      <c r="V34" s="75">
+        <f t="shared" si="5"/>
+        <v>168.08333333333334</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="27">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="B35" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="C35" s="70"/>
+      <c r="D35" s="70"/>
+      <c r="E35" s="70"/>
+      <c r="F35" s="70"/>
+      <c r="G35" s="70"/>
+      <c r="H35" s="70"/>
+      <c r="I35" s="70"/>
+      <c r="J35" s="71"/>
+      <c r="K35" s="72"/>
+      <c r="L35" s="55"/>
+      <c r="M35" s="73"/>
+      <c r="N35" s="74"/>
+      <c r="O35" s="70"/>
+      <c r="P35" s="71"/>
+      <c r="Q35" s="71"/>
+      <c r="R35" s="72"/>
+      <c r="S35" s="55"/>
+      <c r="T35" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U35" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V35" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A36" s="27">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+      <c r="B36" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="70"/>
+      <c r="D36" s="70"/>
+      <c r="E36" s="70"/>
+      <c r="F36" s="70"/>
+      <c r="G36" s="70"/>
+      <c r="H36" s="70"/>
+      <c r="I36" s="70"/>
+      <c r="J36" s="71"/>
+      <c r="K36" s="72"/>
+      <c r="L36" s="55"/>
+      <c r="M36" s="73"/>
+      <c r="N36" s="74"/>
+      <c r="O36" s="70"/>
+      <c r="P36" s="71"/>
+      <c r="Q36" s="71"/>
+      <c r="R36" s="72"/>
+      <c r="S36" s="55"/>
+      <c r="T36" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U36" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="27">
+        <f t="shared" si="1"/>
+        <v>34</v>
+      </c>
+      <c r="B37" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="C37" s="59">
+        <f>864+2376+16</f>
+        <v>3256</v>
+      </c>
+      <c r="D37" s="59"/>
+      <c r="E37" s="59"/>
+      <c r="F37" s="59"/>
+      <c r="G37" s="59"/>
+      <c r="H37" s="59">
+        <v>3</v>
+      </c>
+      <c r="I37" s="59">
+        <v>2</v>
+      </c>
+      <c r="J37" s="60">
+        <v>6</v>
+      </c>
+      <c r="K37" s="61">
+        <f>2+6</f>
+        <v>8</v>
+      </c>
+      <c r="L37" s="62"/>
+      <c r="M37" s="63"/>
+      <c r="N37" s="64"/>
+      <c r="O37" s="65">
+        <v>32</v>
+      </c>
+      <c r="P37" s="66"/>
+      <c r="Q37" s="66">
+        <v>54</v>
+      </c>
+      <c r="R37" s="67"/>
+      <c r="S37" s="62"/>
+      <c r="T37" s="77">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="U37" s="77">
+        <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
+        <v>20071</v>
+      </c>
+      <c r="V37" s="77">
+        <f>U37/6</f>
+        <v>3345.1666666666665</v>
+      </c>
+      <c r="W37" s="50"/>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A38" s="27">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="B38" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" s="70"/>
+      <c r="D38" s="70"/>
+      <c r="E38" s="70"/>
+      <c r="F38" s="70"/>
+      <c r="G38" s="70"/>
+      <c r="H38" s="70"/>
+      <c r="I38" s="70"/>
+      <c r="J38" s="71"/>
+      <c r="K38" s="72"/>
+      <c r="L38" s="55"/>
+      <c r="M38" s="73"/>
+      <c r="N38" s="74"/>
+      <c r="O38" s="70"/>
+      <c r="P38" s="71"/>
+      <c r="Q38" s="71"/>
+      <c r="R38" s="72"/>
+      <c r="S38" s="55"/>
+      <c r="T38" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U38" s="75">
+        <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
+        <v>0</v>
+      </c>
+      <c r="V38" s="75">
+        <f>U38/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A39" s="27">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="B39" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="C39" s="78"/>
+      <c r="D39" s="78"/>
+      <c r="E39" s="78"/>
+      <c r="F39" s="78"/>
+      <c r="G39" s="78"/>
+      <c r="H39" s="78"/>
+      <c r="I39" s="78"/>
+      <c r="J39" s="79"/>
+      <c r="K39" s="80"/>
+      <c r="L39" s="55"/>
+      <c r="M39" s="73"/>
+      <c r="N39" s="74"/>
+      <c r="O39" s="70"/>
+      <c r="P39" s="71"/>
+      <c r="Q39" s="71"/>
+      <c r="R39" s="72"/>
+      <c r="S39" s="95"/>
+      <c r="T39" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U39" s="75">
+        <f>C39*24+M39*24+O39*24+Q39*24+T39</f>
+        <v>0</v>
+      </c>
+      <c r="V39" s="75">
+        <f>U39/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="27">
+        <f t="shared" si="1"/>
+        <v>37</v>
+      </c>
+      <c r="B40" s="42" t="s">
+        <v>21</v>
+      </c>
+      <c r="C40" s="59">
+        <f>51+189</f>
+        <v>240</v>
+      </c>
+      <c r="D40" s="59"/>
+      <c r="E40" s="59"/>
+      <c r="F40" s="59"/>
+      <c r="G40" s="59"/>
+      <c r="H40" s="59"/>
+      <c r="I40" s="59"/>
+      <c r="J40" s="60"/>
+      <c r="K40" s="61">
+        <v>20</v>
+      </c>
+      <c r="L40" s="62"/>
+      <c r="M40" s="63"/>
+      <c r="N40" s="64"/>
+      <c r="O40" s="65">
+        <v>2</v>
+      </c>
+      <c r="P40" s="66"/>
+      <c r="Q40" s="66">
+        <v>15</v>
+      </c>
+      <c r="R40" s="67"/>
+      <c r="S40" s="62"/>
+      <c r="T40" s="77">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="U40" s="77">
+        <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
+        <v>6188</v>
+      </c>
+      <c r="V40" s="77">
+        <f>U40/24</f>
+        <v>257.83333333333331</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="27">
+        <f t="shared" si="1"/>
+        <v>38</v>
+      </c>
+      <c r="B41" s="43" t="s">
+        <v>22</v>
+      </c>
+      <c r="C41" s="82">
+        <f>192+91</f>
+        <v>283</v>
+      </c>
+      <c r="D41" s="82"/>
+      <c r="E41" s="82"/>
+      <c r="F41" s="82"/>
+      <c r="G41" s="82"/>
+      <c r="H41" s="82"/>
+      <c r="I41" s="82"/>
+      <c r="J41" s="83"/>
+      <c r="K41" s="84"/>
+      <c r="L41" s="85"/>
+      <c r="M41" s="86"/>
+      <c r="N41" s="87"/>
+      <c r="O41" s="82">
+        <v>10</v>
+      </c>
+      <c r="P41" s="83"/>
+      <c r="Q41" s="83">
+        <v>35</v>
+      </c>
+      <c r="R41" s="84"/>
+      <c r="S41" s="85"/>
+      <c r="T41" s="88">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U41" s="88">
+        <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
+        <v>3936</v>
+      </c>
+      <c r="V41" s="88">
+        <f>U41/12</f>
+        <v>328</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="27">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+      <c r="B42" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C42" s="70"/>
+      <c r="D42" s="70"/>
+      <c r="E42" s="70"/>
+      <c r="F42" s="70"/>
+      <c r="G42" s="70"/>
+      <c r="H42" s="70"/>
+      <c r="I42" s="70"/>
+      <c r="J42" s="71"/>
+      <c r="K42" s="72"/>
+      <c r="L42" s="55"/>
+      <c r="M42" s="73"/>
+      <c r="N42" s="74"/>
+      <c r="O42" s="70"/>
+      <c r="P42" s="71"/>
+      <c r="Q42" s="71"/>
+      <c r="R42" s="72"/>
+      <c r="S42" s="55"/>
+      <c r="T42" s="75"/>
+      <c r="U42" s="75"/>
+      <c r="V42" s="75"/>
+    </row>
+    <row r="43" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="27">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="B43" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="C43" s="65">
+        <f>8856+19764+9033</f>
+        <v>37653</v>
+      </c>
+      <c r="D43" s="65"/>
+      <c r="E43" s="65"/>
+      <c r="F43" s="65"/>
+      <c r="G43" s="65"/>
+      <c r="H43" s="65">
+        <v>3</v>
+      </c>
+      <c r="I43" s="65">
+        <v>12</v>
+      </c>
+      <c r="J43" s="66">
+        <f>26*6+4</f>
+        <v>160</v>
+      </c>
+      <c r="K43" s="67">
+        <f>69*6+1</f>
+        <v>415</v>
+      </c>
+      <c r="L43" s="62"/>
+      <c r="M43" s="63">
+        <v>43</v>
+      </c>
+      <c r="N43" s="64"/>
+      <c r="O43" s="65">
+        <v>470</v>
+      </c>
+      <c r="P43" s="66"/>
+      <c r="Q43" s="66">
+        <v>364</v>
+      </c>
+      <c r="R43" s="67"/>
+      <c r="S43" s="62"/>
+      <c r="T43" s="77">
+        <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
+        <v>590</v>
+      </c>
+      <c r="U43" s="77">
+        <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
+        <v>231770</v>
+      </c>
+      <c r="V43" s="77">
+        <f>U43/6</f>
+        <v>38628.333333333336</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="27">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+      <c r="B44" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="70"/>
+      <c r="D44" s="70"/>
+      <c r="E44" s="70"/>
+      <c r="F44" s="70"/>
+      <c r="G44" s="70"/>
+      <c r="H44" s="70"/>
+      <c r="I44" s="70"/>
+      <c r="J44" s="71"/>
+      <c r="K44" s="72"/>
+      <c r="L44" s="55"/>
+      <c r="M44" s="73"/>
+      <c r="N44" s="74"/>
+      <c r="O44" s="70"/>
+      <c r="P44" s="71"/>
+      <c r="Q44" s="71"/>
+      <c r="R44" s="72"/>
+      <c r="S44" s="55"/>
+      <c r="T44" s="75"/>
+      <c r="U44" s="75"/>
+      <c r="V44" s="75"/>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A45" s="27">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="B45" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="70"/>
+      <c r="D45" s="70"/>
+      <c r="E45" s="70"/>
+      <c r="F45" s="70"/>
+      <c r="G45" s="70"/>
+      <c r="H45" s="70"/>
+      <c r="I45" s="70"/>
+      <c r="J45" s="71"/>
+      <c r="K45" s="72"/>
+      <c r="L45" s="55"/>
+      <c r="M45" s="73"/>
+      <c r="N45" s="74"/>
+      <c r="O45" s="70"/>
+      <c r="P45" s="71"/>
+      <c r="Q45" s="71"/>
+      <c r="R45" s="72"/>
+      <c r="S45" s="55"/>
+      <c r="T45" s="75">
+        <f t="shared" ref="T45:T54" si="7">H45+I45+J45+K45+N45+P45+R45</f>
+        <v>0</v>
+      </c>
+      <c r="U45" s="75">
+        <f>C45*24+M45*24+O45*24+Q45*24+T45</f>
+        <v>0</v>
+      </c>
+      <c r="V45" s="75">
+        <f>U45/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A46" s="27">
+        <f t="shared" si="1"/>
+        <v>43</v>
+      </c>
+      <c r="B46" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="C46" s="70"/>
+      <c r="D46" s="70"/>
+      <c r="E46" s="70"/>
+      <c r="F46" s="70"/>
+      <c r="G46" s="70"/>
+      <c r="H46" s="70"/>
+      <c r="I46" s="70"/>
+      <c r="J46" s="71"/>
+      <c r="K46" s="72"/>
+      <c r="L46" s="55"/>
+      <c r="M46" s="73"/>
+      <c r="N46" s="74"/>
+      <c r="O46" s="70"/>
+      <c r="P46" s="71"/>
+      <c r="Q46" s="71"/>
+      <c r="R46" s="72"/>
+      <c r="S46" s="55"/>
+      <c r="T46" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U46" s="75">
+        <f t="shared" ref="U46:U50" si="8">C46*24+M46*24+O46*24+Q46*24+T46</f>
+        <v>0</v>
+      </c>
+      <c r="V46" s="75">
+        <f t="shared" ref="V46:V54" si="9">U46/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="27">
+        <f t="shared" si="1"/>
+        <v>44</v>
+      </c>
+      <c r="B47" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="C47" s="65">
+        <f>89+648+324+88+432+83+103+324+432+106</f>
+        <v>2629</v>
+      </c>
+      <c r="D47" s="65"/>
+      <c r="E47" s="65"/>
+      <c r="F47" s="65"/>
+      <c r="G47" s="65"/>
+      <c r="H47" s="65">
+        <v>1</v>
+      </c>
+      <c r="I47" s="65"/>
+      <c r="J47" s="66"/>
+      <c r="K47" s="67">
+        <v>5</v>
+      </c>
+      <c r="L47" s="62"/>
+      <c r="M47" s="63">
+        <v>2</v>
+      </c>
+      <c r="N47" s="64"/>
+      <c r="O47" s="65">
+        <v>15</v>
+      </c>
+      <c r="P47" s="66"/>
+      <c r="Q47" s="66">
+        <v>20</v>
+      </c>
+      <c r="R47" s="67">
+        <v>3</v>
+      </c>
+      <c r="S47" s="62"/>
+      <c r="T47" s="77">
+        <f t="shared" si="7"/>
+        <v>9</v>
+      </c>
+      <c r="U47" s="77">
+        <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
+        <v>16005</v>
+      </c>
+      <c r="V47" s="77">
+        <f>U47/6</f>
+        <v>2667.5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A48" s="27">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="B48" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C48" s="70"/>
+      <c r="D48" s="70"/>
+      <c r="E48" s="70"/>
+      <c r="F48" s="70"/>
+      <c r="G48" s="70"/>
+      <c r="H48" s="70">
+        <v>24</v>
+      </c>
+      <c r="I48" s="70"/>
+      <c r="J48" s="71"/>
+      <c r="K48" s="72"/>
+      <c r="L48" s="55"/>
+      <c r="M48" s="73"/>
+      <c r="N48" s="74"/>
+      <c r="O48" s="70"/>
+      <c r="P48" s="71"/>
+      <c r="Q48" s="71"/>
+      <c r="R48" s="72"/>
+      <c r="S48" s="55"/>
+      <c r="T48" s="75">
+        <f t="shared" si="7"/>
+        <v>24</v>
+      </c>
+      <c r="U48" s="75">
+        <f t="shared" si="8"/>
+        <v>24</v>
+      </c>
+      <c r="V48" s="75">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A49" s="27">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="B49" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C49" s="70"/>
+      <c r="D49" s="70"/>
+      <c r="E49" s="70"/>
+      <c r="F49" s="70"/>
+      <c r="G49" s="70"/>
+      <c r="H49" s="70"/>
+      <c r="I49" s="70"/>
+      <c r="J49" s="71"/>
+      <c r="K49" s="72"/>
+      <c r="L49" s="55"/>
+      <c r="M49" s="73"/>
+      <c r="N49" s="74"/>
+      <c r="O49" s="70"/>
+      <c r="P49" s="71"/>
+      <c r="Q49" s="71"/>
+      <c r="R49" s="72"/>
+      <c r="S49" s="55"/>
+      <c r="T49" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U49" s="75">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V49" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A50" s="27">
+        <f t="shared" si="1"/>
+        <v>47</v>
+      </c>
+      <c r="B50" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="C50" s="70"/>
+      <c r="D50" s="70"/>
+      <c r="E50" s="70"/>
+      <c r="F50" s="70"/>
+      <c r="G50" s="70"/>
+      <c r="H50" s="70"/>
+      <c r="I50" s="70"/>
+      <c r="J50" s="71"/>
+      <c r="K50" s="72"/>
+      <c r="L50" s="55"/>
+      <c r="M50" s="73"/>
+      <c r="N50" s="74"/>
+      <c r="O50" s="70"/>
+      <c r="P50" s="71"/>
+      <c r="Q50" s="71"/>
+      <c r="R50" s="72"/>
+      <c r="S50" s="55"/>
+      <c r="T50" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U50" s="75">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V50" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="27">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+      <c r="B51" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="C51" s="65">
+        <v>34</v>
+      </c>
+      <c r="D51" s="65"/>
+      <c r="E51" s="65"/>
+      <c r="F51" s="65"/>
+      <c r="G51" s="65"/>
+      <c r="H51" s="65"/>
+      <c r="I51" s="65"/>
+      <c r="J51" s="66"/>
+      <c r="K51" s="67"/>
+      <c r="L51" s="62"/>
+      <c r="M51" s="63"/>
+      <c r="N51" s="64"/>
+      <c r="O51" s="65"/>
+      <c r="P51" s="66"/>
+      <c r="Q51" s="66"/>
+      <c r="R51" s="67"/>
+      <c r="S51" s="62"/>
+      <c r="T51" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U51" s="77">
+        <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
+        <v>204</v>
+      </c>
+      <c r="V51" s="77">
+        <f>U51/6</f>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A52" s="27">
+        <f t="shared" si="1"/>
+        <v>49</v>
+      </c>
+      <c r="B52" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="C52" s="70"/>
+      <c r="D52" s="70"/>
+      <c r="E52" s="70"/>
+      <c r="F52" s="70"/>
+      <c r="G52" s="70"/>
+      <c r="H52" s="70"/>
+      <c r="I52" s="70"/>
+      <c r="J52" s="71"/>
+      <c r="K52" s="72"/>
+      <c r="L52" s="55"/>
+      <c r="M52" s="73"/>
+      <c r="N52" s="74"/>
+      <c r="O52" s="70"/>
+      <c r="P52" s="71"/>
+      <c r="Q52" s="71"/>
+      <c r="R52" s="72"/>
+      <c r="S52" s="55"/>
+      <c r="T52" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U52" s="75">
+        <f t="shared" ref="U52:U54" si="10">C52*24+M52*24+O52*24+Q52*24+T52</f>
+        <v>0</v>
+      </c>
+      <c r="V52" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A53" s="27">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="B53" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C53" s="70">
+        <v>7</v>
+      </c>
+      <c r="D53" s="70"/>
+      <c r="E53" s="70"/>
+      <c r="F53" s="70"/>
+      <c r="G53" s="70"/>
+      <c r="H53" s="70"/>
+      <c r="I53" s="70"/>
+      <c r="J53" s="71"/>
+      <c r="K53" s="72"/>
+      <c r="L53" s="55"/>
+      <c r="M53" s="73"/>
+      <c r="N53" s="74"/>
+      <c r="O53" s="70"/>
+      <c r="P53" s="71"/>
+      <c r="Q53" s="71"/>
+      <c r="R53" s="72"/>
+      <c r="S53" s="55"/>
+      <c r="T53" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U53" s="75">
+        <f t="shared" si="10"/>
+        <v>168</v>
+      </c>
+      <c r="V53" s="75">
+        <f t="shared" si="9"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A54" s="27">
+        <f t="shared" si="1"/>
+        <v>51</v>
+      </c>
+      <c r="B54" s="26"/>
+      <c r="C54" s="70"/>
+      <c r="D54" s="70"/>
+      <c r="E54" s="70"/>
+      <c r="F54" s="70"/>
+      <c r="G54" s="70"/>
+      <c r="H54" s="70"/>
+      <c r="I54" s="70"/>
+      <c r="J54" s="71"/>
+      <c r="K54" s="72"/>
+      <c r="L54" s="55"/>
+      <c r="M54" s="73"/>
+      <c r="N54" s="74"/>
+      <c r="O54" s="70"/>
+      <c r="P54" s="71"/>
+      <c r="Q54" s="71"/>
+      <c r="R54" s="72"/>
+      <c r="S54" s="55"/>
+      <c r="T54" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U54" s="75">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V54" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A55" s="27">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="B55" s="26"/>
+      <c r="C55" s="70"/>
+      <c r="D55" s="70"/>
+      <c r="E55" s="70"/>
+      <c r="F55" s="70"/>
+      <c r="G55" s="70"/>
+      <c r="H55" s="70"/>
+      <c r="I55" s="70"/>
+      <c r="J55" s="71"/>
+      <c r="K55" s="72"/>
+      <c r="L55" s="55"/>
+      <c r="M55" s="73"/>
+      <c r="N55" s="74"/>
+      <c r="O55" s="70"/>
+      <c r="P55" s="71"/>
+      <c r="Q55" s="71"/>
+      <c r="R55" s="72"/>
+      <c r="S55" s="55"/>
+      <c r="T55" s="75"/>
+      <c r="U55" s="75"/>
+      <c r="V55" s="75"/>
+    </row>
+    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A56" s="27">
+        <f t="shared" si="1"/>
+        <v>53</v>
+      </c>
+      <c r="B56" s="26"/>
+      <c r="C56" s="70"/>
+      <c r="D56" s="70"/>
+      <c r="E56" s="70"/>
+      <c r="F56" s="70"/>
+      <c r="G56" s="70"/>
+      <c r="H56" s="70"/>
+      <c r="I56" s="70"/>
+      <c r="J56" s="71"/>
+      <c r="K56" s="72"/>
+      <c r="L56" s="55"/>
+      <c r="M56" s="73"/>
+      <c r="N56" s="74"/>
+      <c r="O56" s="70"/>
+      <c r="P56" s="71"/>
+      <c r="Q56" s="71"/>
+      <c r="R56" s="72"/>
+      <c r="S56" s="55"/>
+      <c r="T56" s="75"/>
+      <c r="U56" s="75"/>
+      <c r="V56" s="75"/>
+    </row>
+    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A57" s="27">
+        <f t="shared" si="1"/>
+        <v>54</v>
+      </c>
+      <c r="B57" s="26"/>
+      <c r="C57" s="70"/>
+      <c r="D57" s="70"/>
+      <c r="E57" s="70"/>
+      <c r="F57" s="70"/>
+      <c r="G57" s="70"/>
+      <c r="H57" s="70"/>
+      <c r="I57" s="70"/>
+      <c r="J57" s="71"/>
+      <c r="K57" s="72"/>
+      <c r="L57" s="55"/>
+      <c r="M57" s="73"/>
+      <c r="N57" s="74"/>
+      <c r="O57" s="70"/>
+      <c r="P57" s="71"/>
+      <c r="Q57" s="71"/>
+      <c r="R57" s="72"/>
+      <c r="S57" s="55"/>
+      <c r="T57" s="75"/>
+      <c r="U57" s="75"/>
+      <c r="V57" s="75"/>
+    </row>
+    <row r="58" spans="1:22" s="15" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B58" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="C58" s="2">
+        <f>SUM(C7:C57)</f>
+        <v>47722</v>
+      </c>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2">
+        <f t="shared" ref="F58:K58" si="11">SUM(F7:F57)</f>
+        <v>0</v>
+      </c>
+      <c r="G58" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="H58" s="2">
+        <f t="shared" si="11"/>
+        <v>1190</v>
+      </c>
+      <c r="I58" s="6">
+        <f t="shared" si="11"/>
+        <v>44</v>
+      </c>
+      <c r="J58" s="6">
+        <f t="shared" si="11"/>
+        <v>166</v>
+      </c>
+      <c r="K58" s="6">
+        <f t="shared" si="11"/>
+        <v>457</v>
+      </c>
+      <c r="M58" s="5">
+        <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
+        <v>46</v>
+      </c>
+      <c r="N58" s="5">
+        <f t="shared" si="12"/>
+        <v>10</v>
+      </c>
+      <c r="O58" s="5">
+        <f t="shared" si="12"/>
+        <v>550</v>
+      </c>
+      <c r="P58" s="5">
+        <f t="shared" si="12"/>
+        <v>24</v>
+      </c>
+      <c r="Q58" s="5">
+        <f t="shared" si="12"/>
+        <v>561</v>
+      </c>
+      <c r="R58" s="5">
+        <f t="shared" si="12"/>
+        <v>3</v>
+      </c>
+      <c r="S58" s="55"/>
+      <c r="T58" s="4">
+        <f>SUM(T7:T57)</f>
+        <v>1894</v>
+      </c>
+      <c r="U58" s="90">
+        <f>SUM(U7:U57)</f>
+        <v>368758</v>
+      </c>
+      <c r="V58" s="4">
+        <f>SUM(V7:V57)</f>
+        <v>49035.166666666672</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="60" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="C60" s="108" t="s">
+        <v>41</v>
+      </c>
+      <c r="D60" s="109"/>
+      <c r="E60" s="109"/>
+      <c r="F60" s="109"/>
+      <c r="G60" s="109"/>
+      <c r="H60" s="109"/>
+      <c r="I60" s="109"/>
+      <c r="J60" s="109"/>
+      <c r="K60" s="110"/>
+      <c r="U60" s="24" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B61" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="C61" s="19"/>
+      <c r="D61" s="19"/>
+      <c r="E61" s="19"/>
+      <c r="F61" s="19"/>
+      <c r="G61" s="19"/>
+      <c r="H61" s="19"/>
+      <c r="I61" s="19"/>
+      <c r="J61" s="45"/>
+      <c r="K61" s="20"/>
+      <c r="U61" s="7"/>
+    </row>
+    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B62" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+      <c r="J62" s="44"/>
+      <c r="K62" s="21"/>
+      <c r="U62" s="3"/>
+    </row>
+    <row r="63" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B63" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C63" s="22"/>
+      <c r="D63" s="22"/>
+      <c r="E63" s="22"/>
+      <c r="F63" s="22"/>
+      <c r="G63" s="22"/>
+      <c r="H63" s="22"/>
+      <c r="I63" s="22"/>
+      <c r="J63" s="46"/>
+      <c r="K63" s="23"/>
+      <c r="U63" s="8"/>
+    </row>
+    <row r="64" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B65" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="C65" s="19"/>
+      <c r="D65" s="19"/>
+      <c r="E65" s="19"/>
+      <c r="F65" s="19"/>
+      <c r="G65" s="19"/>
+      <c r="H65" s="19"/>
+      <c r="I65" s="19"/>
+      <c r="J65" s="45"/>
+      <c r="K65" s="20"/>
+      <c r="U65" s="7"/>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B66" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C66" s="1"/>
+      <c r="D66" s="1"/>
+      <c r="E66" s="1"/>
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="J66" s="44"/>
+      <c r="K66" s="21"/>
+      <c r="U66" s="3"/>
+    </row>
+    <row r="67" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B67" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C67" s="22"/>
+      <c r="D67" s="22"/>
+      <c r="E67" s="22"/>
+      <c r="F67" s="22"/>
+      <c r="G67" s="22"/>
+      <c r="H67" s="22"/>
+      <c r="I67" s="22"/>
+      <c r="J67" s="46"/>
+      <c r="K67" s="23"/>
+      <c r="U67" s="8"/>
+    </row>
+    <row r="68" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B69" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="C69" s="19"/>
+      <c r="D69" s="19"/>
+      <c r="E69" s="19"/>
+      <c r="F69" s="19"/>
+      <c r="G69" s="19"/>
+      <c r="H69" s="19"/>
+      <c r="I69" s="19"/>
+      <c r="J69" s="45"/>
+      <c r="K69" s="20"/>
+      <c r="U69" s="7"/>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B70" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="J70" s="44"/>
+      <c r="K70" s="21"/>
+      <c r="U70" s="3"/>
+    </row>
+    <row r="71" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B71" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C71" s="22"/>
+      <c r="D71" s="22"/>
+      <c r="E71" s="22"/>
+      <c r="F71" s="22"/>
+      <c r="G71" s="22"/>
+      <c r="H71" s="22"/>
+      <c r="I71" s="22"/>
+      <c r="J71" s="46"/>
+      <c r="K71" s="23"/>
+      <c r="U71" s="8"/>
+    </row>
+    <row r="72" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B73" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="C73" s="19"/>
+      <c r="D73" s="19"/>
+      <c r="E73" s="19"/>
+      <c r="F73" s="19"/>
+      <c r="G73" s="19"/>
+      <c r="H73" s="19"/>
+      <c r="I73" s="19"/>
+      <c r="J73" s="45"/>
+      <c r="K73" s="20"/>
+      <c r="U73" s="7"/>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B74" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C74" s="1"/>
+      <c r="D74" s="1"/>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1"/>
+      <c r="J74" s="44"/>
+      <c r="K74" s="21"/>
+      <c r="U74" s="3"/>
+    </row>
+    <row r="75" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B75" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C75" s="22"/>
+      <c r="D75" s="22"/>
+      <c r="E75" s="22"/>
+      <c r="F75" s="22"/>
+      <c r="G75" s="22"/>
+      <c r="H75" s="22"/>
+      <c r="I75" s="22"/>
+      <c r="J75" s="46"/>
+      <c r="K75" s="23"/>
+      <c r="U75" s="8"/>
+    </row>
+    <row r="76" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B77" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="C77" s="19"/>
+      <c r="D77" s="19"/>
+      <c r="E77" s="19"/>
+      <c r="F77" s="19"/>
+      <c r="G77" s="19"/>
+      <c r="H77" s="19"/>
+      <c r="I77" s="19"/>
+      <c r="J77" s="45"/>
+      <c r="K77" s="20"/>
+      <c r="U77" s="7"/>
+    </row>
+    <row r="78" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B78" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C78" s="1"/>
+      <c r="D78" s="1"/>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+      <c r="J78" s="44"/>
+      <c r="K78" s="21"/>
+      <c r="U78" s="3"/>
+    </row>
+    <row r="79" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B79" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C79" s="22"/>
+      <c r="D79" s="22"/>
+      <c r="E79" s="22"/>
+      <c r="F79" s="22"/>
+      <c r="G79" s="22"/>
+      <c r="H79" s="22"/>
+      <c r="I79" s="22"/>
+      <c r="J79" s="46"/>
+      <c r="K79" s="23"/>
+      <c r="U79" s="8"/>
+    </row>
+    <row r="80" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="81" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B81" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="C81" s="17"/>
+      <c r="D81" s="17"/>
+      <c r="E81" s="17"/>
+      <c r="F81" s="17"/>
+      <c r="G81" s="17"/>
+      <c r="H81" s="17"/>
+      <c r="I81" s="17"/>
+      <c r="J81" s="47"/>
+      <c r="K81" s="18"/>
+      <c r="U81" s="16"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="C60:K60"/>
+    <mergeCell ref="I1:U1"/>
+    <mergeCell ref="C4:K4"/>
+    <mergeCell ref="T4:T5"/>
+    <mergeCell ref="U4:U5"/>
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -26953,21 +30079,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="110" t="s">
+      <c r="I1" s="111" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="110"/>
-      <c r="K1" s="110"/>
-      <c r="L1" s="110"/>
-      <c r="M1" s="110"/>
-      <c r="N1" s="110"/>
-      <c r="O1" s="110"/>
-      <c r="P1" s="110"/>
-      <c r="Q1" s="110"/>
-      <c r="R1" s="110"/>
-      <c r="S1" s="110"/>
-      <c r="T1" s="110"/>
-      <c r="U1" s="110"/>
+      <c r="J1" s="111"/>
+      <c r="K1" s="111"/>
+      <c r="L1" s="111"/>
+      <c r="M1" s="111"/>
+      <c r="N1" s="111"/>
+      <c r="O1" s="111"/>
+      <c r="P1" s="111"/>
+      <c r="Q1" s="111"/>
+      <c r="R1" s="111"/>
+      <c r="S1" s="111"/>
+      <c r="T1" s="111"/>
+      <c r="U1" s="111"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -26979,17 +30105,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="111" t="s">
+      <c r="C4" s="112" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="111"/>
-      <c r="E4" s="111"/>
-      <c r="F4" s="111"/>
-      <c r="G4" s="111"/>
-      <c r="H4" s="111"/>
-      <c r="I4" s="111"/>
-      <c r="J4" s="112"/>
-      <c r="K4" s="113"/>
+      <c r="D4" s="112"/>
+      <c r="E4" s="112"/>
+      <c r="F4" s="112"/>
+      <c r="G4" s="112"/>
+      <c r="H4" s="112"/>
+      <c r="I4" s="112"/>
+      <c r="J4" s="113"/>
+      <c r="K4" s="114"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -27009,13 +30135,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="114" t="s">
+      <c r="T4" s="115" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="120" t="s">
+      <c r="U4" s="121" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="103" t="s">
+      <c r="V4" s="104" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -27055,10 +30181,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="118" t="s">
+      <c r="J5" s="119" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="119"/>
+      <c r="K5" s="120"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -27066,9 +30192,9 @@
       <c r="Q5" s="96"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="115"/>
-      <c r="U5" s="121"/>
-      <c r="V5" s="104"/>
+      <c r="T5" s="116"/>
+      <c r="U5" s="122"/>
+      <c r="V5" s="105"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -29778,17 +32904,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="107" t="s">
+      <c r="C60" s="108" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="108"/>
-      <c r="E60" s="108"/>
-      <c r="F60" s="108"/>
-      <c r="G60" s="108"/>
-      <c r="H60" s="108"/>
-      <c r="I60" s="108"/>
-      <c r="J60" s="108"/>
-      <c r="K60" s="109"/>
+      <c r="D60" s="109"/>
+      <c r="E60" s="109"/>
+      <c r="F60" s="109"/>
+      <c r="G60" s="109"/>
+      <c r="H60" s="109"/>
+      <c r="I60" s="109"/>
+      <c r="J60" s="109"/>
+      <c r="K60" s="110"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -30097,21 +33223,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="110" t="s">
+      <c r="I1" s="111" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="110"/>
-      <c r="K1" s="110"/>
-      <c r="L1" s="110"/>
-      <c r="M1" s="110"/>
-      <c r="N1" s="110"/>
-      <c r="O1" s="110"/>
-      <c r="P1" s="110"/>
-      <c r="Q1" s="110"/>
-      <c r="R1" s="110"/>
-      <c r="S1" s="110"/>
-      <c r="T1" s="110"/>
-      <c r="U1" s="110"/>
+      <c r="J1" s="111"/>
+      <c r="K1" s="111"/>
+      <c r="L1" s="111"/>
+      <c r="M1" s="111"/>
+      <c r="N1" s="111"/>
+      <c r="O1" s="111"/>
+      <c r="P1" s="111"/>
+      <c r="Q1" s="111"/>
+      <c r="R1" s="111"/>
+      <c r="S1" s="111"/>
+      <c r="T1" s="111"/>
+      <c r="U1" s="111"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -30123,17 +33249,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="111" t="s">
+      <c r="C4" s="112" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="111"/>
-      <c r="E4" s="111"/>
-      <c r="F4" s="111"/>
-      <c r="G4" s="111"/>
-      <c r="H4" s="111"/>
-      <c r="I4" s="111"/>
-      <c r="J4" s="112"/>
-      <c r="K4" s="113"/>
+      <c r="D4" s="112"/>
+      <c r="E4" s="112"/>
+      <c r="F4" s="112"/>
+      <c r="G4" s="112"/>
+      <c r="H4" s="112"/>
+      <c r="I4" s="112"/>
+      <c r="J4" s="113"/>
+      <c r="K4" s="114"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -30153,13 +33279,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="114" t="s">
+      <c r="T4" s="115" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="120" t="s">
+      <c r="U4" s="121" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="103" t="s">
+      <c r="V4" s="104" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -30199,10 +33325,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="118" t="s">
+      <c r="J5" s="119" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="119"/>
+      <c r="K5" s="120"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -30210,9 +33336,9 @@
       <c r="Q5" s="97"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="115"/>
-      <c r="U5" s="121"/>
-      <c r="V5" s="104"/>
+      <c r="T5" s="116"/>
+      <c r="U5" s="122"/>
+      <c r="V5" s="105"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -32912,17 +36038,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="107" t="s">
+      <c r="C60" s="108" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="108"/>
-      <c r="E60" s="108"/>
-      <c r="F60" s="108"/>
-      <c r="G60" s="108"/>
-      <c r="H60" s="108"/>
-      <c r="I60" s="108"/>
-      <c r="J60" s="108"/>
-      <c r="K60" s="109"/>
+      <c r="D60" s="109"/>
+      <c r="E60" s="109"/>
+      <c r="F60" s="109"/>
+      <c r="G60" s="109"/>
+      <c r="H60" s="109"/>
+      <c r="I60" s="109"/>
+      <c r="J60" s="109"/>
+      <c r="K60" s="110"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -33231,21 +36357,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="110" t="s">
+      <c r="I1" s="111" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="110"/>
-      <c r="K1" s="110"/>
-      <c r="L1" s="110"/>
-      <c r="M1" s="110"/>
-      <c r="N1" s="110"/>
-      <c r="O1" s="110"/>
-      <c r="P1" s="110"/>
-      <c r="Q1" s="110"/>
-      <c r="R1" s="110"/>
-      <c r="S1" s="110"/>
-      <c r="T1" s="110"/>
-      <c r="U1" s="110"/>
+      <c r="J1" s="111"/>
+      <c r="K1" s="111"/>
+      <c r="L1" s="111"/>
+      <c r="M1" s="111"/>
+      <c r="N1" s="111"/>
+      <c r="O1" s="111"/>
+      <c r="P1" s="111"/>
+      <c r="Q1" s="111"/>
+      <c r="R1" s="111"/>
+      <c r="S1" s="111"/>
+      <c r="T1" s="111"/>
+      <c r="U1" s="111"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -33257,17 +36383,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="111" t="s">
+      <c r="C4" s="112" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="111"/>
-      <c r="E4" s="111"/>
-      <c r="F4" s="111"/>
-      <c r="G4" s="111"/>
-      <c r="H4" s="111"/>
-      <c r="I4" s="111"/>
-      <c r="J4" s="112"/>
-      <c r="K4" s="113"/>
+      <c r="D4" s="112"/>
+      <c r="E4" s="112"/>
+      <c r="F4" s="112"/>
+      <c r="G4" s="112"/>
+      <c r="H4" s="112"/>
+      <c r="I4" s="112"/>
+      <c r="J4" s="113"/>
+      <c r="K4" s="114"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -33287,13 +36413,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="114" t="s">
+      <c r="T4" s="115" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="120" t="s">
+      <c r="U4" s="121" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="103" t="s">
+      <c r="V4" s="104" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -33333,10 +36459,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="118" t="s">
+      <c r="J5" s="119" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="119"/>
+      <c r="K5" s="120"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -33344,9 +36470,9 @@
       <c r="Q5" s="97"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="115"/>
-      <c r="U5" s="121"/>
-      <c r="V5" s="104"/>
+      <c r="T5" s="116"/>
+      <c r="U5" s="122"/>
+      <c r="V5" s="105"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -36046,17 +39172,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="107" t="s">
+      <c r="C60" s="108" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="108"/>
-      <c r="E60" s="108"/>
-      <c r="F60" s="108"/>
-      <c r="G60" s="108"/>
-      <c r="H60" s="108"/>
-      <c r="I60" s="108"/>
-      <c r="J60" s="108"/>
-      <c r="K60" s="109"/>
+      <c r="D60" s="109"/>
+      <c r="E60" s="109"/>
+      <c r="F60" s="109"/>
+      <c r="G60" s="109"/>
+      <c r="H60" s="109"/>
+      <c r="I60" s="109"/>
+      <c r="J60" s="109"/>
+      <c r="K60" s="110"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -36365,21 +39491,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="110" t="s">
+      <c r="I1" s="111" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="110"/>
-      <c r="K1" s="110"/>
-      <c r="L1" s="110"/>
-      <c r="M1" s="110"/>
-      <c r="N1" s="110"/>
-      <c r="O1" s="110"/>
-      <c r="P1" s="110"/>
-      <c r="Q1" s="110"/>
-      <c r="R1" s="110"/>
-      <c r="S1" s="110"/>
-      <c r="T1" s="110"/>
-      <c r="U1" s="110"/>
+      <c r="J1" s="111"/>
+      <c r="K1" s="111"/>
+      <c r="L1" s="111"/>
+      <c r="M1" s="111"/>
+      <c r="N1" s="111"/>
+      <c r="O1" s="111"/>
+      <c r="P1" s="111"/>
+      <c r="Q1" s="111"/>
+      <c r="R1" s="111"/>
+      <c r="S1" s="111"/>
+      <c r="T1" s="111"/>
+      <c r="U1" s="111"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -36391,17 +39517,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="111" t="s">
+      <c r="C4" s="112" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="111"/>
-      <c r="E4" s="111"/>
-      <c r="F4" s="111"/>
-      <c r="G4" s="111"/>
-      <c r="H4" s="111"/>
-      <c r="I4" s="111"/>
-      <c r="J4" s="112"/>
-      <c r="K4" s="113"/>
+      <c r="D4" s="112"/>
+      <c r="E4" s="112"/>
+      <c r="F4" s="112"/>
+      <c r="G4" s="112"/>
+      <c r="H4" s="112"/>
+      <c r="I4" s="112"/>
+      <c r="J4" s="113"/>
+      <c r="K4" s="114"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -36421,13 +39547,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="114" t="s">
+      <c r="T4" s="115" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="120" t="s">
+      <c r="U4" s="121" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="103" t="s">
+      <c r="V4" s="104" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -36467,10 +39593,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="118" t="s">
+      <c r="J5" s="119" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="119"/>
+      <c r="K5" s="120"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -36478,9 +39604,9 @@
       <c r="Q5" s="97"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="115"/>
-      <c r="U5" s="121"/>
-      <c r="V5" s="104"/>
+      <c r="T5" s="116"/>
+      <c r="U5" s="122"/>
+      <c r="V5" s="105"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -39170,17 +42296,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="107" t="s">
+      <c r="C60" s="108" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="108"/>
-      <c r="E60" s="108"/>
-      <c r="F60" s="108"/>
-      <c r="G60" s="108"/>
-      <c r="H60" s="108"/>
-      <c r="I60" s="108"/>
-      <c r="J60" s="108"/>
-      <c r="K60" s="109"/>
+      <c r="D60" s="109"/>
+      <c r="E60" s="109"/>
+      <c r="F60" s="109"/>
+      <c r="G60" s="109"/>
+      <c r="H60" s="109"/>
+      <c r="I60" s="109"/>
+      <c r="J60" s="109"/>
+      <c r="K60" s="110"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -39489,21 +42615,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="110" t="s">
+      <c r="I1" s="111" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="110"/>
-      <c r="K1" s="110"/>
-      <c r="L1" s="110"/>
-      <c r="M1" s="110"/>
-      <c r="N1" s="110"/>
-      <c r="O1" s="110"/>
-      <c r="P1" s="110"/>
-      <c r="Q1" s="110"/>
-      <c r="R1" s="110"/>
-      <c r="S1" s="110"/>
-      <c r="T1" s="110"/>
-      <c r="U1" s="110"/>
+      <c r="J1" s="111"/>
+      <c r="K1" s="111"/>
+      <c r="L1" s="111"/>
+      <c r="M1" s="111"/>
+      <c r="N1" s="111"/>
+      <c r="O1" s="111"/>
+      <c r="P1" s="111"/>
+      <c r="Q1" s="111"/>
+      <c r="R1" s="111"/>
+      <c r="S1" s="111"/>
+      <c r="T1" s="111"/>
+      <c r="U1" s="111"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -39515,17 +42641,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="111" t="s">
+      <c r="C4" s="112" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="111"/>
-      <c r="E4" s="111"/>
-      <c r="F4" s="111"/>
-      <c r="G4" s="111"/>
-      <c r="H4" s="111"/>
-      <c r="I4" s="111"/>
-      <c r="J4" s="112"/>
-      <c r="K4" s="113"/>
+      <c r="D4" s="112"/>
+      <c r="E4" s="112"/>
+      <c r="F4" s="112"/>
+      <c r="G4" s="112"/>
+      <c r="H4" s="112"/>
+      <c r="I4" s="112"/>
+      <c r="J4" s="113"/>
+      <c r="K4" s="114"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -39545,13 +42671,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="114" t="s">
+      <c r="T4" s="115" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="120" t="s">
+      <c r="U4" s="121" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="103" t="s">
+      <c r="V4" s="104" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -39591,10 +42717,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="118" t="s">
+      <c r="J5" s="119" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="119"/>
+      <c r="K5" s="120"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -39602,9 +42728,9 @@
       <c r="Q5" s="98"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="115"/>
-      <c r="U5" s="121"/>
-      <c r="V5" s="104"/>
+      <c r="T5" s="116"/>
+      <c r="U5" s="122"/>
+      <c r="V5" s="105"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -42319,17 +45445,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="107" t="s">
+      <c r="C60" s="108" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="108"/>
-      <c r="E60" s="108"/>
-      <c r="F60" s="108"/>
-      <c r="G60" s="108"/>
-      <c r="H60" s="108"/>
-      <c r="I60" s="108"/>
-      <c r="J60" s="108"/>
-      <c r="K60" s="109"/>
+      <c r="D60" s="109"/>
+      <c r="E60" s="109"/>
+      <c r="F60" s="109"/>
+      <c r="G60" s="109"/>
+      <c r="H60" s="109"/>
+      <c r="I60" s="109"/>
+      <c r="J60" s="109"/>
+      <c r="K60" s="110"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -42638,21 +45764,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="110" t="s">
+      <c r="I1" s="111" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="110"/>
-      <c r="K1" s="110"/>
-      <c r="L1" s="110"/>
-      <c r="M1" s="110"/>
-      <c r="N1" s="110"/>
-      <c r="O1" s="110"/>
-      <c r="P1" s="110"/>
-      <c r="Q1" s="110"/>
-      <c r="R1" s="110"/>
-      <c r="S1" s="110"/>
-      <c r="T1" s="110"/>
-      <c r="U1" s="110"/>
+      <c r="J1" s="111"/>
+      <c r="K1" s="111"/>
+      <c r="L1" s="111"/>
+      <c r="M1" s="111"/>
+      <c r="N1" s="111"/>
+      <c r="O1" s="111"/>
+      <c r="P1" s="111"/>
+      <c r="Q1" s="111"/>
+      <c r="R1" s="111"/>
+      <c r="S1" s="111"/>
+      <c r="T1" s="111"/>
+      <c r="U1" s="111"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -42664,17 +45790,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="111" t="s">
+      <c r="C4" s="112" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="111"/>
-      <c r="E4" s="111"/>
-      <c r="F4" s="111"/>
-      <c r="G4" s="111"/>
-      <c r="H4" s="111"/>
-      <c r="I4" s="111"/>
-      <c r="J4" s="112"/>
-      <c r="K4" s="113"/>
+      <c r="D4" s="112"/>
+      <c r="E4" s="112"/>
+      <c r="F4" s="112"/>
+      <c r="G4" s="112"/>
+      <c r="H4" s="112"/>
+      <c r="I4" s="112"/>
+      <c r="J4" s="113"/>
+      <c r="K4" s="114"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -42694,13 +45820,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="114" t="s">
+      <c r="T4" s="115" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="120" t="s">
+      <c r="U4" s="121" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="103" t="s">
+      <c r="V4" s="104" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -42740,10 +45866,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="118" t="s">
+      <c r="J5" s="119" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="119"/>
+      <c r="K5" s="120"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -42751,9 +45877,9 @@
       <c r="Q5" s="98"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="115"/>
-      <c r="U5" s="121"/>
-      <c r="V5" s="104"/>
+      <c r="T5" s="116"/>
+      <c r="U5" s="122"/>
+      <c r="V5" s="105"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -45458,17 +48584,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="107" t="s">
+      <c r="C60" s="108" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="108"/>
-      <c r="E60" s="108"/>
-      <c r="F60" s="108"/>
-      <c r="G60" s="108"/>
-      <c r="H60" s="108"/>
-      <c r="I60" s="108"/>
-      <c r="J60" s="108"/>
-      <c r="K60" s="109"/>
+      <c r="D60" s="109"/>
+      <c r="E60" s="109"/>
+      <c r="F60" s="109"/>
+      <c r="G60" s="109"/>
+      <c r="H60" s="109"/>
+      <c r="I60" s="109"/>
+      <c r="J60" s="109"/>
+      <c r="K60" s="110"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -45777,21 +48903,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="110" t="s">
+      <c r="I1" s="111" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="110"/>
-      <c r="K1" s="110"/>
-      <c r="L1" s="110"/>
-      <c r="M1" s="110"/>
-      <c r="N1" s="110"/>
-      <c r="O1" s="110"/>
-      <c r="P1" s="110"/>
-      <c r="Q1" s="110"/>
-      <c r="R1" s="110"/>
-      <c r="S1" s="110"/>
-      <c r="T1" s="110"/>
-      <c r="U1" s="110"/>
+      <c r="J1" s="111"/>
+      <c r="K1" s="111"/>
+      <c r="L1" s="111"/>
+      <c r="M1" s="111"/>
+      <c r="N1" s="111"/>
+      <c r="O1" s="111"/>
+      <c r="P1" s="111"/>
+      <c r="Q1" s="111"/>
+      <c r="R1" s="111"/>
+      <c r="S1" s="111"/>
+      <c r="T1" s="111"/>
+      <c r="U1" s="111"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -45803,17 +48929,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="111" t="s">
+      <c r="C4" s="112" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="111"/>
-      <c r="E4" s="111"/>
-      <c r="F4" s="111"/>
-      <c r="G4" s="111"/>
-      <c r="H4" s="111"/>
-      <c r="I4" s="111"/>
-      <c r="J4" s="112"/>
-      <c r="K4" s="113"/>
+      <c r="D4" s="112"/>
+      <c r="E4" s="112"/>
+      <c r="F4" s="112"/>
+      <c r="G4" s="112"/>
+      <c r="H4" s="112"/>
+      <c r="I4" s="112"/>
+      <c r="J4" s="113"/>
+      <c r="K4" s="114"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -45833,13 +48959,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="114" t="s">
+      <c r="T4" s="115" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="120" t="s">
+      <c r="U4" s="121" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="103" t="s">
+      <c r="V4" s="104" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -45879,10 +49005,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="118" t="s">
+      <c r="J5" s="119" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="119"/>
+      <c r="K5" s="120"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -45890,9 +49016,9 @@
       <c r="Q5" s="98"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="115"/>
-      <c r="U5" s="121"/>
-      <c r="V5" s="104"/>
+      <c r="T5" s="116"/>
+      <c r="U5" s="122"/>
+      <c r="V5" s="105"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -48594,17 +51720,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="107" t="s">
+      <c r="C60" s="108" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="108"/>
-      <c r="E60" s="108"/>
-      <c r="F60" s="108"/>
-      <c r="G60" s="108"/>
-      <c r="H60" s="108"/>
-      <c r="I60" s="108"/>
-      <c r="J60" s="108"/>
-      <c r="K60" s="109"/>
+      <c r="D60" s="109"/>
+      <c r="E60" s="109"/>
+      <c r="F60" s="109"/>
+      <c r="G60" s="109"/>
+      <c r="H60" s="109"/>
+      <c r="I60" s="109"/>
+      <c r="J60" s="109"/>
+      <c r="K60" s="110"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -48913,21 +52039,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="110" t="s">
+      <c r="I1" s="111" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="110"/>
-      <c r="K1" s="110"/>
-      <c r="L1" s="110"/>
-      <c r="M1" s="110"/>
-      <c r="N1" s="110"/>
-      <c r="O1" s="110"/>
-      <c r="P1" s="110"/>
-      <c r="Q1" s="110"/>
-      <c r="R1" s="110"/>
-      <c r="S1" s="110"/>
-      <c r="T1" s="110"/>
-      <c r="U1" s="110"/>
+      <c r="J1" s="111"/>
+      <c r="K1" s="111"/>
+      <c r="L1" s="111"/>
+      <c r="M1" s="111"/>
+      <c r="N1" s="111"/>
+      <c r="O1" s="111"/>
+      <c r="P1" s="111"/>
+      <c r="Q1" s="111"/>
+      <c r="R1" s="111"/>
+      <c r="S1" s="111"/>
+      <c r="T1" s="111"/>
+      <c r="U1" s="111"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -48939,17 +52065,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="111" t="s">
+      <c r="C4" s="112" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="111"/>
-      <c r="E4" s="111"/>
-      <c r="F4" s="111"/>
-      <c r="G4" s="111"/>
-      <c r="H4" s="111"/>
-      <c r="I4" s="111"/>
-      <c r="J4" s="112"/>
-      <c r="K4" s="113"/>
+      <c r="D4" s="112"/>
+      <c r="E4" s="112"/>
+      <c r="F4" s="112"/>
+      <c r="G4" s="112"/>
+      <c r="H4" s="112"/>
+      <c r="I4" s="112"/>
+      <c r="J4" s="113"/>
+      <c r="K4" s="114"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -48969,13 +52095,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="114" t="s">
+      <c r="T4" s="115" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="120" t="s">
+      <c r="U4" s="121" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="103" t="s">
+      <c r="V4" s="104" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -49015,10 +52141,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="118" t="s">
+      <c r="J5" s="119" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="119"/>
+      <c r="K5" s="120"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -49026,9 +52152,9 @@
       <c r="Q5" s="98"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="115"/>
-      <c r="U5" s="121"/>
-      <c r="V5" s="104"/>
+      <c r="T5" s="116"/>
+      <c r="U5" s="122"/>
+      <c r="V5" s="105"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -51740,17 +54866,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="107" t="s">
+      <c r="C60" s="108" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="108"/>
-      <c r="E60" s="108"/>
-      <c r="F60" s="108"/>
-      <c r="G60" s="108"/>
-      <c r="H60" s="108"/>
-      <c r="I60" s="108"/>
-      <c r="J60" s="108"/>
-      <c r="K60" s="109"/>
+      <c r="D60" s="109"/>
+      <c r="E60" s="109"/>
+      <c r="F60" s="109"/>
+      <c r="G60" s="109"/>
+      <c r="H60" s="109"/>
+      <c r="I60" s="109"/>
+      <c r="J60" s="109"/>
+      <c r="K60" s="110"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>

--- a/GBDS AUGUST FILES 2026/INVENTORY COUNT SHEET - AUGUST 2026.xlsx
+++ b/GBDS AUGUST FILES 2026/INVENTORY COUNT SHEET - AUGUST 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS AUGUST FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB1D556D-AD9A-4983-92C9-9A4B9FCFC299}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B4B8A19-83EF-435C-970F-950E650EBACA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="7" activeTab="16" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
   </bookViews>
   <sheets>
     <sheet name="SAMPLE" sheetId="32" r:id="rId1"/>
@@ -30022,13 +30022,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
     <mergeCell ref="C60:K60"/>
     <mergeCell ref="I1:U1"/>
     <mergeCell ref="C4:K4"/>
     <mergeCell ref="T4:T5"/>
     <mergeCell ref="U4:U5"/>
-    <mergeCell ref="V4:V5"/>
-    <mergeCell ref="J5:K5"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>

--- a/GBDS AUGUST FILES 2026/INVENTORY COUNT SHEET - AUGUST 2026.xlsx
+++ b/GBDS AUGUST FILES 2026/INVENTORY COUNT SHEET - AUGUST 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS AUGUST FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B4B8A19-83EF-435C-970F-950E650EBACA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F894931-DDD2-4BE0-83DB-DC5650DE07A1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="9" activeTab="18" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
   </bookViews>
   <sheets>
     <sheet name="SAMPLE" sheetId="32" r:id="rId1"/>
@@ -30,6 +30,8 @@
     <sheet name="08-19-2026" sheetId="82" r:id="rId15"/>
     <sheet name="08-20-2026" sheetId="83" r:id="rId16"/>
     <sheet name="08-21-2026" sheetId="84" r:id="rId17"/>
+    <sheet name="08-24-2026" sheetId="85" r:id="rId18"/>
+    <sheet name="08-25-2026" sheetId="86" r:id="rId19"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'08-03-2026'!$A$1:$W$59</definedName>
@@ -48,6 +50,8 @@
     <definedName name="_xlnm.Print_Area" localSheetId="14">'08-19-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="15">'08-20-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="16">'08-21-2026'!$A$1:$W$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="17">'08-24-2026'!$A$1:$W$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="18">'08-25-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">SAMPLE!$A$1:$W$85</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -66,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1428" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1596" uniqueCount="89">
   <si>
     <t>ROUTE 1</t>
   </si>
@@ -328,6 +332,12 @@
   </si>
   <si>
     <t>DATE: 08/21/2026</t>
+  </si>
+  <si>
+    <t>DATE: 08/24/2026</t>
+  </si>
+  <si>
+    <t>DATE: 08/25/2026</t>
   </si>
 </sst>
 </file>
@@ -1314,7 +1324,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="123">
+  <cellXfs count="125">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1600,6 +1610,12 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="63" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2037,21 +2053,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="111" t="s">
+      <c r="I1" s="113" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="111"/>
-      <c r="K1" s="111"/>
-      <c r="L1" s="111"/>
-      <c r="M1" s="111"/>
-      <c r="N1" s="111"/>
-      <c r="O1" s="111"/>
-      <c r="P1" s="111"/>
-      <c r="Q1" s="111"/>
-      <c r="R1" s="111"/>
-      <c r="S1" s="111"/>
-      <c r="T1" s="111"/>
-      <c r="U1" s="111"/>
+      <c r="J1" s="113"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="113"/>
+      <c r="M1" s="113"/>
+      <c r="N1" s="113"/>
+      <c r="O1" s="113"/>
+      <c r="P1" s="113"/>
+      <c r="Q1" s="113"/>
+      <c r="R1" s="113"/>
+      <c r="S1" s="113"/>
+      <c r="T1" s="113"/>
+      <c r="U1" s="113"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -2063,17 +2079,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="112" t="s">
+      <c r="C4" s="114" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="112"/>
-      <c r="E4" s="112"/>
-      <c r="F4" s="112"/>
-      <c r="G4" s="112"/>
-      <c r="H4" s="112"/>
-      <c r="I4" s="112"/>
-      <c r="J4" s="113"/>
-      <c r="K4" s="114"/>
+      <c r="D4" s="114"/>
+      <c r="E4" s="114"/>
+      <c r="F4" s="114"/>
+      <c r="G4" s="114"/>
+      <c r="H4" s="114"/>
+      <c r="I4" s="114"/>
+      <c r="J4" s="115"/>
+      <c r="K4" s="116"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -2093,13 +2109,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="115" t="s">
+      <c r="T4" s="117" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="117" t="s">
+      <c r="U4" s="119" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="104" t="s">
+      <c r="V4" s="106" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -2139,10 +2155,10 @@
       <c r="I5" s="93" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="106" t="s">
+      <c r="J5" s="108" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="107"/>
+      <c r="K5" s="109"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -2150,9 +2166,9 @@
       <c r="Q5" s="89"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="116"/>
-      <c r="U5" s="118"/>
-      <c r="V5" s="105"/>
+      <c r="T5" s="118"/>
+      <c r="U5" s="120"/>
+      <c r="V5" s="107"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -4683,17 +4699,17 @@
       <c r="B62" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C62" s="108" t="s">
+      <c r="C62" s="110" t="s">
         <v>41</v>
       </c>
-      <c r="D62" s="109"/>
-      <c r="E62" s="109"/>
-      <c r="F62" s="109"/>
-      <c r="G62" s="109"/>
-      <c r="H62" s="109"/>
-      <c r="I62" s="109"/>
-      <c r="J62" s="109"/>
-      <c r="K62" s="110"/>
+      <c r="D62" s="111"/>
+      <c r="E62" s="111"/>
+      <c r="F62" s="111"/>
+      <c r="G62" s="111"/>
+      <c r="H62" s="111"/>
+      <c r="I62" s="111"/>
+      <c r="J62" s="111"/>
+      <c r="K62" s="112"/>
       <c r="U62" s="24" t="s">
         <v>51</v>
       </c>
@@ -5002,21 +5018,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="111" t="s">
+      <c r="I1" s="113" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="111"/>
-      <c r="K1" s="111"/>
-      <c r="L1" s="111"/>
-      <c r="M1" s="111"/>
-      <c r="N1" s="111"/>
-      <c r="O1" s="111"/>
-      <c r="P1" s="111"/>
-      <c r="Q1" s="111"/>
-      <c r="R1" s="111"/>
-      <c r="S1" s="111"/>
-      <c r="T1" s="111"/>
-      <c r="U1" s="111"/>
+      <c r="J1" s="113"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="113"/>
+      <c r="M1" s="113"/>
+      <c r="N1" s="113"/>
+      <c r="O1" s="113"/>
+      <c r="P1" s="113"/>
+      <c r="Q1" s="113"/>
+      <c r="R1" s="113"/>
+      <c r="S1" s="113"/>
+      <c r="T1" s="113"/>
+      <c r="U1" s="113"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -5028,17 +5044,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="112" t="s">
+      <c r="C4" s="114" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="112"/>
-      <c r="E4" s="112"/>
-      <c r="F4" s="112"/>
-      <c r="G4" s="112"/>
-      <c r="H4" s="112"/>
-      <c r="I4" s="112"/>
-      <c r="J4" s="113"/>
-      <c r="K4" s="114"/>
+      <c r="D4" s="114"/>
+      <c r="E4" s="114"/>
+      <c r="F4" s="114"/>
+      <c r="G4" s="114"/>
+      <c r="H4" s="114"/>
+      <c r="I4" s="114"/>
+      <c r="J4" s="115"/>
+      <c r="K4" s="116"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -5058,13 +5074,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="115" t="s">
+      <c r="T4" s="117" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="121" t="s">
+      <c r="U4" s="123" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="104" t="s">
+      <c r="V4" s="106" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -5104,10 +5120,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="119" t="s">
+      <c r="J5" s="121" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="120"/>
+      <c r="K5" s="122"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -5115,9 +5131,9 @@
       <c r="Q5" s="99"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="116"/>
-      <c r="U5" s="122"/>
-      <c r="V5" s="105"/>
+      <c r="T5" s="118"/>
+      <c r="U5" s="124"/>
+      <c r="V5" s="107"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -7828,17 +7844,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="108" t="s">
+      <c r="C60" s="110" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="109"/>
-      <c r="E60" s="109"/>
-      <c r="F60" s="109"/>
-      <c r="G60" s="109"/>
-      <c r="H60" s="109"/>
-      <c r="I60" s="109"/>
-      <c r="J60" s="109"/>
-      <c r="K60" s="110"/>
+      <c r="D60" s="111"/>
+      <c r="E60" s="111"/>
+      <c r="F60" s="111"/>
+      <c r="G60" s="111"/>
+      <c r="H60" s="111"/>
+      <c r="I60" s="111"/>
+      <c r="J60" s="111"/>
+      <c r="K60" s="112"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -8147,21 +8163,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="111" t="s">
+      <c r="I1" s="113" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="111"/>
-      <c r="K1" s="111"/>
-      <c r="L1" s="111"/>
-      <c r="M1" s="111"/>
-      <c r="N1" s="111"/>
-      <c r="O1" s="111"/>
-      <c r="P1" s="111"/>
-      <c r="Q1" s="111"/>
-      <c r="R1" s="111"/>
-      <c r="S1" s="111"/>
-      <c r="T1" s="111"/>
-      <c r="U1" s="111"/>
+      <c r="J1" s="113"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="113"/>
+      <c r="M1" s="113"/>
+      <c r="N1" s="113"/>
+      <c r="O1" s="113"/>
+      <c r="P1" s="113"/>
+      <c r="Q1" s="113"/>
+      <c r="R1" s="113"/>
+      <c r="S1" s="113"/>
+      <c r="T1" s="113"/>
+      <c r="U1" s="113"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -8173,17 +8189,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="112" t="s">
+      <c r="C4" s="114" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="112"/>
-      <c r="E4" s="112"/>
-      <c r="F4" s="112"/>
-      <c r="G4" s="112"/>
-      <c r="H4" s="112"/>
-      <c r="I4" s="112"/>
-      <c r="J4" s="113"/>
-      <c r="K4" s="114"/>
+      <c r="D4" s="114"/>
+      <c r="E4" s="114"/>
+      <c r="F4" s="114"/>
+      <c r="G4" s="114"/>
+      <c r="H4" s="114"/>
+      <c r="I4" s="114"/>
+      <c r="J4" s="115"/>
+      <c r="K4" s="116"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -8203,13 +8219,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="115" t="s">
+      <c r="T4" s="117" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="121" t="s">
+      <c r="U4" s="123" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="104" t="s">
+      <c r="V4" s="106" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -8249,10 +8265,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="119" t="s">
+      <c r="J5" s="121" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="120"/>
+      <c r="K5" s="122"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -8260,9 +8276,9 @@
       <c r="Q5" s="99"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="116"/>
-      <c r="U5" s="122"/>
-      <c r="V5" s="105"/>
+      <c r="T5" s="118"/>
+      <c r="U5" s="124"/>
+      <c r="V5" s="107"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -10975,17 +10991,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="108" t="s">
+      <c r="C60" s="110" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="109"/>
-      <c r="E60" s="109"/>
-      <c r="F60" s="109"/>
-      <c r="G60" s="109"/>
-      <c r="H60" s="109"/>
-      <c r="I60" s="109"/>
-      <c r="J60" s="109"/>
-      <c r="K60" s="110"/>
+      <c r="D60" s="111"/>
+      <c r="E60" s="111"/>
+      <c r="F60" s="111"/>
+      <c r="G60" s="111"/>
+      <c r="H60" s="111"/>
+      <c r="I60" s="111"/>
+      <c r="J60" s="111"/>
+      <c r="K60" s="112"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -11294,21 +11310,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="111" t="s">
+      <c r="I1" s="113" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="111"/>
-      <c r="K1" s="111"/>
-      <c r="L1" s="111"/>
-      <c r="M1" s="111"/>
-      <c r="N1" s="111"/>
-      <c r="O1" s="111"/>
-      <c r="P1" s="111"/>
-      <c r="Q1" s="111"/>
-      <c r="R1" s="111"/>
-      <c r="S1" s="111"/>
-      <c r="T1" s="111"/>
-      <c r="U1" s="111"/>
+      <c r="J1" s="113"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="113"/>
+      <c r="M1" s="113"/>
+      <c r="N1" s="113"/>
+      <c r="O1" s="113"/>
+      <c r="P1" s="113"/>
+      <c r="Q1" s="113"/>
+      <c r="R1" s="113"/>
+      <c r="S1" s="113"/>
+      <c r="T1" s="113"/>
+      <c r="U1" s="113"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -11320,17 +11336,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="112" t="s">
+      <c r="C4" s="114" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="112"/>
-      <c r="E4" s="112"/>
-      <c r="F4" s="112"/>
-      <c r="G4" s="112"/>
-      <c r="H4" s="112"/>
-      <c r="I4" s="112"/>
-      <c r="J4" s="113"/>
-      <c r="K4" s="114"/>
+      <c r="D4" s="114"/>
+      <c r="E4" s="114"/>
+      <c r="F4" s="114"/>
+      <c r="G4" s="114"/>
+      <c r="H4" s="114"/>
+      <c r="I4" s="114"/>
+      <c r="J4" s="115"/>
+      <c r="K4" s="116"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -11350,13 +11366,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="115" t="s">
+      <c r="T4" s="117" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="121" t="s">
+      <c r="U4" s="123" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="104" t="s">
+      <c r="V4" s="106" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -11396,10 +11412,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="119" t="s">
+      <c r="J5" s="121" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="120"/>
+      <c r="K5" s="122"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -11407,9 +11423,9 @@
       <c r="Q5" s="99"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="116"/>
-      <c r="U5" s="122"/>
-      <c r="V5" s="105"/>
+      <c r="T5" s="118"/>
+      <c r="U5" s="124"/>
+      <c r="V5" s="107"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -14111,17 +14127,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="108" t="s">
+      <c r="C60" s="110" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="109"/>
-      <c r="E60" s="109"/>
-      <c r="F60" s="109"/>
-      <c r="G60" s="109"/>
-      <c r="H60" s="109"/>
-      <c r="I60" s="109"/>
-      <c r="J60" s="109"/>
-      <c r="K60" s="110"/>
+      <c r="D60" s="111"/>
+      <c r="E60" s="111"/>
+      <c r="F60" s="111"/>
+      <c r="G60" s="111"/>
+      <c r="H60" s="111"/>
+      <c r="I60" s="111"/>
+      <c r="J60" s="111"/>
+      <c r="K60" s="112"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -14430,21 +14446,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="111" t="s">
+      <c r="I1" s="113" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="111"/>
-      <c r="K1" s="111"/>
-      <c r="L1" s="111"/>
-      <c r="M1" s="111"/>
-      <c r="N1" s="111"/>
-      <c r="O1" s="111"/>
-      <c r="P1" s="111"/>
-      <c r="Q1" s="111"/>
-      <c r="R1" s="111"/>
-      <c r="S1" s="111"/>
-      <c r="T1" s="111"/>
-      <c r="U1" s="111"/>
+      <c r="J1" s="113"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="113"/>
+      <c r="M1" s="113"/>
+      <c r="N1" s="113"/>
+      <c r="O1" s="113"/>
+      <c r="P1" s="113"/>
+      <c r="Q1" s="113"/>
+      <c r="R1" s="113"/>
+      <c r="S1" s="113"/>
+      <c r="T1" s="113"/>
+      <c r="U1" s="113"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -14456,17 +14472,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="112" t="s">
+      <c r="C4" s="114" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="112"/>
-      <c r="E4" s="112"/>
-      <c r="F4" s="112"/>
-      <c r="G4" s="112"/>
-      <c r="H4" s="112"/>
-      <c r="I4" s="112"/>
-      <c r="J4" s="113"/>
-      <c r="K4" s="114"/>
+      <c r="D4" s="114"/>
+      <c r="E4" s="114"/>
+      <c r="F4" s="114"/>
+      <c r="G4" s="114"/>
+      <c r="H4" s="114"/>
+      <c r="I4" s="114"/>
+      <c r="J4" s="115"/>
+      <c r="K4" s="116"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -14486,13 +14502,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="115" t="s">
+      <c r="T4" s="117" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="121" t="s">
+      <c r="U4" s="123" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="104" t="s">
+      <c r="V4" s="106" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -14532,10 +14548,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="119" t="s">
+      <c r="J5" s="121" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="120"/>
+      <c r="K5" s="122"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -14543,9 +14559,9 @@
       <c r="Q5" s="99"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="116"/>
-      <c r="U5" s="122"/>
-      <c r="V5" s="105"/>
+      <c r="T5" s="118"/>
+      <c r="U5" s="124"/>
+      <c r="V5" s="107"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -17246,17 +17262,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="108" t="s">
+      <c r="C60" s="110" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="109"/>
-      <c r="E60" s="109"/>
-      <c r="F60" s="109"/>
-      <c r="G60" s="109"/>
-      <c r="H60" s="109"/>
-      <c r="I60" s="109"/>
-      <c r="J60" s="109"/>
-      <c r="K60" s="110"/>
+      <c r="D60" s="111"/>
+      <c r="E60" s="111"/>
+      <c r="F60" s="111"/>
+      <c r="G60" s="111"/>
+      <c r="H60" s="111"/>
+      <c r="I60" s="111"/>
+      <c r="J60" s="111"/>
+      <c r="K60" s="112"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -17565,21 +17581,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="111" t="s">
+      <c r="I1" s="113" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="111"/>
-      <c r="K1" s="111"/>
-      <c r="L1" s="111"/>
-      <c r="M1" s="111"/>
-      <c r="N1" s="111"/>
-      <c r="O1" s="111"/>
-      <c r="P1" s="111"/>
-      <c r="Q1" s="111"/>
-      <c r="R1" s="111"/>
-      <c r="S1" s="111"/>
-      <c r="T1" s="111"/>
-      <c r="U1" s="111"/>
+      <c r="J1" s="113"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="113"/>
+      <c r="M1" s="113"/>
+      <c r="N1" s="113"/>
+      <c r="O1" s="113"/>
+      <c r="P1" s="113"/>
+      <c r="Q1" s="113"/>
+      <c r="R1" s="113"/>
+      <c r="S1" s="113"/>
+      <c r="T1" s="113"/>
+      <c r="U1" s="113"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -17591,17 +17607,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="112" t="s">
+      <c r="C4" s="114" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="112"/>
-      <c r="E4" s="112"/>
-      <c r="F4" s="112"/>
-      <c r="G4" s="112"/>
-      <c r="H4" s="112"/>
-      <c r="I4" s="112"/>
-      <c r="J4" s="113"/>
-      <c r="K4" s="114"/>
+      <c r="D4" s="114"/>
+      <c r="E4" s="114"/>
+      <c r="F4" s="114"/>
+      <c r="G4" s="114"/>
+      <c r="H4" s="114"/>
+      <c r="I4" s="114"/>
+      <c r="J4" s="115"/>
+      <c r="K4" s="116"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -17621,13 +17637,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="115" t="s">
+      <c r="T4" s="117" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="121" t="s">
+      <c r="U4" s="123" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="104" t="s">
+      <c r="V4" s="106" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -17667,10 +17683,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="119" t="s">
+      <c r="J5" s="121" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="120"/>
+      <c r="K5" s="122"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -17678,9 +17694,9 @@
       <c r="Q5" s="100"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="116"/>
-      <c r="U5" s="122"/>
-      <c r="V5" s="105"/>
+      <c r="T5" s="118"/>
+      <c r="U5" s="124"/>
+      <c r="V5" s="107"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -20375,17 +20391,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="108" t="s">
+      <c r="C60" s="110" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="109"/>
-      <c r="E60" s="109"/>
-      <c r="F60" s="109"/>
-      <c r="G60" s="109"/>
-      <c r="H60" s="109"/>
-      <c r="I60" s="109"/>
-      <c r="J60" s="109"/>
-      <c r="K60" s="110"/>
+      <c r="D60" s="111"/>
+      <c r="E60" s="111"/>
+      <c r="F60" s="111"/>
+      <c r="G60" s="111"/>
+      <c r="H60" s="111"/>
+      <c r="I60" s="111"/>
+      <c r="J60" s="111"/>
+      <c r="K60" s="112"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -20694,21 +20710,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="111" t="s">
+      <c r="I1" s="113" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="111"/>
-      <c r="K1" s="111"/>
-      <c r="L1" s="111"/>
-      <c r="M1" s="111"/>
-      <c r="N1" s="111"/>
-      <c r="O1" s="111"/>
-      <c r="P1" s="111"/>
-      <c r="Q1" s="111"/>
-      <c r="R1" s="111"/>
-      <c r="S1" s="111"/>
-      <c r="T1" s="111"/>
-      <c r="U1" s="111"/>
+      <c r="J1" s="113"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="113"/>
+      <c r="M1" s="113"/>
+      <c r="N1" s="113"/>
+      <c r="O1" s="113"/>
+      <c r="P1" s="113"/>
+      <c r="Q1" s="113"/>
+      <c r="R1" s="113"/>
+      <c r="S1" s="113"/>
+      <c r="T1" s="113"/>
+      <c r="U1" s="113"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -20720,17 +20736,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="112" t="s">
+      <c r="C4" s="114" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="112"/>
-      <c r="E4" s="112"/>
-      <c r="F4" s="112"/>
-      <c r="G4" s="112"/>
-      <c r="H4" s="112"/>
-      <c r="I4" s="112"/>
-      <c r="J4" s="113"/>
-      <c r="K4" s="114"/>
+      <c r="D4" s="114"/>
+      <c r="E4" s="114"/>
+      <c r="F4" s="114"/>
+      <c r="G4" s="114"/>
+      <c r="H4" s="114"/>
+      <c r="I4" s="114"/>
+      <c r="J4" s="115"/>
+      <c r="K4" s="116"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -20750,13 +20766,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="115" t="s">
+      <c r="T4" s="117" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="121" t="s">
+      <c r="U4" s="123" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="104" t="s">
+      <c r="V4" s="106" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -20796,10 +20812,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="119" t="s">
+      <c r="J5" s="121" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="120"/>
+      <c r="K5" s="122"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -20807,9 +20823,9 @@
       <c r="Q5" s="101"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="116"/>
-      <c r="U5" s="122"/>
-      <c r="V5" s="105"/>
+      <c r="T5" s="118"/>
+      <c r="U5" s="124"/>
+      <c r="V5" s="107"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -23500,17 +23516,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="108" t="s">
+      <c r="C60" s="110" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="109"/>
-      <c r="E60" s="109"/>
-      <c r="F60" s="109"/>
-      <c r="G60" s="109"/>
-      <c r="H60" s="109"/>
-      <c r="I60" s="109"/>
-      <c r="J60" s="109"/>
-      <c r="K60" s="110"/>
+      <c r="D60" s="111"/>
+      <c r="E60" s="111"/>
+      <c r="F60" s="111"/>
+      <c r="G60" s="111"/>
+      <c r="H60" s="111"/>
+      <c r="I60" s="111"/>
+      <c r="J60" s="111"/>
+      <c r="K60" s="112"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -23819,21 +23835,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="111" t="s">
+      <c r="I1" s="113" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="111"/>
-      <c r="K1" s="111"/>
-      <c r="L1" s="111"/>
-      <c r="M1" s="111"/>
-      <c r="N1" s="111"/>
-      <c r="O1" s="111"/>
-      <c r="P1" s="111"/>
-      <c r="Q1" s="111"/>
-      <c r="R1" s="111"/>
-      <c r="S1" s="111"/>
-      <c r="T1" s="111"/>
-      <c r="U1" s="111"/>
+      <c r="J1" s="113"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="113"/>
+      <c r="M1" s="113"/>
+      <c r="N1" s="113"/>
+      <c r="O1" s="113"/>
+      <c r="P1" s="113"/>
+      <c r="Q1" s="113"/>
+      <c r="R1" s="113"/>
+      <c r="S1" s="113"/>
+      <c r="T1" s="113"/>
+      <c r="U1" s="113"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -23845,17 +23861,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="112" t="s">
+      <c r="C4" s="114" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="112"/>
-      <c r="E4" s="112"/>
-      <c r="F4" s="112"/>
-      <c r="G4" s="112"/>
-      <c r="H4" s="112"/>
-      <c r="I4" s="112"/>
-      <c r="J4" s="113"/>
-      <c r="K4" s="114"/>
+      <c r="D4" s="114"/>
+      <c r="E4" s="114"/>
+      <c r="F4" s="114"/>
+      <c r="G4" s="114"/>
+      <c r="H4" s="114"/>
+      <c r="I4" s="114"/>
+      <c r="J4" s="115"/>
+      <c r="K4" s="116"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -23875,13 +23891,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="115" t="s">
+      <c r="T4" s="117" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="121" t="s">
+      <c r="U4" s="123" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="104" t="s">
+      <c r="V4" s="106" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -23921,10 +23937,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="119" t="s">
+      <c r="J5" s="121" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="120"/>
+      <c r="K5" s="122"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -23932,9 +23948,9 @@
       <c r="Q5" s="102"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="116"/>
-      <c r="U5" s="122"/>
-      <c r="V5" s="105"/>
+      <c r="T5" s="118"/>
+      <c r="U5" s="124"/>
+      <c r="V5" s="107"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -26642,17 +26658,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="108" t="s">
+      <c r="C60" s="110" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="109"/>
-      <c r="E60" s="109"/>
-      <c r="F60" s="109"/>
-      <c r="G60" s="109"/>
-      <c r="H60" s="109"/>
-      <c r="I60" s="109"/>
-      <c r="J60" s="109"/>
-      <c r="K60" s="110"/>
+      <c r="D60" s="111"/>
+      <c r="E60" s="111"/>
+      <c r="F60" s="111"/>
+      <c r="G60" s="111"/>
+      <c r="H60" s="111"/>
+      <c r="I60" s="111"/>
+      <c r="J60" s="111"/>
+      <c r="K60" s="112"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -26961,21 +26977,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="111" t="s">
+      <c r="I1" s="113" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="111"/>
-      <c r="K1" s="111"/>
-      <c r="L1" s="111"/>
-      <c r="M1" s="111"/>
-      <c r="N1" s="111"/>
-      <c r="O1" s="111"/>
-      <c r="P1" s="111"/>
-      <c r="Q1" s="111"/>
-      <c r="R1" s="111"/>
-      <c r="S1" s="111"/>
-      <c r="T1" s="111"/>
-      <c r="U1" s="111"/>
+      <c r="J1" s="113"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="113"/>
+      <c r="M1" s="113"/>
+      <c r="N1" s="113"/>
+      <c r="O1" s="113"/>
+      <c r="P1" s="113"/>
+      <c r="Q1" s="113"/>
+      <c r="R1" s="113"/>
+      <c r="S1" s="113"/>
+      <c r="T1" s="113"/>
+      <c r="U1" s="113"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -26987,17 +27003,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="112" t="s">
+      <c r="C4" s="114" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="112"/>
-      <c r="E4" s="112"/>
-      <c r="F4" s="112"/>
-      <c r="G4" s="112"/>
-      <c r="H4" s="112"/>
-      <c r="I4" s="112"/>
-      <c r="J4" s="113"/>
-      <c r="K4" s="114"/>
+      <c r="D4" s="114"/>
+      <c r="E4" s="114"/>
+      <c r="F4" s="114"/>
+      <c r="G4" s="114"/>
+      <c r="H4" s="114"/>
+      <c r="I4" s="114"/>
+      <c r="J4" s="115"/>
+      <c r="K4" s="116"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -27017,13 +27033,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="115" t="s">
+      <c r="T4" s="117" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="121" t="s">
+      <c r="U4" s="123" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="104" t="s">
+      <c r="V4" s="106" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -27063,10 +27079,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="119" t="s">
+      <c r="J5" s="121" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="120"/>
+      <c r="K5" s="122"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -27074,9 +27090,9 @@
       <c r="Q5" s="103"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="116"/>
-      <c r="U5" s="122"/>
-      <c r="V5" s="105"/>
+      <c r="T5" s="118"/>
+      <c r="U5" s="124"/>
+      <c r="V5" s="107"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -29760,17 +29776,6246 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="108" t="s">
+      <c r="C60" s="110" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="109"/>
-      <c r="E60" s="109"/>
-      <c r="F60" s="109"/>
-      <c r="G60" s="109"/>
-      <c r="H60" s="109"/>
-      <c r="I60" s="109"/>
-      <c r="J60" s="109"/>
-      <c r="K60" s="110"/>
+      <c r="D60" s="111"/>
+      <c r="E60" s="111"/>
+      <c r="F60" s="111"/>
+      <c r="G60" s="111"/>
+      <c r="H60" s="111"/>
+      <c r="I60" s="111"/>
+      <c r="J60" s="111"/>
+      <c r="K60" s="112"/>
+      <c r="U60" s="24" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B61" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="C61" s="19"/>
+      <c r="D61" s="19"/>
+      <c r="E61" s="19"/>
+      <c r="F61" s="19"/>
+      <c r="G61" s="19"/>
+      <c r="H61" s="19"/>
+      <c r="I61" s="19"/>
+      <c r="J61" s="45"/>
+      <c r="K61" s="20"/>
+      <c r="U61" s="7"/>
+    </row>
+    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B62" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+      <c r="J62" s="44"/>
+      <c r="K62" s="21"/>
+      <c r="U62" s="3"/>
+    </row>
+    <row r="63" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B63" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C63" s="22"/>
+      <c r="D63" s="22"/>
+      <c r="E63" s="22"/>
+      <c r="F63" s="22"/>
+      <c r="G63" s="22"/>
+      <c r="H63" s="22"/>
+      <c r="I63" s="22"/>
+      <c r="J63" s="46"/>
+      <c r="K63" s="23"/>
+      <c r="U63" s="8"/>
+    </row>
+    <row r="64" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B65" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="C65" s="19"/>
+      <c r="D65" s="19"/>
+      <c r="E65" s="19"/>
+      <c r="F65" s="19"/>
+      <c r="G65" s="19"/>
+      <c r="H65" s="19"/>
+      <c r="I65" s="19"/>
+      <c r="J65" s="45"/>
+      <c r="K65" s="20"/>
+      <c r="U65" s="7"/>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B66" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C66" s="1"/>
+      <c r="D66" s="1"/>
+      <c r="E66" s="1"/>
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="J66" s="44"/>
+      <c r="K66" s="21"/>
+      <c r="U66" s="3"/>
+    </row>
+    <row r="67" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B67" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C67" s="22"/>
+      <c r="D67" s="22"/>
+      <c r="E67" s="22"/>
+      <c r="F67" s="22"/>
+      <c r="G67" s="22"/>
+      <c r="H67" s="22"/>
+      <c r="I67" s="22"/>
+      <c r="J67" s="46"/>
+      <c r="K67" s="23"/>
+      <c r="U67" s="8"/>
+    </row>
+    <row r="68" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B69" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="C69" s="19"/>
+      <c r="D69" s="19"/>
+      <c r="E69" s="19"/>
+      <c r="F69" s="19"/>
+      <c r="G69" s="19"/>
+      <c r="H69" s="19"/>
+      <c r="I69" s="19"/>
+      <c r="J69" s="45"/>
+      <c r="K69" s="20"/>
+      <c r="U69" s="7"/>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B70" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="J70" s="44"/>
+      <c r="K70" s="21"/>
+      <c r="U70" s="3"/>
+    </row>
+    <row r="71" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B71" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C71" s="22"/>
+      <c r="D71" s="22"/>
+      <c r="E71" s="22"/>
+      <c r="F71" s="22"/>
+      <c r="G71" s="22"/>
+      <c r="H71" s="22"/>
+      <c r="I71" s="22"/>
+      <c r="J71" s="46"/>
+      <c r="K71" s="23"/>
+      <c r="U71" s="8"/>
+    </row>
+    <row r="72" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B73" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="C73" s="19"/>
+      <c r="D73" s="19"/>
+      <c r="E73" s="19"/>
+      <c r="F73" s="19"/>
+      <c r="G73" s="19"/>
+      <c r="H73" s="19"/>
+      <c r="I73" s="19"/>
+      <c r="J73" s="45"/>
+      <c r="K73" s="20"/>
+      <c r="U73" s="7"/>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B74" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C74" s="1"/>
+      <c r="D74" s="1"/>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1"/>
+      <c r="J74" s="44"/>
+      <c r="K74" s="21"/>
+      <c r="U74" s="3"/>
+    </row>
+    <row r="75" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B75" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C75" s="22"/>
+      <c r="D75" s="22"/>
+      <c r="E75" s="22"/>
+      <c r="F75" s="22"/>
+      <c r="G75" s="22"/>
+      <c r="H75" s="22"/>
+      <c r="I75" s="22"/>
+      <c r="J75" s="46"/>
+      <c r="K75" s="23"/>
+      <c r="U75" s="8"/>
+    </row>
+    <row r="76" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B77" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="C77" s="19"/>
+      <c r="D77" s="19"/>
+      <c r="E77" s="19"/>
+      <c r="F77" s="19"/>
+      <c r="G77" s="19"/>
+      <c r="H77" s="19"/>
+      <c r="I77" s="19"/>
+      <c r="J77" s="45"/>
+      <c r="K77" s="20"/>
+      <c r="U77" s="7"/>
+    </row>
+    <row r="78" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B78" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C78" s="1"/>
+      <c r="D78" s="1"/>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+      <c r="J78" s="44"/>
+      <c r="K78" s="21"/>
+      <c r="U78" s="3"/>
+    </row>
+    <row r="79" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B79" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C79" s="22"/>
+      <c r="D79" s="22"/>
+      <c r="E79" s="22"/>
+      <c r="F79" s="22"/>
+      <c r="G79" s="22"/>
+      <c r="H79" s="22"/>
+      <c r="I79" s="22"/>
+      <c r="J79" s="46"/>
+      <c r="K79" s="23"/>
+      <c r="U79" s="8"/>
+    </row>
+    <row r="80" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="81" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B81" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="C81" s="17"/>
+      <c r="D81" s="17"/>
+      <c r="E81" s="17"/>
+      <c r="F81" s="17"/>
+      <c r="G81" s="17"/>
+      <c r="H81" s="17"/>
+      <c r="I81" s="17"/>
+      <c r="J81" s="47"/>
+      <c r="K81" s="18"/>
+      <c r="U81" s="16"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="C60:K60"/>
+    <mergeCell ref="I1:U1"/>
+    <mergeCell ref="C4:K4"/>
+    <mergeCell ref="T4:T5"/>
+    <mergeCell ref="U4:U5"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
+  <pageSetup paperSize="14" scale="70" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="24" max="80" man="1"/>
+  </colBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98135CE8-2A84-40FE-B7B5-D26F7437D5B3}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BB81"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="28" customWidth="1"/>
+    <col min="3" max="6" width="10" style="9" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" style="9" customWidth="1"/>
+    <col min="8" max="8" width="7.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.85546875" style="9" customWidth="1"/>
+    <col min="11" max="11" width="7.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.42578125" style="9" customWidth="1"/>
+    <col min="13" max="13" width="10" style="9" customWidth="1"/>
+    <col min="14" max="14" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" style="9" customWidth="1"/>
+    <col min="16" max="16" width="5.5703125" style="9" customWidth="1"/>
+    <col min="17" max="17" width="10" style="9" customWidth="1"/>
+    <col min="18" max="18" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="1.42578125" style="9" customWidth="1"/>
+    <col min="20" max="20" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="9" customWidth="1"/>
+    <col min="22" max="22" width="19.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="23" max="49" width="7.28515625" style="9" customWidth="1"/>
+    <col min="50" max="50" width="1.5703125" style="9" customWidth="1"/>
+    <col min="51" max="51" width="9.42578125" style="9" customWidth="1"/>
+    <col min="52" max="52" width="1.28515625" style="9" customWidth="1"/>
+    <col min="53" max="53" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="10.28515625" style="9" bestFit="1" customWidth="1"/>
+    <col min="55" max="16384" width="9.140625" style="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="113" t="s">
+        <v>43</v>
+      </c>
+      <c r="J1" s="113"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="113"/>
+      <c r="M1" s="113"/>
+      <c r="N1" s="113"/>
+      <c r="O1" s="113"/>
+      <c r="P1" s="113"/>
+      <c r="Q1" s="113"/>
+      <c r="R1" s="113"/>
+      <c r="S1" s="113"/>
+      <c r="T1" s="113"/>
+      <c r="U1" s="113"/>
+    </row>
+    <row r="2" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="B2" s="28" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B4" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="114" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="114"/>
+      <c r="E4" s="114"/>
+      <c r="F4" s="114"/>
+      <c r="G4" s="114"/>
+      <c r="H4" s="114"/>
+      <c r="I4" s="114"/>
+      <c r="J4" s="115"/>
+      <c r="K4" s="116"/>
+      <c r="M4" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="N4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="O4" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="P4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q4" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="R4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="S4" s="9"/>
+      <c r="T4" s="117" t="s">
+        <v>68</v>
+      </c>
+      <c r="U4" s="123" t="s">
+        <v>67</v>
+      </c>
+      <c r="V4" s="106" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF4" s="11"/>
+      <c r="AG4" s="11"/>
+      <c r="AH4" s="11"/>
+      <c r="AI4" s="11"/>
+      <c r="AJ4" s="11"/>
+      <c r="AK4" s="11"/>
+      <c r="AL4" s="11"/>
+      <c r="AM4" s="11"/>
+      <c r="AN4" s="11"/>
+      <c r="AO4" s="11"/>
+      <c r="AP4" s="11"/>
+      <c r="AQ4" s="11"/>
+      <c r="AR4" s="11"/>
+      <c r="AS4" s="11"/>
+      <c r="AT4" s="11"/>
+      <c r="AU4" s="11"/>
+      <c r="AV4" s="11"/>
+      <c r="AW4" s="11"/>
+      <c r="AX4" s="11"/>
+      <c r="AY4" s="11"/>
+      <c r="AZ4" s="11"/>
+      <c r="BA4" s="11"/>
+      <c r="BB4" s="11"/>
+    </row>
+    <row r="5" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="37"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40" t="s">
+        <v>64</v>
+      </c>
+      <c r="I5" s="40" t="s">
+        <v>60</v>
+      </c>
+      <c r="J5" s="121" t="s">
+        <v>65</v>
+      </c>
+      <c r="K5" s="122"/>
+      <c r="M5" s="37"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="40"/>
+      <c r="P5" s="104"/>
+      <c r="Q5" s="104"/>
+      <c r="R5" s="38"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="118"/>
+      <c r="U5" s="124"/>
+      <c r="V5" s="107"/>
+      <c r="AF5" s="11"/>
+      <c r="AG5" s="11"/>
+      <c r="AH5" s="11"/>
+      <c r="AI5" s="11"/>
+      <c r="AJ5" s="11"/>
+      <c r="AK5" s="11"/>
+      <c r="AL5" s="11"/>
+      <c r="AM5" s="11"/>
+      <c r="AN5" s="11"/>
+      <c r="AO5" s="11"/>
+      <c r="AP5" s="11"/>
+      <c r="AQ5" s="11"/>
+      <c r="AR5" s="11"/>
+      <c r="AS5" s="11"/>
+      <c r="AT5" s="11"/>
+      <c r="AU5" s="11"/>
+      <c r="AV5" s="11"/>
+      <c r="AW5" s="11"/>
+      <c r="AX5" s="11"/>
+      <c r="AY5" s="11"/>
+      <c r="AZ5" s="11"/>
+      <c r="BA5" s="11"/>
+      <c r="BB5" s="11"/>
+    </row>
+    <row r="6" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="37"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="104"/>
+      <c r="K6" s="38"/>
+      <c r="M6" s="37"/>
+      <c r="N6" s="49"/>
+      <c r="O6" s="40"/>
+      <c r="P6" s="104"/>
+      <c r="Q6" s="104"/>
+      <c r="R6" s="38"/>
+      <c r="S6" s="9"/>
+      <c r="T6" s="39"/>
+      <c r="U6" s="39"/>
+      <c r="V6" s="39"/>
+      <c r="AF6" s="11"/>
+      <c r="AG6" s="11"/>
+      <c r="AH6" s="11"/>
+      <c r="AI6" s="11"/>
+      <c r="AJ6" s="11"/>
+      <c r="AK6" s="11"/>
+      <c r="AL6" s="11"/>
+      <c r="AM6" s="11"/>
+      <c r="AN6" s="11"/>
+      <c r="AO6" s="11"/>
+      <c r="AP6" s="11"/>
+      <c r="AQ6" s="11"/>
+      <c r="AR6" s="11"/>
+      <c r="AS6" s="11"/>
+      <c r="AT6" s="11"/>
+      <c r="AU6" s="11"/>
+      <c r="AV6" s="11"/>
+      <c r="AW6" s="11"/>
+      <c r="AX6" s="11"/>
+      <c r="AY6" s="11"/>
+      <c r="AZ6" s="11"/>
+      <c r="BA6" s="11"/>
+      <c r="BB6" s="11"/>
+    </row>
+    <row r="7" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A7" s="27">
+        <v>1</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="52">
+        <v>30</v>
+      </c>
+      <c r="D7" s="52"/>
+      <c r="E7" s="52"/>
+      <c r="F7" s="52"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="52"/>
+      <c r="I7" s="52">
+        <v>3</v>
+      </c>
+      <c r="J7" s="53"/>
+      <c r="K7" s="54">
+        <v>6</v>
+      </c>
+      <c r="L7" s="55"/>
+      <c r="M7" s="56"/>
+      <c r="N7" s="57"/>
+      <c r="O7" s="52">
+        <v>1</v>
+      </c>
+      <c r="P7" s="53"/>
+      <c r="Q7" s="53"/>
+      <c r="R7" s="54"/>
+      <c r="S7" s="55"/>
+      <c r="T7" s="58">
+        <f>H7+I7+J7+K7+N7+P7+R7</f>
+        <v>9</v>
+      </c>
+      <c r="U7" s="58">
+        <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
+        <v>753</v>
+      </c>
+      <c r="V7" s="58">
+        <f>U7/24</f>
+        <v>31.375</v>
+      </c>
+      <c r="W7" s="50"/>
+      <c r="AF7" s="12"/>
+      <c r="AG7" s="12"/>
+      <c r="AH7" s="12"/>
+      <c r="AI7" s="12"/>
+      <c r="AJ7" s="12"/>
+      <c r="AK7" s="12"/>
+      <c r="AL7" s="12"/>
+      <c r="AM7" s="12"/>
+      <c r="AN7" s="12"/>
+      <c r="AO7" s="12"/>
+      <c r="AP7" s="12"/>
+      <c r="AQ7" s="12"/>
+      <c r="AR7" s="12"/>
+      <c r="AS7" s="12"/>
+      <c r="AT7" s="12"/>
+      <c r="AU7" s="12"/>
+      <c r="AV7" s="12"/>
+      <c r="AW7" s="12"/>
+      <c r="AX7" s="12"/>
+      <c r="AY7" s="12"/>
+      <c r="AZ7" s="12"/>
+      <c r="BA7" s="12"/>
+      <c r="BB7" s="12"/>
+    </row>
+    <row r="8" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="27">
+        <f>A7+1</f>
+        <v>2</v>
+      </c>
+      <c r="B8" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="59">
+        <f>37+30</f>
+        <v>67</v>
+      </c>
+      <c r="D8" s="59"/>
+      <c r="E8" s="59"/>
+      <c r="F8" s="59"/>
+      <c r="G8" s="59"/>
+      <c r="H8" s="59"/>
+      <c r="I8" s="59"/>
+      <c r="J8" s="60"/>
+      <c r="K8" s="61"/>
+      <c r="L8" s="62"/>
+      <c r="M8" s="63">
+        <v>1</v>
+      </c>
+      <c r="N8" s="64"/>
+      <c r="O8" s="65">
+        <v>1</v>
+      </c>
+      <c r="P8" s="66">
+        <v>12</v>
+      </c>
+      <c r="Q8" s="66">
+        <v>2</v>
+      </c>
+      <c r="R8" s="67"/>
+      <c r="S8" s="62"/>
+      <c r="T8" s="68">
+        <f t="shared" ref="T8:T41" si="0">H8+I8+J8+K8+N8+P8+R8</f>
+        <v>12</v>
+      </c>
+      <c r="U8" s="69">
+        <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
+        <v>1716</v>
+      </c>
+      <c r="V8" s="69">
+        <f>U8/24</f>
+        <v>71.5</v>
+      </c>
+      <c r="W8" s="50"/>
+      <c r="AF8" s="12"/>
+      <c r="AG8" s="12"/>
+      <c r="AH8" s="12"/>
+      <c r="AI8" s="12"/>
+      <c r="AJ8" s="12"/>
+      <c r="AK8" s="12"/>
+      <c r="AL8" s="12"/>
+      <c r="AM8" s="12"/>
+      <c r="AN8" s="12"/>
+      <c r="AO8" s="12"/>
+      <c r="AP8" s="12"/>
+      <c r="AQ8" s="12"/>
+      <c r="AR8" s="12"/>
+      <c r="AS8" s="12"/>
+      <c r="AT8" s="12"/>
+      <c r="AU8" s="12"/>
+      <c r="AV8" s="12"/>
+      <c r="AW8" s="12"/>
+      <c r="AX8" s="12"/>
+      <c r="AY8" s="12"/>
+      <c r="AZ8" s="12"/>
+      <c r="BA8" s="12"/>
+      <c r="BB8" s="12"/>
+    </row>
+    <row r="9" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A9" s="27">
+        <f t="shared" ref="A9:A57" si="1">A8+1</f>
+        <v>3</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="70">
+        <f>26+30</f>
+        <v>56</v>
+      </c>
+      <c r="D9" s="70"/>
+      <c r="E9" s="70"/>
+      <c r="F9" s="70"/>
+      <c r="G9" s="70"/>
+      <c r="H9" s="70"/>
+      <c r="I9" s="70"/>
+      <c r="J9" s="71"/>
+      <c r="K9" s="72"/>
+      <c r="L9" s="55"/>
+      <c r="M9" s="73"/>
+      <c r="N9" s="74"/>
+      <c r="O9" s="70"/>
+      <c r="P9" s="71"/>
+      <c r="Q9" s="71"/>
+      <c r="R9" s="72"/>
+      <c r="S9" s="55"/>
+      <c r="T9" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U9" s="76">
+        <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
+        <v>1344</v>
+      </c>
+      <c r="V9" s="76">
+        <f t="shared" ref="V9:V11" si="3">U9/24</f>
+        <v>56</v>
+      </c>
+      <c r="W9" s="50"/>
+      <c r="AF9" s="12"/>
+      <c r="AG9" s="12"/>
+      <c r="AH9" s="12"/>
+      <c r="AI9" s="12"/>
+      <c r="AJ9" s="12"/>
+      <c r="AK9" s="12"/>
+      <c r="AL9" s="12"/>
+      <c r="AM9" s="12"/>
+      <c r="AN9" s="12"/>
+      <c r="AO9" s="12"/>
+      <c r="AP9" s="12"/>
+      <c r="AQ9" s="12"/>
+      <c r="AR9" s="12"/>
+      <c r="AS9" s="12"/>
+      <c r="AT9" s="12"/>
+      <c r="AU9" s="12"/>
+      <c r="AV9" s="12"/>
+      <c r="AW9" s="12"/>
+      <c r="AX9" s="12"/>
+      <c r="AY9" s="12"/>
+      <c r="AZ9" s="12"/>
+      <c r="BA9" s="12"/>
+      <c r="BB9" s="12"/>
+    </row>
+    <row r="10" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A10" s="27">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="70">
+        <f>5+10</f>
+        <v>15</v>
+      </c>
+      <c r="D10" s="70"/>
+      <c r="E10" s="70"/>
+      <c r="F10" s="70"/>
+      <c r="G10" s="70"/>
+      <c r="H10" s="70"/>
+      <c r="I10" s="70"/>
+      <c r="J10" s="71"/>
+      <c r="K10" s="72"/>
+      <c r="L10" s="55"/>
+      <c r="M10" s="73"/>
+      <c r="N10" s="74"/>
+      <c r="O10" s="70"/>
+      <c r="P10" s="71"/>
+      <c r="Q10" s="71"/>
+      <c r="R10" s="72"/>
+      <c r="S10" s="55"/>
+      <c r="T10" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U10" s="58">
+        <f t="shared" si="2"/>
+        <v>360</v>
+      </c>
+      <c r="V10" s="58">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="W10" s="50"/>
+      <c r="AF10" s="12"/>
+      <c r="AG10" s="12"/>
+      <c r="AH10" s="12"/>
+      <c r="AI10" s="12"/>
+      <c r="AJ10" s="12"/>
+      <c r="AK10" s="12"/>
+      <c r="AL10" s="12"/>
+      <c r="AM10" s="12"/>
+      <c r="AN10" s="12"/>
+      <c r="AO10" s="12"/>
+      <c r="AP10" s="12"/>
+      <c r="AQ10" s="12"/>
+      <c r="AR10" s="12"/>
+      <c r="AS10" s="12"/>
+      <c r="AT10" s="12"/>
+      <c r="AU10" s="12"/>
+      <c r="AV10" s="12"/>
+      <c r="AW10" s="12"/>
+      <c r="AX10" s="12"/>
+      <c r="AY10" s="12"/>
+      <c r="AZ10" s="12"/>
+      <c r="BA10" s="12"/>
+      <c r="BB10" s="12"/>
+    </row>
+    <row r="11" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A11" s="27">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="70"/>
+      <c r="D11" s="70"/>
+      <c r="E11" s="70"/>
+      <c r="F11" s="70"/>
+      <c r="G11" s="70"/>
+      <c r="H11" s="70"/>
+      <c r="I11" s="70"/>
+      <c r="J11" s="71"/>
+      <c r="K11" s="72">
+        <v>2</v>
+      </c>
+      <c r="L11" s="55"/>
+      <c r="M11" s="73"/>
+      <c r="N11" s="74"/>
+      <c r="O11" s="70"/>
+      <c r="P11" s="71"/>
+      <c r="Q11" s="71"/>
+      <c r="R11" s="72"/>
+      <c r="S11" s="55"/>
+      <c r="T11" s="58">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="U11" s="58">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="V11" s="58">
+        <f t="shared" si="3"/>
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="AF11" s="12"/>
+      <c r="AG11" s="12"/>
+      <c r="AH11" s="12"/>
+      <c r="AI11" s="12"/>
+      <c r="AJ11" s="12"/>
+      <c r="AK11" s="12"/>
+      <c r="AL11" s="12"/>
+      <c r="AM11" s="12"/>
+      <c r="AN11" s="12"/>
+      <c r="AO11" s="12"/>
+      <c r="AP11" s="12"/>
+      <c r="AQ11" s="12"/>
+      <c r="AR11" s="12"/>
+      <c r="AS11" s="12"/>
+      <c r="AT11" s="12"/>
+      <c r="AU11" s="12"/>
+      <c r="AV11" s="12"/>
+      <c r="AW11" s="12"/>
+      <c r="AX11" s="12"/>
+      <c r="AY11" s="12"/>
+      <c r="AZ11" s="12"/>
+      <c r="BA11" s="12"/>
+      <c r="BB11" s="12"/>
+    </row>
+    <row r="12" spans="1:54" s="13" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="27">
+        <v>7</v>
+      </c>
+      <c r="B12" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="59">
+        <f>1224+53+648+61+1080+29</f>
+        <v>3095</v>
+      </c>
+      <c r="D12" s="59"/>
+      <c r="E12" s="59"/>
+      <c r="F12" s="59"/>
+      <c r="G12" s="59"/>
+      <c r="H12" s="59"/>
+      <c r="I12" s="59"/>
+      <c r="J12" s="60"/>
+      <c r="K12" s="61"/>
+      <c r="L12" s="62"/>
+      <c r="M12" s="63">
+        <v>25</v>
+      </c>
+      <c r="N12" s="64">
+        <v>10</v>
+      </c>
+      <c r="O12" s="65">
+        <v>6</v>
+      </c>
+      <c r="P12" s="66">
+        <v>12</v>
+      </c>
+      <c r="Q12" s="66">
+        <v>22</v>
+      </c>
+      <c r="R12" s="67"/>
+      <c r="S12" s="62"/>
+      <c r="T12" s="69">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="U12" s="69">
+        <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
+        <v>75574</v>
+      </c>
+      <c r="V12" s="69">
+        <f>U12/24</f>
+        <v>3148.9166666666665</v>
+      </c>
+      <c r="W12" s="9"/>
+      <c r="X12" s="9"/>
+      <c r="Y12" s="9"/>
+      <c r="Z12" s="9"/>
+      <c r="AA12" s="9"/>
+      <c r="AB12" s="9"/>
+      <c r="AC12" s="9"/>
+      <c r="AD12" s="9"/>
+      <c r="AE12" s="9"/>
+      <c r="AF12" s="12"/>
+      <c r="AG12" s="12"/>
+      <c r="AH12" s="12"/>
+      <c r="AI12" s="12"/>
+      <c r="AJ12" s="12"/>
+      <c r="AK12" s="12"/>
+      <c r="AL12" s="12"/>
+      <c r="AM12" s="12"/>
+      <c r="AN12" s="12"/>
+      <c r="AO12" s="12"/>
+      <c r="AP12" s="12"/>
+      <c r="AQ12" s="12"/>
+      <c r="AR12" s="12"/>
+      <c r="AS12" s="12"/>
+      <c r="AT12" s="12"/>
+      <c r="AU12" s="12"/>
+      <c r="AV12" s="12"/>
+      <c r="AW12" s="12"/>
+      <c r="AX12" s="12"/>
+      <c r="AY12" s="12"/>
+      <c r="AZ12" s="12"/>
+      <c r="BA12" s="12"/>
+      <c r="BB12" s="12"/>
+    </row>
+    <row r="13" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A13" s="27">
+        <v>11</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="70">
+        <v>2</v>
+      </c>
+      <c r="D13" s="70"/>
+      <c r="E13" s="70"/>
+      <c r="F13" s="70"/>
+      <c r="G13" s="70"/>
+      <c r="H13" s="70">
+        <v>16</v>
+      </c>
+      <c r="I13" s="70"/>
+      <c r="J13" s="71"/>
+      <c r="K13" s="72"/>
+      <c r="L13" s="55"/>
+      <c r="M13" s="73"/>
+      <c r="N13" s="74"/>
+      <c r="O13" s="70"/>
+      <c r="P13" s="71"/>
+      <c r="Q13" s="71"/>
+      <c r="R13" s="72"/>
+      <c r="S13" s="55"/>
+      <c r="T13" s="76">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="U13" s="76">
+        <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
+        <v>64</v>
+      </c>
+      <c r="V13" s="76">
+        <f>U13/24</f>
+        <v>2.6666666666666665</v>
+      </c>
+      <c r="AF13" s="12"/>
+      <c r="AG13" s="12"/>
+      <c r="AH13" s="12"/>
+      <c r="AI13" s="12"/>
+      <c r="AJ13" s="12"/>
+      <c r="AK13" s="12"/>
+      <c r="AL13" s="12"/>
+      <c r="AM13" s="12"/>
+      <c r="AN13" s="12"/>
+      <c r="AO13" s="12"/>
+      <c r="AP13" s="12"/>
+      <c r="AQ13" s="12"/>
+      <c r="AR13" s="12"/>
+      <c r="AS13" s="12"/>
+      <c r="AT13" s="12"/>
+      <c r="AU13" s="12"/>
+      <c r="AV13" s="12"/>
+      <c r="AW13" s="12"/>
+      <c r="AX13" s="12"/>
+      <c r="AY13" s="12"/>
+      <c r="AZ13" s="12"/>
+      <c r="BA13" s="12"/>
+      <c r="BB13" s="12"/>
+    </row>
+    <row r="14" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A14" s="27">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="70">
+        <v>2</v>
+      </c>
+      <c r="D14" s="70"/>
+      <c r="E14" s="70"/>
+      <c r="F14" s="70"/>
+      <c r="G14" s="70"/>
+      <c r="H14" s="70"/>
+      <c r="I14" s="70"/>
+      <c r="J14" s="71"/>
+      <c r="K14" s="72"/>
+      <c r="L14" s="55"/>
+      <c r="M14" s="73"/>
+      <c r="N14" s="74"/>
+      <c r="O14" s="70"/>
+      <c r="P14" s="71"/>
+      <c r="Q14" s="71"/>
+      <c r="R14" s="72"/>
+      <c r="S14" s="55"/>
+      <c r="T14" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U14" s="75">
+        <f t="shared" ref="U14:U36" si="4">C14*24+M14*24+O14*24+Q14*24+T14</f>
+        <v>48</v>
+      </c>
+      <c r="V14" s="75">
+        <f t="shared" ref="V14:V36" si="5">U14/24</f>
+        <v>2</v>
+      </c>
+      <c r="AF14" s="12"/>
+      <c r="AG14" s="12"/>
+      <c r="AH14" s="12"/>
+      <c r="AI14" s="12"/>
+      <c r="AJ14" s="12"/>
+      <c r="AK14" s="12"/>
+      <c r="AL14" s="12"/>
+      <c r="AM14" s="12"/>
+      <c r="AN14" s="12"/>
+      <c r="AO14" s="12"/>
+      <c r="AP14" s="12"/>
+      <c r="AQ14" s="12"/>
+      <c r="AR14" s="12"/>
+      <c r="AS14" s="12"/>
+      <c r="AT14" s="12"/>
+      <c r="AU14" s="12"/>
+      <c r="AV14" s="12"/>
+      <c r="AW14" s="12"/>
+      <c r="AX14" s="12"/>
+      <c r="AY14" s="12"/>
+      <c r="AZ14" s="12"/>
+      <c r="BA14" s="12"/>
+      <c r="BB14" s="12"/>
+    </row>
+    <row r="15" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A15" s="27">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="70"/>
+      <c r="D15" s="70"/>
+      <c r="E15" s="70"/>
+      <c r="F15" s="70"/>
+      <c r="G15" s="70"/>
+      <c r="H15" s="70"/>
+      <c r="I15" s="70"/>
+      <c r="J15" s="71"/>
+      <c r="K15" s="72"/>
+      <c r="L15" s="55"/>
+      <c r="M15" s="73"/>
+      <c r="N15" s="74"/>
+      <c r="O15" s="70"/>
+      <c r="P15" s="71"/>
+      <c r="Q15" s="71"/>
+      <c r="R15" s="72"/>
+      <c r="S15" s="55"/>
+      <c r="T15" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U15" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF15" s="12"/>
+      <c r="AG15" s="12"/>
+      <c r="AH15" s="12"/>
+      <c r="AI15" s="12"/>
+      <c r="AJ15" s="12"/>
+      <c r="AK15" s="12"/>
+      <c r="AL15" s="12"/>
+      <c r="AM15" s="12"/>
+      <c r="AN15" s="12"/>
+      <c r="AO15" s="12"/>
+      <c r="AP15" s="12"/>
+      <c r="AQ15" s="12"/>
+      <c r="AR15" s="12"/>
+      <c r="AS15" s="12"/>
+      <c r="AT15" s="12"/>
+      <c r="AU15" s="12"/>
+      <c r="AV15" s="12"/>
+      <c r="AW15" s="12"/>
+      <c r="AX15" s="12"/>
+      <c r="AY15" s="12"/>
+      <c r="AZ15" s="12"/>
+      <c r="BA15" s="12"/>
+      <c r="BB15" s="12"/>
+    </row>
+    <row r="16" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A16" s="27">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="70"/>
+      <c r="D16" s="70"/>
+      <c r="E16" s="70"/>
+      <c r="F16" s="70"/>
+      <c r="G16" s="70"/>
+      <c r="H16" s="70"/>
+      <c r="I16" s="70"/>
+      <c r="J16" s="71"/>
+      <c r="K16" s="72"/>
+      <c r="L16" s="55"/>
+      <c r="M16" s="73"/>
+      <c r="N16" s="74"/>
+      <c r="O16" s="70"/>
+      <c r="P16" s="71"/>
+      <c r="Q16" s="71"/>
+      <c r="R16" s="72"/>
+      <c r="S16" s="55"/>
+      <c r="T16" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U16" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF16" s="12"/>
+      <c r="AG16" s="12"/>
+      <c r="AH16" s="12"/>
+      <c r="AI16" s="12"/>
+      <c r="AJ16" s="12"/>
+      <c r="AK16" s="12"/>
+      <c r="AL16" s="12"/>
+      <c r="AM16" s="12"/>
+      <c r="AN16" s="12"/>
+      <c r="AO16" s="12"/>
+      <c r="AP16" s="12"/>
+      <c r="AQ16" s="12"/>
+      <c r="AR16" s="12"/>
+      <c r="AS16" s="12"/>
+      <c r="AT16" s="12"/>
+      <c r="AU16" s="12"/>
+      <c r="AV16" s="12"/>
+      <c r="AW16" s="12"/>
+      <c r="AX16" s="12"/>
+      <c r="AY16" s="12"/>
+      <c r="AZ16" s="12"/>
+      <c r="BA16" s="12"/>
+      <c r="BB16" s="12"/>
+    </row>
+    <row r="17" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A17" s="27">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="70"/>
+      <c r="D17" s="70"/>
+      <c r="E17" s="70"/>
+      <c r="F17" s="70"/>
+      <c r="G17" s="70"/>
+      <c r="H17" s="70">
+        <f>3*24</f>
+        <v>72</v>
+      </c>
+      <c r="I17" s="70"/>
+      <c r="J17" s="71"/>
+      <c r="K17" s="72"/>
+      <c r="L17" s="55"/>
+      <c r="M17" s="73"/>
+      <c r="N17" s="74"/>
+      <c r="O17" s="70"/>
+      <c r="P17" s="71"/>
+      <c r="Q17" s="71"/>
+      <c r="R17" s="72"/>
+      <c r="S17" s="55"/>
+      <c r="T17" s="58">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="U17" s="75">
+        <f t="shared" si="4"/>
+        <v>72</v>
+      </c>
+      <c r="V17" s="75">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="AF17" s="12"/>
+      <c r="AG17" s="12"/>
+      <c r="AH17" s="12"/>
+      <c r="AI17" s="12"/>
+      <c r="AJ17" s="12"/>
+      <c r="AK17" s="12"/>
+      <c r="AL17" s="12"/>
+      <c r="AM17" s="12"/>
+      <c r="AN17" s="12"/>
+      <c r="AO17" s="12"/>
+      <c r="AP17" s="12"/>
+      <c r="AQ17" s="12"/>
+      <c r="AR17" s="12"/>
+      <c r="AS17" s="12"/>
+      <c r="AT17" s="12"/>
+      <c r="AU17" s="12"/>
+      <c r="AV17" s="12"/>
+      <c r="AW17" s="12"/>
+      <c r="AX17" s="12"/>
+      <c r="AY17" s="12"/>
+      <c r="AZ17" s="12"/>
+      <c r="BA17" s="12"/>
+      <c r="BB17" s="12"/>
+    </row>
+    <row r="18" spans="1:54" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="27">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="70"/>
+      <c r="D18" s="70"/>
+      <c r="E18" s="70"/>
+      <c r="F18" s="70"/>
+      <c r="G18" s="70"/>
+      <c r="H18" s="70"/>
+      <c r="I18" s="70"/>
+      <c r="J18" s="71"/>
+      <c r="K18" s="72"/>
+      <c r="L18" s="55"/>
+      <c r="M18" s="73"/>
+      <c r="N18" s="74"/>
+      <c r="O18" s="70"/>
+      <c r="P18" s="71"/>
+      <c r="Q18" s="71"/>
+      <c r="R18" s="72"/>
+      <c r="S18" s="55"/>
+      <c r="T18" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U18" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF18" s="12"/>
+      <c r="AG18" s="12"/>
+      <c r="AH18" s="12"/>
+      <c r="AI18" s="12"/>
+      <c r="AJ18" s="12"/>
+      <c r="AK18" s="12"/>
+      <c r="AL18" s="12"/>
+      <c r="AM18" s="12"/>
+      <c r="AN18" s="12"/>
+      <c r="AO18" s="12"/>
+      <c r="AP18" s="12"/>
+      <c r="AQ18" s="12"/>
+      <c r="AR18" s="12"/>
+      <c r="AS18" s="12"/>
+      <c r="AT18" s="12"/>
+      <c r="AU18" s="12"/>
+      <c r="AV18" s="12"/>
+      <c r="AW18" s="12"/>
+      <c r="AX18" s="12"/>
+      <c r="AY18" s="12"/>
+      <c r="AZ18" s="12"/>
+      <c r="BA18" s="12"/>
+      <c r="BB18" s="12"/>
+    </row>
+    <row r="19" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A19" s="27">
+        <v>16</v>
+      </c>
+      <c r="B19" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="70">
+        <v>1</v>
+      </c>
+      <c r="D19" s="70"/>
+      <c r="E19" s="70"/>
+      <c r="F19" s="70"/>
+      <c r="G19" s="70"/>
+      <c r="H19" s="70">
+        <f>20+24</f>
+        <v>44</v>
+      </c>
+      <c r="I19" s="70"/>
+      <c r="J19" s="71"/>
+      <c r="K19" s="72"/>
+      <c r="L19" s="55"/>
+      <c r="M19" s="73"/>
+      <c r="N19" s="74"/>
+      <c r="O19" s="70"/>
+      <c r="P19" s="71"/>
+      <c r="Q19" s="71"/>
+      <c r="R19" s="72"/>
+      <c r="S19" s="55"/>
+      <c r="T19" s="58">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="U19" s="75">
+        <f t="shared" si="4"/>
+        <v>68</v>
+      </c>
+      <c r="V19" s="75">
+        <f t="shared" si="5"/>
+        <v>2.8333333333333335</v>
+      </c>
+      <c r="AF19" s="12"/>
+      <c r="AG19" s="12"/>
+      <c r="AH19" s="12"/>
+      <c r="AI19" s="12"/>
+      <c r="AJ19" s="12"/>
+      <c r="AK19" s="12"/>
+      <c r="AL19" s="12"/>
+      <c r="AM19" s="12"/>
+      <c r="AN19" s="12"/>
+      <c r="AO19" s="12"/>
+      <c r="AP19" s="12"/>
+      <c r="AQ19" s="12"/>
+      <c r="AR19" s="12"/>
+      <c r="AS19" s="12"/>
+      <c r="AT19" s="12"/>
+      <c r="AU19" s="12"/>
+      <c r="AV19" s="12"/>
+      <c r="AW19" s="12"/>
+      <c r="AX19" s="12"/>
+      <c r="AY19" s="12"/>
+      <c r="AZ19" s="12"/>
+      <c r="BA19" s="12"/>
+      <c r="BB19" s="12"/>
+    </row>
+    <row r="20" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A20" s="27">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="B20" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="70">
+        <v>5</v>
+      </c>
+      <c r="D20" s="70"/>
+      <c r="E20" s="70"/>
+      <c r="F20" s="70"/>
+      <c r="G20" s="70"/>
+      <c r="H20" s="70"/>
+      <c r="I20" s="70"/>
+      <c r="J20" s="71"/>
+      <c r="K20" s="72"/>
+      <c r="L20" s="55"/>
+      <c r="M20" s="73"/>
+      <c r="N20" s="74"/>
+      <c r="O20" s="70"/>
+      <c r="P20" s="71"/>
+      <c r="Q20" s="71"/>
+      <c r="R20" s="72"/>
+      <c r="S20" s="55"/>
+      <c r="T20" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U20" s="75">
+        <f t="shared" si="4"/>
+        <v>120</v>
+      </c>
+      <c r="V20" s="75">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="AF20" s="12"/>
+      <c r="AG20" s="12"/>
+      <c r="AH20" s="12"/>
+      <c r="AI20" s="12"/>
+      <c r="AJ20" s="12"/>
+      <c r="AK20" s="12"/>
+      <c r="AL20" s="12"/>
+      <c r="AM20" s="12"/>
+      <c r="AN20" s="12"/>
+      <c r="AO20" s="12"/>
+      <c r="AP20" s="12"/>
+      <c r="AQ20" s="12"/>
+      <c r="AR20" s="12"/>
+      <c r="AS20" s="12"/>
+      <c r="AT20" s="12"/>
+      <c r="AU20" s="12"/>
+      <c r="AV20" s="12"/>
+      <c r="AW20" s="12"/>
+      <c r="AX20" s="12"/>
+      <c r="AY20" s="12"/>
+      <c r="AZ20" s="12"/>
+      <c r="BA20" s="12"/>
+      <c r="BB20" s="12"/>
+    </row>
+    <row r="21" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A21" s="27">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="B21" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="70"/>
+      <c r="D21" s="70"/>
+      <c r="E21" s="70"/>
+      <c r="F21" s="70"/>
+      <c r="G21" s="70"/>
+      <c r="H21" s="70">
+        <f>2*24</f>
+        <v>48</v>
+      </c>
+      <c r="I21" s="70"/>
+      <c r="J21" s="71"/>
+      <c r="K21" s="72"/>
+      <c r="L21" s="55"/>
+      <c r="M21" s="73"/>
+      <c r="N21" s="74"/>
+      <c r="O21" s="70"/>
+      <c r="P21" s="71"/>
+      <c r="Q21" s="71"/>
+      <c r="R21" s="72"/>
+      <c r="S21" s="55"/>
+      <c r="T21" s="58">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+      <c r="U21" s="75">
+        <f t="shared" si="4"/>
+        <v>48</v>
+      </c>
+      <c r="V21" s="75">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="AF21" s="12"/>
+      <c r="AG21" s="12"/>
+      <c r="AH21" s="12"/>
+      <c r="AI21" s="12"/>
+      <c r="AJ21" s="12"/>
+      <c r="AK21" s="12"/>
+      <c r="AL21" s="12"/>
+      <c r="AM21" s="12"/>
+      <c r="AN21" s="12"/>
+      <c r="AO21" s="12"/>
+      <c r="AP21" s="12"/>
+      <c r="AQ21" s="12"/>
+      <c r="AR21" s="12"/>
+      <c r="AS21" s="12"/>
+      <c r="AT21" s="12"/>
+      <c r="AU21" s="12"/>
+      <c r="AV21" s="12"/>
+      <c r="AW21" s="12"/>
+      <c r="AX21" s="12"/>
+      <c r="AY21" s="12"/>
+      <c r="AZ21" s="12"/>
+      <c r="BA21" s="12"/>
+      <c r="BB21" s="12"/>
+    </row>
+    <row r="22" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="27">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="B22" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="70">
+        <v>1</v>
+      </c>
+      <c r="D22" s="70"/>
+      <c r="E22" s="70"/>
+      <c r="F22" s="70"/>
+      <c r="G22" s="70"/>
+      <c r="H22" s="70"/>
+      <c r="I22" s="70">
+        <v>20</v>
+      </c>
+      <c r="J22" s="71"/>
+      <c r="K22" s="72"/>
+      <c r="L22" s="55"/>
+      <c r="M22" s="73"/>
+      <c r="N22" s="74"/>
+      <c r="O22" s="70"/>
+      <c r="P22" s="71"/>
+      <c r="Q22" s="71"/>
+      <c r="R22" s="72"/>
+      <c r="S22" s="55"/>
+      <c r="T22" s="58">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="U22" s="75">
+        <f t="shared" si="4"/>
+        <v>44</v>
+      </c>
+      <c r="V22" s="75">
+        <f t="shared" si="5"/>
+        <v>1.8333333333333333</v>
+      </c>
+      <c r="W22" s="9"/>
+      <c r="X22" s="9"/>
+      <c r="Y22" s="9"/>
+      <c r="Z22" s="9"/>
+      <c r="AA22" s="9"/>
+      <c r="AB22" s="9"/>
+      <c r="AC22" s="9"/>
+      <c r="AD22" s="9"/>
+      <c r="AE22" s="9"/>
+      <c r="AF22" s="12"/>
+      <c r="AG22" s="12"/>
+      <c r="AH22" s="12"/>
+      <c r="AI22" s="12"/>
+      <c r="AJ22" s="12"/>
+      <c r="AK22" s="12"/>
+      <c r="AL22" s="12"/>
+      <c r="AM22" s="12"/>
+      <c r="AN22" s="12"/>
+      <c r="AO22" s="12"/>
+      <c r="AP22" s="12"/>
+      <c r="AQ22" s="12"/>
+      <c r="AR22" s="12"/>
+      <c r="AS22" s="12"/>
+      <c r="AT22" s="12"/>
+      <c r="AU22" s="12"/>
+      <c r="AV22" s="12"/>
+      <c r="AW22" s="12"/>
+      <c r="AX22" s="12"/>
+      <c r="AY22" s="12"/>
+      <c r="AZ22" s="12"/>
+      <c r="BA22" s="12"/>
+      <c r="BB22" s="12"/>
+    </row>
+    <row r="23" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="27">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="B23" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="70"/>
+      <c r="D23" s="70"/>
+      <c r="E23" s="70"/>
+      <c r="F23" s="70"/>
+      <c r="G23" s="70"/>
+      <c r="H23" s="70">
+        <f>37*24+19</f>
+        <v>907</v>
+      </c>
+      <c r="I23" s="70"/>
+      <c r="J23" s="71"/>
+      <c r="K23" s="72"/>
+      <c r="L23" s="55"/>
+      <c r="M23" s="73"/>
+      <c r="N23" s="74"/>
+      <c r="O23" s="70"/>
+      <c r="P23" s="71"/>
+      <c r="Q23" s="71"/>
+      <c r="R23" s="72"/>
+      <c r="S23" s="55"/>
+      <c r="T23" s="58">
+        <f t="shared" si="0"/>
+        <v>907</v>
+      </c>
+      <c r="U23" s="75">
+        <f t="shared" si="4"/>
+        <v>907</v>
+      </c>
+      <c r="V23" s="75">
+        <f t="shared" si="5"/>
+        <v>37.791666666666664</v>
+      </c>
+      <c r="W23" s="9"/>
+      <c r="X23" s="9"/>
+      <c r="Y23" s="9"/>
+      <c r="Z23" s="9"/>
+      <c r="AA23" s="9"/>
+      <c r="AB23" s="9"/>
+      <c r="AC23" s="9"/>
+      <c r="AD23" s="9"/>
+      <c r="AE23" s="9"/>
+      <c r="AF23" s="12"/>
+      <c r="AG23" s="12"/>
+      <c r="AH23" s="12"/>
+      <c r="AI23" s="12"/>
+      <c r="AJ23" s="12"/>
+      <c r="AK23" s="12"/>
+      <c r="AL23" s="12"/>
+      <c r="AM23" s="12"/>
+      <c r="AN23" s="12"/>
+      <c r="AO23" s="12"/>
+      <c r="AP23" s="12"/>
+      <c r="AQ23" s="12"/>
+      <c r="AR23" s="12"/>
+      <c r="AS23" s="12"/>
+      <c r="AT23" s="12"/>
+      <c r="AU23" s="12"/>
+      <c r="AV23" s="12"/>
+      <c r="AW23" s="12"/>
+      <c r="AX23" s="12"/>
+      <c r="AY23" s="12"/>
+      <c r="AZ23" s="12"/>
+      <c r="BA23" s="12"/>
+      <c r="BB23" s="12"/>
+    </row>
+    <row r="24" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A24" s="27">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="B24" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" s="70">
+        <v>2</v>
+      </c>
+      <c r="D24" s="70"/>
+      <c r="E24" s="70"/>
+      <c r="F24" s="70"/>
+      <c r="G24" s="70"/>
+      <c r="H24" s="70">
+        <f>3*24</f>
+        <v>72</v>
+      </c>
+      <c r="I24" s="70"/>
+      <c r="J24" s="71"/>
+      <c r="K24" s="72"/>
+      <c r="L24" s="55"/>
+      <c r="M24" s="73"/>
+      <c r="N24" s="74"/>
+      <c r="O24" s="70"/>
+      <c r="P24" s="71"/>
+      <c r="Q24" s="71"/>
+      <c r="R24" s="72"/>
+      <c r="S24" s="55"/>
+      <c r="T24" s="58">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="U24" s="75">
+        <f t="shared" si="4"/>
+        <v>120</v>
+      </c>
+      <c r="V24" s="75">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="AF24" s="12"/>
+      <c r="AG24" s="12"/>
+      <c r="AH24" s="12"/>
+      <c r="AI24" s="12"/>
+      <c r="AJ24" s="12"/>
+      <c r="AK24" s="12"/>
+      <c r="AL24" s="12"/>
+      <c r="AM24" s="12"/>
+      <c r="AN24" s="12"/>
+      <c r="AO24" s="12"/>
+      <c r="AP24" s="12"/>
+      <c r="AQ24" s="12"/>
+      <c r="AR24" s="12"/>
+      <c r="AS24" s="12"/>
+      <c r="AT24" s="12"/>
+      <c r="AU24" s="12"/>
+      <c r="AV24" s="12"/>
+      <c r="AW24" s="12"/>
+      <c r="AX24" s="12"/>
+      <c r="AY24" s="12"/>
+      <c r="AZ24" s="12"/>
+      <c r="BA24" s="12"/>
+      <c r="BB24" s="12"/>
+    </row>
+    <row r="25" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A25" s="27">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="70">
+        <f>126+24</f>
+        <v>150</v>
+      </c>
+      <c r="D25" s="70"/>
+      <c r="E25" s="70"/>
+      <c r="F25" s="70"/>
+      <c r="G25" s="70"/>
+      <c r="H25" s="70"/>
+      <c r="I25" s="70">
+        <v>1</v>
+      </c>
+      <c r="J25" s="71"/>
+      <c r="K25" s="72"/>
+      <c r="L25" s="55"/>
+      <c r="M25" s="73"/>
+      <c r="N25" s="74"/>
+      <c r="O25" s="70">
+        <v>1</v>
+      </c>
+      <c r="P25" s="71"/>
+      <c r="Q25" s="71">
+        <v>1</v>
+      </c>
+      <c r="R25" s="72"/>
+      <c r="S25" s="55"/>
+      <c r="T25" s="58">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="U25" s="75">
+        <f t="shared" si="4"/>
+        <v>3649</v>
+      </c>
+      <c r="V25" s="75">
+        <f t="shared" si="5"/>
+        <v>152.04166666666666</v>
+      </c>
+      <c r="AY25" s="14" t="e">
+        <f>#REF!-AY24</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="27">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="B26" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="70"/>
+      <c r="D26" s="70"/>
+      <c r="E26" s="70"/>
+      <c r="F26" s="70"/>
+      <c r="G26" s="70"/>
+      <c r="H26" s="70"/>
+      <c r="I26" s="70"/>
+      <c r="J26" s="71"/>
+      <c r="K26" s="72"/>
+      <c r="L26" s="55"/>
+      <c r="M26" s="73"/>
+      <c r="N26" s="74"/>
+      <c r="O26" s="70"/>
+      <c r="P26" s="71"/>
+      <c r="Q26" s="71"/>
+      <c r="R26" s="72"/>
+      <c r="S26" s="55"/>
+      <c r="T26" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U26" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V26" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W26" s="9"/>
+      <c r="X26" s="9"/>
+      <c r="Y26" s="9"/>
+      <c r="Z26" s="9"/>
+      <c r="AA26" s="9"/>
+      <c r="AB26" s="9"/>
+      <c r="AC26" s="9"/>
+      <c r="AD26" s="9"/>
+      <c r="AE26" s="9"/>
+    </row>
+    <row r="27" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="27">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="B27" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27" s="70">
+        <v>1</v>
+      </c>
+      <c r="D27" s="70"/>
+      <c r="E27" s="70"/>
+      <c r="F27" s="70"/>
+      <c r="G27" s="70"/>
+      <c r="H27" s="70"/>
+      <c r="I27" s="70"/>
+      <c r="J27" s="71"/>
+      <c r="K27" s="72"/>
+      <c r="L27" s="55"/>
+      <c r="M27" s="73"/>
+      <c r="N27" s="74"/>
+      <c r="O27" s="70"/>
+      <c r="P27" s="71"/>
+      <c r="Q27" s="71"/>
+      <c r="R27" s="72"/>
+      <c r="S27" s="55"/>
+      <c r="T27" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U27" s="75">
+        <f t="shared" si="4"/>
+        <v>24</v>
+      </c>
+      <c r="V27" s="75">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="W27" s="9"/>
+      <c r="X27" s="9"/>
+      <c r="Y27" s="9"/>
+      <c r="Z27" s="9"/>
+      <c r="AA27" s="9"/>
+      <c r="AB27" s="9"/>
+      <c r="AC27" s="9"/>
+      <c r="AD27" s="9"/>
+      <c r="AE27" s="9"/>
+    </row>
+    <row r="28" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="27">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="B28" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="70"/>
+      <c r="D28" s="70"/>
+      <c r="E28" s="70"/>
+      <c r="F28" s="70"/>
+      <c r="G28" s="70"/>
+      <c r="H28" s="70"/>
+      <c r="I28" s="70"/>
+      <c r="J28" s="71"/>
+      <c r="K28" s="72"/>
+      <c r="L28" s="55"/>
+      <c r="M28" s="73"/>
+      <c r="N28" s="74"/>
+      <c r="O28" s="70"/>
+      <c r="P28" s="71"/>
+      <c r="Q28" s="71"/>
+      <c r="R28" s="72"/>
+      <c r="S28" s="55"/>
+      <c r="T28" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U28" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V28" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W28" s="9"/>
+      <c r="X28" s="9"/>
+      <c r="Y28" s="9"/>
+      <c r="Z28" s="9"/>
+      <c r="AA28" s="9"/>
+      <c r="AB28" s="9"/>
+      <c r="AC28" s="9"/>
+      <c r="AD28" s="9"/>
+      <c r="AE28" s="9"/>
+    </row>
+    <row r="29" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A29" s="27">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="B29" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" s="70"/>
+      <c r="D29" s="70"/>
+      <c r="E29" s="70"/>
+      <c r="F29" s="70"/>
+      <c r="G29" s="70"/>
+      <c r="H29" s="70"/>
+      <c r="I29" s="70">
+        <v>5</v>
+      </c>
+      <c r="J29" s="71"/>
+      <c r="K29" s="72"/>
+      <c r="L29" s="55"/>
+      <c r="M29" s="73"/>
+      <c r="N29" s="74"/>
+      <c r="O29" s="70"/>
+      <c r="P29" s="71"/>
+      <c r="Q29" s="71"/>
+      <c r="R29" s="72"/>
+      <c r="S29" s="55"/>
+      <c r="T29" s="58">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="U29" s="75">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="V29" s="75">
+        <f t="shared" si="5"/>
+        <v>0.20833333333333334</v>
+      </c>
+    </row>
+    <row r="30" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A30" s="27">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="B30" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="70">
+        <v>1</v>
+      </c>
+      <c r="D30" s="70"/>
+      <c r="E30" s="70"/>
+      <c r="F30" s="70"/>
+      <c r="G30" s="70"/>
+      <c r="H30" s="70"/>
+      <c r="I30" s="70"/>
+      <c r="J30" s="71"/>
+      <c r="K30" s="72"/>
+      <c r="L30" s="55"/>
+      <c r="M30" s="73"/>
+      <c r="N30" s="74"/>
+      <c r="O30" s="70"/>
+      <c r="P30" s="71"/>
+      <c r="Q30" s="71">
+        <v>1</v>
+      </c>
+      <c r="R30" s="72"/>
+      <c r="S30" s="55"/>
+      <c r="T30" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U30" s="75">
+        <f t="shared" si="4"/>
+        <v>48</v>
+      </c>
+      <c r="V30" s="75">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A31" s="27">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="B31" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" s="70"/>
+      <c r="D31" s="70"/>
+      <c r="E31" s="70"/>
+      <c r="F31" s="70"/>
+      <c r="G31" s="70"/>
+      <c r="H31" s="70"/>
+      <c r="I31" s="70"/>
+      <c r="J31" s="71"/>
+      <c r="K31" s="72"/>
+      <c r="L31" s="55"/>
+      <c r="M31" s="73"/>
+      <c r="N31" s="74"/>
+      <c r="O31" s="70"/>
+      <c r="P31" s="71"/>
+      <c r="Q31" s="71"/>
+      <c r="R31" s="72"/>
+      <c r="S31" s="55"/>
+      <c r="T31" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U31" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V31" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A32" s="27">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="B32" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" s="70"/>
+      <c r="D32" s="70"/>
+      <c r="E32" s="70"/>
+      <c r="F32" s="70"/>
+      <c r="G32" s="70"/>
+      <c r="H32" s="70"/>
+      <c r="I32" s="70"/>
+      <c r="J32" s="71"/>
+      <c r="K32" s="72"/>
+      <c r="L32" s="55"/>
+      <c r="M32" s="73"/>
+      <c r="N32" s="74"/>
+      <c r="O32" s="70"/>
+      <c r="P32" s="71"/>
+      <c r="Q32" s="71"/>
+      <c r="R32" s="72"/>
+      <c r="S32" s="55"/>
+      <c r="T32" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U32" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V32" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A33" s="27">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="B33" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" s="70"/>
+      <c r="D33" s="70"/>
+      <c r="E33" s="70"/>
+      <c r="F33" s="70"/>
+      <c r="G33" s="70"/>
+      <c r="H33" s="70"/>
+      <c r="I33" s="70"/>
+      <c r="J33" s="71"/>
+      <c r="K33" s="72"/>
+      <c r="L33" s="55"/>
+      <c r="M33" s="73"/>
+      <c r="N33" s="74"/>
+      <c r="O33" s="70"/>
+      <c r="P33" s="71"/>
+      <c r="Q33" s="71"/>
+      <c r="R33" s="72"/>
+      <c r="S33" s="55"/>
+      <c r="T33" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U33" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V33" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A34" s="27">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="B34" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" s="70">
+        <f>68+72</f>
+        <v>140</v>
+      </c>
+      <c r="D34" s="70"/>
+      <c r="E34" s="70"/>
+      <c r="F34" s="70"/>
+      <c r="G34" s="70"/>
+      <c r="H34" s="70"/>
+      <c r="I34" s="70">
+        <v>1</v>
+      </c>
+      <c r="J34" s="71"/>
+      <c r="K34" s="72">
+        <v>1</v>
+      </c>
+      <c r="L34" s="55"/>
+      <c r="M34" s="73"/>
+      <c r="N34" s="74"/>
+      <c r="O34" s="70"/>
+      <c r="P34" s="71"/>
+      <c r="Q34" s="71">
+        <v>3</v>
+      </c>
+      <c r="R34" s="72"/>
+      <c r="S34" s="55"/>
+      <c r="T34" s="58">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="U34" s="75">
+        <f t="shared" si="4"/>
+        <v>3434</v>
+      </c>
+      <c r="V34" s="75">
+        <f t="shared" si="5"/>
+        <v>143.08333333333334</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="27">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="B35" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="C35" s="70"/>
+      <c r="D35" s="70"/>
+      <c r="E35" s="70"/>
+      <c r="F35" s="70"/>
+      <c r="G35" s="70"/>
+      <c r="H35" s="70"/>
+      <c r="I35" s="70"/>
+      <c r="J35" s="71"/>
+      <c r="K35" s="72"/>
+      <c r="L35" s="55"/>
+      <c r="M35" s="73"/>
+      <c r="N35" s="74"/>
+      <c r="O35" s="70"/>
+      <c r="P35" s="71"/>
+      <c r="Q35" s="71"/>
+      <c r="R35" s="72"/>
+      <c r="S35" s="55"/>
+      <c r="T35" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U35" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V35" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A36" s="27">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+      <c r="B36" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="70"/>
+      <c r="D36" s="70"/>
+      <c r="E36" s="70"/>
+      <c r="F36" s="70"/>
+      <c r="G36" s="70"/>
+      <c r="H36" s="70"/>
+      <c r="I36" s="70"/>
+      <c r="J36" s="71"/>
+      <c r="K36" s="72"/>
+      <c r="L36" s="55"/>
+      <c r="M36" s="73"/>
+      <c r="N36" s="74"/>
+      <c r="O36" s="70"/>
+      <c r="P36" s="71"/>
+      <c r="Q36" s="71"/>
+      <c r="R36" s="72"/>
+      <c r="S36" s="55"/>
+      <c r="T36" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U36" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="27">
+        <f t="shared" si="1"/>
+        <v>34</v>
+      </c>
+      <c r="B37" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="C37" s="59">
+        <f>864+2160+78</f>
+        <v>3102</v>
+      </c>
+      <c r="D37" s="59"/>
+      <c r="E37" s="59"/>
+      <c r="F37" s="59"/>
+      <c r="G37" s="59"/>
+      <c r="H37" s="59">
+        <v>3</v>
+      </c>
+      <c r="I37" s="59">
+        <v>2</v>
+      </c>
+      <c r="J37" s="60">
+        <v>6</v>
+      </c>
+      <c r="K37" s="61">
+        <f>6+2</f>
+        <v>8</v>
+      </c>
+      <c r="L37" s="62"/>
+      <c r="M37" s="63">
+        <v>30</v>
+      </c>
+      <c r="N37" s="64"/>
+      <c r="O37" s="65"/>
+      <c r="P37" s="66"/>
+      <c r="Q37" s="66">
+        <v>109</v>
+      </c>
+      <c r="R37" s="67"/>
+      <c r="S37" s="62"/>
+      <c r="T37" s="77">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="U37" s="77">
+        <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
+        <v>19465</v>
+      </c>
+      <c r="V37" s="77">
+        <f>U37/6</f>
+        <v>3244.1666666666665</v>
+      </c>
+      <c r="W37" s="50"/>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A38" s="27">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="B38" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" s="70"/>
+      <c r="D38" s="70"/>
+      <c r="E38" s="70"/>
+      <c r="F38" s="70"/>
+      <c r="G38" s="70"/>
+      <c r="H38" s="70"/>
+      <c r="I38" s="70"/>
+      <c r="J38" s="71"/>
+      <c r="K38" s="72"/>
+      <c r="L38" s="55"/>
+      <c r="M38" s="73"/>
+      <c r="N38" s="74"/>
+      <c r="O38" s="70"/>
+      <c r="P38" s="71"/>
+      <c r="Q38" s="71"/>
+      <c r="R38" s="72"/>
+      <c r="S38" s="55"/>
+      <c r="T38" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U38" s="75">
+        <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
+        <v>0</v>
+      </c>
+      <c r="V38" s="75">
+        <f>U38/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A39" s="27">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="B39" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="C39" s="78"/>
+      <c r="D39" s="78"/>
+      <c r="E39" s="78"/>
+      <c r="F39" s="78"/>
+      <c r="G39" s="78"/>
+      <c r="H39" s="78"/>
+      <c r="I39" s="78"/>
+      <c r="J39" s="79"/>
+      <c r="K39" s="80"/>
+      <c r="L39" s="55"/>
+      <c r="M39" s="73"/>
+      <c r="N39" s="74"/>
+      <c r="O39" s="70"/>
+      <c r="P39" s="71"/>
+      <c r="Q39" s="71"/>
+      <c r="R39" s="72"/>
+      <c r="S39" s="95"/>
+      <c r="T39" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U39" s="75">
+        <f>C39*24+M39*24+O39*24+Q39*24+T39</f>
+        <v>0</v>
+      </c>
+      <c r="V39" s="75">
+        <f>U39/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="27">
+        <f t="shared" si="1"/>
+        <v>37</v>
+      </c>
+      <c r="B40" s="42" t="s">
+        <v>21</v>
+      </c>
+      <c r="C40" s="59">
+        <f>189+49</f>
+        <v>238</v>
+      </c>
+      <c r="D40" s="59"/>
+      <c r="E40" s="59"/>
+      <c r="F40" s="59"/>
+      <c r="G40" s="59"/>
+      <c r="H40" s="59"/>
+      <c r="I40" s="59"/>
+      <c r="J40" s="60"/>
+      <c r="K40" s="61">
+        <v>20</v>
+      </c>
+      <c r="L40" s="62"/>
+      <c r="M40" s="63"/>
+      <c r="N40" s="64"/>
+      <c r="O40" s="65">
+        <v>1</v>
+      </c>
+      <c r="P40" s="66"/>
+      <c r="Q40" s="66">
+        <v>2</v>
+      </c>
+      <c r="R40" s="67"/>
+      <c r="S40" s="62"/>
+      <c r="T40" s="77">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="U40" s="77">
+        <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
+        <v>5804</v>
+      </c>
+      <c r="V40" s="77">
+        <f>U40/24</f>
+        <v>241.83333333333334</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="27">
+        <f t="shared" si="1"/>
+        <v>38</v>
+      </c>
+      <c r="B41" s="43" t="s">
+        <v>22</v>
+      </c>
+      <c r="C41" s="82">
+        <f>192+38</f>
+        <v>230</v>
+      </c>
+      <c r="D41" s="82"/>
+      <c r="E41" s="82"/>
+      <c r="F41" s="82"/>
+      <c r="G41" s="82"/>
+      <c r="H41" s="82"/>
+      <c r="I41" s="82"/>
+      <c r="J41" s="83"/>
+      <c r="K41" s="84"/>
+      <c r="L41" s="85"/>
+      <c r="M41" s="86">
+        <v>5</v>
+      </c>
+      <c r="N41" s="87"/>
+      <c r="O41" s="82">
+        <v>10</v>
+      </c>
+      <c r="P41" s="83"/>
+      <c r="Q41" s="83">
+        <v>48</v>
+      </c>
+      <c r="R41" s="84"/>
+      <c r="S41" s="85"/>
+      <c r="T41" s="88">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U41" s="88">
+        <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
+        <v>3516</v>
+      </c>
+      <c r="V41" s="88">
+        <f>U41/12</f>
+        <v>293</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="27">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+      <c r="B42" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C42" s="70"/>
+      <c r="D42" s="70"/>
+      <c r="E42" s="70"/>
+      <c r="F42" s="70"/>
+      <c r="G42" s="70"/>
+      <c r="H42" s="70"/>
+      <c r="I42" s="70"/>
+      <c r="J42" s="71"/>
+      <c r="K42" s="72"/>
+      <c r="L42" s="55"/>
+      <c r="M42" s="73"/>
+      <c r="N42" s="74"/>
+      <c r="O42" s="70"/>
+      <c r="P42" s="71"/>
+      <c r="Q42" s="71"/>
+      <c r="R42" s="72"/>
+      <c r="S42" s="55"/>
+      <c r="T42" s="75"/>
+      <c r="U42" s="75"/>
+      <c r="V42" s="75"/>
+    </row>
+    <row r="43" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="27">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="B43" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="C43" s="65">
+        <f>8856+19764+7452+19</f>
+        <v>36091</v>
+      </c>
+      <c r="D43" s="65"/>
+      <c r="E43" s="65"/>
+      <c r="F43" s="65"/>
+      <c r="G43" s="65"/>
+      <c r="H43" s="65">
+        <v>3</v>
+      </c>
+      <c r="I43" s="65">
+        <v>12</v>
+      </c>
+      <c r="J43" s="66">
+        <f>27*6+4</f>
+        <v>166</v>
+      </c>
+      <c r="K43" s="67">
+        <f>69*6+1</f>
+        <v>415</v>
+      </c>
+      <c r="L43" s="62"/>
+      <c r="M43" s="63">
+        <v>799</v>
+      </c>
+      <c r="N43" s="64"/>
+      <c r="O43" s="65">
+        <v>331</v>
+      </c>
+      <c r="P43" s="66"/>
+      <c r="Q43" s="66">
+        <v>550</v>
+      </c>
+      <c r="R43" s="67"/>
+      <c r="S43" s="62"/>
+      <c r="T43" s="77">
+        <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
+        <v>596</v>
+      </c>
+      <c r="U43" s="77">
+        <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
+        <v>227222</v>
+      </c>
+      <c r="V43" s="77">
+        <f>U43/6</f>
+        <v>37870.333333333336</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="27">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+      <c r="B44" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="70"/>
+      <c r="D44" s="70"/>
+      <c r="E44" s="70"/>
+      <c r="F44" s="70"/>
+      <c r="G44" s="70"/>
+      <c r="H44" s="70"/>
+      <c r="I44" s="70"/>
+      <c r="J44" s="71"/>
+      <c r="K44" s="72"/>
+      <c r="L44" s="55"/>
+      <c r="M44" s="73"/>
+      <c r="N44" s="74"/>
+      <c r="O44" s="70"/>
+      <c r="P44" s="71"/>
+      <c r="Q44" s="71"/>
+      <c r="R44" s="72"/>
+      <c r="S44" s="55"/>
+      <c r="T44" s="75"/>
+      <c r="U44" s="75"/>
+      <c r="V44" s="75"/>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A45" s="27">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="B45" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="70"/>
+      <c r="D45" s="70"/>
+      <c r="E45" s="70"/>
+      <c r="F45" s="70"/>
+      <c r="G45" s="70"/>
+      <c r="H45" s="70"/>
+      <c r="I45" s="70"/>
+      <c r="J45" s="71"/>
+      <c r="K45" s="72"/>
+      <c r="L45" s="55"/>
+      <c r="M45" s="73"/>
+      <c r="N45" s="74"/>
+      <c r="O45" s="70"/>
+      <c r="P45" s="71"/>
+      <c r="Q45" s="71"/>
+      <c r="R45" s="72"/>
+      <c r="S45" s="55"/>
+      <c r="T45" s="75">
+        <f t="shared" ref="T45:T54" si="7">H45+I45+J45+K45+N45+P45+R45</f>
+        <v>0</v>
+      </c>
+      <c r="U45" s="75">
+        <f>C45*24+M45*24+O45*24+Q45*24+T45</f>
+        <v>0</v>
+      </c>
+      <c r="V45" s="75">
+        <f>U45/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A46" s="27">
+        <f t="shared" si="1"/>
+        <v>43</v>
+      </c>
+      <c r="B46" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="C46" s="70"/>
+      <c r="D46" s="70"/>
+      <c r="E46" s="70"/>
+      <c r="F46" s="70"/>
+      <c r="G46" s="70"/>
+      <c r="H46" s="70"/>
+      <c r="I46" s="70"/>
+      <c r="J46" s="71"/>
+      <c r="K46" s="72"/>
+      <c r="L46" s="55"/>
+      <c r="M46" s="73"/>
+      <c r="N46" s="74"/>
+      <c r="O46" s="70"/>
+      <c r="P46" s="71"/>
+      <c r="Q46" s="71"/>
+      <c r="R46" s="72"/>
+      <c r="S46" s="55"/>
+      <c r="T46" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U46" s="75">
+        <f t="shared" ref="U46:U50" si="8">C46*24+M46*24+O46*24+Q46*24+T46</f>
+        <v>0</v>
+      </c>
+      <c r="V46" s="75">
+        <f t="shared" ref="V46:V54" si="9">U46/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="27">
+        <f t="shared" si="1"/>
+        <v>44</v>
+      </c>
+      <c r="B47" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="C47" s="65">
+        <f>89+648+324+88+432+83+103+324+432+106</f>
+        <v>2629</v>
+      </c>
+      <c r="D47" s="65"/>
+      <c r="E47" s="65"/>
+      <c r="F47" s="65"/>
+      <c r="G47" s="65"/>
+      <c r="H47" s="65">
+        <v>1</v>
+      </c>
+      <c r="I47" s="65"/>
+      <c r="J47" s="66"/>
+      <c r="K47" s="67">
+        <v>5</v>
+      </c>
+      <c r="L47" s="62"/>
+      <c r="M47" s="63">
+        <v>2</v>
+      </c>
+      <c r="N47" s="64"/>
+      <c r="O47" s="65">
+        <v>15</v>
+      </c>
+      <c r="P47" s="66"/>
+      <c r="Q47" s="66">
+        <v>5</v>
+      </c>
+      <c r="R47" s="67">
+        <v>3</v>
+      </c>
+      <c r="S47" s="62"/>
+      <c r="T47" s="77">
+        <f t="shared" si="7"/>
+        <v>9</v>
+      </c>
+      <c r="U47" s="77">
+        <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
+        <v>15915</v>
+      </c>
+      <c r="V47" s="77">
+        <f>U47/6</f>
+        <v>2652.5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A48" s="27">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="B48" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C48" s="70"/>
+      <c r="D48" s="70"/>
+      <c r="E48" s="70"/>
+      <c r="F48" s="70"/>
+      <c r="G48" s="70"/>
+      <c r="H48" s="70">
+        <v>24</v>
+      </c>
+      <c r="I48" s="70"/>
+      <c r="J48" s="71"/>
+      <c r="K48" s="72"/>
+      <c r="L48" s="55"/>
+      <c r="M48" s="73"/>
+      <c r="N48" s="74"/>
+      <c r="O48" s="70"/>
+      <c r="P48" s="71"/>
+      <c r="Q48" s="71"/>
+      <c r="R48" s="72"/>
+      <c r="S48" s="55"/>
+      <c r="T48" s="75">
+        <f t="shared" si="7"/>
+        <v>24</v>
+      </c>
+      <c r="U48" s="75">
+        <f t="shared" si="8"/>
+        <v>24</v>
+      </c>
+      <c r="V48" s="75">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A49" s="27">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="B49" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C49" s="70"/>
+      <c r="D49" s="70"/>
+      <c r="E49" s="70"/>
+      <c r="F49" s="70"/>
+      <c r="G49" s="70"/>
+      <c r="H49" s="70"/>
+      <c r="I49" s="70"/>
+      <c r="J49" s="71"/>
+      <c r="K49" s="72"/>
+      <c r="L49" s="55"/>
+      <c r="M49" s="73"/>
+      <c r="N49" s="74"/>
+      <c r="O49" s="70"/>
+      <c r="P49" s="71"/>
+      <c r="Q49" s="71"/>
+      <c r="R49" s="72"/>
+      <c r="S49" s="55"/>
+      <c r="T49" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U49" s="75">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V49" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A50" s="27">
+        <f t="shared" si="1"/>
+        <v>47</v>
+      </c>
+      <c r="B50" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="C50" s="70"/>
+      <c r="D50" s="70"/>
+      <c r="E50" s="70"/>
+      <c r="F50" s="70"/>
+      <c r="G50" s="70"/>
+      <c r="H50" s="70"/>
+      <c r="I50" s="70"/>
+      <c r="J50" s="71"/>
+      <c r="K50" s="72"/>
+      <c r="L50" s="55"/>
+      <c r="M50" s="73"/>
+      <c r="N50" s="74"/>
+      <c r="O50" s="70"/>
+      <c r="P50" s="71"/>
+      <c r="Q50" s="71"/>
+      <c r="R50" s="72"/>
+      <c r="S50" s="55"/>
+      <c r="T50" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U50" s="75">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V50" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="27">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+      <c r="B51" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="C51" s="65">
+        <v>34</v>
+      </c>
+      <c r="D51" s="65"/>
+      <c r="E51" s="65"/>
+      <c r="F51" s="65"/>
+      <c r="G51" s="65"/>
+      <c r="H51" s="65"/>
+      <c r="I51" s="65"/>
+      <c r="J51" s="66"/>
+      <c r="K51" s="67"/>
+      <c r="L51" s="62"/>
+      <c r="M51" s="63"/>
+      <c r="N51" s="64"/>
+      <c r="O51" s="65"/>
+      <c r="P51" s="66"/>
+      <c r="Q51" s="66"/>
+      <c r="R51" s="67"/>
+      <c r="S51" s="62"/>
+      <c r="T51" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U51" s="77">
+        <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
+        <v>204</v>
+      </c>
+      <c r="V51" s="77">
+        <f>U51/6</f>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A52" s="27">
+        <f t="shared" si="1"/>
+        <v>49</v>
+      </c>
+      <c r="B52" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="C52" s="70"/>
+      <c r="D52" s="70"/>
+      <c r="E52" s="70"/>
+      <c r="F52" s="70"/>
+      <c r="G52" s="70"/>
+      <c r="H52" s="70"/>
+      <c r="I52" s="70"/>
+      <c r="J52" s="71"/>
+      <c r="K52" s="72"/>
+      <c r="L52" s="55"/>
+      <c r="M52" s="73"/>
+      <c r="N52" s="74"/>
+      <c r="O52" s="70"/>
+      <c r="P52" s="71"/>
+      <c r="Q52" s="71"/>
+      <c r="R52" s="72"/>
+      <c r="S52" s="55"/>
+      <c r="T52" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U52" s="75">
+        <f t="shared" ref="U52:U54" si="10">C52*24+M52*24+O52*24+Q52*24+T52</f>
+        <v>0</v>
+      </c>
+      <c r="V52" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A53" s="27">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="B53" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C53" s="70">
+        <v>7</v>
+      </c>
+      <c r="D53" s="70"/>
+      <c r="E53" s="70"/>
+      <c r="F53" s="70"/>
+      <c r="G53" s="70"/>
+      <c r="H53" s="70"/>
+      <c r="I53" s="70"/>
+      <c r="J53" s="71"/>
+      <c r="K53" s="72"/>
+      <c r="L53" s="55"/>
+      <c r="M53" s="73"/>
+      <c r="N53" s="74"/>
+      <c r="O53" s="70"/>
+      <c r="P53" s="71"/>
+      <c r="Q53" s="71"/>
+      <c r="R53" s="72"/>
+      <c r="S53" s="55"/>
+      <c r="T53" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U53" s="75">
+        <f t="shared" si="10"/>
+        <v>168</v>
+      </c>
+      <c r="V53" s="75">
+        <f t="shared" si="9"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A54" s="27">
+        <f t="shared" si="1"/>
+        <v>51</v>
+      </c>
+      <c r="B54" s="26"/>
+      <c r="C54" s="70"/>
+      <c r="D54" s="70"/>
+      <c r="E54" s="70"/>
+      <c r="F54" s="70"/>
+      <c r="G54" s="70"/>
+      <c r="H54" s="70"/>
+      <c r="I54" s="70"/>
+      <c r="J54" s="71"/>
+      <c r="K54" s="72"/>
+      <c r="L54" s="55"/>
+      <c r="M54" s="73"/>
+      <c r="N54" s="74"/>
+      <c r="O54" s="70"/>
+      <c r="P54" s="71"/>
+      <c r="Q54" s="71"/>
+      <c r="R54" s="72"/>
+      <c r="S54" s="55"/>
+      <c r="T54" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U54" s="75">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V54" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A55" s="27">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="B55" s="26"/>
+      <c r="C55" s="70"/>
+      <c r="D55" s="70"/>
+      <c r="E55" s="70"/>
+      <c r="F55" s="70"/>
+      <c r="G55" s="70"/>
+      <c r="H55" s="70"/>
+      <c r="I55" s="70"/>
+      <c r="J55" s="71"/>
+      <c r="K55" s="72"/>
+      <c r="L55" s="55"/>
+      <c r="M55" s="73"/>
+      <c r="N55" s="74"/>
+      <c r="O55" s="70"/>
+      <c r="P55" s="71"/>
+      <c r="Q55" s="71"/>
+      <c r="R55" s="72"/>
+      <c r="S55" s="55"/>
+      <c r="T55" s="75"/>
+      <c r="U55" s="75"/>
+      <c r="V55" s="75"/>
+    </row>
+    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A56" s="27">
+        <f t="shared" si="1"/>
+        <v>53</v>
+      </c>
+      <c r="B56" s="26"/>
+      <c r="C56" s="70"/>
+      <c r="D56" s="70"/>
+      <c r="E56" s="70"/>
+      <c r="F56" s="70"/>
+      <c r="G56" s="70"/>
+      <c r="H56" s="70"/>
+      <c r="I56" s="70"/>
+      <c r="J56" s="71"/>
+      <c r="K56" s="72"/>
+      <c r="L56" s="55"/>
+      <c r="M56" s="73"/>
+      <c r="N56" s="74"/>
+      <c r="O56" s="70"/>
+      <c r="P56" s="71"/>
+      <c r="Q56" s="71"/>
+      <c r="R56" s="72"/>
+      <c r="S56" s="55"/>
+      <c r="T56" s="75"/>
+      <c r="U56" s="75"/>
+      <c r="V56" s="75"/>
+    </row>
+    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A57" s="27">
+        <f t="shared" si="1"/>
+        <v>54</v>
+      </c>
+      <c r="B57" s="26"/>
+      <c r="C57" s="70"/>
+      <c r="D57" s="70"/>
+      <c r="E57" s="70"/>
+      <c r="F57" s="70"/>
+      <c r="G57" s="70"/>
+      <c r="H57" s="70"/>
+      <c r="I57" s="70"/>
+      <c r="J57" s="71"/>
+      <c r="K57" s="72"/>
+      <c r="L57" s="55"/>
+      <c r="M57" s="73"/>
+      <c r="N57" s="74"/>
+      <c r="O57" s="70"/>
+      <c r="P57" s="71"/>
+      <c r="Q57" s="71"/>
+      <c r="R57" s="72"/>
+      <c r="S57" s="55"/>
+      <c r="T57" s="75"/>
+      <c r="U57" s="75"/>
+      <c r="V57" s="75"/>
+    </row>
+    <row r="58" spans="1:22" s="15" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B58" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="C58" s="2">
+        <f>SUM(C7:C57)</f>
+        <v>45899</v>
+      </c>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2">
+        <f t="shared" ref="F58:K58" si="11">SUM(F7:F57)</f>
+        <v>0</v>
+      </c>
+      <c r="G58" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="H58" s="2">
+        <f t="shared" si="11"/>
+        <v>1190</v>
+      </c>
+      <c r="I58" s="6">
+        <f t="shared" si="11"/>
+        <v>44</v>
+      </c>
+      <c r="J58" s="6">
+        <f t="shared" si="11"/>
+        <v>172</v>
+      </c>
+      <c r="K58" s="6">
+        <f t="shared" si="11"/>
+        <v>457</v>
+      </c>
+      <c r="M58" s="5">
+        <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
+        <v>862</v>
+      </c>
+      <c r="N58" s="5">
+        <f t="shared" si="12"/>
+        <v>10</v>
+      </c>
+      <c r="O58" s="5">
+        <f t="shared" si="12"/>
+        <v>366</v>
+      </c>
+      <c r="P58" s="5">
+        <f t="shared" si="12"/>
+        <v>24</v>
+      </c>
+      <c r="Q58" s="5">
+        <f t="shared" si="12"/>
+        <v>743</v>
+      </c>
+      <c r="R58" s="5">
+        <f t="shared" si="12"/>
+        <v>3</v>
+      </c>
+      <c r="S58" s="55"/>
+      <c r="T58" s="4">
+        <f>SUM(T7:T57)</f>
+        <v>1900</v>
+      </c>
+      <c r="U58" s="90">
+        <f>SUM(U7:U57)</f>
+        <v>360718</v>
+      </c>
+      <c r="V58" s="4">
+        <f>SUM(V7:V57)</f>
+        <v>48027.166666666672</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="60" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="C60" s="110" t="s">
+        <v>41</v>
+      </c>
+      <c r="D60" s="111"/>
+      <c r="E60" s="111"/>
+      <c r="F60" s="111"/>
+      <c r="G60" s="111"/>
+      <c r="H60" s="111"/>
+      <c r="I60" s="111"/>
+      <c r="J60" s="111"/>
+      <c r="K60" s="112"/>
+      <c r="U60" s="24" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B61" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="C61" s="19"/>
+      <c r="D61" s="19"/>
+      <c r="E61" s="19"/>
+      <c r="F61" s="19"/>
+      <c r="G61" s="19"/>
+      <c r="H61" s="19"/>
+      <c r="I61" s="19"/>
+      <c r="J61" s="45"/>
+      <c r="K61" s="20"/>
+      <c r="U61" s="7"/>
+    </row>
+    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B62" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+      <c r="J62" s="44"/>
+      <c r="K62" s="21"/>
+      <c r="U62" s="3"/>
+    </row>
+    <row r="63" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B63" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C63" s="22"/>
+      <c r="D63" s="22"/>
+      <c r="E63" s="22"/>
+      <c r="F63" s="22"/>
+      <c r="G63" s="22"/>
+      <c r="H63" s="22"/>
+      <c r="I63" s="22"/>
+      <c r="J63" s="46"/>
+      <c r="K63" s="23"/>
+      <c r="U63" s="8"/>
+    </row>
+    <row r="64" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B65" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="C65" s="19"/>
+      <c r="D65" s="19"/>
+      <c r="E65" s="19"/>
+      <c r="F65" s="19"/>
+      <c r="G65" s="19"/>
+      <c r="H65" s="19"/>
+      <c r="I65" s="19"/>
+      <c r="J65" s="45"/>
+      <c r="K65" s="20"/>
+      <c r="U65" s="7"/>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B66" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C66" s="1"/>
+      <c r="D66" s="1"/>
+      <c r="E66" s="1"/>
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="J66" s="44"/>
+      <c r="K66" s="21"/>
+      <c r="U66" s="3"/>
+    </row>
+    <row r="67" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B67" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C67" s="22"/>
+      <c r="D67" s="22"/>
+      <c r="E67" s="22"/>
+      <c r="F67" s="22"/>
+      <c r="G67" s="22"/>
+      <c r="H67" s="22"/>
+      <c r="I67" s="22"/>
+      <c r="J67" s="46"/>
+      <c r="K67" s="23"/>
+      <c r="U67" s="8"/>
+    </row>
+    <row r="68" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B69" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="C69" s="19"/>
+      <c r="D69" s="19"/>
+      <c r="E69" s="19"/>
+      <c r="F69" s="19"/>
+      <c r="G69" s="19"/>
+      <c r="H69" s="19"/>
+      <c r="I69" s="19"/>
+      <c r="J69" s="45"/>
+      <c r="K69" s="20"/>
+      <c r="U69" s="7"/>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B70" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="J70" s="44"/>
+      <c r="K70" s="21"/>
+      <c r="U70" s="3"/>
+    </row>
+    <row r="71" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B71" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C71" s="22"/>
+      <c r="D71" s="22"/>
+      <c r="E71" s="22"/>
+      <c r="F71" s="22"/>
+      <c r="G71" s="22"/>
+      <c r="H71" s="22"/>
+      <c r="I71" s="22"/>
+      <c r="J71" s="46"/>
+      <c r="K71" s="23"/>
+      <c r="U71" s="8"/>
+    </row>
+    <row r="72" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B73" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="C73" s="19"/>
+      <c r="D73" s="19"/>
+      <c r="E73" s="19"/>
+      <c r="F73" s="19"/>
+      <c r="G73" s="19"/>
+      <c r="H73" s="19"/>
+      <c r="I73" s="19"/>
+      <c r="J73" s="45"/>
+      <c r="K73" s="20"/>
+      <c r="U73" s="7"/>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B74" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C74" s="1"/>
+      <c r="D74" s="1"/>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1"/>
+      <c r="J74" s="44"/>
+      <c r="K74" s="21"/>
+      <c r="U74" s="3"/>
+    </row>
+    <row r="75" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B75" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C75" s="22"/>
+      <c r="D75" s="22"/>
+      <c r="E75" s="22"/>
+      <c r="F75" s="22"/>
+      <c r="G75" s="22"/>
+      <c r="H75" s="22"/>
+      <c r="I75" s="22"/>
+      <c r="J75" s="46"/>
+      <c r="K75" s="23"/>
+      <c r="U75" s="8"/>
+    </row>
+    <row r="76" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B77" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="C77" s="19"/>
+      <c r="D77" s="19"/>
+      <c r="E77" s="19"/>
+      <c r="F77" s="19"/>
+      <c r="G77" s="19"/>
+      <c r="H77" s="19"/>
+      <c r="I77" s="19"/>
+      <c r="J77" s="45"/>
+      <c r="K77" s="20"/>
+      <c r="U77" s="7"/>
+    </row>
+    <row r="78" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B78" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C78" s="1"/>
+      <c r="D78" s="1"/>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+      <c r="J78" s="44"/>
+      <c r="K78" s="21"/>
+      <c r="U78" s="3"/>
+    </row>
+    <row r="79" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B79" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C79" s="22"/>
+      <c r="D79" s="22"/>
+      <c r="E79" s="22"/>
+      <c r="F79" s="22"/>
+      <c r="G79" s="22"/>
+      <c r="H79" s="22"/>
+      <c r="I79" s="22"/>
+      <c r="J79" s="46"/>
+      <c r="K79" s="23"/>
+      <c r="U79" s="8"/>
+    </row>
+    <row r="80" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="81" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B81" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="C81" s="17"/>
+      <c r="D81" s="17"/>
+      <c r="E81" s="17"/>
+      <c r="F81" s="17"/>
+      <c r="G81" s="17"/>
+      <c r="H81" s="17"/>
+      <c r="I81" s="17"/>
+      <c r="J81" s="47"/>
+      <c r="K81" s="18"/>
+      <c r="U81" s="16"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="C60:K60"/>
+    <mergeCell ref="I1:U1"/>
+    <mergeCell ref="C4:K4"/>
+    <mergeCell ref="T4:T5"/>
+    <mergeCell ref="U4:U5"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
+  <pageSetup paperSize="14" scale="70" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="24" max="80" man="1"/>
+  </colBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B602C5D-37D6-4617-B02F-10237C64E9FC}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BB81"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="28" customWidth="1"/>
+    <col min="3" max="6" width="10" style="9" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" style="9" customWidth="1"/>
+    <col min="8" max="8" width="7.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.85546875" style="9" customWidth="1"/>
+    <col min="11" max="11" width="7.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.42578125" style="9" customWidth="1"/>
+    <col min="13" max="13" width="10" style="9" customWidth="1"/>
+    <col min="14" max="14" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" style="9" customWidth="1"/>
+    <col min="16" max="16" width="5.5703125" style="9" customWidth="1"/>
+    <col min="17" max="17" width="10" style="9" customWidth="1"/>
+    <col min="18" max="18" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="1.42578125" style="9" customWidth="1"/>
+    <col min="20" max="20" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="9" customWidth="1"/>
+    <col min="22" max="22" width="19.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="23" max="49" width="7.28515625" style="9" customWidth="1"/>
+    <col min="50" max="50" width="1.5703125" style="9" customWidth="1"/>
+    <col min="51" max="51" width="9.42578125" style="9" customWidth="1"/>
+    <col min="52" max="52" width="1.28515625" style="9" customWidth="1"/>
+    <col min="53" max="53" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="10.28515625" style="9" bestFit="1" customWidth="1"/>
+    <col min="55" max="16384" width="9.140625" style="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="113" t="s">
+        <v>43</v>
+      </c>
+      <c r="J1" s="113"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="113"/>
+      <c r="M1" s="113"/>
+      <c r="N1" s="113"/>
+      <c r="O1" s="113"/>
+      <c r="P1" s="113"/>
+      <c r="Q1" s="113"/>
+      <c r="R1" s="113"/>
+      <c r="S1" s="113"/>
+      <c r="T1" s="113"/>
+      <c r="U1" s="113"/>
+    </row>
+    <row r="2" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="B2" s="28" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B4" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="114" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="114"/>
+      <c r="E4" s="114"/>
+      <c r="F4" s="114"/>
+      <c r="G4" s="114"/>
+      <c r="H4" s="114"/>
+      <c r="I4" s="114"/>
+      <c r="J4" s="115"/>
+      <c r="K4" s="116"/>
+      <c r="M4" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="N4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="O4" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="P4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q4" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="R4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="S4" s="9"/>
+      <c r="T4" s="117" t="s">
+        <v>68</v>
+      </c>
+      <c r="U4" s="123" t="s">
+        <v>67</v>
+      </c>
+      <c r="V4" s="106" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF4" s="11"/>
+      <c r="AG4" s="11"/>
+      <c r="AH4" s="11"/>
+      <c r="AI4" s="11"/>
+      <c r="AJ4" s="11"/>
+      <c r="AK4" s="11"/>
+      <c r="AL4" s="11"/>
+      <c r="AM4" s="11"/>
+      <c r="AN4" s="11"/>
+      <c r="AO4" s="11"/>
+      <c r="AP4" s="11"/>
+      <c r="AQ4" s="11"/>
+      <c r="AR4" s="11"/>
+      <c r="AS4" s="11"/>
+      <c r="AT4" s="11"/>
+      <c r="AU4" s="11"/>
+      <c r="AV4" s="11"/>
+      <c r="AW4" s="11"/>
+      <c r="AX4" s="11"/>
+      <c r="AY4" s="11"/>
+      <c r="AZ4" s="11"/>
+      <c r="BA4" s="11"/>
+      <c r="BB4" s="11"/>
+    </row>
+    <row r="5" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="37"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40" t="s">
+        <v>64</v>
+      </c>
+      <c r="I5" s="40" t="s">
+        <v>60</v>
+      </c>
+      <c r="J5" s="121" t="s">
+        <v>65</v>
+      </c>
+      <c r="K5" s="122"/>
+      <c r="M5" s="37"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="40"/>
+      <c r="P5" s="105"/>
+      <c r="Q5" s="105"/>
+      <c r="R5" s="38"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="118"/>
+      <c r="U5" s="124"/>
+      <c r="V5" s="107"/>
+      <c r="AF5" s="11"/>
+      <c r="AG5" s="11"/>
+      <c r="AH5" s="11"/>
+      <c r="AI5" s="11"/>
+      <c r="AJ5" s="11"/>
+      <c r="AK5" s="11"/>
+      <c r="AL5" s="11"/>
+      <c r="AM5" s="11"/>
+      <c r="AN5" s="11"/>
+      <c r="AO5" s="11"/>
+      <c r="AP5" s="11"/>
+      <c r="AQ5" s="11"/>
+      <c r="AR5" s="11"/>
+      <c r="AS5" s="11"/>
+      <c r="AT5" s="11"/>
+      <c r="AU5" s="11"/>
+      <c r="AV5" s="11"/>
+      <c r="AW5" s="11"/>
+      <c r="AX5" s="11"/>
+      <c r="AY5" s="11"/>
+      <c r="AZ5" s="11"/>
+      <c r="BA5" s="11"/>
+      <c r="BB5" s="11"/>
+    </row>
+    <row r="6" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="37"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="105"/>
+      <c r="K6" s="38"/>
+      <c r="M6" s="37"/>
+      <c r="N6" s="49"/>
+      <c r="O6" s="40"/>
+      <c r="P6" s="105"/>
+      <c r="Q6" s="105"/>
+      <c r="R6" s="38"/>
+      <c r="S6" s="9"/>
+      <c r="T6" s="39"/>
+      <c r="U6" s="39"/>
+      <c r="V6" s="39"/>
+      <c r="AF6" s="11"/>
+      <c r="AG6" s="11"/>
+      <c r="AH6" s="11"/>
+      <c r="AI6" s="11"/>
+      <c r="AJ6" s="11"/>
+      <c r="AK6" s="11"/>
+      <c r="AL6" s="11"/>
+      <c r="AM6" s="11"/>
+      <c r="AN6" s="11"/>
+      <c r="AO6" s="11"/>
+      <c r="AP6" s="11"/>
+      <c r="AQ6" s="11"/>
+      <c r="AR6" s="11"/>
+      <c r="AS6" s="11"/>
+      <c r="AT6" s="11"/>
+      <c r="AU6" s="11"/>
+      <c r="AV6" s="11"/>
+      <c r="AW6" s="11"/>
+      <c r="AX6" s="11"/>
+      <c r="AY6" s="11"/>
+      <c r="AZ6" s="11"/>
+      <c r="BA6" s="11"/>
+      <c r="BB6" s="11"/>
+    </row>
+    <row r="7" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A7" s="27">
+        <v>1</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="52">
+        <v>30</v>
+      </c>
+      <c r="D7" s="52"/>
+      <c r="E7" s="52"/>
+      <c r="F7" s="52"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="52"/>
+      <c r="I7" s="52">
+        <v>3</v>
+      </c>
+      <c r="J7" s="53"/>
+      <c r="K7" s="54">
+        <v>6</v>
+      </c>
+      <c r="L7" s="55"/>
+      <c r="M7" s="56"/>
+      <c r="N7" s="57"/>
+      <c r="O7" s="52">
+        <v>1</v>
+      </c>
+      <c r="P7" s="53"/>
+      <c r="Q7" s="53"/>
+      <c r="R7" s="54"/>
+      <c r="S7" s="55"/>
+      <c r="T7" s="58">
+        <f>H7+I7+J7+K7+N7+P7+R7</f>
+        <v>9</v>
+      </c>
+      <c r="U7" s="58">
+        <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
+        <v>753</v>
+      </c>
+      <c r="V7" s="58">
+        <f>U7/24</f>
+        <v>31.375</v>
+      </c>
+      <c r="W7" s="50"/>
+      <c r="AF7" s="12"/>
+      <c r="AG7" s="12"/>
+      <c r="AH7" s="12"/>
+      <c r="AI7" s="12"/>
+      <c r="AJ7" s="12"/>
+      <c r="AK7" s="12"/>
+      <c r="AL7" s="12"/>
+      <c r="AM7" s="12"/>
+      <c r="AN7" s="12"/>
+      <c r="AO7" s="12"/>
+      <c r="AP7" s="12"/>
+      <c r="AQ7" s="12"/>
+      <c r="AR7" s="12"/>
+      <c r="AS7" s="12"/>
+      <c r="AT7" s="12"/>
+      <c r="AU7" s="12"/>
+      <c r="AV7" s="12"/>
+      <c r="AW7" s="12"/>
+      <c r="AX7" s="12"/>
+      <c r="AY7" s="12"/>
+      <c r="AZ7" s="12"/>
+      <c r="BA7" s="12"/>
+      <c r="BB7" s="12"/>
+    </row>
+    <row r="8" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="27">
+        <f>A7+1</f>
+        <v>2</v>
+      </c>
+      <c r="B8" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="59">
+        <f>37+30</f>
+        <v>67</v>
+      </c>
+      <c r="D8" s="59"/>
+      <c r="E8" s="59"/>
+      <c r="F8" s="59"/>
+      <c r="G8" s="59"/>
+      <c r="H8" s="59"/>
+      <c r="I8" s="59"/>
+      <c r="J8" s="60"/>
+      <c r="K8" s="61"/>
+      <c r="L8" s="62"/>
+      <c r="M8" s="63">
+        <v>1</v>
+      </c>
+      <c r="N8" s="64"/>
+      <c r="O8" s="65">
+        <v>1</v>
+      </c>
+      <c r="P8" s="66">
+        <v>12</v>
+      </c>
+      <c r="Q8" s="66">
+        <v>2</v>
+      </c>
+      <c r="R8" s="67"/>
+      <c r="S8" s="62"/>
+      <c r="T8" s="68">
+        <f t="shared" ref="T8:T41" si="0">H8+I8+J8+K8+N8+P8+R8</f>
+        <v>12</v>
+      </c>
+      <c r="U8" s="69">
+        <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
+        <v>1716</v>
+      </c>
+      <c r="V8" s="69">
+        <f>U8/24</f>
+        <v>71.5</v>
+      </c>
+      <c r="W8" s="50"/>
+      <c r="AF8" s="12"/>
+      <c r="AG8" s="12"/>
+      <c r="AH8" s="12"/>
+      <c r="AI8" s="12"/>
+      <c r="AJ8" s="12"/>
+      <c r="AK8" s="12"/>
+      <c r="AL8" s="12"/>
+      <c r="AM8" s="12"/>
+      <c r="AN8" s="12"/>
+      <c r="AO8" s="12"/>
+      <c r="AP8" s="12"/>
+      <c r="AQ8" s="12"/>
+      <c r="AR8" s="12"/>
+      <c r="AS8" s="12"/>
+      <c r="AT8" s="12"/>
+      <c r="AU8" s="12"/>
+      <c r="AV8" s="12"/>
+      <c r="AW8" s="12"/>
+      <c r="AX8" s="12"/>
+      <c r="AY8" s="12"/>
+      <c r="AZ8" s="12"/>
+      <c r="BA8" s="12"/>
+      <c r="BB8" s="12"/>
+    </row>
+    <row r="9" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A9" s="27">
+        <f t="shared" ref="A9:A57" si="1">A8+1</f>
+        <v>3</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="70">
+        <f>24+30</f>
+        <v>54</v>
+      </c>
+      <c r="D9" s="70"/>
+      <c r="E9" s="70"/>
+      <c r="F9" s="70"/>
+      <c r="G9" s="70"/>
+      <c r="H9" s="70"/>
+      <c r="I9" s="70"/>
+      <c r="J9" s="71"/>
+      <c r="K9" s="72"/>
+      <c r="L9" s="55"/>
+      <c r="M9" s="73"/>
+      <c r="N9" s="74"/>
+      <c r="O9" s="70">
+        <v>1</v>
+      </c>
+      <c r="P9" s="71"/>
+      <c r="Q9" s="71"/>
+      <c r="R9" s="72"/>
+      <c r="S9" s="55"/>
+      <c r="T9" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U9" s="76">
+        <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
+        <v>1320</v>
+      </c>
+      <c r="V9" s="76">
+        <f t="shared" ref="V9:V11" si="3">U9/24</f>
+        <v>55</v>
+      </c>
+      <c r="W9" s="50"/>
+      <c r="AF9" s="12"/>
+      <c r="AG9" s="12"/>
+      <c r="AH9" s="12"/>
+      <c r="AI9" s="12"/>
+      <c r="AJ9" s="12"/>
+      <c r="AK9" s="12"/>
+      <c r="AL9" s="12"/>
+      <c r="AM9" s="12"/>
+      <c r="AN9" s="12"/>
+      <c r="AO9" s="12"/>
+      <c r="AP9" s="12"/>
+      <c r="AQ9" s="12"/>
+      <c r="AR9" s="12"/>
+      <c r="AS9" s="12"/>
+      <c r="AT9" s="12"/>
+      <c r="AU9" s="12"/>
+      <c r="AV9" s="12"/>
+      <c r="AW9" s="12"/>
+      <c r="AX9" s="12"/>
+      <c r="AY9" s="12"/>
+      <c r="AZ9" s="12"/>
+      <c r="BA9" s="12"/>
+      <c r="BB9" s="12"/>
+    </row>
+    <row r="10" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A10" s="27">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="70">
+        <f>3+10</f>
+        <v>13</v>
+      </c>
+      <c r="D10" s="70"/>
+      <c r="E10" s="70"/>
+      <c r="F10" s="70"/>
+      <c r="G10" s="70"/>
+      <c r="H10" s="70"/>
+      <c r="I10" s="70"/>
+      <c r="J10" s="71"/>
+      <c r="K10" s="72"/>
+      <c r="L10" s="55"/>
+      <c r="M10" s="73"/>
+      <c r="N10" s="74"/>
+      <c r="O10" s="70">
+        <v>1</v>
+      </c>
+      <c r="P10" s="71"/>
+      <c r="Q10" s="71"/>
+      <c r="R10" s="72"/>
+      <c r="S10" s="55"/>
+      <c r="T10" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U10" s="58">
+        <f t="shared" si="2"/>
+        <v>336</v>
+      </c>
+      <c r="V10" s="58">
+        <f t="shared" si="3"/>
+        <v>14</v>
+      </c>
+      <c r="W10" s="50"/>
+      <c r="AF10" s="12"/>
+      <c r="AG10" s="12"/>
+      <c r="AH10" s="12"/>
+      <c r="AI10" s="12"/>
+      <c r="AJ10" s="12"/>
+      <c r="AK10" s="12"/>
+      <c r="AL10" s="12"/>
+      <c r="AM10" s="12"/>
+      <c r="AN10" s="12"/>
+      <c r="AO10" s="12"/>
+      <c r="AP10" s="12"/>
+      <c r="AQ10" s="12"/>
+      <c r="AR10" s="12"/>
+      <c r="AS10" s="12"/>
+      <c r="AT10" s="12"/>
+      <c r="AU10" s="12"/>
+      <c r="AV10" s="12"/>
+      <c r="AW10" s="12"/>
+      <c r="AX10" s="12"/>
+      <c r="AY10" s="12"/>
+      <c r="AZ10" s="12"/>
+      <c r="BA10" s="12"/>
+      <c r="BB10" s="12"/>
+    </row>
+    <row r="11" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A11" s="27">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="70"/>
+      <c r="D11" s="70"/>
+      <c r="E11" s="70"/>
+      <c r="F11" s="70"/>
+      <c r="G11" s="70"/>
+      <c r="H11" s="70"/>
+      <c r="I11" s="70"/>
+      <c r="J11" s="71"/>
+      <c r="K11" s="72">
+        <v>2</v>
+      </c>
+      <c r="L11" s="55"/>
+      <c r="M11" s="73"/>
+      <c r="N11" s="74"/>
+      <c r="O11" s="70"/>
+      <c r="P11" s="71"/>
+      <c r="Q11" s="71"/>
+      <c r="R11" s="72"/>
+      <c r="S11" s="55"/>
+      <c r="T11" s="58">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="U11" s="58">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="V11" s="58">
+        <f t="shared" si="3"/>
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="AF11" s="12"/>
+      <c r="AG11" s="12"/>
+      <c r="AH11" s="12"/>
+      <c r="AI11" s="12"/>
+      <c r="AJ11" s="12"/>
+      <c r="AK11" s="12"/>
+      <c r="AL11" s="12"/>
+      <c r="AM11" s="12"/>
+      <c r="AN11" s="12"/>
+      <c r="AO11" s="12"/>
+      <c r="AP11" s="12"/>
+      <c r="AQ11" s="12"/>
+      <c r="AR11" s="12"/>
+      <c r="AS11" s="12"/>
+      <c r="AT11" s="12"/>
+      <c r="AU11" s="12"/>
+      <c r="AV11" s="12"/>
+      <c r="AW11" s="12"/>
+      <c r="AX11" s="12"/>
+      <c r="AY11" s="12"/>
+      <c r="AZ11" s="12"/>
+      <c r="BA11" s="12"/>
+      <c r="BB11" s="12"/>
+    </row>
+    <row r="12" spans="1:54" s="13" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="27">
+        <v>7</v>
+      </c>
+      <c r="B12" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="59">
+        <f>1224+53+576+41+1080+29</f>
+        <v>3003</v>
+      </c>
+      <c r="D12" s="59"/>
+      <c r="E12" s="59"/>
+      <c r="F12" s="59"/>
+      <c r="G12" s="59"/>
+      <c r="H12" s="59"/>
+      <c r="I12" s="59"/>
+      <c r="J12" s="60"/>
+      <c r="K12" s="61"/>
+      <c r="L12" s="62"/>
+      <c r="M12" s="63">
+        <v>31</v>
+      </c>
+      <c r="N12" s="64">
+        <v>10</v>
+      </c>
+      <c r="O12" s="65">
+        <v>15</v>
+      </c>
+      <c r="P12" s="66">
+        <v>17</v>
+      </c>
+      <c r="Q12" s="66">
+        <v>39</v>
+      </c>
+      <c r="R12" s="67">
+        <v>13</v>
+      </c>
+      <c r="S12" s="62"/>
+      <c r="T12" s="69">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="U12" s="69">
+        <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
+        <v>74152</v>
+      </c>
+      <c r="V12" s="69">
+        <f>U12/24</f>
+        <v>3089.6666666666665</v>
+      </c>
+      <c r="W12" s="9"/>
+      <c r="X12" s="9"/>
+      <c r="Y12" s="9"/>
+      <c r="Z12" s="9"/>
+      <c r="AA12" s="9"/>
+      <c r="AB12" s="9"/>
+      <c r="AC12" s="9"/>
+      <c r="AD12" s="9"/>
+      <c r="AE12" s="9"/>
+      <c r="AF12" s="12"/>
+      <c r="AG12" s="12"/>
+      <c r="AH12" s="12"/>
+      <c r="AI12" s="12"/>
+      <c r="AJ12" s="12"/>
+      <c r="AK12" s="12"/>
+      <c r="AL12" s="12"/>
+      <c r="AM12" s="12"/>
+      <c r="AN12" s="12"/>
+      <c r="AO12" s="12"/>
+      <c r="AP12" s="12"/>
+      <c r="AQ12" s="12"/>
+      <c r="AR12" s="12"/>
+      <c r="AS12" s="12"/>
+      <c r="AT12" s="12"/>
+      <c r="AU12" s="12"/>
+      <c r="AV12" s="12"/>
+      <c r="AW12" s="12"/>
+      <c r="AX12" s="12"/>
+      <c r="AY12" s="12"/>
+      <c r="AZ12" s="12"/>
+      <c r="BA12" s="12"/>
+      <c r="BB12" s="12"/>
+    </row>
+    <row r="13" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A13" s="27">
+        <v>11</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="70">
+        <v>2</v>
+      </c>
+      <c r="D13" s="70"/>
+      <c r="E13" s="70"/>
+      <c r="F13" s="70"/>
+      <c r="G13" s="70"/>
+      <c r="H13" s="70">
+        <v>16</v>
+      </c>
+      <c r="I13" s="70"/>
+      <c r="J13" s="71"/>
+      <c r="K13" s="72"/>
+      <c r="L13" s="55"/>
+      <c r="M13" s="73"/>
+      <c r="N13" s="74"/>
+      <c r="O13" s="70"/>
+      <c r="P13" s="71"/>
+      <c r="Q13" s="71"/>
+      <c r="R13" s="72"/>
+      <c r="S13" s="55"/>
+      <c r="T13" s="76">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="U13" s="76">
+        <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
+        <v>64</v>
+      </c>
+      <c r="V13" s="76">
+        <f>U13/24</f>
+        <v>2.6666666666666665</v>
+      </c>
+      <c r="AF13" s="12"/>
+      <c r="AG13" s="12"/>
+      <c r="AH13" s="12"/>
+      <c r="AI13" s="12"/>
+      <c r="AJ13" s="12"/>
+      <c r="AK13" s="12"/>
+      <c r="AL13" s="12"/>
+      <c r="AM13" s="12"/>
+      <c r="AN13" s="12"/>
+      <c r="AO13" s="12"/>
+      <c r="AP13" s="12"/>
+      <c r="AQ13" s="12"/>
+      <c r="AR13" s="12"/>
+      <c r="AS13" s="12"/>
+      <c r="AT13" s="12"/>
+      <c r="AU13" s="12"/>
+      <c r="AV13" s="12"/>
+      <c r="AW13" s="12"/>
+      <c r="AX13" s="12"/>
+      <c r="AY13" s="12"/>
+      <c r="AZ13" s="12"/>
+      <c r="BA13" s="12"/>
+      <c r="BB13" s="12"/>
+    </row>
+    <row r="14" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A14" s="27">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="70">
+        <v>2</v>
+      </c>
+      <c r="D14" s="70"/>
+      <c r="E14" s="70"/>
+      <c r="F14" s="70"/>
+      <c r="G14" s="70"/>
+      <c r="H14" s="70"/>
+      <c r="I14" s="70"/>
+      <c r="J14" s="71"/>
+      <c r="K14" s="72"/>
+      <c r="L14" s="55"/>
+      <c r="M14" s="73"/>
+      <c r="N14" s="74"/>
+      <c r="O14" s="70"/>
+      <c r="P14" s="71"/>
+      <c r="Q14" s="71"/>
+      <c r="R14" s="72"/>
+      <c r="S14" s="55"/>
+      <c r="T14" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U14" s="75">
+        <f t="shared" ref="U14:U36" si="4">C14*24+M14*24+O14*24+Q14*24+T14</f>
+        <v>48</v>
+      </c>
+      <c r="V14" s="75">
+        <f t="shared" ref="V14:V36" si="5">U14/24</f>
+        <v>2</v>
+      </c>
+      <c r="AF14" s="12"/>
+      <c r="AG14" s="12"/>
+      <c r="AH14" s="12"/>
+      <c r="AI14" s="12"/>
+      <c r="AJ14" s="12"/>
+      <c r="AK14" s="12"/>
+      <c r="AL14" s="12"/>
+      <c r="AM14" s="12"/>
+      <c r="AN14" s="12"/>
+      <c r="AO14" s="12"/>
+      <c r="AP14" s="12"/>
+      <c r="AQ14" s="12"/>
+      <c r="AR14" s="12"/>
+      <c r="AS14" s="12"/>
+      <c r="AT14" s="12"/>
+      <c r="AU14" s="12"/>
+      <c r="AV14" s="12"/>
+      <c r="AW14" s="12"/>
+      <c r="AX14" s="12"/>
+      <c r="AY14" s="12"/>
+      <c r="AZ14" s="12"/>
+      <c r="BA14" s="12"/>
+      <c r="BB14" s="12"/>
+    </row>
+    <row r="15" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A15" s="27">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="70"/>
+      <c r="D15" s="70"/>
+      <c r="E15" s="70"/>
+      <c r="F15" s="70"/>
+      <c r="G15" s="70"/>
+      <c r="H15" s="70"/>
+      <c r="I15" s="70"/>
+      <c r="J15" s="71"/>
+      <c r="K15" s="72"/>
+      <c r="L15" s="55"/>
+      <c r="M15" s="73"/>
+      <c r="N15" s="74"/>
+      <c r="O15" s="70"/>
+      <c r="P15" s="71"/>
+      <c r="Q15" s="71"/>
+      <c r="R15" s="72"/>
+      <c r="S15" s="55"/>
+      <c r="T15" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U15" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF15" s="12"/>
+      <c r="AG15" s="12"/>
+      <c r="AH15" s="12"/>
+      <c r="AI15" s="12"/>
+      <c r="AJ15" s="12"/>
+      <c r="AK15" s="12"/>
+      <c r="AL15" s="12"/>
+      <c r="AM15" s="12"/>
+      <c r="AN15" s="12"/>
+      <c r="AO15" s="12"/>
+      <c r="AP15" s="12"/>
+      <c r="AQ15" s="12"/>
+      <c r="AR15" s="12"/>
+      <c r="AS15" s="12"/>
+      <c r="AT15" s="12"/>
+      <c r="AU15" s="12"/>
+      <c r="AV15" s="12"/>
+      <c r="AW15" s="12"/>
+      <c r="AX15" s="12"/>
+      <c r="AY15" s="12"/>
+      <c r="AZ15" s="12"/>
+      <c r="BA15" s="12"/>
+      <c r="BB15" s="12"/>
+    </row>
+    <row r="16" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A16" s="27">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="70"/>
+      <c r="D16" s="70"/>
+      <c r="E16" s="70"/>
+      <c r="F16" s="70"/>
+      <c r="G16" s="70"/>
+      <c r="H16" s="70"/>
+      <c r="I16" s="70"/>
+      <c r="J16" s="71"/>
+      <c r="K16" s="72"/>
+      <c r="L16" s="55"/>
+      <c r="M16" s="73"/>
+      <c r="N16" s="74"/>
+      <c r="O16" s="70"/>
+      <c r="P16" s="71"/>
+      <c r="Q16" s="71"/>
+      <c r="R16" s="72"/>
+      <c r="S16" s="55"/>
+      <c r="T16" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U16" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF16" s="12"/>
+      <c r="AG16" s="12"/>
+      <c r="AH16" s="12"/>
+      <c r="AI16" s="12"/>
+      <c r="AJ16" s="12"/>
+      <c r="AK16" s="12"/>
+      <c r="AL16" s="12"/>
+      <c r="AM16" s="12"/>
+      <c r="AN16" s="12"/>
+      <c r="AO16" s="12"/>
+      <c r="AP16" s="12"/>
+      <c r="AQ16" s="12"/>
+      <c r="AR16" s="12"/>
+      <c r="AS16" s="12"/>
+      <c r="AT16" s="12"/>
+      <c r="AU16" s="12"/>
+      <c r="AV16" s="12"/>
+      <c r="AW16" s="12"/>
+      <c r="AX16" s="12"/>
+      <c r="AY16" s="12"/>
+      <c r="AZ16" s="12"/>
+      <c r="BA16" s="12"/>
+      <c r="BB16" s="12"/>
+    </row>
+    <row r="17" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A17" s="27">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="70"/>
+      <c r="D17" s="70"/>
+      <c r="E17" s="70"/>
+      <c r="F17" s="70"/>
+      <c r="G17" s="70"/>
+      <c r="H17" s="70">
+        <f>3*24</f>
+        <v>72</v>
+      </c>
+      <c r="I17" s="70"/>
+      <c r="J17" s="71"/>
+      <c r="K17" s="72"/>
+      <c r="L17" s="55"/>
+      <c r="M17" s="73"/>
+      <c r="N17" s="74"/>
+      <c r="O17" s="70"/>
+      <c r="P17" s="71"/>
+      <c r="Q17" s="71"/>
+      <c r="R17" s="72"/>
+      <c r="S17" s="55"/>
+      <c r="T17" s="58">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="U17" s="75">
+        <f t="shared" si="4"/>
+        <v>72</v>
+      </c>
+      <c r="V17" s="75">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="AF17" s="12"/>
+      <c r="AG17" s="12"/>
+      <c r="AH17" s="12"/>
+      <c r="AI17" s="12"/>
+      <c r="AJ17" s="12"/>
+      <c r="AK17" s="12"/>
+      <c r="AL17" s="12"/>
+      <c r="AM17" s="12"/>
+      <c r="AN17" s="12"/>
+      <c r="AO17" s="12"/>
+      <c r="AP17" s="12"/>
+      <c r="AQ17" s="12"/>
+      <c r="AR17" s="12"/>
+      <c r="AS17" s="12"/>
+      <c r="AT17" s="12"/>
+      <c r="AU17" s="12"/>
+      <c r="AV17" s="12"/>
+      <c r="AW17" s="12"/>
+      <c r="AX17" s="12"/>
+      <c r="AY17" s="12"/>
+      <c r="AZ17" s="12"/>
+      <c r="BA17" s="12"/>
+      <c r="BB17" s="12"/>
+    </row>
+    <row r="18" spans="1:54" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="27">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="70"/>
+      <c r="D18" s="70"/>
+      <c r="E18" s="70"/>
+      <c r="F18" s="70"/>
+      <c r="G18" s="70"/>
+      <c r="H18" s="70"/>
+      <c r="I18" s="70"/>
+      <c r="J18" s="71"/>
+      <c r="K18" s="72"/>
+      <c r="L18" s="55"/>
+      <c r="M18" s="73"/>
+      <c r="N18" s="74"/>
+      <c r="O18" s="70"/>
+      <c r="P18" s="71"/>
+      <c r="Q18" s="71"/>
+      <c r="R18" s="72"/>
+      <c r="S18" s="55"/>
+      <c r="T18" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U18" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF18" s="12"/>
+      <c r="AG18" s="12"/>
+      <c r="AH18" s="12"/>
+      <c r="AI18" s="12"/>
+      <c r="AJ18" s="12"/>
+      <c r="AK18" s="12"/>
+      <c r="AL18" s="12"/>
+      <c r="AM18" s="12"/>
+      <c r="AN18" s="12"/>
+      <c r="AO18" s="12"/>
+      <c r="AP18" s="12"/>
+      <c r="AQ18" s="12"/>
+      <c r="AR18" s="12"/>
+      <c r="AS18" s="12"/>
+      <c r="AT18" s="12"/>
+      <c r="AU18" s="12"/>
+      <c r="AV18" s="12"/>
+      <c r="AW18" s="12"/>
+      <c r="AX18" s="12"/>
+      <c r="AY18" s="12"/>
+      <c r="AZ18" s="12"/>
+      <c r="BA18" s="12"/>
+      <c r="BB18" s="12"/>
+    </row>
+    <row r="19" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A19" s="27">
+        <v>16</v>
+      </c>
+      <c r="B19" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="70">
+        <v>1</v>
+      </c>
+      <c r="D19" s="70"/>
+      <c r="E19" s="70"/>
+      <c r="F19" s="70"/>
+      <c r="G19" s="70"/>
+      <c r="H19" s="70">
+        <f>20+24</f>
+        <v>44</v>
+      </c>
+      <c r="I19" s="70"/>
+      <c r="J19" s="71"/>
+      <c r="K19" s="72"/>
+      <c r="L19" s="55"/>
+      <c r="M19" s="73"/>
+      <c r="N19" s="74"/>
+      <c r="O19" s="70"/>
+      <c r="P19" s="71"/>
+      <c r="Q19" s="71"/>
+      <c r="R19" s="72"/>
+      <c r="S19" s="55"/>
+      <c r="T19" s="58">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="U19" s="75">
+        <f t="shared" si="4"/>
+        <v>68</v>
+      </c>
+      <c r="V19" s="75">
+        <f t="shared" si="5"/>
+        <v>2.8333333333333335</v>
+      </c>
+      <c r="AF19" s="12"/>
+      <c r="AG19" s="12"/>
+      <c r="AH19" s="12"/>
+      <c r="AI19" s="12"/>
+      <c r="AJ19" s="12"/>
+      <c r="AK19" s="12"/>
+      <c r="AL19" s="12"/>
+      <c r="AM19" s="12"/>
+      <c r="AN19" s="12"/>
+      <c r="AO19" s="12"/>
+      <c r="AP19" s="12"/>
+      <c r="AQ19" s="12"/>
+      <c r="AR19" s="12"/>
+      <c r="AS19" s="12"/>
+      <c r="AT19" s="12"/>
+      <c r="AU19" s="12"/>
+      <c r="AV19" s="12"/>
+      <c r="AW19" s="12"/>
+      <c r="AX19" s="12"/>
+      <c r="AY19" s="12"/>
+      <c r="AZ19" s="12"/>
+      <c r="BA19" s="12"/>
+      <c r="BB19" s="12"/>
+    </row>
+    <row r="20" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A20" s="27">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="B20" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="70">
+        <v>5</v>
+      </c>
+      <c r="D20" s="70"/>
+      <c r="E20" s="70"/>
+      <c r="F20" s="70"/>
+      <c r="G20" s="70"/>
+      <c r="H20" s="70"/>
+      <c r="I20" s="70"/>
+      <c r="J20" s="71"/>
+      <c r="K20" s="72"/>
+      <c r="L20" s="55"/>
+      <c r="M20" s="73"/>
+      <c r="N20" s="74"/>
+      <c r="O20" s="70"/>
+      <c r="P20" s="71"/>
+      <c r="Q20" s="71"/>
+      <c r="R20" s="72"/>
+      <c r="S20" s="55"/>
+      <c r="T20" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U20" s="75">
+        <f t="shared" si="4"/>
+        <v>120</v>
+      </c>
+      <c r="V20" s="75">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="AF20" s="12"/>
+      <c r="AG20" s="12"/>
+      <c r="AH20" s="12"/>
+      <c r="AI20" s="12"/>
+      <c r="AJ20" s="12"/>
+      <c r="AK20" s="12"/>
+      <c r="AL20" s="12"/>
+      <c r="AM20" s="12"/>
+      <c r="AN20" s="12"/>
+      <c r="AO20" s="12"/>
+      <c r="AP20" s="12"/>
+      <c r="AQ20" s="12"/>
+      <c r="AR20" s="12"/>
+      <c r="AS20" s="12"/>
+      <c r="AT20" s="12"/>
+      <c r="AU20" s="12"/>
+      <c r="AV20" s="12"/>
+      <c r="AW20" s="12"/>
+      <c r="AX20" s="12"/>
+      <c r="AY20" s="12"/>
+      <c r="AZ20" s="12"/>
+      <c r="BA20" s="12"/>
+      <c r="BB20" s="12"/>
+    </row>
+    <row r="21" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A21" s="27">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="B21" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="70"/>
+      <c r="D21" s="70"/>
+      <c r="E21" s="70"/>
+      <c r="F21" s="70"/>
+      <c r="G21" s="70"/>
+      <c r="H21" s="70">
+        <f>2*24</f>
+        <v>48</v>
+      </c>
+      <c r="I21" s="70"/>
+      <c r="J21" s="71"/>
+      <c r="K21" s="72"/>
+      <c r="L21" s="55"/>
+      <c r="M21" s="73"/>
+      <c r="N21" s="74"/>
+      <c r="O21" s="70"/>
+      <c r="P21" s="71"/>
+      <c r="Q21" s="71"/>
+      <c r="R21" s="72"/>
+      <c r="S21" s="55"/>
+      <c r="T21" s="58">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+      <c r="U21" s="75">
+        <f t="shared" si="4"/>
+        <v>48</v>
+      </c>
+      <c r="V21" s="75">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="AF21" s="12"/>
+      <c r="AG21" s="12"/>
+      <c r="AH21" s="12"/>
+      <c r="AI21" s="12"/>
+      <c r="AJ21" s="12"/>
+      <c r="AK21" s="12"/>
+      <c r="AL21" s="12"/>
+      <c r="AM21" s="12"/>
+      <c r="AN21" s="12"/>
+      <c r="AO21" s="12"/>
+      <c r="AP21" s="12"/>
+      <c r="AQ21" s="12"/>
+      <c r="AR21" s="12"/>
+      <c r="AS21" s="12"/>
+      <c r="AT21" s="12"/>
+      <c r="AU21" s="12"/>
+      <c r="AV21" s="12"/>
+      <c r="AW21" s="12"/>
+      <c r="AX21" s="12"/>
+      <c r="AY21" s="12"/>
+      <c r="AZ21" s="12"/>
+      <c r="BA21" s="12"/>
+      <c r="BB21" s="12"/>
+    </row>
+    <row r="22" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="27">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="B22" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="70">
+        <v>1</v>
+      </c>
+      <c r="D22" s="70"/>
+      <c r="E22" s="70"/>
+      <c r="F22" s="70"/>
+      <c r="G22" s="70"/>
+      <c r="H22" s="70"/>
+      <c r="I22" s="70">
+        <v>20</v>
+      </c>
+      <c r="J22" s="71"/>
+      <c r="K22" s="72"/>
+      <c r="L22" s="55"/>
+      <c r="M22" s="73"/>
+      <c r="N22" s="74"/>
+      <c r="O22" s="70"/>
+      <c r="P22" s="71"/>
+      <c r="Q22" s="71"/>
+      <c r="R22" s="72"/>
+      <c r="S22" s="55"/>
+      <c r="T22" s="58">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="U22" s="75">
+        <f t="shared" si="4"/>
+        <v>44</v>
+      </c>
+      <c r="V22" s="75">
+        <f t="shared" si="5"/>
+        <v>1.8333333333333333</v>
+      </c>
+      <c r="W22" s="9"/>
+      <c r="X22" s="9"/>
+      <c r="Y22" s="9"/>
+      <c r="Z22" s="9"/>
+      <c r="AA22" s="9"/>
+      <c r="AB22" s="9"/>
+      <c r="AC22" s="9"/>
+      <c r="AD22" s="9"/>
+      <c r="AE22" s="9"/>
+      <c r="AF22" s="12"/>
+      <c r="AG22" s="12"/>
+      <c r="AH22" s="12"/>
+      <c r="AI22" s="12"/>
+      <c r="AJ22" s="12"/>
+      <c r="AK22" s="12"/>
+      <c r="AL22" s="12"/>
+      <c r="AM22" s="12"/>
+      <c r="AN22" s="12"/>
+      <c r="AO22" s="12"/>
+      <c r="AP22" s="12"/>
+      <c r="AQ22" s="12"/>
+      <c r="AR22" s="12"/>
+      <c r="AS22" s="12"/>
+      <c r="AT22" s="12"/>
+      <c r="AU22" s="12"/>
+      <c r="AV22" s="12"/>
+      <c r="AW22" s="12"/>
+      <c r="AX22" s="12"/>
+      <c r="AY22" s="12"/>
+      <c r="AZ22" s="12"/>
+      <c r="BA22" s="12"/>
+      <c r="BB22" s="12"/>
+    </row>
+    <row r="23" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="27">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="B23" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="70"/>
+      <c r="D23" s="70"/>
+      <c r="E23" s="70"/>
+      <c r="F23" s="70"/>
+      <c r="G23" s="70"/>
+      <c r="H23" s="70">
+        <f>37*24+19</f>
+        <v>907</v>
+      </c>
+      <c r="I23" s="70"/>
+      <c r="J23" s="71"/>
+      <c r="K23" s="72"/>
+      <c r="L23" s="55"/>
+      <c r="M23" s="73"/>
+      <c r="N23" s="74"/>
+      <c r="O23" s="70"/>
+      <c r="P23" s="71"/>
+      <c r="Q23" s="71"/>
+      <c r="R23" s="72"/>
+      <c r="S23" s="55"/>
+      <c r="T23" s="58">
+        <f t="shared" si="0"/>
+        <v>907</v>
+      </c>
+      <c r="U23" s="75">
+        <f t="shared" si="4"/>
+        <v>907</v>
+      </c>
+      <c r="V23" s="75">
+        <f t="shared" si="5"/>
+        <v>37.791666666666664</v>
+      </c>
+      <c r="W23" s="9"/>
+      <c r="X23" s="9"/>
+      <c r="Y23" s="9"/>
+      <c r="Z23" s="9"/>
+      <c r="AA23" s="9"/>
+      <c r="AB23" s="9"/>
+      <c r="AC23" s="9"/>
+      <c r="AD23" s="9"/>
+      <c r="AE23" s="9"/>
+      <c r="AF23" s="12"/>
+      <c r="AG23" s="12"/>
+      <c r="AH23" s="12"/>
+      <c r="AI23" s="12"/>
+      <c r="AJ23" s="12"/>
+      <c r="AK23" s="12"/>
+      <c r="AL23" s="12"/>
+      <c r="AM23" s="12"/>
+      <c r="AN23" s="12"/>
+      <c r="AO23" s="12"/>
+      <c r="AP23" s="12"/>
+      <c r="AQ23" s="12"/>
+      <c r="AR23" s="12"/>
+      <c r="AS23" s="12"/>
+      <c r="AT23" s="12"/>
+      <c r="AU23" s="12"/>
+      <c r="AV23" s="12"/>
+      <c r="AW23" s="12"/>
+      <c r="AX23" s="12"/>
+      <c r="AY23" s="12"/>
+      <c r="AZ23" s="12"/>
+      <c r="BA23" s="12"/>
+      <c r="BB23" s="12"/>
+    </row>
+    <row r="24" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A24" s="27">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="B24" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" s="70">
+        <v>2</v>
+      </c>
+      <c r="D24" s="70"/>
+      <c r="E24" s="70"/>
+      <c r="F24" s="70"/>
+      <c r="G24" s="70"/>
+      <c r="H24" s="70">
+        <f>3*24</f>
+        <v>72</v>
+      </c>
+      <c r="I24" s="70"/>
+      <c r="J24" s="71"/>
+      <c r="K24" s="72"/>
+      <c r="L24" s="55"/>
+      <c r="M24" s="73"/>
+      <c r="N24" s="74"/>
+      <c r="O24" s="70"/>
+      <c r="P24" s="71"/>
+      <c r="Q24" s="71"/>
+      <c r="R24" s="72"/>
+      <c r="S24" s="55"/>
+      <c r="T24" s="58">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="U24" s="75">
+        <f t="shared" si="4"/>
+        <v>120</v>
+      </c>
+      <c r="V24" s="75">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="AF24" s="12"/>
+      <c r="AG24" s="12"/>
+      <c r="AH24" s="12"/>
+      <c r="AI24" s="12"/>
+      <c r="AJ24" s="12"/>
+      <c r="AK24" s="12"/>
+      <c r="AL24" s="12"/>
+      <c r="AM24" s="12"/>
+      <c r="AN24" s="12"/>
+      <c r="AO24" s="12"/>
+      <c r="AP24" s="12"/>
+      <c r="AQ24" s="12"/>
+      <c r="AR24" s="12"/>
+      <c r="AS24" s="12"/>
+      <c r="AT24" s="12"/>
+      <c r="AU24" s="12"/>
+      <c r="AV24" s="12"/>
+      <c r="AW24" s="12"/>
+      <c r="AX24" s="12"/>
+      <c r="AY24" s="12"/>
+      <c r="AZ24" s="12"/>
+      <c r="BA24" s="12"/>
+      <c r="BB24" s="12"/>
+    </row>
+    <row r="25" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A25" s="27">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="70">
+        <f>9+126</f>
+        <v>135</v>
+      </c>
+      <c r="D25" s="70"/>
+      <c r="E25" s="70"/>
+      <c r="F25" s="70"/>
+      <c r="G25" s="70"/>
+      <c r="H25" s="70"/>
+      <c r="I25" s="70"/>
+      <c r="J25" s="71">
+        <v>1</v>
+      </c>
+      <c r="K25" s="72"/>
+      <c r="L25" s="55"/>
+      <c r="M25" s="73"/>
+      <c r="N25" s="74"/>
+      <c r="O25" s="70">
+        <v>1</v>
+      </c>
+      <c r="P25" s="71"/>
+      <c r="Q25" s="71">
+        <v>16</v>
+      </c>
+      <c r="R25" s="72"/>
+      <c r="S25" s="55"/>
+      <c r="T25" s="58">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="U25" s="75">
+        <f t="shared" si="4"/>
+        <v>3649</v>
+      </c>
+      <c r="V25" s="75">
+        <f t="shared" si="5"/>
+        <v>152.04166666666666</v>
+      </c>
+      <c r="AY25" s="14" t="e">
+        <f>#REF!-AY24</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="27">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="B26" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="70"/>
+      <c r="D26" s="70"/>
+      <c r="E26" s="70"/>
+      <c r="F26" s="70"/>
+      <c r="G26" s="70"/>
+      <c r="H26" s="70"/>
+      <c r="I26" s="70"/>
+      <c r="J26" s="71"/>
+      <c r="K26" s="72"/>
+      <c r="L26" s="55"/>
+      <c r="M26" s="73"/>
+      <c r="N26" s="74"/>
+      <c r="O26" s="70"/>
+      <c r="P26" s="71"/>
+      <c r="Q26" s="71"/>
+      <c r="R26" s="72"/>
+      <c r="S26" s="55"/>
+      <c r="T26" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U26" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V26" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W26" s="9"/>
+      <c r="X26" s="9"/>
+      <c r="Y26" s="9"/>
+      <c r="Z26" s="9"/>
+      <c r="AA26" s="9"/>
+      <c r="AB26" s="9"/>
+      <c r="AC26" s="9"/>
+      <c r="AD26" s="9"/>
+      <c r="AE26" s="9"/>
+    </row>
+    <row r="27" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="27">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="B27" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27" s="70">
+        <v>1</v>
+      </c>
+      <c r="D27" s="70"/>
+      <c r="E27" s="70"/>
+      <c r="F27" s="70"/>
+      <c r="G27" s="70"/>
+      <c r="H27" s="70"/>
+      <c r="I27" s="70"/>
+      <c r="J27" s="71"/>
+      <c r="K27" s="72"/>
+      <c r="L27" s="55"/>
+      <c r="M27" s="73"/>
+      <c r="N27" s="74"/>
+      <c r="O27" s="70"/>
+      <c r="P27" s="71"/>
+      <c r="Q27" s="71"/>
+      <c r="R27" s="72"/>
+      <c r="S27" s="55"/>
+      <c r="T27" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U27" s="75">
+        <f t="shared" si="4"/>
+        <v>24</v>
+      </c>
+      <c r="V27" s="75">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="W27" s="9"/>
+      <c r="X27" s="9"/>
+      <c r="Y27" s="9"/>
+      <c r="Z27" s="9"/>
+      <c r="AA27" s="9"/>
+      <c r="AB27" s="9"/>
+      <c r="AC27" s="9"/>
+      <c r="AD27" s="9"/>
+      <c r="AE27" s="9"/>
+    </row>
+    <row r="28" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="27">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="B28" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="70">
+        <f>1+252+46</f>
+        <v>299</v>
+      </c>
+      <c r="D28" s="70"/>
+      <c r="E28" s="70"/>
+      <c r="F28" s="70"/>
+      <c r="G28" s="70"/>
+      <c r="H28" s="70"/>
+      <c r="I28" s="70"/>
+      <c r="J28" s="71"/>
+      <c r="K28" s="72"/>
+      <c r="L28" s="55"/>
+      <c r="M28" s="73"/>
+      <c r="N28" s="74"/>
+      <c r="O28" s="70"/>
+      <c r="P28" s="71"/>
+      <c r="Q28" s="71">
+        <v>17</v>
+      </c>
+      <c r="R28" s="72"/>
+      <c r="S28" s="55"/>
+      <c r="T28" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U28" s="75">
+        <f t="shared" si="4"/>
+        <v>7584</v>
+      </c>
+      <c r="V28" s="75">
+        <f t="shared" si="5"/>
+        <v>316</v>
+      </c>
+      <c r="W28" s="9"/>
+      <c r="X28" s="9"/>
+      <c r="Y28" s="9"/>
+      <c r="Z28" s="9"/>
+      <c r="AA28" s="9"/>
+      <c r="AB28" s="9"/>
+      <c r="AC28" s="9"/>
+      <c r="AD28" s="9"/>
+      <c r="AE28" s="9"/>
+    </row>
+    <row r="29" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A29" s="27">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="B29" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" s="70"/>
+      <c r="D29" s="70"/>
+      <c r="E29" s="70"/>
+      <c r="F29" s="70"/>
+      <c r="G29" s="70"/>
+      <c r="H29" s="70"/>
+      <c r="I29" s="70"/>
+      <c r="J29" s="71">
+        <v>5</v>
+      </c>
+      <c r="K29" s="72"/>
+      <c r="L29" s="55"/>
+      <c r="M29" s="73"/>
+      <c r="N29" s="74"/>
+      <c r="O29" s="70"/>
+      <c r="P29" s="71"/>
+      <c r="Q29" s="71"/>
+      <c r="R29" s="72"/>
+      <c r="S29" s="55"/>
+      <c r="T29" s="58">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="U29" s="75">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="V29" s="75">
+        <f t="shared" si="5"/>
+        <v>0.20833333333333334</v>
+      </c>
+    </row>
+    <row r="30" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A30" s="27">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="B30" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="70"/>
+      <c r="D30" s="70"/>
+      <c r="E30" s="70"/>
+      <c r="F30" s="70"/>
+      <c r="G30" s="70"/>
+      <c r="H30" s="70"/>
+      <c r="I30" s="70"/>
+      <c r="J30" s="71"/>
+      <c r="K30" s="72"/>
+      <c r="L30" s="55"/>
+      <c r="M30" s="73"/>
+      <c r="N30" s="74"/>
+      <c r="O30" s="70"/>
+      <c r="P30" s="71"/>
+      <c r="Q30" s="71">
+        <v>1</v>
+      </c>
+      <c r="R30" s="72"/>
+      <c r="S30" s="55"/>
+      <c r="T30" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U30" s="75">
+        <f t="shared" si="4"/>
+        <v>24</v>
+      </c>
+      <c r="V30" s="75">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A31" s="27">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="B31" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" s="70"/>
+      <c r="D31" s="70"/>
+      <c r="E31" s="70"/>
+      <c r="F31" s="70"/>
+      <c r="G31" s="70"/>
+      <c r="H31" s="70"/>
+      <c r="I31" s="70"/>
+      <c r="J31" s="71"/>
+      <c r="K31" s="72"/>
+      <c r="L31" s="55"/>
+      <c r="M31" s="73"/>
+      <c r="N31" s="74"/>
+      <c r="O31" s="70"/>
+      <c r="P31" s="71"/>
+      <c r="Q31" s="71"/>
+      <c r="R31" s="72"/>
+      <c r="S31" s="55"/>
+      <c r="T31" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U31" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V31" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A32" s="27">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="B32" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" s="70"/>
+      <c r="D32" s="70"/>
+      <c r="E32" s="70"/>
+      <c r="F32" s="70"/>
+      <c r="G32" s="70"/>
+      <c r="H32" s="70"/>
+      <c r="I32" s="70"/>
+      <c r="J32" s="71"/>
+      <c r="K32" s="72"/>
+      <c r="L32" s="55"/>
+      <c r="M32" s="73"/>
+      <c r="N32" s="74"/>
+      <c r="O32" s="70"/>
+      <c r="P32" s="71"/>
+      <c r="Q32" s="71"/>
+      <c r="R32" s="72"/>
+      <c r="S32" s="55"/>
+      <c r="T32" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U32" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V32" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A33" s="27">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="B33" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" s="70"/>
+      <c r="D33" s="70"/>
+      <c r="E33" s="70"/>
+      <c r="F33" s="70"/>
+      <c r="G33" s="70"/>
+      <c r="H33" s="70"/>
+      <c r="I33" s="70"/>
+      <c r="J33" s="71"/>
+      <c r="K33" s="72"/>
+      <c r="L33" s="55"/>
+      <c r="M33" s="73"/>
+      <c r="N33" s="74"/>
+      <c r="O33" s="70"/>
+      <c r="P33" s="71"/>
+      <c r="Q33" s="71"/>
+      <c r="R33" s="72"/>
+      <c r="S33" s="55"/>
+      <c r="T33" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U33" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V33" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A34" s="27">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="B34" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" s="70">
+        <f>72+58</f>
+        <v>130</v>
+      </c>
+      <c r="D34" s="70"/>
+      <c r="E34" s="70"/>
+      <c r="F34" s="70"/>
+      <c r="G34" s="70"/>
+      <c r="H34" s="70"/>
+      <c r="I34" s="70">
+        <v>1</v>
+      </c>
+      <c r="J34" s="71"/>
+      <c r="K34" s="72">
+        <v>1</v>
+      </c>
+      <c r="L34" s="55"/>
+      <c r="M34" s="73"/>
+      <c r="N34" s="74"/>
+      <c r="O34" s="70"/>
+      <c r="P34" s="71"/>
+      <c r="Q34" s="71">
+        <v>10</v>
+      </c>
+      <c r="R34" s="72"/>
+      <c r="S34" s="55"/>
+      <c r="T34" s="58">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="U34" s="75">
+        <f t="shared" si="4"/>
+        <v>3362</v>
+      </c>
+      <c r="V34" s="75">
+        <f t="shared" si="5"/>
+        <v>140.08333333333334</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="27">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="B35" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="C35" s="70"/>
+      <c r="D35" s="70"/>
+      <c r="E35" s="70"/>
+      <c r="F35" s="70"/>
+      <c r="G35" s="70"/>
+      <c r="H35" s="70"/>
+      <c r="I35" s="70"/>
+      <c r="J35" s="71"/>
+      <c r="K35" s="72"/>
+      <c r="L35" s="55"/>
+      <c r="M35" s="73"/>
+      <c r="N35" s="74"/>
+      <c r="O35" s="70"/>
+      <c r="P35" s="71"/>
+      <c r="Q35" s="71"/>
+      <c r="R35" s="72"/>
+      <c r="S35" s="55"/>
+      <c r="T35" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U35" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V35" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A36" s="27">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+      <c r="B36" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="70"/>
+      <c r="D36" s="70"/>
+      <c r="E36" s="70"/>
+      <c r="F36" s="70"/>
+      <c r="G36" s="70"/>
+      <c r="H36" s="70"/>
+      <c r="I36" s="70"/>
+      <c r="J36" s="71"/>
+      <c r="K36" s="72"/>
+      <c r="L36" s="55"/>
+      <c r="M36" s="73"/>
+      <c r="N36" s="74"/>
+      <c r="O36" s="70"/>
+      <c r="P36" s="71"/>
+      <c r="Q36" s="71"/>
+      <c r="R36" s="72"/>
+      <c r="S36" s="55"/>
+      <c r="T36" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U36" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="27">
+        <f t="shared" si="1"/>
+        <v>34</v>
+      </c>
+      <c r="B37" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="C37" s="59">
+        <f>864+1944+89</f>
+        <v>2897</v>
+      </c>
+      <c r="D37" s="59"/>
+      <c r="E37" s="59"/>
+      <c r="F37" s="59"/>
+      <c r="G37" s="59"/>
+      <c r="H37" s="59">
+        <v>3</v>
+      </c>
+      <c r="I37" s="59">
+        <v>2</v>
+      </c>
+      <c r="J37" s="60"/>
+      <c r="K37" s="61">
+        <f>2*6+2</f>
+        <v>14</v>
+      </c>
+      <c r="L37" s="62"/>
+      <c r="M37" s="63">
+        <v>19</v>
+      </c>
+      <c r="N37" s="64"/>
+      <c r="O37" s="65">
+        <v>136</v>
+      </c>
+      <c r="P37" s="66"/>
+      <c r="Q37" s="66">
+        <v>38</v>
+      </c>
+      <c r="R37" s="67"/>
+      <c r="S37" s="62"/>
+      <c r="T37" s="77">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="U37" s="77">
+        <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
+        <v>18559</v>
+      </c>
+      <c r="V37" s="77">
+        <f>U37/6</f>
+        <v>3093.1666666666665</v>
+      </c>
+      <c r="W37" s="50"/>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A38" s="27">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="B38" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" s="70"/>
+      <c r="D38" s="70"/>
+      <c r="E38" s="70"/>
+      <c r="F38" s="70"/>
+      <c r="G38" s="70"/>
+      <c r="H38" s="70"/>
+      <c r="I38" s="70"/>
+      <c r="J38" s="71"/>
+      <c r="K38" s="72"/>
+      <c r="L38" s="55"/>
+      <c r="M38" s="73"/>
+      <c r="N38" s="74"/>
+      <c r="O38" s="70"/>
+      <c r="P38" s="71"/>
+      <c r="Q38" s="71"/>
+      <c r="R38" s="72"/>
+      <c r="S38" s="55"/>
+      <c r="T38" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U38" s="75">
+        <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
+        <v>0</v>
+      </c>
+      <c r="V38" s="75">
+        <f>U38/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A39" s="27">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="B39" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="C39" s="78"/>
+      <c r="D39" s="78"/>
+      <c r="E39" s="78"/>
+      <c r="F39" s="78"/>
+      <c r="G39" s="78"/>
+      <c r="H39" s="78"/>
+      <c r="I39" s="78"/>
+      <c r="J39" s="79"/>
+      <c r="K39" s="80"/>
+      <c r="L39" s="55"/>
+      <c r="M39" s="73"/>
+      <c r="N39" s="74"/>
+      <c r="O39" s="70"/>
+      <c r="P39" s="71"/>
+      <c r="Q39" s="71"/>
+      <c r="R39" s="72"/>
+      <c r="S39" s="95"/>
+      <c r="T39" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U39" s="75">
+        <f>C39*24+M39*24+O39*24+Q39*24+T39</f>
+        <v>0</v>
+      </c>
+      <c r="V39" s="75">
+        <f>U39/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="27">
+        <f t="shared" si="1"/>
+        <v>37</v>
+      </c>
+      <c r="B40" s="42" t="s">
+        <v>21</v>
+      </c>
+      <c r="C40" s="59">
+        <f>189+47</f>
+        <v>236</v>
+      </c>
+      <c r="D40" s="59"/>
+      <c r="E40" s="59"/>
+      <c r="F40" s="59"/>
+      <c r="G40" s="59"/>
+      <c r="H40" s="59"/>
+      <c r="I40" s="59"/>
+      <c r="J40" s="60"/>
+      <c r="K40" s="61">
+        <v>20</v>
+      </c>
+      <c r="L40" s="62"/>
+      <c r="M40" s="63"/>
+      <c r="N40" s="64"/>
+      <c r="O40" s="65">
+        <v>1</v>
+      </c>
+      <c r="P40" s="66"/>
+      <c r="Q40" s="66">
+        <v>4</v>
+      </c>
+      <c r="R40" s="67"/>
+      <c r="S40" s="62"/>
+      <c r="T40" s="77">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="U40" s="77">
+        <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
+        <v>5804</v>
+      </c>
+      <c r="V40" s="77">
+        <f>U40/24</f>
+        <v>241.83333333333334</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="27">
+        <f t="shared" si="1"/>
+        <v>38</v>
+      </c>
+      <c r="B41" s="43" t="s">
+        <v>22</v>
+      </c>
+      <c r="C41" s="82">
+        <f>192+18</f>
+        <v>210</v>
+      </c>
+      <c r="D41" s="82"/>
+      <c r="E41" s="82"/>
+      <c r="F41" s="82"/>
+      <c r="G41" s="82"/>
+      <c r="H41" s="82"/>
+      <c r="I41" s="82"/>
+      <c r="J41" s="83"/>
+      <c r="K41" s="84"/>
+      <c r="L41" s="85"/>
+      <c r="M41" s="86">
+        <v>4</v>
+      </c>
+      <c r="N41" s="87"/>
+      <c r="O41" s="82">
+        <v>10</v>
+      </c>
+      <c r="P41" s="83"/>
+      <c r="Q41" s="83">
+        <v>33</v>
+      </c>
+      <c r="R41" s="84"/>
+      <c r="S41" s="85"/>
+      <c r="T41" s="88">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U41" s="88">
+        <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
+        <v>3084</v>
+      </c>
+      <c r="V41" s="88">
+        <f>U41/12</f>
+        <v>257</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="27">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+      <c r="B42" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C42" s="70"/>
+      <c r="D42" s="70"/>
+      <c r="E42" s="70"/>
+      <c r="F42" s="70"/>
+      <c r="G42" s="70"/>
+      <c r="H42" s="70"/>
+      <c r="I42" s="70"/>
+      <c r="J42" s="71"/>
+      <c r="K42" s="72"/>
+      <c r="L42" s="55"/>
+      <c r="M42" s="73"/>
+      <c r="N42" s="74"/>
+      <c r="O42" s="70"/>
+      <c r="P42" s="71"/>
+      <c r="Q42" s="71"/>
+      <c r="R42" s="72"/>
+      <c r="S42" s="55"/>
+      <c r="T42" s="75"/>
+      <c r="U42" s="75"/>
+      <c r="V42" s="75"/>
+    </row>
+    <row r="43" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="27">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="B43" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="C43" s="65">
+        <f>11988+19764+5129</f>
+        <v>36881</v>
+      </c>
+      <c r="D43" s="65"/>
+      <c r="E43" s="65"/>
+      <c r="F43" s="65"/>
+      <c r="G43" s="65"/>
+      <c r="H43" s="65">
+        <v>5</v>
+      </c>
+      <c r="I43" s="65">
+        <v>12</v>
+      </c>
+      <c r="J43" s="66">
+        <f>3*6+2</f>
+        <v>20</v>
+      </c>
+      <c r="K43" s="67">
+        <f>95*6+1</f>
+        <v>571</v>
+      </c>
+      <c r="L43" s="62"/>
+      <c r="M43" s="63">
+        <v>1020</v>
+      </c>
+      <c r="N43" s="64"/>
+      <c r="O43" s="65">
+        <v>434</v>
+      </c>
+      <c r="P43" s="66"/>
+      <c r="Q43" s="66">
+        <v>757</v>
+      </c>
+      <c r="R43" s="67"/>
+      <c r="S43" s="62"/>
+      <c r="T43" s="77">
+        <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
+        <v>608</v>
+      </c>
+      <c r="U43" s="77">
+        <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
+        <v>235160</v>
+      </c>
+      <c r="V43" s="77">
+        <f>U43/6</f>
+        <v>39193.333333333336</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="27">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+      <c r="B44" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="70"/>
+      <c r="D44" s="70"/>
+      <c r="E44" s="70"/>
+      <c r="F44" s="70"/>
+      <c r="G44" s="70"/>
+      <c r="H44" s="70"/>
+      <c r="I44" s="70"/>
+      <c r="J44" s="71"/>
+      <c r="K44" s="72"/>
+      <c r="L44" s="55"/>
+      <c r="M44" s="73"/>
+      <c r="N44" s="74"/>
+      <c r="O44" s="70"/>
+      <c r="P44" s="71"/>
+      <c r="Q44" s="71"/>
+      <c r="R44" s="72"/>
+      <c r="S44" s="55"/>
+      <c r="T44" s="75"/>
+      <c r="U44" s="75"/>
+      <c r="V44" s="75"/>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A45" s="27">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="B45" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="70"/>
+      <c r="D45" s="70"/>
+      <c r="E45" s="70"/>
+      <c r="F45" s="70"/>
+      <c r="G45" s="70"/>
+      <c r="H45" s="70"/>
+      <c r="I45" s="70"/>
+      <c r="J45" s="71"/>
+      <c r="K45" s="72"/>
+      <c r="L45" s="55"/>
+      <c r="M45" s="73"/>
+      <c r="N45" s="74"/>
+      <c r="O45" s="70"/>
+      <c r="P45" s="71"/>
+      <c r="Q45" s="71"/>
+      <c r="R45" s="72"/>
+      <c r="S45" s="55"/>
+      <c r="T45" s="75">
+        <f t="shared" ref="T45:T54" si="7">H45+I45+J45+K45+N45+P45+R45</f>
+        <v>0</v>
+      </c>
+      <c r="U45" s="75">
+        <f>C45*24+M45*24+O45*24+Q45*24+T45</f>
+        <v>0</v>
+      </c>
+      <c r="V45" s="75">
+        <f>U45/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A46" s="27">
+        <f t="shared" si="1"/>
+        <v>43</v>
+      </c>
+      <c r="B46" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="C46" s="70"/>
+      <c r="D46" s="70"/>
+      <c r="E46" s="70"/>
+      <c r="F46" s="70"/>
+      <c r="G46" s="70"/>
+      <c r="H46" s="70"/>
+      <c r="I46" s="70"/>
+      <c r="J46" s="71"/>
+      <c r="K46" s="72"/>
+      <c r="L46" s="55"/>
+      <c r="M46" s="73"/>
+      <c r="N46" s="74"/>
+      <c r="O46" s="70"/>
+      <c r="P46" s="71"/>
+      <c r="Q46" s="71"/>
+      <c r="R46" s="72"/>
+      <c r="S46" s="55"/>
+      <c r="T46" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U46" s="75">
+        <f t="shared" ref="U46:U50" si="8">C46*24+M46*24+O46*24+Q46*24+T46</f>
+        <v>0</v>
+      </c>
+      <c r="V46" s="75">
+        <f t="shared" ref="V46:V54" si="9">U46/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="27">
+        <f t="shared" si="1"/>
+        <v>44</v>
+      </c>
+      <c r="B47" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="C47" s="65">
+        <f>89+648+324+88+432+83+103+324+432+106</f>
+        <v>2629</v>
+      </c>
+      <c r="D47" s="65"/>
+      <c r="E47" s="65"/>
+      <c r="F47" s="65"/>
+      <c r="G47" s="65"/>
+      <c r="H47" s="65">
+        <v>1</v>
+      </c>
+      <c r="I47" s="65"/>
+      <c r="J47" s="66"/>
+      <c r="K47" s="67">
+        <v>5</v>
+      </c>
+      <c r="L47" s="62"/>
+      <c r="M47" s="63">
+        <v>2</v>
+      </c>
+      <c r="N47" s="64"/>
+      <c r="O47" s="65">
+        <v>15</v>
+      </c>
+      <c r="P47" s="66"/>
+      <c r="Q47" s="66">
+        <v>5</v>
+      </c>
+      <c r="R47" s="67">
+        <v>3</v>
+      </c>
+      <c r="S47" s="62"/>
+      <c r="T47" s="77">
+        <f t="shared" si="7"/>
+        <v>9</v>
+      </c>
+      <c r="U47" s="77">
+        <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
+        <v>15915</v>
+      </c>
+      <c r="V47" s="77">
+        <f>U47/6</f>
+        <v>2652.5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A48" s="27">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="B48" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C48" s="70"/>
+      <c r="D48" s="70"/>
+      <c r="E48" s="70"/>
+      <c r="F48" s="70"/>
+      <c r="G48" s="70"/>
+      <c r="H48" s="70">
+        <v>24</v>
+      </c>
+      <c r="I48" s="70"/>
+      <c r="J48" s="71"/>
+      <c r="K48" s="72"/>
+      <c r="L48" s="55"/>
+      <c r="M48" s="73"/>
+      <c r="N48" s="74"/>
+      <c r="O48" s="70"/>
+      <c r="P48" s="71"/>
+      <c r="Q48" s="71"/>
+      <c r="R48" s="72"/>
+      <c r="S48" s="55"/>
+      <c r="T48" s="75">
+        <f t="shared" si="7"/>
+        <v>24</v>
+      </c>
+      <c r="U48" s="75">
+        <f t="shared" si="8"/>
+        <v>24</v>
+      </c>
+      <c r="V48" s="75">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A49" s="27">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="B49" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C49" s="70"/>
+      <c r="D49" s="70"/>
+      <c r="E49" s="70"/>
+      <c r="F49" s="70"/>
+      <c r="G49" s="70"/>
+      <c r="H49" s="70"/>
+      <c r="I49" s="70"/>
+      <c r="J49" s="71"/>
+      <c r="K49" s="72"/>
+      <c r="L49" s="55"/>
+      <c r="M49" s="73"/>
+      <c r="N49" s="74"/>
+      <c r="O49" s="70"/>
+      <c r="P49" s="71"/>
+      <c r="Q49" s="71"/>
+      <c r="R49" s="72"/>
+      <c r="S49" s="55"/>
+      <c r="T49" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U49" s="75">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V49" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A50" s="27">
+        <f t="shared" si="1"/>
+        <v>47</v>
+      </c>
+      <c r="B50" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="C50" s="70"/>
+      <c r="D50" s="70"/>
+      <c r="E50" s="70"/>
+      <c r="F50" s="70"/>
+      <c r="G50" s="70"/>
+      <c r="H50" s="70"/>
+      <c r="I50" s="70"/>
+      <c r="J50" s="71"/>
+      <c r="K50" s="72"/>
+      <c r="L50" s="55"/>
+      <c r="M50" s="73"/>
+      <c r="N50" s="74"/>
+      <c r="O50" s="70"/>
+      <c r="P50" s="71"/>
+      <c r="Q50" s="71"/>
+      <c r="R50" s="72"/>
+      <c r="S50" s="55"/>
+      <c r="T50" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U50" s="75">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V50" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="27">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+      <c r="B51" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="C51" s="65">
+        <v>34</v>
+      </c>
+      <c r="D51" s="65"/>
+      <c r="E51" s="65"/>
+      <c r="F51" s="65"/>
+      <c r="G51" s="65"/>
+      <c r="H51" s="65"/>
+      <c r="I51" s="65"/>
+      <c r="J51" s="66"/>
+      <c r="K51" s="67"/>
+      <c r="L51" s="62"/>
+      <c r="M51" s="63"/>
+      <c r="N51" s="64"/>
+      <c r="O51" s="65"/>
+      <c r="P51" s="66"/>
+      <c r="Q51" s="66"/>
+      <c r="R51" s="67"/>
+      <c r="S51" s="62"/>
+      <c r="T51" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U51" s="77">
+        <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
+        <v>204</v>
+      </c>
+      <c r="V51" s="77">
+        <f>U51/6</f>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A52" s="27">
+        <f t="shared" si="1"/>
+        <v>49</v>
+      </c>
+      <c r="B52" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="C52" s="70"/>
+      <c r="D52" s="70"/>
+      <c r="E52" s="70"/>
+      <c r="F52" s="70"/>
+      <c r="G52" s="70"/>
+      <c r="H52" s="70"/>
+      <c r="I52" s="70"/>
+      <c r="J52" s="71"/>
+      <c r="K52" s="72"/>
+      <c r="L52" s="55"/>
+      <c r="M52" s="73"/>
+      <c r="N52" s="74"/>
+      <c r="O52" s="70"/>
+      <c r="P52" s="71"/>
+      <c r="Q52" s="71"/>
+      <c r="R52" s="72"/>
+      <c r="S52" s="55"/>
+      <c r="T52" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U52" s="75">
+        <f t="shared" ref="U52:U54" si="10">C52*24+M52*24+O52*24+Q52*24+T52</f>
+        <v>0</v>
+      </c>
+      <c r="V52" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A53" s="27">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="B53" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C53" s="70">
+        <v>7</v>
+      </c>
+      <c r="D53" s="70"/>
+      <c r="E53" s="70"/>
+      <c r="F53" s="70"/>
+      <c r="G53" s="70"/>
+      <c r="H53" s="70"/>
+      <c r="I53" s="70"/>
+      <c r="J53" s="71"/>
+      <c r="K53" s="72"/>
+      <c r="L53" s="55"/>
+      <c r="M53" s="73"/>
+      <c r="N53" s="74"/>
+      <c r="O53" s="70"/>
+      <c r="P53" s="71"/>
+      <c r="Q53" s="71"/>
+      <c r="R53" s="72"/>
+      <c r="S53" s="55"/>
+      <c r="T53" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U53" s="75">
+        <f t="shared" si="10"/>
+        <v>168</v>
+      </c>
+      <c r="V53" s="75">
+        <f t="shared" si="9"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A54" s="27">
+        <f t="shared" si="1"/>
+        <v>51</v>
+      </c>
+      <c r="B54" s="26"/>
+      <c r="C54" s="70"/>
+      <c r="D54" s="70"/>
+      <c r="E54" s="70"/>
+      <c r="F54" s="70"/>
+      <c r="G54" s="70"/>
+      <c r="H54" s="70"/>
+      <c r="I54" s="70"/>
+      <c r="J54" s="71"/>
+      <c r="K54" s="72"/>
+      <c r="L54" s="55"/>
+      <c r="M54" s="73"/>
+      <c r="N54" s="74"/>
+      <c r="O54" s="70"/>
+      <c r="P54" s="71"/>
+      <c r="Q54" s="71"/>
+      <c r="R54" s="72"/>
+      <c r="S54" s="55"/>
+      <c r="T54" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U54" s="75">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V54" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A55" s="27">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="B55" s="26"/>
+      <c r="C55" s="70"/>
+      <c r="D55" s="70"/>
+      <c r="E55" s="70"/>
+      <c r="F55" s="70"/>
+      <c r="G55" s="70"/>
+      <c r="H55" s="70"/>
+      <c r="I55" s="70"/>
+      <c r="J55" s="71"/>
+      <c r="K55" s="72"/>
+      <c r="L55" s="55"/>
+      <c r="M55" s="73"/>
+      <c r="N55" s="74"/>
+      <c r="O55" s="70"/>
+      <c r="P55" s="71"/>
+      <c r="Q55" s="71"/>
+      <c r="R55" s="72"/>
+      <c r="S55" s="55"/>
+      <c r="T55" s="75"/>
+      <c r="U55" s="75"/>
+      <c r="V55" s="75"/>
+    </row>
+    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A56" s="27">
+        <f t="shared" si="1"/>
+        <v>53</v>
+      </c>
+      <c r="B56" s="26"/>
+      <c r="C56" s="70"/>
+      <c r="D56" s="70"/>
+      <c r="E56" s="70"/>
+      <c r="F56" s="70"/>
+      <c r="G56" s="70"/>
+      <c r="H56" s="70"/>
+      <c r="I56" s="70"/>
+      <c r="J56" s="71"/>
+      <c r="K56" s="72"/>
+      <c r="L56" s="55"/>
+      <c r="M56" s="73"/>
+      <c r="N56" s="74"/>
+      <c r="O56" s="70"/>
+      <c r="P56" s="71"/>
+      <c r="Q56" s="71"/>
+      <c r="R56" s="72"/>
+      <c r="S56" s="55"/>
+      <c r="T56" s="75"/>
+      <c r="U56" s="75"/>
+      <c r="V56" s="75"/>
+    </row>
+    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A57" s="27">
+        <f t="shared" si="1"/>
+        <v>54</v>
+      </c>
+      <c r="B57" s="26"/>
+      <c r="C57" s="70"/>
+      <c r="D57" s="70"/>
+      <c r="E57" s="70"/>
+      <c r="F57" s="70"/>
+      <c r="G57" s="70"/>
+      <c r="H57" s="70"/>
+      <c r="I57" s="70"/>
+      <c r="J57" s="71"/>
+      <c r="K57" s="72"/>
+      <c r="L57" s="55"/>
+      <c r="M57" s="73"/>
+      <c r="N57" s="74"/>
+      <c r="O57" s="70"/>
+      <c r="P57" s="71"/>
+      <c r="Q57" s="71"/>
+      <c r="R57" s="72"/>
+      <c r="S57" s="55"/>
+      <c r="T57" s="75"/>
+      <c r="U57" s="75"/>
+      <c r="V57" s="75"/>
+    </row>
+    <row r="58" spans="1:22" s="15" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B58" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="C58" s="2">
+        <f>SUM(C7:C57)</f>
+        <v>46639</v>
+      </c>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2">
+        <f t="shared" ref="F58:K58" si="11">SUM(F7:F57)</f>
+        <v>0</v>
+      </c>
+      <c r="G58" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="H58" s="2">
+        <f t="shared" si="11"/>
+        <v>1192</v>
+      </c>
+      <c r="I58" s="6">
+        <f t="shared" si="11"/>
+        <v>38</v>
+      </c>
+      <c r="J58" s="6">
+        <f t="shared" si="11"/>
+        <v>26</v>
+      </c>
+      <c r="K58" s="6">
+        <f t="shared" si="11"/>
+        <v>619</v>
+      </c>
+      <c r="M58" s="5">
+        <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
+        <v>1077</v>
+      </c>
+      <c r="N58" s="5">
+        <f t="shared" si="12"/>
+        <v>10</v>
+      </c>
+      <c r="O58" s="5">
+        <f t="shared" si="12"/>
+        <v>616</v>
+      </c>
+      <c r="P58" s="5">
+        <f t="shared" si="12"/>
+        <v>29</v>
+      </c>
+      <c r="Q58" s="5">
+        <f t="shared" si="12"/>
+        <v>922</v>
+      </c>
+      <c r="R58" s="5">
+        <f t="shared" si="12"/>
+        <v>16</v>
+      </c>
+      <c r="S58" s="55"/>
+      <c r="T58" s="4">
+        <f>SUM(T7:T57)</f>
+        <v>1930</v>
+      </c>
+      <c r="U58" s="90">
+        <f>SUM(U7:U57)</f>
+        <v>373336</v>
+      </c>
+      <c r="V58" s="4">
+        <f>SUM(V7:V57)</f>
+        <v>49413.916666666672</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="60" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="C60" s="110" t="s">
+        <v>41</v>
+      </c>
+      <c r="D60" s="111"/>
+      <c r="E60" s="111"/>
+      <c r="F60" s="111"/>
+      <c r="G60" s="111"/>
+      <c r="H60" s="111"/>
+      <c r="I60" s="111"/>
+      <c r="J60" s="111"/>
+      <c r="K60" s="112"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -30079,21 +36324,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="111" t="s">
+      <c r="I1" s="113" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="111"/>
-      <c r="K1" s="111"/>
-      <c r="L1" s="111"/>
-      <c r="M1" s="111"/>
-      <c r="N1" s="111"/>
-      <c r="O1" s="111"/>
-      <c r="P1" s="111"/>
-      <c r="Q1" s="111"/>
-      <c r="R1" s="111"/>
-      <c r="S1" s="111"/>
-      <c r="T1" s="111"/>
-      <c r="U1" s="111"/>
+      <c r="J1" s="113"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="113"/>
+      <c r="M1" s="113"/>
+      <c r="N1" s="113"/>
+      <c r="O1" s="113"/>
+      <c r="P1" s="113"/>
+      <c r="Q1" s="113"/>
+      <c r="R1" s="113"/>
+      <c r="S1" s="113"/>
+      <c r="T1" s="113"/>
+      <c r="U1" s="113"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -30105,17 +36350,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="112" t="s">
+      <c r="C4" s="114" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="112"/>
-      <c r="E4" s="112"/>
-      <c r="F4" s="112"/>
-      <c r="G4" s="112"/>
-      <c r="H4" s="112"/>
-      <c r="I4" s="112"/>
-      <c r="J4" s="113"/>
-      <c r="K4" s="114"/>
+      <c r="D4" s="114"/>
+      <c r="E4" s="114"/>
+      <c r="F4" s="114"/>
+      <c r="G4" s="114"/>
+      <c r="H4" s="114"/>
+      <c r="I4" s="114"/>
+      <c r="J4" s="115"/>
+      <c r="K4" s="116"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -30135,13 +36380,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="115" t="s">
+      <c r="T4" s="117" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="121" t="s">
+      <c r="U4" s="123" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="104" t="s">
+      <c r="V4" s="106" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -30181,10 +36426,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="119" t="s">
+      <c r="J5" s="121" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="120"/>
+      <c r="K5" s="122"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -30192,9 +36437,9 @@
       <c r="Q5" s="96"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="116"/>
-      <c r="U5" s="122"/>
-      <c r="V5" s="105"/>
+      <c r="T5" s="118"/>
+      <c r="U5" s="124"/>
+      <c r="V5" s="107"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -32904,17 +39149,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="108" t="s">
+      <c r="C60" s="110" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="109"/>
-      <c r="E60" s="109"/>
-      <c r="F60" s="109"/>
-      <c r="G60" s="109"/>
-      <c r="H60" s="109"/>
-      <c r="I60" s="109"/>
-      <c r="J60" s="109"/>
-      <c r="K60" s="110"/>
+      <c r="D60" s="111"/>
+      <c r="E60" s="111"/>
+      <c r="F60" s="111"/>
+      <c r="G60" s="111"/>
+      <c r="H60" s="111"/>
+      <c r="I60" s="111"/>
+      <c r="J60" s="111"/>
+      <c r="K60" s="112"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -33223,21 +39468,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="111" t="s">
+      <c r="I1" s="113" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="111"/>
-      <c r="K1" s="111"/>
-      <c r="L1" s="111"/>
-      <c r="M1" s="111"/>
-      <c r="N1" s="111"/>
-      <c r="O1" s="111"/>
-      <c r="P1" s="111"/>
-      <c r="Q1" s="111"/>
-      <c r="R1" s="111"/>
-      <c r="S1" s="111"/>
-      <c r="T1" s="111"/>
-      <c r="U1" s="111"/>
+      <c r="J1" s="113"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="113"/>
+      <c r="M1" s="113"/>
+      <c r="N1" s="113"/>
+      <c r="O1" s="113"/>
+      <c r="P1" s="113"/>
+      <c r="Q1" s="113"/>
+      <c r="R1" s="113"/>
+      <c r="S1" s="113"/>
+      <c r="T1" s="113"/>
+      <c r="U1" s="113"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -33249,17 +39494,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="112" t="s">
+      <c r="C4" s="114" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="112"/>
-      <c r="E4" s="112"/>
-      <c r="F4" s="112"/>
-      <c r="G4" s="112"/>
-      <c r="H4" s="112"/>
-      <c r="I4" s="112"/>
-      <c r="J4" s="113"/>
-      <c r="K4" s="114"/>
+      <c r="D4" s="114"/>
+      <c r="E4" s="114"/>
+      <c r="F4" s="114"/>
+      <c r="G4" s="114"/>
+      <c r="H4" s="114"/>
+      <c r="I4" s="114"/>
+      <c r="J4" s="115"/>
+      <c r="K4" s="116"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -33279,13 +39524,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="115" t="s">
+      <c r="T4" s="117" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="121" t="s">
+      <c r="U4" s="123" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="104" t="s">
+      <c r="V4" s="106" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -33325,10 +39570,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="119" t="s">
+      <c r="J5" s="121" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="120"/>
+      <c r="K5" s="122"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -33336,9 +39581,9 @@
       <c r="Q5" s="97"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="116"/>
-      <c r="U5" s="122"/>
-      <c r="V5" s="105"/>
+      <c r="T5" s="118"/>
+      <c r="U5" s="124"/>
+      <c r="V5" s="107"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -36038,17 +42283,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="108" t="s">
+      <c r="C60" s="110" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="109"/>
-      <c r="E60" s="109"/>
-      <c r="F60" s="109"/>
-      <c r="G60" s="109"/>
-      <c r="H60" s="109"/>
-      <c r="I60" s="109"/>
-      <c r="J60" s="109"/>
-      <c r="K60" s="110"/>
+      <c r="D60" s="111"/>
+      <c r="E60" s="111"/>
+      <c r="F60" s="111"/>
+      <c r="G60" s="111"/>
+      <c r="H60" s="111"/>
+      <c r="I60" s="111"/>
+      <c r="J60" s="111"/>
+      <c r="K60" s="112"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -36357,21 +42602,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="111" t="s">
+      <c r="I1" s="113" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="111"/>
-      <c r="K1" s="111"/>
-      <c r="L1" s="111"/>
-      <c r="M1" s="111"/>
-      <c r="N1" s="111"/>
-      <c r="O1" s="111"/>
-      <c r="P1" s="111"/>
-      <c r="Q1" s="111"/>
-      <c r="R1" s="111"/>
-      <c r="S1" s="111"/>
-      <c r="T1" s="111"/>
-      <c r="U1" s="111"/>
+      <c r="J1" s="113"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="113"/>
+      <c r="M1" s="113"/>
+      <c r="N1" s="113"/>
+      <c r="O1" s="113"/>
+      <c r="P1" s="113"/>
+      <c r="Q1" s="113"/>
+      <c r="R1" s="113"/>
+      <c r="S1" s="113"/>
+      <c r="T1" s="113"/>
+      <c r="U1" s="113"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -36383,17 +42628,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="112" t="s">
+      <c r="C4" s="114" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="112"/>
-      <c r="E4" s="112"/>
-      <c r="F4" s="112"/>
-      <c r="G4" s="112"/>
-      <c r="H4" s="112"/>
-      <c r="I4" s="112"/>
-      <c r="J4" s="113"/>
-      <c r="K4" s="114"/>
+      <c r="D4" s="114"/>
+      <c r="E4" s="114"/>
+      <c r="F4" s="114"/>
+      <c r="G4" s="114"/>
+      <c r="H4" s="114"/>
+      <c r="I4" s="114"/>
+      <c r="J4" s="115"/>
+      <c r="K4" s="116"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -36413,13 +42658,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="115" t="s">
+      <c r="T4" s="117" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="121" t="s">
+      <c r="U4" s="123" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="104" t="s">
+      <c r="V4" s="106" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -36459,10 +42704,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="119" t="s">
+      <c r="J5" s="121" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="120"/>
+      <c r="K5" s="122"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -36470,9 +42715,9 @@
       <c r="Q5" s="97"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="116"/>
-      <c r="U5" s="122"/>
-      <c r="V5" s="105"/>
+      <c r="T5" s="118"/>
+      <c r="U5" s="124"/>
+      <c r="V5" s="107"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -39172,17 +45417,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="108" t="s">
+      <c r="C60" s="110" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="109"/>
-      <c r="E60" s="109"/>
-      <c r="F60" s="109"/>
-      <c r="G60" s="109"/>
-      <c r="H60" s="109"/>
-      <c r="I60" s="109"/>
-      <c r="J60" s="109"/>
-      <c r="K60" s="110"/>
+      <c r="D60" s="111"/>
+      <c r="E60" s="111"/>
+      <c r="F60" s="111"/>
+      <c r="G60" s="111"/>
+      <c r="H60" s="111"/>
+      <c r="I60" s="111"/>
+      <c r="J60" s="111"/>
+      <c r="K60" s="112"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -39491,21 +45736,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="111" t="s">
+      <c r="I1" s="113" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="111"/>
-      <c r="K1" s="111"/>
-      <c r="L1" s="111"/>
-      <c r="M1" s="111"/>
-      <c r="N1" s="111"/>
-      <c r="O1" s="111"/>
-      <c r="P1" s="111"/>
-      <c r="Q1" s="111"/>
-      <c r="R1" s="111"/>
-      <c r="S1" s="111"/>
-      <c r="T1" s="111"/>
-      <c r="U1" s="111"/>
+      <c r="J1" s="113"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="113"/>
+      <c r="M1" s="113"/>
+      <c r="N1" s="113"/>
+      <c r="O1" s="113"/>
+      <c r="P1" s="113"/>
+      <c r="Q1" s="113"/>
+      <c r="R1" s="113"/>
+      <c r="S1" s="113"/>
+      <c r="T1" s="113"/>
+      <c r="U1" s="113"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -39517,17 +45762,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="112" t="s">
+      <c r="C4" s="114" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="112"/>
-      <c r="E4" s="112"/>
-      <c r="F4" s="112"/>
-      <c r="G4" s="112"/>
-      <c r="H4" s="112"/>
-      <c r="I4" s="112"/>
-      <c r="J4" s="113"/>
-      <c r="K4" s="114"/>
+      <c r="D4" s="114"/>
+      <c r="E4" s="114"/>
+      <c r="F4" s="114"/>
+      <c r="G4" s="114"/>
+      <c r="H4" s="114"/>
+      <c r="I4" s="114"/>
+      <c r="J4" s="115"/>
+      <c r="K4" s="116"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -39547,13 +45792,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="115" t="s">
+      <c r="T4" s="117" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="121" t="s">
+      <c r="U4" s="123" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="104" t="s">
+      <c r="V4" s="106" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -39593,10 +45838,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="119" t="s">
+      <c r="J5" s="121" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="120"/>
+      <c r="K5" s="122"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -39604,9 +45849,9 @@
       <c r="Q5" s="97"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="116"/>
-      <c r="U5" s="122"/>
-      <c r="V5" s="105"/>
+      <c r="T5" s="118"/>
+      <c r="U5" s="124"/>
+      <c r="V5" s="107"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -42296,17 +48541,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="108" t="s">
+      <c r="C60" s="110" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="109"/>
-      <c r="E60" s="109"/>
-      <c r="F60" s="109"/>
-      <c r="G60" s="109"/>
-      <c r="H60" s="109"/>
-      <c r="I60" s="109"/>
-      <c r="J60" s="109"/>
-      <c r="K60" s="110"/>
+      <c r="D60" s="111"/>
+      <c r="E60" s="111"/>
+      <c r="F60" s="111"/>
+      <c r="G60" s="111"/>
+      <c r="H60" s="111"/>
+      <c r="I60" s="111"/>
+      <c r="J60" s="111"/>
+      <c r="K60" s="112"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -42615,21 +48860,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="111" t="s">
+      <c r="I1" s="113" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="111"/>
-      <c r="K1" s="111"/>
-      <c r="L1" s="111"/>
-      <c r="M1" s="111"/>
-      <c r="N1" s="111"/>
-      <c r="O1" s="111"/>
-      <c r="P1" s="111"/>
-      <c r="Q1" s="111"/>
-      <c r="R1" s="111"/>
-      <c r="S1" s="111"/>
-      <c r="T1" s="111"/>
-      <c r="U1" s="111"/>
+      <c r="J1" s="113"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="113"/>
+      <c r="M1" s="113"/>
+      <c r="N1" s="113"/>
+      <c r="O1" s="113"/>
+      <c r="P1" s="113"/>
+      <c r="Q1" s="113"/>
+      <c r="R1" s="113"/>
+      <c r="S1" s="113"/>
+      <c r="T1" s="113"/>
+      <c r="U1" s="113"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -42641,17 +48886,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="112" t="s">
+      <c r="C4" s="114" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="112"/>
-      <c r="E4" s="112"/>
-      <c r="F4" s="112"/>
-      <c r="G4" s="112"/>
-      <c r="H4" s="112"/>
-      <c r="I4" s="112"/>
-      <c r="J4" s="113"/>
-      <c r="K4" s="114"/>
+      <c r="D4" s="114"/>
+      <c r="E4" s="114"/>
+      <c r="F4" s="114"/>
+      <c r="G4" s="114"/>
+      <c r="H4" s="114"/>
+      <c r="I4" s="114"/>
+      <c r="J4" s="115"/>
+      <c r="K4" s="116"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -42671,13 +48916,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="115" t="s">
+      <c r="T4" s="117" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="121" t="s">
+      <c r="U4" s="123" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="104" t="s">
+      <c r="V4" s="106" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -42717,10 +48962,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="119" t="s">
+      <c r="J5" s="121" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="120"/>
+      <c r="K5" s="122"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -42728,9 +48973,9 @@
       <c r="Q5" s="98"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="116"/>
-      <c r="U5" s="122"/>
-      <c r="V5" s="105"/>
+      <c r="T5" s="118"/>
+      <c r="U5" s="124"/>
+      <c r="V5" s="107"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -45445,17 +51690,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="108" t="s">
+      <c r="C60" s="110" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="109"/>
-      <c r="E60" s="109"/>
-      <c r="F60" s="109"/>
-      <c r="G60" s="109"/>
-      <c r="H60" s="109"/>
-      <c r="I60" s="109"/>
-      <c r="J60" s="109"/>
-      <c r="K60" s="110"/>
+      <c r="D60" s="111"/>
+      <c r="E60" s="111"/>
+      <c r="F60" s="111"/>
+      <c r="G60" s="111"/>
+      <c r="H60" s="111"/>
+      <c r="I60" s="111"/>
+      <c r="J60" s="111"/>
+      <c r="K60" s="112"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -45764,21 +52009,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="111" t="s">
+      <c r="I1" s="113" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="111"/>
-      <c r="K1" s="111"/>
-      <c r="L1" s="111"/>
-      <c r="M1" s="111"/>
-      <c r="N1" s="111"/>
-      <c r="O1" s="111"/>
-      <c r="P1" s="111"/>
-      <c r="Q1" s="111"/>
-      <c r="R1" s="111"/>
-      <c r="S1" s="111"/>
-      <c r="T1" s="111"/>
-      <c r="U1" s="111"/>
+      <c r="J1" s="113"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="113"/>
+      <c r="M1" s="113"/>
+      <c r="N1" s="113"/>
+      <c r="O1" s="113"/>
+      <c r="P1" s="113"/>
+      <c r="Q1" s="113"/>
+      <c r="R1" s="113"/>
+      <c r="S1" s="113"/>
+      <c r="T1" s="113"/>
+      <c r="U1" s="113"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -45790,17 +52035,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="112" t="s">
+      <c r="C4" s="114" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="112"/>
-      <c r="E4" s="112"/>
-      <c r="F4" s="112"/>
-      <c r="G4" s="112"/>
-      <c r="H4" s="112"/>
-      <c r="I4" s="112"/>
-      <c r="J4" s="113"/>
-      <c r="K4" s="114"/>
+      <c r="D4" s="114"/>
+      <c r="E4" s="114"/>
+      <c r="F4" s="114"/>
+      <c r="G4" s="114"/>
+      <c r="H4" s="114"/>
+      <c r="I4" s="114"/>
+      <c r="J4" s="115"/>
+      <c r="K4" s="116"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -45820,13 +52065,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="115" t="s">
+      <c r="T4" s="117" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="121" t="s">
+      <c r="U4" s="123" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="104" t="s">
+      <c r="V4" s="106" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -45866,10 +52111,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="119" t="s">
+      <c r="J5" s="121" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="120"/>
+      <c r="K5" s="122"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -45877,9 +52122,9 @@
       <c r="Q5" s="98"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="116"/>
-      <c r="U5" s="122"/>
-      <c r="V5" s="105"/>
+      <c r="T5" s="118"/>
+      <c r="U5" s="124"/>
+      <c r="V5" s="107"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -48584,17 +54829,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="108" t="s">
+      <c r="C60" s="110" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="109"/>
-      <c r="E60" s="109"/>
-      <c r="F60" s="109"/>
-      <c r="G60" s="109"/>
-      <c r="H60" s="109"/>
-      <c r="I60" s="109"/>
-      <c r="J60" s="109"/>
-      <c r="K60" s="110"/>
+      <c r="D60" s="111"/>
+      <c r="E60" s="111"/>
+      <c r="F60" s="111"/>
+      <c r="G60" s="111"/>
+      <c r="H60" s="111"/>
+      <c r="I60" s="111"/>
+      <c r="J60" s="111"/>
+      <c r="K60" s="112"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -48903,21 +55148,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="111" t="s">
+      <c r="I1" s="113" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="111"/>
-      <c r="K1" s="111"/>
-      <c r="L1" s="111"/>
-      <c r="M1" s="111"/>
-      <c r="N1" s="111"/>
-      <c r="O1" s="111"/>
-      <c r="P1" s="111"/>
-      <c r="Q1" s="111"/>
-      <c r="R1" s="111"/>
-      <c r="S1" s="111"/>
-      <c r="T1" s="111"/>
-      <c r="U1" s="111"/>
+      <c r="J1" s="113"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="113"/>
+      <c r="M1" s="113"/>
+      <c r="N1" s="113"/>
+      <c r="O1" s="113"/>
+      <c r="P1" s="113"/>
+      <c r="Q1" s="113"/>
+      <c r="R1" s="113"/>
+      <c r="S1" s="113"/>
+      <c r="T1" s="113"/>
+      <c r="U1" s="113"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -48929,17 +55174,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="112" t="s">
+      <c r="C4" s="114" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="112"/>
-      <c r="E4" s="112"/>
-      <c r="F4" s="112"/>
-      <c r="G4" s="112"/>
-      <c r="H4" s="112"/>
-      <c r="I4" s="112"/>
-      <c r="J4" s="113"/>
-      <c r="K4" s="114"/>
+      <c r="D4" s="114"/>
+      <c r="E4" s="114"/>
+      <c r="F4" s="114"/>
+      <c r="G4" s="114"/>
+      <c r="H4" s="114"/>
+      <c r="I4" s="114"/>
+      <c r="J4" s="115"/>
+      <c r="K4" s="116"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -48959,13 +55204,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="115" t="s">
+      <c r="T4" s="117" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="121" t="s">
+      <c r="U4" s="123" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="104" t="s">
+      <c r="V4" s="106" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -49005,10 +55250,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="119" t="s">
+      <c r="J5" s="121" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="120"/>
+      <c r="K5" s="122"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -49016,9 +55261,9 @@
       <c r="Q5" s="98"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="116"/>
-      <c r="U5" s="122"/>
-      <c r="V5" s="105"/>
+      <c r="T5" s="118"/>
+      <c r="U5" s="124"/>
+      <c r="V5" s="107"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -51720,17 +57965,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="108" t="s">
+      <c r="C60" s="110" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="109"/>
-      <c r="E60" s="109"/>
-      <c r="F60" s="109"/>
-      <c r="G60" s="109"/>
-      <c r="H60" s="109"/>
-      <c r="I60" s="109"/>
-      <c r="J60" s="109"/>
-      <c r="K60" s="110"/>
+      <c r="D60" s="111"/>
+      <c r="E60" s="111"/>
+      <c r="F60" s="111"/>
+      <c r="G60" s="111"/>
+      <c r="H60" s="111"/>
+      <c r="I60" s="111"/>
+      <c r="J60" s="111"/>
+      <c r="K60" s="112"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -52039,21 +58284,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="111" t="s">
+      <c r="I1" s="113" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="111"/>
-      <c r="K1" s="111"/>
-      <c r="L1" s="111"/>
-      <c r="M1" s="111"/>
-      <c r="N1" s="111"/>
-      <c r="O1" s="111"/>
-      <c r="P1" s="111"/>
-      <c r="Q1" s="111"/>
-      <c r="R1" s="111"/>
-      <c r="S1" s="111"/>
-      <c r="T1" s="111"/>
-      <c r="U1" s="111"/>
+      <c r="J1" s="113"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="113"/>
+      <c r="M1" s="113"/>
+      <c r="N1" s="113"/>
+      <c r="O1" s="113"/>
+      <c r="P1" s="113"/>
+      <c r="Q1" s="113"/>
+      <c r="R1" s="113"/>
+      <c r="S1" s="113"/>
+      <c r="T1" s="113"/>
+      <c r="U1" s="113"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -52065,17 +58310,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="112" t="s">
+      <c r="C4" s="114" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="112"/>
-      <c r="E4" s="112"/>
-      <c r="F4" s="112"/>
-      <c r="G4" s="112"/>
-      <c r="H4" s="112"/>
-      <c r="I4" s="112"/>
-      <c r="J4" s="113"/>
-      <c r="K4" s="114"/>
+      <c r="D4" s="114"/>
+      <c r="E4" s="114"/>
+      <c r="F4" s="114"/>
+      <c r="G4" s="114"/>
+      <c r="H4" s="114"/>
+      <c r="I4" s="114"/>
+      <c r="J4" s="115"/>
+      <c r="K4" s="116"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -52095,13 +58340,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="115" t="s">
+      <c r="T4" s="117" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="121" t="s">
+      <c r="U4" s="123" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="104" t="s">
+      <c r="V4" s="106" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -52141,10 +58386,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="119" t="s">
+      <c r="J5" s="121" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="120"/>
+      <c r="K5" s="122"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -52152,9 +58397,9 @@
       <c r="Q5" s="98"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="116"/>
-      <c r="U5" s="122"/>
-      <c r="V5" s="105"/>
+      <c r="T5" s="118"/>
+      <c r="U5" s="124"/>
+      <c r="V5" s="107"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -54866,17 +61111,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="108" t="s">
+      <c r="C60" s="110" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="109"/>
-      <c r="E60" s="109"/>
-      <c r="F60" s="109"/>
-      <c r="G60" s="109"/>
-      <c r="H60" s="109"/>
-      <c r="I60" s="109"/>
-      <c r="J60" s="109"/>
-      <c r="K60" s="110"/>
+      <c r="D60" s="111"/>
+      <c r="E60" s="111"/>
+      <c r="F60" s="111"/>
+      <c r="G60" s="111"/>
+      <c r="H60" s="111"/>
+      <c r="I60" s="111"/>
+      <c r="J60" s="111"/>
+      <c r="K60" s="112"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>

--- a/GBDS AUGUST FILES 2026/INVENTORY COUNT SHEET - AUGUST 2026.xlsx
+++ b/GBDS AUGUST FILES 2026/INVENTORY COUNT SHEET - AUGUST 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS AUGUST FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F894931-DDD2-4BE0-83DB-DC5650DE07A1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BDE953D-2D23-4B89-91F2-7CCB7E5F6321}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="9" activeTab="18" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="10" activeTab="18" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
   </bookViews>
   <sheets>
     <sheet name="SAMPLE" sheetId="32" r:id="rId1"/>
@@ -32,6 +32,7 @@
     <sheet name="08-21-2026" sheetId="84" r:id="rId17"/>
     <sheet name="08-24-2026" sheetId="85" r:id="rId18"/>
     <sheet name="08-25-2026" sheetId="86" r:id="rId19"/>
+    <sheet name="08-26-2026" sheetId="87" r:id="rId20"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'08-03-2026'!$A$1:$W$59</definedName>
@@ -52,6 +53,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="16">'08-21-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="17">'08-24-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="18">'08-25-2026'!$A$1:$W$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="19">'08-26-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">SAMPLE!$A$1:$W$85</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -70,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1596" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1680" uniqueCount="90">
   <si>
     <t>ROUTE 1</t>
   </si>
@@ -338,6 +340,9 @@
   </si>
   <si>
     <t>DATE: 08/25/2026</t>
+  </si>
+  <si>
+    <t>DATE: 08/26/2026</t>
   </si>
 </sst>
 </file>
@@ -1324,7 +1329,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="125">
+  <cellXfs count="126">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1610,6 +1615,9 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="63" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2053,21 +2061,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="113" t="s">
+      <c r="I1" s="114" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="113"/>
-      <c r="K1" s="113"/>
-      <c r="L1" s="113"/>
-      <c r="M1" s="113"/>
-      <c r="N1" s="113"/>
-      <c r="O1" s="113"/>
-      <c r="P1" s="113"/>
-      <c r="Q1" s="113"/>
-      <c r="R1" s="113"/>
-      <c r="S1" s="113"/>
-      <c r="T1" s="113"/>
-      <c r="U1" s="113"/>
+      <c r="J1" s="114"/>
+      <c r="K1" s="114"/>
+      <c r="L1" s="114"/>
+      <c r="M1" s="114"/>
+      <c r="N1" s="114"/>
+      <c r="O1" s="114"/>
+      <c r="P1" s="114"/>
+      <c r="Q1" s="114"/>
+      <c r="R1" s="114"/>
+      <c r="S1" s="114"/>
+      <c r="T1" s="114"/>
+      <c r="U1" s="114"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -2079,17 +2087,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="114" t="s">
+      <c r="C4" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="114"/>
-      <c r="E4" s="114"/>
-      <c r="F4" s="114"/>
-      <c r="G4" s="114"/>
-      <c r="H4" s="114"/>
-      <c r="I4" s="114"/>
-      <c r="J4" s="115"/>
-      <c r="K4" s="116"/>
+      <c r="D4" s="115"/>
+      <c r="E4" s="115"/>
+      <c r="F4" s="115"/>
+      <c r="G4" s="115"/>
+      <c r="H4" s="115"/>
+      <c r="I4" s="115"/>
+      <c r="J4" s="116"/>
+      <c r="K4" s="117"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -2109,13 +2117,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="117" t="s">
+      <c r="T4" s="118" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="119" t="s">
+      <c r="U4" s="120" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="106" t="s">
+      <c r="V4" s="107" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -2155,10 +2163,10 @@
       <c r="I5" s="93" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="108" t="s">
+      <c r="J5" s="109" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="109"/>
+      <c r="K5" s="110"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -2166,9 +2174,9 @@
       <c r="Q5" s="89"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="118"/>
-      <c r="U5" s="120"/>
-      <c r="V5" s="107"/>
+      <c r="T5" s="119"/>
+      <c r="U5" s="121"/>
+      <c r="V5" s="108"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -4699,17 +4707,17 @@
       <c r="B62" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C62" s="110" t="s">
+      <c r="C62" s="111" t="s">
         <v>41</v>
       </c>
-      <c r="D62" s="111"/>
-      <c r="E62" s="111"/>
-      <c r="F62" s="111"/>
-      <c r="G62" s="111"/>
-      <c r="H62" s="111"/>
-      <c r="I62" s="111"/>
-      <c r="J62" s="111"/>
-      <c r="K62" s="112"/>
+      <c r="D62" s="112"/>
+      <c r="E62" s="112"/>
+      <c r="F62" s="112"/>
+      <c r="G62" s="112"/>
+      <c r="H62" s="112"/>
+      <c r="I62" s="112"/>
+      <c r="J62" s="112"/>
+      <c r="K62" s="113"/>
       <c r="U62" s="24" t="s">
         <v>51</v>
       </c>
@@ -5018,21 +5026,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="113" t="s">
+      <c r="I1" s="114" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="113"/>
-      <c r="K1" s="113"/>
-      <c r="L1" s="113"/>
-      <c r="M1" s="113"/>
-      <c r="N1" s="113"/>
-      <c r="O1" s="113"/>
-      <c r="P1" s="113"/>
-      <c r="Q1" s="113"/>
-      <c r="R1" s="113"/>
-      <c r="S1" s="113"/>
-      <c r="T1" s="113"/>
-      <c r="U1" s="113"/>
+      <c r="J1" s="114"/>
+      <c r="K1" s="114"/>
+      <c r="L1" s="114"/>
+      <c r="M1" s="114"/>
+      <c r="N1" s="114"/>
+      <c r="O1" s="114"/>
+      <c r="P1" s="114"/>
+      <c r="Q1" s="114"/>
+      <c r="R1" s="114"/>
+      <c r="S1" s="114"/>
+      <c r="T1" s="114"/>
+      <c r="U1" s="114"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -5044,17 +5052,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="114" t="s">
+      <c r="C4" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="114"/>
-      <c r="E4" s="114"/>
-      <c r="F4" s="114"/>
-      <c r="G4" s="114"/>
-      <c r="H4" s="114"/>
-      <c r="I4" s="114"/>
-      <c r="J4" s="115"/>
-      <c r="K4" s="116"/>
+      <c r="D4" s="115"/>
+      <c r="E4" s="115"/>
+      <c r="F4" s="115"/>
+      <c r="G4" s="115"/>
+      <c r="H4" s="115"/>
+      <c r="I4" s="115"/>
+      <c r="J4" s="116"/>
+      <c r="K4" s="117"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -5074,13 +5082,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="117" t="s">
+      <c r="T4" s="118" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="123" t="s">
+      <c r="U4" s="124" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="106" t="s">
+      <c r="V4" s="107" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -5120,10 +5128,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="121" t="s">
+      <c r="J5" s="122" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="122"/>
+      <c r="K5" s="123"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -5131,9 +5139,9 @@
       <c r="Q5" s="99"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="118"/>
-      <c r="U5" s="124"/>
-      <c r="V5" s="107"/>
+      <c r="T5" s="119"/>
+      <c r="U5" s="125"/>
+      <c r="V5" s="108"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -7844,17 +7852,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="110" t="s">
+      <c r="C60" s="111" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="111"/>
-      <c r="E60" s="111"/>
-      <c r="F60" s="111"/>
-      <c r="G60" s="111"/>
-      <c r="H60" s="111"/>
-      <c r="I60" s="111"/>
-      <c r="J60" s="111"/>
-      <c r="K60" s="112"/>
+      <c r="D60" s="112"/>
+      <c r="E60" s="112"/>
+      <c r="F60" s="112"/>
+      <c r="G60" s="112"/>
+      <c r="H60" s="112"/>
+      <c r="I60" s="112"/>
+      <c r="J60" s="112"/>
+      <c r="K60" s="113"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -8163,21 +8171,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="113" t="s">
+      <c r="I1" s="114" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="113"/>
-      <c r="K1" s="113"/>
-      <c r="L1" s="113"/>
-      <c r="M1" s="113"/>
-      <c r="N1" s="113"/>
-      <c r="O1" s="113"/>
-      <c r="P1" s="113"/>
-      <c r="Q1" s="113"/>
-      <c r="R1" s="113"/>
-      <c r="S1" s="113"/>
-      <c r="T1" s="113"/>
-      <c r="U1" s="113"/>
+      <c r="J1" s="114"/>
+      <c r="K1" s="114"/>
+      <c r="L1" s="114"/>
+      <c r="M1" s="114"/>
+      <c r="N1" s="114"/>
+      <c r="O1" s="114"/>
+      <c r="P1" s="114"/>
+      <c r="Q1" s="114"/>
+      <c r="R1" s="114"/>
+      <c r="S1" s="114"/>
+      <c r="T1" s="114"/>
+      <c r="U1" s="114"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -8189,17 +8197,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="114" t="s">
+      <c r="C4" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="114"/>
-      <c r="E4" s="114"/>
-      <c r="F4" s="114"/>
-      <c r="G4" s="114"/>
-      <c r="H4" s="114"/>
-      <c r="I4" s="114"/>
-      <c r="J4" s="115"/>
-      <c r="K4" s="116"/>
+      <c r="D4" s="115"/>
+      <c r="E4" s="115"/>
+      <c r="F4" s="115"/>
+      <c r="G4" s="115"/>
+      <c r="H4" s="115"/>
+      <c r="I4" s="115"/>
+      <c r="J4" s="116"/>
+      <c r="K4" s="117"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -8219,13 +8227,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="117" t="s">
+      <c r="T4" s="118" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="123" t="s">
+      <c r="U4" s="124" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="106" t="s">
+      <c r="V4" s="107" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -8265,10 +8273,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="121" t="s">
+      <c r="J5" s="122" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="122"/>
+      <c r="K5" s="123"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -8276,9 +8284,9 @@
       <c r="Q5" s="99"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="118"/>
-      <c r="U5" s="124"/>
-      <c r="V5" s="107"/>
+      <c r="T5" s="119"/>
+      <c r="U5" s="125"/>
+      <c r="V5" s="108"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -10991,17 +10999,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="110" t="s">
+      <c r="C60" s="111" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="111"/>
-      <c r="E60" s="111"/>
-      <c r="F60" s="111"/>
-      <c r="G60" s="111"/>
-      <c r="H60" s="111"/>
-      <c r="I60" s="111"/>
-      <c r="J60" s="111"/>
-      <c r="K60" s="112"/>
+      <c r="D60" s="112"/>
+      <c r="E60" s="112"/>
+      <c r="F60" s="112"/>
+      <c r="G60" s="112"/>
+      <c r="H60" s="112"/>
+      <c r="I60" s="112"/>
+      <c r="J60" s="112"/>
+      <c r="K60" s="113"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -11310,21 +11318,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="113" t="s">
+      <c r="I1" s="114" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="113"/>
-      <c r="K1" s="113"/>
-      <c r="L1" s="113"/>
-      <c r="M1" s="113"/>
-      <c r="N1" s="113"/>
-      <c r="O1" s="113"/>
-      <c r="P1" s="113"/>
-      <c r="Q1" s="113"/>
-      <c r="R1" s="113"/>
-      <c r="S1" s="113"/>
-      <c r="T1" s="113"/>
-      <c r="U1" s="113"/>
+      <c r="J1" s="114"/>
+      <c r="K1" s="114"/>
+      <c r="L1" s="114"/>
+      <c r="M1" s="114"/>
+      <c r="N1" s="114"/>
+      <c r="O1" s="114"/>
+      <c r="P1" s="114"/>
+      <c r="Q1" s="114"/>
+      <c r="R1" s="114"/>
+      <c r="S1" s="114"/>
+      <c r="T1" s="114"/>
+      <c r="U1" s="114"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -11336,17 +11344,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="114" t="s">
+      <c r="C4" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="114"/>
-      <c r="E4" s="114"/>
-      <c r="F4" s="114"/>
-      <c r="G4" s="114"/>
-      <c r="H4" s="114"/>
-      <c r="I4" s="114"/>
-      <c r="J4" s="115"/>
-      <c r="K4" s="116"/>
+      <c r="D4" s="115"/>
+      <c r="E4" s="115"/>
+      <c r="F4" s="115"/>
+      <c r="G4" s="115"/>
+      <c r="H4" s="115"/>
+      <c r="I4" s="115"/>
+      <c r="J4" s="116"/>
+      <c r="K4" s="117"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -11366,13 +11374,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="117" t="s">
+      <c r="T4" s="118" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="123" t="s">
+      <c r="U4" s="124" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="106" t="s">
+      <c r="V4" s="107" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -11412,10 +11420,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="121" t="s">
+      <c r="J5" s="122" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="122"/>
+      <c r="K5" s="123"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -11423,9 +11431,9 @@
       <c r="Q5" s="99"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="118"/>
-      <c r="U5" s="124"/>
-      <c r="V5" s="107"/>
+      <c r="T5" s="119"/>
+      <c r="U5" s="125"/>
+      <c r="V5" s="108"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -14127,17 +14135,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="110" t="s">
+      <c r="C60" s="111" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="111"/>
-      <c r="E60" s="111"/>
-      <c r="F60" s="111"/>
-      <c r="G60" s="111"/>
-      <c r="H60" s="111"/>
-      <c r="I60" s="111"/>
-      <c r="J60" s="111"/>
-      <c r="K60" s="112"/>
+      <c r="D60" s="112"/>
+      <c r="E60" s="112"/>
+      <c r="F60" s="112"/>
+      <c r="G60" s="112"/>
+      <c r="H60" s="112"/>
+      <c r="I60" s="112"/>
+      <c r="J60" s="112"/>
+      <c r="K60" s="113"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -14446,21 +14454,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="113" t="s">
+      <c r="I1" s="114" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="113"/>
-      <c r="K1" s="113"/>
-      <c r="L1" s="113"/>
-      <c r="M1" s="113"/>
-      <c r="N1" s="113"/>
-      <c r="O1" s="113"/>
-      <c r="P1" s="113"/>
-      <c r="Q1" s="113"/>
-      <c r="R1" s="113"/>
-      <c r="S1" s="113"/>
-      <c r="T1" s="113"/>
-      <c r="U1" s="113"/>
+      <c r="J1" s="114"/>
+      <c r="K1" s="114"/>
+      <c r="L1" s="114"/>
+      <c r="M1" s="114"/>
+      <c r="N1" s="114"/>
+      <c r="O1" s="114"/>
+      <c r="P1" s="114"/>
+      <c r="Q1" s="114"/>
+      <c r="R1" s="114"/>
+      <c r="S1" s="114"/>
+      <c r="T1" s="114"/>
+      <c r="U1" s="114"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -14472,17 +14480,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="114" t="s">
+      <c r="C4" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="114"/>
-      <c r="E4" s="114"/>
-      <c r="F4" s="114"/>
-      <c r="G4" s="114"/>
-      <c r="H4" s="114"/>
-      <c r="I4" s="114"/>
-      <c r="J4" s="115"/>
-      <c r="K4" s="116"/>
+      <c r="D4" s="115"/>
+      <c r="E4" s="115"/>
+      <c r="F4" s="115"/>
+      <c r="G4" s="115"/>
+      <c r="H4" s="115"/>
+      <c r="I4" s="115"/>
+      <c r="J4" s="116"/>
+      <c r="K4" s="117"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -14502,13 +14510,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="117" t="s">
+      <c r="T4" s="118" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="123" t="s">
+      <c r="U4" s="124" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="106" t="s">
+      <c r="V4" s="107" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -14548,10 +14556,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="121" t="s">
+      <c r="J5" s="122" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="122"/>
+      <c r="K5" s="123"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -14559,9 +14567,9 @@
       <c r="Q5" s="99"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="118"/>
-      <c r="U5" s="124"/>
-      <c r="V5" s="107"/>
+      <c r="T5" s="119"/>
+      <c r="U5" s="125"/>
+      <c r="V5" s="108"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -17262,17 +17270,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="110" t="s">
+      <c r="C60" s="111" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="111"/>
-      <c r="E60" s="111"/>
-      <c r="F60" s="111"/>
-      <c r="G60" s="111"/>
-      <c r="H60" s="111"/>
-      <c r="I60" s="111"/>
-      <c r="J60" s="111"/>
-      <c r="K60" s="112"/>
+      <c r="D60" s="112"/>
+      <c r="E60" s="112"/>
+      <c r="F60" s="112"/>
+      <c r="G60" s="112"/>
+      <c r="H60" s="112"/>
+      <c r="I60" s="112"/>
+      <c r="J60" s="112"/>
+      <c r="K60" s="113"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -17581,21 +17589,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="113" t="s">
+      <c r="I1" s="114" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="113"/>
-      <c r="K1" s="113"/>
-      <c r="L1" s="113"/>
-      <c r="M1" s="113"/>
-      <c r="N1" s="113"/>
-      <c r="O1" s="113"/>
-      <c r="P1" s="113"/>
-      <c r="Q1" s="113"/>
-      <c r="R1" s="113"/>
-      <c r="S1" s="113"/>
-      <c r="T1" s="113"/>
-      <c r="U1" s="113"/>
+      <c r="J1" s="114"/>
+      <c r="K1" s="114"/>
+      <c r="L1" s="114"/>
+      <c r="M1" s="114"/>
+      <c r="N1" s="114"/>
+      <c r="O1" s="114"/>
+      <c r="P1" s="114"/>
+      <c r="Q1" s="114"/>
+      <c r="R1" s="114"/>
+      <c r="S1" s="114"/>
+      <c r="T1" s="114"/>
+      <c r="U1" s="114"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -17607,17 +17615,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="114" t="s">
+      <c r="C4" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="114"/>
-      <c r="E4" s="114"/>
-      <c r="F4" s="114"/>
-      <c r="G4" s="114"/>
-      <c r="H4" s="114"/>
-      <c r="I4" s="114"/>
-      <c r="J4" s="115"/>
-      <c r="K4" s="116"/>
+      <c r="D4" s="115"/>
+      <c r="E4" s="115"/>
+      <c r="F4" s="115"/>
+      <c r="G4" s="115"/>
+      <c r="H4" s="115"/>
+      <c r="I4" s="115"/>
+      <c r="J4" s="116"/>
+      <c r="K4" s="117"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -17637,13 +17645,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="117" t="s">
+      <c r="T4" s="118" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="123" t="s">
+      <c r="U4" s="124" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="106" t="s">
+      <c r="V4" s="107" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -17683,10 +17691,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="121" t="s">
+      <c r="J5" s="122" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="122"/>
+      <c r="K5" s="123"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -17694,9 +17702,9 @@
       <c r="Q5" s="100"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="118"/>
-      <c r="U5" s="124"/>
-      <c r="V5" s="107"/>
+      <c r="T5" s="119"/>
+      <c r="U5" s="125"/>
+      <c r="V5" s="108"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -20391,17 +20399,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="110" t="s">
+      <c r="C60" s="111" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="111"/>
-      <c r="E60" s="111"/>
-      <c r="F60" s="111"/>
-      <c r="G60" s="111"/>
-      <c r="H60" s="111"/>
-      <c r="I60" s="111"/>
-      <c r="J60" s="111"/>
-      <c r="K60" s="112"/>
+      <c r="D60" s="112"/>
+      <c r="E60" s="112"/>
+      <c r="F60" s="112"/>
+      <c r="G60" s="112"/>
+      <c r="H60" s="112"/>
+      <c r="I60" s="112"/>
+      <c r="J60" s="112"/>
+      <c r="K60" s="113"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -20710,21 +20718,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="113" t="s">
+      <c r="I1" s="114" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="113"/>
-      <c r="K1" s="113"/>
-      <c r="L1" s="113"/>
-      <c r="M1" s="113"/>
-      <c r="N1" s="113"/>
-      <c r="O1" s="113"/>
-      <c r="P1" s="113"/>
-      <c r="Q1" s="113"/>
-      <c r="R1" s="113"/>
-      <c r="S1" s="113"/>
-      <c r="T1" s="113"/>
-      <c r="U1" s="113"/>
+      <c r="J1" s="114"/>
+      <c r="K1" s="114"/>
+      <c r="L1" s="114"/>
+      <c r="M1" s="114"/>
+      <c r="N1" s="114"/>
+      <c r="O1" s="114"/>
+      <c r="P1" s="114"/>
+      <c r="Q1" s="114"/>
+      <c r="R1" s="114"/>
+      <c r="S1" s="114"/>
+      <c r="T1" s="114"/>
+      <c r="U1" s="114"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -20736,17 +20744,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="114" t="s">
+      <c r="C4" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="114"/>
-      <c r="E4" s="114"/>
-      <c r="F4" s="114"/>
-      <c r="G4" s="114"/>
-      <c r="H4" s="114"/>
-      <c r="I4" s="114"/>
-      <c r="J4" s="115"/>
-      <c r="K4" s="116"/>
+      <c r="D4" s="115"/>
+      <c r="E4" s="115"/>
+      <c r="F4" s="115"/>
+      <c r="G4" s="115"/>
+      <c r="H4" s="115"/>
+      <c r="I4" s="115"/>
+      <c r="J4" s="116"/>
+      <c r="K4" s="117"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -20766,13 +20774,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="117" t="s">
+      <c r="T4" s="118" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="123" t="s">
+      <c r="U4" s="124" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="106" t="s">
+      <c r="V4" s="107" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -20812,10 +20820,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="121" t="s">
+      <c r="J5" s="122" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="122"/>
+      <c r="K5" s="123"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -20823,9 +20831,9 @@
       <c r="Q5" s="101"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="118"/>
-      <c r="U5" s="124"/>
-      <c r="V5" s="107"/>
+      <c r="T5" s="119"/>
+      <c r="U5" s="125"/>
+      <c r="V5" s="108"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -23516,17 +23524,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="110" t="s">
+      <c r="C60" s="111" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="111"/>
-      <c r="E60" s="111"/>
-      <c r="F60" s="111"/>
-      <c r="G60" s="111"/>
-      <c r="H60" s="111"/>
-      <c r="I60" s="111"/>
-      <c r="J60" s="111"/>
-      <c r="K60" s="112"/>
+      <c r="D60" s="112"/>
+      <c r="E60" s="112"/>
+      <c r="F60" s="112"/>
+      <c r="G60" s="112"/>
+      <c r="H60" s="112"/>
+      <c r="I60" s="112"/>
+      <c r="J60" s="112"/>
+      <c r="K60" s="113"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -23835,21 +23843,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="113" t="s">
+      <c r="I1" s="114" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="113"/>
-      <c r="K1" s="113"/>
-      <c r="L1" s="113"/>
-      <c r="M1" s="113"/>
-      <c r="N1" s="113"/>
-      <c r="O1" s="113"/>
-      <c r="P1" s="113"/>
-      <c r="Q1" s="113"/>
-      <c r="R1" s="113"/>
-      <c r="S1" s="113"/>
-      <c r="T1" s="113"/>
-      <c r="U1" s="113"/>
+      <c r="J1" s="114"/>
+      <c r="K1" s="114"/>
+      <c r="L1" s="114"/>
+      <c r="M1" s="114"/>
+      <c r="N1" s="114"/>
+      <c r="O1" s="114"/>
+      <c r="P1" s="114"/>
+      <c r="Q1" s="114"/>
+      <c r="R1" s="114"/>
+      <c r="S1" s="114"/>
+      <c r="T1" s="114"/>
+      <c r="U1" s="114"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -23861,17 +23869,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="114" t="s">
+      <c r="C4" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="114"/>
-      <c r="E4" s="114"/>
-      <c r="F4" s="114"/>
-      <c r="G4" s="114"/>
-      <c r="H4" s="114"/>
-      <c r="I4" s="114"/>
-      <c r="J4" s="115"/>
-      <c r="K4" s="116"/>
+      <c r="D4" s="115"/>
+      <c r="E4" s="115"/>
+      <c r="F4" s="115"/>
+      <c r="G4" s="115"/>
+      <c r="H4" s="115"/>
+      <c r="I4" s="115"/>
+      <c r="J4" s="116"/>
+      <c r="K4" s="117"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -23891,13 +23899,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="117" t="s">
+      <c r="T4" s="118" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="123" t="s">
+      <c r="U4" s="124" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="106" t="s">
+      <c r="V4" s="107" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -23937,10 +23945,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="121" t="s">
+      <c r="J5" s="122" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="122"/>
+      <c r="K5" s="123"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -23948,9 +23956,9 @@
       <c r="Q5" s="102"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="118"/>
-      <c r="U5" s="124"/>
-      <c r="V5" s="107"/>
+      <c r="T5" s="119"/>
+      <c r="U5" s="125"/>
+      <c r="V5" s="108"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -26658,17 +26666,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="110" t="s">
+      <c r="C60" s="111" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="111"/>
-      <c r="E60" s="111"/>
-      <c r="F60" s="111"/>
-      <c r="G60" s="111"/>
-      <c r="H60" s="111"/>
-      <c r="I60" s="111"/>
-      <c r="J60" s="111"/>
-      <c r="K60" s="112"/>
+      <c r="D60" s="112"/>
+      <c r="E60" s="112"/>
+      <c r="F60" s="112"/>
+      <c r="G60" s="112"/>
+      <c r="H60" s="112"/>
+      <c r="I60" s="112"/>
+      <c r="J60" s="112"/>
+      <c r="K60" s="113"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -26977,21 +26985,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="113" t="s">
+      <c r="I1" s="114" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="113"/>
-      <c r="K1" s="113"/>
-      <c r="L1" s="113"/>
-      <c r="M1" s="113"/>
-      <c r="N1" s="113"/>
-      <c r="O1" s="113"/>
-      <c r="P1" s="113"/>
-      <c r="Q1" s="113"/>
-      <c r="R1" s="113"/>
-      <c r="S1" s="113"/>
-      <c r="T1" s="113"/>
-      <c r="U1" s="113"/>
+      <c r="J1" s="114"/>
+      <c r="K1" s="114"/>
+      <c r="L1" s="114"/>
+      <c r="M1" s="114"/>
+      <c r="N1" s="114"/>
+      <c r="O1" s="114"/>
+      <c r="P1" s="114"/>
+      <c r="Q1" s="114"/>
+      <c r="R1" s="114"/>
+      <c r="S1" s="114"/>
+      <c r="T1" s="114"/>
+      <c r="U1" s="114"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -27003,17 +27011,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="114" t="s">
+      <c r="C4" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="114"/>
-      <c r="E4" s="114"/>
-      <c r="F4" s="114"/>
-      <c r="G4" s="114"/>
-      <c r="H4" s="114"/>
-      <c r="I4" s="114"/>
-      <c r="J4" s="115"/>
-      <c r="K4" s="116"/>
+      <c r="D4" s="115"/>
+      <c r="E4" s="115"/>
+      <c r="F4" s="115"/>
+      <c r="G4" s="115"/>
+      <c r="H4" s="115"/>
+      <c r="I4" s="115"/>
+      <c r="J4" s="116"/>
+      <c r="K4" s="117"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -27033,13 +27041,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="117" t="s">
+      <c r="T4" s="118" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="123" t="s">
+      <c r="U4" s="124" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="106" t="s">
+      <c r="V4" s="107" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -27079,10 +27087,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="121" t="s">
+      <c r="J5" s="122" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="122"/>
+      <c r="K5" s="123"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -27090,9 +27098,9 @@
       <c r="Q5" s="103"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="118"/>
-      <c r="U5" s="124"/>
-      <c r="V5" s="107"/>
+      <c r="T5" s="119"/>
+      <c r="U5" s="125"/>
+      <c r="V5" s="108"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -29776,17 +29784,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="110" t="s">
+      <c r="C60" s="111" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="111"/>
-      <c r="E60" s="111"/>
-      <c r="F60" s="111"/>
-      <c r="G60" s="111"/>
-      <c r="H60" s="111"/>
-      <c r="I60" s="111"/>
-      <c r="J60" s="111"/>
-      <c r="K60" s="112"/>
+      <c r="D60" s="112"/>
+      <c r="E60" s="112"/>
+      <c r="F60" s="112"/>
+      <c r="G60" s="112"/>
+      <c r="H60" s="112"/>
+      <c r="I60" s="112"/>
+      <c r="J60" s="112"/>
+      <c r="K60" s="113"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -30095,21 +30103,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="113" t="s">
+      <c r="I1" s="114" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="113"/>
-      <c r="K1" s="113"/>
-      <c r="L1" s="113"/>
-      <c r="M1" s="113"/>
-      <c r="N1" s="113"/>
-      <c r="O1" s="113"/>
-      <c r="P1" s="113"/>
-      <c r="Q1" s="113"/>
-      <c r="R1" s="113"/>
-      <c r="S1" s="113"/>
-      <c r="T1" s="113"/>
-      <c r="U1" s="113"/>
+      <c r="J1" s="114"/>
+      <c r="K1" s="114"/>
+      <c r="L1" s="114"/>
+      <c r="M1" s="114"/>
+      <c r="N1" s="114"/>
+      <c r="O1" s="114"/>
+      <c r="P1" s="114"/>
+      <c r="Q1" s="114"/>
+      <c r="R1" s="114"/>
+      <c r="S1" s="114"/>
+      <c r="T1" s="114"/>
+      <c r="U1" s="114"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -30121,17 +30129,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="114" t="s">
+      <c r="C4" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="114"/>
-      <c r="E4" s="114"/>
-      <c r="F4" s="114"/>
-      <c r="G4" s="114"/>
-      <c r="H4" s="114"/>
-      <c r="I4" s="114"/>
-      <c r="J4" s="115"/>
-      <c r="K4" s="116"/>
+      <c r="D4" s="115"/>
+      <c r="E4" s="115"/>
+      <c r="F4" s="115"/>
+      <c r="G4" s="115"/>
+      <c r="H4" s="115"/>
+      <c r="I4" s="115"/>
+      <c r="J4" s="116"/>
+      <c r="K4" s="117"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -30151,13 +30159,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="117" t="s">
+      <c r="T4" s="118" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="123" t="s">
+      <c r="U4" s="124" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="106" t="s">
+      <c r="V4" s="107" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -30197,10 +30205,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="121" t="s">
+      <c r="J5" s="122" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="122"/>
+      <c r="K5" s="123"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -30208,9 +30216,9 @@
       <c r="Q5" s="104"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="118"/>
-      <c r="U5" s="124"/>
-      <c r="V5" s="107"/>
+      <c r="T5" s="119"/>
+      <c r="U5" s="125"/>
+      <c r="V5" s="108"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -32886,17 +32894,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="110" t="s">
+      <c r="C60" s="111" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="111"/>
-      <c r="E60" s="111"/>
-      <c r="F60" s="111"/>
-      <c r="G60" s="111"/>
-      <c r="H60" s="111"/>
-      <c r="I60" s="111"/>
-      <c r="J60" s="111"/>
-      <c r="K60" s="112"/>
+      <c r="D60" s="112"/>
+      <c r="E60" s="112"/>
+      <c r="F60" s="112"/>
+      <c r="G60" s="112"/>
+      <c r="H60" s="112"/>
+      <c r="I60" s="112"/>
+      <c r="J60" s="112"/>
+      <c r="K60" s="113"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -33205,21 +33213,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="113" t="s">
+      <c r="I1" s="114" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="113"/>
-      <c r="K1" s="113"/>
-      <c r="L1" s="113"/>
-      <c r="M1" s="113"/>
-      <c r="N1" s="113"/>
-      <c r="O1" s="113"/>
-      <c r="P1" s="113"/>
-      <c r="Q1" s="113"/>
-      <c r="R1" s="113"/>
-      <c r="S1" s="113"/>
-      <c r="T1" s="113"/>
-      <c r="U1" s="113"/>
+      <c r="J1" s="114"/>
+      <c r="K1" s="114"/>
+      <c r="L1" s="114"/>
+      <c r="M1" s="114"/>
+      <c r="N1" s="114"/>
+      <c r="O1" s="114"/>
+      <c r="P1" s="114"/>
+      <c r="Q1" s="114"/>
+      <c r="R1" s="114"/>
+      <c r="S1" s="114"/>
+      <c r="T1" s="114"/>
+      <c r="U1" s="114"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -33231,17 +33239,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="114" t="s">
+      <c r="C4" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="114"/>
-      <c r="E4" s="114"/>
-      <c r="F4" s="114"/>
-      <c r="G4" s="114"/>
-      <c r="H4" s="114"/>
-      <c r="I4" s="114"/>
-      <c r="J4" s="115"/>
-      <c r="K4" s="116"/>
+      <c r="D4" s="115"/>
+      <c r="E4" s="115"/>
+      <c r="F4" s="115"/>
+      <c r="G4" s="115"/>
+      <c r="H4" s="115"/>
+      <c r="I4" s="115"/>
+      <c r="J4" s="116"/>
+      <c r="K4" s="117"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -33261,13 +33269,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="117" t="s">
+      <c r="T4" s="118" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="123" t="s">
+      <c r="U4" s="124" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="106" t="s">
+      <c r="V4" s="107" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -33307,10 +33315,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="121" t="s">
+      <c r="J5" s="122" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="122"/>
+      <c r="K5" s="123"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -33318,9 +33326,9 @@
       <c r="Q5" s="105"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="118"/>
-      <c r="U5" s="124"/>
-      <c r="V5" s="107"/>
+      <c r="T5" s="119"/>
+      <c r="U5" s="125"/>
+      <c r="V5" s="108"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -36005,17 +36013,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="110" t="s">
+      <c r="C60" s="111" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="111"/>
-      <c r="E60" s="111"/>
-      <c r="F60" s="111"/>
-      <c r="G60" s="111"/>
-      <c r="H60" s="111"/>
-      <c r="I60" s="111"/>
-      <c r="J60" s="111"/>
-      <c r="K60" s="112"/>
+      <c r="D60" s="112"/>
+      <c r="E60" s="112"/>
+      <c r="F60" s="112"/>
+      <c r="G60" s="112"/>
+      <c r="H60" s="112"/>
+      <c r="I60" s="112"/>
+      <c r="J60" s="112"/>
+      <c r="K60" s="113"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -36324,21 +36332,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="113" t="s">
+      <c r="I1" s="114" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="113"/>
-      <c r="K1" s="113"/>
-      <c r="L1" s="113"/>
-      <c r="M1" s="113"/>
-      <c r="N1" s="113"/>
-      <c r="O1" s="113"/>
-      <c r="P1" s="113"/>
-      <c r="Q1" s="113"/>
-      <c r="R1" s="113"/>
-      <c r="S1" s="113"/>
-      <c r="T1" s="113"/>
-      <c r="U1" s="113"/>
+      <c r="J1" s="114"/>
+      <c r="K1" s="114"/>
+      <c r="L1" s="114"/>
+      <c r="M1" s="114"/>
+      <c r="N1" s="114"/>
+      <c r="O1" s="114"/>
+      <c r="P1" s="114"/>
+      <c r="Q1" s="114"/>
+      <c r="R1" s="114"/>
+      <c r="S1" s="114"/>
+      <c r="T1" s="114"/>
+      <c r="U1" s="114"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -36350,17 +36358,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="114" t="s">
+      <c r="C4" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="114"/>
-      <c r="E4" s="114"/>
-      <c r="F4" s="114"/>
-      <c r="G4" s="114"/>
-      <c r="H4" s="114"/>
-      <c r="I4" s="114"/>
-      <c r="J4" s="115"/>
-      <c r="K4" s="116"/>
+      <c r="D4" s="115"/>
+      <c r="E4" s="115"/>
+      <c r="F4" s="115"/>
+      <c r="G4" s="115"/>
+      <c r="H4" s="115"/>
+      <c r="I4" s="115"/>
+      <c r="J4" s="116"/>
+      <c r="K4" s="117"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -36380,13 +36388,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="117" t="s">
+      <c r="T4" s="118" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="123" t="s">
+      <c r="U4" s="124" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="106" t="s">
+      <c r="V4" s="107" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -36426,10 +36434,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="121" t="s">
+      <c r="J5" s="122" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="122"/>
+      <c r="K5" s="123"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -36437,9 +36445,9 @@
       <c r="Q5" s="96"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="118"/>
-      <c r="U5" s="124"/>
-      <c r="V5" s="107"/>
+      <c r="T5" s="119"/>
+      <c r="U5" s="125"/>
+      <c r="V5" s="108"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -39149,17 +39157,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="110" t="s">
+      <c r="C60" s="111" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="111"/>
-      <c r="E60" s="111"/>
-      <c r="F60" s="111"/>
-      <c r="G60" s="111"/>
-      <c r="H60" s="111"/>
-      <c r="I60" s="111"/>
-      <c r="J60" s="111"/>
-      <c r="K60" s="112"/>
+      <c r="D60" s="112"/>
+      <c r="E60" s="112"/>
+      <c r="F60" s="112"/>
+      <c r="G60" s="112"/>
+      <c r="H60" s="112"/>
+      <c r="I60" s="112"/>
+      <c r="J60" s="112"/>
+      <c r="K60" s="113"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -39418,6 +39426,3136 @@
     <mergeCell ref="C4:K4"/>
     <mergeCell ref="T4:T5"/>
     <mergeCell ref="U4:U5"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
+  <pageSetup paperSize="14" scale="70" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="24" max="80" man="1"/>
+  </colBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCB7E47D-FEA8-487E-A2AF-D4BE6C09E59A}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BB81"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="28" customWidth="1"/>
+    <col min="3" max="6" width="10" style="9" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" style="9" customWidth="1"/>
+    <col min="8" max="8" width="7.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.85546875" style="9" customWidth="1"/>
+    <col min="11" max="11" width="7.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.42578125" style="9" customWidth="1"/>
+    <col min="13" max="13" width="10" style="9" customWidth="1"/>
+    <col min="14" max="14" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" style="9" customWidth="1"/>
+    <col min="16" max="16" width="5.5703125" style="9" customWidth="1"/>
+    <col min="17" max="17" width="10" style="9" customWidth="1"/>
+    <col min="18" max="18" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="1.42578125" style="9" customWidth="1"/>
+    <col min="20" max="20" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="9" customWidth="1"/>
+    <col min="22" max="22" width="19.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="23" max="49" width="7.28515625" style="9" customWidth="1"/>
+    <col min="50" max="50" width="1.5703125" style="9" customWidth="1"/>
+    <col min="51" max="51" width="9.42578125" style="9" customWidth="1"/>
+    <col min="52" max="52" width="1.28515625" style="9" customWidth="1"/>
+    <col min="53" max="53" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="10.28515625" style="9" bestFit="1" customWidth="1"/>
+    <col min="55" max="16384" width="9.140625" style="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="114" t="s">
+        <v>43</v>
+      </c>
+      <c r="J1" s="114"/>
+      <c r="K1" s="114"/>
+      <c r="L1" s="114"/>
+      <c r="M1" s="114"/>
+      <c r="N1" s="114"/>
+      <c r="O1" s="114"/>
+      <c r="P1" s="114"/>
+      <c r="Q1" s="114"/>
+      <c r="R1" s="114"/>
+      <c r="S1" s="114"/>
+      <c r="T1" s="114"/>
+      <c r="U1" s="114"/>
+    </row>
+    <row r="2" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="B2" s="28" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B4" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="115" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="115"/>
+      <c r="E4" s="115"/>
+      <c r="F4" s="115"/>
+      <c r="G4" s="115"/>
+      <c r="H4" s="115"/>
+      <c r="I4" s="115"/>
+      <c r="J4" s="116"/>
+      <c r="K4" s="117"/>
+      <c r="M4" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="N4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="O4" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="P4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q4" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="R4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="S4" s="9"/>
+      <c r="T4" s="118" t="s">
+        <v>68</v>
+      </c>
+      <c r="U4" s="124" t="s">
+        <v>67</v>
+      </c>
+      <c r="V4" s="107" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF4" s="11"/>
+      <c r="AG4" s="11"/>
+      <c r="AH4" s="11"/>
+      <c r="AI4" s="11"/>
+      <c r="AJ4" s="11"/>
+      <c r="AK4" s="11"/>
+      <c r="AL4" s="11"/>
+      <c r="AM4" s="11"/>
+      <c r="AN4" s="11"/>
+      <c r="AO4" s="11"/>
+      <c r="AP4" s="11"/>
+      <c r="AQ4" s="11"/>
+      <c r="AR4" s="11"/>
+      <c r="AS4" s="11"/>
+      <c r="AT4" s="11"/>
+      <c r="AU4" s="11"/>
+      <c r="AV4" s="11"/>
+      <c r="AW4" s="11"/>
+      <c r="AX4" s="11"/>
+      <c r="AY4" s="11"/>
+      <c r="AZ4" s="11"/>
+      <c r="BA4" s="11"/>
+      <c r="BB4" s="11"/>
+    </row>
+    <row r="5" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="37"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40" t="s">
+        <v>64</v>
+      </c>
+      <c r="I5" s="40" t="s">
+        <v>60</v>
+      </c>
+      <c r="J5" s="122" t="s">
+        <v>65</v>
+      </c>
+      <c r="K5" s="123"/>
+      <c r="M5" s="37"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="40"/>
+      <c r="P5" s="106"/>
+      <c r="Q5" s="106"/>
+      <c r="R5" s="38"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="119"/>
+      <c r="U5" s="125"/>
+      <c r="V5" s="108"/>
+      <c r="AF5" s="11"/>
+      <c r="AG5" s="11"/>
+      <c r="AH5" s="11"/>
+      <c r="AI5" s="11"/>
+      <c r="AJ5" s="11"/>
+      <c r="AK5" s="11"/>
+      <c r="AL5" s="11"/>
+      <c r="AM5" s="11"/>
+      <c r="AN5" s="11"/>
+      <c r="AO5" s="11"/>
+      <c r="AP5" s="11"/>
+      <c r="AQ5" s="11"/>
+      <c r="AR5" s="11"/>
+      <c r="AS5" s="11"/>
+      <c r="AT5" s="11"/>
+      <c r="AU5" s="11"/>
+      <c r="AV5" s="11"/>
+      <c r="AW5" s="11"/>
+      <c r="AX5" s="11"/>
+      <c r="AY5" s="11"/>
+      <c r="AZ5" s="11"/>
+      <c r="BA5" s="11"/>
+      <c r="BB5" s="11"/>
+    </row>
+    <row r="6" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="37"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="106"/>
+      <c r="K6" s="38"/>
+      <c r="M6" s="37"/>
+      <c r="N6" s="49"/>
+      <c r="O6" s="40"/>
+      <c r="P6" s="106"/>
+      <c r="Q6" s="106"/>
+      <c r="R6" s="38"/>
+      <c r="S6" s="9"/>
+      <c r="T6" s="39"/>
+      <c r="U6" s="39"/>
+      <c r="V6" s="39"/>
+      <c r="AF6" s="11"/>
+      <c r="AG6" s="11"/>
+      <c r="AH6" s="11"/>
+      <c r="AI6" s="11"/>
+      <c r="AJ6" s="11"/>
+      <c r="AK6" s="11"/>
+      <c r="AL6" s="11"/>
+      <c r="AM6" s="11"/>
+      <c r="AN6" s="11"/>
+      <c r="AO6" s="11"/>
+      <c r="AP6" s="11"/>
+      <c r="AQ6" s="11"/>
+      <c r="AR6" s="11"/>
+      <c r="AS6" s="11"/>
+      <c r="AT6" s="11"/>
+      <c r="AU6" s="11"/>
+      <c r="AV6" s="11"/>
+      <c r="AW6" s="11"/>
+      <c r="AX6" s="11"/>
+      <c r="AY6" s="11"/>
+      <c r="AZ6" s="11"/>
+      <c r="BA6" s="11"/>
+      <c r="BB6" s="11"/>
+    </row>
+    <row r="7" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A7" s="27">
+        <v>1</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="52">
+        <v>29</v>
+      </c>
+      <c r="D7" s="52"/>
+      <c r="E7" s="52"/>
+      <c r="F7" s="52"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="52"/>
+      <c r="I7" s="52">
+        <v>3</v>
+      </c>
+      <c r="J7" s="53"/>
+      <c r="K7" s="54">
+        <v>6</v>
+      </c>
+      <c r="L7" s="55"/>
+      <c r="M7" s="56"/>
+      <c r="N7" s="57"/>
+      <c r="O7" s="52">
+        <v>1</v>
+      </c>
+      <c r="P7" s="53"/>
+      <c r="Q7" s="53">
+        <v>1</v>
+      </c>
+      <c r="R7" s="54"/>
+      <c r="S7" s="55"/>
+      <c r="T7" s="58">
+        <f>H7+I7+J7+K7+N7+P7+R7</f>
+        <v>9</v>
+      </c>
+      <c r="U7" s="58">
+        <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
+        <v>753</v>
+      </c>
+      <c r="V7" s="58">
+        <f>U7/24</f>
+        <v>31.375</v>
+      </c>
+      <c r="W7" s="50"/>
+      <c r="AF7" s="12"/>
+      <c r="AG7" s="12"/>
+      <c r="AH7" s="12"/>
+      <c r="AI7" s="12"/>
+      <c r="AJ7" s="12"/>
+      <c r="AK7" s="12"/>
+      <c r="AL7" s="12"/>
+      <c r="AM7" s="12"/>
+      <c r="AN7" s="12"/>
+      <c r="AO7" s="12"/>
+      <c r="AP7" s="12"/>
+      <c r="AQ7" s="12"/>
+      <c r="AR7" s="12"/>
+      <c r="AS7" s="12"/>
+      <c r="AT7" s="12"/>
+      <c r="AU7" s="12"/>
+      <c r="AV7" s="12"/>
+      <c r="AW7" s="12"/>
+      <c r="AX7" s="12"/>
+      <c r="AY7" s="12"/>
+      <c r="AZ7" s="12"/>
+      <c r="BA7" s="12"/>
+      <c r="BB7" s="12"/>
+    </row>
+    <row r="8" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="27">
+        <f>A7+1</f>
+        <v>2</v>
+      </c>
+      <c r="B8" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="59">
+        <f>36+30</f>
+        <v>66</v>
+      </c>
+      <c r="D8" s="59"/>
+      <c r="E8" s="59"/>
+      <c r="F8" s="59"/>
+      <c r="G8" s="59"/>
+      <c r="H8" s="59"/>
+      <c r="I8" s="59"/>
+      <c r="J8" s="60"/>
+      <c r="K8" s="61"/>
+      <c r="L8" s="62"/>
+      <c r="M8" s="63">
+        <v>1</v>
+      </c>
+      <c r="N8" s="64"/>
+      <c r="O8" s="65">
+        <v>1</v>
+      </c>
+      <c r="P8" s="66">
+        <v>12</v>
+      </c>
+      <c r="Q8" s="66">
+        <v>1</v>
+      </c>
+      <c r="R8" s="67"/>
+      <c r="S8" s="62"/>
+      <c r="T8" s="68">
+        <f t="shared" ref="T8:T41" si="0">H8+I8+J8+K8+N8+P8+R8</f>
+        <v>12</v>
+      </c>
+      <c r="U8" s="69">
+        <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
+        <v>1668</v>
+      </c>
+      <c r="V8" s="69">
+        <f>U8/24</f>
+        <v>69.5</v>
+      </c>
+      <c r="W8" s="50"/>
+      <c r="AF8" s="12"/>
+      <c r="AG8" s="12"/>
+      <c r="AH8" s="12"/>
+      <c r="AI8" s="12"/>
+      <c r="AJ8" s="12"/>
+      <c r="AK8" s="12"/>
+      <c r="AL8" s="12"/>
+      <c r="AM8" s="12"/>
+      <c r="AN8" s="12"/>
+      <c r="AO8" s="12"/>
+      <c r="AP8" s="12"/>
+      <c r="AQ8" s="12"/>
+      <c r="AR8" s="12"/>
+      <c r="AS8" s="12"/>
+      <c r="AT8" s="12"/>
+      <c r="AU8" s="12"/>
+      <c r="AV8" s="12"/>
+      <c r="AW8" s="12"/>
+      <c r="AX8" s="12"/>
+      <c r="AY8" s="12"/>
+      <c r="AZ8" s="12"/>
+      <c r="BA8" s="12"/>
+      <c r="BB8" s="12"/>
+    </row>
+    <row r="9" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A9" s="27">
+        <f t="shared" ref="A9:A57" si="1">A8+1</f>
+        <v>3</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="70">
+        <f>23+30</f>
+        <v>53</v>
+      </c>
+      <c r="D9" s="70"/>
+      <c r="E9" s="70"/>
+      <c r="F9" s="70"/>
+      <c r="G9" s="70"/>
+      <c r="H9" s="70"/>
+      <c r="I9" s="70"/>
+      <c r="J9" s="71"/>
+      <c r="K9" s="72"/>
+      <c r="L9" s="55"/>
+      <c r="M9" s="73"/>
+      <c r="N9" s="74"/>
+      <c r="O9" s="70">
+        <v>1</v>
+      </c>
+      <c r="P9" s="71"/>
+      <c r="Q9" s="71"/>
+      <c r="R9" s="72"/>
+      <c r="S9" s="55"/>
+      <c r="T9" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U9" s="76">
+        <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
+        <v>1296</v>
+      </c>
+      <c r="V9" s="76">
+        <f t="shared" ref="V9:V11" si="3">U9/24</f>
+        <v>54</v>
+      </c>
+      <c r="W9" s="50"/>
+      <c r="AF9" s="12"/>
+      <c r="AG9" s="12"/>
+      <c r="AH9" s="12"/>
+      <c r="AI9" s="12"/>
+      <c r="AJ9" s="12"/>
+      <c r="AK9" s="12"/>
+      <c r="AL9" s="12"/>
+      <c r="AM9" s="12"/>
+      <c r="AN9" s="12"/>
+      <c r="AO9" s="12"/>
+      <c r="AP9" s="12"/>
+      <c r="AQ9" s="12"/>
+      <c r="AR9" s="12"/>
+      <c r="AS9" s="12"/>
+      <c r="AT9" s="12"/>
+      <c r="AU9" s="12"/>
+      <c r="AV9" s="12"/>
+      <c r="AW9" s="12"/>
+      <c r="AX9" s="12"/>
+      <c r="AY9" s="12"/>
+      <c r="AZ9" s="12"/>
+      <c r="BA9" s="12"/>
+      <c r="BB9" s="12"/>
+    </row>
+    <row r="10" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A10" s="27">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="70">
+        <v>9</v>
+      </c>
+      <c r="D10" s="70"/>
+      <c r="E10" s="70"/>
+      <c r="F10" s="70"/>
+      <c r="G10" s="70"/>
+      <c r="H10" s="70"/>
+      <c r="I10" s="70"/>
+      <c r="J10" s="71"/>
+      <c r="K10" s="72"/>
+      <c r="L10" s="55"/>
+      <c r="M10" s="73"/>
+      <c r="N10" s="74"/>
+      <c r="O10" s="70">
+        <v>1</v>
+      </c>
+      <c r="P10" s="71"/>
+      <c r="Q10" s="71">
+        <v>3</v>
+      </c>
+      <c r="R10" s="72"/>
+      <c r="S10" s="55"/>
+      <c r="T10" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U10" s="58">
+        <f t="shared" si="2"/>
+        <v>312</v>
+      </c>
+      <c r="V10" s="58">
+        <f t="shared" si="3"/>
+        <v>13</v>
+      </c>
+      <c r="W10" s="50"/>
+      <c r="AF10" s="12"/>
+      <c r="AG10" s="12"/>
+      <c r="AH10" s="12"/>
+      <c r="AI10" s="12"/>
+      <c r="AJ10" s="12"/>
+      <c r="AK10" s="12"/>
+      <c r="AL10" s="12"/>
+      <c r="AM10" s="12"/>
+      <c r="AN10" s="12"/>
+      <c r="AO10" s="12"/>
+      <c r="AP10" s="12"/>
+      <c r="AQ10" s="12"/>
+      <c r="AR10" s="12"/>
+      <c r="AS10" s="12"/>
+      <c r="AT10" s="12"/>
+      <c r="AU10" s="12"/>
+      <c r="AV10" s="12"/>
+      <c r="AW10" s="12"/>
+      <c r="AX10" s="12"/>
+      <c r="AY10" s="12"/>
+      <c r="AZ10" s="12"/>
+      <c r="BA10" s="12"/>
+      <c r="BB10" s="12"/>
+    </row>
+    <row r="11" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A11" s="27">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="70"/>
+      <c r="D11" s="70"/>
+      <c r="E11" s="70"/>
+      <c r="F11" s="70"/>
+      <c r="G11" s="70"/>
+      <c r="H11" s="70"/>
+      <c r="I11" s="70"/>
+      <c r="J11" s="71"/>
+      <c r="K11" s="72">
+        <v>2</v>
+      </c>
+      <c r="L11" s="55"/>
+      <c r="M11" s="73"/>
+      <c r="N11" s="74"/>
+      <c r="O11" s="70"/>
+      <c r="P11" s="71"/>
+      <c r="Q11" s="71"/>
+      <c r="R11" s="72"/>
+      <c r="S11" s="55"/>
+      <c r="T11" s="58">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="U11" s="58">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="V11" s="58">
+        <f t="shared" si="3"/>
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="AF11" s="12"/>
+      <c r="AG11" s="12"/>
+      <c r="AH11" s="12"/>
+      <c r="AI11" s="12"/>
+      <c r="AJ11" s="12"/>
+      <c r="AK11" s="12"/>
+      <c r="AL11" s="12"/>
+      <c r="AM11" s="12"/>
+      <c r="AN11" s="12"/>
+      <c r="AO11" s="12"/>
+      <c r="AP11" s="12"/>
+      <c r="AQ11" s="12"/>
+      <c r="AR11" s="12"/>
+      <c r="AS11" s="12"/>
+      <c r="AT11" s="12"/>
+      <c r="AU11" s="12"/>
+      <c r="AV11" s="12"/>
+      <c r="AW11" s="12"/>
+      <c r="AX11" s="12"/>
+      <c r="AY11" s="12"/>
+      <c r="AZ11" s="12"/>
+      <c r="BA11" s="12"/>
+      <c r="BB11" s="12"/>
+    </row>
+    <row r="12" spans="1:54" s="13" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="27">
+        <v>7</v>
+      </c>
+      <c r="B12" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="70">
+        <f>1224+53+504+62+1080+29+4</f>
+        <v>2956</v>
+      </c>
+      <c r="D12" s="70"/>
+      <c r="E12" s="70"/>
+      <c r="F12" s="70"/>
+      <c r="G12" s="70"/>
+      <c r="H12" s="70"/>
+      <c r="I12" s="70"/>
+      <c r="J12" s="71"/>
+      <c r="K12" s="72"/>
+      <c r="L12" s="55"/>
+      <c r="M12" s="73">
+        <v>16</v>
+      </c>
+      <c r="N12" s="74">
+        <v>10</v>
+      </c>
+      <c r="O12" s="70">
+        <v>11</v>
+      </c>
+      <c r="P12" s="71">
+        <v>7</v>
+      </c>
+      <c r="Q12" s="71">
+        <v>25</v>
+      </c>
+      <c r="R12" s="72">
+        <v>7</v>
+      </c>
+      <c r="S12" s="62"/>
+      <c r="T12" s="69">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="U12" s="69">
+        <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
+        <v>72216</v>
+      </c>
+      <c r="V12" s="69">
+        <f>U12/24</f>
+        <v>3009</v>
+      </c>
+      <c r="W12" s="9"/>
+      <c r="X12" s="9"/>
+      <c r="Y12" s="9"/>
+      <c r="Z12" s="9"/>
+      <c r="AA12" s="9"/>
+      <c r="AB12" s="9"/>
+      <c r="AC12" s="9"/>
+      <c r="AD12" s="9"/>
+      <c r="AE12" s="9"/>
+      <c r="AF12" s="12"/>
+      <c r="AG12" s="12"/>
+      <c r="AH12" s="12"/>
+      <c r="AI12" s="12"/>
+      <c r="AJ12" s="12"/>
+      <c r="AK12" s="12"/>
+      <c r="AL12" s="12"/>
+      <c r="AM12" s="12"/>
+      <c r="AN12" s="12"/>
+      <c r="AO12" s="12"/>
+      <c r="AP12" s="12"/>
+      <c r="AQ12" s="12"/>
+      <c r="AR12" s="12"/>
+      <c r="AS12" s="12"/>
+      <c r="AT12" s="12"/>
+      <c r="AU12" s="12"/>
+      <c r="AV12" s="12"/>
+      <c r="AW12" s="12"/>
+      <c r="AX12" s="12"/>
+      <c r="AY12" s="12"/>
+      <c r="AZ12" s="12"/>
+      <c r="BA12" s="12"/>
+      <c r="BB12" s="12"/>
+    </row>
+    <row r="13" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A13" s="27">
+        <v>11</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="70">
+        <v>2</v>
+      </c>
+      <c r="D13" s="70"/>
+      <c r="E13" s="70"/>
+      <c r="F13" s="70"/>
+      <c r="G13" s="70"/>
+      <c r="H13" s="70">
+        <v>16</v>
+      </c>
+      <c r="I13" s="70"/>
+      <c r="J13" s="71"/>
+      <c r="K13" s="72"/>
+      <c r="L13" s="55"/>
+      <c r="M13" s="73"/>
+      <c r="N13" s="74"/>
+      <c r="O13" s="70"/>
+      <c r="P13" s="71"/>
+      <c r="Q13" s="71"/>
+      <c r="R13" s="72"/>
+      <c r="S13" s="55"/>
+      <c r="T13" s="76">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="U13" s="76">
+        <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
+        <v>64</v>
+      </c>
+      <c r="V13" s="76">
+        <f>U13/24</f>
+        <v>2.6666666666666665</v>
+      </c>
+      <c r="AF13" s="12"/>
+      <c r="AG13" s="12"/>
+      <c r="AH13" s="12"/>
+      <c r="AI13" s="12"/>
+      <c r="AJ13" s="12"/>
+      <c r="AK13" s="12"/>
+      <c r="AL13" s="12"/>
+      <c r="AM13" s="12"/>
+      <c r="AN13" s="12"/>
+      <c r="AO13" s="12"/>
+      <c r="AP13" s="12"/>
+      <c r="AQ13" s="12"/>
+      <c r="AR13" s="12"/>
+      <c r="AS13" s="12"/>
+      <c r="AT13" s="12"/>
+      <c r="AU13" s="12"/>
+      <c r="AV13" s="12"/>
+      <c r="AW13" s="12"/>
+      <c r="AX13" s="12"/>
+      <c r="AY13" s="12"/>
+      <c r="AZ13" s="12"/>
+      <c r="BA13" s="12"/>
+      <c r="BB13" s="12"/>
+    </row>
+    <row r="14" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A14" s="27">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="70">
+        <v>2</v>
+      </c>
+      <c r="D14" s="70"/>
+      <c r="E14" s="70"/>
+      <c r="F14" s="70"/>
+      <c r="G14" s="70"/>
+      <c r="H14" s="70"/>
+      <c r="I14" s="70"/>
+      <c r="J14" s="71"/>
+      <c r="K14" s="72"/>
+      <c r="L14" s="55"/>
+      <c r="M14" s="73"/>
+      <c r="N14" s="74"/>
+      <c r="O14" s="70"/>
+      <c r="P14" s="71"/>
+      <c r="Q14" s="71"/>
+      <c r="R14" s="72"/>
+      <c r="S14" s="55"/>
+      <c r="T14" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U14" s="75">
+        <f t="shared" ref="U14:U36" si="4">C14*24+M14*24+O14*24+Q14*24+T14</f>
+        <v>48</v>
+      </c>
+      <c r="V14" s="75">
+        <f t="shared" ref="V14:V36" si="5">U14/24</f>
+        <v>2</v>
+      </c>
+      <c r="AF14" s="12"/>
+      <c r="AG14" s="12"/>
+      <c r="AH14" s="12"/>
+      <c r="AI14" s="12"/>
+      <c r="AJ14" s="12"/>
+      <c r="AK14" s="12"/>
+      <c r="AL14" s="12"/>
+      <c r="AM14" s="12"/>
+      <c r="AN14" s="12"/>
+      <c r="AO14" s="12"/>
+      <c r="AP14" s="12"/>
+      <c r="AQ14" s="12"/>
+      <c r="AR14" s="12"/>
+      <c r="AS14" s="12"/>
+      <c r="AT14" s="12"/>
+      <c r="AU14" s="12"/>
+      <c r="AV14" s="12"/>
+      <c r="AW14" s="12"/>
+      <c r="AX14" s="12"/>
+      <c r="AY14" s="12"/>
+      <c r="AZ14" s="12"/>
+      <c r="BA14" s="12"/>
+      <c r="BB14" s="12"/>
+    </row>
+    <row r="15" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A15" s="27">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="70"/>
+      <c r="D15" s="70"/>
+      <c r="E15" s="70"/>
+      <c r="F15" s="70"/>
+      <c r="G15" s="70"/>
+      <c r="H15" s="70"/>
+      <c r="I15" s="70"/>
+      <c r="J15" s="71"/>
+      <c r="K15" s="72"/>
+      <c r="L15" s="55"/>
+      <c r="M15" s="73"/>
+      <c r="N15" s="74"/>
+      <c r="O15" s="70"/>
+      <c r="P15" s="71"/>
+      <c r="Q15" s="71"/>
+      <c r="R15" s="72"/>
+      <c r="S15" s="55"/>
+      <c r="T15" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U15" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF15" s="12"/>
+      <c r="AG15" s="12"/>
+      <c r="AH15" s="12"/>
+      <c r="AI15" s="12"/>
+      <c r="AJ15" s="12"/>
+      <c r="AK15" s="12"/>
+      <c r="AL15" s="12"/>
+      <c r="AM15" s="12"/>
+      <c r="AN15" s="12"/>
+      <c r="AO15" s="12"/>
+      <c r="AP15" s="12"/>
+      <c r="AQ15" s="12"/>
+      <c r="AR15" s="12"/>
+      <c r="AS15" s="12"/>
+      <c r="AT15" s="12"/>
+      <c r="AU15" s="12"/>
+      <c r="AV15" s="12"/>
+      <c r="AW15" s="12"/>
+      <c r="AX15" s="12"/>
+      <c r="AY15" s="12"/>
+      <c r="AZ15" s="12"/>
+      <c r="BA15" s="12"/>
+      <c r="BB15" s="12"/>
+    </row>
+    <row r="16" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A16" s="27">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="70"/>
+      <c r="D16" s="70"/>
+      <c r="E16" s="70"/>
+      <c r="F16" s="70"/>
+      <c r="G16" s="70"/>
+      <c r="H16" s="70"/>
+      <c r="I16" s="70"/>
+      <c r="J16" s="71"/>
+      <c r="K16" s="72"/>
+      <c r="L16" s="55"/>
+      <c r="M16" s="73"/>
+      <c r="N16" s="74"/>
+      <c r="O16" s="70"/>
+      <c r="P16" s="71"/>
+      <c r="Q16" s="71"/>
+      <c r="R16" s="72"/>
+      <c r="S16" s="55"/>
+      <c r="T16" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U16" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF16" s="12"/>
+      <c r="AG16" s="12"/>
+      <c r="AH16" s="12"/>
+      <c r="AI16" s="12"/>
+      <c r="AJ16" s="12"/>
+      <c r="AK16" s="12"/>
+      <c r="AL16" s="12"/>
+      <c r="AM16" s="12"/>
+      <c r="AN16" s="12"/>
+      <c r="AO16" s="12"/>
+      <c r="AP16" s="12"/>
+      <c r="AQ16" s="12"/>
+      <c r="AR16" s="12"/>
+      <c r="AS16" s="12"/>
+      <c r="AT16" s="12"/>
+      <c r="AU16" s="12"/>
+      <c r="AV16" s="12"/>
+      <c r="AW16" s="12"/>
+      <c r="AX16" s="12"/>
+      <c r="AY16" s="12"/>
+      <c r="AZ16" s="12"/>
+      <c r="BA16" s="12"/>
+      <c r="BB16" s="12"/>
+    </row>
+    <row r="17" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A17" s="27">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="70"/>
+      <c r="D17" s="70"/>
+      <c r="E17" s="70"/>
+      <c r="F17" s="70"/>
+      <c r="G17" s="70"/>
+      <c r="H17" s="70">
+        <f>3*24</f>
+        <v>72</v>
+      </c>
+      <c r="I17" s="70"/>
+      <c r="J17" s="71"/>
+      <c r="K17" s="72"/>
+      <c r="L17" s="55"/>
+      <c r="M17" s="73"/>
+      <c r="N17" s="74"/>
+      <c r="O17" s="70"/>
+      <c r="P17" s="71"/>
+      <c r="Q17" s="71"/>
+      <c r="R17" s="72"/>
+      <c r="S17" s="55"/>
+      <c r="T17" s="58">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="U17" s="75">
+        <f t="shared" si="4"/>
+        <v>72</v>
+      </c>
+      <c r="V17" s="75">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="AF17" s="12"/>
+      <c r="AG17" s="12"/>
+      <c r="AH17" s="12"/>
+      <c r="AI17" s="12"/>
+      <c r="AJ17" s="12"/>
+      <c r="AK17" s="12"/>
+      <c r="AL17" s="12"/>
+      <c r="AM17" s="12"/>
+      <c r="AN17" s="12"/>
+      <c r="AO17" s="12"/>
+      <c r="AP17" s="12"/>
+      <c r="AQ17" s="12"/>
+      <c r="AR17" s="12"/>
+      <c r="AS17" s="12"/>
+      <c r="AT17" s="12"/>
+      <c r="AU17" s="12"/>
+      <c r="AV17" s="12"/>
+      <c r="AW17" s="12"/>
+      <c r="AX17" s="12"/>
+      <c r="AY17" s="12"/>
+      <c r="AZ17" s="12"/>
+      <c r="BA17" s="12"/>
+      <c r="BB17" s="12"/>
+    </row>
+    <row r="18" spans="1:54" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="27">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="70"/>
+      <c r="D18" s="70"/>
+      <c r="E18" s="70"/>
+      <c r="F18" s="70"/>
+      <c r="G18" s="70"/>
+      <c r="H18" s="70"/>
+      <c r="I18" s="70"/>
+      <c r="J18" s="71"/>
+      <c r="K18" s="72"/>
+      <c r="L18" s="55"/>
+      <c r="M18" s="73"/>
+      <c r="N18" s="74"/>
+      <c r="O18" s="70"/>
+      <c r="P18" s="71"/>
+      <c r="Q18" s="71"/>
+      <c r="R18" s="72"/>
+      <c r="S18" s="55"/>
+      <c r="T18" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U18" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF18" s="12"/>
+      <c r="AG18" s="12"/>
+      <c r="AH18" s="12"/>
+      <c r="AI18" s="12"/>
+      <c r="AJ18" s="12"/>
+      <c r="AK18" s="12"/>
+      <c r="AL18" s="12"/>
+      <c r="AM18" s="12"/>
+      <c r="AN18" s="12"/>
+      <c r="AO18" s="12"/>
+      <c r="AP18" s="12"/>
+      <c r="AQ18" s="12"/>
+      <c r="AR18" s="12"/>
+      <c r="AS18" s="12"/>
+      <c r="AT18" s="12"/>
+      <c r="AU18" s="12"/>
+      <c r="AV18" s="12"/>
+      <c r="AW18" s="12"/>
+      <c r="AX18" s="12"/>
+      <c r="AY18" s="12"/>
+      <c r="AZ18" s="12"/>
+      <c r="BA18" s="12"/>
+      <c r="BB18" s="12"/>
+    </row>
+    <row r="19" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A19" s="27">
+        <v>16</v>
+      </c>
+      <c r="B19" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="70">
+        <v>1</v>
+      </c>
+      <c r="D19" s="70"/>
+      <c r="E19" s="70"/>
+      <c r="F19" s="70"/>
+      <c r="G19" s="70"/>
+      <c r="H19" s="70">
+        <f>20+24</f>
+        <v>44</v>
+      </c>
+      <c r="I19" s="70"/>
+      <c r="J19" s="71"/>
+      <c r="K19" s="72"/>
+      <c r="L19" s="55"/>
+      <c r="M19" s="73"/>
+      <c r="N19" s="74"/>
+      <c r="O19" s="70"/>
+      <c r="P19" s="71"/>
+      <c r="Q19" s="71"/>
+      <c r="R19" s="72"/>
+      <c r="S19" s="55"/>
+      <c r="T19" s="58">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="U19" s="75">
+        <f t="shared" si="4"/>
+        <v>68</v>
+      </c>
+      <c r="V19" s="75">
+        <f t="shared" si="5"/>
+        <v>2.8333333333333335</v>
+      </c>
+      <c r="AF19" s="12"/>
+      <c r="AG19" s="12"/>
+      <c r="AH19" s="12"/>
+      <c r="AI19" s="12"/>
+      <c r="AJ19" s="12"/>
+      <c r="AK19" s="12"/>
+      <c r="AL19" s="12"/>
+      <c r="AM19" s="12"/>
+      <c r="AN19" s="12"/>
+      <c r="AO19" s="12"/>
+      <c r="AP19" s="12"/>
+      <c r="AQ19" s="12"/>
+      <c r="AR19" s="12"/>
+      <c r="AS19" s="12"/>
+      <c r="AT19" s="12"/>
+      <c r="AU19" s="12"/>
+      <c r="AV19" s="12"/>
+      <c r="AW19" s="12"/>
+      <c r="AX19" s="12"/>
+      <c r="AY19" s="12"/>
+      <c r="AZ19" s="12"/>
+      <c r="BA19" s="12"/>
+      <c r="BB19" s="12"/>
+    </row>
+    <row r="20" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A20" s="27">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="B20" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="70">
+        <v>5</v>
+      </c>
+      <c r="D20" s="70"/>
+      <c r="E20" s="70"/>
+      <c r="F20" s="70"/>
+      <c r="G20" s="70"/>
+      <c r="H20" s="70"/>
+      <c r="I20" s="70"/>
+      <c r="J20" s="71"/>
+      <c r="K20" s="72"/>
+      <c r="L20" s="55"/>
+      <c r="M20" s="73"/>
+      <c r="N20" s="74"/>
+      <c r="O20" s="70"/>
+      <c r="P20" s="71"/>
+      <c r="Q20" s="71"/>
+      <c r="R20" s="72"/>
+      <c r="S20" s="55"/>
+      <c r="T20" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U20" s="75">
+        <f t="shared" si="4"/>
+        <v>120</v>
+      </c>
+      <c r="V20" s="75">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="AF20" s="12"/>
+      <c r="AG20" s="12"/>
+      <c r="AH20" s="12"/>
+      <c r="AI20" s="12"/>
+      <c r="AJ20" s="12"/>
+      <c r="AK20" s="12"/>
+      <c r="AL20" s="12"/>
+      <c r="AM20" s="12"/>
+      <c r="AN20" s="12"/>
+      <c r="AO20" s="12"/>
+      <c r="AP20" s="12"/>
+      <c r="AQ20" s="12"/>
+      <c r="AR20" s="12"/>
+      <c r="AS20" s="12"/>
+      <c r="AT20" s="12"/>
+      <c r="AU20" s="12"/>
+      <c r="AV20" s="12"/>
+      <c r="AW20" s="12"/>
+      <c r="AX20" s="12"/>
+      <c r="AY20" s="12"/>
+      <c r="AZ20" s="12"/>
+      <c r="BA20" s="12"/>
+      <c r="BB20" s="12"/>
+    </row>
+    <row r="21" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A21" s="27">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="B21" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="70"/>
+      <c r="D21" s="70"/>
+      <c r="E21" s="70"/>
+      <c r="F21" s="70"/>
+      <c r="G21" s="70"/>
+      <c r="H21" s="70">
+        <f>2*24</f>
+        <v>48</v>
+      </c>
+      <c r="I21" s="70"/>
+      <c r="J21" s="71"/>
+      <c r="K21" s="72"/>
+      <c r="L21" s="55"/>
+      <c r="M21" s="73"/>
+      <c r="N21" s="74"/>
+      <c r="O21" s="70"/>
+      <c r="P21" s="71"/>
+      <c r="Q21" s="71"/>
+      <c r="R21" s="72"/>
+      <c r="S21" s="55"/>
+      <c r="T21" s="58">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+      <c r="U21" s="75">
+        <f t="shared" si="4"/>
+        <v>48</v>
+      </c>
+      <c r="V21" s="75">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="AF21" s="12"/>
+      <c r="AG21" s="12"/>
+      <c r="AH21" s="12"/>
+      <c r="AI21" s="12"/>
+      <c r="AJ21" s="12"/>
+      <c r="AK21" s="12"/>
+      <c r="AL21" s="12"/>
+      <c r="AM21" s="12"/>
+      <c r="AN21" s="12"/>
+      <c r="AO21" s="12"/>
+      <c r="AP21" s="12"/>
+      <c r="AQ21" s="12"/>
+      <c r="AR21" s="12"/>
+      <c r="AS21" s="12"/>
+      <c r="AT21" s="12"/>
+      <c r="AU21" s="12"/>
+      <c r="AV21" s="12"/>
+      <c r="AW21" s="12"/>
+      <c r="AX21" s="12"/>
+      <c r="AY21" s="12"/>
+      <c r="AZ21" s="12"/>
+      <c r="BA21" s="12"/>
+      <c r="BB21" s="12"/>
+    </row>
+    <row r="22" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="27">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="B22" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="70">
+        <v>1</v>
+      </c>
+      <c r="D22" s="70"/>
+      <c r="E22" s="70"/>
+      <c r="F22" s="70"/>
+      <c r="G22" s="70"/>
+      <c r="H22" s="70"/>
+      <c r="I22" s="70">
+        <v>20</v>
+      </c>
+      <c r="J22" s="71"/>
+      <c r="K22" s="72"/>
+      <c r="L22" s="55"/>
+      <c r="M22" s="73"/>
+      <c r="N22" s="74"/>
+      <c r="O22" s="70"/>
+      <c r="P22" s="71"/>
+      <c r="Q22" s="71"/>
+      <c r="R22" s="72"/>
+      <c r="S22" s="55"/>
+      <c r="T22" s="58">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="U22" s="75">
+        <f t="shared" si="4"/>
+        <v>44</v>
+      </c>
+      <c r="V22" s="75">
+        <f t="shared" si="5"/>
+        <v>1.8333333333333333</v>
+      </c>
+      <c r="W22" s="9"/>
+      <c r="X22" s="9"/>
+      <c r="Y22" s="9"/>
+      <c r="Z22" s="9"/>
+      <c r="AA22" s="9"/>
+      <c r="AB22" s="9"/>
+      <c r="AC22" s="9"/>
+      <c r="AD22" s="9"/>
+      <c r="AE22" s="9"/>
+      <c r="AF22" s="12"/>
+      <c r="AG22" s="12"/>
+      <c r="AH22" s="12"/>
+      <c r="AI22" s="12"/>
+      <c r="AJ22" s="12"/>
+      <c r="AK22" s="12"/>
+      <c r="AL22" s="12"/>
+      <c r="AM22" s="12"/>
+      <c r="AN22" s="12"/>
+      <c r="AO22" s="12"/>
+      <c r="AP22" s="12"/>
+      <c r="AQ22" s="12"/>
+      <c r="AR22" s="12"/>
+      <c r="AS22" s="12"/>
+      <c r="AT22" s="12"/>
+      <c r="AU22" s="12"/>
+      <c r="AV22" s="12"/>
+      <c r="AW22" s="12"/>
+      <c r="AX22" s="12"/>
+      <c r="AY22" s="12"/>
+      <c r="AZ22" s="12"/>
+      <c r="BA22" s="12"/>
+      <c r="BB22" s="12"/>
+    </row>
+    <row r="23" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="27">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="B23" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="70"/>
+      <c r="D23" s="70"/>
+      <c r="E23" s="70"/>
+      <c r="F23" s="70"/>
+      <c r="G23" s="70"/>
+      <c r="H23" s="70">
+        <f>37*24+19</f>
+        <v>907</v>
+      </c>
+      <c r="I23" s="70"/>
+      <c r="J23" s="71"/>
+      <c r="K23" s="72"/>
+      <c r="L23" s="55"/>
+      <c r="M23" s="73"/>
+      <c r="N23" s="74"/>
+      <c r="O23" s="70"/>
+      <c r="P23" s="71"/>
+      <c r="Q23" s="71"/>
+      <c r="R23" s="72"/>
+      <c r="S23" s="55"/>
+      <c r="T23" s="58">
+        <f t="shared" si="0"/>
+        <v>907</v>
+      </c>
+      <c r="U23" s="75">
+        <f t="shared" si="4"/>
+        <v>907</v>
+      </c>
+      <c r="V23" s="75">
+        <f t="shared" si="5"/>
+        <v>37.791666666666664</v>
+      </c>
+      <c r="W23" s="9"/>
+      <c r="X23" s="9"/>
+      <c r="Y23" s="9"/>
+      <c r="Z23" s="9"/>
+      <c r="AA23" s="9"/>
+      <c r="AB23" s="9"/>
+      <c r="AC23" s="9"/>
+      <c r="AD23" s="9"/>
+      <c r="AE23" s="9"/>
+      <c r="AF23" s="12"/>
+      <c r="AG23" s="12"/>
+      <c r="AH23" s="12"/>
+      <c r="AI23" s="12"/>
+      <c r="AJ23" s="12"/>
+      <c r="AK23" s="12"/>
+      <c r="AL23" s="12"/>
+      <c r="AM23" s="12"/>
+      <c r="AN23" s="12"/>
+      <c r="AO23" s="12"/>
+      <c r="AP23" s="12"/>
+      <c r="AQ23" s="12"/>
+      <c r="AR23" s="12"/>
+      <c r="AS23" s="12"/>
+      <c r="AT23" s="12"/>
+      <c r="AU23" s="12"/>
+      <c r="AV23" s="12"/>
+      <c r="AW23" s="12"/>
+      <c r="AX23" s="12"/>
+      <c r="AY23" s="12"/>
+      <c r="AZ23" s="12"/>
+      <c r="BA23" s="12"/>
+      <c r="BB23" s="12"/>
+    </row>
+    <row r="24" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A24" s="27">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="B24" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" s="70">
+        <v>2</v>
+      </c>
+      <c r="D24" s="70"/>
+      <c r="E24" s="70"/>
+      <c r="F24" s="70"/>
+      <c r="G24" s="70"/>
+      <c r="H24" s="70">
+        <f>3*24</f>
+        <v>72</v>
+      </c>
+      <c r="I24" s="70"/>
+      <c r="J24" s="71"/>
+      <c r="K24" s="72"/>
+      <c r="L24" s="55"/>
+      <c r="M24" s="73"/>
+      <c r="N24" s="74"/>
+      <c r="O24" s="70"/>
+      <c r="P24" s="71"/>
+      <c r="Q24" s="71"/>
+      <c r="R24" s="72"/>
+      <c r="S24" s="55"/>
+      <c r="T24" s="58">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="U24" s="75">
+        <f t="shared" si="4"/>
+        <v>120</v>
+      </c>
+      <c r="V24" s="75">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="AF24" s="12"/>
+      <c r="AG24" s="12"/>
+      <c r="AH24" s="12"/>
+      <c r="AI24" s="12"/>
+      <c r="AJ24" s="12"/>
+      <c r="AK24" s="12"/>
+      <c r="AL24" s="12"/>
+      <c r="AM24" s="12"/>
+      <c r="AN24" s="12"/>
+      <c r="AO24" s="12"/>
+      <c r="AP24" s="12"/>
+      <c r="AQ24" s="12"/>
+      <c r="AR24" s="12"/>
+      <c r="AS24" s="12"/>
+      <c r="AT24" s="12"/>
+      <c r="AU24" s="12"/>
+      <c r="AV24" s="12"/>
+      <c r="AW24" s="12"/>
+      <c r="AX24" s="12"/>
+      <c r="AY24" s="12"/>
+      <c r="AZ24" s="12"/>
+      <c r="BA24" s="12"/>
+      <c r="BB24" s="12"/>
+    </row>
+    <row r="25" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A25" s="27">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="70">
+        <f>7+126</f>
+        <v>133</v>
+      </c>
+      <c r="D25" s="70"/>
+      <c r="E25" s="70"/>
+      <c r="F25" s="70"/>
+      <c r="G25" s="70"/>
+      <c r="H25" s="70"/>
+      <c r="I25" s="70"/>
+      <c r="J25" s="71">
+        <v>1</v>
+      </c>
+      <c r="K25" s="72"/>
+      <c r="L25" s="55"/>
+      <c r="M25" s="73"/>
+      <c r="N25" s="74"/>
+      <c r="O25" s="70">
+        <v>1</v>
+      </c>
+      <c r="P25" s="71"/>
+      <c r="Q25" s="71">
+        <v>2</v>
+      </c>
+      <c r="R25" s="72"/>
+      <c r="S25" s="55"/>
+      <c r="T25" s="58">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="U25" s="75">
+        <f t="shared" si="4"/>
+        <v>3265</v>
+      </c>
+      <c r="V25" s="75">
+        <f t="shared" si="5"/>
+        <v>136.04166666666666</v>
+      </c>
+      <c r="AY25" s="14" t="e">
+        <f>#REF!-AY24</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="27">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="B26" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="70">
+        <v>5</v>
+      </c>
+      <c r="D26" s="70"/>
+      <c r="E26" s="70"/>
+      <c r="F26" s="70"/>
+      <c r="G26" s="70"/>
+      <c r="H26" s="70"/>
+      <c r="I26" s="70"/>
+      <c r="J26" s="71"/>
+      <c r="K26" s="72"/>
+      <c r="L26" s="55"/>
+      <c r="M26" s="73"/>
+      <c r="N26" s="74"/>
+      <c r="O26" s="70"/>
+      <c r="P26" s="71"/>
+      <c r="Q26" s="71"/>
+      <c r="R26" s="72"/>
+      <c r="S26" s="55"/>
+      <c r="T26" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U26" s="75">
+        <f t="shared" si="4"/>
+        <v>120</v>
+      </c>
+      <c r="V26" s="75">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="W26" s="9"/>
+      <c r="X26" s="9"/>
+      <c r="Y26" s="9"/>
+      <c r="Z26" s="9"/>
+      <c r="AA26" s="9"/>
+      <c r="AB26" s="9"/>
+      <c r="AC26" s="9"/>
+      <c r="AD26" s="9"/>
+      <c r="AE26" s="9"/>
+    </row>
+    <row r="27" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="27">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="B27" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27" s="70">
+        <v>1</v>
+      </c>
+      <c r="D27" s="70"/>
+      <c r="E27" s="70"/>
+      <c r="F27" s="70"/>
+      <c r="G27" s="70"/>
+      <c r="H27" s="70"/>
+      <c r="I27" s="70"/>
+      <c r="J27" s="71"/>
+      <c r="K27" s="72"/>
+      <c r="L27" s="55"/>
+      <c r="M27" s="73"/>
+      <c r="N27" s="74"/>
+      <c r="O27" s="70"/>
+      <c r="P27" s="71"/>
+      <c r="Q27" s="71"/>
+      <c r="R27" s="72"/>
+      <c r="S27" s="55"/>
+      <c r="T27" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U27" s="75">
+        <f t="shared" si="4"/>
+        <v>24</v>
+      </c>
+      <c r="V27" s="75">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="W27" s="9"/>
+      <c r="X27" s="9"/>
+      <c r="Y27" s="9"/>
+      <c r="Z27" s="9"/>
+      <c r="AA27" s="9"/>
+      <c r="AB27" s="9"/>
+      <c r="AC27" s="9"/>
+      <c r="AD27" s="9"/>
+      <c r="AE27" s="9"/>
+    </row>
+    <row r="28" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="27">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="B28" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="70">
+        <f>252+40</f>
+        <v>292</v>
+      </c>
+      <c r="D28" s="70"/>
+      <c r="E28" s="70"/>
+      <c r="F28" s="70"/>
+      <c r="G28" s="70"/>
+      <c r="H28" s="70"/>
+      <c r="I28" s="70"/>
+      <c r="J28" s="71"/>
+      <c r="K28" s="72"/>
+      <c r="L28" s="55"/>
+      <c r="M28" s="73"/>
+      <c r="N28" s="74"/>
+      <c r="O28" s="70">
+        <v>2</v>
+      </c>
+      <c r="P28" s="71"/>
+      <c r="Q28" s="71">
+        <v>5</v>
+      </c>
+      <c r="R28" s="72"/>
+      <c r="S28" s="55"/>
+      <c r="T28" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U28" s="75">
+        <f t="shared" si="4"/>
+        <v>7176</v>
+      </c>
+      <c r="V28" s="75">
+        <f t="shared" si="5"/>
+        <v>299</v>
+      </c>
+      <c r="W28" s="9"/>
+      <c r="X28" s="9"/>
+      <c r="Y28" s="9"/>
+      <c r="Z28" s="9"/>
+      <c r="AA28" s="9"/>
+      <c r="AB28" s="9"/>
+      <c r="AC28" s="9"/>
+      <c r="AD28" s="9"/>
+      <c r="AE28" s="9"/>
+    </row>
+    <row r="29" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A29" s="27">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="B29" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" s="70"/>
+      <c r="D29" s="70"/>
+      <c r="E29" s="70"/>
+      <c r="F29" s="70"/>
+      <c r="G29" s="70"/>
+      <c r="H29" s="70"/>
+      <c r="I29" s="70"/>
+      <c r="J29" s="71">
+        <v>5</v>
+      </c>
+      <c r="K29" s="72"/>
+      <c r="L29" s="55"/>
+      <c r="M29" s="73"/>
+      <c r="N29" s="74"/>
+      <c r="O29" s="70"/>
+      <c r="P29" s="71"/>
+      <c r="Q29" s="71"/>
+      <c r="R29" s="72"/>
+      <c r="S29" s="55"/>
+      <c r="T29" s="58">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="U29" s="75">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="V29" s="75">
+        <f t="shared" si="5"/>
+        <v>0.20833333333333334</v>
+      </c>
+    </row>
+    <row r="30" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A30" s="27">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="B30" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="70"/>
+      <c r="D30" s="70"/>
+      <c r="E30" s="70"/>
+      <c r="F30" s="70"/>
+      <c r="G30" s="70"/>
+      <c r="H30" s="70"/>
+      <c r="I30" s="70"/>
+      <c r="J30" s="71"/>
+      <c r="K30" s="72"/>
+      <c r="L30" s="55"/>
+      <c r="M30" s="73"/>
+      <c r="N30" s="74"/>
+      <c r="O30" s="70"/>
+      <c r="P30" s="71"/>
+      <c r="Q30" s="71"/>
+      <c r="R30" s="72"/>
+      <c r="S30" s="55"/>
+      <c r="T30" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U30" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V30" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A31" s="27">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="B31" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" s="70"/>
+      <c r="D31" s="70"/>
+      <c r="E31" s="70"/>
+      <c r="F31" s="70"/>
+      <c r="G31" s="70"/>
+      <c r="H31" s="70"/>
+      <c r="I31" s="70"/>
+      <c r="J31" s="71"/>
+      <c r="K31" s="72"/>
+      <c r="L31" s="55"/>
+      <c r="M31" s="73"/>
+      <c r="N31" s="74"/>
+      <c r="O31" s="70"/>
+      <c r="P31" s="71"/>
+      <c r="Q31" s="71"/>
+      <c r="R31" s="72"/>
+      <c r="S31" s="55"/>
+      <c r="T31" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U31" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V31" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A32" s="27">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="B32" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" s="70"/>
+      <c r="D32" s="70"/>
+      <c r="E32" s="70"/>
+      <c r="F32" s="70"/>
+      <c r="G32" s="70"/>
+      <c r="H32" s="70"/>
+      <c r="I32" s="70"/>
+      <c r="J32" s="71"/>
+      <c r="K32" s="72"/>
+      <c r="L32" s="55"/>
+      <c r="M32" s="73"/>
+      <c r="N32" s="74"/>
+      <c r="O32" s="70"/>
+      <c r="P32" s="71"/>
+      <c r="Q32" s="71"/>
+      <c r="R32" s="72"/>
+      <c r="S32" s="55"/>
+      <c r="T32" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U32" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V32" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A33" s="27">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="B33" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" s="70"/>
+      <c r="D33" s="70"/>
+      <c r="E33" s="70"/>
+      <c r="F33" s="70"/>
+      <c r="G33" s="70"/>
+      <c r="H33" s="70"/>
+      <c r="I33" s="70"/>
+      <c r="J33" s="71"/>
+      <c r="K33" s="72"/>
+      <c r="L33" s="55"/>
+      <c r="M33" s="73"/>
+      <c r="N33" s="74"/>
+      <c r="O33" s="70"/>
+      <c r="P33" s="71"/>
+      <c r="Q33" s="71"/>
+      <c r="R33" s="72"/>
+      <c r="S33" s="55"/>
+      <c r="T33" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U33" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V33" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A34" s="27">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="B34" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" s="70">
+        <f>52+72</f>
+        <v>124</v>
+      </c>
+      <c r="D34" s="70"/>
+      <c r="E34" s="70"/>
+      <c r="F34" s="70"/>
+      <c r="G34" s="70"/>
+      <c r="H34" s="70"/>
+      <c r="I34" s="70">
+        <v>1</v>
+      </c>
+      <c r="J34" s="71"/>
+      <c r="K34" s="72">
+        <v>1</v>
+      </c>
+      <c r="L34" s="55"/>
+      <c r="M34" s="73"/>
+      <c r="N34" s="74"/>
+      <c r="O34" s="70">
+        <v>2</v>
+      </c>
+      <c r="P34" s="71"/>
+      <c r="Q34" s="71">
+        <v>6</v>
+      </c>
+      <c r="R34" s="72"/>
+      <c r="S34" s="55"/>
+      <c r="T34" s="58">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="U34" s="75">
+        <f t="shared" si="4"/>
+        <v>3170</v>
+      </c>
+      <c r="V34" s="75">
+        <f t="shared" si="5"/>
+        <v>132.08333333333334</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="27">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="B35" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="C35" s="70"/>
+      <c r="D35" s="70"/>
+      <c r="E35" s="70"/>
+      <c r="F35" s="70"/>
+      <c r="G35" s="70"/>
+      <c r="H35" s="70"/>
+      <c r="I35" s="70"/>
+      <c r="J35" s="71"/>
+      <c r="K35" s="72"/>
+      <c r="L35" s="55"/>
+      <c r="M35" s="73"/>
+      <c r="N35" s="74"/>
+      <c r="O35" s="70"/>
+      <c r="P35" s="71"/>
+      <c r="Q35" s="71"/>
+      <c r="R35" s="72"/>
+      <c r="S35" s="55"/>
+      <c r="T35" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U35" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V35" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A36" s="27">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+      <c r="B36" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="70"/>
+      <c r="D36" s="70"/>
+      <c r="E36" s="70"/>
+      <c r="F36" s="70"/>
+      <c r="G36" s="70"/>
+      <c r="H36" s="70"/>
+      <c r="I36" s="70"/>
+      <c r="J36" s="71"/>
+      <c r="K36" s="72"/>
+      <c r="L36" s="55"/>
+      <c r="M36" s="73"/>
+      <c r="N36" s="74"/>
+      <c r="O36" s="70"/>
+      <c r="P36" s="71"/>
+      <c r="Q36" s="71"/>
+      <c r="R36" s="72"/>
+      <c r="S36" s="55"/>
+      <c r="T36" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U36" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="27">
+        <f t="shared" si="1"/>
+        <v>34</v>
+      </c>
+      <c r="B37" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="C37" s="59">
+        <f>864+1836</f>
+        <v>2700</v>
+      </c>
+      <c r="D37" s="59"/>
+      <c r="E37" s="59"/>
+      <c r="F37" s="59"/>
+      <c r="G37" s="59"/>
+      <c r="H37" s="59">
+        <v>3</v>
+      </c>
+      <c r="I37" s="59">
+        <v>2</v>
+      </c>
+      <c r="J37" s="60"/>
+      <c r="K37" s="61">
+        <f>2*6+2</f>
+        <v>14</v>
+      </c>
+      <c r="L37" s="62"/>
+      <c r="M37" s="63">
+        <v>87</v>
+      </c>
+      <c r="N37" s="64"/>
+      <c r="O37" s="65">
+        <v>32</v>
+      </c>
+      <c r="P37" s="66"/>
+      <c r="Q37" s="66">
+        <v>77</v>
+      </c>
+      <c r="R37" s="67"/>
+      <c r="S37" s="62"/>
+      <c r="T37" s="77">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="U37" s="77">
+        <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
+        <v>17395</v>
+      </c>
+      <c r="V37" s="77">
+        <f>U37/6</f>
+        <v>2899.1666666666665</v>
+      </c>
+      <c r="W37" s="50"/>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A38" s="27">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="B38" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" s="70">
+        <v>5</v>
+      </c>
+      <c r="D38" s="70"/>
+      <c r="E38" s="70"/>
+      <c r="F38" s="70"/>
+      <c r="G38" s="70"/>
+      <c r="H38" s="70"/>
+      <c r="I38" s="70"/>
+      <c r="J38" s="71"/>
+      <c r="K38" s="72"/>
+      <c r="L38" s="55"/>
+      <c r="M38" s="73"/>
+      <c r="N38" s="74"/>
+      <c r="O38" s="70"/>
+      <c r="P38" s="71"/>
+      <c r="Q38" s="71"/>
+      <c r="R38" s="72"/>
+      <c r="S38" s="55"/>
+      <c r="T38" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U38" s="75">
+        <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
+        <v>120</v>
+      </c>
+      <c r="V38" s="75">
+        <f>U38/24</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A39" s="27">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="B39" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="C39" s="78"/>
+      <c r="D39" s="78"/>
+      <c r="E39" s="78"/>
+      <c r="F39" s="78"/>
+      <c r="G39" s="78"/>
+      <c r="H39" s="78"/>
+      <c r="I39" s="78"/>
+      <c r="J39" s="79"/>
+      <c r="K39" s="80"/>
+      <c r="L39" s="55"/>
+      <c r="M39" s="73"/>
+      <c r="N39" s="74"/>
+      <c r="O39" s="70"/>
+      <c r="P39" s="71"/>
+      <c r="Q39" s="71"/>
+      <c r="R39" s="72"/>
+      <c r="S39" s="95"/>
+      <c r="T39" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U39" s="75">
+        <f>C39*24+M39*24+O39*24+Q39*24+T39</f>
+        <v>0</v>
+      </c>
+      <c r="V39" s="75">
+        <f>U39/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="27">
+        <f t="shared" si="1"/>
+        <v>37</v>
+      </c>
+      <c r="B40" s="42" t="s">
+        <v>21</v>
+      </c>
+      <c r="C40" s="59">
+        <f>252+48</f>
+        <v>300</v>
+      </c>
+      <c r="D40" s="59"/>
+      <c r="E40" s="59"/>
+      <c r="F40" s="59"/>
+      <c r="G40" s="59"/>
+      <c r="H40" s="59"/>
+      <c r="I40" s="59"/>
+      <c r="J40" s="60"/>
+      <c r="K40" s="61">
+        <v>20</v>
+      </c>
+      <c r="L40" s="62"/>
+      <c r="M40" s="63"/>
+      <c r="N40" s="64"/>
+      <c r="O40" s="65">
+        <v>1</v>
+      </c>
+      <c r="P40" s="66"/>
+      <c r="Q40" s="66">
+        <v>4</v>
+      </c>
+      <c r="R40" s="67"/>
+      <c r="S40" s="62"/>
+      <c r="T40" s="77">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="U40" s="77">
+        <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
+        <v>7340</v>
+      </c>
+      <c r="V40" s="77">
+        <f>U40/24</f>
+        <v>305.83333333333331</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="27">
+        <f t="shared" si="1"/>
+        <v>38</v>
+      </c>
+      <c r="B41" s="43" t="s">
+        <v>22</v>
+      </c>
+      <c r="C41" s="82">
+        <f>768+18</f>
+        <v>786</v>
+      </c>
+      <c r="D41" s="82"/>
+      <c r="E41" s="82"/>
+      <c r="F41" s="82"/>
+      <c r="G41" s="82"/>
+      <c r="H41" s="82"/>
+      <c r="I41" s="82"/>
+      <c r="J41" s="83"/>
+      <c r="K41" s="84"/>
+      <c r="L41" s="85"/>
+      <c r="M41" s="86">
+        <v>4</v>
+      </c>
+      <c r="N41" s="87"/>
+      <c r="O41" s="82">
+        <v>10</v>
+      </c>
+      <c r="P41" s="83"/>
+      <c r="Q41" s="83">
+        <v>27</v>
+      </c>
+      <c r="R41" s="84"/>
+      <c r="S41" s="85"/>
+      <c r="T41" s="88">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U41" s="88">
+        <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
+        <v>9924</v>
+      </c>
+      <c r="V41" s="88">
+        <f>U41/12</f>
+        <v>827</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="27">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+      <c r="B42" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C42" s="70"/>
+      <c r="D42" s="70"/>
+      <c r="E42" s="70"/>
+      <c r="F42" s="70"/>
+      <c r="G42" s="70"/>
+      <c r="H42" s="70"/>
+      <c r="I42" s="70"/>
+      <c r="J42" s="71"/>
+      <c r="K42" s="72"/>
+      <c r="L42" s="55"/>
+      <c r="M42" s="73"/>
+      <c r="N42" s="74"/>
+      <c r="O42" s="70"/>
+      <c r="P42" s="71"/>
+      <c r="Q42" s="71"/>
+      <c r="R42" s="72"/>
+      <c r="S42" s="55"/>
+      <c r="T42" s="75"/>
+      <c r="U42" s="75"/>
+      <c r="V42" s="75"/>
+    </row>
+    <row r="43" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="27">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="B43" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="C43" s="65">
+        <f>1835+13068+19764+3348</f>
+        <v>38015</v>
+      </c>
+      <c r="D43" s="65"/>
+      <c r="E43" s="65"/>
+      <c r="F43" s="65"/>
+      <c r="G43" s="65"/>
+      <c r="H43" s="65">
+        <v>9</v>
+      </c>
+      <c r="I43" s="65">
+        <v>12</v>
+      </c>
+      <c r="J43" s="66">
+        <f>4*6+4</f>
+        <v>28</v>
+      </c>
+      <c r="K43" s="67">
+        <f>95*6+1</f>
+        <v>571</v>
+      </c>
+      <c r="L43" s="62"/>
+      <c r="M43" s="63">
+        <v>565</v>
+      </c>
+      <c r="N43" s="64"/>
+      <c r="O43" s="65">
+        <v>483</v>
+      </c>
+      <c r="P43" s="66"/>
+      <c r="Q43" s="66">
+        <v>650</v>
+      </c>
+      <c r="R43" s="67"/>
+      <c r="S43" s="62"/>
+      <c r="T43" s="77">
+        <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
+        <v>620</v>
+      </c>
+      <c r="U43" s="77">
+        <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
+        <v>238898</v>
+      </c>
+      <c r="V43" s="77">
+        <f>U43/6</f>
+        <v>39816.333333333336</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="27">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+      <c r="B44" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="70"/>
+      <c r="D44" s="70"/>
+      <c r="E44" s="70"/>
+      <c r="F44" s="70"/>
+      <c r="G44" s="70"/>
+      <c r="H44" s="70"/>
+      <c r="I44" s="70"/>
+      <c r="J44" s="71"/>
+      <c r="K44" s="72"/>
+      <c r="L44" s="55"/>
+      <c r="M44" s="73"/>
+      <c r="N44" s="74"/>
+      <c r="O44" s="70"/>
+      <c r="P44" s="71"/>
+      <c r="Q44" s="71"/>
+      <c r="R44" s="72"/>
+      <c r="S44" s="55"/>
+      <c r="T44" s="75"/>
+      <c r="U44" s="75"/>
+      <c r="V44" s="75"/>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A45" s="27">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="B45" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="70">
+        <v>5</v>
+      </c>
+      <c r="D45" s="70"/>
+      <c r="E45" s="70"/>
+      <c r="F45" s="70"/>
+      <c r="G45" s="70"/>
+      <c r="H45" s="70"/>
+      <c r="I45" s="70"/>
+      <c r="J45" s="71"/>
+      <c r="K45" s="72"/>
+      <c r="L45" s="55"/>
+      <c r="M45" s="73"/>
+      <c r="N45" s="74"/>
+      <c r="O45" s="70"/>
+      <c r="P45" s="71"/>
+      <c r="Q45" s="71"/>
+      <c r="R45" s="72"/>
+      <c r="S45" s="55"/>
+      <c r="T45" s="75">
+        <f t="shared" ref="T45:T54" si="7">H45+I45+J45+K45+N45+P45+R45</f>
+        <v>0</v>
+      </c>
+      <c r="U45" s="75">
+        <f>C45*24+M45*24+O45*24+Q45*24+T45</f>
+        <v>120</v>
+      </c>
+      <c r="V45" s="75">
+        <f>U45/24</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A46" s="27">
+        <f t="shared" si="1"/>
+        <v>43</v>
+      </c>
+      <c r="B46" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="C46" s="70"/>
+      <c r="D46" s="70"/>
+      <c r="E46" s="70"/>
+      <c r="F46" s="70"/>
+      <c r="G46" s="70"/>
+      <c r="H46" s="70"/>
+      <c r="I46" s="70"/>
+      <c r="J46" s="71"/>
+      <c r="K46" s="72"/>
+      <c r="L46" s="55"/>
+      <c r="M46" s="73"/>
+      <c r="N46" s="74"/>
+      <c r="O46" s="70"/>
+      <c r="P46" s="71"/>
+      <c r="Q46" s="71"/>
+      <c r="R46" s="72"/>
+      <c r="S46" s="55"/>
+      <c r="T46" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U46" s="75">
+        <f t="shared" ref="U46:U50" si="8">C46*24+M46*24+O46*24+Q46*24+T46</f>
+        <v>0</v>
+      </c>
+      <c r="V46" s="75">
+        <f t="shared" ref="V46:V54" si="9">U46/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="27">
+        <f t="shared" si="1"/>
+        <v>44</v>
+      </c>
+      <c r="B47" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="C47" s="65">
+        <f>89+648+324+88+432+83+103+324+432+106</f>
+        <v>2629</v>
+      </c>
+      <c r="D47" s="65"/>
+      <c r="E47" s="65"/>
+      <c r="F47" s="65"/>
+      <c r="G47" s="65"/>
+      <c r="H47" s="65">
+        <v>1</v>
+      </c>
+      <c r="I47" s="65"/>
+      <c r="J47" s="66"/>
+      <c r="K47" s="67">
+        <v>5</v>
+      </c>
+      <c r="L47" s="62"/>
+      <c r="M47" s="63">
+        <v>2</v>
+      </c>
+      <c r="N47" s="64"/>
+      <c r="O47" s="65">
+        <v>15</v>
+      </c>
+      <c r="P47" s="66"/>
+      <c r="Q47" s="66">
+        <v>5</v>
+      </c>
+      <c r="R47" s="67">
+        <v>3</v>
+      </c>
+      <c r="S47" s="62"/>
+      <c r="T47" s="77">
+        <f t="shared" si="7"/>
+        <v>9</v>
+      </c>
+      <c r="U47" s="77">
+        <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
+        <v>15915</v>
+      </c>
+      <c r="V47" s="77">
+        <f>U47/6</f>
+        <v>2652.5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A48" s="27">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="B48" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C48" s="70"/>
+      <c r="D48" s="70"/>
+      <c r="E48" s="70"/>
+      <c r="F48" s="70"/>
+      <c r="G48" s="70"/>
+      <c r="H48" s="70">
+        <v>24</v>
+      </c>
+      <c r="I48" s="70"/>
+      <c r="J48" s="71"/>
+      <c r="K48" s="72"/>
+      <c r="L48" s="55"/>
+      <c r="M48" s="73"/>
+      <c r="N48" s="74"/>
+      <c r="O48" s="70"/>
+      <c r="P48" s="71"/>
+      <c r="Q48" s="71"/>
+      <c r="R48" s="72"/>
+      <c r="S48" s="55"/>
+      <c r="T48" s="75">
+        <f t="shared" si="7"/>
+        <v>24</v>
+      </c>
+      <c r="U48" s="75">
+        <f t="shared" si="8"/>
+        <v>24</v>
+      </c>
+      <c r="V48" s="75">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A49" s="27">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="B49" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C49" s="70"/>
+      <c r="D49" s="70"/>
+      <c r="E49" s="70"/>
+      <c r="F49" s="70"/>
+      <c r="G49" s="70"/>
+      <c r="H49" s="70"/>
+      <c r="I49" s="70"/>
+      <c r="J49" s="71"/>
+      <c r="K49" s="72"/>
+      <c r="L49" s="55"/>
+      <c r="M49" s="73"/>
+      <c r="N49" s="74"/>
+      <c r="O49" s="70"/>
+      <c r="P49" s="71"/>
+      <c r="Q49" s="71"/>
+      <c r="R49" s="72"/>
+      <c r="S49" s="55"/>
+      <c r="T49" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U49" s="75">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V49" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A50" s="27">
+        <f t="shared" si="1"/>
+        <v>47</v>
+      </c>
+      <c r="B50" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="C50" s="70"/>
+      <c r="D50" s="70"/>
+      <c r="E50" s="70"/>
+      <c r="F50" s="70"/>
+      <c r="G50" s="70"/>
+      <c r="H50" s="70"/>
+      <c r="I50" s="70"/>
+      <c r="J50" s="71"/>
+      <c r="K50" s="72"/>
+      <c r="L50" s="55"/>
+      <c r="M50" s="73"/>
+      <c r="N50" s="74"/>
+      <c r="O50" s="70"/>
+      <c r="P50" s="71"/>
+      <c r="Q50" s="71"/>
+      <c r="R50" s="72"/>
+      <c r="S50" s="55"/>
+      <c r="T50" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U50" s="75">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V50" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="27">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+      <c r="B51" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="C51" s="65">
+        <v>34</v>
+      </c>
+      <c r="D51" s="65"/>
+      <c r="E51" s="65"/>
+      <c r="F51" s="65"/>
+      <c r="G51" s="65"/>
+      <c r="H51" s="65"/>
+      <c r="I51" s="65"/>
+      <c r="J51" s="66"/>
+      <c r="K51" s="67"/>
+      <c r="L51" s="62"/>
+      <c r="M51" s="63"/>
+      <c r="N51" s="64"/>
+      <c r="O51" s="65"/>
+      <c r="P51" s="66"/>
+      <c r="Q51" s="66"/>
+      <c r="R51" s="67"/>
+      <c r="S51" s="62"/>
+      <c r="T51" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U51" s="77">
+        <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
+        <v>204</v>
+      </c>
+      <c r="V51" s="77">
+        <f>U51/6</f>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A52" s="27">
+        <f t="shared" si="1"/>
+        <v>49</v>
+      </c>
+      <c r="B52" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="C52" s="70"/>
+      <c r="D52" s="70"/>
+      <c r="E52" s="70"/>
+      <c r="F52" s="70"/>
+      <c r="G52" s="70"/>
+      <c r="H52" s="70"/>
+      <c r="I52" s="70"/>
+      <c r="J52" s="71"/>
+      <c r="K52" s="72"/>
+      <c r="L52" s="55"/>
+      <c r="M52" s="73"/>
+      <c r="N52" s="74"/>
+      <c r="O52" s="70"/>
+      <c r="P52" s="71"/>
+      <c r="Q52" s="71"/>
+      <c r="R52" s="72"/>
+      <c r="S52" s="55"/>
+      <c r="T52" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U52" s="75">
+        <f t="shared" ref="U52:U54" si="10">C52*24+M52*24+O52*24+Q52*24+T52</f>
+        <v>0</v>
+      </c>
+      <c r="V52" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A53" s="27">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="B53" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C53" s="70">
+        <v>7</v>
+      </c>
+      <c r="D53" s="70"/>
+      <c r="E53" s="70"/>
+      <c r="F53" s="70"/>
+      <c r="G53" s="70"/>
+      <c r="H53" s="70"/>
+      <c r="I53" s="70"/>
+      <c r="J53" s="71"/>
+      <c r="K53" s="72"/>
+      <c r="L53" s="55"/>
+      <c r="M53" s="73"/>
+      <c r="N53" s="74"/>
+      <c r="O53" s="70"/>
+      <c r="P53" s="71"/>
+      <c r="Q53" s="71"/>
+      <c r="R53" s="72"/>
+      <c r="S53" s="55"/>
+      <c r="T53" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U53" s="75">
+        <f t="shared" si="10"/>
+        <v>168</v>
+      </c>
+      <c r="V53" s="75">
+        <f t="shared" si="9"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A54" s="27">
+        <f t="shared" si="1"/>
+        <v>51</v>
+      </c>
+      <c r="B54" s="26"/>
+      <c r="C54" s="70"/>
+      <c r="D54" s="70"/>
+      <c r="E54" s="70"/>
+      <c r="F54" s="70"/>
+      <c r="G54" s="70"/>
+      <c r="H54" s="70"/>
+      <c r="I54" s="70"/>
+      <c r="J54" s="71"/>
+      <c r="K54" s="72"/>
+      <c r="L54" s="55"/>
+      <c r="M54" s="73"/>
+      <c r="N54" s="74"/>
+      <c r="O54" s="70"/>
+      <c r="P54" s="71"/>
+      <c r="Q54" s="71"/>
+      <c r="R54" s="72"/>
+      <c r="S54" s="55"/>
+      <c r="T54" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U54" s="75">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V54" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A55" s="27">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="B55" s="26"/>
+      <c r="C55" s="70"/>
+      <c r="D55" s="70"/>
+      <c r="E55" s="70"/>
+      <c r="F55" s="70"/>
+      <c r="G55" s="70"/>
+      <c r="H55" s="70"/>
+      <c r="I55" s="70"/>
+      <c r="J55" s="71"/>
+      <c r="K55" s="72"/>
+      <c r="L55" s="55"/>
+      <c r="M55" s="73"/>
+      <c r="N55" s="74"/>
+      <c r="O55" s="70"/>
+      <c r="P55" s="71"/>
+      <c r="Q55" s="71"/>
+      <c r="R55" s="72"/>
+      <c r="S55" s="55"/>
+      <c r="T55" s="75"/>
+      <c r="U55" s="75"/>
+      <c r="V55" s="75"/>
+    </row>
+    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A56" s="27">
+        <f t="shared" si="1"/>
+        <v>53</v>
+      </c>
+      <c r="B56" s="26"/>
+      <c r="C56" s="70"/>
+      <c r="D56" s="70"/>
+      <c r="E56" s="70"/>
+      <c r="F56" s="70"/>
+      <c r="G56" s="70"/>
+      <c r="H56" s="70"/>
+      <c r="I56" s="70"/>
+      <c r="J56" s="71"/>
+      <c r="K56" s="72"/>
+      <c r="L56" s="55"/>
+      <c r="M56" s="73"/>
+      <c r="N56" s="74"/>
+      <c r="O56" s="70"/>
+      <c r="P56" s="71"/>
+      <c r="Q56" s="71"/>
+      <c r="R56" s="72"/>
+      <c r="S56" s="55"/>
+      <c r="T56" s="75"/>
+      <c r="U56" s="75"/>
+      <c r="V56" s="75"/>
+    </row>
+    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A57" s="27">
+        <f t="shared" si="1"/>
+        <v>54</v>
+      </c>
+      <c r="B57" s="26"/>
+      <c r="C57" s="70"/>
+      <c r="D57" s="70"/>
+      <c r="E57" s="70"/>
+      <c r="F57" s="70"/>
+      <c r="G57" s="70"/>
+      <c r="H57" s="70"/>
+      <c r="I57" s="70"/>
+      <c r="J57" s="71"/>
+      <c r="K57" s="72"/>
+      <c r="L57" s="55"/>
+      <c r="M57" s="73"/>
+      <c r="N57" s="74"/>
+      <c r="O57" s="70"/>
+      <c r="P57" s="71"/>
+      <c r="Q57" s="71"/>
+      <c r="R57" s="72"/>
+      <c r="S57" s="55"/>
+      <c r="T57" s="75"/>
+      <c r="U57" s="75"/>
+      <c r="V57" s="75"/>
+    </row>
+    <row r="58" spans="1:22" s="15" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B58" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="C58" s="2">
+        <f>SUM(C7:C57)</f>
+        <v>48162</v>
+      </c>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2">
+        <f t="shared" ref="F58:K58" si="11">SUM(F7:F57)</f>
+        <v>0</v>
+      </c>
+      <c r="G58" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="H58" s="2">
+        <f t="shared" si="11"/>
+        <v>1196</v>
+      </c>
+      <c r="I58" s="6">
+        <f t="shared" si="11"/>
+        <v>38</v>
+      </c>
+      <c r="J58" s="6">
+        <f t="shared" si="11"/>
+        <v>34</v>
+      </c>
+      <c r="K58" s="6">
+        <f t="shared" si="11"/>
+        <v>619</v>
+      </c>
+      <c r="M58" s="5">
+        <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
+        <v>675</v>
+      </c>
+      <c r="N58" s="5">
+        <f t="shared" si="12"/>
+        <v>10</v>
+      </c>
+      <c r="O58" s="5">
+        <f t="shared" si="12"/>
+        <v>561</v>
+      </c>
+      <c r="P58" s="5">
+        <f t="shared" si="12"/>
+        <v>19</v>
+      </c>
+      <c r="Q58" s="5">
+        <f t="shared" si="12"/>
+        <v>806</v>
+      </c>
+      <c r="R58" s="5">
+        <f t="shared" si="12"/>
+        <v>10</v>
+      </c>
+      <c r="S58" s="55"/>
+      <c r="T58" s="4">
+        <f>SUM(T7:T57)</f>
+        <v>1926</v>
+      </c>
+      <c r="U58" s="90">
+        <f>SUM(U7:U57)</f>
+        <v>381606</v>
+      </c>
+      <c r="V58" s="4">
+        <f>SUM(V7:V57)</f>
+        <v>50365.25</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="60" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="C60" s="111" t="s">
+        <v>41</v>
+      </c>
+      <c r="D60" s="112"/>
+      <c r="E60" s="112"/>
+      <c r="F60" s="112"/>
+      <c r="G60" s="112"/>
+      <c r="H60" s="112"/>
+      <c r="I60" s="112"/>
+      <c r="J60" s="112"/>
+      <c r="K60" s="113"/>
+      <c r="U60" s="24" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B61" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="C61" s="19"/>
+      <c r="D61" s="19"/>
+      <c r="E61" s="19"/>
+      <c r="F61" s="19"/>
+      <c r="G61" s="19"/>
+      <c r="H61" s="19"/>
+      <c r="I61" s="19"/>
+      <c r="J61" s="45"/>
+      <c r="K61" s="20"/>
+      <c r="U61" s="7"/>
+    </row>
+    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B62" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+      <c r="J62" s="44"/>
+      <c r="K62" s="21"/>
+      <c r="U62" s="3"/>
+    </row>
+    <row r="63" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B63" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C63" s="22"/>
+      <c r="D63" s="22"/>
+      <c r="E63" s="22"/>
+      <c r="F63" s="22"/>
+      <c r="G63" s="22"/>
+      <c r="H63" s="22"/>
+      <c r="I63" s="22"/>
+      <c r="J63" s="46"/>
+      <c r="K63" s="23"/>
+      <c r="U63" s="8"/>
+    </row>
+    <row r="64" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B65" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="C65" s="19"/>
+      <c r="D65" s="19"/>
+      <c r="E65" s="19"/>
+      <c r="F65" s="19"/>
+      <c r="G65" s="19"/>
+      <c r="H65" s="19"/>
+      <c r="I65" s="19"/>
+      <c r="J65" s="45"/>
+      <c r="K65" s="20"/>
+      <c r="U65" s="7"/>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B66" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C66" s="1"/>
+      <c r="D66" s="1"/>
+      <c r="E66" s="1"/>
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="J66" s="44"/>
+      <c r="K66" s="21"/>
+      <c r="U66" s="3"/>
+    </row>
+    <row r="67" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B67" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C67" s="22"/>
+      <c r="D67" s="22"/>
+      <c r="E67" s="22"/>
+      <c r="F67" s="22"/>
+      <c r="G67" s="22"/>
+      <c r="H67" s="22"/>
+      <c r="I67" s="22"/>
+      <c r="J67" s="46"/>
+      <c r="K67" s="23"/>
+      <c r="U67" s="8"/>
+    </row>
+    <row r="68" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B69" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="C69" s="19"/>
+      <c r="D69" s="19"/>
+      <c r="E69" s="19"/>
+      <c r="F69" s="19"/>
+      <c r="G69" s="19"/>
+      <c r="H69" s="19"/>
+      <c r="I69" s="19"/>
+      <c r="J69" s="45"/>
+      <c r="K69" s="20"/>
+      <c r="U69" s="7"/>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B70" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="J70" s="44"/>
+      <c r="K70" s="21"/>
+      <c r="U70" s="3"/>
+    </row>
+    <row r="71" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B71" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C71" s="22"/>
+      <c r="D71" s="22"/>
+      <c r="E71" s="22"/>
+      <c r="F71" s="22"/>
+      <c r="G71" s="22"/>
+      <c r="H71" s="22"/>
+      <c r="I71" s="22"/>
+      <c r="J71" s="46"/>
+      <c r="K71" s="23"/>
+      <c r="U71" s="8"/>
+    </row>
+    <row r="72" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B73" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="C73" s="19"/>
+      <c r="D73" s="19"/>
+      <c r="E73" s="19"/>
+      <c r="F73" s="19"/>
+      <c r="G73" s="19"/>
+      <c r="H73" s="19"/>
+      <c r="I73" s="19"/>
+      <c r="J73" s="45"/>
+      <c r="K73" s="20"/>
+      <c r="U73" s="7"/>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B74" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C74" s="1"/>
+      <c r="D74" s="1"/>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1"/>
+      <c r="J74" s="44"/>
+      <c r="K74" s="21"/>
+      <c r="U74" s="3"/>
+    </row>
+    <row r="75" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B75" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C75" s="22"/>
+      <c r="D75" s="22"/>
+      <c r="E75" s="22"/>
+      <c r="F75" s="22"/>
+      <c r="G75" s="22"/>
+      <c r="H75" s="22"/>
+      <c r="I75" s="22"/>
+      <c r="J75" s="46"/>
+      <c r="K75" s="23"/>
+      <c r="U75" s="8"/>
+    </row>
+    <row r="76" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B77" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="C77" s="19"/>
+      <c r="D77" s="19"/>
+      <c r="E77" s="19"/>
+      <c r="F77" s="19"/>
+      <c r="G77" s="19"/>
+      <c r="H77" s="19"/>
+      <c r="I77" s="19"/>
+      <c r="J77" s="45"/>
+      <c r="K77" s="20"/>
+      <c r="U77" s="7"/>
+    </row>
+    <row r="78" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B78" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C78" s="1"/>
+      <c r="D78" s="1"/>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+      <c r="J78" s="44"/>
+      <c r="K78" s="21"/>
+      <c r="U78" s="3"/>
+    </row>
+    <row r="79" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B79" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C79" s="22"/>
+      <c r="D79" s="22"/>
+      <c r="E79" s="22"/>
+      <c r="F79" s="22"/>
+      <c r="G79" s="22"/>
+      <c r="H79" s="22"/>
+      <c r="I79" s="22"/>
+      <c r="J79" s="46"/>
+      <c r="K79" s="23"/>
+      <c r="U79" s="8"/>
+    </row>
+    <row r="80" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="81" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B81" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="C81" s="17"/>
+      <c r="D81" s="17"/>
+      <c r="E81" s="17"/>
+      <c r="F81" s="17"/>
+      <c r="G81" s="17"/>
+      <c r="H81" s="17"/>
+      <c r="I81" s="17"/>
+      <c r="J81" s="47"/>
+      <c r="K81" s="18"/>
+      <c r="U81" s="16"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="C60:K60"/>
+    <mergeCell ref="I1:U1"/>
+    <mergeCell ref="C4:K4"/>
+    <mergeCell ref="T4:T5"/>
+    <mergeCell ref="U4:U5"/>
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -39468,21 +42606,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="113" t="s">
+      <c r="I1" s="114" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="113"/>
-      <c r="K1" s="113"/>
-      <c r="L1" s="113"/>
-      <c r="M1" s="113"/>
-      <c r="N1" s="113"/>
-      <c r="O1" s="113"/>
-      <c r="P1" s="113"/>
-      <c r="Q1" s="113"/>
-      <c r="R1" s="113"/>
-      <c r="S1" s="113"/>
-      <c r="T1" s="113"/>
-      <c r="U1" s="113"/>
+      <c r="J1" s="114"/>
+      <c r="K1" s="114"/>
+      <c r="L1" s="114"/>
+      <c r="M1" s="114"/>
+      <c r="N1" s="114"/>
+      <c r="O1" s="114"/>
+      <c r="P1" s="114"/>
+      <c r="Q1" s="114"/>
+      <c r="R1" s="114"/>
+      <c r="S1" s="114"/>
+      <c r="T1" s="114"/>
+      <c r="U1" s="114"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -39494,17 +42632,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="114" t="s">
+      <c r="C4" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="114"/>
-      <c r="E4" s="114"/>
-      <c r="F4" s="114"/>
-      <c r="G4" s="114"/>
-      <c r="H4" s="114"/>
-      <c r="I4" s="114"/>
-      <c r="J4" s="115"/>
-      <c r="K4" s="116"/>
+      <c r="D4" s="115"/>
+      <c r="E4" s="115"/>
+      <c r="F4" s="115"/>
+      <c r="G4" s="115"/>
+      <c r="H4" s="115"/>
+      <c r="I4" s="115"/>
+      <c r="J4" s="116"/>
+      <c r="K4" s="117"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -39524,13 +42662,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="117" t="s">
+      <c r="T4" s="118" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="123" t="s">
+      <c r="U4" s="124" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="106" t="s">
+      <c r="V4" s="107" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -39570,10 +42708,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="121" t="s">
+      <c r="J5" s="122" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="122"/>
+      <c r="K5" s="123"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -39581,9 +42719,9 @@
       <c r="Q5" s="97"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="118"/>
-      <c r="U5" s="124"/>
-      <c r="V5" s="107"/>
+      <c r="T5" s="119"/>
+      <c r="U5" s="125"/>
+      <c r="V5" s="108"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -42283,17 +45421,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="110" t="s">
+      <c r="C60" s="111" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="111"/>
-      <c r="E60" s="111"/>
-      <c r="F60" s="111"/>
-      <c r="G60" s="111"/>
-      <c r="H60" s="111"/>
-      <c r="I60" s="111"/>
-      <c r="J60" s="111"/>
-      <c r="K60" s="112"/>
+      <c r="D60" s="112"/>
+      <c r="E60" s="112"/>
+      <c r="F60" s="112"/>
+      <c r="G60" s="112"/>
+      <c r="H60" s="112"/>
+      <c r="I60" s="112"/>
+      <c r="J60" s="112"/>
+      <c r="K60" s="113"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -42602,21 +45740,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="113" t="s">
+      <c r="I1" s="114" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="113"/>
-      <c r="K1" s="113"/>
-      <c r="L1" s="113"/>
-      <c r="M1" s="113"/>
-      <c r="N1" s="113"/>
-      <c r="O1" s="113"/>
-      <c r="P1" s="113"/>
-      <c r="Q1" s="113"/>
-      <c r="R1" s="113"/>
-      <c r="S1" s="113"/>
-      <c r="T1" s="113"/>
-      <c r="U1" s="113"/>
+      <c r="J1" s="114"/>
+      <c r="K1" s="114"/>
+      <c r="L1" s="114"/>
+      <c r="M1" s="114"/>
+      <c r="N1" s="114"/>
+      <c r="O1" s="114"/>
+      <c r="P1" s="114"/>
+      <c r="Q1" s="114"/>
+      <c r="R1" s="114"/>
+      <c r="S1" s="114"/>
+      <c r="T1" s="114"/>
+      <c r="U1" s="114"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -42628,17 +45766,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="114" t="s">
+      <c r="C4" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="114"/>
-      <c r="E4" s="114"/>
-      <c r="F4" s="114"/>
-      <c r="G4" s="114"/>
-      <c r="H4" s="114"/>
-      <c r="I4" s="114"/>
-      <c r="J4" s="115"/>
-      <c r="K4" s="116"/>
+      <c r="D4" s="115"/>
+      <c r="E4" s="115"/>
+      <c r="F4" s="115"/>
+      <c r="G4" s="115"/>
+      <c r="H4" s="115"/>
+      <c r="I4" s="115"/>
+      <c r="J4" s="116"/>
+      <c r="K4" s="117"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -42658,13 +45796,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="117" t="s">
+      <c r="T4" s="118" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="123" t="s">
+      <c r="U4" s="124" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="106" t="s">
+      <c r="V4" s="107" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -42704,10 +45842,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="121" t="s">
+      <c r="J5" s="122" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="122"/>
+      <c r="K5" s="123"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -42715,9 +45853,9 @@
       <c r="Q5" s="97"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="118"/>
-      <c r="U5" s="124"/>
-      <c r="V5" s="107"/>
+      <c r="T5" s="119"/>
+      <c r="U5" s="125"/>
+      <c r="V5" s="108"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -45417,17 +48555,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="110" t="s">
+      <c r="C60" s="111" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="111"/>
-      <c r="E60" s="111"/>
-      <c r="F60" s="111"/>
-      <c r="G60" s="111"/>
-      <c r="H60" s="111"/>
-      <c r="I60" s="111"/>
-      <c r="J60" s="111"/>
-      <c r="K60" s="112"/>
+      <c r="D60" s="112"/>
+      <c r="E60" s="112"/>
+      <c r="F60" s="112"/>
+      <c r="G60" s="112"/>
+      <c r="H60" s="112"/>
+      <c r="I60" s="112"/>
+      <c r="J60" s="112"/>
+      <c r="K60" s="113"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -45736,21 +48874,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="113" t="s">
+      <c r="I1" s="114" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="113"/>
-      <c r="K1" s="113"/>
-      <c r="L1" s="113"/>
-      <c r="M1" s="113"/>
-      <c r="N1" s="113"/>
-      <c r="O1" s="113"/>
-      <c r="P1" s="113"/>
-      <c r="Q1" s="113"/>
-      <c r="R1" s="113"/>
-      <c r="S1" s="113"/>
-      <c r="T1" s="113"/>
-      <c r="U1" s="113"/>
+      <c r="J1" s="114"/>
+      <c r="K1" s="114"/>
+      <c r="L1" s="114"/>
+      <c r="M1" s="114"/>
+      <c r="N1" s="114"/>
+      <c r="O1" s="114"/>
+      <c r="P1" s="114"/>
+      <c r="Q1" s="114"/>
+      <c r="R1" s="114"/>
+      <c r="S1" s="114"/>
+      <c r="T1" s="114"/>
+      <c r="U1" s="114"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -45762,17 +48900,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="114" t="s">
+      <c r="C4" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="114"/>
-      <c r="E4" s="114"/>
-      <c r="F4" s="114"/>
-      <c r="G4" s="114"/>
-      <c r="H4" s="114"/>
-      <c r="I4" s="114"/>
-      <c r="J4" s="115"/>
-      <c r="K4" s="116"/>
+      <c r="D4" s="115"/>
+      <c r="E4" s="115"/>
+      <c r="F4" s="115"/>
+      <c r="G4" s="115"/>
+      <c r="H4" s="115"/>
+      <c r="I4" s="115"/>
+      <c r="J4" s="116"/>
+      <c r="K4" s="117"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -45792,13 +48930,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="117" t="s">
+      <c r="T4" s="118" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="123" t="s">
+      <c r="U4" s="124" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="106" t="s">
+      <c r="V4" s="107" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -45838,10 +48976,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="121" t="s">
+      <c r="J5" s="122" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="122"/>
+      <c r="K5" s="123"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -45849,9 +48987,9 @@
       <c r="Q5" s="97"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="118"/>
-      <c r="U5" s="124"/>
-      <c r="V5" s="107"/>
+      <c r="T5" s="119"/>
+      <c r="U5" s="125"/>
+      <c r="V5" s="108"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -48541,17 +51679,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="110" t="s">
+      <c r="C60" s="111" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="111"/>
-      <c r="E60" s="111"/>
-      <c r="F60" s="111"/>
-      <c r="G60" s="111"/>
-      <c r="H60" s="111"/>
-      <c r="I60" s="111"/>
-      <c r="J60" s="111"/>
-      <c r="K60" s="112"/>
+      <c r="D60" s="112"/>
+      <c r="E60" s="112"/>
+      <c r="F60" s="112"/>
+      <c r="G60" s="112"/>
+      <c r="H60" s="112"/>
+      <c r="I60" s="112"/>
+      <c r="J60" s="112"/>
+      <c r="K60" s="113"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -48860,21 +51998,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="113" t="s">
+      <c r="I1" s="114" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="113"/>
-      <c r="K1" s="113"/>
-      <c r="L1" s="113"/>
-      <c r="M1" s="113"/>
-      <c r="N1" s="113"/>
-      <c r="O1" s="113"/>
-      <c r="P1" s="113"/>
-      <c r="Q1" s="113"/>
-      <c r="R1" s="113"/>
-      <c r="S1" s="113"/>
-      <c r="T1" s="113"/>
-      <c r="U1" s="113"/>
+      <c r="J1" s="114"/>
+      <c r="K1" s="114"/>
+      <c r="L1" s="114"/>
+      <c r="M1" s="114"/>
+      <c r="N1" s="114"/>
+      <c r="O1" s="114"/>
+      <c r="P1" s="114"/>
+      <c r="Q1" s="114"/>
+      <c r="R1" s="114"/>
+      <c r="S1" s="114"/>
+      <c r="T1" s="114"/>
+      <c r="U1" s="114"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -48886,17 +52024,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="114" t="s">
+      <c r="C4" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="114"/>
-      <c r="E4" s="114"/>
-      <c r="F4" s="114"/>
-      <c r="G4" s="114"/>
-      <c r="H4" s="114"/>
-      <c r="I4" s="114"/>
-      <c r="J4" s="115"/>
-      <c r="K4" s="116"/>
+      <c r="D4" s="115"/>
+      <c r="E4" s="115"/>
+      <c r="F4" s="115"/>
+      <c r="G4" s="115"/>
+      <c r="H4" s="115"/>
+      <c r="I4" s="115"/>
+      <c r="J4" s="116"/>
+      <c r="K4" s="117"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -48916,13 +52054,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="117" t="s">
+      <c r="T4" s="118" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="123" t="s">
+      <c r="U4" s="124" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="106" t="s">
+      <c r="V4" s="107" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -48962,10 +52100,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="121" t="s">
+      <c r="J5" s="122" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="122"/>
+      <c r="K5" s="123"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -48973,9 +52111,9 @@
       <c r="Q5" s="98"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="118"/>
-      <c r="U5" s="124"/>
-      <c r="V5" s="107"/>
+      <c r="T5" s="119"/>
+      <c r="U5" s="125"/>
+      <c r="V5" s="108"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -51690,17 +54828,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="110" t="s">
+      <c r="C60" s="111" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="111"/>
-      <c r="E60" s="111"/>
-      <c r="F60" s="111"/>
-      <c r="G60" s="111"/>
-      <c r="H60" s="111"/>
-      <c r="I60" s="111"/>
-      <c r="J60" s="111"/>
-      <c r="K60" s="112"/>
+      <c r="D60" s="112"/>
+      <c r="E60" s="112"/>
+      <c r="F60" s="112"/>
+      <c r="G60" s="112"/>
+      <c r="H60" s="112"/>
+      <c r="I60" s="112"/>
+      <c r="J60" s="112"/>
+      <c r="K60" s="113"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -52009,21 +55147,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="113" t="s">
+      <c r="I1" s="114" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="113"/>
-      <c r="K1" s="113"/>
-      <c r="L1" s="113"/>
-      <c r="M1" s="113"/>
-      <c r="N1" s="113"/>
-      <c r="O1" s="113"/>
-      <c r="P1" s="113"/>
-      <c r="Q1" s="113"/>
-      <c r="R1" s="113"/>
-      <c r="S1" s="113"/>
-      <c r="T1" s="113"/>
-      <c r="U1" s="113"/>
+      <c r="J1" s="114"/>
+      <c r="K1" s="114"/>
+      <c r="L1" s="114"/>
+      <c r="M1" s="114"/>
+      <c r="N1" s="114"/>
+      <c r="O1" s="114"/>
+      <c r="P1" s="114"/>
+      <c r="Q1" s="114"/>
+      <c r="R1" s="114"/>
+      <c r="S1" s="114"/>
+      <c r="T1" s="114"/>
+      <c r="U1" s="114"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -52035,17 +55173,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="114" t="s">
+      <c r="C4" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="114"/>
-      <c r="E4" s="114"/>
-      <c r="F4" s="114"/>
-      <c r="G4" s="114"/>
-      <c r="H4" s="114"/>
-      <c r="I4" s="114"/>
-      <c r="J4" s="115"/>
-      <c r="K4" s="116"/>
+      <c r="D4" s="115"/>
+      <c r="E4" s="115"/>
+      <c r="F4" s="115"/>
+      <c r="G4" s="115"/>
+      <c r="H4" s="115"/>
+      <c r="I4" s="115"/>
+      <c r="J4" s="116"/>
+      <c r="K4" s="117"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -52065,13 +55203,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="117" t="s">
+      <c r="T4" s="118" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="123" t="s">
+      <c r="U4" s="124" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="106" t="s">
+      <c r="V4" s="107" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -52111,10 +55249,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="121" t="s">
+      <c r="J5" s="122" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="122"/>
+      <c r="K5" s="123"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -52122,9 +55260,9 @@
       <c r="Q5" s="98"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="118"/>
-      <c r="U5" s="124"/>
-      <c r="V5" s="107"/>
+      <c r="T5" s="119"/>
+      <c r="U5" s="125"/>
+      <c r="V5" s="108"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -54829,17 +57967,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="110" t="s">
+      <c r="C60" s="111" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="111"/>
-      <c r="E60" s="111"/>
-      <c r="F60" s="111"/>
-      <c r="G60" s="111"/>
-      <c r="H60" s="111"/>
-      <c r="I60" s="111"/>
-      <c r="J60" s="111"/>
-      <c r="K60" s="112"/>
+      <c r="D60" s="112"/>
+      <c r="E60" s="112"/>
+      <c r="F60" s="112"/>
+      <c r="G60" s="112"/>
+      <c r="H60" s="112"/>
+      <c r="I60" s="112"/>
+      <c r="J60" s="112"/>
+      <c r="K60" s="113"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -55148,21 +58286,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="113" t="s">
+      <c r="I1" s="114" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="113"/>
-      <c r="K1" s="113"/>
-      <c r="L1" s="113"/>
-      <c r="M1" s="113"/>
-      <c r="N1" s="113"/>
-      <c r="O1" s="113"/>
-      <c r="P1" s="113"/>
-      <c r="Q1" s="113"/>
-      <c r="R1" s="113"/>
-      <c r="S1" s="113"/>
-      <c r="T1" s="113"/>
-      <c r="U1" s="113"/>
+      <c r="J1" s="114"/>
+      <c r="K1" s="114"/>
+      <c r="L1" s="114"/>
+      <c r="M1" s="114"/>
+      <c r="N1" s="114"/>
+      <c r="O1" s="114"/>
+      <c r="P1" s="114"/>
+      <c r="Q1" s="114"/>
+      <c r="R1" s="114"/>
+      <c r="S1" s="114"/>
+      <c r="T1" s="114"/>
+      <c r="U1" s="114"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -55174,17 +58312,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="114" t="s">
+      <c r="C4" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="114"/>
-      <c r="E4" s="114"/>
-      <c r="F4" s="114"/>
-      <c r="G4" s="114"/>
-      <c r="H4" s="114"/>
-      <c r="I4" s="114"/>
-      <c r="J4" s="115"/>
-      <c r="K4" s="116"/>
+      <c r="D4" s="115"/>
+      <c r="E4" s="115"/>
+      <c r="F4" s="115"/>
+      <c r="G4" s="115"/>
+      <c r="H4" s="115"/>
+      <c r="I4" s="115"/>
+      <c r="J4" s="116"/>
+      <c r="K4" s="117"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -55204,13 +58342,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="117" t="s">
+      <c r="T4" s="118" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="123" t="s">
+      <c r="U4" s="124" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="106" t="s">
+      <c r="V4" s="107" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -55250,10 +58388,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="121" t="s">
+      <c r="J5" s="122" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="122"/>
+      <c r="K5" s="123"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -55261,9 +58399,9 @@
       <c r="Q5" s="98"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="118"/>
-      <c r="U5" s="124"/>
-      <c r="V5" s="107"/>
+      <c r="T5" s="119"/>
+      <c r="U5" s="125"/>
+      <c r="V5" s="108"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -57965,17 +61103,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="110" t="s">
+      <c r="C60" s="111" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="111"/>
-      <c r="E60" s="111"/>
-      <c r="F60" s="111"/>
-      <c r="G60" s="111"/>
-      <c r="H60" s="111"/>
-      <c r="I60" s="111"/>
-      <c r="J60" s="111"/>
-      <c r="K60" s="112"/>
+      <c r="D60" s="112"/>
+      <c r="E60" s="112"/>
+      <c r="F60" s="112"/>
+      <c r="G60" s="112"/>
+      <c r="H60" s="112"/>
+      <c r="I60" s="112"/>
+      <c r="J60" s="112"/>
+      <c r="K60" s="113"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -58284,21 +61422,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="113" t="s">
+      <c r="I1" s="114" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="113"/>
-      <c r="K1" s="113"/>
-      <c r="L1" s="113"/>
-      <c r="M1" s="113"/>
-      <c r="N1" s="113"/>
-      <c r="O1" s="113"/>
-      <c r="P1" s="113"/>
-      <c r="Q1" s="113"/>
-      <c r="R1" s="113"/>
-      <c r="S1" s="113"/>
-      <c r="T1" s="113"/>
-      <c r="U1" s="113"/>
+      <c r="J1" s="114"/>
+      <c r="K1" s="114"/>
+      <c r="L1" s="114"/>
+      <c r="M1" s="114"/>
+      <c r="N1" s="114"/>
+      <c r="O1" s="114"/>
+      <c r="P1" s="114"/>
+      <c r="Q1" s="114"/>
+      <c r="R1" s="114"/>
+      <c r="S1" s="114"/>
+      <c r="T1" s="114"/>
+      <c r="U1" s="114"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -58310,17 +61448,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="114" t="s">
+      <c r="C4" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="114"/>
-      <c r="E4" s="114"/>
-      <c r="F4" s="114"/>
-      <c r="G4" s="114"/>
-      <c r="H4" s="114"/>
-      <c r="I4" s="114"/>
-      <c r="J4" s="115"/>
-      <c r="K4" s="116"/>
+      <c r="D4" s="115"/>
+      <c r="E4" s="115"/>
+      <c r="F4" s="115"/>
+      <c r="G4" s="115"/>
+      <c r="H4" s="115"/>
+      <c r="I4" s="115"/>
+      <c r="J4" s="116"/>
+      <c r="K4" s="117"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -58340,13 +61478,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="117" t="s">
+      <c r="T4" s="118" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="123" t="s">
+      <c r="U4" s="124" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="106" t="s">
+      <c r="V4" s="107" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -58386,10 +61524,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="121" t="s">
+      <c r="J5" s="122" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="122"/>
+      <c r="K5" s="123"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -58397,9 +61535,9 @@
       <c r="Q5" s="98"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="118"/>
-      <c r="U5" s="124"/>
-      <c r="V5" s="107"/>
+      <c r="T5" s="119"/>
+      <c r="U5" s="125"/>
+      <c r="V5" s="108"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -61111,17 +64249,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="110" t="s">
+      <c r="C60" s="111" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="111"/>
-      <c r="E60" s="111"/>
-      <c r="F60" s="111"/>
-      <c r="G60" s="111"/>
-      <c r="H60" s="111"/>
-      <c r="I60" s="111"/>
-      <c r="J60" s="111"/>
-      <c r="K60" s="112"/>
+      <c r="D60" s="112"/>
+      <c r="E60" s="112"/>
+      <c r="F60" s="112"/>
+      <c r="G60" s="112"/>
+      <c r="H60" s="112"/>
+      <c r="I60" s="112"/>
+      <c r="J60" s="112"/>
+      <c r="K60" s="113"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>

--- a/GBDS AUGUST FILES 2026/INVENTORY COUNT SHEET - AUGUST 2026.xlsx
+++ b/GBDS AUGUST FILES 2026/INVENTORY COUNT SHEET - AUGUST 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS AUGUST FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BDE953D-2D23-4B89-91F2-7CCB7E5F6321}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{100533F5-82D9-433F-984E-6A9AD0DA9CC6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="10" activeTab="18" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="11" activeTab="20" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
   </bookViews>
   <sheets>
     <sheet name="SAMPLE" sheetId="32" r:id="rId1"/>
@@ -33,6 +33,7 @@
     <sheet name="08-24-2026" sheetId="85" r:id="rId18"/>
     <sheet name="08-25-2026" sheetId="86" r:id="rId19"/>
     <sheet name="08-26-2026" sheetId="87" r:id="rId20"/>
+    <sheet name="08-27-2026" sheetId="88" r:id="rId21"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'08-03-2026'!$A$1:$W$59</definedName>
@@ -54,6 +55,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="17">'08-24-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="18">'08-25-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="19">'08-26-2026'!$A$1:$W$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="20">'08-27-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">SAMPLE!$A$1:$W$85</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -72,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1680" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1764" uniqueCount="91">
   <si>
     <t>ROUTE 1</t>
   </si>
@@ -343,6 +345,9 @@
   </si>
   <si>
     <t>DATE: 08/26/2026</t>
+  </si>
+  <si>
+    <t>DATE: 08/27/2026</t>
   </si>
 </sst>
 </file>
@@ -1329,7 +1334,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="126">
+  <cellXfs count="127">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1615,6 +1620,9 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="63" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2061,21 +2069,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="114" t="s">
+      <c r="I1" s="115" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="114"/>
-      <c r="K1" s="114"/>
-      <c r="L1" s="114"/>
-      <c r="M1" s="114"/>
-      <c r="N1" s="114"/>
-      <c r="O1" s="114"/>
-      <c r="P1" s="114"/>
-      <c r="Q1" s="114"/>
-      <c r="R1" s="114"/>
-      <c r="S1" s="114"/>
-      <c r="T1" s="114"/>
-      <c r="U1" s="114"/>
+      <c r="J1" s="115"/>
+      <c r="K1" s="115"/>
+      <c r="L1" s="115"/>
+      <c r="M1" s="115"/>
+      <c r="N1" s="115"/>
+      <c r="O1" s="115"/>
+      <c r="P1" s="115"/>
+      <c r="Q1" s="115"/>
+      <c r="R1" s="115"/>
+      <c r="S1" s="115"/>
+      <c r="T1" s="115"/>
+      <c r="U1" s="115"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -2087,17 +2095,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="115" t="s">
+      <c r="C4" s="116" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="115"/>
-      <c r="E4" s="115"/>
-      <c r="F4" s="115"/>
-      <c r="G4" s="115"/>
-      <c r="H4" s="115"/>
-      <c r="I4" s="115"/>
-      <c r="J4" s="116"/>
-      <c r="K4" s="117"/>
+      <c r="D4" s="116"/>
+      <c r="E4" s="116"/>
+      <c r="F4" s="116"/>
+      <c r="G4" s="116"/>
+      <c r="H4" s="116"/>
+      <c r="I4" s="116"/>
+      <c r="J4" s="117"/>
+      <c r="K4" s="118"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -2117,13 +2125,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="118" t="s">
+      <c r="T4" s="119" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="120" t="s">
+      <c r="U4" s="121" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="107" t="s">
+      <c r="V4" s="108" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -2163,10 +2171,10 @@
       <c r="I5" s="93" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="109" t="s">
+      <c r="J5" s="110" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="110"/>
+      <c r="K5" s="111"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -2174,9 +2182,9 @@
       <c r="Q5" s="89"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="119"/>
-      <c r="U5" s="121"/>
-      <c r="V5" s="108"/>
+      <c r="T5" s="120"/>
+      <c r="U5" s="122"/>
+      <c r="V5" s="109"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -4707,17 +4715,17 @@
       <c r="B62" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C62" s="111" t="s">
+      <c r="C62" s="112" t="s">
         <v>41</v>
       </c>
-      <c r="D62" s="112"/>
-      <c r="E62" s="112"/>
-      <c r="F62" s="112"/>
-      <c r="G62" s="112"/>
-      <c r="H62" s="112"/>
-      <c r="I62" s="112"/>
-      <c r="J62" s="112"/>
-      <c r="K62" s="113"/>
+      <c r="D62" s="113"/>
+      <c r="E62" s="113"/>
+      <c r="F62" s="113"/>
+      <c r="G62" s="113"/>
+      <c r="H62" s="113"/>
+      <c r="I62" s="113"/>
+      <c r="J62" s="113"/>
+      <c r="K62" s="114"/>
       <c r="U62" s="24" t="s">
         <v>51</v>
       </c>
@@ -5026,21 +5034,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="114" t="s">
+      <c r="I1" s="115" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="114"/>
-      <c r="K1" s="114"/>
-      <c r="L1" s="114"/>
-      <c r="M1" s="114"/>
-      <c r="N1" s="114"/>
-      <c r="O1" s="114"/>
-      <c r="P1" s="114"/>
-      <c r="Q1" s="114"/>
-      <c r="R1" s="114"/>
-      <c r="S1" s="114"/>
-      <c r="T1" s="114"/>
-      <c r="U1" s="114"/>
+      <c r="J1" s="115"/>
+      <c r="K1" s="115"/>
+      <c r="L1" s="115"/>
+      <c r="M1" s="115"/>
+      <c r="N1" s="115"/>
+      <c r="O1" s="115"/>
+      <c r="P1" s="115"/>
+      <c r="Q1" s="115"/>
+      <c r="R1" s="115"/>
+      <c r="S1" s="115"/>
+      <c r="T1" s="115"/>
+      <c r="U1" s="115"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -5052,17 +5060,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="115" t="s">
+      <c r="C4" s="116" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="115"/>
-      <c r="E4" s="115"/>
-      <c r="F4" s="115"/>
-      <c r="G4" s="115"/>
-      <c r="H4" s="115"/>
-      <c r="I4" s="115"/>
-      <c r="J4" s="116"/>
-      <c r="K4" s="117"/>
+      <c r="D4" s="116"/>
+      <c r="E4" s="116"/>
+      <c r="F4" s="116"/>
+      <c r="G4" s="116"/>
+      <c r="H4" s="116"/>
+      <c r="I4" s="116"/>
+      <c r="J4" s="117"/>
+      <c r="K4" s="118"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -5082,13 +5090,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="118" t="s">
+      <c r="T4" s="119" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="124" t="s">
+      <c r="U4" s="125" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="107" t="s">
+      <c r="V4" s="108" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -5128,10 +5136,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="122" t="s">
+      <c r="J5" s="123" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="123"/>
+      <c r="K5" s="124"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -5139,9 +5147,9 @@
       <c r="Q5" s="99"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="119"/>
-      <c r="U5" s="125"/>
-      <c r="V5" s="108"/>
+      <c r="T5" s="120"/>
+      <c r="U5" s="126"/>
+      <c r="V5" s="109"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -7852,17 +7860,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="111" t="s">
+      <c r="C60" s="112" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="112"/>
-      <c r="E60" s="112"/>
-      <c r="F60" s="112"/>
-      <c r="G60" s="112"/>
-      <c r="H60" s="112"/>
-      <c r="I60" s="112"/>
-      <c r="J60" s="112"/>
-      <c r="K60" s="113"/>
+      <c r="D60" s="113"/>
+      <c r="E60" s="113"/>
+      <c r="F60" s="113"/>
+      <c r="G60" s="113"/>
+      <c r="H60" s="113"/>
+      <c r="I60" s="113"/>
+      <c r="J60" s="113"/>
+      <c r="K60" s="114"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -8171,21 +8179,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="114" t="s">
+      <c r="I1" s="115" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="114"/>
-      <c r="K1" s="114"/>
-      <c r="L1" s="114"/>
-      <c r="M1" s="114"/>
-      <c r="N1" s="114"/>
-      <c r="O1" s="114"/>
-      <c r="P1" s="114"/>
-      <c r="Q1" s="114"/>
-      <c r="R1" s="114"/>
-      <c r="S1" s="114"/>
-      <c r="T1" s="114"/>
-      <c r="U1" s="114"/>
+      <c r="J1" s="115"/>
+      <c r="K1" s="115"/>
+      <c r="L1" s="115"/>
+      <c r="M1" s="115"/>
+      <c r="N1" s="115"/>
+      <c r="O1" s="115"/>
+      <c r="P1" s="115"/>
+      <c r="Q1" s="115"/>
+      <c r="R1" s="115"/>
+      <c r="S1" s="115"/>
+      <c r="T1" s="115"/>
+      <c r="U1" s="115"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -8197,17 +8205,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="115" t="s">
+      <c r="C4" s="116" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="115"/>
-      <c r="E4" s="115"/>
-      <c r="F4" s="115"/>
-      <c r="G4" s="115"/>
-      <c r="H4" s="115"/>
-      <c r="I4" s="115"/>
-      <c r="J4" s="116"/>
-      <c r="K4" s="117"/>
+      <c r="D4" s="116"/>
+      <c r="E4" s="116"/>
+      <c r="F4" s="116"/>
+      <c r="G4" s="116"/>
+      <c r="H4" s="116"/>
+      <c r="I4" s="116"/>
+      <c r="J4" s="117"/>
+      <c r="K4" s="118"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -8227,13 +8235,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="118" t="s">
+      <c r="T4" s="119" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="124" t="s">
+      <c r="U4" s="125" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="107" t="s">
+      <c r="V4" s="108" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -8273,10 +8281,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="122" t="s">
+      <c r="J5" s="123" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="123"/>
+      <c r="K5" s="124"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -8284,9 +8292,9 @@
       <c r="Q5" s="99"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="119"/>
-      <c r="U5" s="125"/>
-      <c r="V5" s="108"/>
+      <c r="T5" s="120"/>
+      <c r="U5" s="126"/>
+      <c r="V5" s="109"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -10999,17 +11007,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="111" t="s">
+      <c r="C60" s="112" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="112"/>
-      <c r="E60" s="112"/>
-      <c r="F60" s="112"/>
-      <c r="G60" s="112"/>
-      <c r="H60" s="112"/>
-      <c r="I60" s="112"/>
-      <c r="J60" s="112"/>
-      <c r="K60" s="113"/>
+      <c r="D60" s="113"/>
+      <c r="E60" s="113"/>
+      <c r="F60" s="113"/>
+      <c r="G60" s="113"/>
+      <c r="H60" s="113"/>
+      <c r="I60" s="113"/>
+      <c r="J60" s="113"/>
+      <c r="K60" s="114"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -11318,21 +11326,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="114" t="s">
+      <c r="I1" s="115" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="114"/>
-      <c r="K1" s="114"/>
-      <c r="L1" s="114"/>
-      <c r="M1" s="114"/>
-      <c r="N1" s="114"/>
-      <c r="O1" s="114"/>
-      <c r="P1" s="114"/>
-      <c r="Q1" s="114"/>
-      <c r="R1" s="114"/>
-      <c r="S1" s="114"/>
-      <c r="T1" s="114"/>
-      <c r="U1" s="114"/>
+      <c r="J1" s="115"/>
+      <c r="K1" s="115"/>
+      <c r="L1" s="115"/>
+      <c r="M1" s="115"/>
+      <c r="N1" s="115"/>
+      <c r="O1" s="115"/>
+      <c r="P1" s="115"/>
+      <c r="Q1" s="115"/>
+      <c r="R1" s="115"/>
+      <c r="S1" s="115"/>
+      <c r="T1" s="115"/>
+      <c r="U1" s="115"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -11344,17 +11352,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="115" t="s">
+      <c r="C4" s="116" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="115"/>
-      <c r="E4" s="115"/>
-      <c r="F4" s="115"/>
-      <c r="G4" s="115"/>
-      <c r="H4" s="115"/>
-      <c r="I4" s="115"/>
-      <c r="J4" s="116"/>
-      <c r="K4" s="117"/>
+      <c r="D4" s="116"/>
+      <c r="E4" s="116"/>
+      <c r="F4" s="116"/>
+      <c r="G4" s="116"/>
+      <c r="H4" s="116"/>
+      <c r="I4" s="116"/>
+      <c r="J4" s="117"/>
+      <c r="K4" s="118"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -11374,13 +11382,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="118" t="s">
+      <c r="T4" s="119" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="124" t="s">
+      <c r="U4" s="125" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="107" t="s">
+      <c r="V4" s="108" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -11420,10 +11428,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="122" t="s">
+      <c r="J5" s="123" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="123"/>
+      <c r="K5" s="124"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -11431,9 +11439,9 @@
       <c r="Q5" s="99"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="119"/>
-      <c r="U5" s="125"/>
-      <c r="V5" s="108"/>
+      <c r="T5" s="120"/>
+      <c r="U5" s="126"/>
+      <c r="V5" s="109"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -14135,17 +14143,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="111" t="s">
+      <c r="C60" s="112" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="112"/>
-      <c r="E60" s="112"/>
-      <c r="F60" s="112"/>
-      <c r="G60" s="112"/>
-      <c r="H60" s="112"/>
-      <c r="I60" s="112"/>
-      <c r="J60" s="112"/>
-      <c r="K60" s="113"/>
+      <c r="D60" s="113"/>
+      <c r="E60" s="113"/>
+      <c r="F60" s="113"/>
+      <c r="G60" s="113"/>
+      <c r="H60" s="113"/>
+      <c r="I60" s="113"/>
+      <c r="J60" s="113"/>
+      <c r="K60" s="114"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -14454,21 +14462,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="114" t="s">
+      <c r="I1" s="115" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="114"/>
-      <c r="K1" s="114"/>
-      <c r="L1" s="114"/>
-      <c r="M1" s="114"/>
-      <c r="N1" s="114"/>
-      <c r="O1" s="114"/>
-      <c r="P1" s="114"/>
-      <c r="Q1" s="114"/>
-      <c r="R1" s="114"/>
-      <c r="S1" s="114"/>
-      <c r="T1" s="114"/>
-      <c r="U1" s="114"/>
+      <c r="J1" s="115"/>
+      <c r="K1" s="115"/>
+      <c r="L1" s="115"/>
+      <c r="M1" s="115"/>
+      <c r="N1" s="115"/>
+      <c r="O1" s="115"/>
+      <c r="P1" s="115"/>
+      <c r="Q1" s="115"/>
+      <c r="R1" s="115"/>
+      <c r="S1" s="115"/>
+      <c r="T1" s="115"/>
+      <c r="U1" s="115"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -14480,17 +14488,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="115" t="s">
+      <c r="C4" s="116" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="115"/>
-      <c r="E4" s="115"/>
-      <c r="F4" s="115"/>
-      <c r="G4" s="115"/>
-      <c r="H4" s="115"/>
-      <c r="I4" s="115"/>
-      <c r="J4" s="116"/>
-      <c r="K4" s="117"/>
+      <c r="D4" s="116"/>
+      <c r="E4" s="116"/>
+      <c r="F4" s="116"/>
+      <c r="G4" s="116"/>
+      <c r="H4" s="116"/>
+      <c r="I4" s="116"/>
+      <c r="J4" s="117"/>
+      <c r="K4" s="118"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -14510,13 +14518,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="118" t="s">
+      <c r="T4" s="119" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="124" t="s">
+      <c r="U4" s="125" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="107" t="s">
+      <c r="V4" s="108" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -14556,10 +14564,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="122" t="s">
+      <c r="J5" s="123" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="123"/>
+      <c r="K5" s="124"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -14567,9 +14575,9 @@
       <c r="Q5" s="99"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="119"/>
-      <c r="U5" s="125"/>
-      <c r="V5" s="108"/>
+      <c r="T5" s="120"/>
+      <c r="U5" s="126"/>
+      <c r="V5" s="109"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -17270,17 +17278,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="111" t="s">
+      <c r="C60" s="112" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="112"/>
-      <c r="E60" s="112"/>
-      <c r="F60" s="112"/>
-      <c r="G60" s="112"/>
-      <c r="H60" s="112"/>
-      <c r="I60" s="112"/>
-      <c r="J60" s="112"/>
-      <c r="K60" s="113"/>
+      <c r="D60" s="113"/>
+      <c r="E60" s="113"/>
+      <c r="F60" s="113"/>
+      <c r="G60" s="113"/>
+      <c r="H60" s="113"/>
+      <c r="I60" s="113"/>
+      <c r="J60" s="113"/>
+      <c r="K60" s="114"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -17589,21 +17597,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="114" t="s">
+      <c r="I1" s="115" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="114"/>
-      <c r="K1" s="114"/>
-      <c r="L1" s="114"/>
-      <c r="M1" s="114"/>
-      <c r="N1" s="114"/>
-      <c r="O1" s="114"/>
-      <c r="P1" s="114"/>
-      <c r="Q1" s="114"/>
-      <c r="R1" s="114"/>
-      <c r="S1" s="114"/>
-      <c r="T1" s="114"/>
-      <c r="U1" s="114"/>
+      <c r="J1" s="115"/>
+      <c r="K1" s="115"/>
+      <c r="L1" s="115"/>
+      <c r="M1" s="115"/>
+      <c r="N1" s="115"/>
+      <c r="O1" s="115"/>
+      <c r="P1" s="115"/>
+      <c r="Q1" s="115"/>
+      <c r="R1" s="115"/>
+      <c r="S1" s="115"/>
+      <c r="T1" s="115"/>
+      <c r="U1" s="115"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -17615,17 +17623,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="115" t="s">
+      <c r="C4" s="116" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="115"/>
-      <c r="E4" s="115"/>
-      <c r="F4" s="115"/>
-      <c r="G4" s="115"/>
-      <c r="H4" s="115"/>
-      <c r="I4" s="115"/>
-      <c r="J4" s="116"/>
-      <c r="K4" s="117"/>
+      <c r="D4" s="116"/>
+      <c r="E4" s="116"/>
+      <c r="F4" s="116"/>
+      <c r="G4" s="116"/>
+      <c r="H4" s="116"/>
+      <c r="I4" s="116"/>
+      <c r="J4" s="117"/>
+      <c r="K4" s="118"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -17645,13 +17653,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="118" t="s">
+      <c r="T4" s="119" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="124" t="s">
+      <c r="U4" s="125" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="107" t="s">
+      <c r="V4" s="108" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -17691,10 +17699,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="122" t="s">
+      <c r="J5" s="123" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="123"/>
+      <c r="K5" s="124"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -17702,9 +17710,9 @@
       <c r="Q5" s="100"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="119"/>
-      <c r="U5" s="125"/>
-      <c r="V5" s="108"/>
+      <c r="T5" s="120"/>
+      <c r="U5" s="126"/>
+      <c r="V5" s="109"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -20399,17 +20407,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="111" t="s">
+      <c r="C60" s="112" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="112"/>
-      <c r="E60" s="112"/>
-      <c r="F60" s="112"/>
-      <c r="G60" s="112"/>
-      <c r="H60" s="112"/>
-      <c r="I60" s="112"/>
-      <c r="J60" s="112"/>
-      <c r="K60" s="113"/>
+      <c r="D60" s="113"/>
+      <c r="E60" s="113"/>
+      <c r="F60" s="113"/>
+      <c r="G60" s="113"/>
+      <c r="H60" s="113"/>
+      <c r="I60" s="113"/>
+      <c r="J60" s="113"/>
+      <c r="K60" s="114"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -20718,21 +20726,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="114" t="s">
+      <c r="I1" s="115" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="114"/>
-      <c r="K1" s="114"/>
-      <c r="L1" s="114"/>
-      <c r="M1" s="114"/>
-      <c r="N1" s="114"/>
-      <c r="O1" s="114"/>
-      <c r="P1" s="114"/>
-      <c r="Q1" s="114"/>
-      <c r="R1" s="114"/>
-      <c r="S1" s="114"/>
-      <c r="T1" s="114"/>
-      <c r="U1" s="114"/>
+      <c r="J1" s="115"/>
+      <c r="K1" s="115"/>
+      <c r="L1" s="115"/>
+      <c r="M1" s="115"/>
+      <c r="N1" s="115"/>
+      <c r="O1" s="115"/>
+      <c r="P1" s="115"/>
+      <c r="Q1" s="115"/>
+      <c r="R1" s="115"/>
+      <c r="S1" s="115"/>
+      <c r="T1" s="115"/>
+      <c r="U1" s="115"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -20744,17 +20752,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="115" t="s">
+      <c r="C4" s="116" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="115"/>
-      <c r="E4" s="115"/>
-      <c r="F4" s="115"/>
-      <c r="G4" s="115"/>
-      <c r="H4" s="115"/>
-      <c r="I4" s="115"/>
-      <c r="J4" s="116"/>
-      <c r="K4" s="117"/>
+      <c r="D4" s="116"/>
+      <c r="E4" s="116"/>
+      <c r="F4" s="116"/>
+      <c r="G4" s="116"/>
+      <c r="H4" s="116"/>
+      <c r="I4" s="116"/>
+      <c r="J4" s="117"/>
+      <c r="K4" s="118"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -20774,13 +20782,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="118" t="s">
+      <c r="T4" s="119" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="124" t="s">
+      <c r="U4" s="125" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="107" t="s">
+      <c r="V4" s="108" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -20820,10 +20828,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="122" t="s">
+      <c r="J5" s="123" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="123"/>
+      <c r="K5" s="124"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -20831,9 +20839,9 @@
       <c r="Q5" s="101"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="119"/>
-      <c r="U5" s="125"/>
-      <c r="V5" s="108"/>
+      <c r="T5" s="120"/>
+      <c r="U5" s="126"/>
+      <c r="V5" s="109"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -23524,17 +23532,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="111" t="s">
+      <c r="C60" s="112" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="112"/>
-      <c r="E60" s="112"/>
-      <c r="F60" s="112"/>
-      <c r="G60" s="112"/>
-      <c r="H60" s="112"/>
-      <c r="I60" s="112"/>
-      <c r="J60" s="112"/>
-      <c r="K60" s="113"/>
+      <c r="D60" s="113"/>
+      <c r="E60" s="113"/>
+      <c r="F60" s="113"/>
+      <c r="G60" s="113"/>
+      <c r="H60" s="113"/>
+      <c r="I60" s="113"/>
+      <c r="J60" s="113"/>
+      <c r="K60" s="114"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -23843,21 +23851,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="114" t="s">
+      <c r="I1" s="115" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="114"/>
-      <c r="K1" s="114"/>
-      <c r="L1" s="114"/>
-      <c r="M1" s="114"/>
-      <c r="N1" s="114"/>
-      <c r="O1" s="114"/>
-      <c r="P1" s="114"/>
-      <c r="Q1" s="114"/>
-      <c r="R1" s="114"/>
-      <c r="S1" s="114"/>
-      <c r="T1" s="114"/>
-      <c r="U1" s="114"/>
+      <c r="J1" s="115"/>
+      <c r="K1" s="115"/>
+      <c r="L1" s="115"/>
+      <c r="M1" s="115"/>
+      <c r="N1" s="115"/>
+      <c r="O1" s="115"/>
+      <c r="P1" s="115"/>
+      <c r="Q1" s="115"/>
+      <c r="R1" s="115"/>
+      <c r="S1" s="115"/>
+      <c r="T1" s="115"/>
+      <c r="U1" s="115"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -23869,17 +23877,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="115" t="s">
+      <c r="C4" s="116" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="115"/>
-      <c r="E4" s="115"/>
-      <c r="F4" s="115"/>
-      <c r="G4" s="115"/>
-      <c r="H4" s="115"/>
-      <c r="I4" s="115"/>
-      <c r="J4" s="116"/>
-      <c r="K4" s="117"/>
+      <c r="D4" s="116"/>
+      <c r="E4" s="116"/>
+      <c r="F4" s="116"/>
+      <c r="G4" s="116"/>
+      <c r="H4" s="116"/>
+      <c r="I4" s="116"/>
+      <c r="J4" s="117"/>
+      <c r="K4" s="118"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -23899,13 +23907,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="118" t="s">
+      <c r="T4" s="119" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="124" t="s">
+      <c r="U4" s="125" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="107" t="s">
+      <c r="V4" s="108" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -23945,10 +23953,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="122" t="s">
+      <c r="J5" s="123" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="123"/>
+      <c r="K5" s="124"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -23956,9 +23964,9 @@
       <c r="Q5" s="102"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="119"/>
-      <c r="U5" s="125"/>
-      <c r="V5" s="108"/>
+      <c r="T5" s="120"/>
+      <c r="U5" s="126"/>
+      <c r="V5" s="109"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -26666,17 +26674,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="111" t="s">
+      <c r="C60" s="112" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="112"/>
-      <c r="E60" s="112"/>
-      <c r="F60" s="112"/>
-      <c r="G60" s="112"/>
-      <c r="H60" s="112"/>
-      <c r="I60" s="112"/>
-      <c r="J60" s="112"/>
-      <c r="K60" s="113"/>
+      <c r="D60" s="113"/>
+      <c r="E60" s="113"/>
+      <c r="F60" s="113"/>
+      <c r="G60" s="113"/>
+      <c r="H60" s="113"/>
+      <c r="I60" s="113"/>
+      <c r="J60" s="113"/>
+      <c r="K60" s="114"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -26985,21 +26993,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="114" t="s">
+      <c r="I1" s="115" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="114"/>
-      <c r="K1" s="114"/>
-      <c r="L1" s="114"/>
-      <c r="M1" s="114"/>
-      <c r="N1" s="114"/>
-      <c r="O1" s="114"/>
-      <c r="P1" s="114"/>
-      <c r="Q1" s="114"/>
-      <c r="R1" s="114"/>
-      <c r="S1" s="114"/>
-      <c r="T1" s="114"/>
-      <c r="U1" s="114"/>
+      <c r="J1" s="115"/>
+      <c r="K1" s="115"/>
+      <c r="L1" s="115"/>
+      <c r="M1" s="115"/>
+      <c r="N1" s="115"/>
+      <c r="O1" s="115"/>
+      <c r="P1" s="115"/>
+      <c r="Q1" s="115"/>
+      <c r="R1" s="115"/>
+      <c r="S1" s="115"/>
+      <c r="T1" s="115"/>
+      <c r="U1" s="115"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -27011,17 +27019,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="115" t="s">
+      <c r="C4" s="116" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="115"/>
-      <c r="E4" s="115"/>
-      <c r="F4" s="115"/>
-      <c r="G4" s="115"/>
-      <c r="H4" s="115"/>
-      <c r="I4" s="115"/>
-      <c r="J4" s="116"/>
-      <c r="K4" s="117"/>
+      <c r="D4" s="116"/>
+      <c r="E4" s="116"/>
+      <c r="F4" s="116"/>
+      <c r="G4" s="116"/>
+      <c r="H4" s="116"/>
+      <c r="I4" s="116"/>
+      <c r="J4" s="117"/>
+      <c r="K4" s="118"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -27041,13 +27049,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="118" t="s">
+      <c r="T4" s="119" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="124" t="s">
+      <c r="U4" s="125" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="107" t="s">
+      <c r="V4" s="108" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -27087,10 +27095,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="122" t="s">
+      <c r="J5" s="123" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="123"/>
+      <c r="K5" s="124"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -27098,9 +27106,9 @@
       <c r="Q5" s="103"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="119"/>
-      <c r="U5" s="125"/>
-      <c r="V5" s="108"/>
+      <c r="T5" s="120"/>
+      <c r="U5" s="126"/>
+      <c r="V5" s="109"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -29784,17 +29792,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="111" t="s">
+      <c r="C60" s="112" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="112"/>
-      <c r="E60" s="112"/>
-      <c r="F60" s="112"/>
-      <c r="G60" s="112"/>
-      <c r="H60" s="112"/>
-      <c r="I60" s="112"/>
-      <c r="J60" s="112"/>
-      <c r="K60" s="113"/>
+      <c r="D60" s="113"/>
+      <c r="E60" s="113"/>
+      <c r="F60" s="113"/>
+      <c r="G60" s="113"/>
+      <c r="H60" s="113"/>
+      <c r="I60" s="113"/>
+      <c r="J60" s="113"/>
+      <c r="K60" s="114"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -30103,21 +30111,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="114" t="s">
+      <c r="I1" s="115" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="114"/>
-      <c r="K1" s="114"/>
-      <c r="L1" s="114"/>
-      <c r="M1" s="114"/>
-      <c r="N1" s="114"/>
-      <c r="O1" s="114"/>
-      <c r="P1" s="114"/>
-      <c r="Q1" s="114"/>
-      <c r="R1" s="114"/>
-      <c r="S1" s="114"/>
-      <c r="T1" s="114"/>
-      <c r="U1" s="114"/>
+      <c r="J1" s="115"/>
+      <c r="K1" s="115"/>
+      <c r="L1" s="115"/>
+      <c r="M1" s="115"/>
+      <c r="N1" s="115"/>
+      <c r="O1" s="115"/>
+      <c r="P1" s="115"/>
+      <c r="Q1" s="115"/>
+      <c r="R1" s="115"/>
+      <c r="S1" s="115"/>
+      <c r="T1" s="115"/>
+      <c r="U1" s="115"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -30129,17 +30137,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="115" t="s">
+      <c r="C4" s="116" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="115"/>
-      <c r="E4" s="115"/>
-      <c r="F4" s="115"/>
-      <c r="G4" s="115"/>
-      <c r="H4" s="115"/>
-      <c r="I4" s="115"/>
-      <c r="J4" s="116"/>
-      <c r="K4" s="117"/>
+      <c r="D4" s="116"/>
+      <c r="E4" s="116"/>
+      <c r="F4" s="116"/>
+      <c r="G4" s="116"/>
+      <c r="H4" s="116"/>
+      <c r="I4" s="116"/>
+      <c r="J4" s="117"/>
+      <c r="K4" s="118"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -30159,13 +30167,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="118" t="s">
+      <c r="T4" s="119" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="124" t="s">
+      <c r="U4" s="125" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="107" t="s">
+      <c r="V4" s="108" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -30205,10 +30213,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="122" t="s">
+      <c r="J5" s="123" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="123"/>
+      <c r="K5" s="124"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -30216,9 +30224,9 @@
       <c r="Q5" s="104"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="119"/>
-      <c r="U5" s="125"/>
-      <c r="V5" s="108"/>
+      <c r="T5" s="120"/>
+      <c r="U5" s="126"/>
+      <c r="V5" s="109"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -32894,17 +32902,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="111" t="s">
+      <c r="C60" s="112" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="112"/>
-      <c r="E60" s="112"/>
-      <c r="F60" s="112"/>
-      <c r="G60" s="112"/>
-      <c r="H60" s="112"/>
-      <c r="I60" s="112"/>
-      <c r="J60" s="112"/>
-      <c r="K60" s="113"/>
+      <c r="D60" s="113"/>
+      <c r="E60" s="113"/>
+      <c r="F60" s="113"/>
+      <c r="G60" s="113"/>
+      <c r="H60" s="113"/>
+      <c r="I60" s="113"/>
+      <c r="J60" s="113"/>
+      <c r="K60" s="114"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -33213,21 +33221,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="114" t="s">
+      <c r="I1" s="115" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="114"/>
-      <c r="K1" s="114"/>
-      <c r="L1" s="114"/>
-      <c r="M1" s="114"/>
-      <c r="N1" s="114"/>
-      <c r="O1" s="114"/>
-      <c r="P1" s="114"/>
-      <c r="Q1" s="114"/>
-      <c r="R1" s="114"/>
-      <c r="S1" s="114"/>
-      <c r="T1" s="114"/>
-      <c r="U1" s="114"/>
+      <c r="J1" s="115"/>
+      <c r="K1" s="115"/>
+      <c r="L1" s="115"/>
+      <c r="M1" s="115"/>
+      <c r="N1" s="115"/>
+      <c r="O1" s="115"/>
+      <c r="P1" s="115"/>
+      <c r="Q1" s="115"/>
+      <c r="R1" s="115"/>
+      <c r="S1" s="115"/>
+      <c r="T1" s="115"/>
+      <c r="U1" s="115"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -33239,17 +33247,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="115" t="s">
+      <c r="C4" s="116" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="115"/>
-      <c r="E4" s="115"/>
-      <c r="F4" s="115"/>
-      <c r="G4" s="115"/>
-      <c r="H4" s="115"/>
-      <c r="I4" s="115"/>
-      <c r="J4" s="116"/>
-      <c r="K4" s="117"/>
+      <c r="D4" s="116"/>
+      <c r="E4" s="116"/>
+      <c r="F4" s="116"/>
+      <c r="G4" s="116"/>
+      <c r="H4" s="116"/>
+      <c r="I4" s="116"/>
+      <c r="J4" s="117"/>
+      <c r="K4" s="118"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -33269,13 +33277,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="118" t="s">
+      <c r="T4" s="119" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="124" t="s">
+      <c r="U4" s="125" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="107" t="s">
+      <c r="V4" s="108" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -33315,10 +33323,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="122" t="s">
+      <c r="J5" s="123" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="123"/>
+      <c r="K5" s="124"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -33326,9 +33334,9 @@
       <c r="Q5" s="105"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="119"/>
-      <c r="U5" s="125"/>
-      <c r="V5" s="108"/>
+      <c r="T5" s="120"/>
+      <c r="U5" s="126"/>
+      <c r="V5" s="109"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -36013,17 +36021,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="111" t="s">
+      <c r="C60" s="112" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="112"/>
-      <c r="E60" s="112"/>
-      <c r="F60" s="112"/>
-      <c r="G60" s="112"/>
-      <c r="H60" s="112"/>
-      <c r="I60" s="112"/>
-      <c r="J60" s="112"/>
-      <c r="K60" s="113"/>
+      <c r="D60" s="113"/>
+      <c r="E60" s="113"/>
+      <c r="F60" s="113"/>
+      <c r="G60" s="113"/>
+      <c r="H60" s="113"/>
+      <c r="I60" s="113"/>
+      <c r="J60" s="113"/>
+      <c r="K60" s="114"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -36332,21 +36340,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="114" t="s">
+      <c r="I1" s="115" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="114"/>
-      <c r="K1" s="114"/>
-      <c r="L1" s="114"/>
-      <c r="M1" s="114"/>
-      <c r="N1" s="114"/>
-      <c r="O1" s="114"/>
-      <c r="P1" s="114"/>
-      <c r="Q1" s="114"/>
-      <c r="R1" s="114"/>
-      <c r="S1" s="114"/>
-      <c r="T1" s="114"/>
-      <c r="U1" s="114"/>
+      <c r="J1" s="115"/>
+      <c r="K1" s="115"/>
+      <c r="L1" s="115"/>
+      <c r="M1" s="115"/>
+      <c r="N1" s="115"/>
+      <c r="O1" s="115"/>
+      <c r="P1" s="115"/>
+      <c r="Q1" s="115"/>
+      <c r="R1" s="115"/>
+      <c r="S1" s="115"/>
+      <c r="T1" s="115"/>
+      <c r="U1" s="115"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -36358,17 +36366,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="115" t="s">
+      <c r="C4" s="116" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="115"/>
-      <c r="E4" s="115"/>
-      <c r="F4" s="115"/>
-      <c r="G4" s="115"/>
-      <c r="H4" s="115"/>
-      <c r="I4" s="115"/>
-      <c r="J4" s="116"/>
-      <c r="K4" s="117"/>
+      <c r="D4" s="116"/>
+      <c r="E4" s="116"/>
+      <c r="F4" s="116"/>
+      <c r="G4" s="116"/>
+      <c r="H4" s="116"/>
+      <c r="I4" s="116"/>
+      <c r="J4" s="117"/>
+      <c r="K4" s="118"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -36388,13 +36396,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="118" t="s">
+      <c r="T4" s="119" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="124" t="s">
+      <c r="U4" s="125" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="107" t="s">
+      <c r="V4" s="108" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -36434,10 +36442,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="122" t="s">
+      <c r="J5" s="123" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="123"/>
+      <c r="K5" s="124"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -36445,9 +36453,9 @@
       <c r="Q5" s="96"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="119"/>
-      <c r="U5" s="125"/>
-      <c r="V5" s="108"/>
+      <c r="T5" s="120"/>
+      <c r="U5" s="126"/>
+      <c r="V5" s="109"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -39157,17 +39165,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="111" t="s">
+      <c r="C60" s="112" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="112"/>
-      <c r="E60" s="112"/>
-      <c r="F60" s="112"/>
-      <c r="G60" s="112"/>
-      <c r="H60" s="112"/>
-      <c r="I60" s="112"/>
-      <c r="J60" s="112"/>
-      <c r="K60" s="113"/>
+      <c r="D60" s="113"/>
+      <c r="E60" s="113"/>
+      <c r="F60" s="113"/>
+      <c r="G60" s="113"/>
+      <c r="H60" s="113"/>
+      <c r="I60" s="113"/>
+      <c r="J60" s="113"/>
+      <c r="K60" s="114"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -39476,21 +39484,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="114" t="s">
+      <c r="I1" s="115" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="114"/>
-      <c r="K1" s="114"/>
-      <c r="L1" s="114"/>
-      <c r="M1" s="114"/>
-      <c r="N1" s="114"/>
-      <c r="O1" s="114"/>
-      <c r="P1" s="114"/>
-      <c r="Q1" s="114"/>
-      <c r="R1" s="114"/>
-      <c r="S1" s="114"/>
-      <c r="T1" s="114"/>
-      <c r="U1" s="114"/>
+      <c r="J1" s="115"/>
+      <c r="K1" s="115"/>
+      <c r="L1" s="115"/>
+      <c r="M1" s="115"/>
+      <c r="N1" s="115"/>
+      <c r="O1" s="115"/>
+      <c r="P1" s="115"/>
+      <c r="Q1" s="115"/>
+      <c r="R1" s="115"/>
+      <c r="S1" s="115"/>
+      <c r="T1" s="115"/>
+      <c r="U1" s="115"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -39502,17 +39510,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="115" t="s">
+      <c r="C4" s="116" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="115"/>
-      <c r="E4" s="115"/>
-      <c r="F4" s="115"/>
-      <c r="G4" s="115"/>
-      <c r="H4" s="115"/>
-      <c r="I4" s="115"/>
-      <c r="J4" s="116"/>
-      <c r="K4" s="117"/>
+      <c r="D4" s="116"/>
+      <c r="E4" s="116"/>
+      <c r="F4" s="116"/>
+      <c r="G4" s="116"/>
+      <c r="H4" s="116"/>
+      <c r="I4" s="116"/>
+      <c r="J4" s="117"/>
+      <c r="K4" s="118"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -39532,13 +39540,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="118" t="s">
+      <c r="T4" s="119" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="124" t="s">
+      <c r="U4" s="125" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="107" t="s">
+      <c r="V4" s="108" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -39578,10 +39586,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="122" t="s">
+      <c r="J5" s="123" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="123"/>
+      <c r="K5" s="124"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -39589,9 +39597,9 @@
       <c r="Q5" s="106"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="119"/>
-      <c r="U5" s="125"/>
-      <c r="V5" s="108"/>
+      <c r="T5" s="120"/>
+      <c r="U5" s="126"/>
+      <c r="V5" s="109"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -42287,17 +42295,3145 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="111" t="s">
+      <c r="C60" s="112" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="112"/>
-      <c r="E60" s="112"/>
-      <c r="F60" s="112"/>
-      <c r="G60" s="112"/>
-      <c r="H60" s="112"/>
-      <c r="I60" s="112"/>
-      <c r="J60" s="112"/>
-      <c r="K60" s="113"/>
+      <c r="D60" s="113"/>
+      <c r="E60" s="113"/>
+      <c r="F60" s="113"/>
+      <c r="G60" s="113"/>
+      <c r="H60" s="113"/>
+      <c r="I60" s="113"/>
+      <c r="J60" s="113"/>
+      <c r="K60" s="114"/>
+      <c r="U60" s="24" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B61" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="C61" s="19"/>
+      <c r="D61" s="19"/>
+      <c r="E61" s="19"/>
+      <c r="F61" s="19"/>
+      <c r="G61" s="19"/>
+      <c r="H61" s="19"/>
+      <c r="I61" s="19"/>
+      <c r="J61" s="45"/>
+      <c r="K61" s="20"/>
+      <c r="U61" s="7"/>
+    </row>
+    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B62" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+      <c r="J62" s="44"/>
+      <c r="K62" s="21"/>
+      <c r="U62" s="3"/>
+    </row>
+    <row r="63" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B63" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C63" s="22"/>
+      <c r="D63" s="22"/>
+      <c r="E63" s="22"/>
+      <c r="F63" s="22"/>
+      <c r="G63" s="22"/>
+      <c r="H63" s="22"/>
+      <c r="I63" s="22"/>
+      <c r="J63" s="46"/>
+      <c r="K63" s="23"/>
+      <c r="U63" s="8"/>
+    </row>
+    <row r="64" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B65" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="C65" s="19"/>
+      <c r="D65" s="19"/>
+      <c r="E65" s="19"/>
+      <c r="F65" s="19"/>
+      <c r="G65" s="19"/>
+      <c r="H65" s="19"/>
+      <c r="I65" s="19"/>
+      <c r="J65" s="45"/>
+      <c r="K65" s="20"/>
+      <c r="U65" s="7"/>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B66" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C66" s="1"/>
+      <c r="D66" s="1"/>
+      <c r="E66" s="1"/>
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="J66" s="44"/>
+      <c r="K66" s="21"/>
+      <c r="U66" s="3"/>
+    </row>
+    <row r="67" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B67" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C67" s="22"/>
+      <c r="D67" s="22"/>
+      <c r="E67" s="22"/>
+      <c r="F67" s="22"/>
+      <c r="G67" s="22"/>
+      <c r="H67" s="22"/>
+      <c r="I67" s="22"/>
+      <c r="J67" s="46"/>
+      <c r="K67" s="23"/>
+      <c r="U67" s="8"/>
+    </row>
+    <row r="68" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B69" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="C69" s="19"/>
+      <c r="D69" s="19"/>
+      <c r="E69" s="19"/>
+      <c r="F69" s="19"/>
+      <c r="G69" s="19"/>
+      <c r="H69" s="19"/>
+      <c r="I69" s="19"/>
+      <c r="J69" s="45"/>
+      <c r="K69" s="20"/>
+      <c r="U69" s="7"/>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B70" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="J70" s="44"/>
+      <c r="K70" s="21"/>
+      <c r="U70" s="3"/>
+    </row>
+    <row r="71" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B71" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C71" s="22"/>
+      <c r="D71" s="22"/>
+      <c r="E71" s="22"/>
+      <c r="F71" s="22"/>
+      <c r="G71" s="22"/>
+      <c r="H71" s="22"/>
+      <c r="I71" s="22"/>
+      <c r="J71" s="46"/>
+      <c r="K71" s="23"/>
+      <c r="U71" s="8"/>
+    </row>
+    <row r="72" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B73" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="C73" s="19"/>
+      <c r="D73" s="19"/>
+      <c r="E73" s="19"/>
+      <c r="F73" s="19"/>
+      <c r="G73" s="19"/>
+      <c r="H73" s="19"/>
+      <c r="I73" s="19"/>
+      <c r="J73" s="45"/>
+      <c r="K73" s="20"/>
+      <c r="U73" s="7"/>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B74" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C74" s="1"/>
+      <c r="D74" s="1"/>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1"/>
+      <c r="J74" s="44"/>
+      <c r="K74" s="21"/>
+      <c r="U74" s="3"/>
+    </row>
+    <row r="75" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B75" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C75" s="22"/>
+      <c r="D75" s="22"/>
+      <c r="E75" s="22"/>
+      <c r="F75" s="22"/>
+      <c r="G75" s="22"/>
+      <c r="H75" s="22"/>
+      <c r="I75" s="22"/>
+      <c r="J75" s="46"/>
+      <c r="K75" s="23"/>
+      <c r="U75" s="8"/>
+    </row>
+    <row r="76" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B77" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="C77" s="19"/>
+      <c r="D77" s="19"/>
+      <c r="E77" s="19"/>
+      <c r="F77" s="19"/>
+      <c r="G77" s="19"/>
+      <c r="H77" s="19"/>
+      <c r="I77" s="19"/>
+      <c r="J77" s="45"/>
+      <c r="K77" s="20"/>
+      <c r="U77" s="7"/>
+    </row>
+    <row r="78" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B78" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C78" s="1"/>
+      <c r="D78" s="1"/>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+      <c r="J78" s="44"/>
+      <c r="K78" s="21"/>
+      <c r="U78" s="3"/>
+    </row>
+    <row r="79" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B79" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C79" s="22"/>
+      <c r="D79" s="22"/>
+      <c r="E79" s="22"/>
+      <c r="F79" s="22"/>
+      <c r="G79" s="22"/>
+      <c r="H79" s="22"/>
+      <c r="I79" s="22"/>
+      <c r="J79" s="46"/>
+      <c r="K79" s="23"/>
+      <c r="U79" s="8"/>
+    </row>
+    <row r="80" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="81" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B81" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="C81" s="17"/>
+      <c r="D81" s="17"/>
+      <c r="E81" s="17"/>
+      <c r="F81" s="17"/>
+      <c r="G81" s="17"/>
+      <c r="H81" s="17"/>
+      <c r="I81" s="17"/>
+      <c r="J81" s="47"/>
+      <c r="K81" s="18"/>
+      <c r="U81" s="16"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="C60:K60"/>
+    <mergeCell ref="I1:U1"/>
+    <mergeCell ref="C4:K4"/>
+    <mergeCell ref="T4:T5"/>
+    <mergeCell ref="U4:U5"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
+  <pageSetup paperSize="14" scale="70" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="24" max="80" man="1"/>
+  </colBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A17CFFCE-B26C-46FA-A032-A5304F4677C5}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BB81"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="28" customWidth="1"/>
+    <col min="3" max="6" width="10" style="9" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" style="9" customWidth="1"/>
+    <col min="8" max="8" width="7.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.85546875" style="9" customWidth="1"/>
+    <col min="11" max="11" width="7.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.42578125" style="9" customWidth="1"/>
+    <col min="13" max="13" width="10" style="9" customWidth="1"/>
+    <col min="14" max="14" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" style="9" customWidth="1"/>
+    <col min="16" max="16" width="5.5703125" style="9" customWidth="1"/>
+    <col min="17" max="17" width="10" style="9" customWidth="1"/>
+    <col min="18" max="18" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="1.42578125" style="9" customWidth="1"/>
+    <col min="20" max="20" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="9" customWidth="1"/>
+    <col min="22" max="22" width="19.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="23" max="49" width="7.28515625" style="9" customWidth="1"/>
+    <col min="50" max="50" width="1.5703125" style="9" customWidth="1"/>
+    <col min="51" max="51" width="9.42578125" style="9" customWidth="1"/>
+    <col min="52" max="52" width="1.28515625" style="9" customWidth="1"/>
+    <col min="53" max="53" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="10.28515625" style="9" bestFit="1" customWidth="1"/>
+    <col min="55" max="16384" width="9.140625" style="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="115" t="s">
+        <v>43</v>
+      </c>
+      <c r="J1" s="115"/>
+      <c r="K1" s="115"/>
+      <c r="L1" s="115"/>
+      <c r="M1" s="115"/>
+      <c r="N1" s="115"/>
+      <c r="O1" s="115"/>
+      <c r="P1" s="115"/>
+      <c r="Q1" s="115"/>
+      <c r="R1" s="115"/>
+      <c r="S1" s="115"/>
+      <c r="T1" s="115"/>
+      <c r="U1" s="115"/>
+    </row>
+    <row r="2" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="B2" s="28" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B4" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="116" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="116"/>
+      <c r="E4" s="116"/>
+      <c r="F4" s="116"/>
+      <c r="G4" s="116"/>
+      <c r="H4" s="116"/>
+      <c r="I4" s="116"/>
+      <c r="J4" s="117"/>
+      <c r="K4" s="118"/>
+      <c r="M4" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="N4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="O4" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="P4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q4" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="R4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="S4" s="9"/>
+      <c r="T4" s="119" t="s">
+        <v>68</v>
+      </c>
+      <c r="U4" s="125" t="s">
+        <v>67</v>
+      </c>
+      <c r="V4" s="108" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF4" s="11"/>
+      <c r="AG4" s="11"/>
+      <c r="AH4" s="11"/>
+      <c r="AI4" s="11"/>
+      <c r="AJ4" s="11"/>
+      <c r="AK4" s="11"/>
+      <c r="AL4" s="11"/>
+      <c r="AM4" s="11"/>
+      <c r="AN4" s="11"/>
+      <c r="AO4" s="11"/>
+      <c r="AP4" s="11"/>
+      <c r="AQ4" s="11"/>
+      <c r="AR4" s="11"/>
+      <c r="AS4" s="11"/>
+      <c r="AT4" s="11"/>
+      <c r="AU4" s="11"/>
+      <c r="AV4" s="11"/>
+      <c r="AW4" s="11"/>
+      <c r="AX4" s="11"/>
+      <c r="AY4" s="11"/>
+      <c r="AZ4" s="11"/>
+      <c r="BA4" s="11"/>
+      <c r="BB4" s="11"/>
+    </row>
+    <row r="5" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="37"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40" t="s">
+        <v>64</v>
+      </c>
+      <c r="I5" s="40" t="s">
+        <v>60</v>
+      </c>
+      <c r="J5" s="123" t="s">
+        <v>65</v>
+      </c>
+      <c r="K5" s="124"/>
+      <c r="M5" s="37"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="40"/>
+      <c r="P5" s="107"/>
+      <c r="Q5" s="107"/>
+      <c r="R5" s="38"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="120"/>
+      <c r="U5" s="126"/>
+      <c r="V5" s="109"/>
+      <c r="AF5" s="11"/>
+      <c r="AG5" s="11"/>
+      <c r="AH5" s="11"/>
+      <c r="AI5" s="11"/>
+      <c r="AJ5" s="11"/>
+      <c r="AK5" s="11"/>
+      <c r="AL5" s="11"/>
+      <c r="AM5" s="11"/>
+      <c r="AN5" s="11"/>
+      <c r="AO5" s="11"/>
+      <c r="AP5" s="11"/>
+      <c r="AQ5" s="11"/>
+      <c r="AR5" s="11"/>
+      <c r="AS5" s="11"/>
+      <c r="AT5" s="11"/>
+      <c r="AU5" s="11"/>
+      <c r="AV5" s="11"/>
+      <c r="AW5" s="11"/>
+      <c r="AX5" s="11"/>
+      <c r="AY5" s="11"/>
+      <c r="AZ5" s="11"/>
+      <c r="BA5" s="11"/>
+      <c r="BB5" s="11"/>
+    </row>
+    <row r="6" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="37"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="107"/>
+      <c r="K6" s="38"/>
+      <c r="M6" s="37"/>
+      <c r="N6" s="49"/>
+      <c r="O6" s="40"/>
+      <c r="P6" s="107"/>
+      <c r="Q6" s="107"/>
+      <c r="R6" s="38"/>
+      <c r="S6" s="9"/>
+      <c r="T6" s="39"/>
+      <c r="U6" s="39"/>
+      <c r="V6" s="39"/>
+      <c r="AF6" s="11"/>
+      <c r="AG6" s="11"/>
+      <c r="AH6" s="11"/>
+      <c r="AI6" s="11"/>
+      <c r="AJ6" s="11"/>
+      <c r="AK6" s="11"/>
+      <c r="AL6" s="11"/>
+      <c r="AM6" s="11"/>
+      <c r="AN6" s="11"/>
+      <c r="AO6" s="11"/>
+      <c r="AP6" s="11"/>
+      <c r="AQ6" s="11"/>
+      <c r="AR6" s="11"/>
+      <c r="AS6" s="11"/>
+      <c r="AT6" s="11"/>
+      <c r="AU6" s="11"/>
+      <c r="AV6" s="11"/>
+      <c r="AW6" s="11"/>
+      <c r="AX6" s="11"/>
+      <c r="AY6" s="11"/>
+      <c r="AZ6" s="11"/>
+      <c r="BA6" s="11"/>
+      <c r="BB6" s="11"/>
+    </row>
+    <row r="7" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A7" s="27">
+        <v>1</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="52">
+        <v>29</v>
+      </c>
+      <c r="D7" s="52"/>
+      <c r="E7" s="52"/>
+      <c r="F7" s="52"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="52"/>
+      <c r="I7" s="52">
+        <v>3</v>
+      </c>
+      <c r="J7" s="53"/>
+      <c r="K7" s="54">
+        <v>6</v>
+      </c>
+      <c r="L7" s="55"/>
+      <c r="M7" s="56"/>
+      <c r="N7" s="57"/>
+      <c r="O7" s="52">
+        <v>1</v>
+      </c>
+      <c r="P7" s="53"/>
+      <c r="Q7" s="53">
+        <v>1</v>
+      </c>
+      <c r="R7" s="54"/>
+      <c r="S7" s="55"/>
+      <c r="T7" s="58">
+        <f>H7+I7+J7+K7+N7+P7+R7</f>
+        <v>9</v>
+      </c>
+      <c r="U7" s="58">
+        <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
+        <v>753</v>
+      </c>
+      <c r="V7" s="58">
+        <f>U7/24</f>
+        <v>31.375</v>
+      </c>
+      <c r="W7" s="50"/>
+      <c r="AF7" s="12"/>
+      <c r="AG7" s="12"/>
+      <c r="AH7" s="12"/>
+      <c r="AI7" s="12"/>
+      <c r="AJ7" s="12"/>
+      <c r="AK7" s="12"/>
+      <c r="AL7" s="12"/>
+      <c r="AM7" s="12"/>
+      <c r="AN7" s="12"/>
+      <c r="AO7" s="12"/>
+      <c r="AP7" s="12"/>
+      <c r="AQ7" s="12"/>
+      <c r="AR7" s="12"/>
+      <c r="AS7" s="12"/>
+      <c r="AT7" s="12"/>
+      <c r="AU7" s="12"/>
+      <c r="AV7" s="12"/>
+      <c r="AW7" s="12"/>
+      <c r="AX7" s="12"/>
+      <c r="AY7" s="12"/>
+      <c r="AZ7" s="12"/>
+      <c r="BA7" s="12"/>
+      <c r="BB7" s="12"/>
+    </row>
+    <row r="8" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="27">
+        <f>A7+1</f>
+        <v>2</v>
+      </c>
+      <c r="B8" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="59">
+        <f>36+30</f>
+        <v>66</v>
+      </c>
+      <c r="D8" s="59"/>
+      <c r="E8" s="59"/>
+      <c r="F8" s="59"/>
+      <c r="G8" s="59"/>
+      <c r="H8" s="59"/>
+      <c r="I8" s="59"/>
+      <c r="J8" s="60"/>
+      <c r="K8" s="61"/>
+      <c r="L8" s="62"/>
+      <c r="M8" s="63">
+        <v>1</v>
+      </c>
+      <c r="N8" s="64"/>
+      <c r="O8" s="65">
+        <v>1</v>
+      </c>
+      <c r="P8" s="66">
+        <v>12</v>
+      </c>
+      <c r="Q8" s="66">
+        <v>1</v>
+      </c>
+      <c r="R8" s="67"/>
+      <c r="S8" s="62"/>
+      <c r="T8" s="68">
+        <f t="shared" ref="T8:T41" si="0">H8+I8+J8+K8+N8+P8+R8</f>
+        <v>12</v>
+      </c>
+      <c r="U8" s="69">
+        <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
+        <v>1668</v>
+      </c>
+      <c r="V8" s="69">
+        <f>U8/24</f>
+        <v>69.5</v>
+      </c>
+      <c r="W8" s="50"/>
+      <c r="AF8" s="12"/>
+      <c r="AG8" s="12"/>
+      <c r="AH8" s="12"/>
+      <c r="AI8" s="12"/>
+      <c r="AJ8" s="12"/>
+      <c r="AK8" s="12"/>
+      <c r="AL8" s="12"/>
+      <c r="AM8" s="12"/>
+      <c r="AN8" s="12"/>
+      <c r="AO8" s="12"/>
+      <c r="AP8" s="12"/>
+      <c r="AQ8" s="12"/>
+      <c r="AR8" s="12"/>
+      <c r="AS8" s="12"/>
+      <c r="AT8" s="12"/>
+      <c r="AU8" s="12"/>
+      <c r="AV8" s="12"/>
+      <c r="AW8" s="12"/>
+      <c r="AX8" s="12"/>
+      <c r="AY8" s="12"/>
+      <c r="AZ8" s="12"/>
+      <c r="BA8" s="12"/>
+      <c r="BB8" s="12"/>
+    </row>
+    <row r="9" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A9" s="27">
+        <f t="shared" ref="A9:A57" si="1">A8+1</f>
+        <v>3</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="70">
+        <f>23+30</f>
+        <v>53</v>
+      </c>
+      <c r="D9" s="70"/>
+      <c r="E9" s="70"/>
+      <c r="F9" s="70"/>
+      <c r="G9" s="70"/>
+      <c r="H9" s="70"/>
+      <c r="I9" s="70"/>
+      <c r="J9" s="71"/>
+      <c r="K9" s="72"/>
+      <c r="L9" s="55"/>
+      <c r="M9" s="73"/>
+      <c r="N9" s="74"/>
+      <c r="O9" s="70"/>
+      <c r="P9" s="71"/>
+      <c r="Q9" s="71"/>
+      <c r="R9" s="72"/>
+      <c r="S9" s="55"/>
+      <c r="T9" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U9" s="76">
+        <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
+        <v>1272</v>
+      </c>
+      <c r="V9" s="76">
+        <f t="shared" ref="V9:V11" si="3">U9/24</f>
+        <v>53</v>
+      </c>
+      <c r="W9" s="50"/>
+      <c r="AF9" s="12"/>
+      <c r="AG9" s="12"/>
+      <c r="AH9" s="12"/>
+      <c r="AI9" s="12"/>
+      <c r="AJ9" s="12"/>
+      <c r="AK9" s="12"/>
+      <c r="AL9" s="12"/>
+      <c r="AM9" s="12"/>
+      <c r="AN9" s="12"/>
+      <c r="AO9" s="12"/>
+      <c r="AP9" s="12"/>
+      <c r="AQ9" s="12"/>
+      <c r="AR9" s="12"/>
+      <c r="AS9" s="12"/>
+      <c r="AT9" s="12"/>
+      <c r="AU9" s="12"/>
+      <c r="AV9" s="12"/>
+      <c r="AW9" s="12"/>
+      <c r="AX9" s="12"/>
+      <c r="AY9" s="12"/>
+      <c r="AZ9" s="12"/>
+      <c r="BA9" s="12"/>
+      <c r="BB9" s="12"/>
+    </row>
+    <row r="10" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A10" s="27">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="70">
+        <v>9</v>
+      </c>
+      <c r="D10" s="70"/>
+      <c r="E10" s="70"/>
+      <c r="F10" s="70"/>
+      <c r="G10" s="70"/>
+      <c r="H10" s="70"/>
+      <c r="I10" s="70"/>
+      <c r="J10" s="71"/>
+      <c r="K10" s="72"/>
+      <c r="L10" s="55"/>
+      <c r="M10" s="73"/>
+      <c r="N10" s="74"/>
+      <c r="O10" s="70">
+        <v>1</v>
+      </c>
+      <c r="P10" s="71"/>
+      <c r="Q10" s="71"/>
+      <c r="R10" s="72"/>
+      <c r="S10" s="55"/>
+      <c r="T10" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U10" s="58">
+        <f t="shared" si="2"/>
+        <v>240</v>
+      </c>
+      <c r="V10" s="58">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="W10" s="50"/>
+      <c r="AF10" s="12"/>
+      <c r="AG10" s="12"/>
+      <c r="AH10" s="12"/>
+      <c r="AI10" s="12"/>
+      <c r="AJ10" s="12"/>
+      <c r="AK10" s="12"/>
+      <c r="AL10" s="12"/>
+      <c r="AM10" s="12"/>
+      <c r="AN10" s="12"/>
+      <c r="AO10" s="12"/>
+      <c r="AP10" s="12"/>
+      <c r="AQ10" s="12"/>
+      <c r="AR10" s="12"/>
+      <c r="AS10" s="12"/>
+      <c r="AT10" s="12"/>
+      <c r="AU10" s="12"/>
+      <c r="AV10" s="12"/>
+      <c r="AW10" s="12"/>
+      <c r="AX10" s="12"/>
+      <c r="AY10" s="12"/>
+      <c r="AZ10" s="12"/>
+      <c r="BA10" s="12"/>
+      <c r="BB10" s="12"/>
+    </row>
+    <row r="11" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A11" s="27">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="70"/>
+      <c r="D11" s="70"/>
+      <c r="E11" s="70"/>
+      <c r="F11" s="70"/>
+      <c r="G11" s="70"/>
+      <c r="H11" s="70"/>
+      <c r="I11" s="70"/>
+      <c r="J11" s="71"/>
+      <c r="K11" s="72">
+        <v>2</v>
+      </c>
+      <c r="L11" s="55"/>
+      <c r="M11" s="73"/>
+      <c r="N11" s="74"/>
+      <c r="O11" s="70"/>
+      <c r="P11" s="71"/>
+      <c r="Q11" s="71"/>
+      <c r="R11" s="72"/>
+      <c r="S11" s="55"/>
+      <c r="T11" s="58">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="U11" s="58">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="V11" s="58">
+        <f t="shared" si="3"/>
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="AF11" s="12"/>
+      <c r="AG11" s="12"/>
+      <c r="AH11" s="12"/>
+      <c r="AI11" s="12"/>
+      <c r="AJ11" s="12"/>
+      <c r="AK11" s="12"/>
+      <c r="AL11" s="12"/>
+      <c r="AM11" s="12"/>
+      <c r="AN11" s="12"/>
+      <c r="AO11" s="12"/>
+      <c r="AP11" s="12"/>
+      <c r="AQ11" s="12"/>
+      <c r="AR11" s="12"/>
+      <c r="AS11" s="12"/>
+      <c r="AT11" s="12"/>
+      <c r="AU11" s="12"/>
+      <c r="AV11" s="12"/>
+      <c r="AW11" s="12"/>
+      <c r="AX11" s="12"/>
+      <c r="AY11" s="12"/>
+      <c r="AZ11" s="12"/>
+      <c r="BA11" s="12"/>
+      <c r="BB11" s="12"/>
+    </row>
+    <row r="12" spans="1:54" s="13" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="27">
+        <v>7</v>
+      </c>
+      <c r="B12" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="70">
+        <f>1224+53+4+504+24+1080+29</f>
+        <v>2918</v>
+      </c>
+      <c r="D12" s="70"/>
+      <c r="E12" s="70"/>
+      <c r="F12" s="70"/>
+      <c r="G12" s="70"/>
+      <c r="H12" s="70"/>
+      <c r="I12" s="70"/>
+      <c r="J12" s="71"/>
+      <c r="K12" s="72"/>
+      <c r="L12" s="55"/>
+      <c r="M12" s="73">
+        <v>20</v>
+      </c>
+      <c r="N12" s="74">
+        <v>2</v>
+      </c>
+      <c r="O12" s="70">
+        <v>12</v>
+      </c>
+      <c r="P12" s="71">
+        <v>18</v>
+      </c>
+      <c r="Q12" s="71">
+        <v>22</v>
+      </c>
+      <c r="R12" s="72">
+        <v>3</v>
+      </c>
+      <c r="S12" s="62"/>
+      <c r="T12" s="69">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="U12" s="69">
+        <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
+        <v>71351</v>
+      </c>
+      <c r="V12" s="69">
+        <f>U12/24</f>
+        <v>2972.9583333333335</v>
+      </c>
+      <c r="W12" s="9"/>
+      <c r="X12" s="9"/>
+      <c r="Y12" s="9"/>
+      <c r="Z12" s="9"/>
+      <c r="AA12" s="9"/>
+      <c r="AB12" s="9"/>
+      <c r="AC12" s="9"/>
+      <c r="AD12" s="9"/>
+      <c r="AE12" s="9"/>
+      <c r="AF12" s="12"/>
+      <c r="AG12" s="12"/>
+      <c r="AH12" s="12"/>
+      <c r="AI12" s="12"/>
+      <c r="AJ12" s="12"/>
+      <c r="AK12" s="12"/>
+      <c r="AL12" s="12"/>
+      <c r="AM12" s="12"/>
+      <c r="AN12" s="12"/>
+      <c r="AO12" s="12"/>
+      <c r="AP12" s="12"/>
+      <c r="AQ12" s="12"/>
+      <c r="AR12" s="12"/>
+      <c r="AS12" s="12"/>
+      <c r="AT12" s="12"/>
+      <c r="AU12" s="12"/>
+      <c r="AV12" s="12"/>
+      <c r="AW12" s="12"/>
+      <c r="AX12" s="12"/>
+      <c r="AY12" s="12"/>
+      <c r="AZ12" s="12"/>
+      <c r="BA12" s="12"/>
+      <c r="BB12" s="12"/>
+    </row>
+    <row r="13" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A13" s="27">
+        <v>11</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="70">
+        <v>2</v>
+      </c>
+      <c r="D13" s="70"/>
+      <c r="E13" s="70"/>
+      <c r="F13" s="70"/>
+      <c r="G13" s="70"/>
+      <c r="H13" s="70">
+        <v>16</v>
+      </c>
+      <c r="I13" s="70"/>
+      <c r="J13" s="71"/>
+      <c r="K13" s="72"/>
+      <c r="L13" s="55"/>
+      <c r="M13" s="73"/>
+      <c r="N13" s="74"/>
+      <c r="O13" s="70"/>
+      <c r="P13" s="71"/>
+      <c r="Q13" s="71"/>
+      <c r="R13" s="72"/>
+      <c r="S13" s="55"/>
+      <c r="T13" s="76">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="U13" s="76">
+        <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
+        <v>64</v>
+      </c>
+      <c r="V13" s="76">
+        <f>U13/24</f>
+        <v>2.6666666666666665</v>
+      </c>
+      <c r="AF13" s="12"/>
+      <c r="AG13" s="12"/>
+      <c r="AH13" s="12"/>
+      <c r="AI13" s="12"/>
+      <c r="AJ13" s="12"/>
+      <c r="AK13" s="12"/>
+      <c r="AL13" s="12"/>
+      <c r="AM13" s="12"/>
+      <c r="AN13" s="12"/>
+      <c r="AO13" s="12"/>
+      <c r="AP13" s="12"/>
+      <c r="AQ13" s="12"/>
+      <c r="AR13" s="12"/>
+      <c r="AS13" s="12"/>
+      <c r="AT13" s="12"/>
+      <c r="AU13" s="12"/>
+      <c r="AV13" s="12"/>
+      <c r="AW13" s="12"/>
+      <c r="AX13" s="12"/>
+      <c r="AY13" s="12"/>
+      <c r="AZ13" s="12"/>
+      <c r="BA13" s="12"/>
+      <c r="BB13" s="12"/>
+    </row>
+    <row r="14" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A14" s="27">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="70">
+        <v>2</v>
+      </c>
+      <c r="D14" s="70"/>
+      <c r="E14" s="70"/>
+      <c r="F14" s="70"/>
+      <c r="G14" s="70"/>
+      <c r="H14" s="70"/>
+      <c r="I14" s="70"/>
+      <c r="J14" s="71"/>
+      <c r="K14" s="72"/>
+      <c r="L14" s="55"/>
+      <c r="M14" s="73"/>
+      <c r="N14" s="74"/>
+      <c r="O14" s="70"/>
+      <c r="P14" s="71"/>
+      <c r="Q14" s="71"/>
+      <c r="R14" s="72"/>
+      <c r="S14" s="55"/>
+      <c r="T14" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U14" s="75">
+        <f t="shared" ref="U14:U36" si="4">C14*24+M14*24+O14*24+Q14*24+T14</f>
+        <v>48</v>
+      </c>
+      <c r="V14" s="75">
+        <f t="shared" ref="V14:V36" si="5">U14/24</f>
+        <v>2</v>
+      </c>
+      <c r="AF14" s="12"/>
+      <c r="AG14" s="12"/>
+      <c r="AH14" s="12"/>
+      <c r="AI14" s="12"/>
+      <c r="AJ14" s="12"/>
+      <c r="AK14" s="12"/>
+      <c r="AL14" s="12"/>
+      <c r="AM14" s="12"/>
+      <c r="AN14" s="12"/>
+      <c r="AO14" s="12"/>
+      <c r="AP14" s="12"/>
+      <c r="AQ14" s="12"/>
+      <c r="AR14" s="12"/>
+      <c r="AS14" s="12"/>
+      <c r="AT14" s="12"/>
+      <c r="AU14" s="12"/>
+      <c r="AV14" s="12"/>
+      <c r="AW14" s="12"/>
+      <c r="AX14" s="12"/>
+      <c r="AY14" s="12"/>
+      <c r="AZ14" s="12"/>
+      <c r="BA14" s="12"/>
+      <c r="BB14" s="12"/>
+    </row>
+    <row r="15" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A15" s="27">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="70"/>
+      <c r="D15" s="70"/>
+      <c r="E15" s="70"/>
+      <c r="F15" s="70"/>
+      <c r="G15" s="70"/>
+      <c r="H15" s="70"/>
+      <c r="I15" s="70"/>
+      <c r="J15" s="71"/>
+      <c r="K15" s="72"/>
+      <c r="L15" s="55"/>
+      <c r="M15" s="73"/>
+      <c r="N15" s="74"/>
+      <c r="O15" s="70"/>
+      <c r="P15" s="71"/>
+      <c r="Q15" s="71"/>
+      <c r="R15" s="72"/>
+      <c r="S15" s="55"/>
+      <c r="T15" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U15" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF15" s="12"/>
+      <c r="AG15" s="12"/>
+      <c r="AH15" s="12"/>
+      <c r="AI15" s="12"/>
+      <c r="AJ15" s="12"/>
+      <c r="AK15" s="12"/>
+      <c r="AL15" s="12"/>
+      <c r="AM15" s="12"/>
+      <c r="AN15" s="12"/>
+      <c r="AO15" s="12"/>
+      <c r="AP15" s="12"/>
+      <c r="AQ15" s="12"/>
+      <c r="AR15" s="12"/>
+      <c r="AS15" s="12"/>
+      <c r="AT15" s="12"/>
+      <c r="AU15" s="12"/>
+      <c r="AV15" s="12"/>
+      <c r="AW15" s="12"/>
+      <c r="AX15" s="12"/>
+      <c r="AY15" s="12"/>
+      <c r="AZ15" s="12"/>
+      <c r="BA15" s="12"/>
+      <c r="BB15" s="12"/>
+    </row>
+    <row r="16" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A16" s="27">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="70"/>
+      <c r="D16" s="70"/>
+      <c r="E16" s="70"/>
+      <c r="F16" s="70"/>
+      <c r="G16" s="70"/>
+      <c r="H16" s="70"/>
+      <c r="I16" s="70"/>
+      <c r="J16" s="71"/>
+      <c r="K16" s="72"/>
+      <c r="L16" s="55"/>
+      <c r="M16" s="73"/>
+      <c r="N16" s="74"/>
+      <c r="O16" s="70"/>
+      <c r="P16" s="71"/>
+      <c r="Q16" s="71"/>
+      <c r="R16" s="72"/>
+      <c r="S16" s="55"/>
+      <c r="T16" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U16" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF16" s="12"/>
+      <c r="AG16" s="12"/>
+      <c r="AH16" s="12"/>
+      <c r="AI16" s="12"/>
+      <c r="AJ16" s="12"/>
+      <c r="AK16" s="12"/>
+      <c r="AL16" s="12"/>
+      <c r="AM16" s="12"/>
+      <c r="AN16" s="12"/>
+      <c r="AO16" s="12"/>
+      <c r="AP16" s="12"/>
+      <c r="AQ16" s="12"/>
+      <c r="AR16" s="12"/>
+      <c r="AS16" s="12"/>
+      <c r="AT16" s="12"/>
+      <c r="AU16" s="12"/>
+      <c r="AV16" s="12"/>
+      <c r="AW16" s="12"/>
+      <c r="AX16" s="12"/>
+      <c r="AY16" s="12"/>
+      <c r="AZ16" s="12"/>
+      <c r="BA16" s="12"/>
+      <c r="BB16" s="12"/>
+    </row>
+    <row r="17" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A17" s="27">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="70"/>
+      <c r="D17" s="70"/>
+      <c r="E17" s="70"/>
+      <c r="F17" s="70"/>
+      <c r="G17" s="70"/>
+      <c r="H17" s="70">
+        <f>3*24</f>
+        <v>72</v>
+      </c>
+      <c r="I17" s="70"/>
+      <c r="J17" s="71"/>
+      <c r="K17" s="72"/>
+      <c r="L17" s="55"/>
+      <c r="M17" s="73"/>
+      <c r="N17" s="74"/>
+      <c r="O17" s="70"/>
+      <c r="P17" s="71"/>
+      <c r="Q17" s="71"/>
+      <c r="R17" s="72"/>
+      <c r="S17" s="55"/>
+      <c r="T17" s="58">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="U17" s="75">
+        <f t="shared" si="4"/>
+        <v>72</v>
+      </c>
+      <c r="V17" s="75">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="AF17" s="12"/>
+      <c r="AG17" s="12"/>
+      <c r="AH17" s="12"/>
+      <c r="AI17" s="12"/>
+      <c r="AJ17" s="12"/>
+      <c r="AK17" s="12"/>
+      <c r="AL17" s="12"/>
+      <c r="AM17" s="12"/>
+      <c r="AN17" s="12"/>
+      <c r="AO17" s="12"/>
+      <c r="AP17" s="12"/>
+      <c r="AQ17" s="12"/>
+      <c r="AR17" s="12"/>
+      <c r="AS17" s="12"/>
+      <c r="AT17" s="12"/>
+      <c r="AU17" s="12"/>
+      <c r="AV17" s="12"/>
+      <c r="AW17" s="12"/>
+      <c r="AX17" s="12"/>
+      <c r="AY17" s="12"/>
+      <c r="AZ17" s="12"/>
+      <c r="BA17" s="12"/>
+      <c r="BB17" s="12"/>
+    </row>
+    <row r="18" spans="1:54" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="27">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="70"/>
+      <c r="D18" s="70"/>
+      <c r="E18" s="70"/>
+      <c r="F18" s="70"/>
+      <c r="G18" s="70"/>
+      <c r="H18" s="70"/>
+      <c r="I18" s="70"/>
+      <c r="J18" s="71"/>
+      <c r="K18" s="72"/>
+      <c r="L18" s="55"/>
+      <c r="M18" s="73"/>
+      <c r="N18" s="74"/>
+      <c r="O18" s="70"/>
+      <c r="P18" s="71"/>
+      <c r="Q18" s="71"/>
+      <c r="R18" s="72"/>
+      <c r="S18" s="55"/>
+      <c r="T18" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U18" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF18" s="12"/>
+      <c r="AG18" s="12"/>
+      <c r="AH18" s="12"/>
+      <c r="AI18" s="12"/>
+      <c r="AJ18" s="12"/>
+      <c r="AK18" s="12"/>
+      <c r="AL18" s="12"/>
+      <c r="AM18" s="12"/>
+      <c r="AN18" s="12"/>
+      <c r="AO18" s="12"/>
+      <c r="AP18" s="12"/>
+      <c r="AQ18" s="12"/>
+      <c r="AR18" s="12"/>
+      <c r="AS18" s="12"/>
+      <c r="AT18" s="12"/>
+      <c r="AU18" s="12"/>
+      <c r="AV18" s="12"/>
+      <c r="AW18" s="12"/>
+      <c r="AX18" s="12"/>
+      <c r="AY18" s="12"/>
+      <c r="AZ18" s="12"/>
+      <c r="BA18" s="12"/>
+      <c r="BB18" s="12"/>
+    </row>
+    <row r="19" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A19" s="27">
+        <v>16</v>
+      </c>
+      <c r="B19" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="70">
+        <v>1</v>
+      </c>
+      <c r="D19" s="70"/>
+      <c r="E19" s="70"/>
+      <c r="F19" s="70"/>
+      <c r="G19" s="70"/>
+      <c r="H19" s="70">
+        <f>20+24</f>
+        <v>44</v>
+      </c>
+      <c r="I19" s="70"/>
+      <c r="J19" s="71"/>
+      <c r="K19" s="72"/>
+      <c r="L19" s="55"/>
+      <c r="M19" s="73"/>
+      <c r="N19" s="74"/>
+      <c r="O19" s="70"/>
+      <c r="P19" s="71"/>
+      <c r="Q19" s="71"/>
+      <c r="R19" s="72"/>
+      <c r="S19" s="55"/>
+      <c r="T19" s="58">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="U19" s="75">
+        <f t="shared" si="4"/>
+        <v>68</v>
+      </c>
+      <c r="V19" s="75">
+        <f t="shared" si="5"/>
+        <v>2.8333333333333335</v>
+      </c>
+      <c r="AF19" s="12"/>
+      <c r="AG19" s="12"/>
+      <c r="AH19" s="12"/>
+      <c r="AI19" s="12"/>
+      <c r="AJ19" s="12"/>
+      <c r="AK19" s="12"/>
+      <c r="AL19" s="12"/>
+      <c r="AM19" s="12"/>
+      <c r="AN19" s="12"/>
+      <c r="AO19" s="12"/>
+      <c r="AP19" s="12"/>
+      <c r="AQ19" s="12"/>
+      <c r="AR19" s="12"/>
+      <c r="AS19" s="12"/>
+      <c r="AT19" s="12"/>
+      <c r="AU19" s="12"/>
+      <c r="AV19" s="12"/>
+      <c r="AW19" s="12"/>
+      <c r="AX19" s="12"/>
+      <c r="AY19" s="12"/>
+      <c r="AZ19" s="12"/>
+      <c r="BA19" s="12"/>
+      <c r="BB19" s="12"/>
+    </row>
+    <row r="20" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A20" s="27">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="B20" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="70">
+        <v>5</v>
+      </c>
+      <c r="D20" s="70"/>
+      <c r="E20" s="70"/>
+      <c r="F20" s="70"/>
+      <c r="G20" s="70"/>
+      <c r="H20" s="70"/>
+      <c r="I20" s="70"/>
+      <c r="J20" s="71"/>
+      <c r="K20" s="72"/>
+      <c r="L20" s="55"/>
+      <c r="M20" s="73"/>
+      <c r="N20" s="74"/>
+      <c r="O20" s="70"/>
+      <c r="P20" s="71"/>
+      <c r="Q20" s="71"/>
+      <c r="R20" s="72"/>
+      <c r="S20" s="55"/>
+      <c r="T20" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U20" s="75">
+        <f t="shared" si="4"/>
+        <v>120</v>
+      </c>
+      <c r="V20" s="75">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="AF20" s="12"/>
+      <c r="AG20" s="12"/>
+      <c r="AH20" s="12"/>
+      <c r="AI20" s="12"/>
+      <c r="AJ20" s="12"/>
+      <c r="AK20" s="12"/>
+      <c r="AL20" s="12"/>
+      <c r="AM20" s="12"/>
+      <c r="AN20" s="12"/>
+      <c r="AO20" s="12"/>
+      <c r="AP20" s="12"/>
+      <c r="AQ20" s="12"/>
+      <c r="AR20" s="12"/>
+      <c r="AS20" s="12"/>
+      <c r="AT20" s="12"/>
+      <c r="AU20" s="12"/>
+      <c r="AV20" s="12"/>
+      <c r="AW20" s="12"/>
+      <c r="AX20" s="12"/>
+      <c r="AY20" s="12"/>
+      <c r="AZ20" s="12"/>
+      <c r="BA20" s="12"/>
+      <c r="BB20" s="12"/>
+    </row>
+    <row r="21" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A21" s="27">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="B21" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="70"/>
+      <c r="D21" s="70"/>
+      <c r="E21" s="70"/>
+      <c r="F21" s="70"/>
+      <c r="G21" s="70"/>
+      <c r="H21" s="70">
+        <f>2*24</f>
+        <v>48</v>
+      </c>
+      <c r="I21" s="70"/>
+      <c r="J21" s="71"/>
+      <c r="K21" s="72"/>
+      <c r="L21" s="55"/>
+      <c r="M21" s="73"/>
+      <c r="N21" s="74"/>
+      <c r="O21" s="70"/>
+      <c r="P21" s="71"/>
+      <c r="Q21" s="71"/>
+      <c r="R21" s="72"/>
+      <c r="S21" s="55"/>
+      <c r="T21" s="58">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+      <c r="U21" s="75">
+        <f t="shared" si="4"/>
+        <v>48</v>
+      </c>
+      <c r="V21" s="75">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="AF21" s="12"/>
+      <c r="AG21" s="12"/>
+      <c r="AH21" s="12"/>
+      <c r="AI21" s="12"/>
+      <c r="AJ21" s="12"/>
+      <c r="AK21" s="12"/>
+      <c r="AL21" s="12"/>
+      <c r="AM21" s="12"/>
+      <c r="AN21" s="12"/>
+      <c r="AO21" s="12"/>
+      <c r="AP21" s="12"/>
+      <c r="AQ21" s="12"/>
+      <c r="AR21" s="12"/>
+      <c r="AS21" s="12"/>
+      <c r="AT21" s="12"/>
+      <c r="AU21" s="12"/>
+      <c r="AV21" s="12"/>
+      <c r="AW21" s="12"/>
+      <c r="AX21" s="12"/>
+      <c r="AY21" s="12"/>
+      <c r="AZ21" s="12"/>
+      <c r="BA21" s="12"/>
+      <c r="BB21" s="12"/>
+    </row>
+    <row r="22" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="27">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="B22" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="70">
+        <v>1</v>
+      </c>
+      <c r="D22" s="70"/>
+      <c r="E22" s="70"/>
+      <c r="F22" s="70"/>
+      <c r="G22" s="70"/>
+      <c r="H22" s="70"/>
+      <c r="I22" s="70">
+        <v>20</v>
+      </c>
+      <c r="J22" s="71"/>
+      <c r="K22" s="72"/>
+      <c r="L22" s="55"/>
+      <c r="M22" s="73"/>
+      <c r="N22" s="74"/>
+      <c r="O22" s="70"/>
+      <c r="P22" s="71"/>
+      <c r="Q22" s="71"/>
+      <c r="R22" s="72"/>
+      <c r="S22" s="55"/>
+      <c r="T22" s="58">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="U22" s="75">
+        <f t="shared" si="4"/>
+        <v>44</v>
+      </c>
+      <c r="V22" s="75">
+        <f t="shared" si="5"/>
+        <v>1.8333333333333333</v>
+      </c>
+      <c r="W22" s="9"/>
+      <c r="X22" s="9"/>
+      <c r="Y22" s="9"/>
+      <c r="Z22" s="9"/>
+      <c r="AA22" s="9"/>
+      <c r="AB22" s="9"/>
+      <c r="AC22" s="9"/>
+      <c r="AD22" s="9"/>
+      <c r="AE22" s="9"/>
+      <c r="AF22" s="12"/>
+      <c r="AG22" s="12"/>
+      <c r="AH22" s="12"/>
+      <c r="AI22" s="12"/>
+      <c r="AJ22" s="12"/>
+      <c r="AK22" s="12"/>
+      <c r="AL22" s="12"/>
+      <c r="AM22" s="12"/>
+      <c r="AN22" s="12"/>
+      <c r="AO22" s="12"/>
+      <c r="AP22" s="12"/>
+      <c r="AQ22" s="12"/>
+      <c r="AR22" s="12"/>
+      <c r="AS22" s="12"/>
+      <c r="AT22" s="12"/>
+      <c r="AU22" s="12"/>
+      <c r="AV22" s="12"/>
+      <c r="AW22" s="12"/>
+      <c r="AX22" s="12"/>
+      <c r="AY22" s="12"/>
+      <c r="AZ22" s="12"/>
+      <c r="BA22" s="12"/>
+      <c r="BB22" s="12"/>
+    </row>
+    <row r="23" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="27">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="B23" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="70"/>
+      <c r="D23" s="70"/>
+      <c r="E23" s="70"/>
+      <c r="F23" s="70"/>
+      <c r="G23" s="70"/>
+      <c r="H23" s="70">
+        <f>37*24+19</f>
+        <v>907</v>
+      </c>
+      <c r="I23" s="70"/>
+      <c r="J23" s="71"/>
+      <c r="K23" s="72"/>
+      <c r="L23" s="55"/>
+      <c r="M23" s="73"/>
+      <c r="N23" s="74"/>
+      <c r="O23" s="70"/>
+      <c r="P23" s="71"/>
+      <c r="Q23" s="71"/>
+      <c r="R23" s="72"/>
+      <c r="S23" s="55"/>
+      <c r="T23" s="58">
+        <f t="shared" si="0"/>
+        <v>907</v>
+      </c>
+      <c r="U23" s="75">
+        <f t="shared" si="4"/>
+        <v>907</v>
+      </c>
+      <c r="V23" s="75">
+        <f t="shared" si="5"/>
+        <v>37.791666666666664</v>
+      </c>
+      <c r="W23" s="9"/>
+      <c r="X23" s="9"/>
+      <c r="Y23" s="9"/>
+      <c r="Z23" s="9"/>
+      <c r="AA23" s="9"/>
+      <c r="AB23" s="9"/>
+      <c r="AC23" s="9"/>
+      <c r="AD23" s="9"/>
+      <c r="AE23" s="9"/>
+      <c r="AF23" s="12"/>
+      <c r="AG23" s="12"/>
+      <c r="AH23" s="12"/>
+      <c r="AI23" s="12"/>
+      <c r="AJ23" s="12"/>
+      <c r="AK23" s="12"/>
+      <c r="AL23" s="12"/>
+      <c r="AM23" s="12"/>
+      <c r="AN23" s="12"/>
+      <c r="AO23" s="12"/>
+      <c r="AP23" s="12"/>
+      <c r="AQ23" s="12"/>
+      <c r="AR23" s="12"/>
+      <c r="AS23" s="12"/>
+      <c r="AT23" s="12"/>
+      <c r="AU23" s="12"/>
+      <c r="AV23" s="12"/>
+      <c r="AW23" s="12"/>
+      <c r="AX23" s="12"/>
+      <c r="AY23" s="12"/>
+      <c r="AZ23" s="12"/>
+      <c r="BA23" s="12"/>
+      <c r="BB23" s="12"/>
+    </row>
+    <row r="24" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A24" s="27">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="B24" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" s="70">
+        <v>2</v>
+      </c>
+      <c r="D24" s="70"/>
+      <c r="E24" s="70"/>
+      <c r="F24" s="70"/>
+      <c r="G24" s="70"/>
+      <c r="H24" s="70">
+        <f>3*24</f>
+        <v>72</v>
+      </c>
+      <c r="I24" s="70"/>
+      <c r="J24" s="71"/>
+      <c r="K24" s="72"/>
+      <c r="L24" s="55"/>
+      <c r="M24" s="73"/>
+      <c r="N24" s="74"/>
+      <c r="O24" s="70"/>
+      <c r="P24" s="71"/>
+      <c r="Q24" s="71"/>
+      <c r="R24" s="72"/>
+      <c r="S24" s="55"/>
+      <c r="T24" s="58">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="U24" s="75">
+        <f t="shared" si="4"/>
+        <v>120</v>
+      </c>
+      <c r="V24" s="75">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="AF24" s="12"/>
+      <c r="AG24" s="12"/>
+      <c r="AH24" s="12"/>
+      <c r="AI24" s="12"/>
+      <c r="AJ24" s="12"/>
+      <c r="AK24" s="12"/>
+      <c r="AL24" s="12"/>
+      <c r="AM24" s="12"/>
+      <c r="AN24" s="12"/>
+      <c r="AO24" s="12"/>
+      <c r="AP24" s="12"/>
+      <c r="AQ24" s="12"/>
+      <c r="AR24" s="12"/>
+      <c r="AS24" s="12"/>
+      <c r="AT24" s="12"/>
+      <c r="AU24" s="12"/>
+      <c r="AV24" s="12"/>
+      <c r="AW24" s="12"/>
+      <c r="AX24" s="12"/>
+      <c r="AY24" s="12"/>
+      <c r="AZ24" s="12"/>
+      <c r="BA24" s="12"/>
+      <c r="BB24" s="12"/>
+    </row>
+    <row r="25" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A25" s="27">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="70">
+        <f>7+126</f>
+        <v>133</v>
+      </c>
+      <c r="D25" s="70"/>
+      <c r="E25" s="70"/>
+      <c r="F25" s="70"/>
+      <c r="G25" s="70"/>
+      <c r="H25" s="70"/>
+      <c r="I25" s="70">
+        <v>1</v>
+      </c>
+      <c r="J25" s="71"/>
+      <c r="K25" s="72"/>
+      <c r="L25" s="55"/>
+      <c r="M25" s="73"/>
+      <c r="N25" s="74"/>
+      <c r="O25" s="70">
+        <v>1</v>
+      </c>
+      <c r="P25" s="71"/>
+      <c r="Q25" s="71">
+        <v>2</v>
+      </c>
+      <c r="R25" s="72"/>
+      <c r="S25" s="55"/>
+      <c r="T25" s="58">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="U25" s="75">
+        <f t="shared" si="4"/>
+        <v>3265</v>
+      </c>
+      <c r="V25" s="75">
+        <f t="shared" si="5"/>
+        <v>136.04166666666666</v>
+      </c>
+      <c r="AY25" s="14" t="e">
+        <f>#REF!-AY24</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="27">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="B26" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="70">
+        <v>3</v>
+      </c>
+      <c r="D26" s="70"/>
+      <c r="E26" s="70"/>
+      <c r="F26" s="70"/>
+      <c r="G26" s="70"/>
+      <c r="H26" s="70"/>
+      <c r="I26" s="70"/>
+      <c r="J26" s="71"/>
+      <c r="K26" s="72"/>
+      <c r="L26" s="55"/>
+      <c r="M26" s="73"/>
+      <c r="N26" s="74"/>
+      <c r="O26" s="70"/>
+      <c r="P26" s="71"/>
+      <c r="Q26" s="71">
+        <v>2</v>
+      </c>
+      <c r="R26" s="72"/>
+      <c r="S26" s="55"/>
+      <c r="T26" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U26" s="75">
+        <f t="shared" si="4"/>
+        <v>120</v>
+      </c>
+      <c r="V26" s="75">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="W26" s="9"/>
+      <c r="X26" s="9"/>
+      <c r="Y26" s="9"/>
+      <c r="Z26" s="9"/>
+      <c r="AA26" s="9"/>
+      <c r="AB26" s="9"/>
+      <c r="AC26" s="9"/>
+      <c r="AD26" s="9"/>
+      <c r="AE26" s="9"/>
+    </row>
+    <row r="27" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="27">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="B27" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27" s="70">
+        <v>1</v>
+      </c>
+      <c r="D27" s="70"/>
+      <c r="E27" s="70"/>
+      <c r="F27" s="70"/>
+      <c r="G27" s="70"/>
+      <c r="H27" s="70"/>
+      <c r="I27" s="70"/>
+      <c r="J27" s="71"/>
+      <c r="K27" s="72"/>
+      <c r="L27" s="55"/>
+      <c r="M27" s="73"/>
+      <c r="N27" s="74"/>
+      <c r="O27" s="70"/>
+      <c r="P27" s="71"/>
+      <c r="Q27" s="71"/>
+      <c r="R27" s="72"/>
+      <c r="S27" s="55"/>
+      <c r="T27" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U27" s="75">
+        <f t="shared" si="4"/>
+        <v>24</v>
+      </c>
+      <c r="V27" s="75">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="W27" s="9"/>
+      <c r="X27" s="9"/>
+      <c r="Y27" s="9"/>
+      <c r="Z27" s="9"/>
+      <c r="AA27" s="9"/>
+      <c r="AB27" s="9"/>
+      <c r="AC27" s="9"/>
+      <c r="AD27" s="9"/>
+      <c r="AE27" s="9"/>
+    </row>
+    <row r="28" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="27">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="B28" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="70">
+        <f>34+252</f>
+        <v>286</v>
+      </c>
+      <c r="D28" s="70"/>
+      <c r="E28" s="70"/>
+      <c r="F28" s="70"/>
+      <c r="G28" s="70"/>
+      <c r="H28" s="70"/>
+      <c r="I28" s="70"/>
+      <c r="J28" s="71"/>
+      <c r="K28" s="72"/>
+      <c r="L28" s="55"/>
+      <c r="M28" s="73"/>
+      <c r="N28" s="74"/>
+      <c r="O28" s="70">
+        <v>3</v>
+      </c>
+      <c r="P28" s="71"/>
+      <c r="Q28" s="71">
+        <v>3</v>
+      </c>
+      <c r="R28" s="72"/>
+      <c r="S28" s="55"/>
+      <c r="T28" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U28" s="75">
+        <f t="shared" si="4"/>
+        <v>7008</v>
+      </c>
+      <c r="V28" s="75">
+        <f t="shared" si="5"/>
+        <v>292</v>
+      </c>
+      <c r="W28" s="9"/>
+      <c r="X28" s="9"/>
+      <c r="Y28" s="9"/>
+      <c r="Z28" s="9"/>
+      <c r="AA28" s="9"/>
+      <c r="AB28" s="9"/>
+      <c r="AC28" s="9"/>
+      <c r="AD28" s="9"/>
+      <c r="AE28" s="9"/>
+    </row>
+    <row r="29" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A29" s="27">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="B29" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" s="70"/>
+      <c r="D29" s="70"/>
+      <c r="E29" s="70"/>
+      <c r="F29" s="70"/>
+      <c r="G29" s="70"/>
+      <c r="H29" s="70"/>
+      <c r="I29" s="70">
+        <v>5</v>
+      </c>
+      <c r="J29" s="71"/>
+      <c r="K29" s="72"/>
+      <c r="L29" s="55"/>
+      <c r="M29" s="73"/>
+      <c r="N29" s="74"/>
+      <c r="O29" s="70"/>
+      <c r="P29" s="71"/>
+      <c r="Q29" s="71"/>
+      <c r="R29" s="72"/>
+      <c r="S29" s="55"/>
+      <c r="T29" s="58">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="U29" s="75">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="V29" s="75">
+        <f t="shared" si="5"/>
+        <v>0.20833333333333334</v>
+      </c>
+    </row>
+    <row r="30" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A30" s="27">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="B30" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="70"/>
+      <c r="D30" s="70"/>
+      <c r="E30" s="70"/>
+      <c r="F30" s="70"/>
+      <c r="G30" s="70"/>
+      <c r="H30" s="70"/>
+      <c r="I30" s="70"/>
+      <c r="J30" s="71"/>
+      <c r="K30" s="72"/>
+      <c r="L30" s="55"/>
+      <c r="M30" s="73"/>
+      <c r="N30" s="74"/>
+      <c r="O30" s="70"/>
+      <c r="P30" s="71"/>
+      <c r="Q30" s="71"/>
+      <c r="R30" s="72"/>
+      <c r="S30" s="55"/>
+      <c r="T30" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U30" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V30" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A31" s="27">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="B31" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" s="70"/>
+      <c r="D31" s="70"/>
+      <c r="E31" s="70"/>
+      <c r="F31" s="70"/>
+      <c r="G31" s="70"/>
+      <c r="H31" s="70"/>
+      <c r="I31" s="70"/>
+      <c r="J31" s="71"/>
+      <c r="K31" s="72"/>
+      <c r="L31" s="55"/>
+      <c r="M31" s="73"/>
+      <c r="N31" s="74"/>
+      <c r="O31" s="70"/>
+      <c r="P31" s="71"/>
+      <c r="Q31" s="71"/>
+      <c r="R31" s="72"/>
+      <c r="S31" s="55"/>
+      <c r="T31" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U31" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V31" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A32" s="27">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="B32" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" s="70"/>
+      <c r="D32" s="70"/>
+      <c r="E32" s="70"/>
+      <c r="F32" s="70"/>
+      <c r="G32" s="70"/>
+      <c r="H32" s="70"/>
+      <c r="I32" s="70"/>
+      <c r="J32" s="71"/>
+      <c r="K32" s="72"/>
+      <c r="L32" s="55"/>
+      <c r="M32" s="73"/>
+      <c r="N32" s="74"/>
+      <c r="O32" s="70"/>
+      <c r="P32" s="71"/>
+      <c r="Q32" s="71"/>
+      <c r="R32" s="72"/>
+      <c r="S32" s="55"/>
+      <c r="T32" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U32" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V32" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A33" s="27">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="B33" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" s="70"/>
+      <c r="D33" s="70"/>
+      <c r="E33" s="70"/>
+      <c r="F33" s="70"/>
+      <c r="G33" s="70"/>
+      <c r="H33" s="70"/>
+      <c r="I33" s="70"/>
+      <c r="J33" s="71"/>
+      <c r="K33" s="72"/>
+      <c r="L33" s="55"/>
+      <c r="M33" s="73"/>
+      <c r="N33" s="74"/>
+      <c r="O33" s="70"/>
+      <c r="P33" s="71"/>
+      <c r="Q33" s="71"/>
+      <c r="R33" s="72"/>
+      <c r="S33" s="55"/>
+      <c r="T33" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U33" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V33" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A34" s="27">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="B34" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" s="70">
+        <f>72+52</f>
+        <v>124</v>
+      </c>
+      <c r="D34" s="70"/>
+      <c r="E34" s="70"/>
+      <c r="F34" s="70"/>
+      <c r="G34" s="70"/>
+      <c r="H34" s="70"/>
+      <c r="I34" s="70">
+        <v>1</v>
+      </c>
+      <c r="J34" s="71"/>
+      <c r="K34" s="72">
+        <v>1</v>
+      </c>
+      <c r="L34" s="55"/>
+      <c r="M34" s="73"/>
+      <c r="N34" s="74"/>
+      <c r="O34" s="70">
+        <v>2</v>
+      </c>
+      <c r="P34" s="71"/>
+      <c r="Q34" s="71">
+        <v>2</v>
+      </c>
+      <c r="R34" s="72"/>
+      <c r="S34" s="55"/>
+      <c r="T34" s="58">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="U34" s="75">
+        <f t="shared" si="4"/>
+        <v>3074</v>
+      </c>
+      <c r="V34" s="75">
+        <f t="shared" si="5"/>
+        <v>128.08333333333334</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="27">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="B35" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="C35" s="70"/>
+      <c r="D35" s="70"/>
+      <c r="E35" s="70"/>
+      <c r="F35" s="70"/>
+      <c r="G35" s="70"/>
+      <c r="H35" s="70"/>
+      <c r="I35" s="70"/>
+      <c r="J35" s="71"/>
+      <c r="K35" s="72"/>
+      <c r="L35" s="55"/>
+      <c r="M35" s="73"/>
+      <c r="N35" s="74"/>
+      <c r="O35" s="70"/>
+      <c r="P35" s="71"/>
+      <c r="Q35" s="71"/>
+      <c r="R35" s="72"/>
+      <c r="S35" s="55"/>
+      <c r="T35" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U35" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V35" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A36" s="27">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+      <c r="B36" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="70"/>
+      <c r="D36" s="70"/>
+      <c r="E36" s="70"/>
+      <c r="F36" s="70"/>
+      <c r="G36" s="70"/>
+      <c r="H36" s="70"/>
+      <c r="I36" s="70"/>
+      <c r="J36" s="71"/>
+      <c r="K36" s="72"/>
+      <c r="L36" s="55"/>
+      <c r="M36" s="73"/>
+      <c r="N36" s="74"/>
+      <c r="O36" s="70"/>
+      <c r="P36" s="71"/>
+      <c r="Q36" s="71"/>
+      <c r="R36" s="72"/>
+      <c r="S36" s="55"/>
+      <c r="T36" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U36" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="27">
+        <f t="shared" si="1"/>
+        <v>34</v>
+      </c>
+      <c r="B37" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="C37" s="59">
+        <f>864+1620+52</f>
+        <v>2536</v>
+      </c>
+      <c r="D37" s="59"/>
+      <c r="E37" s="59"/>
+      <c r="F37" s="59"/>
+      <c r="G37" s="59"/>
+      <c r="H37" s="59">
+        <v>3</v>
+      </c>
+      <c r="I37" s="59">
+        <v>2</v>
+      </c>
+      <c r="J37" s="60"/>
+      <c r="K37" s="61">
+        <f>2*6+2</f>
+        <v>14</v>
+      </c>
+      <c r="L37" s="62"/>
+      <c r="M37" s="63">
+        <v>151</v>
+      </c>
+      <c r="N37" s="64"/>
+      <c r="O37" s="65">
+        <v>38</v>
+      </c>
+      <c r="P37" s="66"/>
+      <c r="Q37" s="66">
+        <v>55</v>
+      </c>
+      <c r="R37" s="67"/>
+      <c r="S37" s="62"/>
+      <c r="T37" s="77">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="U37" s="77">
+        <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
+        <v>16699</v>
+      </c>
+      <c r="V37" s="77">
+        <f>U37/6</f>
+        <v>2783.1666666666665</v>
+      </c>
+      <c r="W37" s="50"/>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A38" s="27">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="B38" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" s="70">
+        <v>3</v>
+      </c>
+      <c r="D38" s="70"/>
+      <c r="E38" s="70"/>
+      <c r="F38" s="70"/>
+      <c r="G38" s="70"/>
+      <c r="H38" s="70"/>
+      <c r="I38" s="70"/>
+      <c r="J38" s="71"/>
+      <c r="K38" s="72"/>
+      <c r="L38" s="55"/>
+      <c r="M38" s="73"/>
+      <c r="N38" s="74"/>
+      <c r="O38" s="70"/>
+      <c r="P38" s="71"/>
+      <c r="Q38" s="71">
+        <v>2</v>
+      </c>
+      <c r="R38" s="72"/>
+      <c r="S38" s="55"/>
+      <c r="T38" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U38" s="75">
+        <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
+        <v>120</v>
+      </c>
+      <c r="V38" s="75">
+        <f>U38/24</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A39" s="27">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="B39" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="C39" s="78"/>
+      <c r="D39" s="78"/>
+      <c r="E39" s="78"/>
+      <c r="F39" s="78"/>
+      <c r="G39" s="78"/>
+      <c r="H39" s="78"/>
+      <c r="I39" s="78"/>
+      <c r="J39" s="79"/>
+      <c r="K39" s="80"/>
+      <c r="L39" s="55"/>
+      <c r="M39" s="73"/>
+      <c r="N39" s="74"/>
+      <c r="O39" s="70"/>
+      <c r="P39" s="71"/>
+      <c r="Q39" s="71"/>
+      <c r="R39" s="72"/>
+      <c r="S39" s="95"/>
+      <c r="T39" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U39" s="75">
+        <f>C39*24+M39*24+O39*24+Q39*24+T39</f>
+        <v>0</v>
+      </c>
+      <c r="V39" s="75">
+        <f>U39/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="27">
+        <f t="shared" si="1"/>
+        <v>37</v>
+      </c>
+      <c r="B40" s="42" t="s">
+        <v>21</v>
+      </c>
+      <c r="C40" s="59">
+        <f>252+46</f>
+        <v>298</v>
+      </c>
+      <c r="D40" s="59"/>
+      <c r="E40" s="59"/>
+      <c r="F40" s="59"/>
+      <c r="G40" s="59"/>
+      <c r="H40" s="59"/>
+      <c r="I40" s="59"/>
+      <c r="J40" s="60"/>
+      <c r="K40" s="61">
+        <v>20</v>
+      </c>
+      <c r="L40" s="62"/>
+      <c r="M40" s="63"/>
+      <c r="N40" s="64"/>
+      <c r="O40" s="65">
+        <v>1</v>
+      </c>
+      <c r="P40" s="66"/>
+      <c r="Q40" s="66">
+        <v>3</v>
+      </c>
+      <c r="R40" s="67"/>
+      <c r="S40" s="62"/>
+      <c r="T40" s="77">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="U40" s="77">
+        <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
+        <v>7268</v>
+      </c>
+      <c r="V40" s="77">
+        <f>U40/24</f>
+        <v>302.83333333333331</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="27">
+        <f t="shared" si="1"/>
+        <v>38</v>
+      </c>
+      <c r="B41" s="43" t="s">
+        <v>22</v>
+      </c>
+      <c r="C41" s="82">
+        <f>768+13</f>
+        <v>781</v>
+      </c>
+      <c r="D41" s="82"/>
+      <c r="E41" s="82"/>
+      <c r="F41" s="82"/>
+      <c r="G41" s="82"/>
+      <c r="H41" s="82"/>
+      <c r="I41" s="82"/>
+      <c r="J41" s="83"/>
+      <c r="K41" s="84"/>
+      <c r="L41" s="85"/>
+      <c r="M41" s="86"/>
+      <c r="N41" s="87"/>
+      <c r="O41" s="82">
+        <v>8</v>
+      </c>
+      <c r="P41" s="83"/>
+      <c r="Q41" s="83">
+        <v>16</v>
+      </c>
+      <c r="R41" s="84"/>
+      <c r="S41" s="85"/>
+      <c r="T41" s="88">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U41" s="88">
+        <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
+        <v>9660</v>
+      </c>
+      <c r="V41" s="88">
+        <f>U41/12</f>
+        <v>805</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="27">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+      <c r="B42" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C42" s="70"/>
+      <c r="D42" s="70"/>
+      <c r="E42" s="70"/>
+      <c r="F42" s="70"/>
+      <c r="G42" s="70"/>
+      <c r="H42" s="70"/>
+      <c r="I42" s="70"/>
+      <c r="J42" s="71"/>
+      <c r="K42" s="72"/>
+      <c r="L42" s="55"/>
+      <c r="M42" s="73"/>
+      <c r="N42" s="74"/>
+      <c r="O42" s="70"/>
+      <c r="P42" s="71"/>
+      <c r="Q42" s="71"/>
+      <c r="R42" s="72"/>
+      <c r="S42" s="55"/>
+      <c r="T42" s="75"/>
+      <c r="U42" s="75"/>
+      <c r="V42" s="75"/>
+    </row>
+    <row r="43" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="27">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="B43" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="C43" s="65">
+        <f>13932+19764+5144</f>
+        <v>38840</v>
+      </c>
+      <c r="D43" s="65"/>
+      <c r="E43" s="65"/>
+      <c r="F43" s="65"/>
+      <c r="G43" s="65"/>
+      <c r="H43" s="65">
+        <v>5</v>
+      </c>
+      <c r="I43" s="65">
+        <v>12</v>
+      </c>
+      <c r="J43" s="66">
+        <f>6*6+2</f>
+        <v>38</v>
+      </c>
+      <c r="K43" s="67">
+        <f>95*6+1</f>
+        <v>571</v>
+      </c>
+      <c r="L43" s="62"/>
+      <c r="M43" s="63">
+        <v>260</v>
+      </c>
+      <c r="N43" s="64"/>
+      <c r="O43" s="65">
+        <v>466</v>
+      </c>
+      <c r="P43" s="66"/>
+      <c r="Q43" s="66">
+        <v>541</v>
+      </c>
+      <c r="R43" s="67"/>
+      <c r="S43" s="62"/>
+      <c r="T43" s="77">
+        <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
+        <v>626</v>
+      </c>
+      <c r="U43" s="77">
+        <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
+        <v>241268</v>
+      </c>
+      <c r="V43" s="77">
+        <f>U43/6</f>
+        <v>40211.333333333336</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="27">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+      <c r="B44" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="70"/>
+      <c r="D44" s="70"/>
+      <c r="E44" s="70"/>
+      <c r="F44" s="70"/>
+      <c r="G44" s="70"/>
+      <c r="H44" s="70"/>
+      <c r="I44" s="70"/>
+      <c r="J44" s="71"/>
+      <c r="K44" s="72"/>
+      <c r="L44" s="55"/>
+      <c r="M44" s="73"/>
+      <c r="N44" s="74"/>
+      <c r="O44" s="70"/>
+      <c r="P44" s="71"/>
+      <c r="Q44" s="71"/>
+      <c r="R44" s="72"/>
+      <c r="S44" s="55"/>
+      <c r="T44" s="75"/>
+      <c r="U44" s="75"/>
+      <c r="V44" s="75"/>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A45" s="27">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="B45" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="70">
+        <v>5</v>
+      </c>
+      <c r="D45" s="70"/>
+      <c r="E45" s="70"/>
+      <c r="F45" s="70"/>
+      <c r="G45" s="70"/>
+      <c r="H45" s="70"/>
+      <c r="I45" s="70"/>
+      <c r="J45" s="71"/>
+      <c r="K45" s="72"/>
+      <c r="L45" s="55"/>
+      <c r="M45" s="73"/>
+      <c r="N45" s="74"/>
+      <c r="O45" s="70"/>
+      <c r="P45" s="71"/>
+      <c r="Q45" s="71"/>
+      <c r="R45" s="72"/>
+      <c r="S45" s="55"/>
+      <c r="T45" s="75">
+        <f t="shared" ref="T45:T54" si="7">H45+I45+J45+K45+N45+P45+R45</f>
+        <v>0</v>
+      </c>
+      <c r="U45" s="75">
+        <f>C45*24+M45*24+O45*24+Q45*24+T45</f>
+        <v>120</v>
+      </c>
+      <c r="V45" s="75">
+        <f>U45/24</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A46" s="27">
+        <f t="shared" si="1"/>
+        <v>43</v>
+      </c>
+      <c r="B46" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="C46" s="70"/>
+      <c r="D46" s="70"/>
+      <c r="E46" s="70"/>
+      <c r="F46" s="70"/>
+      <c r="G46" s="70"/>
+      <c r="H46" s="70"/>
+      <c r="I46" s="70"/>
+      <c r="J46" s="71"/>
+      <c r="K46" s="72"/>
+      <c r="L46" s="55"/>
+      <c r="M46" s="73"/>
+      <c r="N46" s="74"/>
+      <c r="O46" s="70"/>
+      <c r="P46" s="71"/>
+      <c r="Q46" s="71"/>
+      <c r="R46" s="72"/>
+      <c r="S46" s="55"/>
+      <c r="T46" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U46" s="75">
+        <f t="shared" ref="U46:U50" si="8">C46*24+M46*24+O46*24+Q46*24+T46</f>
+        <v>0</v>
+      </c>
+      <c r="V46" s="75">
+        <f t="shared" ref="V46:V54" si="9">U46/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="27">
+        <f t="shared" si="1"/>
+        <v>44</v>
+      </c>
+      <c r="B47" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="C47" s="65">
+        <f>89+648+324+88+432+83+103+324+432+106</f>
+        <v>2629</v>
+      </c>
+      <c r="D47" s="65"/>
+      <c r="E47" s="65"/>
+      <c r="F47" s="65"/>
+      <c r="G47" s="65"/>
+      <c r="H47" s="65">
+        <v>1</v>
+      </c>
+      <c r="I47" s="65"/>
+      <c r="J47" s="66"/>
+      <c r="K47" s="67">
+        <v>5</v>
+      </c>
+      <c r="L47" s="62"/>
+      <c r="M47" s="63">
+        <v>2</v>
+      </c>
+      <c r="N47" s="64"/>
+      <c r="O47" s="65">
+        <v>15</v>
+      </c>
+      <c r="P47" s="66"/>
+      <c r="Q47" s="66">
+        <v>5</v>
+      </c>
+      <c r="R47" s="67">
+        <v>3</v>
+      </c>
+      <c r="S47" s="62"/>
+      <c r="T47" s="77">
+        <f t="shared" si="7"/>
+        <v>9</v>
+      </c>
+      <c r="U47" s="77">
+        <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
+        <v>15915</v>
+      </c>
+      <c r="V47" s="77">
+        <f>U47/6</f>
+        <v>2652.5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A48" s="27">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="B48" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C48" s="70"/>
+      <c r="D48" s="70"/>
+      <c r="E48" s="70"/>
+      <c r="F48" s="70"/>
+      <c r="G48" s="70"/>
+      <c r="H48" s="70">
+        <v>24</v>
+      </c>
+      <c r="I48" s="70"/>
+      <c r="J48" s="71"/>
+      <c r="K48" s="72"/>
+      <c r="L48" s="55"/>
+      <c r="M48" s="73"/>
+      <c r="N48" s="74"/>
+      <c r="O48" s="70"/>
+      <c r="P48" s="71"/>
+      <c r="Q48" s="71"/>
+      <c r="R48" s="72"/>
+      <c r="S48" s="55"/>
+      <c r="T48" s="75">
+        <f t="shared" si="7"/>
+        <v>24</v>
+      </c>
+      <c r="U48" s="75">
+        <f t="shared" si="8"/>
+        <v>24</v>
+      </c>
+      <c r="V48" s="75">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A49" s="27">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="B49" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C49" s="70"/>
+      <c r="D49" s="70"/>
+      <c r="E49" s="70"/>
+      <c r="F49" s="70"/>
+      <c r="G49" s="70"/>
+      <c r="H49" s="70"/>
+      <c r="I49" s="70"/>
+      <c r="J49" s="71"/>
+      <c r="K49" s="72"/>
+      <c r="L49" s="55"/>
+      <c r="M49" s="73"/>
+      <c r="N49" s="74"/>
+      <c r="O49" s="70"/>
+      <c r="P49" s="71"/>
+      <c r="Q49" s="71"/>
+      <c r="R49" s="72"/>
+      <c r="S49" s="55"/>
+      <c r="T49" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U49" s="75">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V49" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A50" s="27">
+        <f t="shared" si="1"/>
+        <v>47</v>
+      </c>
+      <c r="B50" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="C50" s="70"/>
+      <c r="D50" s="70"/>
+      <c r="E50" s="70"/>
+      <c r="F50" s="70"/>
+      <c r="G50" s="70"/>
+      <c r="H50" s="70"/>
+      <c r="I50" s="70"/>
+      <c r="J50" s="71"/>
+      <c r="K50" s="72"/>
+      <c r="L50" s="55"/>
+      <c r="M50" s="73"/>
+      <c r="N50" s="74"/>
+      <c r="O50" s="70"/>
+      <c r="P50" s="71"/>
+      <c r="Q50" s="71"/>
+      <c r="R50" s="72"/>
+      <c r="S50" s="55"/>
+      <c r="T50" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U50" s="75">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V50" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="27">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+      <c r="B51" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="C51" s="65">
+        <v>34</v>
+      </c>
+      <c r="D51" s="65"/>
+      <c r="E51" s="65"/>
+      <c r="F51" s="65"/>
+      <c r="G51" s="65"/>
+      <c r="H51" s="65"/>
+      <c r="I51" s="65"/>
+      <c r="J51" s="66"/>
+      <c r="K51" s="67"/>
+      <c r="L51" s="62"/>
+      <c r="M51" s="63"/>
+      <c r="N51" s="64"/>
+      <c r="O51" s="65"/>
+      <c r="P51" s="66"/>
+      <c r="Q51" s="66"/>
+      <c r="R51" s="67"/>
+      <c r="S51" s="62"/>
+      <c r="T51" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U51" s="77">
+        <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
+        <v>204</v>
+      </c>
+      <c r="V51" s="77">
+        <f>U51/6</f>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A52" s="27">
+        <f t="shared" si="1"/>
+        <v>49</v>
+      </c>
+      <c r="B52" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="C52" s="70"/>
+      <c r="D52" s="70"/>
+      <c r="E52" s="70"/>
+      <c r="F52" s="70"/>
+      <c r="G52" s="70"/>
+      <c r="H52" s="70"/>
+      <c r="I52" s="70"/>
+      <c r="J52" s="71"/>
+      <c r="K52" s="72"/>
+      <c r="L52" s="55"/>
+      <c r="M52" s="73"/>
+      <c r="N52" s="74"/>
+      <c r="O52" s="70"/>
+      <c r="P52" s="71"/>
+      <c r="Q52" s="71"/>
+      <c r="R52" s="72"/>
+      <c r="S52" s="55"/>
+      <c r="T52" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U52" s="75">
+        <f t="shared" ref="U52:U54" si="10">C52*24+M52*24+O52*24+Q52*24+T52</f>
+        <v>0</v>
+      </c>
+      <c r="V52" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A53" s="27">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="B53" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C53" s="70">
+        <v>7</v>
+      </c>
+      <c r="D53" s="70"/>
+      <c r="E53" s="70"/>
+      <c r="F53" s="70"/>
+      <c r="G53" s="70"/>
+      <c r="H53" s="70"/>
+      <c r="I53" s="70"/>
+      <c r="J53" s="71"/>
+      <c r="K53" s="72"/>
+      <c r="L53" s="55"/>
+      <c r="M53" s="73"/>
+      <c r="N53" s="74"/>
+      <c r="O53" s="70"/>
+      <c r="P53" s="71"/>
+      <c r="Q53" s="71"/>
+      <c r="R53" s="72"/>
+      <c r="S53" s="55"/>
+      <c r="T53" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U53" s="75">
+        <f t="shared" si="10"/>
+        <v>168</v>
+      </c>
+      <c r="V53" s="75">
+        <f t="shared" si="9"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A54" s="27">
+        <f t="shared" si="1"/>
+        <v>51</v>
+      </c>
+      <c r="B54" s="26"/>
+      <c r="C54" s="70"/>
+      <c r="D54" s="70"/>
+      <c r="E54" s="70"/>
+      <c r="F54" s="70"/>
+      <c r="G54" s="70"/>
+      <c r="H54" s="70"/>
+      <c r="I54" s="70"/>
+      <c r="J54" s="71"/>
+      <c r="K54" s="72"/>
+      <c r="L54" s="55"/>
+      <c r="M54" s="73"/>
+      <c r="N54" s="74"/>
+      <c r="O54" s="70"/>
+      <c r="P54" s="71"/>
+      <c r="Q54" s="71"/>
+      <c r="R54" s="72"/>
+      <c r="S54" s="55"/>
+      <c r="T54" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U54" s="75">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V54" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A55" s="27">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="B55" s="26"/>
+      <c r="C55" s="70"/>
+      <c r="D55" s="70"/>
+      <c r="E55" s="70"/>
+      <c r="F55" s="70"/>
+      <c r="G55" s="70"/>
+      <c r="H55" s="70"/>
+      <c r="I55" s="70"/>
+      <c r="J55" s="71"/>
+      <c r="K55" s="72"/>
+      <c r="L55" s="55"/>
+      <c r="M55" s="73"/>
+      <c r="N55" s="74"/>
+      <c r="O55" s="70"/>
+      <c r="P55" s="71"/>
+      <c r="Q55" s="71"/>
+      <c r="R55" s="72"/>
+      <c r="S55" s="55"/>
+      <c r="T55" s="75"/>
+      <c r="U55" s="75"/>
+      <c r="V55" s="75"/>
+    </row>
+    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A56" s="27">
+        <f t="shared" si="1"/>
+        <v>53</v>
+      </c>
+      <c r="B56" s="26"/>
+      <c r="C56" s="70"/>
+      <c r="D56" s="70"/>
+      <c r="E56" s="70"/>
+      <c r="F56" s="70"/>
+      <c r="G56" s="70"/>
+      <c r="H56" s="70"/>
+      <c r="I56" s="70"/>
+      <c r="J56" s="71"/>
+      <c r="K56" s="72"/>
+      <c r="L56" s="55"/>
+      <c r="M56" s="73"/>
+      <c r="N56" s="74"/>
+      <c r="O56" s="70"/>
+      <c r="P56" s="71"/>
+      <c r="Q56" s="71"/>
+      <c r="R56" s="72"/>
+      <c r="S56" s="55"/>
+      <c r="T56" s="75"/>
+      <c r="U56" s="75"/>
+      <c r="V56" s="75"/>
+    </row>
+    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A57" s="27">
+        <f t="shared" si="1"/>
+        <v>54</v>
+      </c>
+      <c r="B57" s="26"/>
+      <c r="C57" s="70"/>
+      <c r="D57" s="70"/>
+      <c r="E57" s="70"/>
+      <c r="F57" s="70"/>
+      <c r="G57" s="70"/>
+      <c r="H57" s="70"/>
+      <c r="I57" s="70"/>
+      <c r="J57" s="71"/>
+      <c r="K57" s="72"/>
+      <c r="L57" s="55"/>
+      <c r="M57" s="73"/>
+      <c r="N57" s="74"/>
+      <c r="O57" s="70"/>
+      <c r="P57" s="71"/>
+      <c r="Q57" s="71"/>
+      <c r="R57" s="72"/>
+      <c r="S57" s="55"/>
+      <c r="T57" s="75"/>
+      <c r="U57" s="75"/>
+      <c r="V57" s="75"/>
+    </row>
+    <row r="58" spans="1:22" s="15" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B58" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="C58" s="2">
+        <f>SUM(C7:C57)</f>
+        <v>48768</v>
+      </c>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2">
+        <f t="shared" ref="F58:K58" si="11">SUM(F7:F57)</f>
+        <v>0</v>
+      </c>
+      <c r="G58" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="H58" s="2">
+        <f t="shared" si="11"/>
+        <v>1192</v>
+      </c>
+      <c r="I58" s="6">
+        <f t="shared" si="11"/>
+        <v>44</v>
+      </c>
+      <c r="J58" s="6">
+        <f t="shared" si="11"/>
+        <v>38</v>
+      </c>
+      <c r="K58" s="6">
+        <f t="shared" si="11"/>
+        <v>619</v>
+      </c>
+      <c r="M58" s="5">
+        <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
+        <v>434</v>
+      </c>
+      <c r="N58" s="5">
+        <f t="shared" si="12"/>
+        <v>2</v>
+      </c>
+      <c r="O58" s="5">
+        <f t="shared" si="12"/>
+        <v>549</v>
+      </c>
+      <c r="P58" s="5">
+        <f t="shared" si="12"/>
+        <v>30</v>
+      </c>
+      <c r="Q58" s="5">
+        <f t="shared" si="12"/>
+        <v>655</v>
+      </c>
+      <c r="R58" s="5">
+        <f t="shared" si="12"/>
+        <v>6</v>
+      </c>
+      <c r="S58" s="55"/>
+      <c r="T58" s="4">
+        <f>SUM(T7:T57)</f>
+        <v>1931</v>
+      </c>
+      <c r="U58" s="90">
+        <f>SUM(U7:U57)</f>
+        <v>381719</v>
+      </c>
+      <c r="V58" s="4">
+        <f>SUM(V7:V57)</f>
+        <v>50568.208333333336</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="60" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="C60" s="112" t="s">
+        <v>41</v>
+      </c>
+      <c r="D60" s="113"/>
+      <c r="E60" s="113"/>
+      <c r="F60" s="113"/>
+      <c r="G60" s="113"/>
+      <c r="H60" s="113"/>
+      <c r="I60" s="113"/>
+      <c r="J60" s="113"/>
+      <c r="K60" s="114"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -42606,21 +45742,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="114" t="s">
+      <c r="I1" s="115" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="114"/>
-      <c r="K1" s="114"/>
-      <c r="L1" s="114"/>
-      <c r="M1" s="114"/>
-      <c r="N1" s="114"/>
-      <c r="O1" s="114"/>
-      <c r="P1" s="114"/>
-      <c r="Q1" s="114"/>
-      <c r="R1" s="114"/>
-      <c r="S1" s="114"/>
-      <c r="T1" s="114"/>
-      <c r="U1" s="114"/>
+      <c r="J1" s="115"/>
+      <c r="K1" s="115"/>
+      <c r="L1" s="115"/>
+      <c r="M1" s="115"/>
+      <c r="N1" s="115"/>
+      <c r="O1" s="115"/>
+      <c r="P1" s="115"/>
+      <c r="Q1" s="115"/>
+      <c r="R1" s="115"/>
+      <c r="S1" s="115"/>
+      <c r="T1" s="115"/>
+      <c r="U1" s="115"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -42632,17 +45768,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="115" t="s">
+      <c r="C4" s="116" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="115"/>
-      <c r="E4" s="115"/>
-      <c r="F4" s="115"/>
-      <c r="G4" s="115"/>
-      <c r="H4" s="115"/>
-      <c r="I4" s="115"/>
-      <c r="J4" s="116"/>
-      <c r="K4" s="117"/>
+      <c r="D4" s="116"/>
+      <c r="E4" s="116"/>
+      <c r="F4" s="116"/>
+      <c r="G4" s="116"/>
+      <c r="H4" s="116"/>
+      <c r="I4" s="116"/>
+      <c r="J4" s="117"/>
+      <c r="K4" s="118"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -42662,13 +45798,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="118" t="s">
+      <c r="T4" s="119" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="124" t="s">
+      <c r="U4" s="125" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="107" t="s">
+      <c r="V4" s="108" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -42708,10 +45844,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="122" t="s">
+      <c r="J5" s="123" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="123"/>
+      <c r="K5" s="124"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -42719,9 +45855,9 @@
       <c r="Q5" s="97"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="119"/>
-      <c r="U5" s="125"/>
-      <c r="V5" s="108"/>
+      <c r="T5" s="120"/>
+      <c r="U5" s="126"/>
+      <c r="V5" s="109"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -45421,17 +48557,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="111" t="s">
+      <c r="C60" s="112" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="112"/>
-      <c r="E60" s="112"/>
-      <c r="F60" s="112"/>
-      <c r="G60" s="112"/>
-      <c r="H60" s="112"/>
-      <c r="I60" s="112"/>
-      <c r="J60" s="112"/>
-      <c r="K60" s="113"/>
+      <c r="D60" s="113"/>
+      <c r="E60" s="113"/>
+      <c r="F60" s="113"/>
+      <c r="G60" s="113"/>
+      <c r="H60" s="113"/>
+      <c r="I60" s="113"/>
+      <c r="J60" s="113"/>
+      <c r="K60" s="114"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -45740,21 +48876,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="114" t="s">
+      <c r="I1" s="115" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="114"/>
-      <c r="K1" s="114"/>
-      <c r="L1" s="114"/>
-      <c r="M1" s="114"/>
-      <c r="N1" s="114"/>
-      <c r="O1" s="114"/>
-      <c r="P1" s="114"/>
-      <c r="Q1" s="114"/>
-      <c r="R1" s="114"/>
-      <c r="S1" s="114"/>
-      <c r="T1" s="114"/>
-      <c r="U1" s="114"/>
+      <c r="J1" s="115"/>
+      <c r="K1" s="115"/>
+      <c r="L1" s="115"/>
+      <c r="M1" s="115"/>
+      <c r="N1" s="115"/>
+      <c r="O1" s="115"/>
+      <c r="P1" s="115"/>
+      <c r="Q1" s="115"/>
+      <c r="R1" s="115"/>
+      <c r="S1" s="115"/>
+      <c r="T1" s="115"/>
+      <c r="U1" s="115"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -45766,17 +48902,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="115" t="s">
+      <c r="C4" s="116" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="115"/>
-      <c r="E4" s="115"/>
-      <c r="F4" s="115"/>
-      <c r="G4" s="115"/>
-      <c r="H4" s="115"/>
-      <c r="I4" s="115"/>
-      <c r="J4" s="116"/>
-      <c r="K4" s="117"/>
+      <c r="D4" s="116"/>
+      <c r="E4" s="116"/>
+      <c r="F4" s="116"/>
+      <c r="G4" s="116"/>
+      <c r="H4" s="116"/>
+      <c r="I4" s="116"/>
+      <c r="J4" s="117"/>
+      <c r="K4" s="118"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -45796,13 +48932,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="118" t="s">
+      <c r="T4" s="119" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="124" t="s">
+      <c r="U4" s="125" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="107" t="s">
+      <c r="V4" s="108" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -45842,10 +48978,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="122" t="s">
+      <c r="J5" s="123" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="123"/>
+      <c r="K5" s="124"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -45853,9 +48989,9 @@
       <c r="Q5" s="97"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="119"/>
-      <c r="U5" s="125"/>
-      <c r="V5" s="108"/>
+      <c r="T5" s="120"/>
+      <c r="U5" s="126"/>
+      <c r="V5" s="109"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -48555,17 +51691,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="111" t="s">
+      <c r="C60" s="112" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="112"/>
-      <c r="E60" s="112"/>
-      <c r="F60" s="112"/>
-      <c r="G60" s="112"/>
-      <c r="H60" s="112"/>
-      <c r="I60" s="112"/>
-      <c r="J60" s="112"/>
-      <c r="K60" s="113"/>
+      <c r="D60" s="113"/>
+      <c r="E60" s="113"/>
+      <c r="F60" s="113"/>
+      <c r="G60" s="113"/>
+      <c r="H60" s="113"/>
+      <c r="I60" s="113"/>
+      <c r="J60" s="113"/>
+      <c r="K60" s="114"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -48874,21 +52010,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="114" t="s">
+      <c r="I1" s="115" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="114"/>
-      <c r="K1" s="114"/>
-      <c r="L1" s="114"/>
-      <c r="M1" s="114"/>
-      <c r="N1" s="114"/>
-      <c r="O1" s="114"/>
-      <c r="P1" s="114"/>
-      <c r="Q1" s="114"/>
-      <c r="R1" s="114"/>
-      <c r="S1" s="114"/>
-      <c r="T1" s="114"/>
-      <c r="U1" s="114"/>
+      <c r="J1" s="115"/>
+      <c r="K1" s="115"/>
+      <c r="L1" s="115"/>
+      <c r="M1" s="115"/>
+      <c r="N1" s="115"/>
+      <c r="O1" s="115"/>
+      <c r="P1" s="115"/>
+      <c r="Q1" s="115"/>
+      <c r="R1" s="115"/>
+      <c r="S1" s="115"/>
+      <c r="T1" s="115"/>
+      <c r="U1" s="115"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -48900,17 +52036,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="115" t="s">
+      <c r="C4" s="116" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="115"/>
-      <c r="E4" s="115"/>
-      <c r="F4" s="115"/>
-      <c r="G4" s="115"/>
-      <c r="H4" s="115"/>
-      <c r="I4" s="115"/>
-      <c r="J4" s="116"/>
-      <c r="K4" s="117"/>
+      <c r="D4" s="116"/>
+      <c r="E4" s="116"/>
+      <c r="F4" s="116"/>
+      <c r="G4" s="116"/>
+      <c r="H4" s="116"/>
+      <c r="I4" s="116"/>
+      <c r="J4" s="117"/>
+      <c r="K4" s="118"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -48930,13 +52066,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="118" t="s">
+      <c r="T4" s="119" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="124" t="s">
+      <c r="U4" s="125" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="107" t="s">
+      <c r="V4" s="108" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -48976,10 +52112,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="122" t="s">
+      <c r="J5" s="123" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="123"/>
+      <c r="K5" s="124"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -48987,9 +52123,9 @@
       <c r="Q5" s="97"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="119"/>
-      <c r="U5" s="125"/>
-      <c r="V5" s="108"/>
+      <c r="T5" s="120"/>
+      <c r="U5" s="126"/>
+      <c r="V5" s="109"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -51679,17 +54815,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="111" t="s">
+      <c r="C60" s="112" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="112"/>
-      <c r="E60" s="112"/>
-      <c r="F60" s="112"/>
-      <c r="G60" s="112"/>
-      <c r="H60" s="112"/>
-      <c r="I60" s="112"/>
-      <c r="J60" s="112"/>
-      <c r="K60" s="113"/>
+      <c r="D60" s="113"/>
+      <c r="E60" s="113"/>
+      <c r="F60" s="113"/>
+      <c r="G60" s="113"/>
+      <c r="H60" s="113"/>
+      <c r="I60" s="113"/>
+      <c r="J60" s="113"/>
+      <c r="K60" s="114"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -51998,21 +55134,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="114" t="s">
+      <c r="I1" s="115" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="114"/>
-      <c r="K1" s="114"/>
-      <c r="L1" s="114"/>
-      <c r="M1" s="114"/>
-      <c r="N1" s="114"/>
-      <c r="O1" s="114"/>
-      <c r="P1" s="114"/>
-      <c r="Q1" s="114"/>
-      <c r="R1" s="114"/>
-      <c r="S1" s="114"/>
-      <c r="T1" s="114"/>
-      <c r="U1" s="114"/>
+      <c r="J1" s="115"/>
+      <c r="K1" s="115"/>
+      <c r="L1" s="115"/>
+      <c r="M1" s="115"/>
+      <c r="N1" s="115"/>
+      <c r="O1" s="115"/>
+      <c r="P1" s="115"/>
+      <c r="Q1" s="115"/>
+      <c r="R1" s="115"/>
+      <c r="S1" s="115"/>
+      <c r="T1" s="115"/>
+      <c r="U1" s="115"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -52024,17 +55160,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="115" t="s">
+      <c r="C4" s="116" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="115"/>
-      <c r="E4" s="115"/>
-      <c r="F4" s="115"/>
-      <c r="G4" s="115"/>
-      <c r="H4" s="115"/>
-      <c r="I4" s="115"/>
-      <c r="J4" s="116"/>
-      <c r="K4" s="117"/>
+      <c r="D4" s="116"/>
+      <c r="E4" s="116"/>
+      <c r="F4" s="116"/>
+      <c r="G4" s="116"/>
+      <c r="H4" s="116"/>
+      <c r="I4" s="116"/>
+      <c r="J4" s="117"/>
+      <c r="K4" s="118"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -52054,13 +55190,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="118" t="s">
+      <c r="T4" s="119" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="124" t="s">
+      <c r="U4" s="125" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="107" t="s">
+      <c r="V4" s="108" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -52100,10 +55236,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="122" t="s">
+      <c r="J5" s="123" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="123"/>
+      <c r="K5" s="124"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -52111,9 +55247,9 @@
       <c r="Q5" s="98"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="119"/>
-      <c r="U5" s="125"/>
-      <c r="V5" s="108"/>
+      <c r="T5" s="120"/>
+      <c r="U5" s="126"/>
+      <c r="V5" s="109"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -54828,17 +57964,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="111" t="s">
+      <c r="C60" s="112" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="112"/>
-      <c r="E60" s="112"/>
-      <c r="F60" s="112"/>
-      <c r="G60" s="112"/>
-      <c r="H60" s="112"/>
-      <c r="I60" s="112"/>
-      <c r="J60" s="112"/>
-      <c r="K60" s="113"/>
+      <c r="D60" s="113"/>
+      <c r="E60" s="113"/>
+      <c r="F60" s="113"/>
+      <c r="G60" s="113"/>
+      <c r="H60" s="113"/>
+      <c r="I60" s="113"/>
+      <c r="J60" s="113"/>
+      <c r="K60" s="114"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -55147,21 +58283,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="114" t="s">
+      <c r="I1" s="115" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="114"/>
-      <c r="K1" s="114"/>
-      <c r="L1" s="114"/>
-      <c r="M1" s="114"/>
-      <c r="N1" s="114"/>
-      <c r="O1" s="114"/>
-      <c r="P1" s="114"/>
-      <c r="Q1" s="114"/>
-      <c r="R1" s="114"/>
-      <c r="S1" s="114"/>
-      <c r="T1" s="114"/>
-      <c r="U1" s="114"/>
+      <c r="J1" s="115"/>
+      <c r="K1" s="115"/>
+      <c r="L1" s="115"/>
+      <c r="M1" s="115"/>
+      <c r="N1" s="115"/>
+      <c r="O1" s="115"/>
+      <c r="P1" s="115"/>
+      <c r="Q1" s="115"/>
+      <c r="R1" s="115"/>
+      <c r="S1" s="115"/>
+      <c r="T1" s="115"/>
+      <c r="U1" s="115"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -55173,17 +58309,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="115" t="s">
+      <c r="C4" s="116" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="115"/>
-      <c r="E4" s="115"/>
-      <c r="F4" s="115"/>
-      <c r="G4" s="115"/>
-      <c r="H4" s="115"/>
-      <c r="I4" s="115"/>
-      <c r="J4" s="116"/>
-      <c r="K4" s="117"/>
+      <c r="D4" s="116"/>
+      <c r="E4" s="116"/>
+      <c r="F4" s="116"/>
+      <c r="G4" s="116"/>
+      <c r="H4" s="116"/>
+      <c r="I4" s="116"/>
+      <c r="J4" s="117"/>
+      <c r="K4" s="118"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -55203,13 +58339,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="118" t="s">
+      <c r="T4" s="119" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="124" t="s">
+      <c r="U4" s="125" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="107" t="s">
+      <c r="V4" s="108" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -55249,10 +58385,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="122" t="s">
+      <c r="J5" s="123" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="123"/>
+      <c r="K5" s="124"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -55260,9 +58396,9 @@
       <c r="Q5" s="98"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="119"/>
-      <c r="U5" s="125"/>
-      <c r="V5" s="108"/>
+      <c r="T5" s="120"/>
+      <c r="U5" s="126"/>
+      <c r="V5" s="109"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -57967,17 +61103,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="111" t="s">
+      <c r="C60" s="112" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="112"/>
-      <c r="E60" s="112"/>
-      <c r="F60" s="112"/>
-      <c r="G60" s="112"/>
-      <c r="H60" s="112"/>
-      <c r="I60" s="112"/>
-      <c r="J60" s="112"/>
-      <c r="K60" s="113"/>
+      <c r="D60" s="113"/>
+      <c r="E60" s="113"/>
+      <c r="F60" s="113"/>
+      <c r="G60" s="113"/>
+      <c r="H60" s="113"/>
+      <c r="I60" s="113"/>
+      <c r="J60" s="113"/>
+      <c r="K60" s="114"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -58286,21 +61422,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="114" t="s">
+      <c r="I1" s="115" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="114"/>
-      <c r="K1" s="114"/>
-      <c r="L1" s="114"/>
-      <c r="M1" s="114"/>
-      <c r="N1" s="114"/>
-      <c r="O1" s="114"/>
-      <c r="P1" s="114"/>
-      <c r="Q1" s="114"/>
-      <c r="R1" s="114"/>
-      <c r="S1" s="114"/>
-      <c r="T1" s="114"/>
-      <c r="U1" s="114"/>
+      <c r="J1" s="115"/>
+      <c r="K1" s="115"/>
+      <c r="L1" s="115"/>
+      <c r="M1" s="115"/>
+      <c r="N1" s="115"/>
+      <c r="O1" s="115"/>
+      <c r="P1" s="115"/>
+      <c r="Q1" s="115"/>
+      <c r="R1" s="115"/>
+      <c r="S1" s="115"/>
+      <c r="T1" s="115"/>
+      <c r="U1" s="115"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -58312,17 +61448,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="115" t="s">
+      <c r="C4" s="116" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="115"/>
-      <c r="E4" s="115"/>
-      <c r="F4" s="115"/>
-      <c r="G4" s="115"/>
-      <c r="H4" s="115"/>
-      <c r="I4" s="115"/>
-      <c r="J4" s="116"/>
-      <c r="K4" s="117"/>
+      <c r="D4" s="116"/>
+      <c r="E4" s="116"/>
+      <c r="F4" s="116"/>
+      <c r="G4" s="116"/>
+      <c r="H4" s="116"/>
+      <c r="I4" s="116"/>
+      <c r="J4" s="117"/>
+      <c r="K4" s="118"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -58342,13 +61478,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="118" t="s">
+      <c r="T4" s="119" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="124" t="s">
+      <c r="U4" s="125" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="107" t="s">
+      <c r="V4" s="108" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -58388,10 +61524,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="122" t="s">
+      <c r="J5" s="123" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="123"/>
+      <c r="K5" s="124"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -58399,9 +61535,9 @@
       <c r="Q5" s="98"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="119"/>
-      <c r="U5" s="125"/>
-      <c r="V5" s="108"/>
+      <c r="T5" s="120"/>
+      <c r="U5" s="126"/>
+      <c r="V5" s="109"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -61103,17 +64239,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="111" t="s">
+      <c r="C60" s="112" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="112"/>
-      <c r="E60" s="112"/>
-      <c r="F60" s="112"/>
-      <c r="G60" s="112"/>
-      <c r="H60" s="112"/>
-      <c r="I60" s="112"/>
-      <c r="J60" s="112"/>
-      <c r="K60" s="113"/>
+      <c r="D60" s="113"/>
+      <c r="E60" s="113"/>
+      <c r="F60" s="113"/>
+      <c r="G60" s="113"/>
+      <c r="H60" s="113"/>
+      <c r="I60" s="113"/>
+      <c r="J60" s="113"/>
+      <c r="K60" s="114"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -61422,21 +64558,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="114" t="s">
+      <c r="I1" s="115" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="114"/>
-      <c r="K1" s="114"/>
-      <c r="L1" s="114"/>
-      <c r="M1" s="114"/>
-      <c r="N1" s="114"/>
-      <c r="O1" s="114"/>
-      <c r="P1" s="114"/>
-      <c r="Q1" s="114"/>
-      <c r="R1" s="114"/>
-      <c r="S1" s="114"/>
-      <c r="T1" s="114"/>
-      <c r="U1" s="114"/>
+      <c r="J1" s="115"/>
+      <c r="K1" s="115"/>
+      <c r="L1" s="115"/>
+      <c r="M1" s="115"/>
+      <c r="N1" s="115"/>
+      <c r="O1" s="115"/>
+      <c r="P1" s="115"/>
+      <c r="Q1" s="115"/>
+      <c r="R1" s="115"/>
+      <c r="S1" s="115"/>
+      <c r="T1" s="115"/>
+      <c r="U1" s="115"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -61448,17 +64584,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="115" t="s">
+      <c r="C4" s="116" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="115"/>
-      <c r="E4" s="115"/>
-      <c r="F4" s="115"/>
-      <c r="G4" s="115"/>
-      <c r="H4" s="115"/>
-      <c r="I4" s="115"/>
-      <c r="J4" s="116"/>
-      <c r="K4" s="117"/>
+      <c r="D4" s="116"/>
+      <c r="E4" s="116"/>
+      <c r="F4" s="116"/>
+      <c r="G4" s="116"/>
+      <c r="H4" s="116"/>
+      <c r="I4" s="116"/>
+      <c r="J4" s="117"/>
+      <c r="K4" s="118"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -61478,13 +64614,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="118" t="s">
+      <c r="T4" s="119" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="124" t="s">
+      <c r="U4" s="125" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="107" t="s">
+      <c r="V4" s="108" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -61524,10 +64660,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="122" t="s">
+      <c r="J5" s="123" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="123"/>
+      <c r="K5" s="124"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -61535,9 +64671,9 @@
       <c r="Q5" s="98"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="119"/>
-      <c r="U5" s="125"/>
-      <c r="V5" s="108"/>
+      <c r="T5" s="120"/>
+      <c r="U5" s="126"/>
+      <c r="V5" s="109"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -64249,17 +67385,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="111" t="s">
+      <c r="C60" s="112" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="112"/>
-      <c r="E60" s="112"/>
-      <c r="F60" s="112"/>
-      <c r="G60" s="112"/>
-      <c r="H60" s="112"/>
-      <c r="I60" s="112"/>
-      <c r="J60" s="112"/>
-      <c r="K60" s="113"/>
+      <c r="D60" s="113"/>
+      <c r="E60" s="113"/>
+      <c r="F60" s="113"/>
+      <c r="G60" s="113"/>
+      <c r="H60" s="113"/>
+      <c r="I60" s="113"/>
+      <c r="J60" s="113"/>
+      <c r="K60" s="114"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>

--- a/GBDS AUGUST FILES 2026/INVENTORY COUNT SHEET - AUGUST 2026.xlsx
+++ b/GBDS AUGUST FILES 2026/INVENTORY COUNT SHEET - AUGUST 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS AUGUST FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{100533F5-82D9-433F-984E-6A9AD0DA9CC6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ABA0F3D-8DBF-4E45-B47C-5C3724BD110E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="11" activeTab="20" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="12" activeTab="21" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
   </bookViews>
   <sheets>
     <sheet name="SAMPLE" sheetId="32" r:id="rId1"/>
@@ -34,6 +34,7 @@
     <sheet name="08-25-2026" sheetId="86" r:id="rId19"/>
     <sheet name="08-26-2026" sheetId="87" r:id="rId20"/>
     <sheet name="08-27-2026" sheetId="88" r:id="rId21"/>
+    <sheet name="08-28-2026" sheetId="89" r:id="rId22"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'08-03-2026'!$A$1:$W$59</definedName>
@@ -56,6 +57,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="18">'08-25-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="19">'08-26-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="20">'08-27-2026'!$A$1:$W$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="21">'08-28-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">SAMPLE!$A$1:$W$85</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -74,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1764" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1848" uniqueCount="92">
   <si>
     <t>ROUTE 1</t>
   </si>
@@ -348,6 +350,9 @@
   </si>
   <si>
     <t>DATE: 08/27/2026</t>
+  </si>
+  <si>
+    <t>DATE: 08/28/2026</t>
   </si>
 </sst>
 </file>
@@ -1334,7 +1339,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="127">
+  <cellXfs count="128">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1620,6 +1625,9 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="63" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2069,21 +2077,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="115" t="s">
+      <c r="I1" s="116" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="115"/>
-      <c r="K1" s="115"/>
-      <c r="L1" s="115"/>
-      <c r="M1" s="115"/>
-      <c r="N1" s="115"/>
-      <c r="O1" s="115"/>
-      <c r="P1" s="115"/>
-      <c r="Q1" s="115"/>
-      <c r="R1" s="115"/>
-      <c r="S1" s="115"/>
-      <c r="T1" s="115"/>
-      <c r="U1" s="115"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="116"/>
+      <c r="M1" s="116"/>
+      <c r="N1" s="116"/>
+      <c r="O1" s="116"/>
+      <c r="P1" s="116"/>
+      <c r="Q1" s="116"/>
+      <c r="R1" s="116"/>
+      <c r="S1" s="116"/>
+      <c r="T1" s="116"/>
+      <c r="U1" s="116"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -2095,17 +2103,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="116" t="s">
+      <c r="C4" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="116"/>
-      <c r="H4" s="116"/>
-      <c r="I4" s="116"/>
-      <c r="J4" s="117"/>
-      <c r="K4" s="118"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="117"/>
+      <c r="F4" s="117"/>
+      <c r="G4" s="117"/>
+      <c r="H4" s="117"/>
+      <c r="I4" s="117"/>
+      <c r="J4" s="118"/>
+      <c r="K4" s="119"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -2125,13 +2133,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="119" t="s">
+      <c r="T4" s="120" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="121" t="s">
+      <c r="U4" s="122" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="108" t="s">
+      <c r="V4" s="109" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -2171,10 +2179,10 @@
       <c r="I5" s="93" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="110" t="s">
+      <c r="J5" s="111" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="111"/>
+      <c r="K5" s="112"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -2182,9 +2190,9 @@
       <c r="Q5" s="89"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="120"/>
-      <c r="U5" s="122"/>
-      <c r="V5" s="109"/>
+      <c r="T5" s="121"/>
+      <c r="U5" s="123"/>
+      <c r="V5" s="110"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -4715,17 +4723,17 @@
       <c r="B62" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C62" s="112" t="s">
+      <c r="C62" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="D62" s="113"/>
-      <c r="E62" s="113"/>
-      <c r="F62" s="113"/>
-      <c r="G62" s="113"/>
-      <c r="H62" s="113"/>
-      <c r="I62" s="113"/>
-      <c r="J62" s="113"/>
-      <c r="K62" s="114"/>
+      <c r="D62" s="114"/>
+      <c r="E62" s="114"/>
+      <c r="F62" s="114"/>
+      <c r="G62" s="114"/>
+      <c r="H62" s="114"/>
+      <c r="I62" s="114"/>
+      <c r="J62" s="114"/>
+      <c r="K62" s="115"/>
       <c r="U62" s="24" t="s">
         <v>51</v>
       </c>
@@ -5034,21 +5042,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="115" t="s">
+      <c r="I1" s="116" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="115"/>
-      <c r="K1" s="115"/>
-      <c r="L1" s="115"/>
-      <c r="M1" s="115"/>
-      <c r="N1" s="115"/>
-      <c r="O1" s="115"/>
-      <c r="P1" s="115"/>
-      <c r="Q1" s="115"/>
-      <c r="R1" s="115"/>
-      <c r="S1" s="115"/>
-      <c r="T1" s="115"/>
-      <c r="U1" s="115"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="116"/>
+      <c r="M1" s="116"/>
+      <c r="N1" s="116"/>
+      <c r="O1" s="116"/>
+      <c r="P1" s="116"/>
+      <c r="Q1" s="116"/>
+      <c r="R1" s="116"/>
+      <c r="S1" s="116"/>
+      <c r="T1" s="116"/>
+      <c r="U1" s="116"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -5060,17 +5068,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="116" t="s">
+      <c r="C4" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="116"/>
-      <c r="H4" s="116"/>
-      <c r="I4" s="116"/>
-      <c r="J4" s="117"/>
-      <c r="K4" s="118"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="117"/>
+      <c r="F4" s="117"/>
+      <c r="G4" s="117"/>
+      <c r="H4" s="117"/>
+      <c r="I4" s="117"/>
+      <c r="J4" s="118"/>
+      <c r="K4" s="119"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -5090,13 +5098,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="119" t="s">
+      <c r="T4" s="120" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="125" t="s">
+      <c r="U4" s="126" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="108" t="s">
+      <c r="V4" s="109" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -5136,10 +5144,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="123" t="s">
+      <c r="J5" s="124" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="124"/>
+      <c r="K5" s="125"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -5147,9 +5155,9 @@
       <c r="Q5" s="99"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="120"/>
-      <c r="U5" s="126"/>
-      <c r="V5" s="109"/>
+      <c r="T5" s="121"/>
+      <c r="U5" s="127"/>
+      <c r="V5" s="110"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -7860,17 +7868,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="112" t="s">
+      <c r="C60" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="113"/>
-      <c r="E60" s="113"/>
-      <c r="F60" s="113"/>
-      <c r="G60" s="113"/>
-      <c r="H60" s="113"/>
-      <c r="I60" s="113"/>
-      <c r="J60" s="113"/>
-      <c r="K60" s="114"/>
+      <c r="D60" s="114"/>
+      <c r="E60" s="114"/>
+      <c r="F60" s="114"/>
+      <c r="G60" s="114"/>
+      <c r="H60" s="114"/>
+      <c r="I60" s="114"/>
+      <c r="J60" s="114"/>
+      <c r="K60" s="115"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -8179,21 +8187,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="115" t="s">
+      <c r="I1" s="116" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="115"/>
-      <c r="K1" s="115"/>
-      <c r="L1" s="115"/>
-      <c r="M1" s="115"/>
-      <c r="N1" s="115"/>
-      <c r="O1" s="115"/>
-      <c r="P1" s="115"/>
-      <c r="Q1" s="115"/>
-      <c r="R1" s="115"/>
-      <c r="S1" s="115"/>
-      <c r="T1" s="115"/>
-      <c r="U1" s="115"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="116"/>
+      <c r="M1" s="116"/>
+      <c r="N1" s="116"/>
+      <c r="O1" s="116"/>
+      <c r="P1" s="116"/>
+      <c r="Q1" s="116"/>
+      <c r="R1" s="116"/>
+      <c r="S1" s="116"/>
+      <c r="T1" s="116"/>
+      <c r="U1" s="116"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -8205,17 +8213,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="116" t="s">
+      <c r="C4" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="116"/>
-      <c r="H4" s="116"/>
-      <c r="I4" s="116"/>
-      <c r="J4" s="117"/>
-      <c r="K4" s="118"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="117"/>
+      <c r="F4" s="117"/>
+      <c r="G4" s="117"/>
+      <c r="H4" s="117"/>
+      <c r="I4" s="117"/>
+      <c r="J4" s="118"/>
+      <c r="K4" s="119"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -8235,13 +8243,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="119" t="s">
+      <c r="T4" s="120" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="125" t="s">
+      <c r="U4" s="126" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="108" t="s">
+      <c r="V4" s="109" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -8281,10 +8289,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="123" t="s">
+      <c r="J5" s="124" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="124"/>
+      <c r="K5" s="125"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -8292,9 +8300,9 @@
       <c r="Q5" s="99"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="120"/>
-      <c r="U5" s="126"/>
-      <c r="V5" s="109"/>
+      <c r="T5" s="121"/>
+      <c r="U5" s="127"/>
+      <c r="V5" s="110"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -11007,17 +11015,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="112" t="s">
+      <c r="C60" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="113"/>
-      <c r="E60" s="113"/>
-      <c r="F60" s="113"/>
-      <c r="G60" s="113"/>
-      <c r="H60" s="113"/>
-      <c r="I60" s="113"/>
-      <c r="J60" s="113"/>
-      <c r="K60" s="114"/>
+      <c r="D60" s="114"/>
+      <c r="E60" s="114"/>
+      <c r="F60" s="114"/>
+      <c r="G60" s="114"/>
+      <c r="H60" s="114"/>
+      <c r="I60" s="114"/>
+      <c r="J60" s="114"/>
+      <c r="K60" s="115"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -11326,21 +11334,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="115" t="s">
+      <c r="I1" s="116" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="115"/>
-      <c r="K1" s="115"/>
-      <c r="L1" s="115"/>
-      <c r="M1" s="115"/>
-      <c r="N1" s="115"/>
-      <c r="O1" s="115"/>
-      <c r="P1" s="115"/>
-      <c r="Q1" s="115"/>
-      <c r="R1" s="115"/>
-      <c r="S1" s="115"/>
-      <c r="T1" s="115"/>
-      <c r="U1" s="115"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="116"/>
+      <c r="M1" s="116"/>
+      <c r="N1" s="116"/>
+      <c r="O1" s="116"/>
+      <c r="P1" s="116"/>
+      <c r="Q1" s="116"/>
+      <c r="R1" s="116"/>
+      <c r="S1" s="116"/>
+      <c r="T1" s="116"/>
+      <c r="U1" s="116"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -11352,17 +11360,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="116" t="s">
+      <c r="C4" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="116"/>
-      <c r="H4" s="116"/>
-      <c r="I4" s="116"/>
-      <c r="J4" s="117"/>
-      <c r="K4" s="118"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="117"/>
+      <c r="F4" s="117"/>
+      <c r="G4" s="117"/>
+      <c r="H4" s="117"/>
+      <c r="I4" s="117"/>
+      <c r="J4" s="118"/>
+      <c r="K4" s="119"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -11382,13 +11390,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="119" t="s">
+      <c r="T4" s="120" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="125" t="s">
+      <c r="U4" s="126" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="108" t="s">
+      <c r="V4" s="109" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -11428,10 +11436,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="123" t="s">
+      <c r="J5" s="124" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="124"/>
+      <c r="K5" s="125"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -11439,9 +11447,9 @@
       <c r="Q5" s="99"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="120"/>
-      <c r="U5" s="126"/>
-      <c r="V5" s="109"/>
+      <c r="T5" s="121"/>
+      <c r="U5" s="127"/>
+      <c r="V5" s="110"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -14143,17 +14151,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="112" t="s">
+      <c r="C60" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="113"/>
-      <c r="E60" s="113"/>
-      <c r="F60" s="113"/>
-      <c r="G60" s="113"/>
-      <c r="H60" s="113"/>
-      <c r="I60" s="113"/>
-      <c r="J60" s="113"/>
-      <c r="K60" s="114"/>
+      <c r="D60" s="114"/>
+      <c r="E60" s="114"/>
+      <c r="F60" s="114"/>
+      <c r="G60" s="114"/>
+      <c r="H60" s="114"/>
+      <c r="I60" s="114"/>
+      <c r="J60" s="114"/>
+      <c r="K60" s="115"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -14462,21 +14470,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="115" t="s">
+      <c r="I1" s="116" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="115"/>
-      <c r="K1" s="115"/>
-      <c r="L1" s="115"/>
-      <c r="M1" s="115"/>
-      <c r="N1" s="115"/>
-      <c r="O1" s="115"/>
-      <c r="P1" s="115"/>
-      <c r="Q1" s="115"/>
-      <c r="R1" s="115"/>
-      <c r="S1" s="115"/>
-      <c r="T1" s="115"/>
-      <c r="U1" s="115"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="116"/>
+      <c r="M1" s="116"/>
+      <c r="N1" s="116"/>
+      <c r="O1" s="116"/>
+      <c r="P1" s="116"/>
+      <c r="Q1" s="116"/>
+      <c r="R1" s="116"/>
+      <c r="S1" s="116"/>
+      <c r="T1" s="116"/>
+      <c r="U1" s="116"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -14488,17 +14496,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="116" t="s">
+      <c r="C4" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="116"/>
-      <c r="H4" s="116"/>
-      <c r="I4" s="116"/>
-      <c r="J4" s="117"/>
-      <c r="K4" s="118"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="117"/>
+      <c r="F4" s="117"/>
+      <c r="G4" s="117"/>
+      <c r="H4" s="117"/>
+      <c r="I4" s="117"/>
+      <c r="J4" s="118"/>
+      <c r="K4" s="119"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -14518,13 +14526,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="119" t="s">
+      <c r="T4" s="120" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="125" t="s">
+      <c r="U4" s="126" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="108" t="s">
+      <c r="V4" s="109" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -14564,10 +14572,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="123" t="s">
+      <c r="J5" s="124" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="124"/>
+      <c r="K5" s="125"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -14575,9 +14583,9 @@
       <c r="Q5" s="99"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="120"/>
-      <c r="U5" s="126"/>
-      <c r="V5" s="109"/>
+      <c r="T5" s="121"/>
+      <c r="U5" s="127"/>
+      <c r="V5" s="110"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -17278,17 +17286,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="112" t="s">
+      <c r="C60" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="113"/>
-      <c r="E60" s="113"/>
-      <c r="F60" s="113"/>
-      <c r="G60" s="113"/>
-      <c r="H60" s="113"/>
-      <c r="I60" s="113"/>
-      <c r="J60" s="113"/>
-      <c r="K60" s="114"/>
+      <c r="D60" s="114"/>
+      <c r="E60" s="114"/>
+      <c r="F60" s="114"/>
+      <c r="G60" s="114"/>
+      <c r="H60" s="114"/>
+      <c r="I60" s="114"/>
+      <c r="J60" s="114"/>
+      <c r="K60" s="115"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -17597,21 +17605,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="115" t="s">
+      <c r="I1" s="116" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="115"/>
-      <c r="K1" s="115"/>
-      <c r="L1" s="115"/>
-      <c r="M1" s="115"/>
-      <c r="N1" s="115"/>
-      <c r="O1" s="115"/>
-      <c r="P1" s="115"/>
-      <c r="Q1" s="115"/>
-      <c r="R1" s="115"/>
-      <c r="S1" s="115"/>
-      <c r="T1" s="115"/>
-      <c r="U1" s="115"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="116"/>
+      <c r="M1" s="116"/>
+      <c r="N1" s="116"/>
+      <c r="O1" s="116"/>
+      <c r="P1" s="116"/>
+      <c r="Q1" s="116"/>
+      <c r="R1" s="116"/>
+      <c r="S1" s="116"/>
+      <c r="T1" s="116"/>
+      <c r="U1" s="116"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -17623,17 +17631,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="116" t="s">
+      <c r="C4" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="116"/>
-      <c r="H4" s="116"/>
-      <c r="I4" s="116"/>
-      <c r="J4" s="117"/>
-      <c r="K4" s="118"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="117"/>
+      <c r="F4" s="117"/>
+      <c r="G4" s="117"/>
+      <c r="H4" s="117"/>
+      <c r="I4" s="117"/>
+      <c r="J4" s="118"/>
+      <c r="K4" s="119"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -17653,13 +17661,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="119" t="s">
+      <c r="T4" s="120" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="125" t="s">
+      <c r="U4" s="126" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="108" t="s">
+      <c r="V4" s="109" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -17699,10 +17707,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="123" t="s">
+      <c r="J5" s="124" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="124"/>
+      <c r="K5" s="125"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -17710,9 +17718,9 @@
       <c r="Q5" s="100"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="120"/>
-      <c r="U5" s="126"/>
-      <c r="V5" s="109"/>
+      <c r="T5" s="121"/>
+      <c r="U5" s="127"/>
+      <c r="V5" s="110"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -20407,17 +20415,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="112" t="s">
+      <c r="C60" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="113"/>
-      <c r="E60" s="113"/>
-      <c r="F60" s="113"/>
-      <c r="G60" s="113"/>
-      <c r="H60" s="113"/>
-      <c r="I60" s="113"/>
-      <c r="J60" s="113"/>
-      <c r="K60" s="114"/>
+      <c r="D60" s="114"/>
+      <c r="E60" s="114"/>
+      <c r="F60" s="114"/>
+      <c r="G60" s="114"/>
+      <c r="H60" s="114"/>
+      <c r="I60" s="114"/>
+      <c r="J60" s="114"/>
+      <c r="K60" s="115"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -20726,21 +20734,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="115" t="s">
+      <c r="I1" s="116" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="115"/>
-      <c r="K1" s="115"/>
-      <c r="L1" s="115"/>
-      <c r="M1" s="115"/>
-      <c r="N1" s="115"/>
-      <c r="O1" s="115"/>
-      <c r="P1" s="115"/>
-      <c r="Q1" s="115"/>
-      <c r="R1" s="115"/>
-      <c r="S1" s="115"/>
-      <c r="T1" s="115"/>
-      <c r="U1" s="115"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="116"/>
+      <c r="M1" s="116"/>
+      <c r="N1" s="116"/>
+      <c r="O1" s="116"/>
+      <c r="P1" s="116"/>
+      <c r="Q1" s="116"/>
+      <c r="R1" s="116"/>
+      <c r="S1" s="116"/>
+      <c r="T1" s="116"/>
+      <c r="U1" s="116"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -20752,17 +20760,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="116" t="s">
+      <c r="C4" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="116"/>
-      <c r="H4" s="116"/>
-      <c r="I4" s="116"/>
-      <c r="J4" s="117"/>
-      <c r="K4" s="118"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="117"/>
+      <c r="F4" s="117"/>
+      <c r="G4" s="117"/>
+      <c r="H4" s="117"/>
+      <c r="I4" s="117"/>
+      <c r="J4" s="118"/>
+      <c r="K4" s="119"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -20782,13 +20790,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="119" t="s">
+      <c r="T4" s="120" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="125" t="s">
+      <c r="U4" s="126" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="108" t="s">
+      <c r="V4" s="109" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -20828,10 +20836,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="123" t="s">
+      <c r="J5" s="124" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="124"/>
+      <c r="K5" s="125"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -20839,9 +20847,9 @@
       <c r="Q5" s="101"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="120"/>
-      <c r="U5" s="126"/>
-      <c r="V5" s="109"/>
+      <c r="T5" s="121"/>
+      <c r="U5" s="127"/>
+      <c r="V5" s="110"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -23532,17 +23540,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="112" t="s">
+      <c r="C60" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="113"/>
-      <c r="E60" s="113"/>
-      <c r="F60" s="113"/>
-      <c r="G60" s="113"/>
-      <c r="H60" s="113"/>
-      <c r="I60" s="113"/>
-      <c r="J60" s="113"/>
-      <c r="K60" s="114"/>
+      <c r="D60" s="114"/>
+      <c r="E60" s="114"/>
+      <c r="F60" s="114"/>
+      <c r="G60" s="114"/>
+      <c r="H60" s="114"/>
+      <c r="I60" s="114"/>
+      <c r="J60" s="114"/>
+      <c r="K60" s="115"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -23851,21 +23859,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="115" t="s">
+      <c r="I1" s="116" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="115"/>
-      <c r="K1" s="115"/>
-      <c r="L1" s="115"/>
-      <c r="M1" s="115"/>
-      <c r="N1" s="115"/>
-      <c r="O1" s="115"/>
-      <c r="P1" s="115"/>
-      <c r="Q1" s="115"/>
-      <c r="R1" s="115"/>
-      <c r="S1" s="115"/>
-      <c r="T1" s="115"/>
-      <c r="U1" s="115"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="116"/>
+      <c r="M1" s="116"/>
+      <c r="N1" s="116"/>
+      <c r="O1" s="116"/>
+      <c r="P1" s="116"/>
+      <c r="Q1" s="116"/>
+      <c r="R1" s="116"/>
+      <c r="S1" s="116"/>
+      <c r="T1" s="116"/>
+      <c r="U1" s="116"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -23877,17 +23885,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="116" t="s">
+      <c r="C4" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="116"/>
-      <c r="H4" s="116"/>
-      <c r="I4" s="116"/>
-      <c r="J4" s="117"/>
-      <c r="K4" s="118"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="117"/>
+      <c r="F4" s="117"/>
+      <c r="G4" s="117"/>
+      <c r="H4" s="117"/>
+      <c r="I4" s="117"/>
+      <c r="J4" s="118"/>
+      <c r="K4" s="119"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -23907,13 +23915,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="119" t="s">
+      <c r="T4" s="120" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="125" t="s">
+      <c r="U4" s="126" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="108" t="s">
+      <c r="V4" s="109" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -23953,10 +23961,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="123" t="s">
+      <c r="J5" s="124" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="124"/>
+      <c r="K5" s="125"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -23964,9 +23972,9 @@
       <c r="Q5" s="102"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="120"/>
-      <c r="U5" s="126"/>
-      <c r="V5" s="109"/>
+      <c r="T5" s="121"/>
+      <c r="U5" s="127"/>
+      <c r="V5" s="110"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -26674,17 +26682,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="112" t="s">
+      <c r="C60" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="113"/>
-      <c r="E60" s="113"/>
-      <c r="F60" s="113"/>
-      <c r="G60" s="113"/>
-      <c r="H60" s="113"/>
-      <c r="I60" s="113"/>
-      <c r="J60" s="113"/>
-      <c r="K60" s="114"/>
+      <c r="D60" s="114"/>
+      <c r="E60" s="114"/>
+      <c r="F60" s="114"/>
+      <c r="G60" s="114"/>
+      <c r="H60" s="114"/>
+      <c r="I60" s="114"/>
+      <c r="J60" s="114"/>
+      <c r="K60" s="115"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -26993,21 +27001,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="115" t="s">
+      <c r="I1" s="116" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="115"/>
-      <c r="K1" s="115"/>
-      <c r="L1" s="115"/>
-      <c r="M1" s="115"/>
-      <c r="N1" s="115"/>
-      <c r="O1" s="115"/>
-      <c r="P1" s="115"/>
-      <c r="Q1" s="115"/>
-      <c r="R1" s="115"/>
-      <c r="S1" s="115"/>
-      <c r="T1" s="115"/>
-      <c r="U1" s="115"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="116"/>
+      <c r="M1" s="116"/>
+      <c r="N1" s="116"/>
+      <c r="O1" s="116"/>
+      <c r="P1" s="116"/>
+      <c r="Q1" s="116"/>
+      <c r="R1" s="116"/>
+      <c r="S1" s="116"/>
+      <c r="T1" s="116"/>
+      <c r="U1" s="116"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -27019,17 +27027,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="116" t="s">
+      <c r="C4" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="116"/>
-      <c r="H4" s="116"/>
-      <c r="I4" s="116"/>
-      <c r="J4" s="117"/>
-      <c r="K4" s="118"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="117"/>
+      <c r="F4" s="117"/>
+      <c r="G4" s="117"/>
+      <c r="H4" s="117"/>
+      <c r="I4" s="117"/>
+      <c r="J4" s="118"/>
+      <c r="K4" s="119"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -27049,13 +27057,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="119" t="s">
+      <c r="T4" s="120" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="125" t="s">
+      <c r="U4" s="126" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="108" t="s">
+      <c r="V4" s="109" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -27095,10 +27103,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="123" t="s">
+      <c r="J5" s="124" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="124"/>
+      <c r="K5" s="125"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -27106,9 +27114,9 @@
       <c r="Q5" s="103"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="120"/>
-      <c r="U5" s="126"/>
-      <c r="V5" s="109"/>
+      <c r="T5" s="121"/>
+      <c r="U5" s="127"/>
+      <c r="V5" s="110"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -29792,17 +29800,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="112" t="s">
+      <c r="C60" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="113"/>
-      <c r="E60" s="113"/>
-      <c r="F60" s="113"/>
-      <c r="G60" s="113"/>
-      <c r="H60" s="113"/>
-      <c r="I60" s="113"/>
-      <c r="J60" s="113"/>
-      <c r="K60" s="114"/>
+      <c r="D60" s="114"/>
+      <c r="E60" s="114"/>
+      <c r="F60" s="114"/>
+      <c r="G60" s="114"/>
+      <c r="H60" s="114"/>
+      <c r="I60" s="114"/>
+      <c r="J60" s="114"/>
+      <c r="K60" s="115"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -30111,21 +30119,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="115" t="s">
+      <c r="I1" s="116" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="115"/>
-      <c r="K1" s="115"/>
-      <c r="L1" s="115"/>
-      <c r="M1" s="115"/>
-      <c r="N1" s="115"/>
-      <c r="O1" s="115"/>
-      <c r="P1" s="115"/>
-      <c r="Q1" s="115"/>
-      <c r="R1" s="115"/>
-      <c r="S1" s="115"/>
-      <c r="T1" s="115"/>
-      <c r="U1" s="115"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="116"/>
+      <c r="M1" s="116"/>
+      <c r="N1" s="116"/>
+      <c r="O1" s="116"/>
+      <c r="P1" s="116"/>
+      <c r="Q1" s="116"/>
+      <c r="R1" s="116"/>
+      <c r="S1" s="116"/>
+      <c r="T1" s="116"/>
+      <c r="U1" s="116"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -30137,17 +30145,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="116" t="s">
+      <c r="C4" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="116"/>
-      <c r="H4" s="116"/>
-      <c r="I4" s="116"/>
-      <c r="J4" s="117"/>
-      <c r="K4" s="118"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="117"/>
+      <c r="F4" s="117"/>
+      <c r="G4" s="117"/>
+      <c r="H4" s="117"/>
+      <c r="I4" s="117"/>
+      <c r="J4" s="118"/>
+      <c r="K4" s="119"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -30167,13 +30175,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="119" t="s">
+      <c r="T4" s="120" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="125" t="s">
+      <c r="U4" s="126" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="108" t="s">
+      <c r="V4" s="109" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -30213,10 +30221,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="123" t="s">
+      <c r="J5" s="124" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="124"/>
+      <c r="K5" s="125"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -30224,9 +30232,9 @@
       <c r="Q5" s="104"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="120"/>
-      <c r="U5" s="126"/>
-      <c r="V5" s="109"/>
+      <c r="T5" s="121"/>
+      <c r="U5" s="127"/>
+      <c r="V5" s="110"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -32902,17 +32910,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="112" t="s">
+      <c r="C60" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="113"/>
-      <c r="E60" s="113"/>
-      <c r="F60" s="113"/>
-      <c r="G60" s="113"/>
-      <c r="H60" s="113"/>
-      <c r="I60" s="113"/>
-      <c r="J60" s="113"/>
-      <c r="K60" s="114"/>
+      <c r="D60" s="114"/>
+      <c r="E60" s="114"/>
+      <c r="F60" s="114"/>
+      <c r="G60" s="114"/>
+      <c r="H60" s="114"/>
+      <c r="I60" s="114"/>
+      <c r="J60" s="114"/>
+      <c r="K60" s="115"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -33221,21 +33229,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="115" t="s">
+      <c r="I1" s="116" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="115"/>
-      <c r="K1" s="115"/>
-      <c r="L1" s="115"/>
-      <c r="M1" s="115"/>
-      <c r="N1" s="115"/>
-      <c r="O1" s="115"/>
-      <c r="P1" s="115"/>
-      <c r="Q1" s="115"/>
-      <c r="R1" s="115"/>
-      <c r="S1" s="115"/>
-      <c r="T1" s="115"/>
-      <c r="U1" s="115"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="116"/>
+      <c r="M1" s="116"/>
+      <c r="N1" s="116"/>
+      <c r="O1" s="116"/>
+      <c r="P1" s="116"/>
+      <c r="Q1" s="116"/>
+      <c r="R1" s="116"/>
+      <c r="S1" s="116"/>
+      <c r="T1" s="116"/>
+      <c r="U1" s="116"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -33247,17 +33255,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="116" t="s">
+      <c r="C4" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="116"/>
-      <c r="H4" s="116"/>
-      <c r="I4" s="116"/>
-      <c r="J4" s="117"/>
-      <c r="K4" s="118"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="117"/>
+      <c r="F4" s="117"/>
+      <c r="G4" s="117"/>
+      <c r="H4" s="117"/>
+      <c r="I4" s="117"/>
+      <c r="J4" s="118"/>
+      <c r="K4" s="119"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -33277,13 +33285,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="119" t="s">
+      <c r="T4" s="120" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="125" t="s">
+      <c r="U4" s="126" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="108" t="s">
+      <c r="V4" s="109" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -33323,10 +33331,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="123" t="s">
+      <c r="J5" s="124" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="124"/>
+      <c r="K5" s="125"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -33334,9 +33342,9 @@
       <c r="Q5" s="105"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="120"/>
-      <c r="U5" s="126"/>
-      <c r="V5" s="109"/>
+      <c r="T5" s="121"/>
+      <c r="U5" s="127"/>
+      <c r="V5" s="110"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -36021,17 +36029,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="112" t="s">
+      <c r="C60" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="113"/>
-      <c r="E60" s="113"/>
-      <c r="F60" s="113"/>
-      <c r="G60" s="113"/>
-      <c r="H60" s="113"/>
-      <c r="I60" s="113"/>
-      <c r="J60" s="113"/>
-      <c r="K60" s="114"/>
+      <c r="D60" s="114"/>
+      <c r="E60" s="114"/>
+      <c r="F60" s="114"/>
+      <c r="G60" s="114"/>
+      <c r="H60" s="114"/>
+      <c r="I60" s="114"/>
+      <c r="J60" s="114"/>
+      <c r="K60" s="115"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -36340,21 +36348,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="115" t="s">
+      <c r="I1" s="116" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="115"/>
-      <c r="K1" s="115"/>
-      <c r="L1" s="115"/>
-      <c r="M1" s="115"/>
-      <c r="N1" s="115"/>
-      <c r="O1" s="115"/>
-      <c r="P1" s="115"/>
-      <c r="Q1" s="115"/>
-      <c r="R1" s="115"/>
-      <c r="S1" s="115"/>
-      <c r="T1" s="115"/>
-      <c r="U1" s="115"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="116"/>
+      <c r="M1" s="116"/>
+      <c r="N1" s="116"/>
+      <c r="O1" s="116"/>
+      <c r="P1" s="116"/>
+      <c r="Q1" s="116"/>
+      <c r="R1" s="116"/>
+      <c r="S1" s="116"/>
+      <c r="T1" s="116"/>
+      <c r="U1" s="116"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -36366,17 +36374,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="116" t="s">
+      <c r="C4" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="116"/>
-      <c r="H4" s="116"/>
-      <c r="I4" s="116"/>
-      <c r="J4" s="117"/>
-      <c r="K4" s="118"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="117"/>
+      <c r="F4" s="117"/>
+      <c r="G4" s="117"/>
+      <c r="H4" s="117"/>
+      <c r="I4" s="117"/>
+      <c r="J4" s="118"/>
+      <c r="K4" s="119"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -36396,13 +36404,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="119" t="s">
+      <c r="T4" s="120" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="125" t="s">
+      <c r="U4" s="126" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="108" t="s">
+      <c r="V4" s="109" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -36442,10 +36450,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="123" t="s">
+      <c r="J5" s="124" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="124"/>
+      <c r="K5" s="125"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -36453,9 +36461,9 @@
       <c r="Q5" s="96"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="120"/>
-      <c r="U5" s="126"/>
-      <c r="V5" s="109"/>
+      <c r="T5" s="121"/>
+      <c r="U5" s="127"/>
+      <c r="V5" s="110"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -39165,17 +39173,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="112" t="s">
+      <c r="C60" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="113"/>
-      <c r="E60" s="113"/>
-      <c r="F60" s="113"/>
-      <c r="G60" s="113"/>
-      <c r="H60" s="113"/>
-      <c r="I60" s="113"/>
-      <c r="J60" s="113"/>
-      <c r="K60" s="114"/>
+      <c r="D60" s="114"/>
+      <c r="E60" s="114"/>
+      <c r="F60" s="114"/>
+      <c r="G60" s="114"/>
+      <c r="H60" s="114"/>
+      <c r="I60" s="114"/>
+      <c r="J60" s="114"/>
+      <c r="K60" s="115"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -39484,21 +39492,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="115" t="s">
+      <c r="I1" s="116" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="115"/>
-      <c r="K1" s="115"/>
-      <c r="L1" s="115"/>
-      <c r="M1" s="115"/>
-      <c r="N1" s="115"/>
-      <c r="O1" s="115"/>
-      <c r="P1" s="115"/>
-      <c r="Q1" s="115"/>
-      <c r="R1" s="115"/>
-      <c r="S1" s="115"/>
-      <c r="T1" s="115"/>
-      <c r="U1" s="115"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="116"/>
+      <c r="M1" s="116"/>
+      <c r="N1" s="116"/>
+      <c r="O1" s="116"/>
+      <c r="P1" s="116"/>
+      <c r="Q1" s="116"/>
+      <c r="R1" s="116"/>
+      <c r="S1" s="116"/>
+      <c r="T1" s="116"/>
+      <c r="U1" s="116"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -39510,17 +39518,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="116" t="s">
+      <c r="C4" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="116"/>
-      <c r="H4" s="116"/>
-      <c r="I4" s="116"/>
-      <c r="J4" s="117"/>
-      <c r="K4" s="118"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="117"/>
+      <c r="F4" s="117"/>
+      <c r="G4" s="117"/>
+      <c r="H4" s="117"/>
+      <c r="I4" s="117"/>
+      <c r="J4" s="118"/>
+      <c r="K4" s="119"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -39540,13 +39548,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="119" t="s">
+      <c r="T4" s="120" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="125" t="s">
+      <c r="U4" s="126" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="108" t="s">
+      <c r="V4" s="109" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -39586,10 +39594,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="123" t="s">
+      <c r="J5" s="124" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="124"/>
+      <c r="K5" s="125"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -39597,9 +39605,9 @@
       <c r="Q5" s="106"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="120"/>
-      <c r="U5" s="126"/>
-      <c r="V5" s="109"/>
+      <c r="T5" s="121"/>
+      <c r="U5" s="127"/>
+      <c r="V5" s="110"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -42295,17 +42303,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="112" t="s">
+      <c r="C60" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="113"/>
-      <c r="E60" s="113"/>
-      <c r="F60" s="113"/>
-      <c r="G60" s="113"/>
-      <c r="H60" s="113"/>
-      <c r="I60" s="113"/>
-      <c r="J60" s="113"/>
-      <c r="K60" s="114"/>
+      <c r="D60" s="114"/>
+      <c r="E60" s="114"/>
+      <c r="F60" s="114"/>
+      <c r="G60" s="114"/>
+      <c r="H60" s="114"/>
+      <c r="I60" s="114"/>
+      <c r="J60" s="114"/>
+      <c r="K60" s="115"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -42614,21 +42622,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="115" t="s">
+      <c r="I1" s="116" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="115"/>
-      <c r="K1" s="115"/>
-      <c r="L1" s="115"/>
-      <c r="M1" s="115"/>
-      <c r="N1" s="115"/>
-      <c r="O1" s="115"/>
-      <c r="P1" s="115"/>
-      <c r="Q1" s="115"/>
-      <c r="R1" s="115"/>
-      <c r="S1" s="115"/>
-      <c r="T1" s="115"/>
-      <c r="U1" s="115"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="116"/>
+      <c r="M1" s="116"/>
+      <c r="N1" s="116"/>
+      <c r="O1" s="116"/>
+      <c r="P1" s="116"/>
+      <c r="Q1" s="116"/>
+      <c r="R1" s="116"/>
+      <c r="S1" s="116"/>
+      <c r="T1" s="116"/>
+      <c r="U1" s="116"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -42640,17 +42648,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="116" t="s">
+      <c r="C4" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="116"/>
-      <c r="H4" s="116"/>
-      <c r="I4" s="116"/>
-      <c r="J4" s="117"/>
-      <c r="K4" s="118"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="117"/>
+      <c r="F4" s="117"/>
+      <c r="G4" s="117"/>
+      <c r="H4" s="117"/>
+      <c r="I4" s="117"/>
+      <c r="J4" s="118"/>
+      <c r="K4" s="119"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -42670,13 +42678,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="119" t="s">
+      <c r="T4" s="120" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="125" t="s">
+      <c r="U4" s="126" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="108" t="s">
+      <c r="V4" s="109" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -42716,10 +42724,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="123" t="s">
+      <c r="J5" s="124" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="124"/>
+      <c r="K5" s="125"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -42727,9 +42735,9 @@
       <c r="Q5" s="107"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="120"/>
-      <c r="U5" s="126"/>
-      <c r="V5" s="109"/>
+      <c r="T5" s="121"/>
+      <c r="U5" s="127"/>
+      <c r="V5" s="110"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -45423,17 +45431,3139 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="112" t="s">
+      <c r="C60" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="113"/>
-      <c r="E60" s="113"/>
-      <c r="F60" s="113"/>
-      <c r="G60" s="113"/>
-      <c r="H60" s="113"/>
-      <c r="I60" s="113"/>
-      <c r="J60" s="113"/>
-      <c r="K60" s="114"/>
+      <c r="D60" s="114"/>
+      <c r="E60" s="114"/>
+      <c r="F60" s="114"/>
+      <c r="G60" s="114"/>
+      <c r="H60" s="114"/>
+      <c r="I60" s="114"/>
+      <c r="J60" s="114"/>
+      <c r="K60" s="115"/>
+      <c r="U60" s="24" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B61" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="C61" s="19"/>
+      <c r="D61" s="19"/>
+      <c r="E61" s="19"/>
+      <c r="F61" s="19"/>
+      <c r="G61" s="19"/>
+      <c r="H61" s="19"/>
+      <c r="I61" s="19"/>
+      <c r="J61" s="45"/>
+      <c r="K61" s="20"/>
+      <c r="U61" s="7"/>
+    </row>
+    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B62" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+      <c r="J62" s="44"/>
+      <c r="K62" s="21"/>
+      <c r="U62" s="3"/>
+    </row>
+    <row r="63" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B63" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C63" s="22"/>
+      <c r="D63" s="22"/>
+      <c r="E63" s="22"/>
+      <c r="F63" s="22"/>
+      <c r="G63" s="22"/>
+      <c r="H63" s="22"/>
+      <c r="I63" s="22"/>
+      <c r="J63" s="46"/>
+      <c r="K63" s="23"/>
+      <c r="U63" s="8"/>
+    </row>
+    <row r="64" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B65" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="C65" s="19"/>
+      <c r="D65" s="19"/>
+      <c r="E65" s="19"/>
+      <c r="F65" s="19"/>
+      <c r="G65" s="19"/>
+      <c r="H65" s="19"/>
+      <c r="I65" s="19"/>
+      <c r="J65" s="45"/>
+      <c r="K65" s="20"/>
+      <c r="U65" s="7"/>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B66" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C66" s="1"/>
+      <c r="D66" s="1"/>
+      <c r="E66" s="1"/>
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="J66" s="44"/>
+      <c r="K66" s="21"/>
+      <c r="U66" s="3"/>
+    </row>
+    <row r="67" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B67" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C67" s="22"/>
+      <c r="D67" s="22"/>
+      <c r="E67" s="22"/>
+      <c r="F67" s="22"/>
+      <c r="G67" s="22"/>
+      <c r="H67" s="22"/>
+      <c r="I67" s="22"/>
+      <c r="J67" s="46"/>
+      <c r="K67" s="23"/>
+      <c r="U67" s="8"/>
+    </row>
+    <row r="68" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B69" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="C69" s="19"/>
+      <c r="D69" s="19"/>
+      <c r="E69" s="19"/>
+      <c r="F69" s="19"/>
+      <c r="G69" s="19"/>
+      <c r="H69" s="19"/>
+      <c r="I69" s="19"/>
+      <c r="J69" s="45"/>
+      <c r="K69" s="20"/>
+      <c r="U69" s="7"/>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B70" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="J70" s="44"/>
+      <c r="K70" s="21"/>
+      <c r="U70" s="3"/>
+    </row>
+    <row r="71" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B71" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C71" s="22"/>
+      <c r="D71" s="22"/>
+      <c r="E71" s="22"/>
+      <c r="F71" s="22"/>
+      <c r="G71" s="22"/>
+      <c r="H71" s="22"/>
+      <c r="I71" s="22"/>
+      <c r="J71" s="46"/>
+      <c r="K71" s="23"/>
+      <c r="U71" s="8"/>
+    </row>
+    <row r="72" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B73" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="C73" s="19"/>
+      <c r="D73" s="19"/>
+      <c r="E73" s="19"/>
+      <c r="F73" s="19"/>
+      <c r="G73" s="19"/>
+      <c r="H73" s="19"/>
+      <c r="I73" s="19"/>
+      <c r="J73" s="45"/>
+      <c r="K73" s="20"/>
+      <c r="U73" s="7"/>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B74" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C74" s="1"/>
+      <c r="D74" s="1"/>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1"/>
+      <c r="J74" s="44"/>
+      <c r="K74" s="21"/>
+      <c r="U74" s="3"/>
+    </row>
+    <row r="75" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B75" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C75" s="22"/>
+      <c r="D75" s="22"/>
+      <c r="E75" s="22"/>
+      <c r="F75" s="22"/>
+      <c r="G75" s="22"/>
+      <c r="H75" s="22"/>
+      <c r="I75" s="22"/>
+      <c r="J75" s="46"/>
+      <c r="K75" s="23"/>
+      <c r="U75" s="8"/>
+    </row>
+    <row r="76" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B77" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="C77" s="19"/>
+      <c r="D77" s="19"/>
+      <c r="E77" s="19"/>
+      <c r="F77" s="19"/>
+      <c r="G77" s="19"/>
+      <c r="H77" s="19"/>
+      <c r="I77" s="19"/>
+      <c r="J77" s="45"/>
+      <c r="K77" s="20"/>
+      <c r="U77" s="7"/>
+    </row>
+    <row r="78" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B78" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C78" s="1"/>
+      <c r="D78" s="1"/>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+      <c r="J78" s="44"/>
+      <c r="K78" s="21"/>
+      <c r="U78" s="3"/>
+    </row>
+    <row r="79" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B79" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C79" s="22"/>
+      <c r="D79" s="22"/>
+      <c r="E79" s="22"/>
+      <c r="F79" s="22"/>
+      <c r="G79" s="22"/>
+      <c r="H79" s="22"/>
+      <c r="I79" s="22"/>
+      <c r="J79" s="46"/>
+      <c r="K79" s="23"/>
+      <c r="U79" s="8"/>
+    </row>
+    <row r="80" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="81" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B81" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="C81" s="17"/>
+      <c r="D81" s="17"/>
+      <c r="E81" s="17"/>
+      <c r="F81" s="17"/>
+      <c r="G81" s="17"/>
+      <c r="H81" s="17"/>
+      <c r="I81" s="17"/>
+      <c r="J81" s="47"/>
+      <c r="K81" s="18"/>
+      <c r="U81" s="16"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="C60:K60"/>
+    <mergeCell ref="I1:U1"/>
+    <mergeCell ref="C4:K4"/>
+    <mergeCell ref="T4:T5"/>
+    <mergeCell ref="U4:U5"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
+  <pageSetup paperSize="14" scale="70" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="24" max="80" man="1"/>
+  </colBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8771B395-0179-4958-9FA6-E2C851C4F87A}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BB81"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="28" customWidth="1"/>
+    <col min="3" max="6" width="10" style="9" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" style="9" customWidth="1"/>
+    <col min="8" max="8" width="7.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.85546875" style="9" customWidth="1"/>
+    <col min="11" max="11" width="7.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.42578125" style="9" customWidth="1"/>
+    <col min="13" max="13" width="10" style="9" customWidth="1"/>
+    <col min="14" max="14" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" style="9" customWidth="1"/>
+    <col min="16" max="16" width="5.5703125" style="9" customWidth="1"/>
+    <col min="17" max="17" width="10" style="9" customWidth="1"/>
+    <col min="18" max="18" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="1.42578125" style="9" customWidth="1"/>
+    <col min="20" max="20" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="9" customWidth="1"/>
+    <col min="22" max="22" width="19.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="23" max="49" width="7.28515625" style="9" customWidth="1"/>
+    <col min="50" max="50" width="1.5703125" style="9" customWidth="1"/>
+    <col min="51" max="51" width="9.42578125" style="9" customWidth="1"/>
+    <col min="52" max="52" width="1.28515625" style="9" customWidth="1"/>
+    <col min="53" max="53" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="10.28515625" style="9" bestFit="1" customWidth="1"/>
+    <col min="55" max="16384" width="9.140625" style="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="116" t="s">
+        <v>43</v>
+      </c>
+      <c r="J1" s="116"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="116"/>
+      <c r="M1" s="116"/>
+      <c r="N1" s="116"/>
+      <c r="O1" s="116"/>
+      <c r="P1" s="116"/>
+      <c r="Q1" s="116"/>
+      <c r="R1" s="116"/>
+      <c r="S1" s="116"/>
+      <c r="T1" s="116"/>
+      <c r="U1" s="116"/>
+    </row>
+    <row r="2" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="B2" s="28" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B4" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="117" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="117"/>
+      <c r="E4" s="117"/>
+      <c r="F4" s="117"/>
+      <c r="G4" s="117"/>
+      <c r="H4" s="117"/>
+      <c r="I4" s="117"/>
+      <c r="J4" s="118"/>
+      <c r="K4" s="119"/>
+      <c r="M4" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="N4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="O4" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="P4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q4" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="R4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="S4" s="9"/>
+      <c r="T4" s="120" t="s">
+        <v>68</v>
+      </c>
+      <c r="U4" s="126" t="s">
+        <v>67</v>
+      </c>
+      <c r="V4" s="109" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF4" s="11"/>
+      <c r="AG4" s="11"/>
+      <c r="AH4" s="11"/>
+      <c r="AI4" s="11"/>
+      <c r="AJ4" s="11"/>
+      <c r="AK4" s="11"/>
+      <c r="AL4" s="11"/>
+      <c r="AM4" s="11"/>
+      <c r="AN4" s="11"/>
+      <c r="AO4" s="11"/>
+      <c r="AP4" s="11"/>
+      <c r="AQ4" s="11"/>
+      <c r="AR4" s="11"/>
+      <c r="AS4" s="11"/>
+      <c r="AT4" s="11"/>
+      <c r="AU4" s="11"/>
+      <c r="AV4" s="11"/>
+      <c r="AW4" s="11"/>
+      <c r="AX4" s="11"/>
+      <c r="AY4" s="11"/>
+      <c r="AZ4" s="11"/>
+      <c r="BA4" s="11"/>
+      <c r="BB4" s="11"/>
+    </row>
+    <row r="5" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="37"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40" t="s">
+        <v>64</v>
+      </c>
+      <c r="I5" s="40" t="s">
+        <v>60</v>
+      </c>
+      <c r="J5" s="124" t="s">
+        <v>65</v>
+      </c>
+      <c r="K5" s="125"/>
+      <c r="M5" s="37"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="40"/>
+      <c r="P5" s="108"/>
+      <c r="Q5" s="108"/>
+      <c r="R5" s="38"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="121"/>
+      <c r="U5" s="127"/>
+      <c r="V5" s="110"/>
+      <c r="AF5" s="11"/>
+      <c r="AG5" s="11"/>
+      <c r="AH5" s="11"/>
+      <c r="AI5" s="11"/>
+      <c r="AJ5" s="11"/>
+      <c r="AK5" s="11"/>
+      <c r="AL5" s="11"/>
+      <c r="AM5" s="11"/>
+      <c r="AN5" s="11"/>
+      <c r="AO5" s="11"/>
+      <c r="AP5" s="11"/>
+      <c r="AQ5" s="11"/>
+      <c r="AR5" s="11"/>
+      <c r="AS5" s="11"/>
+      <c r="AT5" s="11"/>
+      <c r="AU5" s="11"/>
+      <c r="AV5" s="11"/>
+      <c r="AW5" s="11"/>
+      <c r="AX5" s="11"/>
+      <c r="AY5" s="11"/>
+      <c r="AZ5" s="11"/>
+      <c r="BA5" s="11"/>
+      <c r="BB5" s="11"/>
+    </row>
+    <row r="6" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="37"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="108"/>
+      <c r="K6" s="38"/>
+      <c r="M6" s="37"/>
+      <c r="N6" s="49"/>
+      <c r="O6" s="40"/>
+      <c r="P6" s="108"/>
+      <c r="Q6" s="108"/>
+      <c r="R6" s="38"/>
+      <c r="S6" s="9"/>
+      <c r="T6" s="39"/>
+      <c r="U6" s="39"/>
+      <c r="V6" s="39"/>
+      <c r="AF6" s="11"/>
+      <c r="AG6" s="11"/>
+      <c r="AH6" s="11"/>
+      <c r="AI6" s="11"/>
+      <c r="AJ6" s="11"/>
+      <c r="AK6" s="11"/>
+      <c r="AL6" s="11"/>
+      <c r="AM6" s="11"/>
+      <c r="AN6" s="11"/>
+      <c r="AO6" s="11"/>
+      <c r="AP6" s="11"/>
+      <c r="AQ6" s="11"/>
+      <c r="AR6" s="11"/>
+      <c r="AS6" s="11"/>
+      <c r="AT6" s="11"/>
+      <c r="AU6" s="11"/>
+      <c r="AV6" s="11"/>
+      <c r="AW6" s="11"/>
+      <c r="AX6" s="11"/>
+      <c r="AY6" s="11"/>
+      <c r="AZ6" s="11"/>
+      <c r="BA6" s="11"/>
+      <c r="BB6" s="11"/>
+    </row>
+    <row r="7" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A7" s="27">
+        <v>1</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="52">
+        <v>29</v>
+      </c>
+      <c r="D7" s="52"/>
+      <c r="E7" s="52"/>
+      <c r="F7" s="52"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="52"/>
+      <c r="I7" s="52">
+        <v>3</v>
+      </c>
+      <c r="J7" s="53"/>
+      <c r="K7" s="54">
+        <v>6</v>
+      </c>
+      <c r="L7" s="55"/>
+      <c r="M7" s="56"/>
+      <c r="N7" s="57"/>
+      <c r="O7" s="52">
+        <v>1</v>
+      </c>
+      <c r="P7" s="53"/>
+      <c r="Q7" s="53">
+        <v>1</v>
+      </c>
+      <c r="R7" s="54"/>
+      <c r="S7" s="55"/>
+      <c r="T7" s="58">
+        <f>H7+I7+J7+K7+N7+P7+R7</f>
+        <v>9</v>
+      </c>
+      <c r="U7" s="58">
+        <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
+        <v>753</v>
+      </c>
+      <c r="V7" s="58">
+        <f>U7/24</f>
+        <v>31.375</v>
+      </c>
+      <c r="W7" s="50"/>
+      <c r="AF7" s="12"/>
+      <c r="AG7" s="12"/>
+      <c r="AH7" s="12"/>
+      <c r="AI7" s="12"/>
+      <c r="AJ7" s="12"/>
+      <c r="AK7" s="12"/>
+      <c r="AL7" s="12"/>
+      <c r="AM7" s="12"/>
+      <c r="AN7" s="12"/>
+      <c r="AO7" s="12"/>
+      <c r="AP7" s="12"/>
+      <c r="AQ7" s="12"/>
+      <c r="AR7" s="12"/>
+      <c r="AS7" s="12"/>
+      <c r="AT7" s="12"/>
+      <c r="AU7" s="12"/>
+      <c r="AV7" s="12"/>
+      <c r="AW7" s="12"/>
+      <c r="AX7" s="12"/>
+      <c r="AY7" s="12"/>
+      <c r="AZ7" s="12"/>
+      <c r="BA7" s="12"/>
+      <c r="BB7" s="12"/>
+    </row>
+    <row r="8" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="27">
+        <f>A7+1</f>
+        <v>2</v>
+      </c>
+      <c r="B8" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="59">
+        <f>36+30</f>
+        <v>66</v>
+      </c>
+      <c r="D8" s="59"/>
+      <c r="E8" s="59"/>
+      <c r="F8" s="59"/>
+      <c r="G8" s="59"/>
+      <c r="H8" s="59"/>
+      <c r="I8" s="59"/>
+      <c r="J8" s="60"/>
+      <c r="K8" s="61"/>
+      <c r="L8" s="62"/>
+      <c r="M8" s="63">
+        <v>1</v>
+      </c>
+      <c r="N8" s="64"/>
+      <c r="O8" s="65">
+        <v>1</v>
+      </c>
+      <c r="P8" s="66">
+        <v>12</v>
+      </c>
+      <c r="Q8" s="66"/>
+      <c r="R8" s="67"/>
+      <c r="S8" s="62"/>
+      <c r="T8" s="68">
+        <f t="shared" ref="T8:T41" si="0">H8+I8+J8+K8+N8+P8+R8</f>
+        <v>12</v>
+      </c>
+      <c r="U8" s="69">
+        <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
+        <v>1644</v>
+      </c>
+      <c r="V8" s="69">
+        <f>U8/24</f>
+        <v>68.5</v>
+      </c>
+      <c r="W8" s="50"/>
+      <c r="AF8" s="12"/>
+      <c r="AG8" s="12"/>
+      <c r="AH8" s="12"/>
+      <c r="AI8" s="12"/>
+      <c r="AJ8" s="12"/>
+      <c r="AK8" s="12"/>
+      <c r="AL8" s="12"/>
+      <c r="AM8" s="12"/>
+      <c r="AN8" s="12"/>
+      <c r="AO8" s="12"/>
+      <c r="AP8" s="12"/>
+      <c r="AQ8" s="12"/>
+      <c r="AR8" s="12"/>
+      <c r="AS8" s="12"/>
+      <c r="AT8" s="12"/>
+      <c r="AU8" s="12"/>
+      <c r="AV8" s="12"/>
+      <c r="AW8" s="12"/>
+      <c r="AX8" s="12"/>
+      <c r="AY8" s="12"/>
+      <c r="AZ8" s="12"/>
+      <c r="BA8" s="12"/>
+      <c r="BB8" s="12"/>
+    </row>
+    <row r="9" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A9" s="27">
+        <f t="shared" ref="A9:A57" si="1">A8+1</f>
+        <v>3</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="70">
+        <f>23+30</f>
+        <v>53</v>
+      </c>
+      <c r="D9" s="70"/>
+      <c r="E9" s="70"/>
+      <c r="F9" s="70"/>
+      <c r="G9" s="70"/>
+      <c r="H9" s="70"/>
+      <c r="I9" s="70"/>
+      <c r="J9" s="71"/>
+      <c r="K9" s="72"/>
+      <c r="L9" s="55"/>
+      <c r="M9" s="73"/>
+      <c r="N9" s="74"/>
+      <c r="O9" s="70"/>
+      <c r="P9" s="71"/>
+      <c r="Q9" s="71"/>
+      <c r="R9" s="72"/>
+      <c r="S9" s="55"/>
+      <c r="T9" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U9" s="76">
+        <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
+        <v>1272</v>
+      </c>
+      <c r="V9" s="76">
+        <f t="shared" ref="V9:V11" si="3">U9/24</f>
+        <v>53</v>
+      </c>
+      <c r="W9" s="50"/>
+      <c r="AF9" s="12"/>
+      <c r="AG9" s="12"/>
+      <c r="AH9" s="12"/>
+      <c r="AI9" s="12"/>
+      <c r="AJ9" s="12"/>
+      <c r="AK9" s="12"/>
+      <c r="AL9" s="12"/>
+      <c r="AM9" s="12"/>
+      <c r="AN9" s="12"/>
+      <c r="AO9" s="12"/>
+      <c r="AP9" s="12"/>
+      <c r="AQ9" s="12"/>
+      <c r="AR9" s="12"/>
+      <c r="AS9" s="12"/>
+      <c r="AT9" s="12"/>
+      <c r="AU9" s="12"/>
+      <c r="AV9" s="12"/>
+      <c r="AW9" s="12"/>
+      <c r="AX9" s="12"/>
+      <c r="AY9" s="12"/>
+      <c r="AZ9" s="12"/>
+      <c r="BA9" s="12"/>
+      <c r="BB9" s="12"/>
+    </row>
+    <row r="10" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A10" s="27">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="70">
+        <v>9</v>
+      </c>
+      <c r="D10" s="70"/>
+      <c r="E10" s="70"/>
+      <c r="F10" s="70"/>
+      <c r="G10" s="70"/>
+      <c r="H10" s="70"/>
+      <c r="I10" s="70"/>
+      <c r="J10" s="71"/>
+      <c r="K10" s="72"/>
+      <c r="L10" s="55"/>
+      <c r="M10" s="73"/>
+      <c r="N10" s="74"/>
+      <c r="O10" s="70"/>
+      <c r="P10" s="71"/>
+      <c r="Q10" s="71"/>
+      <c r="R10" s="72"/>
+      <c r="S10" s="55"/>
+      <c r="T10" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U10" s="58">
+        <f t="shared" si="2"/>
+        <v>216</v>
+      </c>
+      <c r="V10" s="58">
+        <f t="shared" si="3"/>
+        <v>9</v>
+      </c>
+      <c r="W10" s="50"/>
+      <c r="AF10" s="12"/>
+      <c r="AG10" s="12"/>
+      <c r="AH10" s="12"/>
+      <c r="AI10" s="12"/>
+      <c r="AJ10" s="12"/>
+      <c r="AK10" s="12"/>
+      <c r="AL10" s="12"/>
+      <c r="AM10" s="12"/>
+      <c r="AN10" s="12"/>
+      <c r="AO10" s="12"/>
+      <c r="AP10" s="12"/>
+      <c r="AQ10" s="12"/>
+      <c r="AR10" s="12"/>
+      <c r="AS10" s="12"/>
+      <c r="AT10" s="12"/>
+      <c r="AU10" s="12"/>
+      <c r="AV10" s="12"/>
+      <c r="AW10" s="12"/>
+      <c r="AX10" s="12"/>
+      <c r="AY10" s="12"/>
+      <c r="AZ10" s="12"/>
+      <c r="BA10" s="12"/>
+      <c r="BB10" s="12"/>
+    </row>
+    <row r="11" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A11" s="27">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="70"/>
+      <c r="D11" s="70"/>
+      <c r="E11" s="70"/>
+      <c r="F11" s="70"/>
+      <c r="G11" s="70"/>
+      <c r="H11" s="70"/>
+      <c r="I11" s="70"/>
+      <c r="J11" s="71"/>
+      <c r="K11" s="72">
+        <v>2</v>
+      </c>
+      <c r="L11" s="55"/>
+      <c r="M11" s="73"/>
+      <c r="N11" s="74"/>
+      <c r="O11" s="70"/>
+      <c r="P11" s="71"/>
+      <c r="Q11" s="71"/>
+      <c r="R11" s="72"/>
+      <c r="S11" s="55"/>
+      <c r="T11" s="58">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="U11" s="58">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="V11" s="58">
+        <f t="shared" si="3"/>
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="AF11" s="12"/>
+      <c r="AG11" s="12"/>
+      <c r="AH11" s="12"/>
+      <c r="AI11" s="12"/>
+      <c r="AJ11" s="12"/>
+      <c r="AK11" s="12"/>
+      <c r="AL11" s="12"/>
+      <c r="AM11" s="12"/>
+      <c r="AN11" s="12"/>
+      <c r="AO11" s="12"/>
+      <c r="AP11" s="12"/>
+      <c r="AQ11" s="12"/>
+      <c r="AR11" s="12"/>
+      <c r="AS11" s="12"/>
+      <c r="AT11" s="12"/>
+      <c r="AU11" s="12"/>
+      <c r="AV11" s="12"/>
+      <c r="AW11" s="12"/>
+      <c r="AX11" s="12"/>
+      <c r="AY11" s="12"/>
+      <c r="AZ11" s="12"/>
+      <c r="BA11" s="12"/>
+      <c r="BB11" s="12"/>
+    </row>
+    <row r="12" spans="1:54" s="13" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="27">
+        <v>7</v>
+      </c>
+      <c r="B12" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="59">
+        <f>1224+53+432+57+1080+29</f>
+        <v>2875</v>
+      </c>
+      <c r="D12" s="59"/>
+      <c r="E12" s="59"/>
+      <c r="F12" s="59"/>
+      <c r="G12" s="59"/>
+      <c r="H12" s="59"/>
+      <c r="I12" s="59"/>
+      <c r="J12" s="60"/>
+      <c r="K12" s="61"/>
+      <c r="L12" s="62"/>
+      <c r="M12" s="63">
+        <v>34</v>
+      </c>
+      <c r="N12" s="64">
+        <v>11</v>
+      </c>
+      <c r="O12" s="65">
+        <v>14</v>
+      </c>
+      <c r="P12" s="66">
+        <v>12</v>
+      </c>
+      <c r="Q12" s="66">
+        <v>16</v>
+      </c>
+      <c r="R12" s="67"/>
+      <c r="S12" s="62"/>
+      <c r="T12" s="69">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="U12" s="69">
+        <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
+        <v>70559</v>
+      </c>
+      <c r="V12" s="69">
+        <f>U12/24</f>
+        <v>2939.9583333333335</v>
+      </c>
+      <c r="W12" s="9"/>
+      <c r="X12" s="9"/>
+      <c r="Y12" s="9"/>
+      <c r="Z12" s="9"/>
+      <c r="AA12" s="9"/>
+      <c r="AB12" s="9"/>
+      <c r="AC12" s="9"/>
+      <c r="AD12" s="9"/>
+      <c r="AE12" s="9"/>
+      <c r="AF12" s="12"/>
+      <c r="AG12" s="12"/>
+      <c r="AH12" s="12"/>
+      <c r="AI12" s="12"/>
+      <c r="AJ12" s="12"/>
+      <c r="AK12" s="12"/>
+      <c r="AL12" s="12"/>
+      <c r="AM12" s="12"/>
+      <c r="AN12" s="12"/>
+      <c r="AO12" s="12"/>
+      <c r="AP12" s="12"/>
+      <c r="AQ12" s="12"/>
+      <c r="AR12" s="12"/>
+      <c r="AS12" s="12"/>
+      <c r="AT12" s="12"/>
+      <c r="AU12" s="12"/>
+      <c r="AV12" s="12"/>
+      <c r="AW12" s="12"/>
+      <c r="AX12" s="12"/>
+      <c r="AY12" s="12"/>
+      <c r="AZ12" s="12"/>
+      <c r="BA12" s="12"/>
+      <c r="BB12" s="12"/>
+    </row>
+    <row r="13" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A13" s="27">
+        <v>11</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="70">
+        <v>2</v>
+      </c>
+      <c r="D13" s="70"/>
+      <c r="E13" s="70"/>
+      <c r="F13" s="70"/>
+      <c r="G13" s="70"/>
+      <c r="H13" s="70">
+        <v>16</v>
+      </c>
+      <c r="I13" s="70"/>
+      <c r="J13" s="71"/>
+      <c r="K13" s="72"/>
+      <c r="L13" s="55"/>
+      <c r="M13" s="73"/>
+      <c r="N13" s="74"/>
+      <c r="O13" s="70"/>
+      <c r="P13" s="71"/>
+      <c r="Q13" s="71"/>
+      <c r="R13" s="72"/>
+      <c r="S13" s="55"/>
+      <c r="T13" s="76">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="U13" s="76">
+        <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
+        <v>64</v>
+      </c>
+      <c r="V13" s="76">
+        <f>U13/24</f>
+        <v>2.6666666666666665</v>
+      </c>
+      <c r="AF13" s="12"/>
+      <c r="AG13" s="12"/>
+      <c r="AH13" s="12"/>
+      <c r="AI13" s="12"/>
+      <c r="AJ13" s="12"/>
+      <c r="AK13" s="12"/>
+      <c r="AL13" s="12"/>
+      <c r="AM13" s="12"/>
+      <c r="AN13" s="12"/>
+      <c r="AO13" s="12"/>
+      <c r="AP13" s="12"/>
+      <c r="AQ13" s="12"/>
+      <c r="AR13" s="12"/>
+      <c r="AS13" s="12"/>
+      <c r="AT13" s="12"/>
+      <c r="AU13" s="12"/>
+      <c r="AV13" s="12"/>
+      <c r="AW13" s="12"/>
+      <c r="AX13" s="12"/>
+      <c r="AY13" s="12"/>
+      <c r="AZ13" s="12"/>
+      <c r="BA13" s="12"/>
+      <c r="BB13" s="12"/>
+    </row>
+    <row r="14" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A14" s="27">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="70">
+        <v>2</v>
+      </c>
+      <c r="D14" s="70"/>
+      <c r="E14" s="70"/>
+      <c r="F14" s="70"/>
+      <c r="G14" s="70"/>
+      <c r="H14" s="70"/>
+      <c r="I14" s="70"/>
+      <c r="J14" s="71"/>
+      <c r="K14" s="72"/>
+      <c r="L14" s="55"/>
+      <c r="M14" s="73"/>
+      <c r="N14" s="74"/>
+      <c r="O14" s="70"/>
+      <c r="P14" s="71"/>
+      <c r="Q14" s="71"/>
+      <c r="R14" s="72"/>
+      <c r="S14" s="55"/>
+      <c r="T14" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U14" s="75">
+        <f t="shared" ref="U14:U36" si="4">C14*24+M14*24+O14*24+Q14*24+T14</f>
+        <v>48</v>
+      </c>
+      <c r="V14" s="75">
+        <f t="shared" ref="V14:V36" si="5">U14/24</f>
+        <v>2</v>
+      </c>
+      <c r="AF14" s="12"/>
+      <c r="AG14" s="12"/>
+      <c r="AH14" s="12"/>
+      <c r="AI14" s="12"/>
+      <c r="AJ14" s="12"/>
+      <c r="AK14" s="12"/>
+      <c r="AL14" s="12"/>
+      <c r="AM14" s="12"/>
+      <c r="AN14" s="12"/>
+      <c r="AO14" s="12"/>
+      <c r="AP14" s="12"/>
+      <c r="AQ14" s="12"/>
+      <c r="AR14" s="12"/>
+      <c r="AS14" s="12"/>
+      <c r="AT14" s="12"/>
+      <c r="AU14" s="12"/>
+      <c r="AV14" s="12"/>
+      <c r="AW14" s="12"/>
+      <c r="AX14" s="12"/>
+      <c r="AY14" s="12"/>
+      <c r="AZ14" s="12"/>
+      <c r="BA14" s="12"/>
+      <c r="BB14" s="12"/>
+    </row>
+    <row r="15" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A15" s="27">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="70"/>
+      <c r="D15" s="70"/>
+      <c r="E15" s="70"/>
+      <c r="F15" s="70"/>
+      <c r="G15" s="70"/>
+      <c r="H15" s="70"/>
+      <c r="I15" s="70"/>
+      <c r="J15" s="71"/>
+      <c r="K15" s="72"/>
+      <c r="L15" s="55"/>
+      <c r="M15" s="73"/>
+      <c r="N15" s="74"/>
+      <c r="O15" s="70"/>
+      <c r="P15" s="71"/>
+      <c r="Q15" s="71"/>
+      <c r="R15" s="72"/>
+      <c r="S15" s="55"/>
+      <c r="T15" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U15" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF15" s="12"/>
+      <c r="AG15" s="12"/>
+      <c r="AH15" s="12"/>
+      <c r="AI15" s="12"/>
+      <c r="AJ15" s="12"/>
+      <c r="AK15" s="12"/>
+      <c r="AL15" s="12"/>
+      <c r="AM15" s="12"/>
+      <c r="AN15" s="12"/>
+      <c r="AO15" s="12"/>
+      <c r="AP15" s="12"/>
+      <c r="AQ15" s="12"/>
+      <c r="AR15" s="12"/>
+      <c r="AS15" s="12"/>
+      <c r="AT15" s="12"/>
+      <c r="AU15" s="12"/>
+      <c r="AV15" s="12"/>
+      <c r="AW15" s="12"/>
+      <c r="AX15" s="12"/>
+      <c r="AY15" s="12"/>
+      <c r="AZ15" s="12"/>
+      <c r="BA15" s="12"/>
+      <c r="BB15" s="12"/>
+    </row>
+    <row r="16" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A16" s="27">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="70"/>
+      <c r="D16" s="70"/>
+      <c r="E16" s="70"/>
+      <c r="F16" s="70"/>
+      <c r="G16" s="70"/>
+      <c r="H16" s="70"/>
+      <c r="I16" s="70"/>
+      <c r="J16" s="71"/>
+      <c r="K16" s="72"/>
+      <c r="L16" s="55"/>
+      <c r="M16" s="73"/>
+      <c r="N16" s="74"/>
+      <c r="O16" s="70"/>
+      <c r="P16" s="71"/>
+      <c r="Q16" s="71"/>
+      <c r="R16" s="72"/>
+      <c r="S16" s="55"/>
+      <c r="T16" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U16" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF16" s="12"/>
+      <c r="AG16" s="12"/>
+      <c r="AH16" s="12"/>
+      <c r="AI16" s="12"/>
+      <c r="AJ16" s="12"/>
+      <c r="AK16" s="12"/>
+      <c r="AL16" s="12"/>
+      <c r="AM16" s="12"/>
+      <c r="AN16" s="12"/>
+      <c r="AO16" s="12"/>
+      <c r="AP16" s="12"/>
+      <c r="AQ16" s="12"/>
+      <c r="AR16" s="12"/>
+      <c r="AS16" s="12"/>
+      <c r="AT16" s="12"/>
+      <c r="AU16" s="12"/>
+      <c r="AV16" s="12"/>
+      <c r="AW16" s="12"/>
+      <c r="AX16" s="12"/>
+      <c r="AY16" s="12"/>
+      <c r="AZ16" s="12"/>
+      <c r="BA16" s="12"/>
+      <c r="BB16" s="12"/>
+    </row>
+    <row r="17" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A17" s="27">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="70"/>
+      <c r="D17" s="70"/>
+      <c r="E17" s="70"/>
+      <c r="F17" s="70"/>
+      <c r="G17" s="70"/>
+      <c r="H17" s="70">
+        <f>3*24</f>
+        <v>72</v>
+      </c>
+      <c r="I17" s="70"/>
+      <c r="J17" s="71"/>
+      <c r="K17" s="72"/>
+      <c r="L17" s="55"/>
+      <c r="M17" s="73"/>
+      <c r="N17" s="74"/>
+      <c r="O17" s="70"/>
+      <c r="P17" s="71"/>
+      <c r="Q17" s="71"/>
+      <c r="R17" s="72"/>
+      <c r="S17" s="55"/>
+      <c r="T17" s="58">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="U17" s="75">
+        <f t="shared" si="4"/>
+        <v>72</v>
+      </c>
+      <c r="V17" s="75">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="AF17" s="12"/>
+      <c r="AG17" s="12"/>
+      <c r="AH17" s="12"/>
+      <c r="AI17" s="12"/>
+      <c r="AJ17" s="12"/>
+      <c r="AK17" s="12"/>
+      <c r="AL17" s="12"/>
+      <c r="AM17" s="12"/>
+      <c r="AN17" s="12"/>
+      <c r="AO17" s="12"/>
+      <c r="AP17" s="12"/>
+      <c r="AQ17" s="12"/>
+      <c r="AR17" s="12"/>
+      <c r="AS17" s="12"/>
+      <c r="AT17" s="12"/>
+      <c r="AU17" s="12"/>
+      <c r="AV17" s="12"/>
+      <c r="AW17" s="12"/>
+      <c r="AX17" s="12"/>
+      <c r="AY17" s="12"/>
+      <c r="AZ17" s="12"/>
+      <c r="BA17" s="12"/>
+      <c r="BB17" s="12"/>
+    </row>
+    <row r="18" spans="1:54" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="27">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="70"/>
+      <c r="D18" s="70"/>
+      <c r="E18" s="70"/>
+      <c r="F18" s="70"/>
+      <c r="G18" s="70"/>
+      <c r="H18" s="70"/>
+      <c r="I18" s="70"/>
+      <c r="J18" s="71"/>
+      <c r="K18" s="72"/>
+      <c r="L18" s="55"/>
+      <c r="M18" s="73"/>
+      <c r="N18" s="74"/>
+      <c r="O18" s="70"/>
+      <c r="P18" s="71"/>
+      <c r="Q18" s="71"/>
+      <c r="R18" s="72"/>
+      <c r="S18" s="55"/>
+      <c r="T18" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U18" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF18" s="12"/>
+      <c r="AG18" s="12"/>
+      <c r="AH18" s="12"/>
+      <c r="AI18" s="12"/>
+      <c r="AJ18" s="12"/>
+      <c r="AK18" s="12"/>
+      <c r="AL18" s="12"/>
+      <c r="AM18" s="12"/>
+      <c r="AN18" s="12"/>
+      <c r="AO18" s="12"/>
+      <c r="AP18" s="12"/>
+      <c r="AQ18" s="12"/>
+      <c r="AR18" s="12"/>
+      <c r="AS18" s="12"/>
+      <c r="AT18" s="12"/>
+      <c r="AU18" s="12"/>
+      <c r="AV18" s="12"/>
+      <c r="AW18" s="12"/>
+      <c r="AX18" s="12"/>
+      <c r="AY18" s="12"/>
+      <c r="AZ18" s="12"/>
+      <c r="BA18" s="12"/>
+      <c r="BB18" s="12"/>
+    </row>
+    <row r="19" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A19" s="27">
+        <v>16</v>
+      </c>
+      <c r="B19" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="70">
+        <v>1</v>
+      </c>
+      <c r="D19" s="70"/>
+      <c r="E19" s="70"/>
+      <c r="F19" s="70"/>
+      <c r="G19" s="70"/>
+      <c r="H19" s="70">
+        <f>24+20</f>
+        <v>44</v>
+      </c>
+      <c r="I19" s="70"/>
+      <c r="J19" s="71"/>
+      <c r="K19" s="72"/>
+      <c r="L19" s="55"/>
+      <c r="M19" s="73"/>
+      <c r="N19" s="74"/>
+      <c r="O19" s="70"/>
+      <c r="P19" s="71"/>
+      <c r="Q19" s="71"/>
+      <c r="R19" s="72"/>
+      <c r="S19" s="55"/>
+      <c r="T19" s="58">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="U19" s="75">
+        <f t="shared" si="4"/>
+        <v>68</v>
+      </c>
+      <c r="V19" s="75">
+        <f t="shared" si="5"/>
+        <v>2.8333333333333335</v>
+      </c>
+      <c r="AF19" s="12"/>
+      <c r="AG19" s="12"/>
+      <c r="AH19" s="12"/>
+      <c r="AI19" s="12"/>
+      <c r="AJ19" s="12"/>
+      <c r="AK19" s="12"/>
+      <c r="AL19" s="12"/>
+      <c r="AM19" s="12"/>
+      <c r="AN19" s="12"/>
+      <c r="AO19" s="12"/>
+      <c r="AP19" s="12"/>
+      <c r="AQ19" s="12"/>
+      <c r="AR19" s="12"/>
+      <c r="AS19" s="12"/>
+      <c r="AT19" s="12"/>
+      <c r="AU19" s="12"/>
+      <c r="AV19" s="12"/>
+      <c r="AW19" s="12"/>
+      <c r="AX19" s="12"/>
+      <c r="AY19" s="12"/>
+      <c r="AZ19" s="12"/>
+      <c r="BA19" s="12"/>
+      <c r="BB19" s="12"/>
+    </row>
+    <row r="20" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A20" s="27">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="B20" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="70">
+        <v>5</v>
+      </c>
+      <c r="D20" s="70"/>
+      <c r="E20" s="70"/>
+      <c r="F20" s="70"/>
+      <c r="G20" s="70"/>
+      <c r="H20" s="70"/>
+      <c r="I20" s="70"/>
+      <c r="J20" s="71"/>
+      <c r="K20" s="72"/>
+      <c r="L20" s="55"/>
+      <c r="M20" s="73"/>
+      <c r="N20" s="74"/>
+      <c r="O20" s="70"/>
+      <c r="P20" s="71"/>
+      <c r="Q20" s="71"/>
+      <c r="R20" s="72"/>
+      <c r="S20" s="55"/>
+      <c r="T20" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U20" s="75">
+        <f t="shared" si="4"/>
+        <v>120</v>
+      </c>
+      <c r="V20" s="75">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="AF20" s="12"/>
+      <c r="AG20" s="12"/>
+      <c r="AH20" s="12"/>
+      <c r="AI20" s="12"/>
+      <c r="AJ20" s="12"/>
+      <c r="AK20" s="12"/>
+      <c r="AL20" s="12"/>
+      <c r="AM20" s="12"/>
+      <c r="AN20" s="12"/>
+      <c r="AO20" s="12"/>
+      <c r="AP20" s="12"/>
+      <c r="AQ20" s="12"/>
+      <c r="AR20" s="12"/>
+      <c r="AS20" s="12"/>
+      <c r="AT20" s="12"/>
+      <c r="AU20" s="12"/>
+      <c r="AV20" s="12"/>
+      <c r="AW20" s="12"/>
+      <c r="AX20" s="12"/>
+      <c r="AY20" s="12"/>
+      <c r="AZ20" s="12"/>
+      <c r="BA20" s="12"/>
+      <c r="BB20" s="12"/>
+    </row>
+    <row r="21" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A21" s="27">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="B21" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="70"/>
+      <c r="D21" s="70"/>
+      <c r="E21" s="70"/>
+      <c r="F21" s="70"/>
+      <c r="G21" s="70"/>
+      <c r="H21" s="70">
+        <f>2*24</f>
+        <v>48</v>
+      </c>
+      <c r="I21" s="70"/>
+      <c r="J21" s="71"/>
+      <c r="K21" s="72"/>
+      <c r="L21" s="55"/>
+      <c r="M21" s="73"/>
+      <c r="N21" s="74"/>
+      <c r="O21" s="70"/>
+      <c r="P21" s="71"/>
+      <c r="Q21" s="71"/>
+      <c r="R21" s="72"/>
+      <c r="S21" s="55"/>
+      <c r="T21" s="58">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+      <c r="U21" s="75">
+        <f t="shared" si="4"/>
+        <v>48</v>
+      </c>
+      <c r="V21" s="75">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="AF21" s="12"/>
+      <c r="AG21" s="12"/>
+      <c r="AH21" s="12"/>
+      <c r="AI21" s="12"/>
+      <c r="AJ21" s="12"/>
+      <c r="AK21" s="12"/>
+      <c r="AL21" s="12"/>
+      <c r="AM21" s="12"/>
+      <c r="AN21" s="12"/>
+      <c r="AO21" s="12"/>
+      <c r="AP21" s="12"/>
+      <c r="AQ21" s="12"/>
+      <c r="AR21" s="12"/>
+      <c r="AS21" s="12"/>
+      <c r="AT21" s="12"/>
+      <c r="AU21" s="12"/>
+      <c r="AV21" s="12"/>
+      <c r="AW21" s="12"/>
+      <c r="AX21" s="12"/>
+      <c r="AY21" s="12"/>
+      <c r="AZ21" s="12"/>
+      <c r="BA21" s="12"/>
+      <c r="BB21" s="12"/>
+    </row>
+    <row r="22" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="27">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="B22" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="70">
+        <v>1</v>
+      </c>
+      <c r="D22" s="70"/>
+      <c r="E22" s="70"/>
+      <c r="F22" s="70"/>
+      <c r="G22" s="70"/>
+      <c r="H22" s="70">
+        <v>20</v>
+      </c>
+      <c r="I22" s="70"/>
+      <c r="J22" s="71"/>
+      <c r="K22" s="72"/>
+      <c r="L22" s="55"/>
+      <c r="M22" s="73"/>
+      <c r="N22" s="74"/>
+      <c r="O22" s="70"/>
+      <c r="P22" s="71"/>
+      <c r="Q22" s="71"/>
+      <c r="R22" s="72"/>
+      <c r="S22" s="55"/>
+      <c r="T22" s="58">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="U22" s="75">
+        <f t="shared" si="4"/>
+        <v>44</v>
+      </c>
+      <c r="V22" s="75">
+        <f t="shared" si="5"/>
+        <v>1.8333333333333333</v>
+      </c>
+      <c r="W22" s="9"/>
+      <c r="X22" s="9"/>
+      <c r="Y22" s="9"/>
+      <c r="Z22" s="9"/>
+      <c r="AA22" s="9"/>
+      <c r="AB22" s="9"/>
+      <c r="AC22" s="9"/>
+      <c r="AD22" s="9"/>
+      <c r="AE22" s="9"/>
+      <c r="AF22" s="12"/>
+      <c r="AG22" s="12"/>
+      <c r="AH22" s="12"/>
+      <c r="AI22" s="12"/>
+      <c r="AJ22" s="12"/>
+      <c r="AK22" s="12"/>
+      <c r="AL22" s="12"/>
+      <c r="AM22" s="12"/>
+      <c r="AN22" s="12"/>
+      <c r="AO22" s="12"/>
+      <c r="AP22" s="12"/>
+      <c r="AQ22" s="12"/>
+      <c r="AR22" s="12"/>
+      <c r="AS22" s="12"/>
+      <c r="AT22" s="12"/>
+      <c r="AU22" s="12"/>
+      <c r="AV22" s="12"/>
+      <c r="AW22" s="12"/>
+      <c r="AX22" s="12"/>
+      <c r="AY22" s="12"/>
+      <c r="AZ22" s="12"/>
+      <c r="BA22" s="12"/>
+      <c r="BB22" s="12"/>
+    </row>
+    <row r="23" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="27">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="B23" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="70"/>
+      <c r="D23" s="70"/>
+      <c r="E23" s="70"/>
+      <c r="F23" s="70"/>
+      <c r="G23" s="70"/>
+      <c r="H23" s="70">
+        <f>37*24+19</f>
+        <v>907</v>
+      </c>
+      <c r="I23" s="70"/>
+      <c r="J23" s="71"/>
+      <c r="K23" s="72"/>
+      <c r="L23" s="55"/>
+      <c r="M23" s="73"/>
+      <c r="N23" s="74"/>
+      <c r="O23" s="70"/>
+      <c r="P23" s="71"/>
+      <c r="Q23" s="71"/>
+      <c r="R23" s="72"/>
+      <c r="S23" s="55"/>
+      <c r="T23" s="58">
+        <f t="shared" si="0"/>
+        <v>907</v>
+      </c>
+      <c r="U23" s="75">
+        <f t="shared" si="4"/>
+        <v>907</v>
+      </c>
+      <c r="V23" s="75">
+        <f t="shared" si="5"/>
+        <v>37.791666666666664</v>
+      </c>
+      <c r="W23" s="9"/>
+      <c r="X23" s="9"/>
+      <c r="Y23" s="9"/>
+      <c r="Z23" s="9"/>
+      <c r="AA23" s="9"/>
+      <c r="AB23" s="9"/>
+      <c r="AC23" s="9"/>
+      <c r="AD23" s="9"/>
+      <c r="AE23" s="9"/>
+      <c r="AF23" s="12"/>
+      <c r="AG23" s="12"/>
+      <c r="AH23" s="12"/>
+      <c r="AI23" s="12"/>
+      <c r="AJ23" s="12"/>
+      <c r="AK23" s="12"/>
+      <c r="AL23" s="12"/>
+      <c r="AM23" s="12"/>
+      <c r="AN23" s="12"/>
+      <c r="AO23" s="12"/>
+      <c r="AP23" s="12"/>
+      <c r="AQ23" s="12"/>
+      <c r="AR23" s="12"/>
+      <c r="AS23" s="12"/>
+      <c r="AT23" s="12"/>
+      <c r="AU23" s="12"/>
+      <c r="AV23" s="12"/>
+      <c r="AW23" s="12"/>
+      <c r="AX23" s="12"/>
+      <c r="AY23" s="12"/>
+      <c r="AZ23" s="12"/>
+      <c r="BA23" s="12"/>
+      <c r="BB23" s="12"/>
+    </row>
+    <row r="24" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A24" s="27">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="B24" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" s="70">
+        <v>2</v>
+      </c>
+      <c r="D24" s="70"/>
+      <c r="E24" s="70"/>
+      <c r="F24" s="70"/>
+      <c r="G24" s="70"/>
+      <c r="H24" s="70">
+        <f>3*24</f>
+        <v>72</v>
+      </c>
+      <c r="I24" s="70"/>
+      <c r="J24" s="71"/>
+      <c r="K24" s="72"/>
+      <c r="L24" s="55"/>
+      <c r="M24" s="73"/>
+      <c r="N24" s="74"/>
+      <c r="O24" s="70"/>
+      <c r="P24" s="71"/>
+      <c r="Q24" s="71"/>
+      <c r="R24" s="72"/>
+      <c r="S24" s="55"/>
+      <c r="T24" s="58">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="U24" s="75">
+        <f t="shared" si="4"/>
+        <v>120</v>
+      </c>
+      <c r="V24" s="75">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="AF24" s="12"/>
+      <c r="AG24" s="12"/>
+      <c r="AH24" s="12"/>
+      <c r="AI24" s="12"/>
+      <c r="AJ24" s="12"/>
+      <c r="AK24" s="12"/>
+      <c r="AL24" s="12"/>
+      <c r="AM24" s="12"/>
+      <c r="AN24" s="12"/>
+      <c r="AO24" s="12"/>
+      <c r="AP24" s="12"/>
+      <c r="AQ24" s="12"/>
+      <c r="AR24" s="12"/>
+      <c r="AS24" s="12"/>
+      <c r="AT24" s="12"/>
+      <c r="AU24" s="12"/>
+      <c r="AV24" s="12"/>
+      <c r="AW24" s="12"/>
+      <c r="AX24" s="12"/>
+      <c r="AY24" s="12"/>
+      <c r="AZ24" s="12"/>
+      <c r="BA24" s="12"/>
+      <c r="BB24" s="12"/>
+    </row>
+    <row r="25" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A25" s="27">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="70">
+        <f>2+126</f>
+        <v>128</v>
+      </c>
+      <c r="D25" s="70"/>
+      <c r="E25" s="70"/>
+      <c r="F25" s="70"/>
+      <c r="G25" s="70"/>
+      <c r="H25" s="70"/>
+      <c r="I25" s="70">
+        <v>1</v>
+      </c>
+      <c r="J25" s="71"/>
+      <c r="K25" s="72"/>
+      <c r="L25" s="55"/>
+      <c r="M25" s="73">
+        <v>1</v>
+      </c>
+      <c r="N25" s="74"/>
+      <c r="O25" s="70"/>
+      <c r="P25" s="71"/>
+      <c r="Q25" s="71">
+        <v>1</v>
+      </c>
+      <c r="R25" s="72"/>
+      <c r="S25" s="55"/>
+      <c r="T25" s="58">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="U25" s="75">
+        <f t="shared" si="4"/>
+        <v>3121</v>
+      </c>
+      <c r="V25" s="75">
+        <f t="shared" si="5"/>
+        <v>130.04166666666666</v>
+      </c>
+      <c r="AY25" s="14" t="e">
+        <f>#REF!-AY24</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="27">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="B26" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="70">
+        <v>3</v>
+      </c>
+      <c r="D26" s="70"/>
+      <c r="E26" s="70"/>
+      <c r="F26" s="70"/>
+      <c r="G26" s="70"/>
+      <c r="H26" s="70"/>
+      <c r="I26" s="70"/>
+      <c r="J26" s="71"/>
+      <c r="K26" s="72"/>
+      <c r="L26" s="55"/>
+      <c r="M26" s="73"/>
+      <c r="N26" s="74"/>
+      <c r="O26" s="70"/>
+      <c r="P26" s="71"/>
+      <c r="Q26" s="71"/>
+      <c r="R26" s="72"/>
+      <c r="S26" s="55"/>
+      <c r="T26" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U26" s="75">
+        <f t="shared" si="4"/>
+        <v>72</v>
+      </c>
+      <c r="V26" s="75">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="W26" s="9"/>
+      <c r="X26" s="9"/>
+      <c r="Y26" s="9"/>
+      <c r="Z26" s="9"/>
+      <c r="AA26" s="9"/>
+      <c r="AB26" s="9"/>
+      <c r="AC26" s="9"/>
+      <c r="AD26" s="9"/>
+      <c r="AE26" s="9"/>
+    </row>
+    <row r="27" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="27">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="B27" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27" s="70">
+        <v>1</v>
+      </c>
+      <c r="D27" s="70"/>
+      <c r="E27" s="70"/>
+      <c r="F27" s="70"/>
+      <c r="G27" s="70"/>
+      <c r="H27" s="70"/>
+      <c r="I27" s="70"/>
+      <c r="J27" s="71"/>
+      <c r="K27" s="72"/>
+      <c r="L27" s="55"/>
+      <c r="M27" s="73"/>
+      <c r="N27" s="74"/>
+      <c r="O27" s="70"/>
+      <c r="P27" s="71"/>
+      <c r="Q27" s="71"/>
+      <c r="R27" s="72"/>
+      <c r="S27" s="55"/>
+      <c r="T27" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U27" s="75">
+        <f t="shared" si="4"/>
+        <v>24</v>
+      </c>
+      <c r="V27" s="75">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="W27" s="9"/>
+      <c r="X27" s="9"/>
+      <c r="Y27" s="9"/>
+      <c r="Z27" s="9"/>
+      <c r="AA27" s="9"/>
+      <c r="AB27" s="9"/>
+      <c r="AC27" s="9"/>
+      <c r="AD27" s="9"/>
+      <c r="AE27" s="9"/>
+    </row>
+    <row r="28" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="27">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="B28" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="70">
+        <f>23+252</f>
+        <v>275</v>
+      </c>
+      <c r="D28" s="70"/>
+      <c r="E28" s="70"/>
+      <c r="F28" s="70"/>
+      <c r="G28" s="70"/>
+      <c r="H28" s="70"/>
+      <c r="I28" s="70"/>
+      <c r="J28" s="71"/>
+      <c r="K28" s="72"/>
+      <c r="L28" s="55"/>
+      <c r="M28" s="73">
+        <v>2</v>
+      </c>
+      <c r="N28" s="74"/>
+      <c r="O28" s="70">
+        <v>5</v>
+      </c>
+      <c r="P28" s="71"/>
+      <c r="Q28" s="71">
+        <v>3</v>
+      </c>
+      <c r="R28" s="72"/>
+      <c r="S28" s="55"/>
+      <c r="T28" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U28" s="75">
+        <f t="shared" si="4"/>
+        <v>6840</v>
+      </c>
+      <c r="V28" s="75">
+        <f t="shared" si="5"/>
+        <v>285</v>
+      </c>
+      <c r="W28" s="9"/>
+      <c r="X28" s="9"/>
+      <c r="Y28" s="9"/>
+      <c r="Z28" s="9"/>
+      <c r="AA28" s="9"/>
+      <c r="AB28" s="9"/>
+      <c r="AC28" s="9"/>
+      <c r="AD28" s="9"/>
+      <c r="AE28" s="9"/>
+    </row>
+    <row r="29" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A29" s="27">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="B29" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" s="70"/>
+      <c r="D29" s="70"/>
+      <c r="E29" s="70"/>
+      <c r="F29" s="70"/>
+      <c r="G29" s="70"/>
+      <c r="H29" s="70"/>
+      <c r="I29" s="70">
+        <v>5</v>
+      </c>
+      <c r="J29" s="71"/>
+      <c r="K29" s="72"/>
+      <c r="L29" s="55"/>
+      <c r="M29" s="73"/>
+      <c r="N29" s="74"/>
+      <c r="O29" s="70"/>
+      <c r="P29" s="71"/>
+      <c r="Q29" s="71"/>
+      <c r="R29" s="72"/>
+      <c r="S29" s="55"/>
+      <c r="T29" s="58">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="U29" s="75">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="V29" s="75">
+        <f t="shared" si="5"/>
+        <v>0.20833333333333334</v>
+      </c>
+    </row>
+    <row r="30" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A30" s="27">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="B30" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="70"/>
+      <c r="D30" s="70"/>
+      <c r="E30" s="70"/>
+      <c r="F30" s="70"/>
+      <c r="G30" s="70"/>
+      <c r="H30" s="70"/>
+      <c r="I30" s="70"/>
+      <c r="J30" s="71"/>
+      <c r="K30" s="72"/>
+      <c r="L30" s="55"/>
+      <c r="M30" s="73"/>
+      <c r="N30" s="74"/>
+      <c r="O30" s="70"/>
+      <c r="P30" s="71"/>
+      <c r="Q30" s="71"/>
+      <c r="R30" s="72"/>
+      <c r="S30" s="55"/>
+      <c r="T30" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U30" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V30" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A31" s="27">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="B31" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" s="70"/>
+      <c r="D31" s="70"/>
+      <c r="E31" s="70"/>
+      <c r="F31" s="70"/>
+      <c r="G31" s="70"/>
+      <c r="H31" s="70"/>
+      <c r="I31" s="70"/>
+      <c r="J31" s="71"/>
+      <c r="K31" s="72"/>
+      <c r="L31" s="55"/>
+      <c r="M31" s="73"/>
+      <c r="N31" s="74"/>
+      <c r="O31" s="70"/>
+      <c r="P31" s="71"/>
+      <c r="Q31" s="71"/>
+      <c r="R31" s="72"/>
+      <c r="S31" s="55"/>
+      <c r="T31" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U31" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V31" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A32" s="27">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="B32" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" s="70"/>
+      <c r="D32" s="70"/>
+      <c r="E32" s="70"/>
+      <c r="F32" s="70"/>
+      <c r="G32" s="70"/>
+      <c r="H32" s="70"/>
+      <c r="I32" s="70"/>
+      <c r="J32" s="71"/>
+      <c r="K32" s="72"/>
+      <c r="L32" s="55"/>
+      <c r="M32" s="73"/>
+      <c r="N32" s="74"/>
+      <c r="O32" s="70"/>
+      <c r="P32" s="71"/>
+      <c r="Q32" s="71"/>
+      <c r="R32" s="72"/>
+      <c r="S32" s="55"/>
+      <c r="T32" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U32" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V32" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A33" s="27">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="B33" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" s="70"/>
+      <c r="D33" s="70"/>
+      <c r="E33" s="70"/>
+      <c r="F33" s="70"/>
+      <c r="G33" s="70"/>
+      <c r="H33" s="70"/>
+      <c r="I33" s="70"/>
+      <c r="J33" s="71"/>
+      <c r="K33" s="72"/>
+      <c r="L33" s="55"/>
+      <c r="M33" s="73"/>
+      <c r="N33" s="74"/>
+      <c r="O33" s="70"/>
+      <c r="P33" s="71"/>
+      <c r="Q33" s="71"/>
+      <c r="R33" s="72"/>
+      <c r="S33" s="55"/>
+      <c r="T33" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U33" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V33" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A34" s="27">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="B34" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" s="70">
+        <f>50+72+144</f>
+        <v>266</v>
+      </c>
+      <c r="D34" s="70"/>
+      <c r="E34" s="70"/>
+      <c r="F34" s="70"/>
+      <c r="G34" s="70"/>
+      <c r="H34" s="70"/>
+      <c r="I34" s="70">
+        <v>1</v>
+      </c>
+      <c r="J34" s="71"/>
+      <c r="K34" s="72">
+        <v>1</v>
+      </c>
+      <c r="L34" s="55"/>
+      <c r="M34" s="73">
+        <v>1</v>
+      </c>
+      <c r="N34" s="74"/>
+      <c r="O34" s="70">
+        <v>2</v>
+      </c>
+      <c r="P34" s="71"/>
+      <c r="Q34" s="71">
+        <v>2</v>
+      </c>
+      <c r="R34" s="72"/>
+      <c r="S34" s="55"/>
+      <c r="T34" s="58">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="U34" s="75">
+        <f t="shared" si="4"/>
+        <v>6506</v>
+      </c>
+      <c r="V34" s="75">
+        <f t="shared" si="5"/>
+        <v>271.08333333333331</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="27">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="B35" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="C35" s="70"/>
+      <c r="D35" s="70"/>
+      <c r="E35" s="70"/>
+      <c r="F35" s="70"/>
+      <c r="G35" s="70"/>
+      <c r="H35" s="70"/>
+      <c r="I35" s="70"/>
+      <c r="J35" s="71"/>
+      <c r="K35" s="72"/>
+      <c r="L35" s="55"/>
+      <c r="M35" s="73"/>
+      <c r="N35" s="74"/>
+      <c r="O35" s="70"/>
+      <c r="P35" s="71"/>
+      <c r="Q35" s="71"/>
+      <c r="R35" s="72"/>
+      <c r="S35" s="55"/>
+      <c r="T35" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U35" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V35" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A36" s="27">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+      <c r="B36" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="70"/>
+      <c r="D36" s="70"/>
+      <c r="E36" s="70"/>
+      <c r="F36" s="70"/>
+      <c r="G36" s="70"/>
+      <c r="H36" s="70"/>
+      <c r="I36" s="70"/>
+      <c r="J36" s="71"/>
+      <c r="K36" s="72"/>
+      <c r="L36" s="55"/>
+      <c r="M36" s="73"/>
+      <c r="N36" s="74"/>
+      <c r="O36" s="70"/>
+      <c r="P36" s="71"/>
+      <c r="Q36" s="71"/>
+      <c r="R36" s="72"/>
+      <c r="S36" s="55"/>
+      <c r="T36" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U36" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="27">
+        <f t="shared" si="1"/>
+        <v>34</v>
+      </c>
+      <c r="B37" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="C37" s="59">
+        <f>324+2376+1620+33</f>
+        <v>4353</v>
+      </c>
+      <c r="D37" s="59"/>
+      <c r="E37" s="59"/>
+      <c r="F37" s="59"/>
+      <c r="G37" s="59"/>
+      <c r="H37" s="59">
+        <v>3</v>
+      </c>
+      <c r="I37" s="59">
+        <v>2</v>
+      </c>
+      <c r="J37" s="60"/>
+      <c r="K37" s="61">
+        <f>2*6+2</f>
+        <v>14</v>
+      </c>
+      <c r="L37" s="62"/>
+      <c r="M37" s="63">
+        <v>20</v>
+      </c>
+      <c r="N37" s="64"/>
+      <c r="O37" s="65">
+        <v>54</v>
+      </c>
+      <c r="P37" s="66"/>
+      <c r="Q37" s="66">
+        <v>48</v>
+      </c>
+      <c r="R37" s="67"/>
+      <c r="S37" s="62"/>
+      <c r="T37" s="77">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="U37" s="77">
+        <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
+        <v>26869</v>
+      </c>
+      <c r="V37" s="77">
+        <f>U37/6</f>
+        <v>4478.166666666667</v>
+      </c>
+      <c r="W37" s="50"/>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A38" s="27">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="B38" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" s="70">
+        <v>3</v>
+      </c>
+      <c r="D38" s="70"/>
+      <c r="E38" s="70"/>
+      <c r="F38" s="70"/>
+      <c r="G38" s="70"/>
+      <c r="H38" s="70"/>
+      <c r="I38" s="70"/>
+      <c r="J38" s="71"/>
+      <c r="K38" s="72"/>
+      <c r="L38" s="55"/>
+      <c r="M38" s="73"/>
+      <c r="N38" s="74"/>
+      <c r="O38" s="70"/>
+      <c r="P38" s="71"/>
+      <c r="Q38" s="71"/>
+      <c r="R38" s="72"/>
+      <c r="S38" s="55"/>
+      <c r="T38" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U38" s="75">
+        <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
+        <v>72</v>
+      </c>
+      <c r="V38" s="75">
+        <f>U38/24</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A39" s="27">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="B39" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="C39" s="78"/>
+      <c r="D39" s="78"/>
+      <c r="E39" s="78"/>
+      <c r="F39" s="78"/>
+      <c r="G39" s="78"/>
+      <c r="H39" s="78"/>
+      <c r="I39" s="78"/>
+      <c r="J39" s="79"/>
+      <c r="K39" s="80"/>
+      <c r="L39" s="55"/>
+      <c r="M39" s="73"/>
+      <c r="N39" s="74"/>
+      <c r="O39" s="70"/>
+      <c r="P39" s="71"/>
+      <c r="Q39" s="71"/>
+      <c r="R39" s="72"/>
+      <c r="S39" s="95"/>
+      <c r="T39" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U39" s="75">
+        <f>C39*24+M39*24+O39*24+Q39*24+T39</f>
+        <v>0</v>
+      </c>
+      <c r="V39" s="75">
+        <f>U39/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="27">
+        <f t="shared" si="1"/>
+        <v>37</v>
+      </c>
+      <c r="B40" s="42" t="s">
+        <v>21</v>
+      </c>
+      <c r="C40" s="59">
+        <v>252</v>
+      </c>
+      <c r="D40" s="59"/>
+      <c r="E40" s="59"/>
+      <c r="F40" s="59"/>
+      <c r="G40" s="59"/>
+      <c r="H40" s="59"/>
+      <c r="I40" s="59"/>
+      <c r="J40" s="60"/>
+      <c r="K40" s="61">
+        <v>20</v>
+      </c>
+      <c r="L40" s="62"/>
+      <c r="M40" s="63">
+        <v>2</v>
+      </c>
+      <c r="N40" s="64"/>
+      <c r="O40" s="65"/>
+      <c r="P40" s="66"/>
+      <c r="Q40" s="66">
+        <v>3</v>
+      </c>
+      <c r="R40" s="67"/>
+      <c r="S40" s="62"/>
+      <c r="T40" s="77">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="U40" s="77">
+        <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
+        <v>6188</v>
+      </c>
+      <c r="V40" s="77">
+        <f>U40/24</f>
+        <v>257.83333333333331</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="27">
+        <f t="shared" si="1"/>
+        <v>38</v>
+      </c>
+      <c r="B41" s="43" t="s">
+        <v>22</v>
+      </c>
+      <c r="C41" s="82">
+        <f>86+672</f>
+        <v>758</v>
+      </c>
+      <c r="D41" s="82"/>
+      <c r="E41" s="82"/>
+      <c r="F41" s="82"/>
+      <c r="G41" s="82"/>
+      <c r="H41" s="82"/>
+      <c r="I41" s="82"/>
+      <c r="J41" s="83"/>
+      <c r="K41" s="84"/>
+      <c r="L41" s="85"/>
+      <c r="M41" s="86">
+        <v>4</v>
+      </c>
+      <c r="N41" s="87"/>
+      <c r="O41" s="82">
+        <v>10</v>
+      </c>
+      <c r="P41" s="83"/>
+      <c r="Q41" s="83"/>
+      <c r="R41" s="84"/>
+      <c r="S41" s="85"/>
+      <c r="T41" s="88">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U41" s="88">
+        <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
+        <v>9264</v>
+      </c>
+      <c r="V41" s="88">
+        <f>U41/12</f>
+        <v>772</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="27">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+      <c r="B42" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C42" s="70"/>
+      <c r="D42" s="70"/>
+      <c r="E42" s="70"/>
+      <c r="F42" s="70"/>
+      <c r="G42" s="70"/>
+      <c r="H42" s="70"/>
+      <c r="I42" s="70"/>
+      <c r="J42" s="71"/>
+      <c r="K42" s="72"/>
+      <c r="L42" s="55"/>
+      <c r="M42" s="73"/>
+      <c r="N42" s="74"/>
+      <c r="O42" s="70"/>
+      <c r="P42" s="71"/>
+      <c r="Q42" s="71"/>
+      <c r="R42" s="72"/>
+      <c r="S42" s="55"/>
+      <c r="T42" s="75"/>
+      <c r="U42" s="75"/>
+      <c r="V42" s="75"/>
+    </row>
+    <row r="43" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="27">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="B43" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="C43" s="65">
+        <f>13932+19764+3240+1620+44</f>
+        <v>38600</v>
+      </c>
+      <c r="D43" s="65"/>
+      <c r="E43" s="65"/>
+      <c r="F43" s="65"/>
+      <c r="G43" s="65"/>
+      <c r="H43" s="65">
+        <v>1</v>
+      </c>
+      <c r="I43" s="65">
+        <v>12</v>
+      </c>
+      <c r="J43" s="66">
+        <f>8*6</f>
+        <v>48</v>
+      </c>
+      <c r="K43" s="67">
+        <f>95*6+1</f>
+        <v>571</v>
+      </c>
+      <c r="L43" s="62"/>
+      <c r="M43" s="63">
+        <v>1012</v>
+      </c>
+      <c r="N43" s="64"/>
+      <c r="O43" s="65">
+        <v>577</v>
+      </c>
+      <c r="P43" s="66"/>
+      <c r="Q43" s="66">
+        <v>433</v>
+      </c>
+      <c r="R43" s="67"/>
+      <c r="S43" s="62"/>
+      <c r="T43" s="77">
+        <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
+        <v>632</v>
+      </c>
+      <c r="U43" s="77">
+        <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
+        <v>244364</v>
+      </c>
+      <c r="V43" s="77">
+        <f>U43/6</f>
+        <v>40727.333333333336</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="27">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+      <c r="B44" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="70"/>
+      <c r="D44" s="70"/>
+      <c r="E44" s="70"/>
+      <c r="F44" s="70"/>
+      <c r="G44" s="70"/>
+      <c r="H44" s="70"/>
+      <c r="I44" s="70"/>
+      <c r="J44" s="71"/>
+      <c r="K44" s="72"/>
+      <c r="L44" s="55"/>
+      <c r="M44" s="73"/>
+      <c r="N44" s="74"/>
+      <c r="O44" s="70"/>
+      <c r="P44" s="71"/>
+      <c r="Q44" s="71"/>
+      <c r="R44" s="72"/>
+      <c r="S44" s="55"/>
+      <c r="T44" s="75"/>
+      <c r="U44" s="75"/>
+      <c r="V44" s="75"/>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A45" s="27">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="B45" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="70">
+        <v>5</v>
+      </c>
+      <c r="D45" s="70"/>
+      <c r="E45" s="70"/>
+      <c r="F45" s="70"/>
+      <c r="G45" s="70"/>
+      <c r="H45" s="70"/>
+      <c r="I45" s="70"/>
+      <c r="J45" s="71"/>
+      <c r="K45" s="72"/>
+      <c r="L45" s="55"/>
+      <c r="M45" s="73"/>
+      <c r="N45" s="74"/>
+      <c r="O45" s="70"/>
+      <c r="P45" s="71"/>
+      <c r="Q45" s="71"/>
+      <c r="R45" s="72"/>
+      <c r="S45" s="55"/>
+      <c r="T45" s="75">
+        <f t="shared" ref="T45:T54" si="7">H45+I45+J45+K45+N45+P45+R45</f>
+        <v>0</v>
+      </c>
+      <c r="U45" s="75">
+        <f>C45*24+M45*24+O45*24+Q45*24+T45</f>
+        <v>120</v>
+      </c>
+      <c r="V45" s="75">
+        <f>U45/24</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A46" s="27">
+        <f t="shared" si="1"/>
+        <v>43</v>
+      </c>
+      <c r="B46" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="C46" s="70"/>
+      <c r="D46" s="70"/>
+      <c r="E46" s="70"/>
+      <c r="F46" s="70"/>
+      <c r="G46" s="70"/>
+      <c r="H46" s="70"/>
+      <c r="I46" s="70"/>
+      <c r="J46" s="71"/>
+      <c r="K46" s="72"/>
+      <c r="L46" s="55"/>
+      <c r="M46" s="73"/>
+      <c r="N46" s="74"/>
+      <c r="O46" s="70"/>
+      <c r="P46" s="71"/>
+      <c r="Q46" s="71"/>
+      <c r="R46" s="72"/>
+      <c r="S46" s="55"/>
+      <c r="T46" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U46" s="75">
+        <f t="shared" ref="U46:U50" si="8">C46*24+M46*24+O46*24+Q46*24+T46</f>
+        <v>0</v>
+      </c>
+      <c r="V46" s="75">
+        <f t="shared" ref="V46:V54" si="9">U46/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="27">
+        <f t="shared" si="1"/>
+        <v>44</v>
+      </c>
+      <c r="B47" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="C47" s="65">
+        <v>2629</v>
+      </c>
+      <c r="D47" s="65"/>
+      <c r="E47" s="65"/>
+      <c r="F47" s="65"/>
+      <c r="G47" s="65"/>
+      <c r="H47" s="65">
+        <v>1</v>
+      </c>
+      <c r="I47" s="65"/>
+      <c r="J47" s="66"/>
+      <c r="K47" s="67">
+        <v>5</v>
+      </c>
+      <c r="L47" s="62"/>
+      <c r="M47" s="63">
+        <v>2</v>
+      </c>
+      <c r="N47" s="64"/>
+      <c r="O47" s="65">
+        <v>14</v>
+      </c>
+      <c r="P47" s="66">
+        <v>3</v>
+      </c>
+      <c r="Q47" s="66">
+        <v>5</v>
+      </c>
+      <c r="R47" s="67">
+        <v>3</v>
+      </c>
+      <c r="S47" s="62"/>
+      <c r="T47" s="77">
+        <f t="shared" si="7"/>
+        <v>12</v>
+      </c>
+      <c r="U47" s="77">
+        <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
+        <v>15912</v>
+      </c>
+      <c r="V47" s="77">
+        <f>U47/6</f>
+        <v>2652</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A48" s="27">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="B48" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C48" s="70"/>
+      <c r="D48" s="70"/>
+      <c r="E48" s="70"/>
+      <c r="F48" s="70"/>
+      <c r="G48" s="70"/>
+      <c r="H48" s="70">
+        <v>24</v>
+      </c>
+      <c r="I48" s="70"/>
+      <c r="J48" s="71"/>
+      <c r="K48" s="72"/>
+      <c r="L48" s="55"/>
+      <c r="M48" s="73"/>
+      <c r="N48" s="74"/>
+      <c r="O48" s="70"/>
+      <c r="P48" s="71"/>
+      <c r="Q48" s="71"/>
+      <c r="R48" s="72"/>
+      <c r="S48" s="55"/>
+      <c r="T48" s="75">
+        <f t="shared" si="7"/>
+        <v>24</v>
+      </c>
+      <c r="U48" s="75">
+        <f t="shared" si="8"/>
+        <v>24</v>
+      </c>
+      <c r="V48" s="75">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A49" s="27">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="B49" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C49" s="70"/>
+      <c r="D49" s="70"/>
+      <c r="E49" s="70"/>
+      <c r="F49" s="70"/>
+      <c r="G49" s="70"/>
+      <c r="H49" s="70"/>
+      <c r="I49" s="70"/>
+      <c r="J49" s="71"/>
+      <c r="K49" s="72"/>
+      <c r="L49" s="55"/>
+      <c r="M49" s="73"/>
+      <c r="N49" s="74"/>
+      <c r="O49" s="70"/>
+      <c r="P49" s="71"/>
+      <c r="Q49" s="71"/>
+      <c r="R49" s="72"/>
+      <c r="S49" s="55"/>
+      <c r="T49" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U49" s="75">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V49" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A50" s="27">
+        <f t="shared" si="1"/>
+        <v>47</v>
+      </c>
+      <c r="B50" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="C50" s="70"/>
+      <c r="D50" s="70"/>
+      <c r="E50" s="70"/>
+      <c r="F50" s="70"/>
+      <c r="G50" s="70"/>
+      <c r="H50" s="70"/>
+      <c r="I50" s="70"/>
+      <c r="J50" s="71"/>
+      <c r="K50" s="72"/>
+      <c r="L50" s="55"/>
+      <c r="M50" s="73"/>
+      <c r="N50" s="74"/>
+      <c r="O50" s="70"/>
+      <c r="P50" s="71"/>
+      <c r="Q50" s="71"/>
+      <c r="R50" s="72"/>
+      <c r="S50" s="55"/>
+      <c r="T50" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U50" s="75">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V50" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="27">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+      <c r="B51" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="C51" s="65">
+        <v>34</v>
+      </c>
+      <c r="D51" s="65"/>
+      <c r="E51" s="65"/>
+      <c r="F51" s="65"/>
+      <c r="G51" s="65"/>
+      <c r="H51" s="65"/>
+      <c r="I51" s="65"/>
+      <c r="J51" s="66"/>
+      <c r="K51" s="67"/>
+      <c r="L51" s="62"/>
+      <c r="M51" s="63"/>
+      <c r="N51" s="64"/>
+      <c r="O51" s="65"/>
+      <c r="P51" s="66"/>
+      <c r="Q51" s="66"/>
+      <c r="R51" s="67"/>
+      <c r="S51" s="62"/>
+      <c r="T51" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U51" s="77">
+        <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
+        <v>204</v>
+      </c>
+      <c r="V51" s="77">
+        <f>U51/6</f>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A52" s="27">
+        <f t="shared" si="1"/>
+        <v>49</v>
+      </c>
+      <c r="B52" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="C52" s="70"/>
+      <c r="D52" s="70"/>
+      <c r="E52" s="70"/>
+      <c r="F52" s="70"/>
+      <c r="G52" s="70"/>
+      <c r="H52" s="70"/>
+      <c r="I52" s="70"/>
+      <c r="J52" s="71"/>
+      <c r="K52" s="72"/>
+      <c r="L52" s="55"/>
+      <c r="M52" s="73"/>
+      <c r="N52" s="74"/>
+      <c r="O52" s="70"/>
+      <c r="P52" s="71"/>
+      <c r="Q52" s="71"/>
+      <c r="R52" s="72"/>
+      <c r="S52" s="55"/>
+      <c r="T52" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U52" s="75">
+        <f t="shared" ref="U52:U54" si="10">C52*24+M52*24+O52*24+Q52*24+T52</f>
+        <v>0</v>
+      </c>
+      <c r="V52" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A53" s="27">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="B53" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C53" s="70">
+        <v>7</v>
+      </c>
+      <c r="D53" s="70"/>
+      <c r="E53" s="70"/>
+      <c r="F53" s="70"/>
+      <c r="G53" s="70"/>
+      <c r="H53" s="70"/>
+      <c r="I53" s="70"/>
+      <c r="J53" s="71"/>
+      <c r="K53" s="72"/>
+      <c r="L53" s="55"/>
+      <c r="M53" s="73"/>
+      <c r="N53" s="74"/>
+      <c r="O53" s="70"/>
+      <c r="P53" s="71"/>
+      <c r="Q53" s="71"/>
+      <c r="R53" s="72"/>
+      <c r="S53" s="55"/>
+      <c r="T53" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U53" s="75">
+        <f t="shared" si="10"/>
+        <v>168</v>
+      </c>
+      <c r="V53" s="75">
+        <f t="shared" si="9"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A54" s="27">
+        <f t="shared" si="1"/>
+        <v>51</v>
+      </c>
+      <c r="B54" s="26"/>
+      <c r="C54" s="70"/>
+      <c r="D54" s="70"/>
+      <c r="E54" s="70"/>
+      <c r="F54" s="70"/>
+      <c r="G54" s="70"/>
+      <c r="H54" s="70"/>
+      <c r="I54" s="70"/>
+      <c r="J54" s="71"/>
+      <c r="K54" s="72"/>
+      <c r="L54" s="55"/>
+      <c r="M54" s="73"/>
+      <c r="N54" s="74"/>
+      <c r="O54" s="70"/>
+      <c r="P54" s="71"/>
+      <c r="Q54" s="71"/>
+      <c r="R54" s="72"/>
+      <c r="S54" s="55"/>
+      <c r="T54" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U54" s="75">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V54" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A55" s="27">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="B55" s="26"/>
+      <c r="C55" s="70"/>
+      <c r="D55" s="70"/>
+      <c r="E55" s="70"/>
+      <c r="F55" s="70"/>
+      <c r="G55" s="70"/>
+      <c r="H55" s="70"/>
+      <c r="I55" s="70"/>
+      <c r="J55" s="71"/>
+      <c r="K55" s="72"/>
+      <c r="L55" s="55"/>
+      <c r="M55" s="73"/>
+      <c r="N55" s="74"/>
+      <c r="O55" s="70"/>
+      <c r="P55" s="71"/>
+      <c r="Q55" s="71"/>
+      <c r="R55" s="72"/>
+      <c r="S55" s="55"/>
+      <c r="T55" s="75"/>
+      <c r="U55" s="75"/>
+      <c r="V55" s="75"/>
+    </row>
+    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A56" s="27">
+        <f t="shared" si="1"/>
+        <v>53</v>
+      </c>
+      <c r="B56" s="26"/>
+      <c r="C56" s="70"/>
+      <c r="D56" s="70"/>
+      <c r="E56" s="70"/>
+      <c r="F56" s="70"/>
+      <c r="G56" s="70"/>
+      <c r="H56" s="70"/>
+      <c r="I56" s="70"/>
+      <c r="J56" s="71"/>
+      <c r="K56" s="72"/>
+      <c r="L56" s="55"/>
+      <c r="M56" s="73"/>
+      <c r="N56" s="74"/>
+      <c r="O56" s="70"/>
+      <c r="P56" s="71"/>
+      <c r="Q56" s="71"/>
+      <c r="R56" s="72"/>
+      <c r="S56" s="55"/>
+      <c r="T56" s="75"/>
+      <c r="U56" s="75"/>
+      <c r="V56" s="75"/>
+    </row>
+    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A57" s="27">
+        <f t="shared" si="1"/>
+        <v>54</v>
+      </c>
+      <c r="B57" s="26"/>
+      <c r="C57" s="70"/>
+      <c r="D57" s="70"/>
+      <c r="E57" s="70"/>
+      <c r="F57" s="70"/>
+      <c r="G57" s="70"/>
+      <c r="H57" s="70"/>
+      <c r="I57" s="70"/>
+      <c r="J57" s="71"/>
+      <c r="K57" s="72"/>
+      <c r="L57" s="55"/>
+      <c r="M57" s="73"/>
+      <c r="N57" s="74"/>
+      <c r="O57" s="70"/>
+      <c r="P57" s="71"/>
+      <c r="Q57" s="71"/>
+      <c r="R57" s="72"/>
+      <c r="S57" s="55"/>
+      <c r="T57" s="75"/>
+      <c r="U57" s="75"/>
+      <c r="V57" s="75"/>
+    </row>
+    <row r="58" spans="1:22" s="15" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B58" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="C58" s="2">
+        <f>SUM(C7:C57)</f>
+        <v>50359</v>
+      </c>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2">
+        <f t="shared" ref="F58:K58" si="11">SUM(F7:F57)</f>
+        <v>0</v>
+      </c>
+      <c r="G58" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="H58" s="2">
+        <f t="shared" si="11"/>
+        <v>1208</v>
+      </c>
+      <c r="I58" s="6">
+        <f t="shared" si="11"/>
+        <v>24</v>
+      </c>
+      <c r="J58" s="6">
+        <f t="shared" si="11"/>
+        <v>48</v>
+      </c>
+      <c r="K58" s="6">
+        <f t="shared" si="11"/>
+        <v>619</v>
+      </c>
+      <c r="M58" s="5">
+        <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
+        <v>1079</v>
+      </c>
+      <c r="N58" s="5">
+        <f t="shared" si="12"/>
+        <v>11</v>
+      </c>
+      <c r="O58" s="5">
+        <f t="shared" si="12"/>
+        <v>678</v>
+      </c>
+      <c r="P58" s="5">
+        <f t="shared" si="12"/>
+        <v>27</v>
+      </c>
+      <c r="Q58" s="5">
+        <f t="shared" si="12"/>
+        <v>512</v>
+      </c>
+      <c r="R58" s="5">
+        <f t="shared" si="12"/>
+        <v>3</v>
+      </c>
+      <c r="S58" s="55"/>
+      <c r="T58" s="4">
+        <f>SUM(T7:T57)</f>
+        <v>1940</v>
+      </c>
+      <c r="U58" s="90">
+        <f>SUM(U7:U57)</f>
+        <v>395690</v>
+      </c>
+      <c r="V58" s="4">
+        <f>SUM(V7:V57)</f>
+        <v>52791.708333333336</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="60" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="C60" s="113" t="s">
+        <v>41</v>
+      </c>
+      <c r="D60" s="114"/>
+      <c r="E60" s="114"/>
+      <c r="F60" s="114"/>
+      <c r="G60" s="114"/>
+      <c r="H60" s="114"/>
+      <c r="I60" s="114"/>
+      <c r="J60" s="114"/>
+      <c r="K60" s="115"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -45742,21 +48872,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="115" t="s">
+      <c r="I1" s="116" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="115"/>
-      <c r="K1" s="115"/>
-      <c r="L1" s="115"/>
-      <c r="M1" s="115"/>
-      <c r="N1" s="115"/>
-      <c r="O1" s="115"/>
-      <c r="P1" s="115"/>
-      <c r="Q1" s="115"/>
-      <c r="R1" s="115"/>
-      <c r="S1" s="115"/>
-      <c r="T1" s="115"/>
-      <c r="U1" s="115"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="116"/>
+      <c r="M1" s="116"/>
+      <c r="N1" s="116"/>
+      <c r="O1" s="116"/>
+      <c r="P1" s="116"/>
+      <c r="Q1" s="116"/>
+      <c r="R1" s="116"/>
+      <c r="S1" s="116"/>
+      <c r="T1" s="116"/>
+      <c r="U1" s="116"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -45768,17 +48898,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="116" t="s">
+      <c r="C4" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="116"/>
-      <c r="H4" s="116"/>
-      <c r="I4" s="116"/>
-      <c r="J4" s="117"/>
-      <c r="K4" s="118"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="117"/>
+      <c r="F4" s="117"/>
+      <c r="G4" s="117"/>
+      <c r="H4" s="117"/>
+      <c r="I4" s="117"/>
+      <c r="J4" s="118"/>
+      <c r="K4" s="119"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -45798,13 +48928,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="119" t="s">
+      <c r="T4" s="120" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="125" t="s">
+      <c r="U4" s="126" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="108" t="s">
+      <c r="V4" s="109" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -45844,10 +48974,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="123" t="s">
+      <c r="J5" s="124" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="124"/>
+      <c r="K5" s="125"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -45855,9 +48985,9 @@
       <c r="Q5" s="97"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="120"/>
-      <c r="U5" s="126"/>
-      <c r="V5" s="109"/>
+      <c r="T5" s="121"/>
+      <c r="U5" s="127"/>
+      <c r="V5" s="110"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -48557,17 +51687,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="112" t="s">
+      <c r="C60" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="113"/>
-      <c r="E60" s="113"/>
-      <c r="F60" s="113"/>
-      <c r="G60" s="113"/>
-      <c r="H60" s="113"/>
-      <c r="I60" s="113"/>
-      <c r="J60" s="113"/>
-      <c r="K60" s="114"/>
+      <c r="D60" s="114"/>
+      <c r="E60" s="114"/>
+      <c r="F60" s="114"/>
+      <c r="G60" s="114"/>
+      <c r="H60" s="114"/>
+      <c r="I60" s="114"/>
+      <c r="J60" s="114"/>
+      <c r="K60" s="115"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -48876,21 +52006,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="115" t="s">
+      <c r="I1" s="116" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="115"/>
-      <c r="K1" s="115"/>
-      <c r="L1" s="115"/>
-      <c r="M1" s="115"/>
-      <c r="N1" s="115"/>
-      <c r="O1" s="115"/>
-      <c r="P1" s="115"/>
-      <c r="Q1" s="115"/>
-      <c r="R1" s="115"/>
-      <c r="S1" s="115"/>
-      <c r="T1" s="115"/>
-      <c r="U1" s="115"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="116"/>
+      <c r="M1" s="116"/>
+      <c r="N1" s="116"/>
+      <c r="O1" s="116"/>
+      <c r="P1" s="116"/>
+      <c r="Q1" s="116"/>
+      <c r="R1" s="116"/>
+      <c r="S1" s="116"/>
+      <c r="T1" s="116"/>
+      <c r="U1" s="116"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -48902,17 +52032,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="116" t="s">
+      <c r="C4" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="116"/>
-      <c r="H4" s="116"/>
-      <c r="I4" s="116"/>
-      <c r="J4" s="117"/>
-      <c r="K4" s="118"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="117"/>
+      <c r="F4" s="117"/>
+      <c r="G4" s="117"/>
+      <c r="H4" s="117"/>
+      <c r="I4" s="117"/>
+      <c r="J4" s="118"/>
+      <c r="K4" s="119"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -48932,13 +52062,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="119" t="s">
+      <c r="T4" s="120" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="125" t="s">
+      <c r="U4" s="126" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="108" t="s">
+      <c r="V4" s="109" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -48978,10 +52108,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="123" t="s">
+      <c r="J5" s="124" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="124"/>
+      <c r="K5" s="125"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -48989,9 +52119,9 @@
       <c r="Q5" s="97"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="120"/>
-      <c r="U5" s="126"/>
-      <c r="V5" s="109"/>
+      <c r="T5" s="121"/>
+      <c r="U5" s="127"/>
+      <c r="V5" s="110"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -51691,17 +54821,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="112" t="s">
+      <c r="C60" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="113"/>
-      <c r="E60" s="113"/>
-      <c r="F60" s="113"/>
-      <c r="G60" s="113"/>
-      <c r="H60" s="113"/>
-      <c r="I60" s="113"/>
-      <c r="J60" s="113"/>
-      <c r="K60" s="114"/>
+      <c r="D60" s="114"/>
+      <c r="E60" s="114"/>
+      <c r="F60" s="114"/>
+      <c r="G60" s="114"/>
+      <c r="H60" s="114"/>
+      <c r="I60" s="114"/>
+      <c r="J60" s="114"/>
+      <c r="K60" s="115"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -52010,21 +55140,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="115" t="s">
+      <c r="I1" s="116" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="115"/>
-      <c r="K1" s="115"/>
-      <c r="L1" s="115"/>
-      <c r="M1" s="115"/>
-      <c r="N1" s="115"/>
-      <c r="O1" s="115"/>
-      <c r="P1" s="115"/>
-      <c r="Q1" s="115"/>
-      <c r="R1" s="115"/>
-      <c r="S1" s="115"/>
-      <c r="T1" s="115"/>
-      <c r="U1" s="115"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="116"/>
+      <c r="M1" s="116"/>
+      <c r="N1" s="116"/>
+      <c r="O1" s="116"/>
+      <c r="P1" s="116"/>
+      <c r="Q1" s="116"/>
+      <c r="R1" s="116"/>
+      <c r="S1" s="116"/>
+      <c r="T1" s="116"/>
+      <c r="U1" s="116"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -52036,17 +55166,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="116" t="s">
+      <c r="C4" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="116"/>
-      <c r="H4" s="116"/>
-      <c r="I4" s="116"/>
-      <c r="J4" s="117"/>
-      <c r="K4" s="118"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="117"/>
+      <c r="F4" s="117"/>
+      <c r="G4" s="117"/>
+      <c r="H4" s="117"/>
+      <c r="I4" s="117"/>
+      <c r="J4" s="118"/>
+      <c r="K4" s="119"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -52066,13 +55196,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="119" t="s">
+      <c r="T4" s="120" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="125" t="s">
+      <c r="U4" s="126" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="108" t="s">
+      <c r="V4" s="109" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -52112,10 +55242,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="123" t="s">
+      <c r="J5" s="124" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="124"/>
+      <c r="K5" s="125"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -52123,9 +55253,9 @@
       <c r="Q5" s="97"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="120"/>
-      <c r="U5" s="126"/>
-      <c r="V5" s="109"/>
+      <c r="T5" s="121"/>
+      <c r="U5" s="127"/>
+      <c r="V5" s="110"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -54815,17 +57945,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="112" t="s">
+      <c r="C60" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="113"/>
-      <c r="E60" s="113"/>
-      <c r="F60" s="113"/>
-      <c r="G60" s="113"/>
-      <c r="H60" s="113"/>
-      <c r="I60" s="113"/>
-      <c r="J60" s="113"/>
-      <c r="K60" s="114"/>
+      <c r="D60" s="114"/>
+      <c r="E60" s="114"/>
+      <c r="F60" s="114"/>
+      <c r="G60" s="114"/>
+      <c r="H60" s="114"/>
+      <c r="I60" s="114"/>
+      <c r="J60" s="114"/>
+      <c r="K60" s="115"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -55134,21 +58264,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="115" t="s">
+      <c r="I1" s="116" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="115"/>
-      <c r="K1" s="115"/>
-      <c r="L1" s="115"/>
-      <c r="M1" s="115"/>
-      <c r="N1" s="115"/>
-      <c r="O1" s="115"/>
-      <c r="P1" s="115"/>
-      <c r="Q1" s="115"/>
-      <c r="R1" s="115"/>
-      <c r="S1" s="115"/>
-      <c r="T1" s="115"/>
-      <c r="U1" s="115"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="116"/>
+      <c r="M1" s="116"/>
+      <c r="N1" s="116"/>
+      <c r="O1" s="116"/>
+      <c r="P1" s="116"/>
+      <c r="Q1" s="116"/>
+      <c r="R1" s="116"/>
+      <c r="S1" s="116"/>
+      <c r="T1" s="116"/>
+      <c r="U1" s="116"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -55160,17 +58290,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="116" t="s">
+      <c r="C4" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="116"/>
-      <c r="H4" s="116"/>
-      <c r="I4" s="116"/>
-      <c r="J4" s="117"/>
-      <c r="K4" s="118"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="117"/>
+      <c r="F4" s="117"/>
+      <c r="G4" s="117"/>
+      <c r="H4" s="117"/>
+      <c r="I4" s="117"/>
+      <c r="J4" s="118"/>
+      <c r="K4" s="119"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -55190,13 +58320,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="119" t="s">
+      <c r="T4" s="120" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="125" t="s">
+      <c r="U4" s="126" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="108" t="s">
+      <c r="V4" s="109" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -55236,10 +58366,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="123" t="s">
+      <c r="J5" s="124" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="124"/>
+      <c r="K5" s="125"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -55247,9 +58377,9 @@
       <c r="Q5" s="98"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="120"/>
-      <c r="U5" s="126"/>
-      <c r="V5" s="109"/>
+      <c r="T5" s="121"/>
+      <c r="U5" s="127"/>
+      <c r="V5" s="110"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -57964,17 +61094,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="112" t="s">
+      <c r="C60" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="113"/>
-      <c r="E60" s="113"/>
-      <c r="F60" s="113"/>
-      <c r="G60" s="113"/>
-      <c r="H60" s="113"/>
-      <c r="I60" s="113"/>
-      <c r="J60" s="113"/>
-      <c r="K60" s="114"/>
+      <c r="D60" s="114"/>
+      <c r="E60" s="114"/>
+      <c r="F60" s="114"/>
+      <c r="G60" s="114"/>
+      <c r="H60" s="114"/>
+      <c r="I60" s="114"/>
+      <c r="J60" s="114"/>
+      <c r="K60" s="115"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -58283,21 +61413,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="115" t="s">
+      <c r="I1" s="116" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="115"/>
-      <c r="K1" s="115"/>
-      <c r="L1" s="115"/>
-      <c r="M1" s="115"/>
-      <c r="N1" s="115"/>
-      <c r="O1" s="115"/>
-      <c r="P1" s="115"/>
-      <c r="Q1" s="115"/>
-      <c r="R1" s="115"/>
-      <c r="S1" s="115"/>
-      <c r="T1" s="115"/>
-      <c r="U1" s="115"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="116"/>
+      <c r="M1" s="116"/>
+      <c r="N1" s="116"/>
+      <c r="O1" s="116"/>
+      <c r="P1" s="116"/>
+      <c r="Q1" s="116"/>
+      <c r="R1" s="116"/>
+      <c r="S1" s="116"/>
+      <c r="T1" s="116"/>
+      <c r="U1" s="116"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -58309,17 +61439,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="116" t="s">
+      <c r="C4" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="116"/>
-      <c r="H4" s="116"/>
-      <c r="I4" s="116"/>
-      <c r="J4" s="117"/>
-      <c r="K4" s="118"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="117"/>
+      <c r="F4" s="117"/>
+      <c r="G4" s="117"/>
+      <c r="H4" s="117"/>
+      <c r="I4" s="117"/>
+      <c r="J4" s="118"/>
+      <c r="K4" s="119"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -58339,13 +61469,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="119" t="s">
+      <c r="T4" s="120" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="125" t="s">
+      <c r="U4" s="126" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="108" t="s">
+      <c r="V4" s="109" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -58385,10 +61515,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="123" t="s">
+      <c r="J5" s="124" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="124"/>
+      <c r="K5" s="125"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -58396,9 +61526,9 @@
       <c r="Q5" s="98"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="120"/>
-      <c r="U5" s="126"/>
-      <c r="V5" s="109"/>
+      <c r="T5" s="121"/>
+      <c r="U5" s="127"/>
+      <c r="V5" s="110"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -61103,17 +64233,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="112" t="s">
+      <c r="C60" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="113"/>
-      <c r="E60" s="113"/>
-      <c r="F60" s="113"/>
-      <c r="G60" s="113"/>
-      <c r="H60" s="113"/>
-      <c r="I60" s="113"/>
-      <c r="J60" s="113"/>
-      <c r="K60" s="114"/>
+      <c r="D60" s="114"/>
+      <c r="E60" s="114"/>
+      <c r="F60" s="114"/>
+      <c r="G60" s="114"/>
+      <c r="H60" s="114"/>
+      <c r="I60" s="114"/>
+      <c r="J60" s="114"/>
+      <c r="K60" s="115"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -61422,21 +64552,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="115" t="s">
+      <c r="I1" s="116" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="115"/>
-      <c r="K1" s="115"/>
-      <c r="L1" s="115"/>
-      <c r="M1" s="115"/>
-      <c r="N1" s="115"/>
-      <c r="O1" s="115"/>
-      <c r="P1" s="115"/>
-      <c r="Q1" s="115"/>
-      <c r="R1" s="115"/>
-      <c r="S1" s="115"/>
-      <c r="T1" s="115"/>
-      <c r="U1" s="115"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="116"/>
+      <c r="M1" s="116"/>
+      <c r="N1" s="116"/>
+      <c r="O1" s="116"/>
+      <c r="P1" s="116"/>
+      <c r="Q1" s="116"/>
+      <c r="R1" s="116"/>
+      <c r="S1" s="116"/>
+      <c r="T1" s="116"/>
+      <c r="U1" s="116"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -61448,17 +64578,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="116" t="s">
+      <c r="C4" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="116"/>
-      <c r="H4" s="116"/>
-      <c r="I4" s="116"/>
-      <c r="J4" s="117"/>
-      <c r="K4" s="118"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="117"/>
+      <c r="F4" s="117"/>
+      <c r="G4" s="117"/>
+      <c r="H4" s="117"/>
+      <c r="I4" s="117"/>
+      <c r="J4" s="118"/>
+      <c r="K4" s="119"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -61478,13 +64608,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="119" t="s">
+      <c r="T4" s="120" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="125" t="s">
+      <c r="U4" s="126" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="108" t="s">
+      <c r="V4" s="109" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -61524,10 +64654,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="123" t="s">
+      <c r="J5" s="124" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="124"/>
+      <c r="K5" s="125"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -61535,9 +64665,9 @@
       <c r="Q5" s="98"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="120"/>
-      <c r="U5" s="126"/>
-      <c r="V5" s="109"/>
+      <c r="T5" s="121"/>
+      <c r="U5" s="127"/>
+      <c r="V5" s="110"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -64239,17 +67369,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="112" t="s">
+      <c r="C60" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="113"/>
-      <c r="E60" s="113"/>
-      <c r="F60" s="113"/>
-      <c r="G60" s="113"/>
-      <c r="H60" s="113"/>
-      <c r="I60" s="113"/>
-      <c r="J60" s="113"/>
-      <c r="K60" s="114"/>
+      <c r="D60" s="114"/>
+      <c r="E60" s="114"/>
+      <c r="F60" s="114"/>
+      <c r="G60" s="114"/>
+      <c r="H60" s="114"/>
+      <c r="I60" s="114"/>
+      <c r="J60" s="114"/>
+      <c r="K60" s="115"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -64558,21 +67688,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="115" t="s">
+      <c r="I1" s="116" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="115"/>
-      <c r="K1" s="115"/>
-      <c r="L1" s="115"/>
-      <c r="M1" s="115"/>
-      <c r="N1" s="115"/>
-      <c r="O1" s="115"/>
-      <c r="P1" s="115"/>
-      <c r="Q1" s="115"/>
-      <c r="R1" s="115"/>
-      <c r="S1" s="115"/>
-      <c r="T1" s="115"/>
-      <c r="U1" s="115"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="116"/>
+      <c r="M1" s="116"/>
+      <c r="N1" s="116"/>
+      <c r="O1" s="116"/>
+      <c r="P1" s="116"/>
+      <c r="Q1" s="116"/>
+      <c r="R1" s="116"/>
+      <c r="S1" s="116"/>
+      <c r="T1" s="116"/>
+      <c r="U1" s="116"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -64584,17 +67714,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="116" t="s">
+      <c r="C4" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="116"/>
-      <c r="H4" s="116"/>
-      <c r="I4" s="116"/>
-      <c r="J4" s="117"/>
-      <c r="K4" s="118"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="117"/>
+      <c r="F4" s="117"/>
+      <c r="G4" s="117"/>
+      <c r="H4" s="117"/>
+      <c r="I4" s="117"/>
+      <c r="J4" s="118"/>
+      <c r="K4" s="119"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -64614,13 +67744,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="119" t="s">
+      <c r="T4" s="120" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="125" t="s">
+      <c r="U4" s="126" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="108" t="s">
+      <c r="V4" s="109" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -64660,10 +67790,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="123" t="s">
+      <c r="J5" s="124" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="124"/>
+      <c r="K5" s="125"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -64671,9 +67801,9 @@
       <c r="Q5" s="98"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="120"/>
-      <c r="U5" s="126"/>
-      <c r="V5" s="109"/>
+      <c r="T5" s="121"/>
+      <c r="U5" s="127"/>
+      <c r="V5" s="110"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -67385,17 +70515,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="112" t="s">
+      <c r="C60" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="113"/>
-      <c r="E60" s="113"/>
-      <c r="F60" s="113"/>
-      <c r="G60" s="113"/>
-      <c r="H60" s="113"/>
-      <c r="I60" s="113"/>
-      <c r="J60" s="113"/>
-      <c r="K60" s="114"/>
+      <c r="D60" s="114"/>
+      <c r="E60" s="114"/>
+      <c r="F60" s="114"/>
+      <c r="G60" s="114"/>
+      <c r="H60" s="114"/>
+      <c r="I60" s="114"/>
+      <c r="J60" s="114"/>
+      <c r="K60" s="115"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>

--- a/GBDS AUGUST FILES 2026/INVENTORY COUNT SHEET - AUGUST 2026.xlsx
+++ b/GBDS AUGUST FILES 2026/INVENTORY COUNT SHEET - AUGUST 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS AUGUST FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ABA0F3D-8DBF-4E45-B47C-5C3724BD110E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEF16AEA-3BA9-4AA2-A08F-BD3B156D80D3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="12" activeTab="21" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="13" activeTab="22" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
   </bookViews>
   <sheets>
     <sheet name="SAMPLE" sheetId="32" r:id="rId1"/>
@@ -35,6 +35,7 @@
     <sheet name="08-26-2026" sheetId="87" r:id="rId20"/>
     <sheet name="08-27-2026" sheetId="88" r:id="rId21"/>
     <sheet name="08-28-2026" sheetId="89" r:id="rId22"/>
+    <sheet name="08-29-2026" sheetId="90" r:id="rId23"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'08-03-2026'!$A$1:$W$59</definedName>
@@ -58,6 +59,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="19">'08-26-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="20">'08-27-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="21">'08-28-2026'!$A$1:$W$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="22">'08-29-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">SAMPLE!$A$1:$W$85</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -76,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1848" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1932" uniqueCount="93">
   <si>
     <t>ROUTE 1</t>
   </si>
@@ -353,6 +355,9 @@
   </si>
   <si>
     <t>DATE: 08/28/2026</t>
+  </si>
+  <si>
+    <t>DATE: 08/29/2026</t>
   </si>
 </sst>
 </file>
@@ -1339,7 +1344,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="128">
+  <cellXfs count="129">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1625,6 +1630,9 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="63" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2077,21 +2085,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="116" t="s">
+      <c r="I1" s="117" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="116"/>
-      <c r="K1" s="116"/>
-      <c r="L1" s="116"/>
-      <c r="M1" s="116"/>
-      <c r="N1" s="116"/>
-      <c r="O1" s="116"/>
-      <c r="P1" s="116"/>
-      <c r="Q1" s="116"/>
-      <c r="R1" s="116"/>
-      <c r="S1" s="116"/>
-      <c r="T1" s="116"/>
-      <c r="U1" s="116"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -2103,17 +2111,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="117" t="s">
+      <c r="C4" s="118" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="117"/>
-      <c r="E4" s="117"/>
-      <c r="F4" s="117"/>
-      <c r="G4" s="117"/>
-      <c r="H4" s="117"/>
-      <c r="I4" s="117"/>
-      <c r="J4" s="118"/>
-      <c r="K4" s="119"/>
+      <c r="D4" s="118"/>
+      <c r="E4" s="118"/>
+      <c r="F4" s="118"/>
+      <c r="G4" s="118"/>
+      <c r="H4" s="118"/>
+      <c r="I4" s="118"/>
+      <c r="J4" s="119"/>
+      <c r="K4" s="120"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -2133,13 +2141,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="120" t="s">
+      <c r="T4" s="121" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="122" t="s">
+      <c r="U4" s="123" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="109" t="s">
+      <c r="V4" s="110" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -2179,10 +2187,10 @@
       <c r="I5" s="93" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="111" t="s">
+      <c r="J5" s="112" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="112"/>
+      <c r="K5" s="113"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -2190,9 +2198,9 @@
       <c r="Q5" s="89"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="121"/>
-      <c r="U5" s="123"/>
-      <c r="V5" s="110"/>
+      <c r="T5" s="122"/>
+      <c r="U5" s="124"/>
+      <c r="V5" s="111"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -4723,17 +4731,17 @@
       <c r="B62" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C62" s="113" t="s">
+      <c r="C62" s="114" t="s">
         <v>41</v>
       </c>
-      <c r="D62" s="114"/>
-      <c r="E62" s="114"/>
-      <c r="F62" s="114"/>
-      <c r="G62" s="114"/>
-      <c r="H62" s="114"/>
-      <c r="I62" s="114"/>
-      <c r="J62" s="114"/>
-      <c r="K62" s="115"/>
+      <c r="D62" s="115"/>
+      <c r="E62" s="115"/>
+      <c r="F62" s="115"/>
+      <c r="G62" s="115"/>
+      <c r="H62" s="115"/>
+      <c r="I62" s="115"/>
+      <c r="J62" s="115"/>
+      <c r="K62" s="116"/>
       <c r="U62" s="24" t="s">
         <v>51</v>
       </c>
@@ -5042,21 +5050,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="116" t="s">
+      <c r="I1" s="117" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="116"/>
-      <c r="K1" s="116"/>
-      <c r="L1" s="116"/>
-      <c r="M1" s="116"/>
-      <c r="N1" s="116"/>
-      <c r="O1" s="116"/>
-      <c r="P1" s="116"/>
-      <c r="Q1" s="116"/>
-      <c r="R1" s="116"/>
-      <c r="S1" s="116"/>
-      <c r="T1" s="116"/>
-      <c r="U1" s="116"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -5068,17 +5076,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="117" t="s">
+      <c r="C4" s="118" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="117"/>
-      <c r="E4" s="117"/>
-      <c r="F4" s="117"/>
-      <c r="G4" s="117"/>
-      <c r="H4" s="117"/>
-      <c r="I4" s="117"/>
-      <c r="J4" s="118"/>
-      <c r="K4" s="119"/>
+      <c r="D4" s="118"/>
+      <c r="E4" s="118"/>
+      <c r="F4" s="118"/>
+      <c r="G4" s="118"/>
+      <c r="H4" s="118"/>
+      <c r="I4" s="118"/>
+      <c r="J4" s="119"/>
+      <c r="K4" s="120"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -5098,13 +5106,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="120" t="s">
+      <c r="T4" s="121" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="126" t="s">
+      <c r="U4" s="127" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="109" t="s">
+      <c r="V4" s="110" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -5144,10 +5152,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="124" t="s">
+      <c r="J5" s="125" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="125"/>
+      <c r="K5" s="126"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -5155,9 +5163,9 @@
       <c r="Q5" s="99"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="121"/>
-      <c r="U5" s="127"/>
-      <c r="V5" s="110"/>
+      <c r="T5" s="122"/>
+      <c r="U5" s="128"/>
+      <c r="V5" s="111"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -7868,17 +7876,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="113" t="s">
+      <c r="C60" s="114" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="114"/>
-      <c r="E60" s="114"/>
-      <c r="F60" s="114"/>
-      <c r="G60" s="114"/>
-      <c r="H60" s="114"/>
-      <c r="I60" s="114"/>
-      <c r="J60" s="114"/>
-      <c r="K60" s="115"/>
+      <c r="D60" s="115"/>
+      <c r="E60" s="115"/>
+      <c r="F60" s="115"/>
+      <c r="G60" s="115"/>
+      <c r="H60" s="115"/>
+      <c r="I60" s="115"/>
+      <c r="J60" s="115"/>
+      <c r="K60" s="116"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -8187,21 +8195,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="116" t="s">
+      <c r="I1" s="117" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="116"/>
-      <c r="K1" s="116"/>
-      <c r="L1" s="116"/>
-      <c r="M1" s="116"/>
-      <c r="N1" s="116"/>
-      <c r="O1" s="116"/>
-      <c r="P1" s="116"/>
-      <c r="Q1" s="116"/>
-      <c r="R1" s="116"/>
-      <c r="S1" s="116"/>
-      <c r="T1" s="116"/>
-      <c r="U1" s="116"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -8213,17 +8221,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="117" t="s">
+      <c r="C4" s="118" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="117"/>
-      <c r="E4" s="117"/>
-      <c r="F4" s="117"/>
-      <c r="G4" s="117"/>
-      <c r="H4" s="117"/>
-      <c r="I4" s="117"/>
-      <c r="J4" s="118"/>
-      <c r="K4" s="119"/>
+      <c r="D4" s="118"/>
+      <c r="E4" s="118"/>
+      <c r="F4" s="118"/>
+      <c r="G4" s="118"/>
+      <c r="H4" s="118"/>
+      <c r="I4" s="118"/>
+      <c r="J4" s="119"/>
+      <c r="K4" s="120"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -8243,13 +8251,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="120" t="s">
+      <c r="T4" s="121" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="126" t="s">
+      <c r="U4" s="127" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="109" t="s">
+      <c r="V4" s="110" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -8289,10 +8297,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="124" t="s">
+      <c r="J5" s="125" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="125"/>
+      <c r="K5" s="126"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -8300,9 +8308,9 @@
       <c r="Q5" s="99"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="121"/>
-      <c r="U5" s="127"/>
-      <c r="V5" s="110"/>
+      <c r="T5" s="122"/>
+      <c r="U5" s="128"/>
+      <c r="V5" s="111"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -11015,17 +11023,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="113" t="s">
+      <c r="C60" s="114" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="114"/>
-      <c r="E60" s="114"/>
-      <c r="F60" s="114"/>
-      <c r="G60" s="114"/>
-      <c r="H60" s="114"/>
-      <c r="I60" s="114"/>
-      <c r="J60" s="114"/>
-      <c r="K60" s="115"/>
+      <c r="D60" s="115"/>
+      <c r="E60" s="115"/>
+      <c r="F60" s="115"/>
+      <c r="G60" s="115"/>
+      <c r="H60" s="115"/>
+      <c r="I60" s="115"/>
+      <c r="J60" s="115"/>
+      <c r="K60" s="116"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -11334,21 +11342,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="116" t="s">
+      <c r="I1" s="117" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="116"/>
-      <c r="K1" s="116"/>
-      <c r="L1" s="116"/>
-      <c r="M1" s="116"/>
-      <c r="N1" s="116"/>
-      <c r="O1" s="116"/>
-      <c r="P1" s="116"/>
-      <c r="Q1" s="116"/>
-      <c r="R1" s="116"/>
-      <c r="S1" s="116"/>
-      <c r="T1" s="116"/>
-      <c r="U1" s="116"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -11360,17 +11368,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="117" t="s">
+      <c r="C4" s="118" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="117"/>
-      <c r="E4" s="117"/>
-      <c r="F4" s="117"/>
-      <c r="G4" s="117"/>
-      <c r="H4" s="117"/>
-      <c r="I4" s="117"/>
-      <c r="J4" s="118"/>
-      <c r="K4" s="119"/>
+      <c r="D4" s="118"/>
+      <c r="E4" s="118"/>
+      <c r="F4" s="118"/>
+      <c r="G4" s="118"/>
+      <c r="H4" s="118"/>
+      <c r="I4" s="118"/>
+      <c r="J4" s="119"/>
+      <c r="K4" s="120"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -11390,13 +11398,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="120" t="s">
+      <c r="T4" s="121" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="126" t="s">
+      <c r="U4" s="127" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="109" t="s">
+      <c r="V4" s="110" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -11436,10 +11444,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="124" t="s">
+      <c r="J5" s="125" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="125"/>
+      <c r="K5" s="126"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -11447,9 +11455,9 @@
       <c r="Q5" s="99"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="121"/>
-      <c r="U5" s="127"/>
-      <c r="V5" s="110"/>
+      <c r="T5" s="122"/>
+      <c r="U5" s="128"/>
+      <c r="V5" s="111"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -14151,17 +14159,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="113" t="s">
+      <c r="C60" s="114" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="114"/>
-      <c r="E60" s="114"/>
-      <c r="F60" s="114"/>
-      <c r="G60" s="114"/>
-      <c r="H60" s="114"/>
-      <c r="I60" s="114"/>
-      <c r="J60" s="114"/>
-      <c r="K60" s="115"/>
+      <c r="D60" s="115"/>
+      <c r="E60" s="115"/>
+      <c r="F60" s="115"/>
+      <c r="G60" s="115"/>
+      <c r="H60" s="115"/>
+      <c r="I60" s="115"/>
+      <c r="J60" s="115"/>
+      <c r="K60" s="116"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -14470,21 +14478,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="116" t="s">
+      <c r="I1" s="117" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="116"/>
-      <c r="K1" s="116"/>
-      <c r="L1" s="116"/>
-      <c r="M1" s="116"/>
-      <c r="N1" s="116"/>
-      <c r="O1" s="116"/>
-      <c r="P1" s="116"/>
-      <c r="Q1" s="116"/>
-      <c r="R1" s="116"/>
-      <c r="S1" s="116"/>
-      <c r="T1" s="116"/>
-      <c r="U1" s="116"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -14496,17 +14504,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="117" t="s">
+      <c r="C4" s="118" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="117"/>
-      <c r="E4" s="117"/>
-      <c r="F4" s="117"/>
-      <c r="G4" s="117"/>
-      <c r="H4" s="117"/>
-      <c r="I4" s="117"/>
-      <c r="J4" s="118"/>
-      <c r="K4" s="119"/>
+      <c r="D4" s="118"/>
+      <c r="E4" s="118"/>
+      <c r="F4" s="118"/>
+      <c r="G4" s="118"/>
+      <c r="H4" s="118"/>
+      <c r="I4" s="118"/>
+      <c r="J4" s="119"/>
+      <c r="K4" s="120"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -14526,13 +14534,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="120" t="s">
+      <c r="T4" s="121" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="126" t="s">
+      <c r="U4" s="127" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="109" t="s">
+      <c r="V4" s="110" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -14572,10 +14580,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="124" t="s">
+      <c r="J5" s="125" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="125"/>
+      <c r="K5" s="126"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -14583,9 +14591,9 @@
       <c r="Q5" s="99"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="121"/>
-      <c r="U5" s="127"/>
-      <c r="V5" s="110"/>
+      <c r="T5" s="122"/>
+      <c r="U5" s="128"/>
+      <c r="V5" s="111"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -17286,17 +17294,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="113" t="s">
+      <c r="C60" s="114" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="114"/>
-      <c r="E60" s="114"/>
-      <c r="F60" s="114"/>
-      <c r="G60" s="114"/>
-      <c r="H60" s="114"/>
-      <c r="I60" s="114"/>
-      <c r="J60" s="114"/>
-      <c r="K60" s="115"/>
+      <c r="D60" s="115"/>
+      <c r="E60" s="115"/>
+      <c r="F60" s="115"/>
+      <c r="G60" s="115"/>
+      <c r="H60" s="115"/>
+      <c r="I60" s="115"/>
+      <c r="J60" s="115"/>
+      <c r="K60" s="116"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -17605,21 +17613,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="116" t="s">
+      <c r="I1" s="117" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="116"/>
-      <c r="K1" s="116"/>
-      <c r="L1" s="116"/>
-      <c r="M1" s="116"/>
-      <c r="N1" s="116"/>
-      <c r="O1" s="116"/>
-      <c r="P1" s="116"/>
-      <c r="Q1" s="116"/>
-      <c r="R1" s="116"/>
-      <c r="S1" s="116"/>
-      <c r="T1" s="116"/>
-      <c r="U1" s="116"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -17631,17 +17639,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="117" t="s">
+      <c r="C4" s="118" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="117"/>
-      <c r="E4" s="117"/>
-      <c r="F4" s="117"/>
-      <c r="G4" s="117"/>
-      <c r="H4" s="117"/>
-      <c r="I4" s="117"/>
-      <c r="J4" s="118"/>
-      <c r="K4" s="119"/>
+      <c r="D4" s="118"/>
+      <c r="E4" s="118"/>
+      <c r="F4" s="118"/>
+      <c r="G4" s="118"/>
+      <c r="H4" s="118"/>
+      <c r="I4" s="118"/>
+      <c r="J4" s="119"/>
+      <c r="K4" s="120"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -17661,13 +17669,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="120" t="s">
+      <c r="T4" s="121" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="126" t="s">
+      <c r="U4" s="127" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="109" t="s">
+      <c r="V4" s="110" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -17707,10 +17715,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="124" t="s">
+      <c r="J5" s="125" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="125"/>
+      <c r="K5" s="126"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -17718,9 +17726,9 @@
       <c r="Q5" s="100"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="121"/>
-      <c r="U5" s="127"/>
-      <c r="V5" s="110"/>
+      <c r="T5" s="122"/>
+      <c r="U5" s="128"/>
+      <c r="V5" s="111"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -20415,17 +20423,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="113" t="s">
+      <c r="C60" s="114" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="114"/>
-      <c r="E60" s="114"/>
-      <c r="F60" s="114"/>
-      <c r="G60" s="114"/>
-      <c r="H60" s="114"/>
-      <c r="I60" s="114"/>
-      <c r="J60" s="114"/>
-      <c r="K60" s="115"/>
+      <c r="D60" s="115"/>
+      <c r="E60" s="115"/>
+      <c r="F60" s="115"/>
+      <c r="G60" s="115"/>
+      <c r="H60" s="115"/>
+      <c r="I60" s="115"/>
+      <c r="J60" s="115"/>
+      <c r="K60" s="116"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -20734,21 +20742,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="116" t="s">
+      <c r="I1" s="117" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="116"/>
-      <c r="K1" s="116"/>
-      <c r="L1" s="116"/>
-      <c r="M1" s="116"/>
-      <c r="N1" s="116"/>
-      <c r="O1" s="116"/>
-      <c r="P1" s="116"/>
-      <c r="Q1" s="116"/>
-      <c r="R1" s="116"/>
-      <c r="S1" s="116"/>
-      <c r="T1" s="116"/>
-      <c r="U1" s="116"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -20760,17 +20768,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="117" t="s">
+      <c r="C4" s="118" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="117"/>
-      <c r="E4" s="117"/>
-      <c r="F4" s="117"/>
-      <c r="G4" s="117"/>
-      <c r="H4" s="117"/>
-      <c r="I4" s="117"/>
-      <c r="J4" s="118"/>
-      <c r="K4" s="119"/>
+      <c r="D4" s="118"/>
+      <c r="E4" s="118"/>
+      <c r="F4" s="118"/>
+      <c r="G4" s="118"/>
+      <c r="H4" s="118"/>
+      <c r="I4" s="118"/>
+      <c r="J4" s="119"/>
+      <c r="K4" s="120"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -20790,13 +20798,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="120" t="s">
+      <c r="T4" s="121" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="126" t="s">
+      <c r="U4" s="127" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="109" t="s">
+      <c r="V4" s="110" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -20836,10 +20844,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="124" t="s">
+      <c r="J5" s="125" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="125"/>
+      <c r="K5" s="126"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -20847,9 +20855,9 @@
       <c r="Q5" s="101"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="121"/>
-      <c r="U5" s="127"/>
-      <c r="V5" s="110"/>
+      <c r="T5" s="122"/>
+      <c r="U5" s="128"/>
+      <c r="V5" s="111"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -23540,17 +23548,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="113" t="s">
+      <c r="C60" s="114" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="114"/>
-      <c r="E60" s="114"/>
-      <c r="F60" s="114"/>
-      <c r="G60" s="114"/>
-      <c r="H60" s="114"/>
-      <c r="I60" s="114"/>
-      <c r="J60" s="114"/>
-      <c r="K60" s="115"/>
+      <c r="D60" s="115"/>
+      <c r="E60" s="115"/>
+      <c r="F60" s="115"/>
+      <c r="G60" s="115"/>
+      <c r="H60" s="115"/>
+      <c r="I60" s="115"/>
+      <c r="J60" s="115"/>
+      <c r="K60" s="116"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -23859,21 +23867,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="116" t="s">
+      <c r="I1" s="117" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="116"/>
-      <c r="K1" s="116"/>
-      <c r="L1" s="116"/>
-      <c r="M1" s="116"/>
-      <c r="N1" s="116"/>
-      <c r="O1" s="116"/>
-      <c r="P1" s="116"/>
-      <c r="Q1" s="116"/>
-      <c r="R1" s="116"/>
-      <c r="S1" s="116"/>
-      <c r="T1" s="116"/>
-      <c r="U1" s="116"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -23885,17 +23893,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="117" t="s">
+      <c r="C4" s="118" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="117"/>
-      <c r="E4" s="117"/>
-      <c r="F4" s="117"/>
-      <c r="G4" s="117"/>
-      <c r="H4" s="117"/>
-      <c r="I4" s="117"/>
-      <c r="J4" s="118"/>
-      <c r="K4" s="119"/>
+      <c r="D4" s="118"/>
+      <c r="E4" s="118"/>
+      <c r="F4" s="118"/>
+      <c r="G4" s="118"/>
+      <c r="H4" s="118"/>
+      <c r="I4" s="118"/>
+      <c r="J4" s="119"/>
+      <c r="K4" s="120"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -23915,13 +23923,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="120" t="s">
+      <c r="T4" s="121" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="126" t="s">
+      <c r="U4" s="127" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="109" t="s">
+      <c r="V4" s="110" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -23961,10 +23969,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="124" t="s">
+      <c r="J5" s="125" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="125"/>
+      <c r="K5" s="126"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -23972,9 +23980,9 @@
       <c r="Q5" s="102"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="121"/>
-      <c r="U5" s="127"/>
-      <c r="V5" s="110"/>
+      <c r="T5" s="122"/>
+      <c r="U5" s="128"/>
+      <c r="V5" s="111"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -26682,17 +26690,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="113" t="s">
+      <c r="C60" s="114" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="114"/>
-      <c r="E60" s="114"/>
-      <c r="F60" s="114"/>
-      <c r="G60" s="114"/>
-      <c r="H60" s="114"/>
-      <c r="I60" s="114"/>
-      <c r="J60" s="114"/>
-      <c r="K60" s="115"/>
+      <c r="D60" s="115"/>
+      <c r="E60" s="115"/>
+      <c r="F60" s="115"/>
+      <c r="G60" s="115"/>
+      <c r="H60" s="115"/>
+      <c r="I60" s="115"/>
+      <c r="J60" s="115"/>
+      <c r="K60" s="116"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -27001,21 +27009,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="116" t="s">
+      <c r="I1" s="117" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="116"/>
-      <c r="K1" s="116"/>
-      <c r="L1" s="116"/>
-      <c r="M1" s="116"/>
-      <c r="N1" s="116"/>
-      <c r="O1" s="116"/>
-      <c r="P1" s="116"/>
-      <c r="Q1" s="116"/>
-      <c r="R1" s="116"/>
-      <c r="S1" s="116"/>
-      <c r="T1" s="116"/>
-      <c r="U1" s="116"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -27027,17 +27035,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="117" t="s">
+      <c r="C4" s="118" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="117"/>
-      <c r="E4" s="117"/>
-      <c r="F4" s="117"/>
-      <c r="G4" s="117"/>
-      <c r="H4" s="117"/>
-      <c r="I4" s="117"/>
-      <c r="J4" s="118"/>
-      <c r="K4" s="119"/>
+      <c r="D4" s="118"/>
+      <c r="E4" s="118"/>
+      <c r="F4" s="118"/>
+      <c r="G4" s="118"/>
+      <c r="H4" s="118"/>
+      <c r="I4" s="118"/>
+      <c r="J4" s="119"/>
+      <c r="K4" s="120"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -27057,13 +27065,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="120" t="s">
+      <c r="T4" s="121" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="126" t="s">
+      <c r="U4" s="127" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="109" t="s">
+      <c r="V4" s="110" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -27103,10 +27111,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="124" t="s">
+      <c r="J5" s="125" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="125"/>
+      <c r="K5" s="126"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -27114,9 +27122,9 @@
       <c r="Q5" s="103"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="121"/>
-      <c r="U5" s="127"/>
-      <c r="V5" s="110"/>
+      <c r="T5" s="122"/>
+      <c r="U5" s="128"/>
+      <c r="V5" s="111"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -29800,17 +29808,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="113" t="s">
+      <c r="C60" s="114" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="114"/>
-      <c r="E60" s="114"/>
-      <c r="F60" s="114"/>
-      <c r="G60" s="114"/>
-      <c r="H60" s="114"/>
-      <c r="I60" s="114"/>
-      <c r="J60" s="114"/>
-      <c r="K60" s="115"/>
+      <c r="D60" s="115"/>
+      <c r="E60" s="115"/>
+      <c r="F60" s="115"/>
+      <c r="G60" s="115"/>
+      <c r="H60" s="115"/>
+      <c r="I60" s="115"/>
+      <c r="J60" s="115"/>
+      <c r="K60" s="116"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -30119,21 +30127,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="116" t="s">
+      <c r="I1" s="117" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="116"/>
-      <c r="K1" s="116"/>
-      <c r="L1" s="116"/>
-      <c r="M1" s="116"/>
-      <c r="N1" s="116"/>
-      <c r="O1" s="116"/>
-      <c r="P1" s="116"/>
-      <c r="Q1" s="116"/>
-      <c r="R1" s="116"/>
-      <c r="S1" s="116"/>
-      <c r="T1" s="116"/>
-      <c r="U1" s="116"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -30145,17 +30153,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="117" t="s">
+      <c r="C4" s="118" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="117"/>
-      <c r="E4" s="117"/>
-      <c r="F4" s="117"/>
-      <c r="G4" s="117"/>
-      <c r="H4" s="117"/>
-      <c r="I4" s="117"/>
-      <c r="J4" s="118"/>
-      <c r="K4" s="119"/>
+      <c r="D4" s="118"/>
+      <c r="E4" s="118"/>
+      <c r="F4" s="118"/>
+      <c r="G4" s="118"/>
+      <c r="H4" s="118"/>
+      <c r="I4" s="118"/>
+      <c r="J4" s="119"/>
+      <c r="K4" s="120"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -30175,13 +30183,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="120" t="s">
+      <c r="T4" s="121" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="126" t="s">
+      <c r="U4" s="127" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="109" t="s">
+      <c r="V4" s="110" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -30221,10 +30229,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="124" t="s">
+      <c r="J5" s="125" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="125"/>
+      <c r="K5" s="126"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -30232,9 +30240,9 @@
       <c r="Q5" s="104"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="121"/>
-      <c r="U5" s="127"/>
-      <c r="V5" s="110"/>
+      <c r="T5" s="122"/>
+      <c r="U5" s="128"/>
+      <c r="V5" s="111"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -32910,17 +32918,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="113" t="s">
+      <c r="C60" s="114" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="114"/>
-      <c r="E60" s="114"/>
-      <c r="F60" s="114"/>
-      <c r="G60" s="114"/>
-      <c r="H60" s="114"/>
-      <c r="I60" s="114"/>
-      <c r="J60" s="114"/>
-      <c r="K60" s="115"/>
+      <c r="D60" s="115"/>
+      <c r="E60" s="115"/>
+      <c r="F60" s="115"/>
+      <c r="G60" s="115"/>
+      <c r="H60" s="115"/>
+      <c r="I60" s="115"/>
+      <c r="J60" s="115"/>
+      <c r="K60" s="116"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -33229,21 +33237,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="116" t="s">
+      <c r="I1" s="117" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="116"/>
-      <c r="K1" s="116"/>
-      <c r="L1" s="116"/>
-      <c r="M1" s="116"/>
-      <c r="N1" s="116"/>
-      <c r="O1" s="116"/>
-      <c r="P1" s="116"/>
-      <c r="Q1" s="116"/>
-      <c r="R1" s="116"/>
-      <c r="S1" s="116"/>
-      <c r="T1" s="116"/>
-      <c r="U1" s="116"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -33255,17 +33263,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="117" t="s">
+      <c r="C4" s="118" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="117"/>
-      <c r="E4" s="117"/>
-      <c r="F4" s="117"/>
-      <c r="G4" s="117"/>
-      <c r="H4" s="117"/>
-      <c r="I4" s="117"/>
-      <c r="J4" s="118"/>
-      <c r="K4" s="119"/>
+      <c r="D4" s="118"/>
+      <c r="E4" s="118"/>
+      <c r="F4" s="118"/>
+      <c r="G4" s="118"/>
+      <c r="H4" s="118"/>
+      <c r="I4" s="118"/>
+      <c r="J4" s="119"/>
+      <c r="K4" s="120"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -33285,13 +33293,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="120" t="s">
+      <c r="T4" s="121" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="126" t="s">
+      <c r="U4" s="127" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="109" t="s">
+      <c r="V4" s="110" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -33331,10 +33339,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="124" t="s">
+      <c r="J5" s="125" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="125"/>
+      <c r="K5" s="126"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -33342,9 +33350,9 @@
       <c r="Q5" s="105"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="121"/>
-      <c r="U5" s="127"/>
-      <c r="V5" s="110"/>
+      <c r="T5" s="122"/>
+      <c r="U5" s="128"/>
+      <c r="V5" s="111"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -36029,17 +36037,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="113" t="s">
+      <c r="C60" s="114" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="114"/>
-      <c r="E60" s="114"/>
-      <c r="F60" s="114"/>
-      <c r="G60" s="114"/>
-      <c r="H60" s="114"/>
-      <c r="I60" s="114"/>
-      <c r="J60" s="114"/>
-      <c r="K60" s="115"/>
+      <c r="D60" s="115"/>
+      <c r="E60" s="115"/>
+      <c r="F60" s="115"/>
+      <c r="G60" s="115"/>
+      <c r="H60" s="115"/>
+      <c r="I60" s="115"/>
+      <c r="J60" s="115"/>
+      <c r="K60" s="116"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -36348,21 +36356,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="116" t="s">
+      <c r="I1" s="117" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="116"/>
-      <c r="K1" s="116"/>
-      <c r="L1" s="116"/>
-      <c r="M1" s="116"/>
-      <c r="N1" s="116"/>
-      <c r="O1" s="116"/>
-      <c r="P1" s="116"/>
-      <c r="Q1" s="116"/>
-      <c r="R1" s="116"/>
-      <c r="S1" s="116"/>
-      <c r="T1" s="116"/>
-      <c r="U1" s="116"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -36374,17 +36382,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="117" t="s">
+      <c r="C4" s="118" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="117"/>
-      <c r="E4" s="117"/>
-      <c r="F4" s="117"/>
-      <c r="G4" s="117"/>
-      <c r="H4" s="117"/>
-      <c r="I4" s="117"/>
-      <c r="J4" s="118"/>
-      <c r="K4" s="119"/>
+      <c r="D4" s="118"/>
+      <c r="E4" s="118"/>
+      <c r="F4" s="118"/>
+      <c r="G4" s="118"/>
+      <c r="H4" s="118"/>
+      <c r="I4" s="118"/>
+      <c r="J4" s="119"/>
+      <c r="K4" s="120"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -36404,13 +36412,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="120" t="s">
+      <c r="T4" s="121" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="126" t="s">
+      <c r="U4" s="127" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="109" t="s">
+      <c r="V4" s="110" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -36450,10 +36458,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="124" t="s">
+      <c r="J5" s="125" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="125"/>
+      <c r="K5" s="126"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -36461,9 +36469,9 @@
       <c r="Q5" s="96"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="121"/>
-      <c r="U5" s="127"/>
-      <c r="V5" s="110"/>
+      <c r="T5" s="122"/>
+      <c r="U5" s="128"/>
+      <c r="V5" s="111"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -39173,17 +39181,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="113" t="s">
+      <c r="C60" s="114" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="114"/>
-      <c r="E60" s="114"/>
-      <c r="F60" s="114"/>
-      <c r="G60" s="114"/>
-      <c r="H60" s="114"/>
-      <c r="I60" s="114"/>
-      <c r="J60" s="114"/>
-      <c r="K60" s="115"/>
+      <c r="D60" s="115"/>
+      <c r="E60" s="115"/>
+      <c r="F60" s="115"/>
+      <c r="G60" s="115"/>
+      <c r="H60" s="115"/>
+      <c r="I60" s="115"/>
+      <c r="J60" s="115"/>
+      <c r="K60" s="116"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -39492,21 +39500,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="116" t="s">
+      <c r="I1" s="117" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="116"/>
-      <c r="K1" s="116"/>
-      <c r="L1" s="116"/>
-      <c r="M1" s="116"/>
-      <c r="N1" s="116"/>
-      <c r="O1" s="116"/>
-      <c r="P1" s="116"/>
-      <c r="Q1" s="116"/>
-      <c r="R1" s="116"/>
-      <c r="S1" s="116"/>
-      <c r="T1" s="116"/>
-      <c r="U1" s="116"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -39518,17 +39526,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="117" t="s">
+      <c r="C4" s="118" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="117"/>
-      <c r="E4" s="117"/>
-      <c r="F4" s="117"/>
-      <c r="G4" s="117"/>
-      <c r="H4" s="117"/>
-      <c r="I4" s="117"/>
-      <c r="J4" s="118"/>
-      <c r="K4" s="119"/>
+      <c r="D4" s="118"/>
+      <c r="E4" s="118"/>
+      <c r="F4" s="118"/>
+      <c r="G4" s="118"/>
+      <c r="H4" s="118"/>
+      <c r="I4" s="118"/>
+      <c r="J4" s="119"/>
+      <c r="K4" s="120"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -39548,13 +39556,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="120" t="s">
+      <c r="T4" s="121" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="126" t="s">
+      <c r="U4" s="127" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="109" t="s">
+      <c r="V4" s="110" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -39594,10 +39602,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="124" t="s">
+      <c r="J5" s="125" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="125"/>
+      <c r="K5" s="126"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -39605,9 +39613,9 @@
       <c r="Q5" s="106"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="121"/>
-      <c r="U5" s="127"/>
-      <c r="V5" s="110"/>
+      <c r="T5" s="122"/>
+      <c r="U5" s="128"/>
+      <c r="V5" s="111"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -42303,17 +42311,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="113" t="s">
+      <c r="C60" s="114" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="114"/>
-      <c r="E60" s="114"/>
-      <c r="F60" s="114"/>
-      <c r="G60" s="114"/>
-      <c r="H60" s="114"/>
-      <c r="I60" s="114"/>
-      <c r="J60" s="114"/>
-      <c r="K60" s="115"/>
+      <c r="D60" s="115"/>
+      <c r="E60" s="115"/>
+      <c r="F60" s="115"/>
+      <c r="G60" s="115"/>
+      <c r="H60" s="115"/>
+      <c r="I60" s="115"/>
+      <c r="J60" s="115"/>
+      <c r="K60" s="116"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -42622,21 +42630,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="116" t="s">
+      <c r="I1" s="117" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="116"/>
-      <c r="K1" s="116"/>
-      <c r="L1" s="116"/>
-      <c r="M1" s="116"/>
-      <c r="N1" s="116"/>
-      <c r="O1" s="116"/>
-      <c r="P1" s="116"/>
-      <c r="Q1" s="116"/>
-      <c r="R1" s="116"/>
-      <c r="S1" s="116"/>
-      <c r="T1" s="116"/>
-      <c r="U1" s="116"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -42648,17 +42656,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="117" t="s">
+      <c r="C4" s="118" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="117"/>
-      <c r="E4" s="117"/>
-      <c r="F4" s="117"/>
-      <c r="G4" s="117"/>
-      <c r="H4" s="117"/>
-      <c r="I4" s="117"/>
-      <c r="J4" s="118"/>
-      <c r="K4" s="119"/>
+      <c r="D4" s="118"/>
+      <c r="E4" s="118"/>
+      <c r="F4" s="118"/>
+      <c r="G4" s="118"/>
+      <c r="H4" s="118"/>
+      <c r="I4" s="118"/>
+      <c r="J4" s="119"/>
+      <c r="K4" s="120"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -42678,13 +42686,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="120" t="s">
+      <c r="T4" s="121" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="126" t="s">
+      <c r="U4" s="127" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="109" t="s">
+      <c r="V4" s="110" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -42724,10 +42732,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="124" t="s">
+      <c r="J5" s="125" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="125"/>
+      <c r="K5" s="126"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -42735,9 +42743,9 @@
       <c r="Q5" s="107"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="121"/>
-      <c r="U5" s="127"/>
-      <c r="V5" s="110"/>
+      <c r="T5" s="122"/>
+      <c r="U5" s="128"/>
+      <c r="V5" s="111"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -45431,17 +45439,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="113" t="s">
+      <c r="C60" s="114" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="114"/>
-      <c r="E60" s="114"/>
-      <c r="F60" s="114"/>
-      <c r="G60" s="114"/>
-      <c r="H60" s="114"/>
-      <c r="I60" s="114"/>
-      <c r="J60" s="114"/>
-      <c r="K60" s="115"/>
+      <c r="D60" s="115"/>
+      <c r="E60" s="115"/>
+      <c r="F60" s="115"/>
+      <c r="G60" s="115"/>
+      <c r="H60" s="115"/>
+      <c r="I60" s="115"/>
+      <c r="J60" s="115"/>
+      <c r="K60" s="116"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -45750,21 +45758,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="116" t="s">
+      <c r="I1" s="117" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="116"/>
-      <c r="K1" s="116"/>
-      <c r="L1" s="116"/>
-      <c r="M1" s="116"/>
-      <c r="N1" s="116"/>
-      <c r="O1" s="116"/>
-      <c r="P1" s="116"/>
-      <c r="Q1" s="116"/>
-      <c r="R1" s="116"/>
-      <c r="S1" s="116"/>
-      <c r="T1" s="116"/>
-      <c r="U1" s="116"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -45776,17 +45784,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="117" t="s">
+      <c r="C4" s="118" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="117"/>
-      <c r="E4" s="117"/>
-      <c r="F4" s="117"/>
-      <c r="G4" s="117"/>
-      <c r="H4" s="117"/>
-      <c r="I4" s="117"/>
-      <c r="J4" s="118"/>
-      <c r="K4" s="119"/>
+      <c r="D4" s="118"/>
+      <c r="E4" s="118"/>
+      <c r="F4" s="118"/>
+      <c r="G4" s="118"/>
+      <c r="H4" s="118"/>
+      <c r="I4" s="118"/>
+      <c r="J4" s="119"/>
+      <c r="K4" s="120"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -45806,13 +45814,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="120" t="s">
+      <c r="T4" s="121" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="126" t="s">
+      <c r="U4" s="127" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="109" t="s">
+      <c r="V4" s="110" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -45852,10 +45860,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="124" t="s">
+      <c r="J5" s="125" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="125"/>
+      <c r="K5" s="126"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -45863,9 +45871,9 @@
       <c r="Q5" s="108"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="121"/>
-      <c r="U5" s="127"/>
-      <c r="V5" s="110"/>
+      <c r="T5" s="122"/>
+      <c r="U5" s="128"/>
+      <c r="V5" s="111"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -48553,17 +48561,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="113" t="s">
+      <c r="C60" s="114" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="114"/>
-      <c r="E60" s="114"/>
-      <c r="F60" s="114"/>
-      <c r="G60" s="114"/>
-      <c r="H60" s="114"/>
-      <c r="I60" s="114"/>
-      <c r="J60" s="114"/>
-      <c r="K60" s="115"/>
+      <c r="D60" s="115"/>
+      <c r="E60" s="115"/>
+      <c r="F60" s="115"/>
+      <c r="G60" s="115"/>
+      <c r="H60" s="115"/>
+      <c r="I60" s="115"/>
+      <c r="J60" s="115"/>
+      <c r="K60" s="116"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -48815,13 +48823,3142 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
     <mergeCell ref="C60:K60"/>
     <mergeCell ref="I1:U1"/>
     <mergeCell ref="C4:K4"/>
     <mergeCell ref="T4:T5"/>
     <mergeCell ref="U4:U5"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
+  <pageSetup paperSize="14" scale="70" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="24" max="80" man="1"/>
+  </colBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFBAFFD0-9180-4908-A864-4759E5CB4BA7}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BB81"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="28" customWidth="1"/>
+    <col min="3" max="6" width="10" style="9" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" style="9" customWidth="1"/>
+    <col min="8" max="8" width="7.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.85546875" style="9" customWidth="1"/>
+    <col min="11" max="11" width="7.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.42578125" style="9" customWidth="1"/>
+    <col min="13" max="13" width="10" style="9" customWidth="1"/>
+    <col min="14" max="14" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" style="9" customWidth="1"/>
+    <col min="16" max="16" width="5.5703125" style="9" customWidth="1"/>
+    <col min="17" max="17" width="10" style="9" customWidth="1"/>
+    <col min="18" max="18" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="1.42578125" style="9" customWidth="1"/>
+    <col min="20" max="20" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="9" customWidth="1"/>
+    <col min="22" max="22" width="19.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="23" max="49" width="7.28515625" style="9" customWidth="1"/>
+    <col min="50" max="50" width="1.5703125" style="9" customWidth="1"/>
+    <col min="51" max="51" width="9.42578125" style="9" customWidth="1"/>
+    <col min="52" max="52" width="1.28515625" style="9" customWidth="1"/>
+    <col min="53" max="53" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="10.28515625" style="9" bestFit="1" customWidth="1"/>
+    <col min="55" max="16384" width="9.140625" style="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="117" t="s">
+        <v>43</v>
+      </c>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
+    </row>
+    <row r="2" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="B2" s="28" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B4" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="118" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="118"/>
+      <c r="E4" s="118"/>
+      <c r="F4" s="118"/>
+      <c r="G4" s="118"/>
+      <c r="H4" s="118"/>
+      <c r="I4" s="118"/>
+      <c r="J4" s="119"/>
+      <c r="K4" s="120"/>
+      <c r="M4" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="N4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="O4" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="P4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q4" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="R4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="S4" s="9"/>
+      <c r="T4" s="121" t="s">
+        <v>68</v>
+      </c>
+      <c r="U4" s="127" t="s">
+        <v>67</v>
+      </c>
+      <c r="V4" s="110" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF4" s="11"/>
+      <c r="AG4" s="11"/>
+      <c r="AH4" s="11"/>
+      <c r="AI4" s="11"/>
+      <c r="AJ4" s="11"/>
+      <c r="AK4" s="11"/>
+      <c r="AL4" s="11"/>
+      <c r="AM4" s="11"/>
+      <c r="AN4" s="11"/>
+      <c r="AO4" s="11"/>
+      <c r="AP4" s="11"/>
+      <c r="AQ4" s="11"/>
+      <c r="AR4" s="11"/>
+      <c r="AS4" s="11"/>
+      <c r="AT4" s="11"/>
+      <c r="AU4" s="11"/>
+      <c r="AV4" s="11"/>
+      <c r="AW4" s="11"/>
+      <c r="AX4" s="11"/>
+      <c r="AY4" s="11"/>
+      <c r="AZ4" s="11"/>
+      <c r="BA4" s="11"/>
+      <c r="BB4" s="11"/>
+    </row>
+    <row r="5" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="37"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40" t="s">
+        <v>64</v>
+      </c>
+      <c r="I5" s="40" t="s">
+        <v>60</v>
+      </c>
+      <c r="J5" s="125" t="s">
+        <v>65</v>
+      </c>
+      <c r="K5" s="126"/>
+      <c r="M5" s="37"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="40"/>
+      <c r="P5" s="109"/>
+      <c r="Q5" s="109"/>
+      <c r="R5" s="38"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="122"/>
+      <c r="U5" s="128"/>
+      <c r="V5" s="111"/>
+      <c r="AF5" s="11"/>
+      <c r="AG5" s="11"/>
+      <c r="AH5" s="11"/>
+      <c r="AI5" s="11"/>
+      <c r="AJ5" s="11"/>
+      <c r="AK5" s="11"/>
+      <c r="AL5" s="11"/>
+      <c r="AM5" s="11"/>
+      <c r="AN5" s="11"/>
+      <c r="AO5" s="11"/>
+      <c r="AP5" s="11"/>
+      <c r="AQ5" s="11"/>
+      <c r="AR5" s="11"/>
+      <c r="AS5" s="11"/>
+      <c r="AT5" s="11"/>
+      <c r="AU5" s="11"/>
+      <c r="AV5" s="11"/>
+      <c r="AW5" s="11"/>
+      <c r="AX5" s="11"/>
+      <c r="AY5" s="11"/>
+      <c r="AZ5" s="11"/>
+      <c r="BA5" s="11"/>
+      <c r="BB5" s="11"/>
+    </row>
+    <row r="6" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="37"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="109"/>
+      <c r="K6" s="38"/>
+      <c r="M6" s="37"/>
+      <c r="N6" s="49"/>
+      <c r="O6" s="40"/>
+      <c r="P6" s="109"/>
+      <c r="Q6" s="109"/>
+      <c r="R6" s="38"/>
+      <c r="S6" s="9"/>
+      <c r="T6" s="39"/>
+      <c r="U6" s="39"/>
+      <c r="V6" s="39"/>
+      <c r="AF6" s="11"/>
+      <c r="AG6" s="11"/>
+      <c r="AH6" s="11"/>
+      <c r="AI6" s="11"/>
+      <c r="AJ6" s="11"/>
+      <c r="AK6" s="11"/>
+      <c r="AL6" s="11"/>
+      <c r="AM6" s="11"/>
+      <c r="AN6" s="11"/>
+      <c r="AO6" s="11"/>
+      <c r="AP6" s="11"/>
+      <c r="AQ6" s="11"/>
+      <c r="AR6" s="11"/>
+      <c r="AS6" s="11"/>
+      <c r="AT6" s="11"/>
+      <c r="AU6" s="11"/>
+      <c r="AV6" s="11"/>
+      <c r="AW6" s="11"/>
+      <c r="AX6" s="11"/>
+      <c r="AY6" s="11"/>
+      <c r="AZ6" s="11"/>
+      <c r="BA6" s="11"/>
+      <c r="BB6" s="11"/>
+    </row>
+    <row r="7" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A7" s="27">
+        <v>1</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="52">
+        <f>29</f>
+        <v>29</v>
+      </c>
+      <c r="D7" s="52"/>
+      <c r="E7" s="52"/>
+      <c r="F7" s="52"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="52"/>
+      <c r="I7" s="52">
+        <v>3</v>
+      </c>
+      <c r="J7" s="53"/>
+      <c r="K7" s="54">
+        <v>6</v>
+      </c>
+      <c r="L7" s="55"/>
+      <c r="M7" s="56"/>
+      <c r="N7" s="57"/>
+      <c r="O7" s="52">
+        <v>1</v>
+      </c>
+      <c r="P7" s="53"/>
+      <c r="Q7" s="53">
+        <v>1</v>
+      </c>
+      <c r="R7" s="54"/>
+      <c r="S7" s="55"/>
+      <c r="T7" s="58">
+        <f>H7+I7+J7+K7+N7+P7+R7</f>
+        <v>9</v>
+      </c>
+      <c r="U7" s="58">
+        <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
+        <v>753</v>
+      </c>
+      <c r="V7" s="58">
+        <f>U7/24</f>
+        <v>31.375</v>
+      </c>
+      <c r="W7" s="50"/>
+      <c r="AF7" s="12"/>
+      <c r="AG7" s="12"/>
+      <c r="AH7" s="12"/>
+      <c r="AI7" s="12"/>
+      <c r="AJ7" s="12"/>
+      <c r="AK7" s="12"/>
+      <c r="AL7" s="12"/>
+      <c r="AM7" s="12"/>
+      <c r="AN7" s="12"/>
+      <c r="AO7" s="12"/>
+      <c r="AP7" s="12"/>
+      <c r="AQ7" s="12"/>
+      <c r="AR7" s="12"/>
+      <c r="AS7" s="12"/>
+      <c r="AT7" s="12"/>
+      <c r="AU7" s="12"/>
+      <c r="AV7" s="12"/>
+      <c r="AW7" s="12"/>
+      <c r="AX7" s="12"/>
+      <c r="AY7" s="12"/>
+      <c r="AZ7" s="12"/>
+      <c r="BA7" s="12"/>
+      <c r="BB7" s="12"/>
+    </row>
+    <row r="8" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="27">
+        <f>A7+1</f>
+        <v>2</v>
+      </c>
+      <c r="B8" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="59">
+        <f>36+30</f>
+        <v>66</v>
+      </c>
+      <c r="D8" s="59"/>
+      <c r="E8" s="59"/>
+      <c r="F8" s="59"/>
+      <c r="G8" s="59"/>
+      <c r="H8" s="59"/>
+      <c r="I8" s="59"/>
+      <c r="J8" s="60"/>
+      <c r="K8" s="61"/>
+      <c r="L8" s="62"/>
+      <c r="M8" s="63">
+        <v>1</v>
+      </c>
+      <c r="N8" s="64"/>
+      <c r="O8" s="65">
+        <v>1</v>
+      </c>
+      <c r="P8" s="66">
+        <v>12</v>
+      </c>
+      <c r="Q8" s="66"/>
+      <c r="R8" s="67"/>
+      <c r="S8" s="62"/>
+      <c r="T8" s="68">
+        <f t="shared" ref="T8:T41" si="0">H8+I8+J8+K8+N8+P8+R8</f>
+        <v>12</v>
+      </c>
+      <c r="U8" s="69">
+        <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
+        <v>1644</v>
+      </c>
+      <c r="V8" s="69">
+        <f>U8/24</f>
+        <v>68.5</v>
+      </c>
+      <c r="W8" s="50"/>
+      <c r="AF8" s="12"/>
+      <c r="AG8" s="12"/>
+      <c r="AH8" s="12"/>
+      <c r="AI8" s="12"/>
+      <c r="AJ8" s="12"/>
+      <c r="AK8" s="12"/>
+      <c r="AL8" s="12"/>
+      <c r="AM8" s="12"/>
+      <c r="AN8" s="12"/>
+      <c r="AO8" s="12"/>
+      <c r="AP8" s="12"/>
+      <c r="AQ8" s="12"/>
+      <c r="AR8" s="12"/>
+      <c r="AS8" s="12"/>
+      <c r="AT8" s="12"/>
+      <c r="AU8" s="12"/>
+      <c r="AV8" s="12"/>
+      <c r="AW8" s="12"/>
+      <c r="AX8" s="12"/>
+      <c r="AY8" s="12"/>
+      <c r="AZ8" s="12"/>
+      <c r="BA8" s="12"/>
+      <c r="BB8" s="12"/>
+    </row>
+    <row r="9" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A9" s="27">
+        <f t="shared" ref="A9:A57" si="1">A8+1</f>
+        <v>3</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="70">
+        <f>20+30</f>
+        <v>50</v>
+      </c>
+      <c r="D9" s="70"/>
+      <c r="E9" s="70"/>
+      <c r="F9" s="70"/>
+      <c r="G9" s="70"/>
+      <c r="H9" s="70"/>
+      <c r="I9" s="70"/>
+      <c r="J9" s="71"/>
+      <c r="K9" s="72"/>
+      <c r="L9" s="55"/>
+      <c r="M9" s="73"/>
+      <c r="N9" s="74"/>
+      <c r="O9" s="70"/>
+      <c r="P9" s="71"/>
+      <c r="Q9" s="71">
+        <v>3</v>
+      </c>
+      <c r="R9" s="72"/>
+      <c r="S9" s="55"/>
+      <c r="T9" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U9" s="76">
+        <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
+        <v>1272</v>
+      </c>
+      <c r="V9" s="76">
+        <f t="shared" ref="V9:V11" si="3">U9/24</f>
+        <v>53</v>
+      </c>
+      <c r="W9" s="50"/>
+      <c r="AF9" s="12"/>
+      <c r="AG9" s="12"/>
+      <c r="AH9" s="12"/>
+      <c r="AI9" s="12"/>
+      <c r="AJ9" s="12"/>
+      <c r="AK9" s="12"/>
+      <c r="AL9" s="12"/>
+      <c r="AM9" s="12"/>
+      <c r="AN9" s="12"/>
+      <c r="AO9" s="12"/>
+      <c r="AP9" s="12"/>
+      <c r="AQ9" s="12"/>
+      <c r="AR9" s="12"/>
+      <c r="AS9" s="12"/>
+      <c r="AT9" s="12"/>
+      <c r="AU9" s="12"/>
+      <c r="AV9" s="12"/>
+      <c r="AW9" s="12"/>
+      <c r="AX9" s="12"/>
+      <c r="AY9" s="12"/>
+      <c r="AZ9" s="12"/>
+      <c r="BA9" s="12"/>
+      <c r="BB9" s="12"/>
+    </row>
+    <row r="10" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A10" s="27">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="70">
+        <v>6</v>
+      </c>
+      <c r="D10" s="70"/>
+      <c r="E10" s="70"/>
+      <c r="F10" s="70"/>
+      <c r="G10" s="70"/>
+      <c r="H10" s="70"/>
+      <c r="I10" s="70"/>
+      <c r="J10" s="71"/>
+      <c r="K10" s="72"/>
+      <c r="L10" s="55"/>
+      <c r="M10" s="73"/>
+      <c r="N10" s="74"/>
+      <c r="O10" s="70"/>
+      <c r="P10" s="71"/>
+      <c r="Q10" s="71">
+        <v>3</v>
+      </c>
+      <c r="R10" s="72"/>
+      <c r="S10" s="55"/>
+      <c r="T10" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U10" s="58">
+        <f t="shared" si="2"/>
+        <v>216</v>
+      </c>
+      <c r="V10" s="58">
+        <f t="shared" si="3"/>
+        <v>9</v>
+      </c>
+      <c r="W10" s="50"/>
+      <c r="AF10" s="12"/>
+      <c r="AG10" s="12"/>
+      <c r="AH10" s="12"/>
+      <c r="AI10" s="12"/>
+      <c r="AJ10" s="12"/>
+      <c r="AK10" s="12"/>
+      <c r="AL10" s="12"/>
+      <c r="AM10" s="12"/>
+      <c r="AN10" s="12"/>
+      <c r="AO10" s="12"/>
+      <c r="AP10" s="12"/>
+      <c r="AQ10" s="12"/>
+      <c r="AR10" s="12"/>
+      <c r="AS10" s="12"/>
+      <c r="AT10" s="12"/>
+      <c r="AU10" s="12"/>
+      <c r="AV10" s="12"/>
+      <c r="AW10" s="12"/>
+      <c r="AX10" s="12"/>
+      <c r="AY10" s="12"/>
+      <c r="AZ10" s="12"/>
+      <c r="BA10" s="12"/>
+      <c r="BB10" s="12"/>
+    </row>
+    <row r="11" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A11" s="27">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="70"/>
+      <c r="D11" s="70"/>
+      <c r="E11" s="70"/>
+      <c r="F11" s="70"/>
+      <c r="G11" s="70"/>
+      <c r="H11" s="70"/>
+      <c r="I11" s="70"/>
+      <c r="J11" s="71"/>
+      <c r="K11" s="72">
+        <v>2</v>
+      </c>
+      <c r="L11" s="55"/>
+      <c r="M11" s="73"/>
+      <c r="N11" s="74"/>
+      <c r="O11" s="70"/>
+      <c r="P11" s="71"/>
+      <c r="Q11" s="71"/>
+      <c r="R11" s="72"/>
+      <c r="S11" s="55"/>
+      <c r="T11" s="58">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="U11" s="58">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="V11" s="58">
+        <f t="shared" si="3"/>
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="AF11" s="12"/>
+      <c r="AG11" s="12"/>
+      <c r="AH11" s="12"/>
+      <c r="AI11" s="12"/>
+      <c r="AJ11" s="12"/>
+      <c r="AK11" s="12"/>
+      <c r="AL11" s="12"/>
+      <c r="AM11" s="12"/>
+      <c r="AN11" s="12"/>
+      <c r="AO11" s="12"/>
+      <c r="AP11" s="12"/>
+      <c r="AQ11" s="12"/>
+      <c r="AR11" s="12"/>
+      <c r="AS11" s="12"/>
+      <c r="AT11" s="12"/>
+      <c r="AU11" s="12"/>
+      <c r="AV11" s="12"/>
+      <c r="AW11" s="12"/>
+      <c r="AX11" s="12"/>
+      <c r="AY11" s="12"/>
+      <c r="AZ11" s="12"/>
+      <c r="BA11" s="12"/>
+      <c r="BB11" s="12"/>
+    </row>
+    <row r="12" spans="1:54" s="13" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="27">
+        <v>7</v>
+      </c>
+      <c r="B12" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="59">
+        <f>1224+432+37+1080+29+53</f>
+        <v>2855</v>
+      </c>
+      <c r="D12" s="59"/>
+      <c r="E12" s="59"/>
+      <c r="F12" s="59"/>
+      <c r="G12" s="59"/>
+      <c r="H12" s="59"/>
+      <c r="I12" s="59"/>
+      <c r="J12" s="60"/>
+      <c r="K12" s="61"/>
+      <c r="L12" s="62"/>
+      <c r="M12" s="63">
+        <v>9</v>
+      </c>
+      <c r="N12" s="64">
+        <v>11</v>
+      </c>
+      <c r="O12" s="65">
+        <v>13</v>
+      </c>
+      <c r="P12" s="66">
+        <v>12</v>
+      </c>
+      <c r="Q12" s="66">
+        <v>23</v>
+      </c>
+      <c r="R12" s="67"/>
+      <c r="S12" s="62"/>
+      <c r="T12" s="69">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="U12" s="69">
+        <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
+        <v>69623</v>
+      </c>
+      <c r="V12" s="69">
+        <f>U12/24</f>
+        <v>2900.9583333333335</v>
+      </c>
+      <c r="W12" s="9"/>
+      <c r="X12" s="9"/>
+      <c r="Y12" s="9"/>
+      <c r="Z12" s="9"/>
+      <c r="AA12" s="9"/>
+      <c r="AB12" s="9"/>
+      <c r="AC12" s="9"/>
+      <c r="AD12" s="9"/>
+      <c r="AE12" s="9"/>
+      <c r="AF12" s="12"/>
+      <c r="AG12" s="12"/>
+      <c r="AH12" s="12"/>
+      <c r="AI12" s="12"/>
+      <c r="AJ12" s="12"/>
+      <c r="AK12" s="12"/>
+      <c r="AL12" s="12"/>
+      <c r="AM12" s="12"/>
+      <c r="AN12" s="12"/>
+      <c r="AO12" s="12"/>
+      <c r="AP12" s="12"/>
+      <c r="AQ12" s="12"/>
+      <c r="AR12" s="12"/>
+      <c r="AS12" s="12"/>
+      <c r="AT12" s="12"/>
+      <c r="AU12" s="12"/>
+      <c r="AV12" s="12"/>
+      <c r="AW12" s="12"/>
+      <c r="AX12" s="12"/>
+      <c r="AY12" s="12"/>
+      <c r="AZ12" s="12"/>
+      <c r="BA12" s="12"/>
+      <c r="BB12" s="12"/>
+    </row>
+    <row r="13" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A13" s="27">
+        <v>11</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="70">
+        <v>2</v>
+      </c>
+      <c r="D13" s="70"/>
+      <c r="E13" s="70"/>
+      <c r="F13" s="70"/>
+      <c r="G13" s="70"/>
+      <c r="H13" s="70">
+        <v>16</v>
+      </c>
+      <c r="I13" s="70"/>
+      <c r="J13" s="71"/>
+      <c r="K13" s="72"/>
+      <c r="L13" s="55"/>
+      <c r="M13" s="73"/>
+      <c r="N13" s="74"/>
+      <c r="O13" s="70"/>
+      <c r="P13" s="71"/>
+      <c r="Q13" s="71"/>
+      <c r="R13" s="72"/>
+      <c r="S13" s="55"/>
+      <c r="T13" s="76">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="U13" s="76">
+        <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
+        <v>64</v>
+      </c>
+      <c r="V13" s="76">
+        <f>U13/24</f>
+        <v>2.6666666666666665</v>
+      </c>
+      <c r="AF13" s="12"/>
+      <c r="AG13" s="12"/>
+      <c r="AH13" s="12"/>
+      <c r="AI13" s="12"/>
+      <c r="AJ13" s="12"/>
+      <c r="AK13" s="12"/>
+      <c r="AL13" s="12"/>
+      <c r="AM13" s="12"/>
+      <c r="AN13" s="12"/>
+      <c r="AO13" s="12"/>
+      <c r="AP13" s="12"/>
+      <c r="AQ13" s="12"/>
+      <c r="AR13" s="12"/>
+      <c r="AS13" s="12"/>
+      <c r="AT13" s="12"/>
+      <c r="AU13" s="12"/>
+      <c r="AV13" s="12"/>
+      <c r="AW13" s="12"/>
+      <c r="AX13" s="12"/>
+      <c r="AY13" s="12"/>
+      <c r="AZ13" s="12"/>
+      <c r="BA13" s="12"/>
+      <c r="BB13" s="12"/>
+    </row>
+    <row r="14" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A14" s="27">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="70">
+        <v>2</v>
+      </c>
+      <c r="D14" s="70"/>
+      <c r="E14" s="70"/>
+      <c r="F14" s="70"/>
+      <c r="G14" s="70"/>
+      <c r="H14" s="70"/>
+      <c r="I14" s="70"/>
+      <c r="J14" s="71"/>
+      <c r="K14" s="72"/>
+      <c r="L14" s="55"/>
+      <c r="M14" s="73"/>
+      <c r="N14" s="74"/>
+      <c r="O14" s="70"/>
+      <c r="P14" s="71"/>
+      <c r="Q14" s="71"/>
+      <c r="R14" s="72"/>
+      <c r="S14" s="55"/>
+      <c r="T14" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U14" s="75">
+        <f t="shared" ref="U14:U36" si="4">C14*24+M14*24+O14*24+Q14*24+T14</f>
+        <v>48</v>
+      </c>
+      <c r="V14" s="75">
+        <f t="shared" ref="V14:V36" si="5">U14/24</f>
+        <v>2</v>
+      </c>
+      <c r="AF14" s="12"/>
+      <c r="AG14" s="12"/>
+      <c r="AH14" s="12"/>
+      <c r="AI14" s="12"/>
+      <c r="AJ14" s="12"/>
+      <c r="AK14" s="12"/>
+      <c r="AL14" s="12"/>
+      <c r="AM14" s="12"/>
+      <c r="AN14" s="12"/>
+      <c r="AO14" s="12"/>
+      <c r="AP14" s="12"/>
+      <c r="AQ14" s="12"/>
+      <c r="AR14" s="12"/>
+      <c r="AS14" s="12"/>
+      <c r="AT14" s="12"/>
+      <c r="AU14" s="12"/>
+      <c r="AV14" s="12"/>
+      <c r="AW14" s="12"/>
+      <c r="AX14" s="12"/>
+      <c r="AY14" s="12"/>
+      <c r="AZ14" s="12"/>
+      <c r="BA14" s="12"/>
+      <c r="BB14" s="12"/>
+    </row>
+    <row r="15" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A15" s="27">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="70"/>
+      <c r="D15" s="70"/>
+      <c r="E15" s="70"/>
+      <c r="F15" s="70"/>
+      <c r="G15" s="70"/>
+      <c r="H15" s="70"/>
+      <c r="I15" s="70"/>
+      <c r="J15" s="71"/>
+      <c r="K15" s="72"/>
+      <c r="L15" s="55"/>
+      <c r="M15" s="73"/>
+      <c r="N15" s="74"/>
+      <c r="O15" s="70"/>
+      <c r="P15" s="71"/>
+      <c r="Q15" s="71"/>
+      <c r="R15" s="72"/>
+      <c r="S15" s="55"/>
+      <c r="T15" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U15" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF15" s="12"/>
+      <c r="AG15" s="12"/>
+      <c r="AH15" s="12"/>
+      <c r="AI15" s="12"/>
+      <c r="AJ15" s="12"/>
+      <c r="AK15" s="12"/>
+      <c r="AL15" s="12"/>
+      <c r="AM15" s="12"/>
+      <c r="AN15" s="12"/>
+      <c r="AO15" s="12"/>
+      <c r="AP15" s="12"/>
+      <c r="AQ15" s="12"/>
+      <c r="AR15" s="12"/>
+      <c r="AS15" s="12"/>
+      <c r="AT15" s="12"/>
+      <c r="AU15" s="12"/>
+      <c r="AV15" s="12"/>
+      <c r="AW15" s="12"/>
+      <c r="AX15" s="12"/>
+      <c r="AY15" s="12"/>
+      <c r="AZ15" s="12"/>
+      <c r="BA15" s="12"/>
+      <c r="BB15" s="12"/>
+    </row>
+    <row r="16" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A16" s="27">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="70"/>
+      <c r="D16" s="70"/>
+      <c r="E16" s="70"/>
+      <c r="F16" s="70"/>
+      <c r="G16" s="70"/>
+      <c r="H16" s="70"/>
+      <c r="I16" s="70"/>
+      <c r="J16" s="71"/>
+      <c r="K16" s="72"/>
+      <c r="L16" s="55"/>
+      <c r="M16" s="73"/>
+      <c r="N16" s="74"/>
+      <c r="O16" s="70"/>
+      <c r="P16" s="71"/>
+      <c r="Q16" s="71"/>
+      <c r="R16" s="72"/>
+      <c r="S16" s="55"/>
+      <c r="T16" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U16" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF16" s="12"/>
+      <c r="AG16" s="12"/>
+      <c r="AH16" s="12"/>
+      <c r="AI16" s="12"/>
+      <c r="AJ16" s="12"/>
+      <c r="AK16" s="12"/>
+      <c r="AL16" s="12"/>
+      <c r="AM16" s="12"/>
+      <c r="AN16" s="12"/>
+      <c r="AO16" s="12"/>
+      <c r="AP16" s="12"/>
+      <c r="AQ16" s="12"/>
+      <c r="AR16" s="12"/>
+      <c r="AS16" s="12"/>
+      <c r="AT16" s="12"/>
+      <c r="AU16" s="12"/>
+      <c r="AV16" s="12"/>
+      <c r="AW16" s="12"/>
+      <c r="AX16" s="12"/>
+      <c r="AY16" s="12"/>
+      <c r="AZ16" s="12"/>
+      <c r="BA16" s="12"/>
+      <c r="BB16" s="12"/>
+    </row>
+    <row r="17" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A17" s="27">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="70"/>
+      <c r="D17" s="70"/>
+      <c r="E17" s="70"/>
+      <c r="F17" s="70"/>
+      <c r="G17" s="70"/>
+      <c r="H17" s="70">
+        <f>3*24</f>
+        <v>72</v>
+      </c>
+      <c r="I17" s="70"/>
+      <c r="J17" s="71"/>
+      <c r="K17" s="72"/>
+      <c r="L17" s="55"/>
+      <c r="M17" s="73"/>
+      <c r="N17" s="74"/>
+      <c r="O17" s="70"/>
+      <c r="P17" s="71"/>
+      <c r="Q17" s="71"/>
+      <c r="R17" s="72"/>
+      <c r="S17" s="55"/>
+      <c r="T17" s="58">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="U17" s="75">
+        <f t="shared" si="4"/>
+        <v>72</v>
+      </c>
+      <c r="V17" s="75">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="AF17" s="12"/>
+      <c r="AG17" s="12"/>
+      <c r="AH17" s="12"/>
+      <c r="AI17" s="12"/>
+      <c r="AJ17" s="12"/>
+      <c r="AK17" s="12"/>
+      <c r="AL17" s="12"/>
+      <c r="AM17" s="12"/>
+      <c r="AN17" s="12"/>
+      <c r="AO17" s="12"/>
+      <c r="AP17" s="12"/>
+      <c r="AQ17" s="12"/>
+      <c r="AR17" s="12"/>
+      <c r="AS17" s="12"/>
+      <c r="AT17" s="12"/>
+      <c r="AU17" s="12"/>
+      <c r="AV17" s="12"/>
+      <c r="AW17" s="12"/>
+      <c r="AX17" s="12"/>
+      <c r="AY17" s="12"/>
+      <c r="AZ17" s="12"/>
+      <c r="BA17" s="12"/>
+      <c r="BB17" s="12"/>
+    </row>
+    <row r="18" spans="1:54" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="27">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="70"/>
+      <c r="D18" s="70"/>
+      <c r="E18" s="70"/>
+      <c r="F18" s="70"/>
+      <c r="G18" s="70"/>
+      <c r="H18" s="70"/>
+      <c r="I18" s="70"/>
+      <c r="J18" s="71"/>
+      <c r="K18" s="72"/>
+      <c r="L18" s="55"/>
+      <c r="M18" s="73"/>
+      <c r="N18" s="74"/>
+      <c r="O18" s="70"/>
+      <c r="P18" s="71"/>
+      <c r="Q18" s="71"/>
+      <c r="R18" s="72"/>
+      <c r="S18" s="55"/>
+      <c r="T18" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U18" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF18" s="12"/>
+      <c r="AG18" s="12"/>
+      <c r="AH18" s="12"/>
+      <c r="AI18" s="12"/>
+      <c r="AJ18" s="12"/>
+      <c r="AK18" s="12"/>
+      <c r="AL18" s="12"/>
+      <c r="AM18" s="12"/>
+      <c r="AN18" s="12"/>
+      <c r="AO18" s="12"/>
+      <c r="AP18" s="12"/>
+      <c r="AQ18" s="12"/>
+      <c r="AR18" s="12"/>
+      <c r="AS18" s="12"/>
+      <c r="AT18" s="12"/>
+      <c r="AU18" s="12"/>
+      <c r="AV18" s="12"/>
+      <c r="AW18" s="12"/>
+      <c r="AX18" s="12"/>
+      <c r="AY18" s="12"/>
+      <c r="AZ18" s="12"/>
+      <c r="BA18" s="12"/>
+      <c r="BB18" s="12"/>
+    </row>
+    <row r="19" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A19" s="27">
+        <v>16</v>
+      </c>
+      <c r="B19" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="70">
+        <v>1</v>
+      </c>
+      <c r="D19" s="70"/>
+      <c r="E19" s="70"/>
+      <c r="F19" s="70"/>
+      <c r="G19" s="70"/>
+      <c r="H19" s="70">
+        <f>20+24</f>
+        <v>44</v>
+      </c>
+      <c r="I19" s="70"/>
+      <c r="J19" s="71"/>
+      <c r="K19" s="72"/>
+      <c r="L19" s="55"/>
+      <c r="M19" s="73"/>
+      <c r="N19" s="74"/>
+      <c r="O19" s="70"/>
+      <c r="P19" s="71"/>
+      <c r="Q19" s="71"/>
+      <c r="R19" s="72"/>
+      <c r="S19" s="55"/>
+      <c r="T19" s="58">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="U19" s="75">
+        <f t="shared" si="4"/>
+        <v>68</v>
+      </c>
+      <c r="V19" s="75">
+        <f t="shared" si="5"/>
+        <v>2.8333333333333335</v>
+      </c>
+      <c r="AF19" s="12"/>
+      <c r="AG19" s="12"/>
+      <c r="AH19" s="12"/>
+      <c r="AI19" s="12"/>
+      <c r="AJ19" s="12"/>
+      <c r="AK19" s="12"/>
+      <c r="AL19" s="12"/>
+      <c r="AM19" s="12"/>
+      <c r="AN19" s="12"/>
+      <c r="AO19" s="12"/>
+      <c r="AP19" s="12"/>
+      <c r="AQ19" s="12"/>
+      <c r="AR19" s="12"/>
+      <c r="AS19" s="12"/>
+      <c r="AT19" s="12"/>
+      <c r="AU19" s="12"/>
+      <c r="AV19" s="12"/>
+      <c r="AW19" s="12"/>
+      <c r="AX19" s="12"/>
+      <c r="AY19" s="12"/>
+      <c r="AZ19" s="12"/>
+      <c r="BA19" s="12"/>
+      <c r="BB19" s="12"/>
+    </row>
+    <row r="20" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A20" s="27">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="B20" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="70">
+        <v>5</v>
+      </c>
+      <c r="D20" s="70"/>
+      <c r="E20" s="70"/>
+      <c r="F20" s="70"/>
+      <c r="G20" s="70"/>
+      <c r="H20" s="70"/>
+      <c r="I20" s="70"/>
+      <c r="J20" s="71"/>
+      <c r="K20" s="72"/>
+      <c r="L20" s="55"/>
+      <c r="M20" s="73"/>
+      <c r="N20" s="74"/>
+      <c r="O20" s="70"/>
+      <c r="P20" s="71"/>
+      <c r="Q20" s="71"/>
+      <c r="R20" s="72"/>
+      <c r="S20" s="55"/>
+      <c r="T20" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U20" s="75">
+        <f t="shared" si="4"/>
+        <v>120</v>
+      </c>
+      <c r="V20" s="75">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="AF20" s="12"/>
+      <c r="AG20" s="12"/>
+      <c r="AH20" s="12"/>
+      <c r="AI20" s="12"/>
+      <c r="AJ20" s="12"/>
+      <c r="AK20" s="12"/>
+      <c r="AL20" s="12"/>
+      <c r="AM20" s="12"/>
+      <c r="AN20" s="12"/>
+      <c r="AO20" s="12"/>
+      <c r="AP20" s="12"/>
+      <c r="AQ20" s="12"/>
+      <c r="AR20" s="12"/>
+      <c r="AS20" s="12"/>
+      <c r="AT20" s="12"/>
+      <c r="AU20" s="12"/>
+      <c r="AV20" s="12"/>
+      <c r="AW20" s="12"/>
+      <c r="AX20" s="12"/>
+      <c r="AY20" s="12"/>
+      <c r="AZ20" s="12"/>
+      <c r="BA20" s="12"/>
+      <c r="BB20" s="12"/>
+    </row>
+    <row r="21" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A21" s="27">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="B21" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="70"/>
+      <c r="D21" s="70"/>
+      <c r="E21" s="70"/>
+      <c r="F21" s="70"/>
+      <c r="G21" s="70"/>
+      <c r="H21" s="70">
+        <f>2*24</f>
+        <v>48</v>
+      </c>
+      <c r="I21" s="70"/>
+      <c r="J21" s="71"/>
+      <c r="K21" s="72"/>
+      <c r="L21" s="55"/>
+      <c r="M21" s="73"/>
+      <c r="N21" s="74"/>
+      <c r="O21" s="70"/>
+      <c r="P21" s="71"/>
+      <c r="Q21" s="71"/>
+      <c r="R21" s="72"/>
+      <c r="S21" s="55"/>
+      <c r="T21" s="58">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+      <c r="U21" s="75">
+        <f t="shared" si="4"/>
+        <v>48</v>
+      </c>
+      <c r="V21" s="75">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="AF21" s="12"/>
+      <c r="AG21" s="12"/>
+      <c r="AH21" s="12"/>
+      <c r="AI21" s="12"/>
+      <c r="AJ21" s="12"/>
+      <c r="AK21" s="12"/>
+      <c r="AL21" s="12"/>
+      <c r="AM21" s="12"/>
+      <c r="AN21" s="12"/>
+      <c r="AO21" s="12"/>
+      <c r="AP21" s="12"/>
+      <c r="AQ21" s="12"/>
+      <c r="AR21" s="12"/>
+      <c r="AS21" s="12"/>
+      <c r="AT21" s="12"/>
+      <c r="AU21" s="12"/>
+      <c r="AV21" s="12"/>
+      <c r="AW21" s="12"/>
+      <c r="AX21" s="12"/>
+      <c r="AY21" s="12"/>
+      <c r="AZ21" s="12"/>
+      <c r="BA21" s="12"/>
+      <c r="BB21" s="12"/>
+    </row>
+    <row r="22" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="27">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="B22" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="70">
+        <v>1</v>
+      </c>
+      <c r="D22" s="70"/>
+      <c r="E22" s="70"/>
+      <c r="F22" s="70"/>
+      <c r="G22" s="70"/>
+      <c r="H22" s="70"/>
+      <c r="I22" s="70">
+        <v>20</v>
+      </c>
+      <c r="J22" s="71"/>
+      <c r="K22" s="72"/>
+      <c r="L22" s="55"/>
+      <c r="M22" s="73"/>
+      <c r="N22" s="74"/>
+      <c r="O22" s="70"/>
+      <c r="P22" s="71"/>
+      <c r="Q22" s="71"/>
+      <c r="R22" s="72"/>
+      <c r="S22" s="55"/>
+      <c r="T22" s="58">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="U22" s="75">
+        <f t="shared" si="4"/>
+        <v>44</v>
+      </c>
+      <c r="V22" s="75">
+        <f t="shared" si="5"/>
+        <v>1.8333333333333333</v>
+      </c>
+      <c r="W22" s="9"/>
+      <c r="X22" s="9"/>
+      <c r="Y22" s="9"/>
+      <c r="Z22" s="9"/>
+      <c r="AA22" s="9"/>
+      <c r="AB22" s="9"/>
+      <c r="AC22" s="9"/>
+      <c r="AD22" s="9"/>
+      <c r="AE22" s="9"/>
+      <c r="AF22" s="12"/>
+      <c r="AG22" s="12"/>
+      <c r="AH22" s="12"/>
+      <c r="AI22" s="12"/>
+      <c r="AJ22" s="12"/>
+      <c r="AK22" s="12"/>
+      <c r="AL22" s="12"/>
+      <c r="AM22" s="12"/>
+      <c r="AN22" s="12"/>
+      <c r="AO22" s="12"/>
+      <c r="AP22" s="12"/>
+      <c r="AQ22" s="12"/>
+      <c r="AR22" s="12"/>
+      <c r="AS22" s="12"/>
+      <c r="AT22" s="12"/>
+      <c r="AU22" s="12"/>
+      <c r="AV22" s="12"/>
+      <c r="AW22" s="12"/>
+      <c r="AX22" s="12"/>
+      <c r="AY22" s="12"/>
+      <c r="AZ22" s="12"/>
+      <c r="BA22" s="12"/>
+      <c r="BB22" s="12"/>
+    </row>
+    <row r="23" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="27">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="B23" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="70"/>
+      <c r="D23" s="70"/>
+      <c r="E23" s="70"/>
+      <c r="F23" s="70"/>
+      <c r="G23" s="70"/>
+      <c r="H23" s="70">
+        <f>37*24+19</f>
+        <v>907</v>
+      </c>
+      <c r="I23" s="70"/>
+      <c r="J23" s="71"/>
+      <c r="K23" s="72"/>
+      <c r="L23" s="55"/>
+      <c r="M23" s="73"/>
+      <c r="N23" s="74"/>
+      <c r="O23" s="70"/>
+      <c r="P23" s="71"/>
+      <c r="Q23" s="71"/>
+      <c r="R23" s="72"/>
+      <c r="S23" s="55"/>
+      <c r="T23" s="58">
+        <f t="shared" si="0"/>
+        <v>907</v>
+      </c>
+      <c r="U23" s="75">
+        <f t="shared" si="4"/>
+        <v>907</v>
+      </c>
+      <c r="V23" s="75">
+        <f t="shared" si="5"/>
+        <v>37.791666666666664</v>
+      </c>
+      <c r="W23" s="9"/>
+      <c r="X23" s="9"/>
+      <c r="Y23" s="9"/>
+      <c r="Z23" s="9"/>
+      <c r="AA23" s="9"/>
+      <c r="AB23" s="9"/>
+      <c r="AC23" s="9"/>
+      <c r="AD23" s="9"/>
+      <c r="AE23" s="9"/>
+      <c r="AF23" s="12"/>
+      <c r="AG23" s="12"/>
+      <c r="AH23" s="12"/>
+      <c r="AI23" s="12"/>
+      <c r="AJ23" s="12"/>
+      <c r="AK23" s="12"/>
+      <c r="AL23" s="12"/>
+      <c r="AM23" s="12"/>
+      <c r="AN23" s="12"/>
+      <c r="AO23" s="12"/>
+      <c r="AP23" s="12"/>
+      <c r="AQ23" s="12"/>
+      <c r="AR23" s="12"/>
+      <c r="AS23" s="12"/>
+      <c r="AT23" s="12"/>
+      <c r="AU23" s="12"/>
+      <c r="AV23" s="12"/>
+      <c r="AW23" s="12"/>
+      <c r="AX23" s="12"/>
+      <c r="AY23" s="12"/>
+      <c r="AZ23" s="12"/>
+      <c r="BA23" s="12"/>
+      <c r="BB23" s="12"/>
+    </row>
+    <row r="24" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A24" s="27">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="B24" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" s="70">
+        <v>2</v>
+      </c>
+      <c r="D24" s="70"/>
+      <c r="E24" s="70"/>
+      <c r="F24" s="70"/>
+      <c r="G24" s="70"/>
+      <c r="H24" s="70">
+        <f>3*24</f>
+        <v>72</v>
+      </c>
+      <c r="I24" s="70"/>
+      <c r="J24" s="71"/>
+      <c r="K24" s="72"/>
+      <c r="L24" s="55"/>
+      <c r="M24" s="73"/>
+      <c r="N24" s="74"/>
+      <c r="O24" s="70"/>
+      <c r="P24" s="71"/>
+      <c r="Q24" s="71"/>
+      <c r="R24" s="72"/>
+      <c r="S24" s="55"/>
+      <c r="T24" s="58">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="U24" s="75">
+        <f t="shared" si="4"/>
+        <v>120</v>
+      </c>
+      <c r="V24" s="75">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="AF24" s="12"/>
+      <c r="AG24" s="12"/>
+      <c r="AH24" s="12"/>
+      <c r="AI24" s="12"/>
+      <c r="AJ24" s="12"/>
+      <c r="AK24" s="12"/>
+      <c r="AL24" s="12"/>
+      <c r="AM24" s="12"/>
+      <c r="AN24" s="12"/>
+      <c r="AO24" s="12"/>
+      <c r="AP24" s="12"/>
+      <c r="AQ24" s="12"/>
+      <c r="AR24" s="12"/>
+      <c r="AS24" s="12"/>
+      <c r="AT24" s="12"/>
+      <c r="AU24" s="12"/>
+      <c r="AV24" s="12"/>
+      <c r="AW24" s="12"/>
+      <c r="AX24" s="12"/>
+      <c r="AY24" s="12"/>
+      <c r="AZ24" s="12"/>
+      <c r="BA24" s="12"/>
+      <c r="BB24" s="12"/>
+    </row>
+    <row r="25" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A25" s="27">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="70">
+        <v>126</v>
+      </c>
+      <c r="D25" s="70"/>
+      <c r="E25" s="70"/>
+      <c r="F25" s="70"/>
+      <c r="G25" s="70"/>
+      <c r="H25" s="70"/>
+      <c r="I25" s="70">
+        <v>1</v>
+      </c>
+      <c r="J25" s="71"/>
+      <c r="K25" s="72"/>
+      <c r="L25" s="55"/>
+      <c r="M25" s="73">
+        <v>1</v>
+      </c>
+      <c r="N25" s="74"/>
+      <c r="O25" s="70"/>
+      <c r="P25" s="71"/>
+      <c r="Q25" s="71">
+        <v>2</v>
+      </c>
+      <c r="R25" s="72"/>
+      <c r="S25" s="55"/>
+      <c r="T25" s="58">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="U25" s="75">
+        <f t="shared" si="4"/>
+        <v>3097</v>
+      </c>
+      <c r="V25" s="75">
+        <f t="shared" si="5"/>
+        <v>129.04166666666666</v>
+      </c>
+      <c r="AY25" s="14" t="e">
+        <f>#REF!-AY24</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="27">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="B26" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="70">
+        <v>2</v>
+      </c>
+      <c r="D26" s="70"/>
+      <c r="E26" s="70"/>
+      <c r="F26" s="70"/>
+      <c r="G26" s="70"/>
+      <c r="H26" s="70"/>
+      <c r="I26" s="70"/>
+      <c r="J26" s="71"/>
+      <c r="K26" s="72"/>
+      <c r="L26" s="55"/>
+      <c r="M26" s="73"/>
+      <c r="N26" s="74"/>
+      <c r="O26" s="70"/>
+      <c r="P26" s="71"/>
+      <c r="Q26" s="71">
+        <v>1</v>
+      </c>
+      <c r="R26" s="72"/>
+      <c r="S26" s="55"/>
+      <c r="T26" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U26" s="75">
+        <f t="shared" si="4"/>
+        <v>72</v>
+      </c>
+      <c r="V26" s="75">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="W26" s="9"/>
+      <c r="X26" s="9"/>
+      <c r="Y26" s="9"/>
+      <c r="Z26" s="9"/>
+      <c r="AA26" s="9"/>
+      <c r="AB26" s="9"/>
+      <c r="AC26" s="9"/>
+      <c r="AD26" s="9"/>
+      <c r="AE26" s="9"/>
+    </row>
+    <row r="27" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="27">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="B27" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27" s="70">
+        <v>1</v>
+      </c>
+      <c r="D27" s="70"/>
+      <c r="E27" s="70"/>
+      <c r="F27" s="70"/>
+      <c r="G27" s="70"/>
+      <c r="H27" s="70"/>
+      <c r="I27" s="70"/>
+      <c r="J27" s="71"/>
+      <c r="K27" s="72"/>
+      <c r="L27" s="55"/>
+      <c r="M27" s="73"/>
+      <c r="N27" s="74"/>
+      <c r="O27" s="70"/>
+      <c r="P27" s="71"/>
+      <c r="Q27" s="71"/>
+      <c r="R27" s="72"/>
+      <c r="S27" s="55"/>
+      <c r="T27" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U27" s="75">
+        <f t="shared" si="4"/>
+        <v>24</v>
+      </c>
+      <c r="V27" s="75">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="W27" s="9"/>
+      <c r="X27" s="9"/>
+      <c r="Y27" s="9"/>
+      <c r="Z27" s="9"/>
+      <c r="AA27" s="9"/>
+      <c r="AB27" s="9"/>
+      <c r="AC27" s="9"/>
+      <c r="AD27" s="9"/>
+      <c r="AE27" s="9"/>
+    </row>
+    <row r="28" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="27">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="B28" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="70">
+        <f>252+16</f>
+        <v>268</v>
+      </c>
+      <c r="D28" s="70"/>
+      <c r="E28" s="70"/>
+      <c r="F28" s="70"/>
+      <c r="G28" s="70"/>
+      <c r="H28" s="70"/>
+      <c r="I28" s="70"/>
+      <c r="J28" s="71"/>
+      <c r="K28" s="72"/>
+      <c r="L28" s="55"/>
+      <c r="M28" s="73">
+        <v>2</v>
+      </c>
+      <c r="N28" s="74"/>
+      <c r="O28" s="70">
+        <v>2</v>
+      </c>
+      <c r="P28" s="71"/>
+      <c r="Q28" s="71">
+        <v>4</v>
+      </c>
+      <c r="R28" s="72"/>
+      <c r="S28" s="55"/>
+      <c r="T28" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U28" s="75">
+        <f t="shared" si="4"/>
+        <v>6624</v>
+      </c>
+      <c r="V28" s="75">
+        <f t="shared" si="5"/>
+        <v>276</v>
+      </c>
+      <c r="W28" s="9"/>
+      <c r="X28" s="9"/>
+      <c r="Y28" s="9"/>
+      <c r="Z28" s="9"/>
+      <c r="AA28" s="9"/>
+      <c r="AB28" s="9"/>
+      <c r="AC28" s="9"/>
+      <c r="AD28" s="9"/>
+      <c r="AE28" s="9"/>
+    </row>
+    <row r="29" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A29" s="27">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="B29" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" s="70"/>
+      <c r="D29" s="70"/>
+      <c r="E29" s="70"/>
+      <c r="F29" s="70"/>
+      <c r="G29" s="70"/>
+      <c r="H29" s="70"/>
+      <c r="I29" s="70">
+        <v>5</v>
+      </c>
+      <c r="J29" s="71"/>
+      <c r="K29" s="72"/>
+      <c r="L29" s="55"/>
+      <c r="M29" s="73"/>
+      <c r="N29" s="74"/>
+      <c r="O29" s="70"/>
+      <c r="P29" s="71"/>
+      <c r="Q29" s="71"/>
+      <c r="R29" s="72"/>
+      <c r="S29" s="55"/>
+      <c r="T29" s="58">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="U29" s="75">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="V29" s="75">
+        <f t="shared" si="5"/>
+        <v>0.20833333333333334</v>
+      </c>
+    </row>
+    <row r="30" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A30" s="27">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="B30" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="70"/>
+      <c r="D30" s="70"/>
+      <c r="E30" s="70"/>
+      <c r="F30" s="70"/>
+      <c r="G30" s="70"/>
+      <c r="H30" s="70"/>
+      <c r="I30" s="70"/>
+      <c r="J30" s="71"/>
+      <c r="K30" s="72"/>
+      <c r="L30" s="55"/>
+      <c r="M30" s="73"/>
+      <c r="N30" s="74"/>
+      <c r="O30" s="70"/>
+      <c r="P30" s="71"/>
+      <c r="Q30" s="71"/>
+      <c r="R30" s="72"/>
+      <c r="S30" s="55"/>
+      <c r="T30" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U30" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V30" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A31" s="27">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="B31" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" s="70"/>
+      <c r="D31" s="70"/>
+      <c r="E31" s="70"/>
+      <c r="F31" s="70"/>
+      <c r="G31" s="70"/>
+      <c r="H31" s="70"/>
+      <c r="I31" s="70"/>
+      <c r="J31" s="71"/>
+      <c r="K31" s="72"/>
+      <c r="L31" s="55"/>
+      <c r="M31" s="73"/>
+      <c r="N31" s="74"/>
+      <c r="O31" s="70"/>
+      <c r="P31" s="71"/>
+      <c r="Q31" s="71"/>
+      <c r="R31" s="72"/>
+      <c r="S31" s="55"/>
+      <c r="T31" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U31" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V31" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A32" s="27">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="B32" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" s="70"/>
+      <c r="D32" s="70"/>
+      <c r="E32" s="70"/>
+      <c r="F32" s="70"/>
+      <c r="G32" s="70"/>
+      <c r="H32" s="70"/>
+      <c r="I32" s="70"/>
+      <c r="J32" s="71"/>
+      <c r="K32" s="72"/>
+      <c r="L32" s="55"/>
+      <c r="M32" s="73"/>
+      <c r="N32" s="74"/>
+      <c r="O32" s="70"/>
+      <c r="P32" s="71"/>
+      <c r="Q32" s="71"/>
+      <c r="R32" s="72"/>
+      <c r="S32" s="55"/>
+      <c r="T32" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U32" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V32" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A33" s="27">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="B33" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" s="70"/>
+      <c r="D33" s="70"/>
+      <c r="E33" s="70"/>
+      <c r="F33" s="70"/>
+      <c r="G33" s="70"/>
+      <c r="H33" s="70"/>
+      <c r="I33" s="70"/>
+      <c r="J33" s="71"/>
+      <c r="K33" s="72"/>
+      <c r="L33" s="55"/>
+      <c r="M33" s="73"/>
+      <c r="N33" s="74"/>
+      <c r="O33" s="70"/>
+      <c r="P33" s="71"/>
+      <c r="Q33" s="71"/>
+      <c r="R33" s="72"/>
+      <c r="S33" s="55"/>
+      <c r="T33" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U33" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V33" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A34" s="27">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="B34" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" s="70">
+        <f>72+48+144</f>
+        <v>264</v>
+      </c>
+      <c r="D34" s="70"/>
+      <c r="E34" s="70"/>
+      <c r="F34" s="70"/>
+      <c r="G34" s="70"/>
+      <c r="H34" s="70"/>
+      <c r="I34" s="70">
+        <v>1</v>
+      </c>
+      <c r="J34" s="71"/>
+      <c r="K34" s="72">
+        <v>1</v>
+      </c>
+      <c r="L34" s="55"/>
+      <c r="M34" s="73">
+        <v>1</v>
+      </c>
+      <c r="N34" s="74"/>
+      <c r="O34" s="70">
+        <v>2</v>
+      </c>
+      <c r="P34" s="71"/>
+      <c r="Q34" s="71">
+        <v>2</v>
+      </c>
+      <c r="R34" s="72"/>
+      <c r="S34" s="55"/>
+      <c r="T34" s="58">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="U34" s="75">
+        <f t="shared" si="4"/>
+        <v>6458</v>
+      </c>
+      <c r="V34" s="75">
+        <f t="shared" si="5"/>
+        <v>269.08333333333331</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="27">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="B35" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="C35" s="70"/>
+      <c r="D35" s="70"/>
+      <c r="E35" s="70"/>
+      <c r="F35" s="70"/>
+      <c r="G35" s="70"/>
+      <c r="H35" s="70"/>
+      <c r="I35" s="70"/>
+      <c r="J35" s="71"/>
+      <c r="K35" s="72"/>
+      <c r="L35" s="55"/>
+      <c r="M35" s="73"/>
+      <c r="N35" s="74"/>
+      <c r="O35" s="70"/>
+      <c r="P35" s="71"/>
+      <c r="Q35" s="71"/>
+      <c r="R35" s="72"/>
+      <c r="S35" s="55"/>
+      <c r="T35" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U35" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V35" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A36" s="27">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+      <c r="B36" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="70"/>
+      <c r="D36" s="70"/>
+      <c r="E36" s="70"/>
+      <c r="F36" s="70"/>
+      <c r="G36" s="70"/>
+      <c r="H36" s="70"/>
+      <c r="I36" s="70"/>
+      <c r="J36" s="71"/>
+      <c r="K36" s="72"/>
+      <c r="L36" s="55"/>
+      <c r="M36" s="73"/>
+      <c r="N36" s="74"/>
+      <c r="O36" s="70"/>
+      <c r="P36" s="71"/>
+      <c r="Q36" s="71"/>
+      <c r="R36" s="72"/>
+      <c r="S36" s="55"/>
+      <c r="T36" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U36" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="27">
+        <f t="shared" si="1"/>
+        <v>34</v>
+      </c>
+      <c r="B37" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="C37" s="59">
+        <f>2376+1512+19+324</f>
+        <v>4231</v>
+      </c>
+      <c r="D37" s="59"/>
+      <c r="E37" s="59"/>
+      <c r="F37" s="59"/>
+      <c r="G37" s="59"/>
+      <c r="H37" s="59">
+        <v>3</v>
+      </c>
+      <c r="I37" s="59">
+        <v>2</v>
+      </c>
+      <c r="J37" s="60"/>
+      <c r="K37" s="61">
+        <f>2*6+2</f>
+        <v>14</v>
+      </c>
+      <c r="L37" s="62"/>
+      <c r="M37" s="63"/>
+      <c r="N37" s="64"/>
+      <c r="O37" s="65">
+        <v>1</v>
+      </c>
+      <c r="P37" s="66"/>
+      <c r="Q37" s="66">
+        <v>109</v>
+      </c>
+      <c r="R37" s="67"/>
+      <c r="S37" s="62"/>
+      <c r="T37" s="77">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="U37" s="77">
+        <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
+        <v>26065</v>
+      </c>
+      <c r="V37" s="77">
+        <f>U37/6</f>
+        <v>4344.166666666667</v>
+      </c>
+      <c r="W37" s="50"/>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A38" s="27">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="B38" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" s="70">
+        <v>2</v>
+      </c>
+      <c r="D38" s="70"/>
+      <c r="E38" s="70"/>
+      <c r="F38" s="70"/>
+      <c r="G38" s="70"/>
+      <c r="H38" s="70"/>
+      <c r="I38" s="70"/>
+      <c r="J38" s="71"/>
+      <c r="K38" s="72"/>
+      <c r="L38" s="55"/>
+      <c r="M38" s="73"/>
+      <c r="N38" s="74"/>
+      <c r="O38" s="70"/>
+      <c r="P38" s="71"/>
+      <c r="Q38" s="71">
+        <v>1</v>
+      </c>
+      <c r="R38" s="72"/>
+      <c r="S38" s="55"/>
+      <c r="T38" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U38" s="75">
+        <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
+        <v>72</v>
+      </c>
+      <c r="V38" s="75">
+        <f>U38/24</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A39" s="27">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="B39" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="C39" s="78"/>
+      <c r="D39" s="78"/>
+      <c r="E39" s="78"/>
+      <c r="F39" s="78"/>
+      <c r="G39" s="78"/>
+      <c r="H39" s="78"/>
+      <c r="I39" s="78"/>
+      <c r="J39" s="79"/>
+      <c r="K39" s="80"/>
+      <c r="L39" s="55"/>
+      <c r="M39" s="73"/>
+      <c r="N39" s="74"/>
+      <c r="O39" s="70"/>
+      <c r="P39" s="71"/>
+      <c r="Q39" s="71"/>
+      <c r="R39" s="72"/>
+      <c r="S39" s="95"/>
+      <c r="T39" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U39" s="75">
+        <f>C39*24+M39*24+O39*24+Q39*24+T39</f>
+        <v>0</v>
+      </c>
+      <c r="V39" s="75">
+        <f>U39/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="27">
+        <f t="shared" si="1"/>
+        <v>37</v>
+      </c>
+      <c r="B40" s="42" t="s">
+        <v>21</v>
+      </c>
+      <c r="C40" s="59">
+        <v>252</v>
+      </c>
+      <c r="D40" s="59"/>
+      <c r="E40" s="59"/>
+      <c r="F40" s="59"/>
+      <c r="G40" s="59"/>
+      <c r="H40" s="59"/>
+      <c r="I40" s="59"/>
+      <c r="J40" s="60"/>
+      <c r="K40" s="61">
+        <v>20</v>
+      </c>
+      <c r="L40" s="62"/>
+      <c r="M40" s="63">
+        <v>2</v>
+      </c>
+      <c r="N40" s="64"/>
+      <c r="O40" s="65"/>
+      <c r="P40" s="66"/>
+      <c r="Q40" s="66">
+        <v>1</v>
+      </c>
+      <c r="R40" s="67"/>
+      <c r="S40" s="62"/>
+      <c r="T40" s="77">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="U40" s="77">
+        <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
+        <v>6140</v>
+      </c>
+      <c r="V40" s="77">
+        <f>U40/24</f>
+        <v>255.83333333333334</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="27">
+        <f t="shared" si="1"/>
+        <v>38</v>
+      </c>
+      <c r="B41" s="43" t="s">
+        <v>22</v>
+      </c>
+      <c r="C41" s="82">
+        <f>672+73</f>
+        <v>745</v>
+      </c>
+      <c r="D41" s="82"/>
+      <c r="E41" s="82"/>
+      <c r="F41" s="82"/>
+      <c r="G41" s="82"/>
+      <c r="H41" s="82"/>
+      <c r="I41" s="82"/>
+      <c r="J41" s="83"/>
+      <c r="K41" s="84"/>
+      <c r="L41" s="85"/>
+      <c r="M41" s="86">
+        <v>1</v>
+      </c>
+      <c r="N41" s="87"/>
+      <c r="O41" s="82"/>
+      <c r="P41" s="83"/>
+      <c r="Q41" s="83">
+        <v>13</v>
+      </c>
+      <c r="R41" s="84"/>
+      <c r="S41" s="85"/>
+      <c r="T41" s="88">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U41" s="88">
+        <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
+        <v>9108</v>
+      </c>
+      <c r="V41" s="88">
+        <f>U41/12</f>
+        <v>759</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="27">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+      <c r="B42" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C42" s="70"/>
+      <c r="D42" s="70"/>
+      <c r="E42" s="70"/>
+      <c r="F42" s="70"/>
+      <c r="G42" s="70"/>
+      <c r="H42" s="70"/>
+      <c r="I42" s="70"/>
+      <c r="J42" s="71"/>
+      <c r="K42" s="72"/>
+      <c r="L42" s="55"/>
+      <c r="M42" s="73"/>
+      <c r="N42" s="74"/>
+      <c r="O42" s="70"/>
+      <c r="P42" s="71"/>
+      <c r="Q42" s="71"/>
+      <c r="R42" s="72"/>
+      <c r="S42" s="55"/>
+      <c r="T42" s="75"/>
+      <c r="U42" s="75"/>
+      <c r="V42" s="75"/>
+    </row>
+    <row r="43" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="27">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="B43" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="C43" s="65">
+        <f>13932+19656+4320</f>
+        <v>37908</v>
+      </c>
+      <c r="D43" s="65"/>
+      <c r="E43" s="65"/>
+      <c r="F43" s="65"/>
+      <c r="G43" s="65"/>
+      <c r="H43" s="65">
+        <v>1</v>
+      </c>
+      <c r="I43" s="65">
+        <v>12</v>
+      </c>
+      <c r="J43" s="66">
+        <f>11*6</f>
+        <v>66</v>
+      </c>
+      <c r="K43" s="67">
+        <f>95*6+1</f>
+        <v>571</v>
+      </c>
+      <c r="L43" s="62"/>
+      <c r="M43" s="63">
+        <v>27</v>
+      </c>
+      <c r="N43" s="64"/>
+      <c r="O43" s="65">
+        <v>417</v>
+      </c>
+      <c r="P43" s="66"/>
+      <c r="Q43" s="66">
+        <v>591</v>
+      </c>
+      <c r="R43" s="67"/>
+      <c r="S43" s="62"/>
+      <c r="T43" s="77">
+        <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
+        <v>650</v>
+      </c>
+      <c r="U43" s="77">
+        <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
+        <v>234308</v>
+      </c>
+      <c r="V43" s="77">
+        <f>U43/6</f>
+        <v>39051.333333333336</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="27">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+      <c r="B44" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="70"/>
+      <c r="D44" s="70"/>
+      <c r="E44" s="70"/>
+      <c r="F44" s="70"/>
+      <c r="G44" s="70"/>
+      <c r="H44" s="70"/>
+      <c r="I44" s="70"/>
+      <c r="J44" s="71"/>
+      <c r="K44" s="72"/>
+      <c r="L44" s="55"/>
+      <c r="M44" s="73"/>
+      <c r="N44" s="74"/>
+      <c r="O44" s="70"/>
+      <c r="P44" s="71"/>
+      <c r="Q44" s="71"/>
+      <c r="R44" s="72"/>
+      <c r="S44" s="55"/>
+      <c r="T44" s="75"/>
+      <c r="U44" s="75"/>
+      <c r="V44" s="75"/>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A45" s="27">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="B45" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="70">
+        <v>5</v>
+      </c>
+      <c r="D45" s="70"/>
+      <c r="E45" s="70"/>
+      <c r="F45" s="70"/>
+      <c r="G45" s="70"/>
+      <c r="H45" s="70"/>
+      <c r="I45" s="70"/>
+      <c r="J45" s="71"/>
+      <c r="K45" s="72"/>
+      <c r="L45" s="55"/>
+      <c r="M45" s="73"/>
+      <c r="N45" s="74"/>
+      <c r="O45" s="70"/>
+      <c r="P45" s="71"/>
+      <c r="Q45" s="71"/>
+      <c r="R45" s="72"/>
+      <c r="S45" s="55"/>
+      <c r="T45" s="75">
+        <f t="shared" ref="T45:T54" si="7">H45+I45+J45+K45+N45+P45+R45</f>
+        <v>0</v>
+      </c>
+      <c r="U45" s="75">
+        <f>C45*24+M45*24+O45*24+Q45*24+T45</f>
+        <v>120</v>
+      </c>
+      <c r="V45" s="75">
+        <f>U45/24</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A46" s="27">
+        <f t="shared" si="1"/>
+        <v>43</v>
+      </c>
+      <c r="B46" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="C46" s="70"/>
+      <c r="D46" s="70"/>
+      <c r="E46" s="70"/>
+      <c r="F46" s="70"/>
+      <c r="G46" s="70"/>
+      <c r="H46" s="70"/>
+      <c r="I46" s="70"/>
+      <c r="J46" s="71"/>
+      <c r="K46" s="72"/>
+      <c r="L46" s="55"/>
+      <c r="M46" s="73"/>
+      <c r="N46" s="74"/>
+      <c r="O46" s="70"/>
+      <c r="P46" s="71"/>
+      <c r="Q46" s="71"/>
+      <c r="R46" s="72"/>
+      <c r="S46" s="55"/>
+      <c r="T46" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U46" s="75">
+        <f t="shared" ref="U46:U50" si="8">C46*24+M46*24+O46*24+Q46*24+T46</f>
+        <v>0</v>
+      </c>
+      <c r="V46" s="75">
+        <f t="shared" ref="V46:V54" si="9">U46/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="27">
+        <f t="shared" si="1"/>
+        <v>44</v>
+      </c>
+      <c r="B47" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="C47" s="65">
+        <f>89+2540</f>
+        <v>2629</v>
+      </c>
+      <c r="D47" s="65"/>
+      <c r="E47" s="65"/>
+      <c r="F47" s="65"/>
+      <c r="G47" s="65"/>
+      <c r="H47" s="65">
+        <v>1</v>
+      </c>
+      <c r="I47" s="65"/>
+      <c r="J47" s="66"/>
+      <c r="K47" s="67">
+        <v>5</v>
+      </c>
+      <c r="L47" s="62"/>
+      <c r="M47" s="63">
+        <v>2</v>
+      </c>
+      <c r="N47" s="64"/>
+      <c r="O47" s="65">
+        <v>14</v>
+      </c>
+      <c r="P47" s="66">
+        <v>3</v>
+      </c>
+      <c r="Q47" s="66">
+        <v>5</v>
+      </c>
+      <c r="R47" s="67">
+        <v>3</v>
+      </c>
+      <c r="S47" s="62"/>
+      <c r="T47" s="77">
+        <f t="shared" si="7"/>
+        <v>12</v>
+      </c>
+      <c r="U47" s="77">
+        <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
+        <v>15912</v>
+      </c>
+      <c r="V47" s="77">
+        <f>U47/6</f>
+        <v>2652</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A48" s="27">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="B48" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C48" s="70"/>
+      <c r="D48" s="70"/>
+      <c r="E48" s="70"/>
+      <c r="F48" s="70"/>
+      <c r="G48" s="70"/>
+      <c r="H48" s="70">
+        <v>24</v>
+      </c>
+      <c r="I48" s="70"/>
+      <c r="J48" s="71"/>
+      <c r="K48" s="72"/>
+      <c r="L48" s="55"/>
+      <c r="M48" s="73"/>
+      <c r="N48" s="74"/>
+      <c r="O48" s="70"/>
+      <c r="P48" s="71"/>
+      <c r="Q48" s="71"/>
+      <c r="R48" s="72"/>
+      <c r="S48" s="55"/>
+      <c r="T48" s="75">
+        <f t="shared" si="7"/>
+        <v>24</v>
+      </c>
+      <c r="U48" s="75">
+        <f t="shared" si="8"/>
+        <v>24</v>
+      </c>
+      <c r="V48" s="75">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A49" s="27">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="B49" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C49" s="70"/>
+      <c r="D49" s="70"/>
+      <c r="E49" s="70"/>
+      <c r="F49" s="70"/>
+      <c r="G49" s="70"/>
+      <c r="H49" s="70"/>
+      <c r="I49" s="70"/>
+      <c r="J49" s="71"/>
+      <c r="K49" s="72"/>
+      <c r="L49" s="55"/>
+      <c r="M49" s="73"/>
+      <c r="N49" s="74"/>
+      <c r="O49" s="70"/>
+      <c r="P49" s="71"/>
+      <c r="Q49" s="71"/>
+      <c r="R49" s="72"/>
+      <c r="S49" s="55"/>
+      <c r="T49" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U49" s="75">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V49" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A50" s="27">
+        <f t="shared" si="1"/>
+        <v>47</v>
+      </c>
+      <c r="B50" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="C50" s="70"/>
+      <c r="D50" s="70"/>
+      <c r="E50" s="70"/>
+      <c r="F50" s="70"/>
+      <c r="G50" s="70"/>
+      <c r="H50" s="70"/>
+      <c r="I50" s="70"/>
+      <c r="J50" s="71"/>
+      <c r="K50" s="72"/>
+      <c r="L50" s="55"/>
+      <c r="M50" s="73"/>
+      <c r="N50" s="74"/>
+      <c r="O50" s="70"/>
+      <c r="P50" s="71"/>
+      <c r="Q50" s="71"/>
+      <c r="R50" s="72"/>
+      <c r="S50" s="55"/>
+      <c r="T50" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U50" s="75">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V50" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="27">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+      <c r="B51" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="C51" s="65">
+        <v>34</v>
+      </c>
+      <c r="D51" s="65"/>
+      <c r="E51" s="65"/>
+      <c r="F51" s="65"/>
+      <c r="G51" s="65"/>
+      <c r="H51" s="65"/>
+      <c r="I51" s="65"/>
+      <c r="J51" s="66"/>
+      <c r="K51" s="67"/>
+      <c r="L51" s="62"/>
+      <c r="M51" s="63"/>
+      <c r="N51" s="64"/>
+      <c r="O51" s="65"/>
+      <c r="P51" s="66"/>
+      <c r="Q51" s="66"/>
+      <c r="R51" s="67"/>
+      <c r="S51" s="62"/>
+      <c r="T51" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U51" s="77">
+        <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
+        <v>204</v>
+      </c>
+      <c r="V51" s="77">
+        <f>U51/6</f>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A52" s="27">
+        <f t="shared" si="1"/>
+        <v>49</v>
+      </c>
+      <c r="B52" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="C52" s="70"/>
+      <c r="D52" s="70"/>
+      <c r="E52" s="70"/>
+      <c r="F52" s="70"/>
+      <c r="G52" s="70"/>
+      <c r="H52" s="70"/>
+      <c r="I52" s="70"/>
+      <c r="J52" s="71"/>
+      <c r="K52" s="72"/>
+      <c r="L52" s="55"/>
+      <c r="M52" s="73"/>
+      <c r="N52" s="74"/>
+      <c r="O52" s="70"/>
+      <c r="P52" s="71"/>
+      <c r="Q52" s="71"/>
+      <c r="R52" s="72"/>
+      <c r="S52" s="55"/>
+      <c r="T52" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U52" s="75">
+        <f t="shared" ref="U52:U54" si="10">C52*24+M52*24+O52*24+Q52*24+T52</f>
+        <v>0</v>
+      </c>
+      <c r="V52" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A53" s="27">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="B53" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C53" s="70">
+        <v>7</v>
+      </c>
+      <c r="D53" s="70"/>
+      <c r="E53" s="70"/>
+      <c r="F53" s="70"/>
+      <c r="G53" s="70"/>
+      <c r="H53" s="70"/>
+      <c r="I53" s="70"/>
+      <c r="J53" s="71"/>
+      <c r="K53" s="72"/>
+      <c r="L53" s="55"/>
+      <c r="M53" s="73"/>
+      <c r="N53" s="74"/>
+      <c r="O53" s="70"/>
+      <c r="P53" s="71"/>
+      <c r="Q53" s="71"/>
+      <c r="R53" s="72"/>
+      <c r="S53" s="55"/>
+      <c r="T53" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U53" s="75">
+        <f t="shared" si="10"/>
+        <v>168</v>
+      </c>
+      <c r="V53" s="75">
+        <f t="shared" si="9"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A54" s="27">
+        <f t="shared" si="1"/>
+        <v>51</v>
+      </c>
+      <c r="B54" s="26"/>
+      <c r="C54" s="70"/>
+      <c r="D54" s="70"/>
+      <c r="E54" s="70"/>
+      <c r="F54" s="70"/>
+      <c r="G54" s="70"/>
+      <c r="H54" s="70"/>
+      <c r="I54" s="70"/>
+      <c r="J54" s="71"/>
+      <c r="K54" s="72"/>
+      <c r="L54" s="55"/>
+      <c r="M54" s="73"/>
+      <c r="N54" s="74"/>
+      <c r="O54" s="70"/>
+      <c r="P54" s="71"/>
+      <c r="Q54" s="71"/>
+      <c r="R54" s="72"/>
+      <c r="S54" s="55"/>
+      <c r="T54" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U54" s="75">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V54" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A55" s="27">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="B55" s="26"/>
+      <c r="C55" s="70"/>
+      <c r="D55" s="70"/>
+      <c r="E55" s="70"/>
+      <c r="F55" s="70"/>
+      <c r="G55" s="70"/>
+      <c r="H55" s="70"/>
+      <c r="I55" s="70"/>
+      <c r="J55" s="71"/>
+      <c r="K55" s="72"/>
+      <c r="L55" s="55"/>
+      <c r="M55" s="73"/>
+      <c r="N55" s="74"/>
+      <c r="O55" s="70"/>
+      <c r="P55" s="71"/>
+      <c r="Q55" s="71"/>
+      <c r="R55" s="72"/>
+      <c r="S55" s="55"/>
+      <c r="T55" s="75"/>
+      <c r="U55" s="75"/>
+      <c r="V55" s="75"/>
+    </row>
+    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A56" s="27">
+        <f t="shared" si="1"/>
+        <v>53</v>
+      </c>
+      <c r="B56" s="26"/>
+      <c r="C56" s="70"/>
+      <c r="D56" s="70"/>
+      <c r="E56" s="70"/>
+      <c r="F56" s="70"/>
+      <c r="G56" s="70"/>
+      <c r="H56" s="70"/>
+      <c r="I56" s="70"/>
+      <c r="J56" s="71"/>
+      <c r="K56" s="72"/>
+      <c r="L56" s="55"/>
+      <c r="M56" s="73"/>
+      <c r="N56" s="74"/>
+      <c r="O56" s="70"/>
+      <c r="P56" s="71"/>
+      <c r="Q56" s="71"/>
+      <c r="R56" s="72"/>
+      <c r="S56" s="55"/>
+      <c r="T56" s="75"/>
+      <c r="U56" s="75"/>
+      <c r="V56" s="75"/>
+    </row>
+    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A57" s="27">
+        <f t="shared" si="1"/>
+        <v>54</v>
+      </c>
+      <c r="B57" s="26"/>
+      <c r="C57" s="70"/>
+      <c r="D57" s="70"/>
+      <c r="E57" s="70"/>
+      <c r="F57" s="70"/>
+      <c r="G57" s="70"/>
+      <c r="H57" s="70"/>
+      <c r="I57" s="70"/>
+      <c r="J57" s="71"/>
+      <c r="K57" s="72"/>
+      <c r="L57" s="55"/>
+      <c r="M57" s="73"/>
+      <c r="N57" s="74"/>
+      <c r="O57" s="70"/>
+      <c r="P57" s="71"/>
+      <c r="Q57" s="71"/>
+      <c r="R57" s="72"/>
+      <c r="S57" s="55"/>
+      <c r="T57" s="75"/>
+      <c r="U57" s="75"/>
+      <c r="V57" s="75"/>
+    </row>
+    <row r="58" spans="1:22" s="15" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B58" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="C58" s="2">
+        <f>SUM(C7:C57)</f>
+        <v>49493</v>
+      </c>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2">
+        <f t="shared" ref="F58:K58" si="11">SUM(F7:F57)</f>
+        <v>0</v>
+      </c>
+      <c r="G58" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="H58" s="2">
+        <f t="shared" si="11"/>
+        <v>1188</v>
+      </c>
+      <c r="I58" s="6">
+        <f t="shared" si="11"/>
+        <v>44</v>
+      </c>
+      <c r="J58" s="6">
+        <f t="shared" si="11"/>
+        <v>66</v>
+      </c>
+      <c r="K58" s="6">
+        <f t="shared" si="11"/>
+        <v>619</v>
+      </c>
+      <c r="M58" s="5">
+        <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
+        <v>46</v>
+      </c>
+      <c r="N58" s="5">
+        <f t="shared" si="12"/>
+        <v>11</v>
+      </c>
+      <c r="O58" s="5">
+        <f t="shared" si="12"/>
+        <v>451</v>
+      </c>
+      <c r="P58" s="5">
+        <f t="shared" si="12"/>
+        <v>27</v>
+      </c>
+      <c r="Q58" s="5">
+        <f t="shared" si="12"/>
+        <v>759</v>
+      </c>
+      <c r="R58" s="5">
+        <f t="shared" si="12"/>
+        <v>3</v>
+      </c>
+      <c r="S58" s="55"/>
+      <c r="T58" s="4">
+        <f>SUM(T7:T57)</f>
+        <v>1958</v>
+      </c>
+      <c r="U58" s="90">
+        <f>SUM(U7:U57)</f>
+        <v>383402</v>
+      </c>
+      <c r="V58" s="4">
+        <f>SUM(V7:V57)</f>
+        <v>50915.708333333336</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="60" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="C60" s="114" t="s">
+        <v>41</v>
+      </c>
+      <c r="D60" s="115"/>
+      <c r="E60" s="115"/>
+      <c r="F60" s="115"/>
+      <c r="G60" s="115"/>
+      <c r="H60" s="115"/>
+      <c r="I60" s="115"/>
+      <c r="J60" s="115"/>
+      <c r="K60" s="116"/>
+      <c r="U60" s="24" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B61" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="C61" s="19"/>
+      <c r="D61" s="19"/>
+      <c r="E61" s="19"/>
+      <c r="F61" s="19"/>
+      <c r="G61" s="19"/>
+      <c r="H61" s="19"/>
+      <c r="I61" s="19"/>
+      <c r="J61" s="45"/>
+      <c r="K61" s="20"/>
+      <c r="U61" s="7"/>
+    </row>
+    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B62" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+      <c r="J62" s="44"/>
+      <c r="K62" s="21"/>
+      <c r="U62" s="3"/>
+    </row>
+    <row r="63" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B63" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C63" s="22"/>
+      <c r="D63" s="22"/>
+      <c r="E63" s="22"/>
+      <c r="F63" s="22"/>
+      <c r="G63" s="22"/>
+      <c r="H63" s="22"/>
+      <c r="I63" s="22"/>
+      <c r="J63" s="46"/>
+      <c r="K63" s="23"/>
+      <c r="U63" s="8"/>
+    </row>
+    <row r="64" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B65" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="C65" s="19"/>
+      <c r="D65" s="19"/>
+      <c r="E65" s="19"/>
+      <c r="F65" s="19"/>
+      <c r="G65" s="19"/>
+      <c r="H65" s="19"/>
+      <c r="I65" s="19"/>
+      <c r="J65" s="45"/>
+      <c r="K65" s="20"/>
+      <c r="U65" s="7"/>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B66" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C66" s="1"/>
+      <c r="D66" s="1"/>
+      <c r="E66" s="1"/>
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="J66" s="44"/>
+      <c r="K66" s="21"/>
+      <c r="U66" s="3"/>
+    </row>
+    <row r="67" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B67" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C67" s="22"/>
+      <c r="D67" s="22"/>
+      <c r="E67" s="22"/>
+      <c r="F67" s="22"/>
+      <c r="G67" s="22"/>
+      <c r="H67" s="22"/>
+      <c r="I67" s="22"/>
+      <c r="J67" s="46"/>
+      <c r="K67" s="23"/>
+      <c r="U67" s="8"/>
+    </row>
+    <row r="68" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B69" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="C69" s="19"/>
+      <c r="D69" s="19"/>
+      <c r="E69" s="19"/>
+      <c r="F69" s="19"/>
+      <c r="G69" s="19"/>
+      <c r="H69" s="19"/>
+      <c r="I69" s="19"/>
+      <c r="J69" s="45"/>
+      <c r="K69" s="20"/>
+      <c r="U69" s="7"/>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B70" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="J70" s="44"/>
+      <c r="K70" s="21"/>
+      <c r="U70" s="3"/>
+    </row>
+    <row r="71" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B71" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C71" s="22"/>
+      <c r="D71" s="22"/>
+      <c r="E71" s="22"/>
+      <c r="F71" s="22"/>
+      <c r="G71" s="22"/>
+      <c r="H71" s="22"/>
+      <c r="I71" s="22"/>
+      <c r="J71" s="46"/>
+      <c r="K71" s="23"/>
+      <c r="U71" s="8"/>
+    </row>
+    <row r="72" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B73" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="C73" s="19"/>
+      <c r="D73" s="19"/>
+      <c r="E73" s="19"/>
+      <c r="F73" s="19"/>
+      <c r="G73" s="19"/>
+      <c r="H73" s="19"/>
+      <c r="I73" s="19"/>
+      <c r="J73" s="45"/>
+      <c r="K73" s="20"/>
+      <c r="U73" s="7"/>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B74" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C74" s="1"/>
+      <c r="D74" s="1"/>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1"/>
+      <c r="J74" s="44"/>
+      <c r="K74" s="21"/>
+      <c r="U74" s="3"/>
+    </row>
+    <row r="75" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B75" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C75" s="22"/>
+      <c r="D75" s="22"/>
+      <c r="E75" s="22"/>
+      <c r="F75" s="22"/>
+      <c r="G75" s="22"/>
+      <c r="H75" s="22"/>
+      <c r="I75" s="22"/>
+      <c r="J75" s="46"/>
+      <c r="K75" s="23"/>
+      <c r="U75" s="8"/>
+    </row>
+    <row r="76" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B77" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="C77" s="19"/>
+      <c r="D77" s="19"/>
+      <c r="E77" s="19"/>
+      <c r="F77" s="19"/>
+      <c r="G77" s="19"/>
+      <c r="H77" s="19"/>
+      <c r="I77" s="19"/>
+      <c r="J77" s="45"/>
+      <c r="K77" s="20"/>
+      <c r="U77" s="7"/>
+    </row>
+    <row r="78" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B78" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C78" s="1"/>
+      <c r="D78" s="1"/>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+      <c r="J78" s="44"/>
+      <c r="K78" s="21"/>
+      <c r="U78" s="3"/>
+    </row>
+    <row r="79" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B79" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C79" s="22"/>
+      <c r="D79" s="22"/>
+      <c r="E79" s="22"/>
+      <c r="F79" s="22"/>
+      <c r="G79" s="22"/>
+      <c r="H79" s="22"/>
+      <c r="I79" s="22"/>
+      <c r="J79" s="46"/>
+      <c r="K79" s="23"/>
+      <c r="U79" s="8"/>
+    </row>
+    <row r="80" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="81" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B81" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="C81" s="17"/>
+      <c r="D81" s="17"/>
+      <c r="E81" s="17"/>
+      <c r="F81" s="17"/>
+      <c r="G81" s="17"/>
+      <c r="H81" s="17"/>
+      <c r="I81" s="17"/>
+      <c r="J81" s="47"/>
+      <c r="K81" s="18"/>
+      <c r="U81" s="16"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
     <mergeCell ref="V4:V5"/>
     <mergeCell ref="J5:K5"/>
+    <mergeCell ref="C60:K60"/>
+    <mergeCell ref="I1:U1"/>
+    <mergeCell ref="C4:K4"/>
+    <mergeCell ref="T4:T5"/>
+    <mergeCell ref="U4:U5"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -48872,21 +52009,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="116" t="s">
+      <c r="I1" s="117" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="116"/>
-      <c r="K1" s="116"/>
-      <c r="L1" s="116"/>
-      <c r="M1" s="116"/>
-      <c r="N1" s="116"/>
-      <c r="O1" s="116"/>
-      <c r="P1" s="116"/>
-      <c r="Q1" s="116"/>
-      <c r="R1" s="116"/>
-      <c r="S1" s="116"/>
-      <c r="T1" s="116"/>
-      <c r="U1" s="116"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -48898,17 +52035,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="117" t="s">
+      <c r="C4" s="118" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="117"/>
-      <c r="E4" s="117"/>
-      <c r="F4" s="117"/>
-      <c r="G4" s="117"/>
-      <c r="H4" s="117"/>
-      <c r="I4" s="117"/>
-      <c r="J4" s="118"/>
-      <c r="K4" s="119"/>
+      <c r="D4" s="118"/>
+      <c r="E4" s="118"/>
+      <c r="F4" s="118"/>
+      <c r="G4" s="118"/>
+      <c r="H4" s="118"/>
+      <c r="I4" s="118"/>
+      <c r="J4" s="119"/>
+      <c r="K4" s="120"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -48928,13 +52065,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="120" t="s">
+      <c r="T4" s="121" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="126" t="s">
+      <c r="U4" s="127" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="109" t="s">
+      <c r="V4" s="110" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -48974,10 +52111,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="124" t="s">
+      <c r="J5" s="125" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="125"/>
+      <c r="K5" s="126"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -48985,9 +52122,9 @@
       <c r="Q5" s="97"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="121"/>
-      <c r="U5" s="127"/>
-      <c r="V5" s="110"/>
+      <c r="T5" s="122"/>
+      <c r="U5" s="128"/>
+      <c r="V5" s="111"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -51687,17 +54824,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="113" t="s">
+      <c r="C60" s="114" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="114"/>
-      <c r="E60" s="114"/>
-      <c r="F60" s="114"/>
-      <c r="G60" s="114"/>
-      <c r="H60" s="114"/>
-      <c r="I60" s="114"/>
-      <c r="J60" s="114"/>
-      <c r="K60" s="115"/>
+      <c r="D60" s="115"/>
+      <c r="E60" s="115"/>
+      <c r="F60" s="115"/>
+      <c r="G60" s="115"/>
+      <c r="H60" s="115"/>
+      <c r="I60" s="115"/>
+      <c r="J60" s="115"/>
+      <c r="K60" s="116"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -52006,21 +55143,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="116" t="s">
+      <c r="I1" s="117" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="116"/>
-      <c r="K1" s="116"/>
-      <c r="L1" s="116"/>
-      <c r="M1" s="116"/>
-      <c r="N1" s="116"/>
-      <c r="O1" s="116"/>
-      <c r="P1" s="116"/>
-      <c r="Q1" s="116"/>
-      <c r="R1" s="116"/>
-      <c r="S1" s="116"/>
-      <c r="T1" s="116"/>
-      <c r="U1" s="116"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -52032,17 +55169,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="117" t="s">
+      <c r="C4" s="118" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="117"/>
-      <c r="E4" s="117"/>
-      <c r="F4" s="117"/>
-      <c r="G4" s="117"/>
-      <c r="H4" s="117"/>
-      <c r="I4" s="117"/>
-      <c r="J4" s="118"/>
-      <c r="K4" s="119"/>
+      <c r="D4" s="118"/>
+      <c r="E4" s="118"/>
+      <c r="F4" s="118"/>
+      <c r="G4" s="118"/>
+      <c r="H4" s="118"/>
+      <c r="I4" s="118"/>
+      <c r="J4" s="119"/>
+      <c r="K4" s="120"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -52062,13 +55199,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="120" t="s">
+      <c r="T4" s="121" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="126" t="s">
+      <c r="U4" s="127" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="109" t="s">
+      <c r="V4" s="110" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -52108,10 +55245,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="124" t="s">
+      <c r="J5" s="125" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="125"/>
+      <c r="K5" s="126"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -52119,9 +55256,9 @@
       <c r="Q5" s="97"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="121"/>
-      <c r="U5" s="127"/>
-      <c r="V5" s="110"/>
+      <c r="T5" s="122"/>
+      <c r="U5" s="128"/>
+      <c r="V5" s="111"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -54821,17 +57958,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="113" t="s">
+      <c r="C60" s="114" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="114"/>
-      <c r="E60" s="114"/>
-      <c r="F60" s="114"/>
-      <c r="G60" s="114"/>
-      <c r="H60" s="114"/>
-      <c r="I60" s="114"/>
-      <c r="J60" s="114"/>
-      <c r="K60" s="115"/>
+      <c r="D60" s="115"/>
+      <c r="E60" s="115"/>
+      <c r="F60" s="115"/>
+      <c r="G60" s="115"/>
+      <c r="H60" s="115"/>
+      <c r="I60" s="115"/>
+      <c r="J60" s="115"/>
+      <c r="K60" s="116"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -55140,21 +58277,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="116" t="s">
+      <c r="I1" s="117" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="116"/>
-      <c r="K1" s="116"/>
-      <c r="L1" s="116"/>
-      <c r="M1" s="116"/>
-      <c r="N1" s="116"/>
-      <c r="O1" s="116"/>
-      <c r="P1" s="116"/>
-      <c r="Q1" s="116"/>
-      <c r="R1" s="116"/>
-      <c r="S1" s="116"/>
-      <c r="T1" s="116"/>
-      <c r="U1" s="116"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -55166,17 +58303,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="117" t="s">
+      <c r="C4" s="118" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="117"/>
-      <c r="E4" s="117"/>
-      <c r="F4" s="117"/>
-      <c r="G4" s="117"/>
-      <c r="H4" s="117"/>
-      <c r="I4" s="117"/>
-      <c r="J4" s="118"/>
-      <c r="K4" s="119"/>
+      <c r="D4" s="118"/>
+      <c r="E4" s="118"/>
+      <c r="F4" s="118"/>
+      <c r="G4" s="118"/>
+      <c r="H4" s="118"/>
+      <c r="I4" s="118"/>
+      <c r="J4" s="119"/>
+      <c r="K4" s="120"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -55196,13 +58333,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="120" t="s">
+      <c r="T4" s="121" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="126" t="s">
+      <c r="U4" s="127" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="109" t="s">
+      <c r="V4" s="110" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -55242,10 +58379,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="124" t="s">
+      <c r="J5" s="125" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="125"/>
+      <c r="K5" s="126"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -55253,9 +58390,9 @@
       <c r="Q5" s="97"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="121"/>
-      <c r="U5" s="127"/>
-      <c r="V5" s="110"/>
+      <c r="T5" s="122"/>
+      <c r="U5" s="128"/>
+      <c r="V5" s="111"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -57945,17 +61082,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="113" t="s">
+      <c r="C60" s="114" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="114"/>
-      <c r="E60" s="114"/>
-      <c r="F60" s="114"/>
-      <c r="G60" s="114"/>
-      <c r="H60" s="114"/>
-      <c r="I60" s="114"/>
-      <c r="J60" s="114"/>
-      <c r="K60" s="115"/>
+      <c r="D60" s="115"/>
+      <c r="E60" s="115"/>
+      <c r="F60" s="115"/>
+      <c r="G60" s="115"/>
+      <c r="H60" s="115"/>
+      <c r="I60" s="115"/>
+      <c r="J60" s="115"/>
+      <c r="K60" s="116"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -58264,21 +61401,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="116" t="s">
+      <c r="I1" s="117" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="116"/>
-      <c r="K1" s="116"/>
-      <c r="L1" s="116"/>
-      <c r="M1" s="116"/>
-      <c r="N1" s="116"/>
-      <c r="O1" s="116"/>
-      <c r="P1" s="116"/>
-      <c r="Q1" s="116"/>
-      <c r="R1" s="116"/>
-      <c r="S1" s="116"/>
-      <c r="T1" s="116"/>
-      <c r="U1" s="116"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -58290,17 +61427,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="117" t="s">
+      <c r="C4" s="118" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="117"/>
-      <c r="E4" s="117"/>
-      <c r="F4" s="117"/>
-      <c r="G4" s="117"/>
-      <c r="H4" s="117"/>
-      <c r="I4" s="117"/>
-      <c r="J4" s="118"/>
-      <c r="K4" s="119"/>
+      <c r="D4" s="118"/>
+      <c r="E4" s="118"/>
+      <c r="F4" s="118"/>
+      <c r="G4" s="118"/>
+      <c r="H4" s="118"/>
+      <c r="I4" s="118"/>
+      <c r="J4" s="119"/>
+      <c r="K4" s="120"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -58320,13 +61457,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="120" t="s">
+      <c r="T4" s="121" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="126" t="s">
+      <c r="U4" s="127" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="109" t="s">
+      <c r="V4" s="110" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -58366,10 +61503,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="124" t="s">
+      <c r="J5" s="125" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="125"/>
+      <c r="K5" s="126"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -58377,9 +61514,9 @@
       <c r="Q5" s="98"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="121"/>
-      <c r="U5" s="127"/>
-      <c r="V5" s="110"/>
+      <c r="T5" s="122"/>
+      <c r="U5" s="128"/>
+      <c r="V5" s="111"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -61094,17 +64231,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="113" t="s">
+      <c r="C60" s="114" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="114"/>
-      <c r="E60" s="114"/>
-      <c r="F60" s="114"/>
-      <c r="G60" s="114"/>
-      <c r="H60" s="114"/>
-      <c r="I60" s="114"/>
-      <c r="J60" s="114"/>
-      <c r="K60" s="115"/>
+      <c r="D60" s="115"/>
+      <c r="E60" s="115"/>
+      <c r="F60" s="115"/>
+      <c r="G60" s="115"/>
+      <c r="H60" s="115"/>
+      <c r="I60" s="115"/>
+      <c r="J60" s="115"/>
+      <c r="K60" s="116"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -61413,21 +64550,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="116" t="s">
+      <c r="I1" s="117" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="116"/>
-      <c r="K1" s="116"/>
-      <c r="L1" s="116"/>
-      <c r="M1" s="116"/>
-      <c r="N1" s="116"/>
-      <c r="O1" s="116"/>
-      <c r="P1" s="116"/>
-      <c r="Q1" s="116"/>
-      <c r="R1" s="116"/>
-      <c r="S1" s="116"/>
-      <c r="T1" s="116"/>
-      <c r="U1" s="116"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -61439,17 +64576,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="117" t="s">
+      <c r="C4" s="118" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="117"/>
-      <c r="E4" s="117"/>
-      <c r="F4" s="117"/>
-      <c r="G4" s="117"/>
-      <c r="H4" s="117"/>
-      <c r="I4" s="117"/>
-      <c r="J4" s="118"/>
-      <c r="K4" s="119"/>
+      <c r="D4" s="118"/>
+      <c r="E4" s="118"/>
+      <c r="F4" s="118"/>
+      <c r="G4" s="118"/>
+      <c r="H4" s="118"/>
+      <c r="I4" s="118"/>
+      <c r="J4" s="119"/>
+      <c r="K4" s="120"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -61469,13 +64606,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="120" t="s">
+      <c r="T4" s="121" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="126" t="s">
+      <c r="U4" s="127" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="109" t="s">
+      <c r="V4" s="110" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -61515,10 +64652,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="124" t="s">
+      <c r="J5" s="125" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="125"/>
+      <c r="K5" s="126"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -61526,9 +64663,9 @@
       <c r="Q5" s="98"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="121"/>
-      <c r="U5" s="127"/>
-      <c r="V5" s="110"/>
+      <c r="T5" s="122"/>
+      <c r="U5" s="128"/>
+      <c r="V5" s="111"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -64233,17 +67370,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="113" t="s">
+      <c r="C60" s="114" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="114"/>
-      <c r="E60" s="114"/>
-      <c r="F60" s="114"/>
-      <c r="G60" s="114"/>
-      <c r="H60" s="114"/>
-      <c r="I60" s="114"/>
-      <c r="J60" s="114"/>
-      <c r="K60" s="115"/>
+      <c r="D60" s="115"/>
+      <c r="E60" s="115"/>
+      <c r="F60" s="115"/>
+      <c r="G60" s="115"/>
+      <c r="H60" s="115"/>
+      <c r="I60" s="115"/>
+      <c r="J60" s="115"/>
+      <c r="K60" s="116"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -64552,21 +67689,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="116" t="s">
+      <c r="I1" s="117" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="116"/>
-      <c r="K1" s="116"/>
-      <c r="L1" s="116"/>
-      <c r="M1" s="116"/>
-      <c r="N1" s="116"/>
-      <c r="O1" s="116"/>
-      <c r="P1" s="116"/>
-      <c r="Q1" s="116"/>
-      <c r="R1" s="116"/>
-      <c r="S1" s="116"/>
-      <c r="T1" s="116"/>
-      <c r="U1" s="116"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -64578,17 +67715,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="117" t="s">
+      <c r="C4" s="118" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="117"/>
-      <c r="E4" s="117"/>
-      <c r="F4" s="117"/>
-      <c r="G4" s="117"/>
-      <c r="H4" s="117"/>
-      <c r="I4" s="117"/>
-      <c r="J4" s="118"/>
-      <c r="K4" s="119"/>
+      <c r="D4" s="118"/>
+      <c r="E4" s="118"/>
+      <c r="F4" s="118"/>
+      <c r="G4" s="118"/>
+      <c r="H4" s="118"/>
+      <c r="I4" s="118"/>
+      <c r="J4" s="119"/>
+      <c r="K4" s="120"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -64608,13 +67745,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="120" t="s">
+      <c r="T4" s="121" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="126" t="s">
+      <c r="U4" s="127" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="109" t="s">
+      <c r="V4" s="110" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -64654,10 +67791,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="124" t="s">
+      <c r="J5" s="125" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="125"/>
+      <c r="K5" s="126"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -64665,9 +67802,9 @@
       <c r="Q5" s="98"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="121"/>
-      <c r="U5" s="127"/>
-      <c r="V5" s="110"/>
+      <c r="T5" s="122"/>
+      <c r="U5" s="128"/>
+      <c r="V5" s="111"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -67369,17 +70506,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="113" t="s">
+      <c r="C60" s="114" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="114"/>
-      <c r="E60" s="114"/>
-      <c r="F60" s="114"/>
-      <c r="G60" s="114"/>
-      <c r="H60" s="114"/>
-      <c r="I60" s="114"/>
-      <c r="J60" s="114"/>
-      <c r="K60" s="115"/>
+      <c r="D60" s="115"/>
+      <c r="E60" s="115"/>
+      <c r="F60" s="115"/>
+      <c r="G60" s="115"/>
+      <c r="H60" s="115"/>
+      <c r="I60" s="115"/>
+      <c r="J60" s="115"/>
+      <c r="K60" s="116"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -67688,21 +70825,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="116" t="s">
+      <c r="I1" s="117" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="116"/>
-      <c r="K1" s="116"/>
-      <c r="L1" s="116"/>
-      <c r="M1" s="116"/>
-      <c r="N1" s="116"/>
-      <c r="O1" s="116"/>
-      <c r="P1" s="116"/>
-      <c r="Q1" s="116"/>
-      <c r="R1" s="116"/>
-      <c r="S1" s="116"/>
-      <c r="T1" s="116"/>
-      <c r="U1" s="116"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -67714,17 +70851,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="117" t="s">
+      <c r="C4" s="118" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="117"/>
-      <c r="E4" s="117"/>
-      <c r="F4" s="117"/>
-      <c r="G4" s="117"/>
-      <c r="H4" s="117"/>
-      <c r="I4" s="117"/>
-      <c r="J4" s="118"/>
-      <c r="K4" s="119"/>
+      <c r="D4" s="118"/>
+      <c r="E4" s="118"/>
+      <c r="F4" s="118"/>
+      <c r="G4" s="118"/>
+      <c r="H4" s="118"/>
+      <c r="I4" s="118"/>
+      <c r="J4" s="119"/>
+      <c r="K4" s="120"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -67744,13 +70881,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="120" t="s">
+      <c r="T4" s="121" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="126" t="s">
+      <c r="U4" s="127" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="109" t="s">
+      <c r="V4" s="110" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -67790,10 +70927,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="124" t="s">
+      <c r="J5" s="125" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="125"/>
+      <c r="K5" s="126"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -67801,9 +70938,9 @@
       <c r="Q5" s="98"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="121"/>
-      <c r="U5" s="127"/>
-      <c r="V5" s="110"/>
+      <c r="T5" s="122"/>
+      <c r="U5" s="128"/>
+      <c r="V5" s="111"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -70515,17 +73652,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="113" t="s">
+      <c r="C60" s="114" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="114"/>
-      <c r="E60" s="114"/>
-      <c r="F60" s="114"/>
-      <c r="G60" s="114"/>
-      <c r="H60" s="114"/>
-      <c r="I60" s="114"/>
-      <c r="J60" s="114"/>
-      <c r="K60" s="115"/>
+      <c r="D60" s="115"/>
+      <c r="E60" s="115"/>
+      <c r="F60" s="115"/>
+      <c r="G60" s="115"/>
+      <c r="H60" s="115"/>
+      <c r="I60" s="115"/>
+      <c r="J60" s="115"/>
+      <c r="K60" s="116"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
